--- a/testrail-import/report-suite-v1-testrail-import.xlsx
+++ b/testrail-import/report-suite-v1-testrail-import.xlsx
@@ -17587,12 +17587,13 @@
       <c r="G358" s="2" t="inlineStr">
         <is>
           <t>1. Four tabs are shown, labeled in this order: "Approved - partially completed", "Approved - not started", "Completed", and "Estimates".
-2. The "Approved - partially completed" tab is selected by default on load.</t>
+2. The "Approved - partially completed" tab is selected by default on load.
+3. There is NO on-screen status filter — the four tabs take the place of a status filter (the tab a job lands in is derived from its status and whether any work has started).</t>
         </is>
       </c>
       <c r="H358" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 1 S1-R2; S1-R3</t>
+          <t>specs/wip-work-in-progress.md Story 1 S1-R2; S1-R3; §3 Key Decisions (no on-screen status filter)</t>
         </is>
       </c>
       <c r="I358" s="2" t="inlineStr"/>
@@ -19191,7 +19192,7 @@
       </c>
       <c r="G391" s="2" t="inlineStr">
         <is>
-          <t>1. Money and numeric columns sort by their underlying numeric value (so $1,100.00 sorts above $900.00 ascending-wise, not alphabetically).
+          <t>1. Money and numeric columns sort by their underlying numeric value (so $1,100.00 is treated as more than $900.00, not compared as text).
 2. Days Open sorts by its day count.
 3. Status sorts by its displayed label.
 4. The Asset column sorts by unit number.

--- a/testrail-import/report-suite-v1-testrail-import.xlsx
+++ b/testrail-import/report-suite-v1-testrail-import.xlsx
@@ -8047,7 +8047,7 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Cancel, X and Escape dismiss the dialog without deactivating; clicking outside does not dismiss it</t>
+          <t>Cancel and X dismiss the Deactivate dialog; Escape and clicking outside do not</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -8072,21 +8072,25 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>1. Click the "Cancel" button; re-open and click the "X" close icon; re-open and press Escape.
-2. After each dismissal, check the staff member's active status.
-3. Re-open and click outside the dialog.</t>
+          <t>1. Click the "Cancel" button and watch the dialog; then re-open it.
+2. Click the "X" close icon and watch the dialog; then re-open it.
+3. Press the "Esc" key on the keyboard and watch the dialog.
+4. Re-open the dialog and click outside it (on the greyed-out background).
+5. After each action, check the staff member's active status.</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>1. The dialog has a "Cancel" button (red outline) and an "X" close icon; it dismisses on Cancel, X, or Escape.
-2. Any dismissal leaves the staff member's active status unchanged.
-3. Clicking outside the dialog does NOT dismiss it.</t>
+          <t>1. The dialog has a "Cancel" button (red outline) and an "X" close icon.
+2. Clicking "Cancel" closes the dialog; clicking the "X" icon closes the dialog.
+3. Pressing the "Esc" key does NOT close the dialog - it stays open (the app's general rule is that pop-ups do not close with the Esc key).
+4. Clicking outside the dialog does NOT close it.
+5. When the dialog closes via Cancel or X, the staff member's active status is unchanged - no deactivation happens.</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 13 S13-R8</t>
+          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R8)</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr"/>
@@ -8095,7 +8099,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>A valid submit shows the in-flight loading state with dismissals locked, then applies the change with assignments untouched</t>
+          <t>Valid submit locks the dialog, then deactivates keeping assignments</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -8126,7 +8130,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>1. The "Deactivate" button enters the standard in-flight loading state (non-interactive, in-progress indicator); the dialog stays open and Cancel/X/Escape are all non-interactive during the request.
+          <t>1. The "Deactivate" button enters the standard in-flight loading state (non-interactive, in-progress indicator); the dialog stays open and the Cancel and X controls are non-interactive during the request (pressing the "Esc" key never closes the dialog at any time).
 2. On success the dialog closes and the change applies.
 3. Customer assignments are NOT modified — every customer stays assigned to this rep; denormalized rep names and past invoice snapshots are preserved.
 4. Deactivation never forces reassignment, blocks on assignments, or auto-reassigns.</t>
@@ -8134,7 +8138,7 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 13 S13-R9; S13-R10; S13-E1</t>
+          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R9; S13-R10; S13-E1)</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr"/>

--- a/testrail-import/report-suite-v1-testrail-import.xlsx
+++ b/testrail-import/report-suite-v1-testrail-import.xlsx
@@ -16522,7 +16522,7 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>Asset cell shows a bold serial number over a muted VIN; VIN is also a column</t>
+          <t>Asset cell identifies the asset by VIN, falling back to Unit #, then plate</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
@@ -16543,26 +16543,28 @@
       <c r="E333" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The report shows work orders including: one whose asset has both a serial number and a vehicle identification number, one with no serial number, and one with no vehicle identification number.</t>
+2. The report shows work orders including: one whose asset has a VIN recorded, one with no VIN but a Unit # recorded, and one with no VIN or Unit # but a plate recorded.</t>
         </is>
       </c>
       <c r="F333" s="2" t="inlineStr">
         <is>
-          <t>1. Read the Asset cell of a row whose asset has both values.
-2. Read the Asset cell of the row with no serial number, then the one with no vehicle identification number.
+          <t>1. Read the Asset cell of the row whose asset has a VIN.
+2. Read the Asset cell of the row with no VIN, then the one with no VIN or Unit #.
 3. Open the column-selection control, turn on the VIN column, and read it.</t>
         </is>
       </c>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t>1. The Asset cell is two lines: the asset's SERIAL NUMBER on the first line in bold, and the vehicle identification number on the second line in a smaller, muted style.
-2. When the asset has no serial number, the first line shows a placeholder (its exact text is confirmed in the build); when it has no vehicle identification number, the second line shows "— no VIN —".
-3. The VIN column (off by default) shows the vehicle identification number on its own line as a separate, sortable column.</t>
+          <t>1. The Asset cell identifies the asset by its VIN.
+2. When the asset has no VIN, the cell shows its Unit # instead; when it has no VIN or Unit #, it shows its plate instead.
+3. Note what the cell's second line shows now that the VIN is the main identifier (the older layout put the VIN on a muted second line) - the exact rendering is confirmed in the build; record what you see.
+4. The VIN column (off by default) shows the VIN on its own line as a separate, sortable column.
+5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.</t>
         </is>
       </c>
       <c r="H333" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R7; S4-R8; S4-R10 — identifier OVERRIDDEN to serial number by kickoff video P24 29:54-30:46, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R7; S4-R8; S4-R10 - identifier RE-RULED to VIN, falling back to Unit #, then plate, by Chris Ward answer A 2026-07-29 (chris-update-2026-07-29/wip-identifier-answer-2026-07-29.md; NEWEST source, last-update-wins), superseding the kickoff video's serial-number ruling P24 AND the spec's unit-number rule)</t>
         </is>
       </c>
       <c r="I333" s="2" t="inlineStr"/>
@@ -17262,7 +17264,7 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>Columns sort by underlying values; Asset sorts by serial number</t>
+          <t>Columns sort by underlying values; Asset sorts by the identifier shown</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
@@ -17283,7 +17285,7 @@
       <c r="E348" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. A tab shows several work orders with a spread of money values (including values over $1,000), differing statuses, and differing serial numbers.</t>
+2. A tab shows several work orders with a spread of money values (including values over $1,000), differing statuses, and differing asset identifiers (VIN, or Unit # / plate where the VIN is missing).</t>
         </is>
       </c>
       <c r="F348" s="2" t="inlineStr">
@@ -17291,7 +17293,7 @@
           <t>1. Sort by a money column (for example Total) and check the order of values like $900.00 vs $1,100.00.
 2. Sort by Days Open and check the order of the day counts.
 3. Sort by Status and check the order against the displayed labels.
-4. Sort by Asset and check the order against the serial numbers.
+4. Sort by Asset and check the order against the identifiers shown in the Asset cells.
 5. Sort by WO #, Customer, and Advisor and check they order as text.</t>
         </is>
       </c>
@@ -17300,13 +17302,13 @@
           <t>1. Money and numeric columns sort by their underlying numeric value (so $1,100.00 is treated as more than $900.00, not compared as text).
 2. Days Open sorts by its day count.
 3. Status sorts by its displayed label.
-4. The Asset column sorts by the serial number.
+4. The Asset column sorts by the identifier it shows - the VIN, falling back to Unit #, then plate.
 5. WO #, Customer, Asset, VIN, Location, and Advisor sort as text.</t>
         </is>
       </c>
       <c r="H348" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R27; S4-R9 — Asset sort key OVERRIDDEN to serial number by kickoff video P24 29:54-30:46, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
+          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R27; S4-R9 - Asset sort key RE-RULED to the VIN chain (VIN, then Unit #, then plate) by Chris Ward answer A 2026-07-29 (chris-update-2026-07-29/wip-identifier-answer-2026-07-29.md; last-update-wins), superseding the video P24 serial ruling AND the spec's 'sorts by unit number')</t>
         </is>
       </c>
       <c r="I348" s="2" t="inlineStr"/>
@@ -17856,7 +17858,7 @@
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
         <is>
-          <t>Asset filter type-ahead matches serial number or VIN, "All assets" when empty</t>
+          <t>Asset filter matches VIN, Unit #, or plate; "All assets" when empty</t>
         </is>
       </c>
       <c r="B360" s="2" t="inlineStr">
@@ -17877,28 +17879,29 @@
       <c r="E360" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The report shows jobs for at least two assets whose serial numbers and vehicle identification numbers you know.</t>
+2. The report shows jobs for at least two assets whose VINs (and Unit #s or plates) you know.</t>
         </is>
       </c>
       <c r="F360" s="2" t="inlineStr">
         <is>
           <t>1. Read the Asset filter's label before selecting anything.
 2. Open the filter and read how each option is presented.
-3. Type part of a serial number and check the matching options; clear and type part of a vehicle identification number instead.
+3. Type part of a VIN and check the matching options; clear and type part of a Unit # instead.
 4. Select one or more assets and watch the rows; then use the "Clear" action.</t>
         </is>
       </c>
       <c r="G360" s="2" t="inlineStr">
         <is>
           <t>1. With no asset selected, the filter reads "All assets" and every job is shown.
-2. Each option shows the serial number and the vehicle identification number.
-3. The typed text matches against EITHER the serial number OR the vehicle identification number.
-4. Selecting assets narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one asset is selected and returns the filter to "All assets".</t>
+2. Each option identifies the asset by its VIN, falling back to Unit #, then plate (the exact option text is confirmed in the build).
+3. The typed text matches against the asset's identifier - the VIN, and the Unit # where the asset has one (the exact fields matched are confirmed in the build).
+4. Selecting assets narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one asset is selected and returns the filter to "All assets".
+5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.</t>
         </is>
       </c>
       <c r="H360" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R4; S7-R5 — option text + match fields OVERRIDDEN from unit number to serial number by kickoff video P24 29:54-30:46, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
+          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R4; S7-R5 - option text + type-ahead match fields RE-RULED to the VIN chain (VIN, then Unit #, then plate) by Chris Ward answer A 2026-07-29 (chris-update-2026-07-29/wip-identifier-answer-2026-07-29.md; last-update-wins), superseding the video P24 serial ruling; the spec's original unit-number+VIN matching partially survives via the chain)</t>
         </is>
       </c>
       <c r="I360" s="2" t="inlineStr"/>
@@ -18677,12 +18680,12 @@
           <t>1. On screen the headers read "Asset" and "Location".
 2. In BOTH the PDF and the CSV, the same two columns are headed "Unit" and "Branch".
 3. This on-screen-vs-export label difference is the EXPECTED, documented v1 behavior.
-4. Note: the on-screen Asset cell now identifies the asset by its serial number; whether the export header text changes from "Unit" is confirmed in the build — record what it shows, do not file a bug either way.</t>
+4. Note: the on-screen Asset cell now identifies the asset by its VIN (falling back to Unit #, then plate); whether the export header text changes from "Unit" is confirmed in the build - record what it shows, do not file a bug either way.</t>
         </is>
       </c>
       <c r="H376" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-E1; §2 Known Limitations (v1) — asset identifier OVERRIDDEN to serial number by kickoff video P24, user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
+          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-E1; §2 Known Limitations (v1) - asset identifier RE-RULED to the VIN chain (VIN, then Unit #, then plate) by Chris Ward answer A 2026-07-29 (chris-update-2026-07-29/wip-identifier-answer-2026-07-29.md; last-update-wins), superseding the video P24 serial ruling; export header text at export unpinned)</t>
         </is>
       </c>
       <c r="I376" s="2" t="inlineStr"/>

--- a/testrail-import/report-suite-v1-testrail-import.xlsx
+++ b/testrail-import/report-suite-v1-testrail-import.xlsx
@@ -490,7 +490,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sales By Customer appears in Reports navigation and opens with correct titles</t>
+          <t>Sales By Customer listed under Performance, below existing links; titles correct</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -517,14 +517,14 @@
       <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports area from the main navigation.
-2. Look through the Reports left-side navigation for the report entry.
+2. Find the Performance group and read its entries from top to bottom.
 3. Click the "Sales By Customer" entry.
 4. Read the page title at the top of the report and the browser tab's title.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. "Sales By Customer" is listed in the Reports left-side navigation.
+          <t>1. "Sales By Customer" is listed in the Performance group of the Reports left-side navigation, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency) — the new reports are added below those items without moving them.
 2. Clicking it opens the Sales By Customer report in the main content area.
 3. The page title reads "Sales By Customer."
 4. The browser tab title reads "Sales By Customer - Report | ShopView".</t>
@@ -532,7 +532,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>specs/sbc-sales-by-customer.md Story 1 S1-R1; S1-R3; S1-R4</t>
+          <t>SV-8600 (specs/sbc-sales-by-customer.md Story 1 S1-R1; S1-R3; S1-R4 — Performance group + below-the-anchors placement per the PRD companion video 2026-07-30 01:18-02:05; the SBC spec names no nav group)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -4460,7 +4460,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Sales By Representative at the bottom of Performance group; titles correct</t>
+          <t>Sales By Representative under Performance, below existing links; titles correct</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4493,7 +4493,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>1. "Sales By Representative" appears in the Performance group, at the BOTTOM of the group — the label is the full word "Representative," not a "Rep" shorthand.
+          <t>1. "Sales By Representative" appears in the Performance group, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency) — the label is the full word "Representative," not a "Rep" shorthand. It need not be the very last entry: the other new reports (Technician Utilization, Work In Progress, Sales By Customer) are added in the same below-the-anchors block, in no set order.
 2. The rest of the navigation matches the previous release: no existing entry is moved, replaced, or reordered — if you can compare against production or an earlier build, the only difference is the added entry.
 3. Selecting the entry opens the report in the main content area.
 4. The page title reads "Sales By Representative".
@@ -4502,7 +4502,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 1 S1-R1; S1-R2; S1-R3; S1-R4; S1-R5; S1-R6</t>
+          <t>SV-8619 (specs/sbr-sales-by-representative.md Story 1 S1-R1; S1-R2; S1-R3; S1-R4; S1-R5; S1-R6 — 'at the bottom' re-based to below-the-named-anchors [Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency] per the PRD companion video 2026-07-30 01:18-02:05; order among the four new reports not important)</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
@@ -9229,7 +9229,7 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>The Sales Rep selector offers only reps whose sales-rep toggle is currently on, and carries the accessible name "Sales Rep"</t>
+          <t>Sales Rep selector offers only reps whose sales-rep toggle is on</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -9249,7 +9249,7 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>1. At least one staff member has the sales-rep toggle ON and at least one has it OFF (arrange and restore afterward).</t>
+          <t>1. At least one staff member has the sales-rep toggle ON and at least one has it OFF. To arrange this: open Settings, go to Staff, edit the staff member, and use the sales-rep toggle there (restore both afterward).</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 19 S19-R2; S19-R8</t>
+          <t>SV-8636 (specs/sbr-sales-by-representative.md Story 19 S19-R2; S19-R8 — toggle entry path Settings -&gt; Staff -&gt; edit the staff member per the PRD companion video 2026-07-30 09:17-09:41; exact toggle label to confirm live in the build)</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr"/>
@@ -9420,7 +9420,7 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>The customer record shows a single Sales Rep row ("Unassigned" when none), and a toggled-off bound rep shows "(Inactive)" in the WO selector</t>
+          <t>Customer record shows a "Sales Representative" row; "Unassigned" when none</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
@@ -9453,14 +9453,14 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>1. The customer record's left-panel sidebar shows a single "Sales Rep" row with the customer's assigned rep.
+          <t>1. The customer record's left-panel sidebar shows a single row labeled "Sales Representative" (the full word — the product owner explicitly corrected the short-form "Sales Rep" label here) with the customer's assigned rep.
 2. When no rep is assigned, the row renders "Unassigned".
 3. On the WO, the selector renders the bound rep's name with an "(Inactive)" indicator so the current assignment stays visible — but that rep is NOT offered as a new selection in the list.</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>specs/sbr-sales-by-representative.md Story 19 S19-R7; S19-E1</t>
+          <t>SV-8636 (specs/sbr-sales-by-representative.md Story 19 S19-R7; S19-E1 — customer-card row label RE-RULED to the full 'Sales Representative' per the PRD companion video 2026-07-30 10:53-11:12, superseding the spec's 'Sales Rep'; video authoritative, newest-wins)</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr"/>
@@ -9791,13 +9791,13 @@
       <c r="G194" s="2" t="inlineStr">
         <is>
           <t>1. A Parts section heading exists in the Reports navigation (this feature creates it - the application had no Parts reports before).
-2. Under Parts there is an entry labeled Parts Velocity (the only Parts report in this release).
+2. Under Parts there is an entry labeled Parts Velocity; Inventory Value also lives under Parts. The order of the two inside the Parts section is not fixed — do not fail the test on which of them comes first.
 3. Clicking it opens the Parts Velocity report.</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>specs/parts-velocity.md S1-R1</t>
+          <t>SV-8641 (specs/parts-velocity.md S1-R1 — the spec's 'only report' sentence is superseded: Parts Velocity and Inventory Value BOTH live under Parts per the PRD companion video 2026-07-30 00:35-01:18; PV S1-R1 vs IV S1-R1 inconsistency flagged to SPEC-WATCH)</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr"/>
@@ -13129,12 +13129,12 @@
         <is>
           <t>1. The report is listed under the Performance group, labeled "Technician Utilization".
 2. Clicking it opens the report.
-3. The entry sits BELOW the previously existing report links (toward the bottom) — the new reports are added without moving or disturbing the existing entries.</t>
+3. The entry sits BELOW the pre-existing report links — Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency — the new reports are added below those items without moving or disturbing them.</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (specs/technician-utilization.md S1-R1 — nav placement tightened per kickoff video P3 05:11-05:19 [below existing items, additive not interruptive], user ruling 2026-07-28: video overrides spec (video newer, last-update-wins))</t>
+          <t>SV-8648 (specs/technician-utilization.md S1-R1 — below the named anchor items [Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency] per the PRD companion video 2026-07-30 01:18-02:05, refining kickoff video P3; video authoritative, newest-wins)</t>
         </is>
       </c>
       <c r="I262" s="2" t="inlineStr"/>
@@ -15981,14 +15981,14 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>1. The reports navigation lists a report labeled "Work In Progress" under the Performance group.
+          <t>1. The reports navigation lists a report labeled "Work In Progress" under the Performance group, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency).
 2. Clicking it opens the Work In Progress report.
 3. The browser page title is exactly "Work In Progress - Report | ShopView" — a plain hyphen with one space on each side.</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
-          <t>specs/wip-work-in-progress.md Story 1 S1-R1; S1-R5</t>
+          <t>SV-8657 (specs/wip-work-in-progress.md Story 1 S1-R1 — Performance group; below the named anchor items [Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency] per the PRD companion video 2026-07-30 01:18-02:05)</t>
         </is>
       </c>
       <c r="I321" s="2" t="inlineStr"/>

--- a/testrail-import/report-suite-v1-testrail-import.xlsx
+++ b/testrail-import/report-suite-v1-testrail-import.xlsx
@@ -1070,7 +1070,8 @@
 4. Expand to an invoice row and read its Location cell.
 5. Open the column selector and look for Location in the list.
 6. Narrow the Location filter to a single location and read the headers again.
-7. Change the Location selection between one location, several, and "All locations", watching the filter control's width.</t>
+7. Change the Location selection between one location, several, and "All locations", watching the filter control's width.
+8. With more than one location still selected, download all four files from the download menu (Summary and Expanded View, PDF and CSV) and read the columns in each one.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1081,12 +1082,13 @@
 4. An invoice row always shows its own exact location — never "Multiple".
 5. Location is NOT offered in the column selector — it appears and disappears on its own, following the location scope.
 6. With a single location in scope the Location column is hidden and the surrounding columns close up with no gap.
-7. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.</t>
+7. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
+8. Every one of the four downloads also contains the Location column, in the same position it holds on screen, showing the same values you just read: a location name on a row whose invoices are all at one location, "Multiple" on a row that aggregates more than one, and the invoice's own location on an invoice row. (Exactly where the column sits inside each file is confirmed in the build.)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>SV-8603 (SBC spec v12 2026-07-29 S4-R12; S4-R12a; S20-R19 — per-row Location column with automatic visibility; "Multiple" on aggregating rows)</t>
+          <t>SV-8603; SV-8612; SV-8613 (SBC spec v12 2026-07-29 S4-R12; S4-R12a; S4-R13; S20-R19 — per-row Location column with automatic visibility; "Multiple" on aggregating rows; S4-R13 = the same column in every export)</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr"/>
@@ -3019,7 +3021,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 S14-R14; S15-R6 — file names now carry the Summary/Expanded version; the old flat sales-by-customer-{range} map is superseded)</t>
+          <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 S14-R14; S14-R15; S15-R6 — file names now carry the Summary/Expanded version; the old flat sales-by-customer-{range} map is superseded)</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3060,7 +3062,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1. The Expanded View CSV has these thirteen columns in this exact order: Customer, Asset, Invoice #, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal.
+          <t>1. With a single location in scope the Expanded View CSV has these thirteen columns in this exact order: Customer, Asset, Invoice #, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal. When more than one location is in scope the file also carries a Location column — immediately after Date, the position it holds on screen — making fourteen.
 2. A customer row fills the Customer cell and leaves Asset, Invoice # and Date blank.
 3. An asset row leaves Customer blank, fills Asset, and leaves Invoice # and Date blank.
 4. An invoice row leaves Customer and Asset blank and fills Invoice # and Date.
@@ -3071,7 +3073,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>SV-8612 (SBC spec v12 2026-07-29 Story 14 S14-R5; S14-R6; S14-R7; S14-R13 — the Expanded CSV now has thirteen columns INCLUDING Asset; with per-level blank-cell rules; the old flat twelve-column shape is superseded)</t>
+          <t>SV-8612; SV-8603 (SBC spec v12 2026-07-29 Story 14 S14-R5; S14-R6; S14-R7; S14-R8; S14-R13 + Story 4 S4-R13 — Expanded CSV thirteen columns INCLUDING Asset; per-level blank-cell rules; plus the automatic Location column in every export)</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3119,7 +3121,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>SV-8612 (specs/sbc-sales-by-customer.md Story 14 S14-R10; S14-R11; S14-R12; S14-R13)</t>
+          <t>SV-8612 (SBC spec v12 2026-07-29 Story 14 S14-R9; S14-R10; S14-R11; S14-R12; S14-R13)</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3261,7 +3263,7 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>SV-8613 (specs/sbc-sales-by-customer.md Story 15 S15-R5; S15-R6)</t>
+          <t>SV-8613 (SBC spec v12 2026-07-29 Story 15 S15-R5; S15-R6; S15-R7; S15-R8 — A4 landscape; 25px margins; standard font; footer label and page numbers)</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3358,7 +3360,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>SV-8613 (specs/sbc-sales-by-customer.md Story 15 S15-R12; S15-R13; S15-R14; S15-R15)</t>
+          <t>SV-8613 (SBC spec v12 2026-07-29 Story 15 S15-R12; S15-R13; S15-R14; S15-R15; S15-R16; S15-R17; S15-R18)</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3398,7 +3400,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>1. The Expanded View PDF's body table has the same thirteen columns, in the same order and with the same labels, as the Expanded View CSV — including the Asset column — and shows the full Customer, then Asset, then Invoice breakdown, one block per customer.
+          <t>1. The Expanded View PDF's body table has the same columns, in the same order and with the same labels, as the Expanded View CSV — thirteen with a single location in scope, plus the Location column after Date when more than one location is in scope — including the Asset column — and shows the full Customer, then Asset, then Invoice breakdown, one block per customer.
 2. Body dates show as "Mon DD YYYY" - for example, "May 14 2026."
 3. The Date cell is blank on customer rows and on asset rows, matching the screen.
 4. Margin % shows an em dash when the row's Subtotal is zero or below.
@@ -3409,7 +3411,7 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>SV-8613 (SBC spec v12 2026-07-29 Story 15 S15-R5; S15-R13; S15-R19; S15-R20; S15-R21; S15-R22; S15-R23; S15-R24 — Expanded PDF body = the Expanded columns with the asset layer; one block per customer; the title is the same for both versions)</t>
+          <t>SV-8613; SV-8603 (SBC spec v12 2026-07-29 Story 15 S15-R5; S15-R13; S15-R19; S15-R20; S15-R21; S15-R22; S15-R23; S15-R24 + Story 4 S4-R13 — Expanded PDF body = the Expanded columns; plus the automatic Location column)</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3458,7 +3460,7 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613 (specs/sbc-sales-by-customer.md Story 14 S14-R14; Story 15 S15-R22; §7 — the Print leg REMOVED per kickoff video P25 31:14 / SV-8614 overridden; user ruling 2026-07-28: video overrides spec (video newer; last-update-wins))</t>
+          <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 S14-R16 CSV cap; S15-R25 PDF cap; S14-R14; S15-R22; §7 — Print leg REMOVED per kickoff video P25 31:14; user ruling 2026-07-28 video-overrides-spec)</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3549,12 +3551,12 @@
 2. Each Summary file gives ONE row per customer, without the asset or invoice detail rows.
 3. Each Expanded View file contains the full Customer, then Asset, then Invoice breakdown.
 4. All four files reflect exactly the filtered data shown on screen.
-5. The Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns.</t>
+5. With a single location in scope the Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When more than one location is in scope a Location column is added with the identifying columns, ahead of the money columns (the Summary files have no Date column for it to follow — confirm its exact position in the build).</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 Story 14 S14-R1/R2/R4 + Story 15 S15-R1/R2/R4/R5 — the four-item Summary/Expanded menu and the Summary column list are now spec-ratified)</t>
+          <t>SV-8612; SV-8613; SV-8603 (SBC spec v12 2026-07-29 Story 14 S14-R1/R2/R4 + Story 15 S15-R1/R2/R4/R5 + Story 4 S4-R13 — four-item Summary/Expanded menu and the Summary column list; plus the automatic Location column in every export)</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -5328,7 +5330,8 @@
 5. Read the Location cell on the Unassigned summary row.
 6. Check that the pinned Subtotal column is still the rightmost column.
 7. Narrow to a single location and read the headers again.
-8. Change the selection between one location, several, and "All Locations", watching the filter control's width.</t>
+8. Change the selection between one location, several, and "All Locations", watching the filter control's width.
+9. With more than one location still selected, download all four files from the ⋯ menu (Summary and Expanded View, PDF and CSV) and read the Location column in each one.</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -5340,12 +5343,13 @@
 5. The Unassigned summary row follows the same rule as any rep summary row.
 6. The pinned Subtotal column is still rightmost — the Location column never displaces it.
 7. With a single location in scope the Location column is hidden.
-8. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.</t>
+8. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
+9. All four downloads include the Location column in the same position it occupies on screen. In the Summary files a rep's row carries that rep's location and reads "Multiple" when the rep spans more than one location; in the Expanded View files each invoice row carries that invoice's own exact location.</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>SV-8638 (SBR spec v15 2026-07-29 S21-R7; S21-R8; S18-R13 — per-row Location column; "Multiple" verbatim on a rep row spanning locations; position after Status; constant-width filter)</t>
+          <t>SV-8638; SV-8631 (SBR spec v15 2026-07-29 S21-R7; S21-R8; S18-R13; S14-R20 — per-row Location column; "Multiple" on a rep row spanning locations; position after Status; constant-width filter; S14-R20 = the same column in all four exports)</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr"/>
@@ -5436,7 +5440,7 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>1. The columns appear left to right: Date, Invoice, Customer, Status, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal (12 columns).
+          <t>1. With a single location in scope the columns appear left to right: Date, Invoice, Customer, Status, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal (12 columns). When more than one location is in scope the automatic Location column is added immediately after Status, making 13.
 2. On a rep summary row the Date cell holds the chevron control followed by the rep's display name ("First Last"); the date value is intentionally blank.
 3. The Invoice, Customer, and Status cells are blank on summary rows; the metric cells carry the rep's totals across all matching invoices.
 4. Rep summary rows are bold (700) so they read as parent rows; detail rows use the default weight (400) — row type is distinguished by font weight, not background color.
@@ -5445,7 +5449,7 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>SV-8623 (specs/sbr-sales-by-representative.md Story 5 S5-R2; S5-R3; S5-R6; S5-R8; S5-R10; S5-N2; Story 6 S6-R4; Story 18 S18-R4; S18-R6a)</t>
+          <t>SV-8623; SV-8638 (SBR spec v15 2026-07-29 Story 5 S5-R2; S5-R3; S5-R6; S5-R8; S5-R10; S5-N2; Story 6 S6-R4; Story 18 S18-R4; S18-R6a + Story 21 S21-R7 — plus the Location column after Status)</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr"/>
@@ -7693,7 +7697,7 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>SV-8640 (specs/sbr-sales-by-representative.md Story 23 S23-R4; S23-N1; Story 2 S2-R4; Story 21 S21-R2)</t>
+          <t>SV-8640 (SBR spec v15 2026-07-29 Story 23 S23-R4; S23-N1; Story 2 S2-R4; S2-R7; Story 21 S21-R2)</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr"/>
@@ -7883,14 +7887,14 @@
         <is>
           <t>1. The PDF is A4 portrait, edge-to-edge, with a header strip on the first page showing the workplace name and address, the organization logo, the report title "Sales By Representative," and the selected date range.
 2. There is one rolled-up row per rep, in the report's currently-active order; a toggled-off contributor's name carries the "(Inactive)" tag.
-3. The columns are: Rep / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal.
+3. With a single location in scope the columns are: Rep / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal. When more than one location is in scope a Location column is added with the identifying columns ahead of Inv. Hrs, and a rep who spans more than one location reads "Multiple" (this file has no Status column for it to follow — confirm its exact position in the build).
 4. Subtotal is bolded across the header, the body rows, and the grand totals row; Inv. Hrs keeps its green/red/default coloring.
 5. The grand totals row reads "Totals" in the Rep cell and aggregates every summary row in the document (including the Unassigned row when Show Unassigned is on); its Margin % is RECOMPUTED as total Margin ÷ total Subtotal (shown "—" when that Subtotal is zero or below), never the sum or average of the rows' percentages.</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R3; S14-R5; Story 2 S2-R5; §3 Margin % definition)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R3; S14-R5; S14-R20; Story 2 S2-R5; §3 Margin % definition — Summary PDF; plus the automatic Location column in all four exports)</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr"/>
@@ -7933,7 +7937,7 @@
       <c r="G155" s="2" t="inlineStr">
         <is>
           <t>1. There is one page-block per rep, in the report's currently-active order, with a page break before each new rep after the first.
-2. Each block shows the header strip (workplace name and address, organization logo, title "Sales By Representative," the selected date range), the rep's name, and a per-invoice table with columns: Date / Invoice / Customer / Status / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal.
+2. Each block shows the header strip (workplace name and address, organization logo, title "Sales By Representative," the selected date range), the rep's name, and a per-invoice table with columns: Date / Invoice / Customer / Status / (Location, only when more than one location is in scope, carrying that invoice's own location) / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal.
 3. The Status column renders the same colored badge as on screen, vertically centered.
 4. Invoices are ordered newest first (the same order as the on-screen expansion: invoice date descending, numeric invoice-number tie-break).
 5. Each block ends with a per-rep totals row — "Totals" in the Date cell; Invoice/Customer/Status blank; each metric aggregated; Margin % recomputed.
@@ -7942,7 +7946,7 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R6; S14-R8; Story 6 S6-R9)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R6; S14-R8; S14-R20; Story 6 S6-R9 — Expanded PDF page-block per rep; plus the automatic Location column after Status)</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr"/>
@@ -8177,16 +8181,17 @@
       <c r="G160" s="2" t="inlineStr">
         <is>
           <t>1. The file is named "sales-by-representative-summary.csv" and starts with a UTF-8 BOM.
-2. The headers, in order, are exactly: Sales Representative, # Invoices, # Customers, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
+2. With a single location in scope the headers, in order, are exactly: Sales Representative, # Invoices, # Customers, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 3. There is one header row plus one row per rep in the current filtered view, in the report's currently-active order.
 4. "# Invoices" equals the on-screen (N); "# Customers" counts distinct customers across those invoices (de-duplicated across locations when several are selected).
 5. The CSV has NO totals row.
-6. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+6. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
+7. When more than one location is in scope the file also carries a Location column, with the identifying columns ahead of the metric columns; a rep whose invoices span more than one location reads "Multiple". (This file has no Status column for it to follow — confirm its exact position in the build.)</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R15; S14-R18)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R15; S14-R18; S14-R20 — Summary CSV headers; plus the automatic Location column in all four exports; S14-R15's header list was left un-updated when S14-R20 was added — spec correction pending)</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr"/>
@@ -8228,14 +8233,15 @@
       <c r="G161" s="2" t="inlineStr">
         <is>
           <t>1. The file is named "sales-by-representative-expanded.csv" and starts with a UTF-8 BOM.
-2. The headers, in order, are exactly: Sales Representative, Date, Invoice #, Customer, Status, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
+2. With a single location in scope the headers, in order, are exactly: Sales Representative, Date, Invoice #, Customer, Status, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 3. There is one header row plus one row per invoice, flattened across all reps in the report's currently-active order, for the current filtered view.
-4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
+5. When more than one location is in scope the file also carries a Location column immediately after Status — the position it holds on screen — and every row shows that invoice's own exact location, never "Multiple".</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R16)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R16; S14-R20 — Expanded CSV headers; plus the automatic Location column after Status; S14-R16's header list was left un-updated when S14-R20 was added — spec correction pending)</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr"/>
@@ -8823,7 +8829,7 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>SV-8633 (specs/sbr-sales-by-representative.md Story 16 S16-R1; S16-R2; S16-R3; S16-N1; §7)</t>
+          <t>SV-8633 (SBR spec v15 2026-07-29 Story 16 S16-R1; S16-R2; S16-R3; S16-N1; Story 2 S2-N1; Story 21 S21-N2; §7)</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr"/>
@@ -10813,7 +10819,8 @@
 3. Read the Location cell on the merged Special Order row.
 4. Open the column picker and look for Location in the list.
 5. Narrow to a single location and read the headers again.
-6. Change the selection between one location, several, and "All Locations", watching the filter control's width.</t>
+6. Change the selection between one location, several, and "All Locations", watching the filter control's width.
+7. With more than one location still selected, download the CSV and the PDF and read their columns from the left.</t>
         </is>
       </c>
       <c r="G214" s="2" t="inlineStr">
@@ -10823,12 +10830,13 @@
 3. The merged Special Order row shows "Multiple", because it is summed across the selected locations.
 4. Location is NOT one of the 20 columns in the picker — it is managed by the location scope, not by you.
 5. With a single location in scope the Location column is hidden.
-6. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.</t>
+6. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
+7. Both downloads include the Location column in the same position it holds on screen (leftmost, before Type), with the same values — each inventory row's own location, and "Multiple" on the merged Special Order row.</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (PV spec v4 2026-07-29 S2-R12; S3-R10; S7-R8 — per-row Location column; leftmost before Type; "Multiple" on the merged special-order row; not in the picker)</t>
+          <t>SV-8642; SV-8646 (PV spec v4 2026-07-29 S2-R12; S3-R10; S7-R8; S6-R11 — per-row Location column; leftmost before Type; "Multiple" on the merged special-order row; not in the picker; S6-R11 = the same column in both exports)</t>
         </is>
       </c>
       <c r="I214" s="2" t="inlineStr"/>
@@ -11411,13 +11419,14 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>1. Exactly these 14 columns show, in this left-to-right order: Type, Part #, Description, Category, Vendor, Units Sold, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand.
-2. The other 6 columns start hidden: Units Returned, Sold (WO), Sold (Parts Sale), Turns / Yr, Min, Max.</t>
+          <t>1. With a single location in scope exactly these 14 columns show, in this left-to-right order: Type, Part #, Description, Category, Vendor, Units Sold, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand.
+2. The other 6 columns start hidden: Units Returned, Sold (WO), Sold (Parts Sale), Turns / Yr, Min, Max.
+3. When more than one location is in scope the automatic Location column shows as well, leftmost before Type — 15 columns. It is not part of the 14-column default set and is not in the column picker, so its presence is expected and is not a failure of this test.</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>SV-8644 (specs/parts-velocity.md S4-R2; S4-R3)</t>
+          <t>SV-8644; SV-8643 (PV spec v4 2026-07-29 S4-R2; S4-R3 + Story 3 S3-R10 — the 14 default-visible columns and the 6 hidden ones; plus the automatic Location column leftmost when more than one location is in scope)</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr"/>
@@ -11459,13 +11468,13 @@
       <c r="G227" s="2" t="inlineStr">
         <is>
           <t>1. Each toggle takes effect immediately - the table re-renders without a page reload.
-2. Columns always render in the fixed canonical left-to-right order regardless of the order they were toggled on: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns / Yr, Min, Max.
+2. Columns always render in the fixed canonical left-to-right order regardless of the order they were toggled on (with the automatic Location column, when shown, sitting leftmost before Type): Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns / Yr, Min, Max.
 3. So Units Returned slots in right after Units Sold, Turns / Yr after On Hand, and Min before Max - not appended at the end.</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>SV-8644 (specs/parts-velocity.md S4-R4; S4-R5)</t>
+          <t>SV-8644; SV-8643 (PV spec v4 2026-07-29 S4-R4; S4-R5 + Story 3 S3-R10 — canonical column order and immediate re-render; plus the automatic Location column leftmost when shown)</t>
         </is>
       </c>
       <c r="I227" s="2" t="inlineStr"/>
@@ -13528,7 +13537,7 @@
       </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (specs/technician-utilization.md S1-R3; S9-R2)</t>
+          <t>SV-8648 (TU spec v5 2026-07-29 S1-R3; S1-R6; S9-R2)</t>
         </is>
       </c>
       <c r="I269" s="2" t="inlineStr"/>
@@ -13812,16 +13821,17 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>1. The headers appear in exactly this order: Technician, Total Hours, WO Hours, Internal Hours, Utilization %, Est. Lost Labor.
+          <t>1. With a single location in scope the headers appear in exactly this order: Technician, Total Hours, WO Hours, Internal Hours, Utilization %, Est. Lost Labor.
 2. Total Hours = all time the technician was clocked in for the range.
 3. WO Hours = time clocked directly to work orders; Internal Hours = time clocked to internal, non-billable activities.
 4. Internal Hours includes ALL internal time - including hours at a location with no configured labor rate.
-5. Hours show two decimal places with NO thousands separator (e.g. "107.70"), rounded from the unrounded hours using round-half-up (a tie rounds away from zero - 0.005 → 0.01).</t>
+5. Hours show two decimal places with NO thousands separator (e.g. "107.70"), rounded from the unrounded hours using round-half-up (a tie rounds away from zero - 0.005 → 0.01).
+6. When more than one location is in scope the automatic Location column also appears, leftmost before Technician — it is not in the Column Selection control and its presence is expected.</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-R1; S2-R2; S2-R3; S2-R4; S2-R5; §3)</t>
+          <t>SV-8649; SV-8656 (TU spec v5 2026-07-29 S2-R1; S2-R2; S2-R3; S2-R4; S2-R5; §3 + Story 9 S9-R9 — header order and the hours columns; plus the automatic Location column leftmost when shown)</t>
         </is>
       </c>
       <c r="I275" s="2" t="inlineStr"/>
@@ -16042,7 +16052,8 @@
 5. Read the Location cell on the Summary row at the bottom.
 6. Open the Column Selection control and look for Location in the list.
 7. Narrow to a single location and read the headers again.
-8. Change the selection between one location, several, and "All Locations", watching the filter control's width.</t>
+8. Change the selection between one location, several, and "All Locations", watching the filter control's width.
+9. With more than one location still selected, download both PDF views and the CSV and read their columns from the left.</t>
         </is>
       </c>
       <c r="G321" s="2" t="inlineStr">
@@ -16054,12 +16065,13 @@
 5. The Summary row leaves the Location cell blank.
 6. Location is never listed in the Column Selection control — it follows the location scope on its own.
 7. With a single location in scope the Location column is hidden.
-8. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.</t>
+8. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
+9. Every download — both PDF views and the CSV — includes the Location column in its on-screen leftmost position, carrying the same values you just read on screen.</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (TU spec v5 2026-07-29 S9-R9; S9-R10; S8-R15; S10-R4 — per-row Location column; leftmost before Technician; "Multiple" on a spanning row; Summary row blank; never in the selector)</t>
+          <t>SV-8656; SV-8654 (TU spec v5 2026-07-29 S9-R9; S9-R10; S8-R15; S10-R4; S7-R13 — per-row Location column; leftmost before Technician; "Multiple" on a spanning row; Summary row blank; not in the selector; S7-R13 = same column in every download)</t>
         </is>
       </c>
       <c r="I321" s="2" t="inlineStr"/>
@@ -16095,27 +16107,29 @@
       <c r="F322" s="2" t="inlineStr">
         <is>
           <t>1. Find the column-selection button in the toolbar and hover it to read its tooltip.
-2. Note its position relative to the three-dot download menu.
-3. Open it and read every toggle in the list, and which ones are on.
-4. Turn Est. Lost Labor off, then turn Internal Hours off, watching the table each time.
-5. Turn both back on and check where each column lands.
-6. Reload the page, then close the browser, reopen it and return to the report.</t>
+2. With the button focused, read the name assistive technology gives it — use the browser's accessibility inspector or a screen reader.
+3. Note its position relative to the three-dot download menu.
+4. Open it and read every toggle in the list, and which ones are on.
+5. Turn Est. Lost Labor off, then turn Internal Hours off, watching the table each time.
+6. Turn both back on and check where each column lands.
+7. Reload the page, then close the browser, reopen it and return to the report.</t>
         </is>
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
           <t>1. The control is an icon button whose tooltip reads "Column Selection", sitting immediately after the three-dot download menu in the toolbar.
-2. The list offers five toggles — Total Hours, WO Hours, Internal Hours, Utilization % and Est. Lost Labor — and all five are on by default.
-3. Technician is always shown and cannot be turned off (it is not offered as a toggle).
-4. The Location column is never listed here — it appears on its own whenever more than one location is in scope.
-5. Turning a toggle off hides that column (header and cells) immediately, with no reload; turning it back on returns it to its usual place in the fixed left-to-right order — the remaining columns never reorder.
-6. Est. Lost Labor can now be hidden like any other column (it used to be always on).
-7. Your column choice is remembered in this browser and is still applied when you come back.</t>
+2. Because the button shows an icon and no text, it still carries a name that assistive technology reads out — it is not left unnamed. (The exact wording is confirmed in the build.)
+3. The list offers five toggles — Total Hours, WO Hours, Internal Hours, Utilization % and Est. Lost Labor — and all five are on by default.
+4. Technician is always shown and cannot be turned off (it is not offered as a toggle).
+5. The Location column is never listed here — it appears on its own whenever more than one location is in scope.
+6. Turning a toggle off hides that column (header and cells) immediately, with no reload; turning it back on returns it to its usual place in the fixed left-to-right order — the remaining columns never reorder.
+7. Est. Lost Labor can now be hidden like any other column (it used to be always on).
+8. Your column choice is remembered in this browser and is still applied when you come back.</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
         <is>
-          <t>SV-8582 (TU spec v5 2026-07-29 Story 10 S10-R1; S10-R2; S10-R3; S10-R4; S10-R5; S10-R6 column selector — NO OWNING JIRA STORY: epic SV-8582 carries no TU Story-10 ticket and the spec's own Jira field reads TBD; epic key used and FLAGGED)</t>
+          <t>SV-8655; SV-8582 (TU spec v5 2026-07-29 Story 10 S10-R1; S10-R2; S10-R3; S10-R4; S10-R5; S10-R6 column selector + Story 8 S8-R16 accessible name — Story 10 has NO owning Jira story so epic SV-8582 is used and FLAGGED; S8-R16 is owned by SV-8655)</t>
         </is>
       </c>
       <c r="I322" s="2" t="inlineStr"/>
@@ -16361,7 +16375,7 @@
       </c>
       <c r="H327" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (specs/wip-work-in-progress.md Story 1 S1-R1 — Performance group; below the named anchor items [Sales; Technician Efficiency; Advisor Analysis; Shop Efficiency] per the PRD companion video 2026-07-30 01:18-02:05)</t>
+          <t>SV-8657 (WIP spec v6 2026-07-29 Story 1 S1-R1; S1-R5 — Performance group; below the named anchor items [Sales; Technician Efficiency; Advisor Analysis; Shop Efficiency] per the PRD video 2026-07-30 01:18-02:05; S1-R5 = browser page title)</t>
         </is>
       </c>
       <c r="I327" s="2" t="inlineStr"/>
@@ -16751,7 +16765,7 @@
       </c>
       <c r="H335" s="2" t="inlineStr">
         <is>
-          <t>SV-8658 (specs/wip-work-in-progress.md Story 2 S2-N1; S2-N2; §7 User Feedback Summary)</t>
+          <t>SV-8658 (WIP spec v6 2026-07-29 Story 2 S2-N1; S2-N2; Story 6 S6-N1; §7 User Feedback Summary)</t>
         </is>
       </c>
       <c r="I335" s="2" t="inlineStr"/>
@@ -18787,7 +18801,7 @@
       </c>
       <c r="H376" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (WIP spec v6 2026-07-29 S7-R13; S7-R14; S4-R3; S9-E1; §4 Location (column) — automatic visibility; never "Multiple"; export header "Branch")</t>
+          <t>SV-8663 (WIP spec v6 2026-07-29 S7-R13; S7-R14; S4-R3; S9-E1; S10-R5a; §4 Location (column) — automatic visibility; never "Multiple"; export header "Branch")</t>
         </is>
       </c>
       <c r="I376" s="2" t="inlineStr"/>
@@ -19081,7 +19095,7 @@
       </c>
       <c r="H382" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R2; S9-R3; S9-R4 + Locations: line in every CSV/PDF export per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
+          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R2; S9-R3; S9-R4; S9-R10a — "Locations:" line in every CSV/PDF export per Chris Ward's 2026-07-29 message [NEWEST source; last-update-wins])</t>
         </is>
       </c>
       <c r="I382" s="2" t="inlineStr"/>
@@ -20423,7 +20437,7 @@
       </c>
       <c r="H410" s="2" t="inlineStr">
         <is>
-          <t>SV-8668 (specs/inventory-value.md Story 1 S1-N2; Story 5 S5-N1; Story 7 S7-N2; Story 12; §7 User Feedback Summary)</t>
+          <t>SV-8668 (IV spec v3 2026-07-29 Story 1 S1-N2; Story 4 S4-N1; Story 5 S5-N1; Story 7 S7-N2; Story 12; §7 User Feedback Summary)</t>
         </is>
       </c>
       <c r="I410" s="2" t="inlineStr"/>
@@ -20899,14 +20913,15 @@
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>1. The columns appear in this order: Part #, Description, Category, Vendor, Qty on Hand, Unit Cost, Unit Sell, Margin, Margin %, Total Sell, Total Cost.
+          <t>1. With a single location in scope the columns appear in this order: Part #, Description, Category, Vendor, Qty on Hand, Unit Cost, Unit Sell, Margin, Margin %, Total Sell, Total Cost.
 2. Part #, Description, Category, and Vendor are left-aligned.
-3. Every other column is right-aligned.</t>
+3. Every other column is right-aligned.
+4. When more than one location is in scope the automatic Location column also appears, between Vendor and Qty on Hand, left-aligned. It is not in the column-selection control, so its presence is expected and is not a failure of this test.</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
         <is>
-          <t>SV-8670 (specs/inventory-value.md Story 3 S3-R1; S3-R2)</t>
+          <t>SV-8670; SV-8674 (IV spec v3 2026-07-29 Story 3 S3-R1; S3-R2 + Story 7 S7-R6 — fixed column order and alignment; plus the automatic Location column between Vendor and Qty on Hand)</t>
         </is>
       </c>
       <c r="I420" s="2" t="inlineStr"/>
@@ -21044,14 +21059,15 @@
       </c>
       <c r="G423" s="2" t="inlineStr">
         <is>
-          <t>1. On first visit, the visible columns are: Part #, Description, Category, Vendor, Qty on Hand, Unit Cost, Unit Sell, Margin %, and Total Cost.
+          <t>1. On first visit with a single location in scope the visible columns are: Part #, Description, Category, Vendor, Qty on Hand, Unit Cost, Unit Sell, Margin %, and Total Cost.
 2. The Margin and Total Sell columns are hidden by default.
-3. Both can be turned on from the column-selection control and then appear in their fixed positions.</t>
+3. Both can be turned on from the column-selection control and then appear in their fixed positions.
+4. When more than one location is in scope the automatic Location column also shows, between Vendor and Qty on Hand — it is not one of the toggleable columns and its presence is expected.</t>
         </is>
       </c>
       <c r="H423" s="2" t="inlineStr">
         <is>
-          <t>SV-8670 (specs/inventory-value.md Story 3 S3-R12; S3-R13; Story 8 S8-R3)</t>
+          <t>SV-8670; SV-8674 (IV spec v3 2026-07-29 Story 3 S3-R12; S3-R13; Story 8 S8-R3 + Story 7 S7-R6 — first-visit default columns; plus the automatic Location column when more than one location is in scope)</t>
         </is>
       </c>
       <c r="I423" s="2" t="inlineStr"/>
@@ -22123,7 +22139,8 @@
 3. Look for any row showing "Multiple".
 4. Open the column-selection control and look for Location in the list.
 5. Narrow to a single location and read the headers again.
-6. Change the selection between one location, several, and "All locations", watching the filter control's width.</t>
+6. Change the selection between one location, several, and "All locations", watching the filter control's width.
+7. With more than one location still selected, download the CSV and the PDF and read their columns.</t>
         </is>
       </c>
       <c r="G445" s="2" t="inlineStr">
@@ -22133,12 +22150,13 @@
 3. NO row ever shows "Multiple" — each row is one part at one location.
 4. Location is NOT offered in the column-selection control — its visibility follows the location scope automatically.
 5. With a single location in scope the Location column is hidden and the surrounding columns close up.
-6. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.</t>
+6. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
+7. Both downloads include the Location column in the same position it holds on screen (between Vendor and Qty on Hand), naming each row's own location.</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
         <is>
-          <t>SV-8674 (IV spec v3 2026-07-29 S7-R6; S7-R7; S3-R1; S12-R10 — Location column inserted between Vendor and Qty on Hand; automatic visibility; never "Multiple")</t>
+          <t>SV-8674; SV-8677 (IV spec v3 2026-07-29 S7-R6; S7-R7; S3-R1; S12-R10; S10-R15 — Location column inserted between Vendor and Qty on Hand; automatic visibility; never "Multiple"; S10-R15 = the same column in every export)</t>
         </is>
       </c>
       <c r="I445" s="2" t="inlineStr"/>
@@ -22228,13 +22246,13 @@
       </c>
       <c r="G447" s="2" t="inlineStr">
         <is>
-          <t>1. Whatever columns are shown, they appear in the fixed left-to-right order (Part #, Description, Category, Vendor, Qty on Hand, Unit Cost, Unit Sell, Margin, Margin %, Total Sell, Total Cost) — toggling visibility never reorders columns.
+          <t>1. Whatever columns are shown, they appear in the fixed left-to-right order — with the automatic Location column, when more than one location is in scope, between Vendor and Qty on Hand (Part #, Description, Category, Vendor, Qty on Hand, Unit Cost, Unit Sell, Margin, Margin %, Total Sell, Total Cost) — toggling visibility never reorders columns.
 2. Total Cost is always the last column.</t>
         </is>
       </c>
       <c r="H447" s="2" t="inlineStr">
         <is>
-          <t>SV-8675 (specs/inventory-value.md Story 8 S8-R4; Story 3 S3-R1)</t>
+          <t>SV-8675; SV-8674 (IV spec v3 2026-07-29 Story 8 S8-R4; Story 3 S3-R1 + Story 7 S7-R6 — toggling never reorders; plus the automatic Location column between Vendor and Qty on Hand)</t>
         </is>
       </c>
       <c r="I447" s="2" t="inlineStr"/>

--- a/testrail-import/report-suite-v1-testrail-import.xlsx
+++ b/testrail-import/report-suite-v1-testrail-import.xlsx
@@ -9972,7 +9972,7 @@
       <c r="E197" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App as a user with the Manager or Office User role.
-2. Your role has the Inventory Reports → View permission.</t>
+2. Your role has the ordinary reports access.</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
@@ -9991,7 +9991,7 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>SV-8641 (PV spec S1-R1 — spec's 'only report' sentence superseded: Parts Velocity and Inventory Value BOTH live under Parts per PRD video 2026-07-30 00:35-01:18; PV-vs-IV S1-R1 clash on SPEC-WATCH)</t>
+          <t>SV-8641 (PV spec S1-R1 — the "only report" sentence is superseded: Parts Velocity and Inventory Value BOTH live under Parts per the PRD video 2026-07-30; access = the one ordinary reports permission per QA lead 2026-08-03)</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr"/>
@@ -10097,7 +10097,7 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>A user with Inventory Reports View can load the report and export it</t>
+          <t>A user with ordinary reports access can load the report and export it</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -10118,7 +10118,7 @@
       <c r="E200" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a user with the Manager or Office User role.
-2. That user's role has the Inventory Reports → View permission.
+2. That user's role has the ordinary reports access (the standard "can this person see reports" setting).
 3. Some parts have sales activity in the selected date range.</t>
         </is>
       </c>
@@ -10132,12 +10132,13 @@
       <c r="G200" s="2" t="inlineStr">
         <is>
           <t>1. The report data loads and rows are shown.
-2. The export downloads successfully (both loading the report and exporting it are allowed by the Inventory Reports → View permission).</t>
+2. The export downloads successfully — both opening the report and exporting it are allowed by the same ordinary reports access.
+3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>SV-8641 (specs/parts-velocity.md S1-R4)</t>
+          <t>SV-8641 (PV spec S1-R4 — one reports permission for all six ruled by Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW"; PV S1-R4 still names Inventory Reports &gt; View — his spec edit owed)</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr"/>
@@ -13472,7 +13473,7 @@
       </c>
       <c r="E268" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in as a user whose role has the timesheet-reports permission.</t>
+          <t>1. You are signed in as a user whose role has the ordinary reports access.</t>
         </is>
       </c>
       <c r="F268" s="2" t="inlineStr">
@@ -13492,7 +13493,7 @@
       </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (TU spec S1-R1 — below the named anchor items [Sales; Technician Efficiency; Advisor Analysis; Shop Efficiency] per PRD video 2026-07-30 01:18-02:05; refines video P3 [newest-wins])</t>
+          <t>SV-8648 (TU spec S1-R1 — below the named anchor items [Sales; Technician Efficiency; Advisor Analysis; Shop Efficiency] per the PRD video 2026-07-30; access = the one ordinary reports permission per QA lead 2026-08-03)</t>
         </is>
       </c>
       <c r="I268" s="2" t="inlineStr"/>
@@ -13742,7 +13743,7 @@
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>Without the timesheet-reports permission Technician Utilization is hidden</t>
+          <t>Without reports access Technician Utilization is hidden</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
@@ -13762,7 +13763,7 @@
       </c>
       <c r="E274" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in as a user whose role lacks the permission that controls the Timesheet Activities report.</t>
+          <t>1. You are signed in as a user whose role does NOT have reports access.</t>
         </is>
       </c>
       <c r="F274" s="2" t="inlineStr">
@@ -13778,7 +13779,7 @@
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (specs/technician-utilization.md S1-N1)</t>
+          <t>SV-8648 (TU spec S1-N1 — the gate is the one ordinary reports access per Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW"; the TU prerequisite still names the timesheet-reports permission — his spec edit owed)</t>
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr"/>
@@ -16404,7 +16405,7 @@
       <c r="E328" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Your role has the permission that grants access to Work In Progress reports.</t>
+2. Your role has the ordinary reports access.</t>
         </is>
       </c>
       <c r="F328" s="2" t="inlineStr">
@@ -16424,7 +16425,7 @@
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (WIP spec v6 2026-07-29 Story 1 S1-R1; S1-R5 — Performance group; below the named anchor items [Sales; Technician Efficiency; Advisor Analysis; Shop Efficiency] per the PRD video 2026-07-30 01:18-02:05; S1-R5 = browser page title)</t>
+          <t>SV-8657 (WIP spec Story 1 S1-R1; S1-R5 — Performance group; below the named anchor items per the PRD video 2026-07-30; S1-R5 = browser page title; access = the one ordinary reports permission per QA lead 2026-08-03)</t>
         </is>
       </c>
       <c r="I328" s="2" t="inlineStr"/>
@@ -19875,7 +19876,7 @@
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
         <is>
-          <t>The Work In Progress reports permission covers opening and downloading</t>
+          <t>Ordinary reports access covers opening and downloading Work In Progress</t>
         </is>
       </c>
       <c r="B399" s="2" t="inlineStr">
@@ -19895,7 +19896,7 @@
       </c>
       <c r="E399" s="2" t="inlineStr">
         <is>
-          <t>1. A test user exists whose role has the permission that grants access to Work In Progress reports (assign the Tech user a suitable role if needed; restore the original role afterward).
+          <t>1. A test user exists whose role has the ordinary reports access (assign the Tech user a suitable role if needed; restore the original role afterward).
 2. You are signed in as that user on a desktop browser.</t>
         </is>
       </c>
@@ -19909,12 +19910,13 @@
       <c r="G399" s="2" t="inlineStr">
         <is>
           <t>1. The report is listed and opens normally.
-2. The download works with the same permission — the report reuses one existing reporting permission, adds no new one, and the same permission covers the report and its downloads.</t>
+2. The download works with the same permission — for now the one ordinary reports access covers the report and its downloads and no new permission is added for it.
+3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.</t>
         </is>
       </c>
       <c r="H399" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (specs/wip-work-in-progress.md Story 1 Prerequisites (+ context note))</t>
+          <t>SV-8657 (WIP spec Story 1 Prerequisites — one reports permission for all six ruled by Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW"; the WIP prerequisite still names a Work In Progress reports permission — his spec edit owed)</t>
         </is>
       </c>
       <c r="I399" s="2" t="inlineStr"/>
@@ -19923,7 +19925,7 @@
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
         <is>
-          <t>Without the permission Work In Progress is absent from the reports navigation</t>
+          <t>Without reports access Work In Progress is absent from the navigation</t>
         </is>
       </c>
       <c r="B400" s="2" t="inlineStr">
@@ -19943,7 +19945,7 @@
       </c>
       <c r="E400" s="2" t="inlineStr">
         <is>
-          <t>1. A test user exists whose role does NOT have the permission that grants access to Work In Progress reports (assign the Tech user such a role; restore the original role afterward).
+          <t>1. A test user exists whose role does NOT have reports access (assign the Tech user such a role; restore the original role afterward).
 2. You are signed in as that user on a desktop browser.</t>
         </is>
       </c>
@@ -19960,7 +19962,7 @@
       </c>
       <c r="H400" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (specs/wip-work-in-progress.md Story 1 S1-N1)</t>
+          <t>SV-8657 (WIP spec Story 1 S1-N1 — the gate is the one ordinary reports access per Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW")</t>
         </is>
       </c>
       <c r="I400" s="2" t="inlineStr"/>
@@ -20276,7 +20278,7 @@
       <c r="E407" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. Your role has the existing inventory-reports permission.</t>
+2. Your role has the ordinary reports access.</t>
         </is>
       </c>
       <c r="F407" s="2" t="inlineStr">
@@ -20294,7 +20296,7 @@
       </c>
       <c r="H407" s="2" t="inlineStr">
         <is>
-          <t>SV-8668 (specs/inventory-value.md Story 1 S1-R1)</t>
+          <t>SV-8668 (IV spec Story 1 S1-R1 — access = the one ordinary reports permission per Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW")</t>
         </is>
       </c>
       <c r="I407" s="2" t="inlineStr"/>
@@ -23281,7 +23283,7 @@
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
         <is>
-          <t>User with the existing inventory-reports permission can open the report</t>
+          <t>A user with ordinary reports access can open Inventory Value</t>
         </is>
       </c>
       <c r="B469" s="2" t="inlineStr">
@@ -23301,7 +23303,7 @@
       </c>
       <c r="E469" s="2" t="inlineStr">
         <is>
-          <t>1. A test user exists whose role has the existing inventory-reports permission (assign the Tech user a suitable role if needed; restore the original role afterward).
+          <t>1. A test user exists whose role has the ordinary reports access (assign the Tech user a suitable role if needed; restore the original role afterward).
 2. You are signed in as that user on a desktop browser.</t>
         </is>
       </c>
@@ -23314,13 +23316,14 @@
       </c>
       <c r="G469" s="2" t="inlineStr">
         <is>
-          <t>1. The report is listed and opens normally for a user holding the existing inventory-reports permission.
-2. No additional, report-specific permission is required — the report reuses the existing inventory-reports permission.</t>
+          <t>1. The report is listed and opens normally for a user holding the ordinary reports access.
+2. No additional report-specific permission is required — for now the one ordinary reports access covers all six of the new reports.
+3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.</t>
         </is>
       </c>
       <c r="H469" s="2" t="inlineStr">
         <is>
-          <t>SV-8668 (specs/inventory-value.md Story 1 Prerequisites)</t>
+          <t>SV-8668 (IV spec Story 1 Prerequisites — one reports permission for all six ruled by Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW"; the IV prerequisite still names the inventory-reports permission — his spec edit owed)</t>
         </is>
       </c>
       <c r="I469" s="2" t="inlineStr"/>
@@ -23329,7 +23332,7 @@
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
         <is>
-          <t>Without the permission Inventory Value is absent from the reports navigation</t>
+          <t>Without reports access Inventory Value is absent from the navigation</t>
         </is>
       </c>
       <c r="B470" s="2" t="inlineStr">
@@ -23349,7 +23352,7 @@
       </c>
       <c r="E470" s="2" t="inlineStr">
         <is>
-          <t>1. A test user exists whose role does NOT have the inventory-reports permission (assign the Tech user such a role; restore the original role afterward).
+          <t>1. A test user exists whose role does NOT have reports access (assign the Tech user such a role; restore the original role afterward).
 2. You are signed in as that user on a desktop browser.</t>
         </is>
       </c>
@@ -23366,7 +23369,7 @@
       </c>
       <c r="H470" s="2" t="inlineStr">
         <is>
-          <t>SV-8668 (specs/inventory-value.md Story 1 S1-N1)</t>
+          <t>SV-8668 (IV spec Story 1 S1-N1 — the gate is the one ordinary reports access per Chris Ward Q2=A + QA lead 2026-08-03 "ONE permission FOR NOW")</t>
         </is>
       </c>
       <c r="I470" s="2" t="inlineStr"/>

--- a/testrail-import/report-suite-v1-testrail-import.xlsx
+++ b/testrail-import/report-suite-v1-testrail-import.xlsx
@@ -828,7 +828,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>SV-8601 (specs/sbc-sales-by-customer.md Story 2 S2-R1; S2-R2)</t>
+          <t>SV-8601 (SBC spec v12 2026-07-29 Story 2 S2-R1; S2-R2 — S2-R2 CLOSES the eleven-option list and its order itself; so the closed list IS the requirement; re-check this case whenever S2-R2 changes)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>SV-8602 (specs/sbc-sales-by-customer.md Story 3 S3-R1; S3-R2; S3-R3; S3-R4; S3-R5; S3-R6)</t>
+          <t>SV-8602 (SBC spec v12 2026-07-29 Story 3 S3-R1; S3-R2; S3-R3; S3-R4; S3-R5; S3-R6 — S3-R2 CLOSES the list itself ("exactly three options ... in this order"); so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>SV-8605 (specs/sbc-sales-by-customer.md §2; §4 Terminology; Story 7 S7-R6; Story 11 S11-R1)</t>
+          <t>SV-8605 (SBC spec v12 2026-07-29 §2; §4 Terminology; Story 7 S7-R6; Story 11 S11-R1 — §2/S7-R6 CLOSE the financial-column list and its order; Location is an identifier column not a financial one [S4-R12; S20-R19] so it never enters this list)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2917,12 +2917,13 @@
           <t>1. The column selector is a separate control next to the overflow menu — it is not an item inside the overflow menu.
 2. Hovering it shows the tooltip "Column Selection."
 3. The panel lists nine toggles, in order: Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %.
-4. With no saved selection, all nine toggleable columns default to visible.</t>
+4. With no saved selection, all nine toggleable columns default to visible.
+5. Note for the tester: there is no Location toggle in this panel. That is correct - the Location column appears by itself when you have more than one location in scope, so it is never something you switch on here.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>SV-8611 (specs/sbc-sales-by-customer.md Story 13 S13-R1; S13-R2; S13-R3; S13-R4; S13-R7)</t>
+          <t>SV-8611 (SBC spec v12 2026-07-29 Story 13 S13-R1; S13-R2; S13-R3; S13-R4; S13-R7 — S13-R4 CLOSES the nine-toggle list and its order; Location is automatic and never a toggle [S4-R12; S4-R13])</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -3018,7 +3019,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613 (SBC spec S14-R1; S14-R2; S15-R1; S15-R2; S20-R16 - menu RESHAPED to 4 Summary/Expanded items by Chris Ward msg 2026-07-29 [newest-wins] [extends video P21]; 'Print' REMOVED per video P25 [same msg confirms])</t>
+          <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 S14-R1; S14-R2; S15-R1; S15-R2; S20-R16 — these CLOSE the four-item menu and its verbatim labels; menu reshaped + "Print" removed per Chris Ward 2026-07-29 [newest-wins])</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3360,7 +3361,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>SV-8613 (SBC spec Story 15 S15-R7; S15-R8; S15-R9; S15-R10; S15-R11 - old 'location not in the header' rule REVERSED by the Locations: line in every export per Chris Ward msg 2026-07-29 [newest-wins])</t>
+          <t>SV-8613 (SBC spec v12 2026-07-29 Story 15 S15-R7; S15-R8; S15-R9; S15-R10; S15-R11; S15-R14 + Story 4 S4-R13 — PDF header block; S15-R14/S4-R13 = the "Locations:" line in every export [Chris Ward 2026-07-29; newest-wins])</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3605,7 +3606,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613; SV-8603 (SBC spec v12 2026-07-29 Story 14 S14-R1/R2/R4 + Story 15 S15-R1/R2/R4/R5 + Story 4 S4-R13 — four-item Summary/Expanded menu and the Summary column list; plus the automatic Location column in every export)</t>
+          <t>SV-8612; SV-8613; SV-8603 (SBC spec v12 2026-07-29 S14-R1; S14-R2; S14-R4; S15-R1; S15-R2; S15-R4; S15-R5; S4-R13 — the four-item Summary/Expanded menu; the Summary column list; the automatic Location column in every export)</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>
@@ -4998,7 +4999,7 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>SV-8621 (specs/sbr-sales-by-representative.md Story 3 S3-R1; S3-R2; S3-R3; S3-R4; S3-R5; S3-R6; S3-R7)</t>
+          <t>SV-8621 (SBR spec v15 2026-07-29 Story 3 S3-R1; S3-R2; S3-R3; S3-R4; S3-R5; S3-R6; S3-R7 — S3-R2 CLOSES the list itself ("exactly three options"); so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
@@ -5047,7 +5048,7 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>SV-8622 (specs/sbr-sales-by-representative.md Story 4 S4-R1; S4-R2; S4-R3; S4-R5)</t>
+          <t>SV-8622 (SBR spec v15 2026-07-29 Story 4 S4-R1; S4-R2; S4-R3; S4-R5 — S4-R2 CLOSES the list itself ("exactly four options"); so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr"/>
@@ -6121,7 +6122,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>SV-8582 (SBR spec §3 definitions; §4 Terminology — money-column labels and the Subtotal/Margin definitions; CROSS-CUTTING across every SBR row level with no single owning story)</t>
+          <t>SV-8623; SV-8582 (SBR spec v15 2026-07-29 S5-R2 = the authoritative 12-column left-to-right order; §3 definitions; §4 Terminology — S5-R2 CLOSES the money-label list; Location sits after Status [S21-R7] and is not a money column)</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr"/>
@@ -6413,7 +6414,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>SV-8627 (specs/sbr-sales-by-representative.md Story 10 S10-R5 (mobile); Story 17 S17-R4)</t>
+          <t>SV-8627 (SBR spec v15 2026-07-29 Story 10 S10-R5 (mobile branch) + Story 17 S17-R4 — S10-R5 CLOSES it in the spec's own words: "Totals" left and the grand Subtotal right "(no other metrics)")</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr"/>
@@ -7418,12 +7419,13 @@
           <t>1. The dropdown lists the seven toggleable metric columns, each with a toggle switch: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %.
 2. On first visit all seven metric columns are visible.
 3. The five always-visible columns (Date, Invoice, Customer, Status, Subtotal) do not appear in the dropdown and cannot be hidden.
-4. With all seven metric columns hidden the table still renders the five always-on columns and the grand Totals indicator — no empty or error state.</t>
+4. With all seven metric columns hidden the table still renders the five always-on columns and the grand Totals indicator — no empty or error state.
+5. Note for the tester: if you have more than one location in scope you will also see a Location column on the table that is in neither list. That is correct - it appears by itself and is not something you can switch on or off here.</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>SV-8637 (specs/sbr-sales-by-representative.md Story 20 S20-R1; S20-R2; S20-R3; S20-R6; S20-N1)</t>
+          <t>SV-8637 (SBR spec v15 2026-07-29 Story 20 S20-R1; S20-R2; S20-R3; S20-R6; S20-N1 — S20-R2/S20-R3 CLOSE the seven toggles and the five always-on columns; Location is automatic and in neither list [S21-R7])</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr"/>
@@ -7839,7 +7841,7 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R1; Story 17 S17-R3 (position))</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R1 + Story 17 S17-R3 (position) — S14-R1 CLOSES it in the spec's own words ("lists exactly four actions"); so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr"/>
@@ -7892,7 +7894,7 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (SBR spec Story 14 S14-R2; S14-R2a; Story 21 S21-R6; Story 22 S22-R4 + Locations: line in every export per Chris Ward msg 2026-07-29 [newest-wins])</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R2; S14-R2a; S14-R20 + Story 21 S21-R6 + Story 22 S22-R4 — all four downloads honour the filters; the full result set and the active order; S14-R20 = the "Locations:" line in every export)</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr"/>
@@ -8091,7 +8093,7 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R4; S14-R3a; S14-R11)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R3a; S14-R4; S14-R11 — S14-R11 CLOSES both PDF filenames verbatim ("deterministic") and S14-R4 closes the footer string; so the exact strings ARE the requirement)</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr"/>
@@ -8485,7 +8487,7 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-E2; §7)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-E2; §7 — 10k-row export cap; no truncated file; toast persists 120s; the toast STRING is the ONE suite-wide message ruled by Chris Ward 2026-07-31 Q2=A [newest-wins]; his SBR spec edit is pending)</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr"/>
@@ -8629,12 +8631,13 @@
           <t>1. The file downloads as "sales-representative-assignments.csv (the short form "rep" is gone from the file name — confirm the exact final file name in the build)".
 2. A success toast shows "Success" with the caption "Report downloaded." and auto-fades after 5 seconds.
 3. The CSV starts with a UTF-8 BOM and its headers, in order, are exactly: Customer Name, Sales Representative, Rep is active?.
-4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
+5. Note for the tester: this file has only those three columns even if you have several locations in scope. It is a separate customer-to-representative list, not one of the report's four downloads, so it has no Location column - do not fail it for that.</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>SV-8632 (specs/sbr-sales-by-representative.md Story 15 S15-R3; S15-R4; §7)</t>
+          <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R3; S15-R4; §7 — S15-R4 CLOSES the three headers; "Sales Rep"→"Sales Representative" per Chris Ward 2026-07-31 Q5 [newest-wins]; NOT one of the four report exports so S14-R20 adds no Location)</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr"/>
@@ -9343,24 +9346,25 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with a rep row showing a (N) count and — if arrangeable — an "(Inactive)" tag; a contrast-checking tool is available.</t>
+          <t>1. You are on the report with a rep row showing a (N) count and - if arrangeable - an "(Inactive)" tag.</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>1. Measure the contrast ratio of the subdued-grey (N) count and "(Inactive)" tag against the white body surface in light mode, and against the dark surface in dark mode.
+          <t>1. Read the subdued-grey (N) count and the "(Inactive)" tag in light mode, then switch to dark mode and read them again.
 2. Review how Inv. Hrs, the status badges, and the links convey their meaning.</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>1. The subdued grey meets at least WCAG AA contrast (4.5:1 or better) against the body surface in BOTH modes — the reduced font size does not drop it below that ratio.
-2. No information is conveyed by color alone: Inv. Hrs carries its +/- sign, status badges carry their text label, and links carry a hover/focus underline.</t>
+          <t>1. In BOTH light mode and dark mode the subdued-grey (N) count and the "(Inactive)" tag are easy to read against the surface behind them - the smaller text does not fade into the background.
+2. No information is conveyed by color alone: Inv. Hrs carries its +/- sign, status badges carry their text label, and links carry a hover/focus underline.
+3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can read the grey text easily in both modes, and only report it if you cannot. (The design rule behind this is WCAG AA contrast of at least 4.5:1, which the design and engineering team check with a contrast tool - not by hand.)</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>SV-8635 (specs/sbr-sales-by-representative.md Story 18 S18-R11; S18-R12)</t>
+          <t>SV-8635 (SBR spec v15 2026-07-29 Story 18 S18-R11; S18-R12 — subdued-grey (N) count and "(Inactive)" tag at ≥ 4.5:1 WCAG AA in both modes; nothing conveyed by colour alone; the ratio is a design-token property so the check is by-eye)</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr"/>
@@ -10193,7 +10197,7 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>Reports access without Inventory Reports View: entry shows; data denied</t>
+          <t>Ordinary reports access alone opens Parts Velocity and its export</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -10214,26 +10218,27 @@
       <c r="E202" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a user with the Manager or Office User role.
-2. That user's role does NOT have the Inventory Reports → View permission.</t>
+2. That user's role has the ordinary reports access turned on (the standard "can this person see reports" setting) and no other reports-related permission turned on.</t>
         </is>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
           <t>1. Open the Reports section and look for the Parts Velocity entry under Parts.
 2. Click the Parts Velocity entry.
-3. If any export control is reachable, try to export.</t>
+3. Use the export control on the report and download a file.</t>
         </is>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>1. The Parts Velocity navigation entry is still visible (the entry follows Reports-section access, not the report permission).
-2. On opening the report, the standard access-denied state is shown instead of data.
-3. The export is likewise denied - no file downloads.</t>
+          <t>1. The Parts Velocity entry is visible in the Reports navigation under Parts.
+2. Opening it shows the report data - not an access-denied screen.
+3. The export downloads.
+4. Note for the tester: for now ONE ordinary reports access opens all six of these new reports, and no report has a permission of its own. If an extra Parts or Inventory reports permission does exist and switching it OFF blocks this report or its export, that is wrong - mark this Failed and report it. If a separate per-report permission is ever added on purpose in a later release, this test will be updated first, so treat that as a planned change and not as a bug.</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>SV-8641 (specs/parts-velocity.md S1-N2; S1-R4)</t>
+          <t>SV-8641 (PV spec S1-N2; S1-R4 - RESCOPED 2026-08-03: the old "Reports access without Inventory Reports View" state cannot exist under one permission; Chris Ward Q2=A + "they can exist and not do anything"; QA lead "ONE permission FOR NOW")</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr"/>
@@ -10286,7 +10291,7 @@
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (PV spec S2-R1; S3-R5 - 'Catalogue' RENAMED to the exact label 'Special Order' [Type filter; Type column; export] per Chris Ward msg 2026-07-29 [newest-wins] [cf video P31])</t>
+          <t>SV-8642 (PV spec v4 2026-07-29 S2-R1; S3-R5 — S2-R1 CLOSES the three Type options and the Both default; 'Catalogue'→'Special Order' per Chris Ward 2026-07-29 [newest-wins])</t>
         </is>
       </c>
       <c r="I203" s="2" t="inlineStr"/>
@@ -10334,7 +10339,7 @@
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R2; §2 Out of Scope)</t>
+          <t>SV-8642 (PV spec v4 2026-07-29 S2-R2; §2 Out of Scope — S2-R2 CLOSES it in the spec's own words ("offering exactly these options") and rules out "All Time"; so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr"/>
@@ -10732,7 +10737,7 @@
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R11; S2-N1; §7)</t>
+          <t>SV-8642 (PV spec v4 2026-07-29 S2-R11; S2-N1; §7 — §7 CLOSES the empty-state string verbatim ("Empty bays" ... "Get Going!") as the standard reports no-data label; so the exact string IS the requirement)</t>
         </is>
       </c>
       <c r="I212" s="2" t="inlineStr"/>
@@ -11186,7 +11191,7 @@
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (specs/parts-velocity.md S3-R6)</t>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-R6 — S3-R6 CLOSES the set (exactly three columns: Units Sold; Demand; Turns / Yr) and quotes each description verbatim; so the closed set and the exact strings ARE the requirement)</t>
         </is>
       </c>
       <c r="I221" s="2" t="inlineStr"/>
@@ -12617,7 +12622,7 @@
       </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (specs/parts-velocity.md S6-R1)</t>
+          <t>SV-8646 (PV spec v4 2026-07-29 S6-R1 — S6-R1 CLOSES it in the spec's own words ("an export menu with two items ... Download (PDF) and Download (CSV)"); so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I250" s="2" t="inlineStr"/>
@@ -12665,7 +12670,7 @@
       </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (specs/parts-velocity.md S6-R2; §3 Key Decisions + Locations: line in every CSV/PDF export per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
+          <t>SV-8646 (PV spec v4 2026-07-29 S6-R2; S6-R11; §3 Key Decisions — both exports reflect the filters and search active at export time; S6-R11 = the "Locations:" line in both exports [Chris Ward 2026-07-29; newest-wins])</t>
         </is>
       </c>
       <c r="I251" s="2" t="inlineStr"/>
@@ -13007,7 +13012,7 @@
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (specs/parts-velocity.md S6-R9; S6-N1; §7 (casing note))</t>
+          <t>SV-8646 (PV spec v4 2026-07-29 S6-R9; S6-N1; §7 (casing note) — S6-R9/S6-N1 CLOSE the toast strings verbatim including the shipped UPPERCASE-success / lowercase-failure casing mix; so the exact strings ARE the requirement)</t>
         </is>
       </c>
       <c r="I258" s="2" t="inlineStr"/>
@@ -13189,18 +13194,19 @@
         <is>
           <t>1. Switch the application to dark mode.
 2. Look at the page background, toolbar, and cells.
-3. Check the grey ⓘ info icon against its cell background in dark mode, then again in light mode.</t>
+3. Look at the grey ⓘ info icon next to a column heading in dark mode, then switch back to light mode and look at it again.</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
           <t>1. The report supports dark mode: page background, toolbar, and cells use their dark-mode equivalents.
-2. The grey ⓘ info icon uses a token meeting at least a 3:1 contrast ratio against the cell background in BOTH light and dark mode.</t>
+2. In BOTH light mode and dark mode the grey ⓘ info icon is clearly visible against the cell behind it - you can see it at a glance without leaning in, and it does not disappear into the background.
+3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes. Only report it if the icon is hard to see. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>SV-8647 (specs/parts-velocity.md S7-R6)</t>
+          <t>SV-8647 (PV spec v4 2026-07-29 S7-R6 — dark-mode support + the grey info icon's colour token at ≥ 3:1 against the cell background in both modes; the ratio is a design-token property so the manual check is by-eye legibility)</t>
         </is>
       </c>
       <c r="I262" s="2" t="inlineStr"/>
@@ -13352,7 +13358,7 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>The backend denies report data AND export without Inventory Reports View</t>
+          <t>The back end serves report data and export on ordinary reports access</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
@@ -13372,7 +13378,7 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>1. You are signed in as a Reports-section user whose role lacks the Inventory Reports → View permission.
+          <t>1. You are signed in as a user whose role has the ordinary reports access turned on and no other reports-related permission turned on.
 2. Browser devtools (network tab) are open.</t>
         </is>
       </c>
@@ -13384,14 +13390,15 @@
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>1. The backend REFUSES the report data request - the user is denied the data (the UI shows the standard access-denied state).
-2. The backend likewise refuses the export request - no file is produced.
-3. Both loading and exporting are gated by the same Inventory Reports → View permission.</t>
+          <t>1. The back end returns the report data - the request is not refused.
+2. The back end returns the export file - the request is not refused.
+3. Both requests succeed with only the ordinary reports access turned on - nothing else had to be enabled.
+4. Note for the tester: if the back end refuses either request for a user who has the ordinary reports access, mark this Failed and report it. If an extra Parts or Inventory reports permission exists in the system it must not change these results - for now it is hidden from the screen and enforces nothing. A per-report permission added on purpose in a later release is a planned change, not a bug, and this test will be updated first.</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>SV-8641 (specs/parts-velocity.md S1-R4; S1-N2)</t>
+          <t>SV-8641 (PV spec S1-R4; S1-N2 - RESCOPED 2026-08-03; same driver as C30327: Chris Ward Q2=A "single Reports permission" + "they can exist and not do anything"; QA lead "ONE permission FOR NOW")</t>
         </is>
       </c>
       <c r="I266" s="2" t="inlineStr"/>
@@ -13828,7 +13835,7 @@
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (specs/technician-utilization.md S1-N2; S9-N2; S5-N1; S3-N1; §7)</t>
+          <t>SV-8648 (TU spec v5 2026-07-29 S1-N2; S3-N1; S5-N1; S9-N2; §7 — §7 CLOSES the no-data string verbatim ("Empty bays" ... "Get Going!") as the standard reports no-data label; so the exact string IS the requirement)</t>
         </is>
       </c>
       <c r="I275" s="2" t="inlineStr"/>
@@ -14730,29 +14737,30 @@
       </c>
       <c r="E294" s="2" t="inlineStr">
         <is>
-          <t>1. A technician clocked time on several (but not all) days of the range - including, for the pooling check, time at two selected locations on the same day.
-2. Browser devtools (network tab) are open for the on-demand check.</t>
+          <t>1. A technician clocked time on several (but not all) days of the range - including, for the pooling check, time at two selected locations on the same day.</t>
         </is>
       </c>
       <c r="F294" s="2" t="inlineStr">
         <is>
-          <t>1. Expand the technician's row and watch the network traffic.
-2. Read the day rows top to bottom.
-3. Look for rows on days the technician did not clock time.
-4. On the double-location day, count the rows for that date.</t>
+          <t>1. Before expanding anything, look at the technician's row - there are no day rows under it yet.
+2. Expand the technician's row and watch the data area as the day rows appear.
+3. Read the day rows top to bottom.
+4. Look for rows on days the technician did not clock time.
+5. On the double-location day, count the rows for that date.</t>
         </is>
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
           <t>1. One row appears for each day the technician clocked time in the range, in date order from earliest to latest.
-2. The day rows are fetched ON EXPAND (on demand) - they are not shipped with the initial report payload.
+2. The day rows are not there until you expand the row - they arrive at the moment you expand it (you may briefly see the standard loading indicator in that area), and the rest of the report does not reload.
 3. A day with no clocked time has NO row.
-4. With several locations selected, a day's row POOLS that day's hours across the selected locations - one day row per date, not one per location.</t>
+4. With several locations selected, a day's row POOLS that day's hours across the selected locations - one day row per date, not one per location.
+5. Note for the tester: you do not need developer tools for this test - just watch the screen.</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>SV-8651 (specs/technician-utilization.md S4-R2; S4-N1; S9-R4)</t>
+          <t>SV-8651 (TU spec v5 2026-07-29 S4-R2; S4-N1; S9-R4 — one row per clocked day in date order; load-on-expand; no row for an unclocked day; per-day pooling across selected locations; the back-end half is covered by C30449 in "TU - API")</t>
         </is>
       </c>
       <c r="I294" s="2" t="inlineStr"/>
@@ -14976,13 +14984,13 @@
       <c r="E299" s="2" t="inlineStr">
         <is>
           <t>1. Several technician rows are visible and the Summary row shows their totals.
-2. Browser devtools (network tab) are open.</t>
+2. Note the current date range so you can confirm it does not change.</t>
         </is>
       </c>
       <c r="F299" s="2" t="inlineStr">
         <is>
           <t>1. Note the Summary values, then deselect one technician in the Filter by Technician filter.
-2. Watch the network traffic and the Summary row.
+2. Watch the data area and the Summary row.
 3. Re-select the technician.</t>
         </is>
       </c>
@@ -14990,13 +14998,14 @@
         <is>
           <t>1. The deselected technician's row is hidden.
 2. The Summary row recalculates over the technicians that remain visible.
-3. NO reload happens - the technician filter works on screen only and does not change the date range or re-query the server.
-4. Re-selecting the technician shows the row again (and the Summary recalculates back).</t>
+3. The report does NOT reload - the technician filter works on screen only: the rows and the Summary update straight away, no loading indicator appears in the data area, and the date range does not change.
+4. Re-selecting the technician shows the row again (and the Summary recalculates back).
+5. Note for the tester: you do not need developer tools for this test - just watch the screen.</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
-          <t>SV-8652 (specs/technician-utilization.md S5-R3; S5-R4; S5-R5; §3; S5 context note)</t>
+          <t>SV-8652 (TU spec v5 2026-07-29 S5-R3; S5-R4; S5-R5 + §3 Key Decisions ("the technician filter works on screen only and does not reload the report"); S5 context note — the server half is covered by C30450 in "TU - API")</t>
         </is>
       </c>
       <c r="I299" s="2" t="inlineStr"/>
@@ -15571,12 +15580,13 @@
 2. Every download covers the location(s) currently selected in the location filter and the date range currently active on the report.
 3. With every technician selected, the download covers all technicians for the range at the selected location(s).
 4. Every download (each PDF and the CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
-5. Every download also mirrors the columns currently shown on screen — a column hidden in the Column Selection control is absent from the files, and a re-shown column comes back.</t>
+5. Every download also mirrors the columns currently shown on screen — a column hidden in the Column Selection control is absent from the files, and a re-shown column comes back.
+6. Note for the tester: when you have more than one location in scope, the files also carry a Location column even though it is not in the Column Selection control. That is correct - it appears by itself. With a single location in scope there is no Location column, and that is also correct.</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (TU spec v5 2026-07-29 S7-R8; S7-R9; S7-R10; S7-E1; S9-R8 — S7-R10 now says the downloads include the columns currently shown; mirroring the column selector)</t>
+          <t>SV-8654 (TU spec v5 2026-07-29 S7-R8; S7-R9; S7-R10; S7-R13; S7-E1; S9-R8 — downloads mirror the shown columns and the technician/location/date scope; S7-R13 = the "Locations:" line and the automatic Location column)</t>
         </is>
       </c>
       <c r="I311" s="2" t="inlineStr"/>
@@ -15766,7 +15776,7 @@
       </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (specs/technician-utilization.md Story 7 Error Handling; §7)</t>
+          <t>SV-8654 (TU spec v5 2026-07-29 Story 7 Error Handling + §7 notifications table — these CLOSE both strings verbatim ("Download started" / "Failed to download report"); Story 7 has no S-anchor for them so §7 is the closing reference)</t>
         </is>
       </c>
       <c r="I315" s="2" t="inlineStr"/>
@@ -16264,20 +16274,21 @@
         <is>
           <t>1. Switch the application to dark mode.
 2. Check each element: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and a "—" glyph.
-3. Measure the information icon's contrast against its background in dark mode, then in light mode.
+3. Look at the information icon in dark mode, then switch back to light mode and look at it again.
 4. Check the Total Hours link's underline/affordance and focus indicator in both modes.</t>
         </is>
       </c>
       <c r="G325" s="2" t="inlineStr">
         <is>
-          <t>1. The report supports dark mode: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and the "—" glyph all use dark-mode-legible colors meeting contrast.
-2. The information icon meets at least a 3:1 contrast ratio against its background in BOTH light and dark mode.
-3. The Total Hours link's non-color affordance and focus indicator apply in both modes.</t>
+          <t>1. The report supports dark mode: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and the "—" glyph are all clearly legible in dark mode.
+2. In BOTH light mode and dark mode the information icon is clearly visible against the background behind it - you can see it at a glance and it does not disappear into the background.
+3. The Total Hours link's non-color affordance and focus indicator apply in both modes.
+4. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes, and only report it if you cannot. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)</t>
         </is>
       </c>
       <c r="H325" s="2" t="inlineStr">
         <is>
-          <t>SV-8655 (specs/technician-utilization.md S8-R9; S8-R13; S8-R14)</t>
+          <t>SV-8655 (TU spec v5 2026-07-29 S8-R9; S8-R13; S8-R14 — dark-mode legibility of every named element; the info icon at ≥ 3:1 in both modes; the Total Hours link affordance/focus in both modes; the ratio is design-token-owned)</t>
         </is>
       </c>
       <c r="I325" s="2" t="inlineStr"/>
@@ -16425,7 +16436,7 @@
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (WIP spec Story 1 S1-R1; S1-R5 — Performance group; below the named anchor items per the PRD video 2026-07-30; S1-R5 = browser page title; access = the one ordinary reports permission per QA lead 2026-08-03)</t>
+          <t>SV-8657 (WIP spec v6 2026-07-29 Story 1 S1-R1; S1-R5 — S1-R5 CLOSES the page title verbatim; Performance group below the named anchor items per the PRD video 2026-07-30; access = the one ordinary reports permission per QA lead 2026-08-03)</t>
         </is>
       </c>
       <c r="I328" s="2" t="inlineStr"/>
@@ -16474,7 +16485,7 @@
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (specs/wip-work-in-progress.md Story 1 S1-R2; S1-R3; §3 Key Decisions (no on-screen status filter))</t>
+          <t>SV-8657 (WIP spec v6 2026-07-29 Story 1 S1-R2; S1-R3; §3 Key Decisions (no on-screen status filter) — S1-R2 CLOSES the four tab labels and their order verbatim; so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I329" s="2" t="inlineStr"/>
@@ -17106,7 +17117,7 @@
       </c>
       <c r="H342" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R6; Story 10 S10-R8)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R6 + Story 10 S10-R8 — S4-R6 CLOSES the five status labels verbatim ("Estimate" ... "Complete") and the label-not-colour rule; so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I342" s="2" t="inlineStr"/>
@@ -18048,7 +18059,7 @@
       </c>
       <c r="H361" s="2" t="inlineStr">
         <is>
-          <t>SV-8661 (specs/wip-work-in-progress.md Story 5 S5-R1; S5-R10)</t>
+          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R1; S5-R10 — S5-R1 CLOSES the seven figures and their order verbatim and S5-R10 closes the currency format; so the closed lists ARE the requirement)</t>
         </is>
       </c>
       <c r="I361" s="2" t="inlineStr"/>
@@ -19140,12 +19151,13 @@
           <t>1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total last.
 2. Both downloads honor the current date range and location filter, and include only the jobs left visible by the advisor, customer, and asset filters.
 3. Both downloads include a Totals row matching the on-screen Totals row for the tab.
-4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).</t>
+4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
+5. Note for the tester: when you have more than one location in scope, the files also carry the location column even though you cannot turn it on or off - and in the file it is headed "Branch", not "Location". Both of those are correct. With a single location in scope there is no such column, and that is also correct.</t>
         </is>
       </c>
       <c r="H383" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R2; S9-R3; S9-R4; S9-R10a — "Locations:" line in every CSV/PDF export per Chris Ward's 2026-07-29 message [NEWEST source; last-update-wins])</t>
+          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R2; S9-R3; S9-R4; S9-R10a + Story 7 S7-R13; S9-E1 — downloads mirror the shown columns; the filters and the Totals row; S9-R10a = the "Locations:" line; S7-R13/S9-E1 = the automatic "Branch" column)</t>
         </is>
       </c>
       <c r="I383" s="2" t="inlineStr"/>
@@ -19339,7 +19351,7 @@
       </c>
       <c r="H387" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R9)</t>
+          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R9 — S9-R9 CLOSES both file names verbatim including the "-2-" segment; so the exact strings ARE the requirement)</t>
         </is>
       </c>
       <c r="I387" s="2" t="inlineStr"/>
@@ -22686,12 +22698,13 @@
           <t>1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total Cost last.
 2. Both downloads honor the current date, category, vendor, location, and part-search filters, and apply the current sort.
 3. Both downloads include a totals row labeled "Totals" matching the on-screen totals (the full-filtered-set totals).
-4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).</t>
+4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
+5. Note for the tester: when you have more than one location in scope, the files also carry a Location column (between Vendor and Qty on Hand) even though it is not in the column-selection control. That is correct - it appears by itself. With a single location in scope there is no Location column, and that is also correct.</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
         <is>
-          <t>SV-8677 (specs/inventory-value.md Story 10 S10-R3; S10-R4; S10-R5; S10-R6 + Locations: line in every CSV/PDF export per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
+          <t>SV-8677 (IV spec v3 2026-07-29 Story 10 S10-R3; S10-R4; S10-R5; S10-R6; S10-R15 — downloads keep the shown columns and order; honour the filters; include the Totals row; S10-R15 = the "Locations:" line and the automatic Location column)</t>
         </is>
       </c>
       <c r="I456" s="2" t="inlineStr"/>
@@ -22837,7 +22850,7 @@
       </c>
       <c r="H459" s="2" t="inlineStr">
         <is>
-          <t>SV-8677 (specs/inventory-value.md Story 10 S10-R10)</t>
+          <t>SV-8677 (IV spec v3 2026-07-29 Story 10 S10-R10 — S10-R10 CLOSES both file names verbatim; so the exact strings ARE the requirement)</t>
         </is>
       </c>
       <c r="I459" s="2" t="inlineStr"/>

--- a/testrail-import/report-suite-v1-testrail-import.xlsx
+++ b/testrail-import/report-suite-v1-testrail-import.xlsx
@@ -828,7 +828,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>SV-8601 (SBC spec v12 2026-07-29 Story 2 S2-R1; S2-R2 — S2-R2 CLOSES the eleven-option list and its order itself; so the closed list IS the requirement; re-check this case whenever S2-R2 changes)</t>
+          <t>SV-8601 (SBC spec v13 2026-07-31 Story 2 S2-R1; S2-R2 — S2-R2 CLOSES the eleven-option list and its order itself; so the closed list IS the requirement; re-check this case whenever S2-R2 changes)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>SV-8602 (SBC spec v12 2026-07-29 Story 3 S3-R1; S3-R2; S3-R3; S3-R4; S3-R5; S3-R6 — S3-R2 CLOSES the list itself ("exactly three options ... in this order"); so the closed list IS the requirement)</t>
+          <t>SV-8602 (SBC spec v13 2026-07-31 Story 3 S3-R1; S3-R2; S3-R3; S3-R4; S3-R5; S3-R6 — S3-R2 CLOSES the list itself ("exactly three options ... in this order"); so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr"/>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>SV-8605 (SBC spec v12 2026-07-29 §2; §4 Terminology; Story 7 S7-R6; Story 11 S11-R1 — §2/S7-R6 CLOSE the financial-column list and its order; Location is an identifier column not a financial one [S4-R12; S20-R19] so it never enters this list)</t>
+          <t>SV-8605 (SBC spec v13 2026-07-31 §2; §4 Terminology; Story 7 S7-R6; Story 11 S11-R1 — §2/S7-R6 CLOSE the financial-column list and its order; Location is an identifier column not a financial one [S4-R12; S20-R19] so it never enters this list)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr"/>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>SV-8611 (SBC spec v12 2026-07-29 Story 13 S13-R1; S13-R2; S13-R3; S13-R4; S13-R7 — S13-R4 CLOSES the nine-toggle list and its order; Location is automatic and never a toggle [S4-R12; S4-R13])</t>
+          <t>SV-8611 (SBC spec v13 2026-07-31 Story 13 S13-R1; S13-R2; S13-R3; S13-R4; S13-R7 — S13-R4 CLOSES the nine-toggle list and its order; Location is automatic and never a toggle [S4-R12; S4-R13])</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr"/>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 S14-R1; S14-R2; S15-R1; S15-R2; S20-R16 — these CLOSE the four-item menu and its verbatim labels; menu reshaped + "Print" removed per Chris Ward 2026-07-29 [newest-wins])</t>
+          <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 S14-R1; S14-R2; S15-R1; S15-R2; S20-R16 — these CLOSE the four-item menu and its verbatim labels; menu reshaped + "Print" removed per Chris Ward 2026-07-29 [newest-wins])</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr"/>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>SV-8613 (SBC spec v12 2026-07-29 Story 15 S15-R7; S15-R8; S15-R9; S15-R10; S15-R11; S15-R14 + Story 4 S4-R13 — PDF header block; S15-R14/S4-R13 = the "Locations:" line in every export [Chris Ward 2026-07-29; newest-wins])</t>
+          <t>SV-8613 (SBC spec v13 2026-07-31 Story 15 S15-R7; S15-R8; S15-R9; S15-R10; S15-R11; S15-R14 + Story 4 S4-R13 — PDF header block; S15-R14/S4-R13 = the "Locations:" line in every export [Chris Ward 2026-07-29; newest-wins])</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr"/>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613; SV-8603 (SBC spec v12 2026-07-29 S14-R1; S14-R2; S14-R4; S15-R1; S15-R2; S15-R4; S15-R5; S4-R13 — the four-item Summary/Expanded menu; the Summary column list; the automatic Location column in every export)</t>
+          <t>SV-8612; SV-8613; SV-8603 (SBC spec v13 2026-07-31 S14-R1; S14-R2; S14-R4; S15-R1; S15-R2; S15-R4; S15-R5; S4-R13 — the four-item Summary/Expanded menu; the Summary column list; the automatic Location column in every export)</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr"/>

--- a/testrail-import/report-suite-v1-testrail-import.xlsx
+++ b/testrail-import/report-suite-v1-testrail-import.xlsx
@@ -21382,7 +21382,7 @@
       </c>
       <c r="F429" s="2" t="inlineStr">
         <is>
-          <t>1. Note the totals row's Qty on Hand, Margin, Total Sell, and Total Cost on page 1.
+          <t>1. Note the totals row's Qty, Margin, Total Sell, and Total Cost on page 1.
 2. Move to page 2 and read the totals row again.
 3. Cross-check the Total Cost total against a known seeded subset (filter down to a handful of ZZAUTOTEST parts whose values you can sum by hand).
 4. Select one Category and read the totals row; clear it, select one Vendor; clear it, type a part search matching a subset — reading the totals row each time (from a later page too if the set spans pages).</t>
@@ -21390,9 +21390,9 @@
       </c>
       <c r="G429" s="2" t="inlineStr">
         <is>
-          <t>1. The totals row sums Qty on Hand, Margin, Total Sell, and Total Cost across the FULL filtered result set — every qualifying row for the current Date, Location, Category, Vendor, and part-search selection, not only the rows on the visible page.
+          <t>1. The totals row sums Qty, Margin, Total Sell, and Total Cost across the FULL filtered result set — every qualifying row for the current Date, Location, Category, Vendor, and part-search selection, not only the rows on the visible page.
 2. The totals are identical on every page (they do not change as you page).
-3. A hand sum of a small seeded subset matches the totals row. On a large set the totals can differ from a hand sum of the displayed values by a few cents, because the server sums the unrounded values - that is correct, not a defect.
+3. The hand-summed subset matches the server-computed totals to the cent.
 4. After each filter change the totals row recomputes on the server over the full filtered set, independent of which page is shown.</t>
         </is>
       </c>
@@ -22658,7 +22658,7 @@
       <c r="F455" s="2" t="inlineStr">
         <is>
           <t>1. Sort by Total Cost and check the order of values like $900.00 vs $1,100.00.
-2. Sort by Qty on Hand and check the numeric order.
+2. Sort by Qty and check the numeric order.
 3. Sort by Description (or Vendor) and check how differently-cased values order.</t>
         </is>
       </c>

--- a/testrail-import/report-suite-v1-testrail-import.xlsx
+++ b/testrail-import/report-suite-v1-testrail-import.xlsx
@@ -528,7 +528,9 @@
 2. Clicking it opens the Sales By Customer report in the main content area.
 3. The page title reads "Sales By Customer."
 4. The browser tab title reads "Sales By Customer - Report | ShopView".
-5. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.</t>
+5. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-R1, S1-R3, S1-R4).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -577,7 +579,9 @@
           <t>1. The "Sales By Customer" entry is visible in the Reports navigation.
 2. The report opens and shows its data.
 3. Ordinary reports access alone is enough — this report does NOT need a permission of its own.
-4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.</t>
+4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-R2).</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -627,7 +631,9 @@
           <t>1. "Sales By Customer" does not appear in the Reports navigation.
 2. Opening the report by direct link does not show the report (the application blocks it with its standard access-denied handling).
 3. The gate is the ordinary reports access — there is no separate Sales By Customer permission to remove.
-4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.</t>
+4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-N1).</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -675,12 +681,14 @@
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1. The destination page shows the application's standard access-denied state.
-2. Pressing back returns you to the Sales By Customer report.</t>
+2. Pressing back returns you to the Sales By Customer report.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S9-N2).</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>SV-8607 (specs/sbc-sales-by-customer.md Story 9 S9-N2)</t>
+          <t>SV-8607 (SBC spec v13 2026-07-31 Story 9 S9-N2)</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr"/>
@@ -727,12 +735,14 @@
           <t>1. The administrator's filter lists every location in the organization.
 2. The non-administrator's filter lists only the locations assigned to them.
 3. A requested location the user does not have access to is ignored — the report does NOT widen to the whole organization.
-4. The report data never includes invoices from a location the user does not have access to.</t>
+4. The report data never includes invoices from a location the user does not have access to.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R7, S4-R8, S4-R9, S4-N1).</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>SV-8603 (specs/sbc-sales-by-customer.md Story 4 S4-R7; S4-R8; S4-R9; S4-N1)</t>
+          <t>SV-8603 (SBC spec v13 2026-07-31 Story 4 S4-R7; S4-R8; S4-R9; S4-N1)</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr"/>
@@ -776,7 +786,9 @@
         <is>
           <t>1. There is NO "Sales By Customer" permission anywhere in the list for an administrator to switch on or off.
 2. The only reports permission offered is the ordinary reports access, and that one covers all six of the new reports.
-3. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.</t>
+3. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-R2).</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -823,7 +835,9 @@
         <is>
           <t>1. A date range picker is visible in the report toolbar.
 2. It offers eleven options, in this order: Today, Yesterday, This Week, Last Week, This Month, Last Month, This Year, Last Year, This Quarter, Last Quarter, Custom.
-3. There is no "All Time" option.</t>
+3. There is no "All Time" option.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R1, S2-R2).</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -869,14 +883,16 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1. Choosing "Custom" opens a date-picker dialog for a start and end date.
+          <t>1. The date range picker shows a month calendar inside it — that is how a custom start and end date are chosen on this build. There is no separate "Custom" item to choose.
 2. A range of 366 days or fewer applies normally.
-3. A range wider than 366 days cannot be applied — the report prevents the selection rather than loading the wider range.</t>
+3. A range wider than 366 days cannot be applied — the report prevents the selection rather than loading the wider range.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R3, S2-R4, S2-N2).</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>SV-8601 (specs/sbc-sales-by-customer.md Story 2 S2-R3; S2-R4; S2-N2)</t>
+          <t>SV-8601 (SBC spec v13 2026-07-31 Story 2 S2-R3; S2-R4; S2-N2)</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr"/>
@@ -918,12 +934,14 @@
       <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1. The chosen date range value is written into the page link.
-2. Opening that link in a browser with no saved view for this report restores the sender's date range.</t>
+2. Opening that link in a browser with no saved view for this report restores the sender's date range.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R6, S2-R9).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>SV-8601 (specs/sbc-sales-by-customer.md Story 2 S2-R6; S2-R9 (context))</t>
+          <t>SV-8601 (SBC spec v13 2026-07-31 Story 2 S2-R6; S2-R9 (context))</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr"/>
@@ -970,7 +988,9 @@
 2. Under "Service only," every invoice shown has a number starting with S; parts invoices are gone and all counts/totals reflect only S invoices.
 3. Under "Parts only," every invoice shown has a number starting with P; service invoices are gone and all counts/totals reflect only P invoices.
 4. With "Parts &amp; Service" selected, no product-type filter is applied — both S and P invoices are included and counts/totals cover both.
-5. The whole invoice is classified by its number prefix — there is no per-line-item split.</t>
+5. The whole invoice is classified by its number prefix — there is no per-line-item split.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6).</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1021,7 +1041,9 @@
 2. It lists the locations the signed-in user has access to.
 3. An "All locations" option is pinned to the top.
 4. Activating "All locations" selects every listed location at once; activating it again clears them all at once.
-5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's data.</t>
+5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's data.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R1, S4-R2, S4-R3); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1073,7 +1095,9 @@
 2. Adding a second location adds that location's invoices to the rows and totals.
 3. With "All locations," the report includes data from every location the user has access to.
 4. With "All locations" active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
-5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).</t>
+5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R5, S4-R6); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1119,8 +1143,7 @@
 4. Expand to an invoice row and read its Location cell.
 5. Open the column selector and look for Location in the list.
 6. Narrow the Location filter to a single location and read the headers again.
-7. Change the Location selection between one location, several, and "All locations", watching the filter control's width.
-8. With more than one location still selected, download all four files from the download menu (Summary and Expanded View, PDF and CSV) and read the columns in each one.</t>
+7. With more than one location still selected, download all four files from the download menu (Summary and Expanded View, PDF and CSV) and read the columns in each one.</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1131,13 +1154,14 @@
 4. An invoice row always shows its own exact location — never "Multiple".
 5. Location is NOT offered in the column selector — it appears and disappears on its own, following the location scope.
 6. With a single location in scope the Location column is hidden and the surrounding columns close up with no gap.
-7. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
-8. Every one of the four downloads also contains the Location column, in the same position it holds on screen, showing the same values you just read: a location name on a row whose invoices are all at one location, "Multiple" on a row that aggregates more than one, and the invoice's own location on an invoice row. (Exactly where the column sits inside each file is confirmed in the build.)</t>
+7. Every one of the four downloads also contains the Location column, in the same position it holds on screen, showing the same values you just read: a location name on a row whose invoices are all at one location, "Multiple" on a row that aggregates more than one, and the invoice's own location on an invoice row. (Exactly where the column sits inside each file is confirmed in the build.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R12, S4-R12a, S4-R13, S20-R19).</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>SV-8603; SV-8612; SV-8613 (SBC spec v12 2026-07-29 S4-R12; S4-R12a; S4-R13; S20-R19 — per-row Location column with automatic visibility; "Multiple" on aggregating rows; S4-R13 = the same column in every export)</t>
+          <t>SV-8603; SV-8612; SV-8613 (SBC spec v13 2026-07-31 S4-R12; S4-R12a; S4-R13; S20-R19 — per-row Location column with automatic visibility; "Multiple" on aggregating rows; S4-R13 = the same column in every export)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr"/>
@@ -1181,12 +1205,14 @@
           <t>1. A Customer filter labeled "Customer" sits between the Product Type filter and the Location filter.
 2. The control carries a search (magnifier) icon marking it as searchable.
 3. Before typing, the dropdown shows the pinned all/clear control at the top and a "Search customers…" hint; individual customers are revealed by typing.
-4. The hint yields to the typed query while you are searching.</t>
+4. The hint yields to the typed query while you are searching.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R1, S18-R2).</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R1; S18-R2)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R1; S18-R2)</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr"/>
@@ -1230,12 +1256,14 @@
         <is>
           <t>1. As you type, customers whose names contain the typed text appear in the list — matching is case-insensitive and matches anywhere in the name (a "contains" match, not starts-with).
 2. The list is scoped to the active date range, Product Type, and location.
-3. A selected customer is shown with a checkmark.</t>
+3. A selected customer is shown with a checkmark.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R2).</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R2)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R2)</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr"/>
@@ -1279,12 +1307,14 @@
           <t>1. In the all-customers state the pinned control reads "Clear all"; activating it clears the selection to an empty set.
 2. When the filter is NOT in the all-customers state the pinned control reads "All customers"; activating it puts the filter back in the all-customers state.
 3. The control is pinned to the top of the dropdown in both states.
-4. After "Clear all": the report shows the empty-state message "No sales data found for the selected filters.", the totals row shows zeros, and the collapsed label reads "None."</t>
+4. After "Clear all": the report shows the empty-state message "No sales data found for the selected filters.", the totals row shows zeros, and the collapsed label reads "None."
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R3, S18-N1, S17-E1).</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R3; S18-N1; S17-E1)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R3; S18-N1; S17-E1)</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr"/>
@@ -1331,12 +1361,14 @@
           <t>1. The Customer filter's collapsed label reads "All customers."
 2. The report shows every customer matching the other active filters.
 3. The all-customers state is an explicit state — while it is active, any customer that appears later (new data) is included automatically.
-4. After the filter change the filter stays in the all-customers state (label still "All customers") and every customer matching the new filters is included — including the newly-appearing one, with no manual re-selection.</t>
+4. After the filter change the filter stays in the all-customers state (label still "All customers") and every customer matching the new filters is included — including the newly-appearing one, with no manual re-selection.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R4, S18-R5, S18-R9, S18-E1).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R4; S18-R5; S18-R9; S18-E1)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R4; S18-R5; S18-R9; S18-E1)</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr"/>
@@ -1381,12 +1413,14 @@
           <t>1. With an empty selection the collapsed label reads "None."
 2. With exactly one customer selected the label shows that customer's name.
 3. With more than one selected the label reads "N selected" where N is the number of selected customers (for example "3 selected").
-4. While typing, the field shows the query text instead of the summary label; the summary label returns when the query is cleared or the field loses focus.</t>
+4. While typing, the field shows the query text instead of the summary label; the summary label returns when the query is cleared or the field loses focus.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R5).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R5)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R5)</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr"/>
@@ -1429,12 +1463,14 @@
         <is>
           <t>1. The report shows only the two selected customers.
 2. The table refreshes as a fresh first page of results.
-3. The totals row updates to cover only the selected customers' matching invoices.</t>
+3. The totals row updates to cover only the selected customers' matching invoices.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R5, S18-R11).</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R5; S18-R11)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R5; S18-R11)</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr"/>
@@ -1478,12 +1514,14 @@
           <t>1. Customer A (still present in the new results) stays selected and is shown.
 2. Customer B (no longer present) is dropped from the selection and not shown; it must be re-selected to appear if it later returns.
 3. Customer C (newly present) is NOT auto-selected and is not shown.
-4. The Customer filter selection itself is not cleared by the date change.</t>
+4. The Customer filter selection itself is not cleared by the date change.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R9, S18-E1).</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R9; S18-E1)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R9; S18-E1)</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr"/>
@@ -1527,13 +1565,16 @@
         <is>
           <t>1. The customer occupies exactly one summary row at the top level of the table.
 2. The customer's name is shown at the start of the row, followed by the number of contributing invoices in parentheses — for example, Acme Corp (5).
-3. The count is rendered in color #616161 at font-weight 600, the same font size as the name.
-4. The count reflects the active date range, Product Type, and location — it drops when the range is narrowed; it is not a lifetime count.</t>
+3. The count is the same size as the customer name next to it, in a slightly softer grey, and is easy to read.
+4. The count reflects the active date range, Product Type, and location — it drops when the range is narrowed; it is not a lifetime count.
+5. Note for the tester: you do not need to measure anything and you do not need any tool for item 3. Just say whether the count looks the right size and is easy to read, and only report it if it looks obviously wrong. (The exact colour and weight behind this are design-token values the design and engineering team check with their own tooling.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-R1, S7-R2, S7-R3, S7-R4, S7-R5).</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>SV-8605 (specs/sbc-sales-by-customer.md Story 7 S7-R1; S7-R2; S7-R3; S7-R4; S7-R5)</t>
+          <t>SV-8605 (SBC spec v13 2026-07-31 Story 7 S7-R1; S7-R2; S7-R3; S7-R4; S7-R5)</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr"/>
@@ -1574,12 +1615,14 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1. The customer is not shown — there are no zero-value placeholder rows.</t>
+          <t>1. The customer is not shown — there are no zero-value placeholder rows.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-N1).</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>SV-8605 (specs/sbc-sales-by-customer.md Story 7 S7-N1)</t>
+          <t>SV-8605 (SBC spec v13 2026-07-31 Story 7 S7-N1)</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr"/>
@@ -1627,12 +1670,14 @@
 4. The Date cell is blank on asset rows.
 5. Asset rows are indented one level under the customer.
 6. Each chevron toggles back to collapsed on a second activation.
-7. Collapsing customer A does not affect customer B's expansion; each asset's expansion state is likewise independent.</t>
+7. Collapsing customer A does not affect customer B's expansion; each asset's expansion state is likewise independent.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R1, S8-R2, S8-R5, S8-R5a, S8-R5b, S8-R5c, S8-R15).</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R1; S8-R2; S8-R5; S8-R5a; S8-R5b; S8-R5c; S8-R15)</t>
+          <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R1; S8-R2; S8-R5; S8-R5a; S8-R5b; S8-R5c; S8-R15)</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr"/>
@@ -1674,12 +1719,14 @@
         <is>
           <t>1. The invoice detail rows for that asset appear, indented one level deeper than the asset row.
 2. Each detail row shows the invoice number (as a link), the invoice date, and the per-invoice Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, and Subtotal.
-3. The invoice date shows in the format "Mon DD YYYY" — for example, May 14 2026.</t>
+3. The invoice date shows in the format "Mon DD YYYY" — for example, May 14 2026.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R4, S8-R12, S8-R12a, S20-R14).</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R4; S8-R12; S8-R12a; Story 20 S20-R14)</t>
+          <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R4; S8-R12; S8-R12a; Story 20 S20-R14)</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr"/>
@@ -1721,12 +1768,14 @@
       <c r="G26" s="2" t="inlineStr">
         <is>
           <t>1. Invoices referencing the same vehicle record (same vehicle id) group into ONE asset row — no duplicate rows for the same vehicle.
-2. An older invoice with no vehicle id on file groups by the invoice's own stored vehicle snapshot instead.</t>
+2. An older invoice with no vehicle id on file groups by the invoice's own stored vehicle snapshot instead.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R3).</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R3)</t>
+          <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R3)</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr"/>
@@ -1768,12 +1817,14 @@
         <is>
           <t>1. The customer's real asset rows are ordered A→Z by their label, case-insensitive.
 2. The no-vehicle work collects under a single row labeled "Parts Sales," always sorted last among that customer's assets.
-3. Changing the column sort does not change the asset order — assets stay A→Z with "Parts Sales" last.</t>
+3. Changing the column sort does not change the asset order — assets stay A→Z with "Parts Sales" last.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R6, S8-R6a, S10-R6).</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R6; S8-R6a; Story 10 S10-R6)</t>
+          <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R6; S8-R6a; Story 10 S10-R6)</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr"/>
@@ -1816,12 +1867,14 @@
         <is>
           <t>1. With at least one visible customer collapsed, the header chevron shows the "expand" icon and its tooltip reads "Expand all."
 2. Clicking it expands every customer on the current page in one action — it acts on the currently visible customers only, not the whole result set.
-3. With all visible customers expanded, the icon switches to "collapse" and the tooltip reads "Collapse all"; clicking collapses them all.</t>
+3. With all visible customers expanded, the icon switches to "collapse" and the tooltip reads "Collapse all"; clicking collapses them all.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R16, S8-R17, S8-R18, S8-R19).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R16; S8-R17; S8-R18; S8-R19)</t>
+          <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R16; S8-R17; S8-R18; S8-R19)</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr"/>
@@ -1865,12 +1918,14 @@
         <is>
           <t>1. Typing in the Customer filter's type-ahead only narrows the dropdown list — the expanded table rows stay expanded.
 2. A change that re-fetches customer rows (date range, Product Type, location, Customer selection, or sort) collapses all expanded rows.
-3. While the re-fetch is in flight the table shows the standard loading state; when it clears, the page shows the first page of the newly ordered set — the customers on the page can change.</t>
+3. While the re-fetch is in flight the table shows the standard loading state; when it clears, the page shows the first page of the newly ordered set — the customers on the page can change.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R20, S8-R21, S10-R8a, S10-R8b, S10-R8c).</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R20; S8-R21; Story 10 S10-R8a; S10-R8b; S10-R8c)</t>
+          <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R20; S8-R21; Story 10 S10-R8a; S10-R8b; S10-R8c)</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr"/>
@@ -1911,12 +1966,14 @@
       <c r="G30" s="2" t="inlineStr">
         <is>
           <t>1. The single-invoice asset expands and shows exactly one invoice detail row.
-2. Customer B shows a single "Parts Sales" row and no vehicle rows.</t>
+2. Customer B shows a single "Parts Sales" row and no vehicle rows.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-E1, S8-E2).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-E1; S8-E2)</t>
+          <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-E1; S8-E2)</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr"/>
@@ -1956,12 +2013,14 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1. The no-vehicle S invoice appears under that customer's "Parts Sales" row — the bucket collects work by the ABSENCE of a vehicle, not by the invoice-number prefix.</t>
+          <t>1. The no-vehicle S invoice appears under that customer's "Parts Sales" row — the bucket collects work by the ABSENCE of a vehicle, not by the invoice-number prefix.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-E3).</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-E3)</t>
+          <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-E3)</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr"/>
@@ -2005,12 +2064,14 @@
         <is>
           <t>1. The reversed/voided invoice never appears as an invoice row.
 2. It is excluded from the customer's "(N)" count and from every row total, regardless of the Product Type filter.
-3. The customer/asset totals drop by exactly that invoice's amounts.</t>
+3. The customer/asset totals drop by exactly that invoice's amounts.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-R7, S7-N2).</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>SV-8605 (specs/sbc-sales-by-customer.md Story 7 S7-R7; S7-N2; §3 Key Decisions)</t>
+          <t>SV-8605 (SBC spec v13 2026-07-31 Story 7 S7-R7; S7-N2; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr"/>
@@ -2046,7 +2107,7 @@
         <is>
           <t>1. Compare the columns of a customer row, an asset row, an invoice row, and the totals row left to right.
 2. Look at the Date cell on the customer and asset rows.
-3. Inspect the font weights on a customer summary row (dev tools).</t>
+3. Look at a customer summary row and compare how heavy its text looks with the invoice rows beneath it.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2054,12 +2115,15 @@
           <t>1. Every row type — customer, asset, invoice, totals — renders the same columns in the same left-to-right order.
 2. A cell with no value for its row (for example the Date cell on a customer or asset row) is left blank and keeps its column position; no value moves into another column.
 3. The Date cell on the customer summary row is blank.
-4. Every cell on a customer summary row uses font-weight 600, except the Subtotal cell which uses font-weight 700.</t>
+4. A customer summary row reads as heavier than the invoice rows under it, and its Subtotal cell is the heaviest cell on that row.
+5. Note for the tester: you do not need to measure anything and you do not need any tool for item 4. Just say whether the summary row stands out from the invoice rows and whether its Subtotal looks the boldest, and only report it if it looks obviously wrong. (The exact weights behind this are design-token values the design and engineering team check with their own tooling.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-R8, S7-R9, S7-R10, S7-R15, S7-R16).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>SV-8605 (specs/sbc-sales-by-customer.md Story 7 S7-R8; S7-R9; S7-R10; S7-R15; S7-R16)</t>
+          <t>SV-8605 (SBC spec v13 2026-07-31 Story 7 S7-R8; S7-R9; S7-R10; S7-R15; S7-R16)</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr"/>
@@ -2102,7 +2166,9 @@
 2. Asset (b) (no VIN) is identified by its Unit # instead.
 3. Asset (c) (no VIN or Unit #) is identified by its plate instead.
 4. For asset (d) (no VIN, Unit #, or plate), note what the label shows - what stands in when all three are missing is confirmed in the build (the older rule showed "Unknown Asset").
-5. Note whether the year/make/model text still appears anywhere in the row - the update says the VIN identifier REPLACES the year/make/model label; confirm the exact rendering in the build.</t>
+5. Note whether the year/make/model text still appears anywhere in the row - the update says the VIN identifier REPLACES the year/make/model label; confirm the exact rendering in the build.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R7, S8-R8, S8-R9, S8-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2149,12 +2215,14 @@
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>1. The duplicate labels are suffixed " (#1)" and " (#2)" (and so on for more duplicates).
-2. The numbering is fixed and repeatable — after a reload the same vehicle keeps the same number.</t>
+2. The numbering is fixed and repeatable — after a reload the same vehicle keeps the same number.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R11).</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R11)</t>
+          <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R11)</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2196,12 +2264,14 @@
         <is>
           <t>1. Each invoice number on a detail row is a clickable link that opens in the SAME browser tab (no new tab).
 2. A service invoice opens the associated work order's Finance tab.
-3. A parts invoice opens the associated part sale's Part Requests tab.</t>
+3. A parts invoice opens the associated part sale's Part Requests tab.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S9-R1, S9-R2, S9-R2a, S9-R2b).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>SV-8607 (specs/sbc-sales-by-customer.md Story 9 S9-R1; S9-R2; S9-R2a; S9-R2b)</t>
+          <t>SV-8607 (SBC spec v13 2026-07-31 Story 9 S9-R1; S9-R2; S9-R2a; S9-R2b)</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr"/>
@@ -2245,12 +2315,14 @@
         <is>
           <t>1. Before navigating, the active date range and Product Type are written to the page link.
 2. Pressing back returns to the report with its filters, sort, and columns restored exactly as set.
-3. Expanded rows are shown collapsed again — expansion is not restored (this is the specified behavior, not a defect).</t>
+3. Expanded rows are shown collapsed again — expansion is not restored (this is the specified behavior, not a defect).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S9-R3, S9-R4).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>SV-8607 (specs/sbc-sales-by-customer.md Story 9 S9-R3; S9-R4)</t>
+          <t>SV-8607 (SBC spec v13 2026-07-31 Story 9 S9-R3; S9-R4)</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr"/>
@@ -2293,12 +2365,14 @@
           <t>1. The customer name on the summary row is plain text, not a link.
 2. The invoice number link is shown in the application's primary color at rest, on hover, and after it has been clicked.
 3. The link has no underline at rest, on hover, or after it has been clicked.
-4. The link never recolors to the browser's visited-link (purple) color.</t>
+4. The link never recolors to the browser's visited-link (purple) color.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S9-R5, S9-R6, S9-R7, S9-R8).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>SV-8607 (specs/sbc-sales-by-customer.md Story 9 S9-R5; S9-R6; S9-R7; S9-R8)</t>
+          <t>SV-8607 (SBC spec v13 2026-07-31 Story 9 S9-R5; S9-R6; S9-R7; S9-R8)</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -2340,12 +2414,14 @@
       <c r="G39" s="2" t="inlineStr">
         <is>
           <t>1. The destination page shows the application's standard "not found" state.
-2. Pressing back returns you to the report.</t>
+2. Pressing back returns you to the report.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S9-N1).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>SV-8607 (specs/sbc-sales-by-customer.md Story 9 S9-N1)</t>
+          <t>SV-8607 (SBC spec v13 2026-07-31 Story 9 S9-N1)</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -2390,12 +2466,14 @@
         <is>
           <t>1. Every column is sortable except the chevron column.
 2. Text columns sort alphabetically; numeric columns sort by value (not as text).
-3. Sorting reorders only the customer summary rows — asset rows keep their own order (A→Z with "Parts Sales" last) and invoice rows keep their order under their asset.</t>
+3. Sorting reorders only the customer summary rows — asset rows keep their own order (A→Z with "Parts Sales" last) and invoice rows keep their order under their asset.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S10-R1, S10-R2, S10-R6).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>SV-8608 (specs/sbc-sales-by-customer.md Story 10 S10-R1; S10-R2; S10-R6)</t>
+          <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R1; S10-R2; S10-R6)</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr"/>
@@ -2437,12 +2515,14 @@
       <c r="G41" s="2" t="inlineStr">
         <is>
           <t>1. On first load, rows are ordered by Customer name, ascending, case-insensitive (a lower-case "acme" sorts by letter, not after all capitals).
-2. Clicking a column header replaces the default with that column's sort.</t>
+2. Clicking a column header replaces the default with that column's sort.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S10-R4, S10-R7).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>SV-8608 (specs/sbc-sales-by-customer.md Story 10 S10-R4; S10-R7)</t>
+          <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R4; S10-R7)</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -2483,12 +2563,14 @@
       <c r="G42" s="2" t="inlineStr">
         <is>
           <t>1. Ascending: the em-dash (missing) row sorts to the bottom.
-2. Descending: the em-dash row sorts to the top.</t>
+2. Descending: the em-dash row sorts to the top.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S10-R3).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>SV-8608 (specs/sbc-sales-by-customer.md Story 10 S10-R3)</t>
+          <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R3)</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr"/>
@@ -2529,12 +2611,14 @@
       <c r="G43" s="2" t="inlineStr">
         <is>
           <t>1. Customer rows order by each customer's most recent invoice date in the current view.
-2. The Date cells on customer rows stay blank — the sort still works.</t>
+2. The Date cells on customer rows stay blank — the sort still works.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S10-R5).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>SV-8608 (specs/sbc-sales-by-customer.md Story 10 S10-R5)</t>
+          <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R5)</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr"/>
@@ -2578,7 +2662,9 @@
           <t>1. The financial columns appear in this order: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin % — with Subtotal as the rightmost column.
 2. Subtotal = Labor Invoiced + Parts Invoiced + Shop Supplies, before tax.
 3. Labor Margin = Labor Invoiced minus labor cost; Parts Margin = Parts Invoiced minus parts cost.
-4. Margin = Labor Margin + Parts Margin — it does NOT include any Shop Supplies amount (shop supplies add to Subtotal but add no profit to Margin).</t>
+4. Margin = Labor Margin + Parts Margin — it does NOT include any Shop Supplies amount (shop supplies add to Subtotal but add no profit to Margin).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-R6, S11-R1, S4-R12, S20-R19).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2627,12 +2713,14 @@
           <t>1. Margin % shows the row's Margin divided by its Subtotal, times 100, to one decimal with a percent sign — for example, 64.7%.
 2. When the row's Subtotal is zero or below, the Margin % cell shows an em dash (—).
 3. Margin % is monochrome — no green or red coloring.
-4. The same calculation and format apply to customer rows, asset rows, and invoice rows.</t>
+4. The same calculation and format apply to customer rows, asset rows, and invoice rows.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-R11, S7-R12, S7-R13, S7-R14).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>SV-8605 (specs/sbc-sales-by-customer.md Story 7 S7-R11; S7-R12; S7-R13; S7-R14)</t>
+          <t>SV-8605 (SBC spec v13 2026-07-31 Story 7 S7-R11; S7-R12; S7-R13; S7-R14)</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr"/>
@@ -2677,12 +2765,14 @@
 3. A positive value shows a leading + sign in the application's standard positive (green) color — for example, +1.5.
 4. A negative value shows a leading - sign in the standard negative (red) color — for example, -1.5.
 5. A zero/break-even value shows 0.0 in the default text color.
-6. The same calculation, label, format, and coloring apply on customer, asset, and invoice rows.</t>
+6. The same calculation, label, format, and coloring apply on customer, asset, and invoice rows.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S12-R1, S12-R2, S12-R3, S12-R4, S12-R5, S12-R6).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>SV-8610 (specs/sbc-sales-by-customer.md Story 12 S12-R1; S12-R2; S12-R3; S12-R4; S12-R5; S12-R6)</t>
+          <t>SV-8610 (SBC spec v13 2026-07-31 Story 12 S12-R1; S12-R2; S12-R3; S12-R4; S12-R5; S12-R6)</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr"/>
@@ -2724,12 +2814,14 @@
         <is>
           <t>1. A customer, asset, or invoice with no labor shows 0.0 in the default color — never blank, "N/A," an em dash, or omitted.
 2. A value that rounds to 0.0 (for example +0.04) is shown as 0.0 in the default text color (not +0.0 in green).
-3. A negative value shows a minus sign and one decimal — for example, -0.5.</t>
+3. A negative value shows a minus sign and one decimal — for example, -0.5.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S12-N1, S12-E1, S12-E2).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>SV-8610 (specs/sbc-sales-by-customer.md Story 12 S12-N1; S12-E1; S12-E2)</t>
+          <t>SV-8610 (SBC spec v13 2026-07-31 Story 12 S12-N1; S12-E1; S12-E2)</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -2772,12 +2864,14 @@
         <is>
           <t>1. An asset's invoice subtotals sum exactly to that asset's row total.
 2. A customer's asset subtotals sum exactly to the customer's row total.
-3. This holds for every financial column, not only Subtotal.</t>
+3. This holds for every financial column, not only Subtotal.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R13).</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R13)</t>
+          <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R13)</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr"/>
@@ -2820,13 +2914,15 @@
         <is>
           <t>1. Subtotal is the rightmost column in the table.
 2. It stays visible pinned at the right edge while the table scrolls horizontally.
-3. Subtotal values are rendered at font-weight 700 on the header, every customer/asset/invoice row, and the totals row.
-4. This holds regardless of permission, data, filters, or sort — the Subtotal column is always present, pinned, and bold.</t>
+3. Subtotal values are shown in bold on the header, on every customer, asset and invoice row, and on the totals row.
+4. Check it still holds after two changes: narrow the date range so fewer rows match, then sort by a different column. Subtotal stays the rightmost column, stays pinned, and stays bold both times.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S11-R1, S11-R2, S11-R3, S11-N1).</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>SV-8609 (specs/sbc-sales-by-customer.md Story 11 S11-R1; S11-R2; S11-R3; S11-N1)</t>
+          <t>SV-8609 (SBC spec v13 2026-07-31 Story 11 S11-R1; S11-R2; S11-R3; S11-N1)</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr"/>
@@ -2868,12 +2964,14 @@
       <c r="G50" s="2" t="inlineStr">
         <is>
           <t>1. The totals row is computed over the full set of customers matching the active filters (date range, Product Type, location, Customer filter).
-2. The totals do not change when you move between pages — they never reflect only the visible page.</t>
+2. The totals do not change when you move between pages — they never reflect only the visible page.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R6).</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R6)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R6)</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr"/>
@@ -2918,7 +3016,9 @@
 2. Hovering it shows the tooltip "Column Selection."
 3. The panel lists nine toggles, in order: Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %.
 4. With no saved selection, all nine toggleable columns default to visible.
-5. Note for the tester: there is no Location toggle in this panel. That is correct - the Location column appears by itself when you have more than one location in scope, so it is never something you switch on here.</t>
+5. Note for the tester: there is no Location toggle in this panel. That is correct - the Location column appears by itself when you have more than one location in scope, so it is never something you switch on here.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S13-R1, S13-R2, S13-R3, S13-R4, S13-R7, S4-R12, S4-R13).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -2966,12 +3066,14 @@
         <is>
           <t>1. Turning a toggle off hides that column's header and all its body cells together; turning it on restores both together.
 2. The Customer and Subtotal columns and the chevron control column do NOT appear in the toggle list and are always present.
-3. All nine columns can be hidden — nothing blocks the last toggle; the table still renders the Customer and Subtotal columns and the totals row still shows its Subtotal.</t>
+3. All nine columns can be hidden — nothing blocks the last toggle; the table still renders the Customer and Subtotal columns and the totals row still shows its Subtotal.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S13-R5, S13-R6, S13-N1).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>SV-8611 (specs/sbc-sales-by-customer.md Story 13 S13-R5; S13-R6; S13-N1)</t>
+          <t>SV-8611 (SBC spec v13 2026-07-31 Story 13 S13-R5; S13-R6; S13-N1)</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr"/>
@@ -3014,7 +3116,9 @@
         <is>
           <t>1. The overflow (export) menu is the leftmost control in the toolbar's action area and is the application's standard overflow-menu control.
 2. The menu items read, in order: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)" - and there is NO "Print" item anywhere in the menu.
-3. There are no separate always-visible export buttons - all exports live behind this one menu.</t>
+3. There are no separate always-visible export buttons - all exports live behind this one menu.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R1, S14-R2, S15-R1, S15-R2, S20-R16); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3066,12 +3170,14 @@
 2. {range} follows this map: Today → today; Yesterday → yesterday; This Week → this_week; Last Week → last_week; This Month → this_month; Last Month → last_month; This Year → this_year; Last Year → last_year; This Quarter → this_quarter; Last Quarter → last_quarter; Custom → custom.
 3. For Custom the literal word "custom" is used — the actual start and end dates are not in the file name.
 4. The file is plain comma-separated text with a .csv extension that opens as rows and columns in a spreadsheet — not an .xlsx workbook and not a JSON file.
-5. The two PDF downloads follow the same names with a .pdf extension — for example, sales-by-customer-summary-this_month.pdf and sales-by-customer-expanded-custom.pdf.</t>
+5. The two PDF downloads follow the same names with a .pdf extension — for example, sales-by-customer-summary-this_month.pdf and sales-by-customer-expanded-custom.pdf.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R14, S14-R15, S15-R6); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 S14-R14; S14-R15; S15-R6 — file names now carry the Summary/Expanded version; the old flat sales-by-customer-{range} map is superseded)</t>
+          <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 S14-R14; S14-R15; S15-R6 — file names now carry the Summary/Expanded version; the old flat sales-by-customer-{range} map is superseded)</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr"/>
@@ -3118,12 +3224,14 @@
 4. An invoice row leaves Customer and Asset blank and fills Invoice # and Date.
 5. Customer names are plain — the "(N)" invoice count is not included.
 6. Work with no vehicle appears as an asset row named "Parts Sales".
-7. The file carries a "Locations:" line naming the location or locations the report was scoped to, or "All locations" when every location you can access is selected — as a leading line above the column headers.</t>
+7. The file carries a "Locations:" line naming the location or locations the report was scoped to, or "All locations" when every location you can access is selected — as a leading line above the column headers.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R5, S14-R6, S14-R7, S14-R8, S14-R13, S4-R13).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8603 (SBC spec v12 2026-07-29 Story 14 S14-R5; S14-R6; S14-R7; S14-R8; S14-R13 + Story 4 S4-R13 — Expanded CSV thirteen columns INCLUDING Asset; per-level blank-cell rules; plus the automatic Location column in every export)</t>
+          <t>SV-8612; SV-8603 (SBC spec v13 2026-07-31 Story 14 S14-R5; S14-R6; S14-R7; S14-R8; S14-R13 + Story 4 S4-R13 — Expanded CSV thirteen columns INCLUDING Asset; per-level blank-cell rules; plus the automatic Location column in every export)</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr"/>
@@ -3166,12 +3274,14 @@
           <t>1. Margin % is a plain number to one decimal with no percent sign (for example, 64.7); it is EMPTY when the row's Subtotal is zero or below.
 2. Dates export as mm-dd-yyyy — for example, 05-14-2026.
 3. Currency values are plain numbers with no dollar sign and no thousands separators.
-4. The CSV has no color; the signed Inv. Hrs value still conveys direction.</t>
+4. The CSV has no color; the signed Inv. Hrs value still conveys direction.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R9, S14-R10, S14-R11, S14-R12, S14-R13).</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>SV-8612 (SBC spec v12 2026-07-29 Story 14 S14-R9; S14-R10; S14-R11; S14-R12; S14-R13)</t>
+          <t>SV-8612 (SBC spec v13 2026-07-31 Story 14 S14-R9; S14-R10; S14-R11; S14-R12; S14-R13)</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr"/>
@@ -3214,12 +3324,14 @@
         <is>
           <t>1. Each export contains exactly the customers matching the active filters — the selected customers, within the active date range, Product Type, and location — in the active sort order.
 2. When every customer is selected, the export contains the full set of customers under those filters.
-3. The chosen date range and Product Type are reflected in both exports.</t>
+3. The chosen date range and Product Type are reflected in both exports.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R7, S3-R7, S4-R10, S14-R3, S15-R3, S18-R7).</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>SV-8601 (specs/sbc-sales-by-customer.md Story 2 S2-R7; Story 3 S3-R7; Story 4 S4-R10; Story 14 S14-R3; Story 15 S15-R3; Story 18 S18-R7)</t>
+          <t>SV-8601 (SBC spec v13 2026-07-31 Story 2 S2-R7; Story 3 S3-R7; Story 4 S4-R10; Story 14 S14-R3; Story 15 S15-R3; Story 18 S18-R7)</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr"/>
@@ -3248,7 +3360,8 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with a large enough data set that a download takes a visible moment.</t>
+          <t>1. You are on the report with a large enough data set that a download takes a visible moment.
+2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3262,12 +3375,14 @@
         <is>
           <t>1. While a download is in progress, ONLY that menu item shows a loading state and is non-interactive; the other three items are unaffected.
 2. If a CSV download fails, an error toast is shown: "CSV export failed." (dismissed by the user).
-3. If a PDF download fails, the toast reads "PDF export failed." — identical behaviour, different wording.</t>
+3. If a PDF download fails, the toast reads "PDF export failed." — identical behaviour, different wording.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-E1, S14-N1, S15-E1, S15-N1).</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 Story 14 S14-E1; S14-N1; Story 15 S15-E1; S15-N1; §7 — the loading state is now per menu item; four items)</t>
+          <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 Story 14 S14-E1; S14-N1; Story 15 S15-E1; S15-N1; §7 — the loading state is now per menu item; four items)</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr"/>
@@ -3308,12 +3423,14 @@
       <c r="G59" s="2" t="inlineStr">
         <is>
           <t>1. The PDF is A4 landscape using the application's standard font; the page margins look uniform on all sides. (The spec's exact 25px margin needs a PDF inspector — check the number only if you have one; otherwise uniform margins pass.)
-2. The footer has a centered "Software Powered by ShopView" label and a right-aligned page number "Page X of Y."</t>
+2. The footer has a centered "Software Powered by ShopView" label and a right-aligned page number "Page X of Y."
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S15-R5, S15-R6, S15-R7, S15-R8).</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>SV-8613 (SBC spec v12 2026-07-29 Story 15 S15-R5; S15-R6; S15-R7; S15-R8 — A4 landscape; 25px margins; standard font; footer label and page numbers)</t>
+          <t>SV-8613 (SBC spec v13 2026-07-31 Story 15 S15-R5; S15-R6; S15-R7; S15-R8 — A4 landscape; 25px margins; standard font; footer label and page numbers)</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr"/>
@@ -3356,7 +3473,9 @@
           <t>1. The header is two columns: a text block on the left (70% width) and the organization logo on the right (30% width).
 2. The text block shows the report title "Sales By Customer Report"; the organization name; the date range; and the filter summary line "Product Type: {value}" where value is "Parts &amp; Service," "Parts only," or "Service only."
 3. The header date range shows start and end in the format "Mon D, YYYY," joined by an em dash - for example, "May 1, 2026 - May 31, 2026" - and always shows both dates (every range is bounded).
-4. The header also carries a "Locations:" line naming the location(s) the report was scoped to (exact placement within the header is confirmed in the build).</t>
+4. The header also carries a "Locations:" line naming the location(s) the report was scoped to (exact placement within the header is confirmed in the build).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S15-R7, S15-R8, S15-R9, S15-R10, S15-R11, S15-R14, S4-R13); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3405,12 +3524,14 @@
           <t>1. With an uploaded logo, that logo appears pinned to the top-right, scaled to fit its area without distortion.
 2. With no uploaded logo, the bundled ShopView logo is used.
 3. When no logo is available at all, the logo column is not rendered and the text column fills the full width.
-4. The logo is embedded in the PDF (renders offline, not loaded from a network address).</t>
+4. The logo is embedded in the PDF (renders offline, not loaded from a network address).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18).</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>SV-8613 (SBC spec v12 2026-07-29 Story 15 S15-R12; S15-R13; S15-R14; S15-R15; S15-R16; S15-R17; S15-R18)</t>
+          <t>SV-8613 (SBC spec v13 2026-07-31 Story 15 S15-R12; S15-R13; S15-R14; S15-R15; S15-R16; S15-R17; S15-R18)</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr"/>
@@ -3439,7 +3560,8 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>1. You have downloaded the PDF for a view with positive and negative Inv. Hrs values and (if seedable) a Subtotal ≤ 0 row.</t>
+          <t>1. You have downloaded the PDF for a view with positive and negative Inv. Hrs values and (if seedable) a Subtotal ≤ 0 row.
+2. This test names exact colours or sizes. Use the browser's own developer tools: press F12, pick the element with the inspector, and read its colour or size from the "Styles" panel. There is nothing to install. If you cannot get a clear reading, mark this test Blocked rather than guessing.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -3456,12 +3578,14 @@
 4. Margin % shows an em dash when the row's Subtotal is zero or below.
 5. The Subtotal column is bold - header, every row, and the totals row.
 6. Inv. Hrs uses the same signs and coloring as on screen, with green rendered as #21ba45 and red as #c10015.
-7. The PDF header title reads "Sales By Customer Report" on the Summary and Expanded versions alike — which version you have is told by the file name and the contents, not by a different title.</t>
+7. The PDF header title reads "Sales By Customer Report" on the Summary and Expanded versions alike — which version you have is told by the file name and the contents, not by a different title.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S15-R5, S15-R13, S15-R19, S15-R20, S15-R21, S15-R22, S15-R23, S15-R24, S4-R13).</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>SV-8613; SV-8603 (SBC spec v12 2026-07-29 Story 15 S15-R5; S15-R13; S15-R19; S15-R20; S15-R21; S15-R22; S15-R23; S15-R24 + Story 4 S4-R13 — Expanded PDF body = the Expanded columns; plus the automatic Location column)</t>
+          <t>SV-8613; SV-8603 (SBC spec v13 2026-07-31 Story 15 S15-R5; S15-R13; S15-R19; S15-R20; S15-R21; S15-R22; S15-R23; S15-R24 + Story 4 S4-R13 — Expanded PDF body = the Expanded columns; plus the automatic Location column)</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr"/>
@@ -3505,12 +3629,15 @@
           <t>1. For both CSV and PDF: no file is generated and no download starts.
 2. An error toast is shown each time: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
 3. The cap counts customer rows plus invoice rows (not the header or totals row) against the active date range, Product Type, location, Customer filter, and sort.
-4. Below the cap the export succeeds normally.</t>
+4. Below the cap the export succeeds normally.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R16, S15-R25, S14-R14, S15-R22); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>SV-8612; SV-8613 (SBC spec v12 2026-07-29 S14-R16 CSV cap; S15-R25 PDF cap; S14-R14; S15-R22; §7 — Print leg REMOVED per kickoff video P25 31:14; user ruling 2026-07-28 video-overrides-spec)</t>
+          <t>SV-8612; SV-8613 (SBC spec v13 2026-07-31 S14-R16 CSV cap; S15-R25 PDF cap; S14-R14; S15-R22; §7 — Print leg REMOVED per kickoff video P25 31:14; user ruling 2026-07-28 video-overrides-spec)</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr"/>
@@ -3551,12 +3678,14 @@
       <c r="G64" s="2" t="inlineStr">
         <is>
           <t>1. The export still downloads — no error and no warning is shown.
-2. The file contains the column headers and a totals row of zeros, with no data rows.</t>
+2. The file contains the column headers and a totals row of zeros, with no data rows.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R10).</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R10)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R10)</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr"/>
@@ -3601,7 +3730,9 @@
 2. Each Summary file gives ONE row per customer, without the asset or invoice detail rows.
 3. Each Expanded View file contains the full Customer, then Asset, then Invoice breakdown.
 4. All four files reflect exactly the filtered data shown on screen.
-5. With a single location in scope the Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When more than one location is in scope a Location column is added with the identifying columns, ahead of the money columns (the Summary files have no Date column for it to follow — confirm its exact position in the build).</t>
+5. With a single location in scope the Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When more than one location is in scope a Location column is added with the identifying columns, ahead of the money columns (the Summary files have no Date column for it to follow — confirm its exact position in the build).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13).</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3648,12 +3779,14 @@
       <c r="G66" s="2" t="inlineStr">
         <is>
           <t>1. The saved view is restored: the date range, the Product Type, the location selection, the Customer filter selection, the sort column and direction, and the visible columns.
-2. On load, the report shows the restored view immediately — the default view is never shown first and then replaced.</t>
+2. On load, the report shows the restored view immediately — the default view is never shown first and then replaced.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S6-R1, S6-R2, S6-R4, S2-R8, S3-R8, S4-R11, S10-R9, S13-R8).</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>SV-8604 (specs/sbc-sales-by-customer.md Story 6 S6-R1; S6-R2; S6-R4; Story 2 S2-R8; Story 3 S3-R8; Story 4 S4-R11; Story 10 S10-R9; Story 13 S13-R8)</t>
+          <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R1; S6-R2; S6-R4; Story 2 S2-R8; Story 3 S3-R8; Story 4 S4-R11; Story 10 S10-R9; Story 13 S13-R8)</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr"/>
@@ -3697,12 +3830,14 @@
           <t>1. The type-ahead search text is gone (only the resulting customer selection is saved).
 2. All rows are collapsed — reloading clears all expansion state.
 3. The scroll position is not restored.
-4. This is the specified behavior (expansion is treated as fresh each visit), not a defect.</t>
+4. This is the specified behavior (expansion is treated as fresh each visit), not a defect.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S6-R3, S8-R22).</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>SV-8604 (specs/sbc-sales-by-customer.md Story 6 S6-R3; Story 8 S8-R22)</t>
+          <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R3; Story 8 S8-R22)</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr"/>
@@ -3745,12 +3880,14 @@
         <is>
           <t>1. The stale saved location is discarded and the location setting uses its default (your active location) instead.
 2. No error appears and the report loads normally.
-3. Per the spec, the same discard-to-default applies to an unknown date range, a sort column that no longer exists, or a column set that does not match the current columns.</t>
+3. Per the spec, the same discard-to-default applies to an unknown date range, a sort column that no longer exists, or a column set that does not match the current columns.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S6-R5, S6-R6).</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>SV-8604 (specs/sbc-sales-by-customer.md Story 6 S6-R5; S6-R6)</t>
+          <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R5; S6-R6)</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr"/>
@@ -3791,12 +3928,14 @@
       <c r="G69" s="2" t="inlineStr">
         <is>
           <t>1. The other report keeps its own defaults/saved view — the Sales By Customer settings do not leak into it.
-2. Sales By Customer still restores its own saved view.</t>
+2. Sales By Customer still restores its own saved view.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S6-R7).</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>SV-8604 (specs/sbc-sales-by-customer.md Story 6 S6-R7)</t>
+          <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-R7)</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr"/>
@@ -3843,12 +3982,14 @@
 3. Location = the single location you are currently working in (your active location) — not all locations.
 4. Customer filter = all customers selected (label "All customers").
 5. Sort = Customer name ascending.
-6. All nine toggleable columns visible.</t>
+6. All nine toggleable columns visible.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S6-N1, S2-R5, S4-R4).</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>SV-8604 (specs/sbc-sales-by-customer.md Story 6 S6-N1; Story 2 S2-R5; Story 4 S4-R4)</t>
+          <t>SV-8604 (SBC spec v13 2026-07-31 Story 6 S6-N1; Story 2 S2-R5; Story 4 S4-R4)</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr"/>
@@ -3890,12 +4031,14 @@
       <c r="G71" s="2" t="inlineStr">
         <is>
           <t>1. The saved view is applied (Last Month) and the link value is ignored.
-2. This is intentional: a shared link restores the sender's range only for a recipient who has no saved range of their own.</t>
+2. This is intentional: a shared link restores the sender's range only for a recipient who has no saved range of their own.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R9).</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>SV-8601 (specs/sbc-sales-by-customer.md Story 2 S2-R9)</t>
+          <t>SV-8601 (SBC spec v13 2026-07-31 Story 2 S2-R9)</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr"/>
@@ -3937,12 +4080,14 @@
       <c r="G72" s="2" t="inlineStr">
         <is>
           <t>1. Scenario A: the filter restores to the all-customers state and the report shows every present customer — including the customer that appeared since the state was saved.
-2. Scenario B: still-present saved ids are re-selected; a saved id no longer present is dropped (a stale saved id never forces an empty view); a customer that appeared since the set was saved is NOT auto-selected.</t>
+2. Scenario B: still-present saved ids are re-selected; a saved id no longer present is dropped (a stale saved id never forces an empty view); a customer that appeared since the set was saved is NOT auto-selected.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R8).</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R8)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R8)</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr"/>
@@ -3989,12 +4134,14 @@
 2. The toolbar stays visible and interactive (all filters including the Customer filter, and the action controls), so you can adjust filters without leaving the page.
 3. The same empty state appears whichever filter caused it (date range, Product Type, or location).
 4. The header-row chevron is hidden when the table has no visible rows.
-5. With a narrowed customer selection and no data, the empty state shows but the selection is KEPT (not cleared) — when the filters change back, the selected customers reappear.</t>
+5. With a narrowed customer selection and no data, the empty state shows but the selection is KEPT (not cleared) — when the filters change back, the selected customers reappear.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1).</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>SV-8615 (specs/sbc-sales-by-customer.md Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1)</t>
+          <t>SV-8615 (SBC spec v13 2026-07-31 Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1)</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -4023,7 +4170,8 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report; a slow network helps (throttle via browser dev tools if needed).</t>
+          <t>1. You are on the report; a slow network helps (throttle via browser dev tools if needed).
+2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -4035,12 +4183,14 @@
       <c r="G74" s="2" t="inlineStr">
         <is>
           <t>1. While the table is loading, the empty-state message is NOT shown (the loading state is shown instead).
-2. The message appears only after the table finishes its initial loading and shows zero customers.</t>
+2. The message appears only after the table finishes its initial loading and shows zero customers.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S17-N1).</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>SV-8615 (specs/sbc-sales-by-customer.md Story 17 S17-N1)</t>
+          <t>SV-8615 (SBC spec v13 2026-07-31 Story 17 S17-N1)</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr"/>
@@ -4069,7 +4219,8 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>1. You can interrupt the network (browser dev tools offline mode).</t>
+          <t>1. You can interrupt the network (browser dev tools offline mode).
+2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -4081,7 +4232,9 @@
       <c r="G75" s="2" t="inlineStr">
         <is>
           <t>1. An error toast is shown: "An error occurred while fetching the report data."
-2. The toast auto-fades after 5 seconds.</t>
+2. The toast auto-fades after 5 seconds.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (§7 User Feedback Summary).</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4120,26 +4273,31 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>1. Inspect the page background, toolbar surface, and paddings with dev tools.
-2. Check the toolbar's position against the top of the page and the table against the side edges.
-3. Compare the title's left edge and the action cluster's right edge with the leftmost/rightmost data-cell positions.
-4. Check the line between the toolbar and the headers, the date-range picker's dropdown arrow size, the table corners, and the outermost cell paddings.</t>
+          <t>1. Look at the page background behind the data area and at the toolbar strip above the table, including the space between its controls and the edges of the strip.
+2. Check whether the toolbar sits flush against the top of the page with no gap, and whether the table reaches the left and right edges next to the side navigation.
+3. Compare the left edge of the title and the right edge of the action cluster with the leftmost and rightmost columns of data.
+4. Look at the line between the toolbar and the column headers, the size of the date-range picker's dropdown arrow next to the other filter arrows, the table's corners, and the space at the far left and far right of the rows.
+5. Open another report in the suite (for example Inventory Value) side by side and compare.</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>1. The page has no padding; the page background is the standard blue-grey (#f9fafb in light mode).
-2. The toolbar surface is white (#ffffff); its padding is 32px top, 24px bottom, and 2rem left and right; it touches the top of the page with no gap, and the table reaches the left and right edges next to the side navigation.
-3. The left edge of the title and the right edge of the action cluster line up with the leftmost and rightmost data-cell positions.
-4. A 1px horizontal line in the standard table-header border color separates the toolbar from the column headers.
-5. The date-range picker's dropdown arrow is 24px, the same size as the other filter dropdown arrows.
-6. The table has no rounded corners; the leftmost cell (header, body, totals) has 2rem left padding and the rightmost cell 2rem right padding.
-7. When the table content does not fill the viewport, the blue-grey page background shows through below the table — no white strip.</t>
+          <t>1. The page background behind the data area is the standard soft blue-grey used across the suite, and the page itself has no border of empty space around it.
+2. The toolbar strip is white, its controls sit clear of the edges rather than pressed up against them, it sits flush against the top of the page with no gap, and the table reaches the left and right edges next to the side navigation.
+3. The left edge of the title lines up with the leftmost column of data, and the right edge of the action cluster lines up with the rightmost column.
+4. A thin dividing line separates the toolbar from the column headers.
+5. The date-range picker's dropdown arrow is the same size as the other filter dropdown arrows next to it.
+6. The table has square corners, and the first and last columns sit clear of the left and right edges of the table — the text is not touching the edge.
+7. When there are too few rows to fill the screen, the blue-grey page background shows through below the table — there is no white strip left over.
+8. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
+9. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing, the alignment and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this — 32px/24px toolbar padding, a 1px header border, 2rem edge padding, a 24px arrow — are design-token values the design and engineering team check with their own tooling, not by hand.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S20-R1, S20-R2, S20-R3, S20-R4, S20-R5, S20-R6, S20-R7, S20-R12, S20-R13, S20-R15, S20-R17).</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>SV-8617 (specs/sbc-sales-by-customer.md Story 20 S20-R1; S20-R2; S20-R3; S20-R4; S20-R5; S20-R6; S20-R7; S20-R12; S20-R13; S20-R15; S20-R17)</t>
+          <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R1; S20-R2; S20-R3; S20-R4; S20-R5; S20-R6; S20-R7; S20-R12; S20-R13; S20-R15; S20-R17)</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr"/>
@@ -4168,7 +4326,8 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report in light mode with a customer expanded down to invoice rows.</t>
+          <t>1. You are on the report in light mode with a customer expanded down to invoice rows.
+2. This test names exact colours or sizes. Use the browser's own developer tools: press F12, pick the element with the inspector, and read its colour or size from the "Styles" panel. There is nothing to install. If you cannot get a clear reading, mark this test Blocked rather than guessing.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -4184,12 +4343,14 @@
 2. Asset rows and invoice rows use the blue-grey background (#f9fafb).
 3. The totals row uses the white surface with a top border and bold text (white on purpose, matching Technician Efficiency).
 4. The pinned Subtotal cell on any row uses that row's own background — never a contrasting strip.
-5. The three tree levels show by indentation: customer at the base, asset rows one level in (chevron and vehicle icon sit in from the customer), invoice rows one level deeper.</t>
+5. The three tree levels show by indentation: customer at the base, asset rows one level in (chevron and vehicle icon sit in from the customer), invoice rows one level deeper.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14).</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>SV-8617 (specs/sbc-sales-by-customer.md Story 20 S20-R8; S20-R9; S20-R10; S20-R11; S20-R14)</t>
+          <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R8; S20-R9; S20-R10; S20-R11; S20-R14)</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr"/>
@@ -4230,12 +4391,14 @@
       <c r="G78" s="2" t="inlineStr">
         <is>
           <t>1. In dark mode every visual rule applies with the dark equivalent of each color (dark background, dark surfaces).
-2. The PDF export always renders in light-mode colors regardless of the user's app mode.</t>
+2. The PDF export always renders in light-mode colors regardless of the user's app mode.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S20-R18).</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>SV-8617 (specs/sbc-sales-by-customer.md Story 20 S20-R18)</t>
+          <t>SV-8617 (SBC spec v13 2026-07-31 Story 20 S20-R18)</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr"/>
@@ -4278,12 +4441,14 @@
         <is>
           <t>1. Every toolbar control is visible and works on touch.
 2. Below 1024px the toolbar uses two rows: the action controls (overflow menu and column selector) on the first row, and the filter dropdowns on the second row, stacked at full width.
-3. At 1024px and above the toolbar uses the desktop single-row layout.</t>
+3. At 1024px and above the toolbar uses the desktop single-row layout.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S21-R1, S21-R2, S21-R3).</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>SV-8618 (specs/sbc-sales-by-customer.md Story 21 S21-R1; S21-R2; S21-R3)</t>
+          <t>SV-8618 (SBC spec v13 2026-07-31 Story 21 S21-R1; S21-R2; S21-R3)</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr"/>
@@ -4326,12 +4491,14 @@
         <is>
           <t>1. The data table scrolls sideways to show all columns, and the pinned Subtotal column stays visible during that scroll.
 2. The chevron expand and collapse control on each row works on touch.
-3. The invoice number link opens the invoice in the same tab, the same as on desktop.</t>
+3. The invoice number link opens the invoice in the same tab, the same as on desktop.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S21-R4, S21-R5, S21-R6).</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>SV-8618 (specs/sbc-sales-by-customer.md Story 21 S21-R4; S21-R5; S21-R6)</t>
+          <t>SV-8618 (SBC spec v13 2026-07-31 Story 21 S21-R4; S21-R5; S21-R6)</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr"/>
@@ -4360,7 +4527,8 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with several customers, with the browser's network activity panel open.</t>
+          <t>1. You are on the report with several customers, with the browser's network activity panel open.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -4375,12 +4543,14 @@
         <is>
           <t>1. Customer summary rows load WITHOUT the asset/invoice detail — the drill-down data is not preloaded.
 2. The first expand of a customer triggers a server fetch for that customer's asset and invoice rows.
-3. Expand-all triggers at most one drill-down fetch per not-yet-expanded customer on the current page — a bounded number never exceeding the page size; it does not fetch customers beyond the current page or the whole result set.</t>
+3. Expand-all triggers at most one drill-down fetch per not-yet-expanded customer on the current page — a bounded number never exceeding the page size; it does not fetch customers beyond the current page or the whole result set.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R14, S8-R16).</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>SV-8606 (specs/sbc-sales-by-customer.md Story 8 S8-R14; S8-R16)</t>
+          <t>SV-8606 (SBC spec v13 2026-07-31 Story 8 S8-R14; S8-R16)</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr"/>
@@ -4409,7 +4579,8 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>1. Enough customers exist to span more than one page; the browser's network panel is open.</t>
+          <t>1. Enough customers exist to span more than one page; the browser's network panel is open.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -4424,12 +4595,14 @@
           <t>1. Clicking a column header issues a server request that returns the customer rows ordered by that column.
 2. The full filtered set is re-ordered and re-paginated on the server — the response is the first page of results in the new order, so page membership can change.
 3. The ordering is not done by re-shuffling rows already in the browser.
-4. A sort request naming a column the report does not offer is safely refused or ignored — never an error page or a crash; sorting works only on the report's own columns.</t>
+4. A sort request naming a column the report does not offer is safely refused or ignored — never an error page or a crash; sorting works only on the report's own columns.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S10-R8, S10-R8b).</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>SV-8608 (specs/sbc-sales-by-customer.md Story 10 S10-R8; S10-R8b; tech-plan-2026-07-29 A2 (server sort whitelist))</t>
+          <t>SV-8608 (SBC spec v13 2026-07-31 Story 10 S10-R8; S10-R8b; tech-plan-2026-07-29 A2 (server sort whitelist))</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr"/>
@@ -4458,7 +4631,8 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with the browser's network panel open.</t>
+          <t>1. You are on the report with the browser's network panel open.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -4472,12 +4646,14 @@
         <is>
           <t>1. The dropdown does not load the full customer list into the browser up front.
 2. As you type, the browser fetches matching customers from the server — case-insensitive "contains" matching on the name, scoped to the active date range, Product Type, and location — and lists the returned customers.
-3. The all-customers state is stored as an explicit state (a flag), not an enumeration of the fetched ids.</t>
+3. The all-customers state is stored as an explicit state (a flag), not an enumeration of the fetched ids.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R2, S18-R4).</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R2; S18-R4)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R2; S18-R4)</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr"/>
@@ -4506,7 +4682,8 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>1. Enough customers exist to span more than one page; the browser's network panel is open.</t>
+          <t>1. Enough customers exist to span more than one page; the browser's network panel is open.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -4520,12 +4697,14 @@
         <is>
           <t>1. Customer rows arrive page by page from the server (server-paginated), not as one full client-side list.
 2. Changing the Customer selection re-fetches the matching customers as a fresh first page.
-3. The totals are computed on the server over the full set of matching customers — they arrive with the data and do not change as you page.</t>
+3. The totals are computed on the server over the full set of matching customers — they arrive with the data and do not change as you page.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R6, S18-R11).</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>SV-8616 (specs/sbc-sales-by-customer.md Story 18 S18-R6; S18-R11)</t>
+          <t>SV-8616 (SBC spec v13 2026-07-31 Story 18 S18-R6; S18-R11)</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr"/>
@@ -4554,7 +4733,8 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>1. The browser's network panel is open; an over-cap filter combination is available if the environment allows.</t>
+          <t>1. The browser's network panel is open; an over-cap filter combination is available if the environment allows.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -4566,12 +4746,15 @@
       <c r="G85" s="2" t="inlineStr">
         <is>
           <t>1. The CSV and PDF are generated on the server from the active date range, Product Type, location, Customer filter, and sort — not assembled from the rows already loaded in the browser.
-2. Over the cap, the server does not generate the file (the request comes back as a refusal, not a file) and the browser starts no download — the count the cap checks is the count the file would contain, against the same filters and sort as the screen.</t>
+2. Over the cap, the server does not generate the file (the request comes back as a refusal, not a file) and the browser starts no download — the count the cap checks is the count the file would contain, against the same filters and sort as the screen.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R3, S14-R14, S15-R3, S15-R22).</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>SV-8612 (specs/sbc-sales-by-customer.md Story 14 S14-R3; S14-R14; Story 15 S15-R3; S15-R22)</t>
+          <t>SV-8612 (SBC spec v13 2026-07-31 Story 14 S14-R3; S14-R14; Story 15 S15-R3; S15-R22)</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr"/>
@@ -4601,7 +4784,8 @@
       <c r="E86" s="2" t="inlineStr">
         <is>
           <t>1. Two sign-ins are available: one user whose role has the ordinary reports access, and one whose role does not have it (for example a Foreman).
-2. You can see the requests the browser makes (the browser's network panel) so you can read the response code.</t>
+2. You can see the requests the browser makes (the browser's network panel) so you can read the response code.
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -4620,7 +4804,9 @@
 2. For that same user, the export request also succeeds (HTTP 200) and a file is produced.
 3. For the user WITHOUT reports access, the data request is refused with HTTP 403 and a message reading "Access denied." — no report data comes back.
 4. For that same user, the export request is refused with HTTP 403 as well — no file is produced.
-5. Note for the tester: one single permission controls all four of these. If you find the report data refused but the export allowed (or the other way round), that is a failure — record both response codes.</t>
+5. Note for the tester: one single permission controls all four of these. If you find the report data refused but the export allowed (or the other way round), that is a failure — record both response codes.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-R2, S1-N1).</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4671,7 +4857,9 @@
 2. The rest of the navigation matches the previous release: no existing entry is moved, replaced, or reordered — if you can compare against production or an earlier build, the only difference is the added entry.
 3. Selecting the entry opens the report in the main content area.
 4. The page title reads "Sales By Representative".
-5. The browser tab title reads "Sales By Representative - Report | ShopView".</t>
+5. The browser tab title reads "Sales By Representative - Report | ShopView".
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S1-R1, S1-R2, S1-R3, S1-R4, S1-R5, S1-R6).</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -4717,12 +4905,14 @@
       <c r="G88" s="2" t="inlineStr">
         <is>
           <t>1. The full "Sales By Representative" label renders without crowding against the entry's edges and without truncation.
-2. The label is not shortened to fit — the fix is the entry's horizontal padding, not the name.</t>
+2. The label is not shortened to fit — the fix is the entry's horizontal padding, not the name.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S1-R7).</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>SV-8619 (specs/sbr-sales-by-representative.md Story 1 S1-R7; §1 naming note)</t>
+          <t>SV-8619 (SBR spec v15 2026-07-29 Story 1 S1-R7; §1 naming note)</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr"/>
@@ -4762,12 +4952,14 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>1. "Sales By Representative" appears in the Performance group for this user — the entry is visible to every user who can see any other report in the same group.</t>
+          <t>1. "Sales By Representative" appears in the Performance group for this user — the entry is visible to every user who can see any other report in the same group.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S1-R1).</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>SV-8619 (specs/sbr-sales-by-representative.md Story 1 S1-R1)</t>
+          <t>SV-8619 (SBR spec v15 2026-07-29 Story 1 S1-R1)</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr"/>
@@ -4811,12 +5003,14 @@
         <is>
           <t>1. The entire Reports navigation — including the "Sales By Representative" entry — is not shown.
 2. The report (and its ⋯ export menu) is not reachable.
-3. The Export Reports dialog and the Sales Representative Assignments download are not reachable.</t>
+3. The Export Reports dialog and the Sales Representative Assignments download are not reachable.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S1-N1, S14-N3, S15-N1).</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>SV-8619 (specs/sbr-sales-by-representative.md Story 1 S1-N1; Story 14 S14-N3; Story 15 S15-N1)</t>
+          <t>SV-8619 (SBR spec v15 2026-07-29 Story 1 S1-N1; Story 14 S14-N3; Story 15 S15-N1)</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr"/>
@@ -4855,12 +5049,14 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>1. The staff-editing surface is not reachable, so the deactivation flow (and its warning dialog) cannot be reached.</t>
+          <t>1. The staff-editing surface is not reachable, so the deactivation flow (and its warning dialog) cannot be reached.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-N1).</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-N1)</t>
+          <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-N1)</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr"/>
@@ -4902,12 +5098,14 @@
         <is>
           <t>1. A date range picker is visible in the report toolbar.
 2. The standard presets are offered: Today, Yesterday, This Week, This Month, Last Month, This Year, Last Year, This Quarter, Last Quarter, Custom.
-3. There is no "All Time" option (removed by the 2026-07-16 spec round).</t>
+3. There is no "All Time" option (removed by the 2026-07-16 spec round).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S2-R1, S2-R2).</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>SV-8620 (specs/sbr-sales-by-representative.md Story 2 S2-R1; S2-R2)</t>
+          <t>SV-8620 (SBR spec v15 2026-07-29 Story 2 S2-R1; S2-R2)</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr"/>
@@ -4948,12 +5146,14 @@
       <c r="G93" s="2" t="inlineStr">
         <is>
           <t>1. A custom range within the cap applies normally via the date-picker dialog.
-2. A custom selection whose span exceeds 366 days is not accepted — the picker holds you to a range of 366 days or fewer.</t>
+2. A custom selection whose span exceeds 366 days is not accepted — the picker holds you to a range of 366 days or fewer.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S2-R3, S2-R6).</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>SV-8620 (specs/sbr-sales-by-representative.md Story 2 S2-R3; S2-R6)</t>
+          <t>SV-8620 (SBR spec v15 2026-07-29 Story 2 S2-R3; S2-R6)</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr"/>
@@ -4996,12 +5196,14 @@
         <is>
           <t>1. The invoices dated on the start and end dates are INCLUDED (inclusive endpoints); the invoice outside the range is excluded.
 2. The date used is the invoice's own date — the value shown in the Date column.
-3. The chosen date range is reflected in both PDF exports' header strips.</t>
+3. The chosen date range is reflected in both PDF exports' header strips.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S2-R5, S2-R8).</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>SV-8620 (specs/sbr-sales-by-representative.md Story 2 S2-R5; S2-R8; §3)</t>
+          <t>SV-8620 (SBR spec v15 2026-07-29 Story 2 S2-R5; S2-R8; §3)</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr"/>
@@ -5048,7 +5250,9 @@
 2. "Parts only" includes only invoices whose number starts with P.
 3. "Service only" includes only invoices whose number starts with S.
 4. "Parts &amp; Service" applies no product-type filter — both appear again.
-5. Each change re-fetches and re-renders the report.</t>
+5. Each change re-fetches and re-renders the report.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6, S3-R7).</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5097,7 +5301,9 @@
           <t>1. An "Invoice Status" dropdown is visible in the toolbar.
 2. It offers exactly four options: "All Statuses," "Unpaid," "Partially Paid," "Paid."
 3. "All Statuses" is the default on first load.
-4. Changing the selection re-fetches and re-renders the report.</t>
+4. Changing the selection re-fetches and re-renders the report.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S4-R1, S4-R2, S4-R3, S4-R5).</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5147,12 +5353,14 @@
           <t>1. "Paid" includes the paid, the overpaid, AND the prepaid-with-zero-balance invoices.
 2. "Partially Paid" includes the partially-paid AND the prepaid-with-a-balance-owed invoices.
 3. "Unpaid" includes only the unpaid invoice.
-4. The filter matches on the mapped display value, the same mapping the status badge uses — prepaid is the only state whose display value depends on the balance owed.</t>
+4. The filter matches on the mapped display value, the same mapping the status badge uses — prepaid is the only state whose display value depends on the balance owed.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S4-R4).</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>SV-8622 (specs/sbr-sales-by-representative.md Story 4 S4-R4; §3 payment-status mapping)</t>
+          <t>SV-8622 (SBR spec v15 2026-07-29 Story 4 S4-R4; §3 payment-status mapping)</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr"/>
@@ -5197,12 +5405,14 @@
           <t>1. Only invoices matching ALL active filters contribute — every metric reflects the intersection; an invoice failing any single filter contributes nothing anywhere.
 2. A rep appears only if at least one invoice matches all active filters.
 3. Parts-only leg: rep A disappears; rep B's summary totals, detail rows, grand Totals, and (N) count reflect only the matching (P) invoices.
-4. Unpaid leg: rep C disappears; rep D's figures reflect only the Unpaid invoices.</t>
+4. Unpaid leg: rep C disappears; rep D's figures reflect only the Unpaid invoices.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S4-R7, S4-R6, S4-N1, S3-R8, S3-N1).</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>SV-8622 (specs/sbr-sales-by-representative.md Story 4 S4-R7; S4-R6; S4-N1; Story 3 S3-R8; S3-N1)</t>
+          <t>SV-8622 (SBR spec v15 2026-07-29 Story 4 S4-R7; S4-R6; S4-N1; Story 3 S3-R8; S3-N1)</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr"/>
@@ -5242,12 +5452,14 @@
       <c r="G99" s="2" t="inlineStr">
         <is>
           <t>1. The invoice shows its FULL invoiced amounts (its full Subtotal) — payments are not netted out.
-2. Filtering to "Unpaid" or "Partially Paid" changes which invoices are included, never the amounts shown.</t>
+2. Filtering to "Unpaid" or "Partially Paid" changes which invoices are included, never the amounts shown.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S4-R8).</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>SV-8622 (specs/sbr-sales-by-representative.md Story 4 S4-R8)</t>
+          <t>SV-8622 (SBR spec v15 2026-07-29 Story 4 S4-R8)</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr"/>
@@ -5288,12 +5500,14 @@
       <c r="G100" s="2" t="inlineStr">
         <is>
           <t>1. The location filter is the rightmost control in the toolbar.
-2. It is a multi-select listing the locations the user has access to, plus an "All Locations" option.</t>
+2. It is a multi-select listing the locations the user has access to, plus an "All Locations" option.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-R1, S18-R7).</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>SV-8638 (specs/sbr-sales-by-representative.md Story 21 S21-R1; Story 18 S18-R7.2)</t>
+          <t>SV-8638 (SBR spec v15 2026-07-29 Story 21 S21-R1; Story 18 S18-R7.2)</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr"/>
@@ -5340,7 +5554,9 @@
 2. Changing the selection re-fetches and re-renders scoped to the chosen set.
 3. "All Locations" means all locations the user can access — location Z's data is never included.
 4. With "All Locations" active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
-5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).</t>
+5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-R3, S21-R4, S21-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5386,7 +5602,9 @@
       <c r="G102" s="2" t="inlineStr">
         <is>
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
-2. For the user with access to two or more locations the Location filter IS shown.</t>
+2. For the user with access to two or more locations the Location filter IS shown.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -5434,8 +5652,7 @@
 5. Read the Location cell on the Unassigned summary row.
 6. Check that the pinned Subtotal column is still the rightmost column.
 7. Narrow to a single location and read the headers again.
-8. Change the selection between one location, several, and "All Locations", watching the filter control's width.
-9. With more than one location still selected, download all four files from the ⋯ menu (Summary and Expanded View, PDF and CSV) and read the Location column in each one.</t>
+8. With more than one location still selected, download all four files from the ⋯ menu (Summary and Expanded View, PDF and CSV) and read the Location column in each one.</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -5447,8 +5664,9 @@
 5. The Unassigned summary row follows the same rule as any rep summary row.
 6. The pinned Subtotal column is still rightmost — the Location column never displaces it.
 7. With a single location in scope the Location column is hidden.
-8. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
-9. All four downloads include the Location column in the same position it occupies on screen. In the Summary files a rep's row carries that rep's location and reads "Multiple" when the rep spans more than one location; in the Expanded View files each invoice row carries that invoice's own exact location.</t>
+8. All four downloads include the Location column in the same position it occupies on screen. In the Summary files a rep's row carries that rep's location and reads "Multiple" when the rep spans more than one location; in the Expanded View files each invoice row carries that invoice's own exact location.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-R7, S21-R8, S18-R13, S14-R20).</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -5497,12 +5715,14 @@
           <t>1. Rep A occupies exactly one summary row.
 2. Reps B and C do not appear — there are no blank placeholder rows, and a reversed invoice never satisfies the contributor gate.
 3. The number of contributing invoices shows in parentheses after the rep's name, in a smaller, subdued grey font — e.g., Mary Smith (12) — and is always at least 1.
-4. A staff member with no matching invoice does not appear regardless of toggle state or historical activity.</t>
+4. A staff member with no matching invoice does not appear regardless of toggle state or historical activity.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S5-R1, S5-R4, S5-N1).</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>SV-8623 (specs/sbr-sales-by-representative.md Story 5 S5-R1; S5-R4; S5-N1; §3 Key Decisions)</t>
+          <t>SV-8623 (SBR spec v15 2026-07-29 Story 5 S5-R1; S5-R4; S5-N1; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr"/>
@@ -5548,7 +5768,9 @@
 2. On a rep summary row the Date cell holds the chevron control followed by the rep's display name ("First Last"); the date value is intentionally blank.
 3. The Invoice, Customer, and Status cells are blank on summary rows; the metric cells carry the rep's totals across all matching invoices.
 4. Rep summary rows are bold (700) so they read as parent rows; detail rows use the default weight (400) — row type is distinguished by font weight, not background color.
-5. Every row renders exactly the report's column count with blanks in position — a cell with nothing to show is blank, never shifted or wrapped (a drifted row is a defect). The grand Totals indicator is exempt: the desktop Totals row merges the four leading identifier columns; the mobile bar is not a table row.</t>
+5. Every row renders exactly the report's column count with blanks in position — a cell with nothing to show is blank, never shifted or wrapped (a drifted row is a defect). The grand Totals indicator is exempt: the desktop Totals row merges the four leading identifier columns; the mobile bar is not a table row.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S5-R2, S5-R3, S5-R6, S5-R8, S5-R10, S5-N2, S6-R4, S18-R4, S18-R6a, S21-R7).</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -5598,12 +5820,14 @@
           <t>1. Rep A still appears with credit intact; the name is followed by a subdued "(Inactive)" tag — e.g., Mary Smith (Inactive) (12) — in the same muted grey as the count.
 2. The tag is display-only: metrics, A→Z position, and expandability are unchanged; a rep whose toggle is on shows no tag.
 3. For a deleted staff record, the display name and sort position come from the denormalized rep-name snapshot on the rep's most recent matching invoice (by invoice date, ties by invoice number), so the row still shows a historical name and sorts correctly.
-4. The grand Totals stay reconciled to the period's invoices — no revenue silently disappears.</t>
+4. The grand Totals stay reconciled to the period's invoices — no revenue silently disappears.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S5-R9).</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>SV-8623 (specs/sbr-sales-by-representative.md Story 5 S5-R9; §3 Key Decisions; §4 Snapshot)</t>
+          <t>SV-8623 (SBR spec v15 2026-07-29 Story 5 S5-R9; §3 Key Decisions; §4 Snapshot)</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr"/>
@@ -5645,12 +5869,14 @@
         <is>
           <t>1. The rep's matching invoices appear as detail rows beneath the summary row; a brief row-level loading indicator shows while they load on the first expand.
 2. Each detail row shows, left to right: the invoice's date, the invoice number, the customer name, the payment status badge, and the per-invoice values for Inv. Hrs and the money columns.
-3. A rep with a single matching invoice can still be expanded — one detail row is shown.</t>
+3. A rep with a single matching invoice can still be expanded — one detail row is shown.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R1, S6-R2, S6-R3, S6-E1).</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>SV-8624 (specs/sbr-sales-by-representative.md Story 6 S6-R1; S6-R2; S6-R3; S6-E1)</t>
+          <t>SV-8624 (SBR spec v15 2026-07-29 Story 6 S6-R1; S6-R2; S6-R3; S6-E1)</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr"/>
@@ -5693,12 +5919,14 @@
         <is>
           <t>1. With at least one rep collapsed the header chevron shows the "expand" glyph.
 2. Clicking expands every visible rep in one action; with every rep expanded the glyph switches to "collapse."
-3. A second activation collapses them all.</t>
+3. A second activation collapses them all.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R5, S6-R6).</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>SV-8624 (specs/sbr-sales-by-representative.md Story 6 S6-R5; S6-R6)</t>
+          <t>SV-8624 (SBR spec v15 2026-07-29 Story 6 S6-R5; S6-R6)</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr"/>
@@ -5739,12 +5967,14 @@
       <c r="G109" s="2" t="inlineStr">
         <is>
           <t>1. Every invoice appears under exactly one rep (the rep credited at invoicing time) or under the Unassigned row — never under two rows.
-2. The sum of all (N) counts equals the number of matching invoices.</t>
+2. The sum of all (N) counts equals the number of matching invoices.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R7).</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>SV-8624 (specs/sbr-sales-by-representative.md Story 6 S6-R7; §3 Key Decisions)</t>
+          <t>SV-8624 (SBR spec v15 2026-07-29 Story 6 S6-R7; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr"/>
@@ -5787,12 +6017,14 @@
         <is>
           <t>1. Expanded state is preserved across filter and sort changes within the same session.
 2. When a filter change removes a rep, the rep and its expansion state are gone; when a later change brings the rep back, the row renders collapsed (it does not auto-re-expand).
-3. A full page reload resets all expansion.</t>
+3. A full page reload resets all expansion.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R8, S6-N1, S23-R2).</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>SV-8624 (specs/sbr-sales-by-representative.md Story 6 S6-R8; S6-N1; Story 23 S23-R2)</t>
+          <t>SV-8624 (SBR spec v15 2026-07-29 Story 6 S6-R8; S6-N1; Story 23 S23-R2)</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr"/>
@@ -5835,12 +6067,14 @@
           <t>1. Detail rows order by invoice date descending (newest first).
 2. Date ties break by invoice number ascending by the numeric portion after the P/S prefix — numeric, not alphabetical, so S999 precedes S1000.
 3. If both the date and the numeric portion tie (e.g., P100 and S100 same day), P (Parts) sorts before S (Service).
-4. This order is independent of the rep-row column sort (which reorders summary rows only).</t>
+4. This order is independent of the rep-row column sort (which reorders summary rows only).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R9, S11-R2).</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>SV-8624 (specs/sbr-sales-by-representative.md Story 6 S6-R9; Story 11 S11-R2)</t>
+          <t>SV-8624 (SBR spec v15 2026-07-29 Story 6 S6-R9; Story 11 S11-R2)</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr"/>
@@ -5882,15 +6116,17 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>1. The Status column sits between the Customer column and the Inv. Hrs column.
+          <t>1. The Status column sits immediately after the Customer column. With a single location in scope the next column to its right is Inv. Hrs; when more than one location is in scope the automatic Location column is inserted immediately after Status, so Inv. Hrs then follows Location.
 2. Every detail row renders a small colored badge reading "Paid," "Partially Paid," or "Unpaid" — badge rendering is unconditional on detail rows.
 3. The mapping is: paid → Paid; overpaid → Paid; prepaid with zero balance → Paid; prepaid with a balance owed → Partially Paid; partially_paid → Partially Paid; unpaid → Unpaid.
-4. Badges are vertically centered in their cells; on rep summary rows the Status cell is blank; the badge's text is the accessible label — status is never conveyed by color alone.</t>
+4. Badges are vertically centered in their cells; on rep summary rows the Status cell is blank; the badge's text is the accessible label — status is never conveyed by color alone.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S8-R1, S8-R2, S8-R4, S8-R5, S8-R6, S8-N1, S18-R6).</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>SV-8625 (specs/sbr-sales-by-representative.md Story 8 S8-R1; S8-R2; S8-R4; S8-R5; S8-R6; S8-N1; §3 payment-status mapping; Story 18 S18-R6)</t>
+          <t>SV-8625 (SBR spec v15 2026-07-29 Story 8 S8-R1; S8-R2; S8-R4; S8-R5; S8-R6; S8-N1; §3 payment-status mapping; Story 18 S18-R6)</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr"/>
@@ -5932,12 +6168,14 @@
         <is>
           <t>1. Paid = dark teal text on light teal; Partially Paid = dark orange on light orange; Unpaid = dark red on light red.
 2. The badges use the same canonical payment-status color tokens as the invoice list, consistent app-wide.
-3. The treatment stays legible and consistent in both light and dark mode.</t>
+3. The treatment stays legible and consistent in both light and dark mode.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S8-R3, S18-R8).</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>SV-8625 (specs/sbr-sales-by-representative.md Story 8 S8-R3; Story 18 S18-R8)</t>
+          <t>SV-8625 (SBR spec v15 2026-07-29 Story 8 S8-R3; Story 18 S18-R8)</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr"/>
@@ -5978,12 +6216,14 @@
       <c r="G114" s="2" t="inlineStr">
         <is>
           <t>1. The column heading reads "Inv. Hrs" (verbatim, including the period after "Inv").
-2. The value equals the billed labor hours minus the technician clocked hours, rounded half-up to one decimal.</t>
+2. The value equals the billed labor hours minus the technician clocked hours, rounded half-up to one decimal.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S9-R1, S9-R2).</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>SV-8626 (specs/sbr-sales-by-representative.md Story 9 S9-R1; S9-R2; §3)</t>
+          <t>SV-8626 (SBR spec v15 2026-07-29 Story 9 S9-R1; S9-R2; §3)</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr"/>
@@ -6029,12 +6269,14 @@
           <t>1. Positive values show a leading + in green (e.g., +1.5); negative values a leading - in red (e.g., -1.5); zero/break-even shows 0.0 in the default text color.
 2. The same calculation, label, format, and coloring apply to rep summary rows, invoice detail rows, and the totals row.
 3. The rep-summary/totals value equals round(sum of unrounded per-invoice deltas).
-4. A value that rounds to 0.0 (e.g., +0.04) shows 0.0 in the default color — not +0.0 in green; negative values always use an explicit minus and one decimal (e.g., -0.5).</t>
+4. A value that rounds to 0.0 (e.g., +0.04) shows 0.0 in the default color — not +0.0 in green; negative values always use an explicit minus and one decimal (e.g., -0.5).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S9-R3, S9-R4, S9-R5, S9-R6, S9-E1, S9-E2).</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>SV-8626 (specs/sbr-sales-by-representative.md Story 9 S9-R3; S9-R4; S9-R5; S9-R6; S9-E1; S9-E2)</t>
+          <t>SV-8626 (SBR spec v15 2026-07-29 Story 9 S9-R3; S9-R4; S9-R5; S9-R6; S9-E1; S9-E2)</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr"/>
@@ -6075,12 +6317,14 @@
       <c r="G116" s="2" t="inlineStr">
         <is>
           <t>1. The invoice with neither billed labor hours nor clocked hours shows Inv. Hrs 0.0 in the default color — never blank, "N/A," or "—".
-2. The invoice with clocked hours but no billed labor line shows the resulting NEGATIVE delta in red (e.g., -3.0) — the worked-but-unbilled signal is not suppressed to 0.0.</t>
+2. The invoice with clocked hours but no billed labor line shows the resulting NEGATIVE delta in red (e.g., -3.0) — the worked-but-unbilled signal is not suppressed to 0.0.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S9-N1).</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>SV-8626 (specs/sbr-sales-by-representative.md Story 9 S9-N1)</t>
+          <t>SV-8626 (SBR spec v15 2026-07-29 Story 9 S9-N1)</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr"/>
@@ -6123,12 +6367,14 @@
         <is>
           <t>1. Margin % = Margin ÷ Subtotal × 100, to one decimal with a trailing % — e.g., 45.2%; a negative renders -8.4% (leading minus, no parentheses, no + on positives).
 2. It renders "—" when Subtotal ≤ 0 — never "0.0%" or a divide-by-zero result.
-3. On every rolled-up row (rep summary rows and every totals row) Margin % is RECOMPUTED from that row-set's total Margin and total Subtotal — never the sum or average of the child percentages.</t>
+3. On every rolled-up row (rep summary rows and every totals row) Margin % is RECOMPUTED from that row-set's total Margin and total Subtotal — never the sum or average of the child percentages.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S10-R5).</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>SV-8627 (specs/sbr-sales-by-representative.md §3 Margin % definition; Story 10 S10-R5)</t>
+          <t>SV-8627 (SBR spec v15 2026-07-29 §3 Margin % definition; Story 10 S10-R5)</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr"/>
@@ -6171,7 +6417,9 @@
           <t>1. The labels read exactly: Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 2. Subtotal = Labor Invoiced + Parts Invoiced, BEFORE tax.
 3. Labor Margin = Labor Invoiced − labor cost; Parts Margin = Parts Invoiced − parts cost; Margin = Labor Margin + Parts Margin.
-4. The same values appear everywhere the numbers show (screen, and later the exports).</t>
+4. The same values appear everywhere the numbers show (screen, and later the exports).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S5-R2, S21-R7).</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6217,7 +6465,9 @@
       <c r="G119" s="2" t="inlineStr">
         <is>
           <t>1. Negative dollar values render in accounting-convention parentheses — ($1,234.56) — on screen, across every money column (Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Subtotal).
-2. Inv. Hrs (a signed time value) and Margin % (a signed percentage) are excluded — they use a leading minus, not parentheses.</t>
+2. Inv. Hrs (a signed time value) and Margin % (a signed percentage) are excluded — they use a leading minus, not parentheses.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (§3 Key Decisions accounting parentheses).</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6263,7 +6513,9 @@
         <is>
           <t>1. All displayed values round half-up (away from zero) at their stated precision — money to cents; Inv. Hrs and Margin % to one decimal.
 2. Rolled-up values are computed from UNROUNDED components and then rounded, so a totals cell may differ from the eye-summed displayed rows by one unit in the last decimal.
-3. That one-unit difference is EXPECTED behavior per the spec — it must NOT be filed as a calculation defect.</t>
+3. That one-unit difference is EXPECTED behavior per the spec — it must NOT be filed as a calculation defect.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (§3 half).</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6311,12 +6563,14 @@
         <is>
           <t>1. The worked-hours side updates — Inv. Hrs (hours invoiced minus hours worked) reflects the edited clock time after the reload.
 2. The billed SELL values (Labor, Parts, Subtotal) stay unchanged — a clock edit never rewrites what was billed.
-3. The figures tied to worked time move together consistently (Margin uses the labor cost behind the worked hours, so it may change too) — nothing is left stale.</t>
+3. The figures tied to worked time move together consistently (Margin uses the labor cost behind the worked hours, so it may change too) — nothing is left stale.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S9-R2).</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>SV-8626 (specs/sbr-sales-by-representative.md §3 (hours worked = technician clocked hours recorded against that work order); Story 9 S9-R2; tech-plan-2026-07-29 Phase 4 FR-F7 clock-change rebuild)</t>
+          <t>SV-8626 (SBR spec v15 2026-07-29 §3 (hours worked = technician clocked hours recorded against that work order); Story 9 S9-R2; tech-plan-2026-07-29 Phase 4 FR-F7 clock-change rebuild)</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr"/>
@@ -6363,12 +6617,14 @@
 2. On screen it is pinned to the right edge and stays visible during horizontal scroll on every rep summary and invoice detail row.
 3. Subtotal values are bold across the header, every summary row, every detail row, and the grand Totals indicator.
 4. The pinned column matches the row's background color (white on body rows) — not a contrasting strip.
-5. The column-header row stays stuck to the top during vertical scroll; the Subtotal header cell stays visible in BOTH axes (top while scrolling down, pinned right while scrolling sideways).</t>
+5. The column-header row stays stuck to the top during vertical scroll; the Subtotal header cell stays visible in BOTH axes (top while scrolling down, pinned right while scrolling sideways).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R6, S10-N1, S18-R7).</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>SV-8627 (specs/sbr-sales-by-representative.md Story 10 S10-R1; S10-R2; S10-R3; S10-R4; S10-R6; S10-N1; Story 18 S18-R7.5)</t>
+          <t>SV-8627 (SBR spec v15 2026-07-29 Story 10 S10-R1; S10-R2; S10-R3; S10-R4; S10-R6; S10-N1; Story 18 S18-R7.5)</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr"/>
@@ -6414,12 +6670,14 @@
 2. Its first cell is a single merged cell spanning the four leading identifier columns (Date, Invoice, Customer, Status) labeled "Totals," followed by a cell per metric column and its own pinned Subtotal cell.
 3. The grand totals cover the FULL filtered result set — every matching non-reversed invoice across every rep, independent of which reps are expanded or loaded.
 4. Money uses accounting parentheses for negatives; Margin % is recomputed; values are round(sum of unrounded).
-5. The indicator is present whenever at least one summary row exists, and hidden during loading and in the empty state.</t>
+5. The indicator is present whenever at least one summary row exists, and hidden during loading and in the empty state.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S10-R5, S10-N1, S16-R4).</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>SV-8627 (specs/sbr-sales-by-representative.md Story 10 S10-R5; S10-N1; Story 16 S16-R4)</t>
+          <t>SV-8627 (SBR spec v15 2026-07-29 Story 10 S10-R5; S10-N1; Story 16 S16-R4)</t>
         </is>
       </c>
       <c r="I123" s="2" t="inlineStr"/>
@@ -6463,7 +6721,9 @@
           <t>1. A simplified external totals bar sits directly below the table, outside its horizontal scroll container, showing "Totals" on the left and the grand Subtotal on the right (no other metrics).
 2. It does not scroll horizontally — it is always fully visible across.
 3. During vertical page scroll it sits after the table in normal flow (not pinned to the viewport bottom).
-4. It uses the white card surface with a thin top border.</t>
+4. It uses the white card surface with a thin top border.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S10-R5, S17-R4).</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -6510,12 +6770,14 @@
         <is>
           <t>1. Each financial column responds to a header click and reorders the rep rows.
 2. The identifier columns (Date, Invoice, Customer, Status) do not respond to header clicks.
-3. The Date header carries the expand/collapse-all chevron, not a sort affordance.</t>
+3. The Date header carries the expand/collapse-all chevron, not a sort affordance.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R1, S11-R6).</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>SV-8628 (specs/sbr-sales-by-representative.md Story 11 S11-R1; S11-R6)</t>
+          <t>SV-8628 (SBR spec v15 2026-07-29 Story 11 S11-R1; S11-R6)</t>
         </is>
       </c>
       <c r="I125" s="2" t="inlineStr"/>
@@ -6555,12 +6817,14 @@
       <c r="G126" s="2" t="inlineStr">
         <is>
           <t>1. Rows render in A→Z order by display name, case-insensitive.
-2. There are NO active/inactive tiers — an "(Inactive)" rep sorts by name among the others, not grouped separately.</t>
+2. There are NO active/inactive tiers — an "(Inactive)" rep sorts by name among the others, not grouped separately.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R4).</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>SV-8628 (specs/sbr-sales-by-representative.md Story 11 S11-R4; §3 Key Decisions)</t>
+          <t>SV-8628 (SBR spec v15 2026-07-29 Story 11 S11-R4; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr"/>
@@ -6605,12 +6869,14 @@
           <t>1. The first click sorts Subtotal ASCENDING and shows an ascending direction indicator on the header.
 2. The second click toggles to DESCENDING.
 3. There is no third "cleared" state — the third click returns to ascending.
-4. Via the column headers there is no way back to A→Z; the A→Z default shows only when a session carries no valid saved financial sort.</t>
+4. Via the column headers there is no way back to A→Z; the A→Z default shows only when a session carries no valid saved financial sort.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R5, S23-R5).</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>SV-8628 (specs/sbr-sales-by-representative.md Story 11 S11-R5; Story 23 S23-R5)</t>
+          <t>SV-8628 (SBR spec v15 2026-07-29 Story 11 S11-R5; Story 23 S23-R5)</t>
         </is>
       </c>
       <c r="I127" s="2" t="inlineStr"/>
@@ -6652,12 +6918,14 @@
         <is>
           <t>1. Only the rep summary rows reorder.
 2. Invoice detail rows stay grouped under their parent rep, keeping their own newest-first order.
-3. The Unassigned row stays pinned to the top regardless of sort.</t>
+3. The Unassigned row stays pinned to the top regardless of sort.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R2, S22-R4).</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>SV-8628 (specs/sbr-sales-by-representative.md Story 11 S11-R2; Story 22 S22-R4)</t>
+          <t>SV-8628 (SBR spec v15 2026-07-29 Story 11 S11-R2; Story 22 S22-R4)</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr"/>
@@ -6698,12 +6966,14 @@
       <c r="G129" s="2" t="inlineStr">
         <is>
           <t>1. Reps with equal values in the sorted column retain the default A→Z order between them.
-2. A Margin % cell rendered "—" (undefined) sorts as zero.</t>
+2. A Margin % cell rendered "—" (undefined) sorts as zero.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R7).</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>SV-8628 (specs/sbr-sales-by-representative.md Story 11 S11-R7)</t>
+          <t>SV-8628 (SBR spec v15 2026-07-29 Story 11 S11-R7)</t>
         </is>
       </c>
       <c r="I129" s="2" t="inlineStr"/>
@@ -6746,12 +7016,14 @@
         <is>
           <t>1. Each invoice number is a clickable link.
 2. Activating it navigates the CURRENT tab to the underlying invoice (work order or parts sale) — never a new tab.
-3. The customer name is likewise a clickable link that navigates the current tab to the customer's record.</t>
+3. The customer name is likewise a clickable link that navigates the current tab to the customer's record.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S12-R1, S12-R2, S12-R3).</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>SV-8629 (specs/sbr-sales-by-representative.md Story 12 S12-R1; S12-R2; S12-R3)</t>
+          <t>SV-8629 (SBR spec v15 2026-07-29 Story 12 S12-R1; S12-R2; S12-R3)</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr"/>
@@ -6794,12 +7066,14 @@
         <is>
           <t>1. Back returns to the report with ALL state intact — date range, product type, invoice status, location, Show Unassigned, every rep's expansion state, and scroll position — exactly as they were.
 2. Back-navigation does not trigger a full report reload.
-3. This is deliberately different from a page reload, which restores persisted filters/columns/sort but resets expansion and scroll.</t>
+3. This is deliberately different from a page reload, which restores persisted filters/columns/sort but resets expansion and scroll.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S12-R3a, S23-R2).</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>SV-8629 (specs/sbr-sales-by-representative.md Story 12 S12-R3a; Story 23 S23-R2)</t>
+          <t>SV-8629 (SBR spec v15 2026-07-29 Story 12 S12-R3a; Story 23 S23-R2)</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr"/>
@@ -6843,12 +7117,14 @@
           <t>1. Invoice-number link: theme-primary color, no underline at rest; an underline appears on hover and on keyboard focus (visible focus indicator); it never recolors to browser-purple after a click.
 2. Customer-name link: inherits the cell's body text color (never theme-blue), no underline at rest; underline on hover and keyboard focus; never browser-purple.
 3. Both hold in light and dark mode and across return visits.
-4. Underlined-at-rest links, browser-blue customer names, purple post-click links, and new-tab destinations are all defects.</t>
+4. Underlined-at-rest links, browser-blue customer names, purple post-click links, and new-tab destinations are all defects.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S12-R4, S12-R5, S12-R6, S12-N3).</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>SV-8629 (specs/sbr-sales-by-representative.md Story 12 S12-R4; S12-R5; S12-R6; S12-N3)</t>
+          <t>SV-8629 (SBR spec v15 2026-07-29 Story 12 S12-R4; S12-R5; S12-R6; S12-N3)</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr"/>
@@ -6889,12 +7165,14 @@
       <c r="G133" s="2" t="inlineStr">
         <is>
           <t>1. The tab navigates to the application's standard not-found/access-denied state.
-2. Pressing back still returns to the report.</t>
+2. Pressing back still returns to the report.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S12-N1, S12-N2).</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>SV-8629 (specs/sbr-sales-by-representative.md Story 12 S12-N1; S12-N2)</t>
+          <t>SV-8629 (SBR spec v15 2026-07-29 Story 12 S12-N1; S12-N2)</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr"/>
@@ -6937,12 +7215,14 @@
         <is>
           <t>1. A warning dialog titled "Deactivate {Staff Name}?" opens BEFORE any change is applied; the deactivation does not commit until confirmed.
 2. The body shows "{Staff Name} is the sales representative on {N} customer{s}." — singular for N=1 ("1 customer"), plural otherwise ("3 customers") — followed by the reassurance line "Their customer assignments will stay where they are."
-3. Focus is trapped within the dialog while open and returns to the invoking control on dismiss.</t>
+3. Focus is trapped within the dialog while open and returns to the invoking control on dismiss.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R1, S13-R3, S13-R4, S13-R12).</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R1; S13-R3; S13-R4; S13-R12)</t>
+          <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R1; S13-R3; S13-R4; S13-R12)</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr"/>
@@ -6987,12 +7267,14 @@
           <t>1. Below the reassurance copy, instruction text reads "Type YES to confirm" (with "YES" emphasized) above a single auto-focused text input.
 2. The primary "Deactivate" button is disabled until the input matches the confirmation word case-insensitively, ignoring leading/trailing whitespace — yes, YES, Yes (and padded variants) all enable it; "no" does not.
 3. While disabled, hovering it shows the tooltip "Type YES above to enable."
-4. Pressing Enter while valid submits.</t>
+4. Pressing Enter while valid submits.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R6, S13-R7).</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R6; S13-R7)</t>
+          <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R6; S13-R7)</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr"/>
@@ -7039,12 +7321,14 @@
 2. Clicking "Cancel" closes the dialog; clicking the "X" icon closes the dialog.
 3. Pressing the "Esc" key does NOT close the dialog - it stays open (the app's general rule is that pop-ups do not close with the Esc key).
 4. Clicking outside the dialog does NOT close it.
-5. When the dialog closes via Cancel or X, the staff member's active status is unchanged - no deactivation happens.</t>
+5. When the dialog closes via Cancel or X, the staff member's active status is unchanged - no deactivation happens.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R8).</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R8)</t>
+          <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R8)</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr"/>
@@ -7087,12 +7371,14 @@
           <t>1. The "Deactivate" button enters the standard in-flight loading state (non-interactive, in-progress indicator); the dialog stays open and the Cancel and X controls are non-interactive during the request (pressing the "Esc" key never closes the dialog at any time).
 2. On success the dialog closes and the change applies.
 3. Customer assignments are NOT modified — every customer stays assigned to this rep; denormalized rep names and past invoice snapshots are preserved.
-4. Deactivation never forces reassignment, blocks on assignments, or auto-reassigns.</t>
+4. Deactivation never forces reassignment, blocks on assignments, or auto-reassigns.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R9, S13-R10, S13-E1).</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R9; S13-R10; S13-E1)</t>
+          <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R9; S13-R10; S13-E1)</t>
         </is>
       </c>
       <c r="I137" s="2" t="inlineStr"/>
@@ -7135,12 +7421,14 @@
         <is>
           <t>1. The sales-representative toggle state is unchanged by the deactivation flow.
 2. In the Sales Representative Assignments CSV the rep's customers show "Rep is active?" = "No" — that column is driven by staff-active status, not the toggle.
-3. In the report the rep still appears with credit intact; the "(Inactive)" marker appears only if the sales-representative TOGGLE is off (a separate flag from staff-active status).</t>
+3. In the report the rep still appears with credit intact; the "(Inactive)" marker appears only if the sales-representative TOGGLE is off (a separate flag from staff-active status).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R11, S15-R6, S5-R9).</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R11; Story 15 S15-R6; Story 5 S5-R9)</t>
+          <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R11; Story 15 S15-R6; Story 5 S5-R9)</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr"/>
@@ -7184,12 +7472,14 @@
           <t>1. For a staff member without the sales-representative toggle, the precondition check is skipped and no warning is shown.
 2. Reactivation never shows the warning dialog (the flow does not apply to an already-inactive member).
 3. After reactivation the assignments re-surface immediately with no extra action.
-4. Deactivating a sales representative with NO customer assignments applies silently — no warning dialog.</t>
+4. Deactivating a sales representative with NO customer assignments applies silently — no warning dialog.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R2, S13-N2, S13-N3, S13-E3).</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R2; S13-N2; S13-N3; S13-E3)</t>
+          <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R2; S13-N2; S13-N3; S13-E3)</t>
         </is>
       </c>
       <c r="I139" s="2" t="inlineStr"/>
@@ -7232,12 +7522,14 @@
         <is>
           <t>1. An error toast is shown: "Ooooops! An error occured" with the caption "For more information, please contact support. Include your request ID: [{request-id}] when reaching out for faster assistance." — it persists 120 seconds or until dismissed.
 2. The active status is unchanged.
-3. Each fresh dialog open requires a fresh confirmation entry — the input clears on open.</t>
+3. Each fresh dialog open requires a fresh confirmation entry — the input clears on open.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-N5).</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-N5; §7)</t>
+          <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-N5; §7)</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr"/>
@@ -7279,12 +7571,14 @@
       <c r="G141" s="2" t="inlineStr">
         <is>
           <t>1. The system NEVER silently deactivates — the warning dialog still opens (fallback), so the type-to-confirm gate still applies.
-2. Because the customer count is unavailable, the dialog OMITS the count headline and shows only the reassurance line "Their customer assignments will stay where they are." above the "Type YES to confirm" gate.</t>
+2. Because the customer count is unavailable, the dialog OMITS the count headline and shows only the reassurance line "Their customer assignments will stay where they are." above the "Type YES to confirm" gate.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-N4).</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-N4)</t>
+          <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-N4)</t>
         </is>
       </c>
       <c r="I141" s="2" t="inlineStr"/>
@@ -7325,12 +7619,14 @@
       <c r="G142" s="2" t="inlineStr">
         <is>
           <t>1. A "Show Unassigned" toggle sits between the column selector and the date range picker; it is OFF by default.
-2. While off, invoices with no assigned rep contribute to nothing — no row, and not counted in any total.</t>
+2. While off, invoices with no assigned rep contribute to nothing — no row, and not counted in any total.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S22-R1, S22-R2, S18-R7).</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>SV-8639 (specs/sbr-sales-by-representative.md Story 22 S22-R1; S22-R2; Story 18 S18-R7.2)</t>
+          <t>SV-8639 (SBR spec v15 2026-07-29 Story 22 S22-R1; S22-R2; Story 18 S18-R7.2)</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr"/>
@@ -7375,12 +7671,14 @@
           <t>1. A single summary row labeled "Unassigned" (verbatim) rolls up every matching invoice that has no assigned rep, respecting all other active filters.
 2. The row is pinned to the TOP of the table, above the A→Z reps, and stays pinned regardless of sort.
 3. Toggling re-renders the report and recomputes the grand Totals to include or exclude the Unassigned row accordingly.
-4. The Unassigned row shows the same metric columns and (N) count as any rep summary row, is expandable to its contributing invoices, is included in the grand Totals, and never carries an "(Inactive)" tag.</t>
+4. The Unassigned row shows the same metric columns and (N) count as any rep summary row, is expandable to its contributing invoices, is included in the grand Totals, and never carries an "(Inactive)" tag.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S22-R3, S22-R4, S22-R5, S22-R6, S6-R1).</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>SV-8639 (specs/sbr-sales-by-representative.md Story 22 S22-R3; S22-R4; S22-R5; S22-R6; Story 6 S6-R1)</t>
+          <t>SV-8639 (SBR spec v15 2026-07-29 Story 22 S22-R3; S22-R4; S22-R5; S22-R6; Story 6 S6-R1)</t>
         </is>
       </c>
       <c r="I143" s="2" t="inlineStr"/>
@@ -7422,12 +7720,14 @@
       <c r="G144" s="2" t="inlineStr">
         <is>
           <t>1. With the toggle on but no matching unassigned invoices, no Unassigned row is shown — an empty Unassigned row is never rendered; with no rep rows either, the empty state applies.
-2. Turning the toggle off removes the expanded row; turning it back on renders it collapsed.</t>
+2. Turning the toggle off removes the expanded row; turning it back on renders it collapsed.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S22-N1, S6-N2).</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>SV-8639 (specs/sbr-sales-by-representative.md Story 22 S22-N1; Story 6 S6-N2)</t>
+          <t>SV-8639 (SBR spec v15 2026-07-29 Story 22 S22-N1; Story 6 S6-N2)</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr"/>
@@ -7474,7 +7774,9 @@
 2. On first visit all seven metric columns are visible.
 3. The five always-visible columns (Date, Invoice, Customer, Status, Subtotal) do not appear in the dropdown and cannot be hidden.
 4. With all seven metric columns hidden the table still renders the five always-on columns and the grand Totals indicator — no empty or error state.
-5. Note for the tester: if you have more than one location in scope you will also see a Location column on the table that is in neither list. That is correct - it appears by itself and is not something you can switch on or off here.</t>
+5. Note for the tester: if you have more than one location in scope you will also see a Location column on the table that is in neither list. That is correct - it appears by itself and is not something you can switch on or off here.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S20-R1, S20-R2, S20-R3, S20-R6, S20-N1, S21-R7).</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7520,12 +7822,14 @@
       <c r="G146" s="2" t="inlineStr">
         <is>
           <t>1. The toggle takes effect immediately — no confirm step.
-2. Hiding a metric column removes it from rep summary rows, invoice detail rows, and the grand Totals indicator simultaneously; showing restores it everywhere at once.</t>
+2. Hiding a metric column removes it from rep summary rows, invoice detail rows, and the grand Totals indicator simultaneously; showing restores it everywhere at once.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S20-R4, S20-R7).</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>SV-8637 (specs/sbr-sales-by-representative.md Story 20 S20-R4; S20-R7)</t>
+          <t>SV-8637 (SBR spec v15 2026-07-29 Story 20 S20-R4; S20-R7)</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr"/>
@@ -7565,12 +7869,14 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>1. All four downloads include ALL metric columns regardless of the on-screen column selector state.</t>
+          <t>1. All four downloads include ALL metric columns regardless of the on-screen column selector state.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S20-R8).</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>SV-8637 (specs/sbr-sales-by-representative.md Story 20 S20-R8)</t>
+          <t>SV-8637 (SBR spec v15 2026-07-29 Story 20 S20-R8)</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr"/>
@@ -7611,12 +7917,14 @@
       <c r="G148" s="2" t="inlineStr">
         <is>
           <t>1. Hiding the active sort column does not clear the sort — rows stay ordered by the now-hidden metric until another sort is chosen or the A→Z default is restored.
-2. Showing the column again reveals the sort indicator on it.</t>
+2. Showing the column again reveals the sort indicator on it.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S20-R9).</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>SV-8637 (specs/sbr-sales-by-representative.md Story 20 S20-R9)</t>
+          <t>SV-8637 (SBR spec v15 2026-07-29 Story 20 S20-R9)</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr"/>
@@ -7658,12 +7966,14 @@
       <c r="G149" s="2" t="inlineStr">
         <is>
           <t>1. Every setting is restored: date range (including the custom start/end), product type, invoice status, location, Show Unassigned, column visibility, and the active column sort (column + direction).
-2. The settings are restored BEFORE the first data fetch — the report does not fetch defaults first and then re-fetch.</t>
+2. The settings are restored BEFORE the first data fetch — the report does not fetch defaults first and then re-fetch.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S23-R1, S20-R5).</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>SV-8640 (specs/sbr-sales-by-representative.md Story 23 S23-R1; Story 20 S20-R5)</t>
+          <t>SV-8640 (SBR spec v15 2026-07-29 Story 23 S23-R1; Story 20 S20-R5)</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr"/>
@@ -7704,12 +8014,14 @@
       <c r="G150" s="2" t="inlineStr">
         <is>
           <t>1. All rows render collapsed and the scroll position resets.
-2. This is the specified behavior (only back-navigation from a drilldown restores expansion/scroll), not a defect.</t>
+2. This is the specified behavior (only back-navigation from a drilldown restores expansion/scroll), not a defect.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S23-R2).</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>SV-8640 (specs/sbr-sales-by-representative.md Story 23 S23-R2; §2 Out of Scope)</t>
+          <t>SV-8640 (SBR spec v15 2026-07-29 Story 23 S23-R2; §2 Out of Scope)</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr"/>
@@ -7751,12 +8063,14 @@
         <is>
           <t>1. The no-longer-valid location falls back to the default (your active location) rather than being sent to the server.
 2. No error occurs — a stale saved setting can never cause an error or an invalid request.
-3. Per the spec the same applies to a range or sort column that no longer exists and to a hidden-but-sorted column.</t>
+3. Per the spec the same applies to a range or sort column that no longer exists and to a hidden-but-sorted column.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S23-R3).</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>SV-8640 (specs/sbr-sales-by-representative.md Story 23 S23-R3)</t>
+          <t>SV-8640 (SBR spec v15 2026-07-29 Story 23 S23-R3)</t>
         </is>
       </c>
       <c r="I151" s="2" t="inlineStr"/>
@@ -7797,7 +8111,9 @@
       <c r="G152" s="2" t="inlineStr">
         <is>
           <t>1. Date range = This Month; Product Type = "Parts &amp; Service"; Invoice Status = "All Statuses"; Location = your currently active location only (the one location you are working in); Show Unassigned = off; all seven metric columns visible; sort = the A→Z default.
-2. Clearing browser storage fully returns the report to first-visit defaults — no server-side profile brings the old settings back.</t>
+2. Clearing browser storage fully returns the report to first-visit defaults — no server-side profile brings the old settings back.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S23-R4, S23-N1, S2-R4, S2-R7, S21-R2).</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -7843,12 +8159,14 @@
       <c r="G153" s="2" t="inlineStr">
         <is>
           <t>1. The report restores to the A→Z default order by rep display name.
-2. No financial column shows a sort indicator — the saved "no financial sort" state restores as A→Z, not as an arbitrary column.</t>
+2. No financial column shows a sort indicator — the saved "no financial sort" state restores as A→Z, not as an arbitrary column.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S23-R5, S11-R4).</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>SV-8640 (specs/sbr-sales-by-representative.md Story 23 S23-R5; Story 11 S11-R4)</t>
+          <t>SV-8640 (SBR spec v15 2026-07-29 Story 23 S23-R5; Story 11 S11-R4)</t>
         </is>
       </c>
       <c r="I153" s="2" t="inlineStr"/>
@@ -7890,7 +8208,9 @@
       <c r="G154" s="2" t="inlineStr">
         <is>
           <t>1. The menu lists exactly four actions: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", and "Download Expanded View (CSV)".
-2. No other entries appear in the menu.</t>
+2. No other entries appear in the menu.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R1, S17-R3).</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -7943,7 +8263,9 @@
 2. The files reflect the FULL result set for those filters — a collapsed (never-expanded) rep's invoices still appear in the Expanded View files; on-screen expansion state does not matter.
 3. Rep rows appear in the report's currently-active order — the active column sort if one is set, otherwise the A→Z default.
 4. The Unassigned row (Show Unassigned on) is pinned first, ahead of the sorted reps.
-5. Every file (all four downloads, PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).</t>
+5. Every file (all four downloads, PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R2, S14-R2a, S14-R20, S21-R6, S22-R4).</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -7994,7 +8316,9 @@
 2. There is one rolled-up row per rep, in the report's currently-active order; a toggled-off contributor's name carries the "(Inactive)" tag.
 3. With a single location in scope the columns are: Rep / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal. When more than one location is in scope a Location column is added with the identifying columns ahead of Inv. Hrs, and a rep who spans more than one location reads "Multiple" (this file has no Status column for it to follow — confirm its exact position in the build).
 4. Subtotal is bolded across the header, the body rows, and the grand totals row; Inv. Hrs keeps its green/red/default coloring.
-5. The grand totals row reads "Totals" in the Rep cell and aggregates every summary row in the document (including the Unassigned row when Show Unassigned is on); its Margin % is RECOMPUTED as total Margin ÷ total Subtotal (shown "—" when that Subtotal is zero or below), never the sum or average of the rows' percentages.</t>
+5. The grand totals row reads "Totals" in the Rep cell and aggregates every summary row in the document (including the Unassigned row when Show Unassigned is on); its Margin % is RECOMPUTED as total Margin ÷ total Subtotal (shown "—" when that Subtotal is zero or below), never the sum or average of the rows' percentages.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R3, S14-R5, S14-R20, S2-R5).</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8046,7 +8370,9 @@
 3. The Status column renders the same colored badge as on screen, vertically centered.
 4. Invoices are ordered newest first (the same order as the on-screen expansion: invoice date descending, numeric invoice-number tie-break).
 5. Each block ends with a per-rep totals row — "Totals" in the Date cell; Invoice/Customer/Status blank; each metric aggregated; Margin % recomputed.
-6. There is NO grand-totals row across all reps at the end of the document.</t>
+6. There is NO grand-totals row across all reps at the end of the document.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R6, S14-R8, S14-R20, S6-R9).</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -8093,12 +8419,14 @@
         <is>
           <t>1. On screen, both invoice numbers show in full — never truncated.
 2. In the PDF, the long number is cut to its first 18 characters followed by an ellipsis (the ellipsis is not counted toward the 18).
-3. In the PDF, the 18-character-or-shorter number shows in full with no ellipsis.</t>
+3. In the PDF, the 18-character-or-shorter number shows in full with no ellipsis.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R7).</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R7)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R7)</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr"/>
@@ -8142,7 +8470,9 @@
         <is>
           <t>1. The files are named exactly "sales-by-representative-summary.pdf" and "sales-by-representative-expanded.pdf".
 2. A footer reading "Software Powered by ShopView" appears on EVERY page of both PDFs.
-3. With no configured logo, the logo region falls back to the default ShopView logo and the PDF still generates normally.</t>
+3. With no configured logo, the logo region falls back to the default ShopView logo and the PDF still generates normally.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R3a, S14-R4, S14-R11).</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8190,12 +8520,14 @@
         <is>
           <t>1. Negative dollar values render in accounting parentheses — for example ($1,234.56) — in both PDFs, with no extra color treatment.
 2. The on-screen (N) invoice count does NOT appear next to any rep name in either PDF.
-3. The "(Inactive)" tag DOES render on toggled-off contributors' names in both PDFs; other rep names render plainly.</t>
+3. The "(Inactive)" tag DOES render on toggled-off contributors' names in both PDFs; other rep names render plainly.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R9, S14-R10).</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R9; S14-R10)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R9; S14-R10)</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr"/>
@@ -8224,7 +8556,8 @@
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>1. You can produce (or seed) filtered views whose LONGEST formatted positive dollar value — checked across every value in the document, including the totals row — falls in different length brackets (for example, $1,234.56 = 9 characters vs $1,000,000.00 = 13 characters).</t>
+          <t>1. You can produce (or seed) filtered views whose LONGEST formatted positive dollar value — checked across every value in the document, including the totals row — falls in different length brackets (for example, $1,234.56 = 9 characters vs $1,000,000.00 = 13 characters).
+2. This test reads what is inside a downloaded PDF. Open the file in any PDF viewer and use the viewer's own text search (Ctrl+F) to find the text named below — that is enough. There is nothing to install.</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
@@ -8238,12 +8571,14 @@
         <is>
           <t>1. As the longest positive dollar value in the document grows past each length bracket, the PDF body text visibly steps DOWN in size — the relative step-downs are the pass criterion for this manual test.
 2. Column widths are fixed for the worst case regardless of tier — the layout never breaks and no value overflows or wraps its column.
-3. Both PDF formats adapt the same way.</t>
+3. Both PDF formats adapt the same way.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R12, S14-R13).</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R12; S14-R13)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R12; S14-R13)</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr"/>
@@ -8291,7 +8626,9 @@
 4. "# Invoices" equals the on-screen (N); "# Customers" counts distinct customers across those invoices (de-duplicated across locations when several are selected).
 5. The CSV has NO totals row.
 6. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
-7. When more than one location is in scope the file also carries a Location column, with the identifying columns ahead of the metric columns; a rep whose invoices span more than one location reads "Multiple". (This file has no Status column for it to follow — confirm its exact position in the build.)</t>
+7. When more than one location is in scope the file also carries a Location column, with the identifying columns ahead of the metric columns; a rep whose invoices span more than one location reads "Multiple". (This file has no Status column for it to follow — confirm its exact position in the build.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R15, S14-R18, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -8341,7 +8678,9 @@
 2. With a single location in scope the headers, in order, are exactly: Sales Representative, Date, Invoice #, Customer, Status, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 3. There is one header row plus one row per invoice, flattened across all reps in the report's currently-active order, for the current filtered view.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
-5. When more than one location is in scope the file also carries a Location column immediately after Status — the position it holds on screen — and every row shows that invoice's own exact location, never "Multiple".</t>
+5. When more than one location is in scope the file also carries a Location column immediately after Status — the position it holds on screen — and every row shows that invoice's own exact location, never "Multiple".
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R16, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -8391,12 +8730,14 @@
 3. Margin % is a plain number to one decimal (for example, 45.2) with no % sign, and the cell is EMPTY where Margin % is undefined (Subtotal ≤ 0).
 4. The "Sales Representative" name carries the "(Inactive)" tag when applicable; the on-screen (N) count is NOT embedded in the name.
 5. Text fields are quoted per standard CSV escaping; both CSVs are monochrome (Inv. Hrs conveys direction only by its sign).
-6. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+6. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R17).</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R17; §3 Key Decisions (CSVs monochrome / plain signed numbers))</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R17; §3 Key Decisions (CSVs monochrome / plain signed numbers))</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr"/>
@@ -8441,12 +8782,14 @@
           <t>1. With the toggle ON: the Summary PDF and Summary CSV each carry one rolled-up row whose Rep / "Sales Representative" cell reads the literal "Unassigned", sorted to the top; the Expanded CSV rows for those invoices carry "Sales Representative" = "Unassigned"; the Expanded View PDF has its own TOP page-block titled "Unassigned".
 2. The Summary PDF grand-totals row aggregates across all summary rows INCLUDING Unassigned; in the Summary CSV the Unassigned row is simply one of the data rows (no totals row exists).
 3. With the toggle OFF: no Unassigned row and no unassigned invoices appear in ANY of the four files.
-4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R19, S22-R2, S22-R4).</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R19; Story 22 S22-R2; S22-R4)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R19; Story 22 S22-R2; S22-R4)</t>
         </is>
       </c>
       <c r="I165" s="2" t="inlineStr"/>
@@ -8476,7 +8819,8 @@
       <c r="E166" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with data showing.
-2. You can force a download failure (for example, cut the network just after triggering the download) — if not forceable, mark this Blocked with the reason.</t>
+2. You can force a download failure (for example, cut the network just after triggering the download) — if not forceable, mark this Blocked with the reason.
+3. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
       <c r="F166" s="2" t="inlineStr">
@@ -8489,12 +8833,14 @@
         <is>
           <t>1. While a PDF is generating, the action shows a loading state and is non-interactive until the file is delivered.
 2. A failed download shows the error toast "Ooooops! An error occured" (the typo is as-shipped) — it persists 120 seconds or until dismissed.
-3. A genuine failure downloads nothing — never a malformed file.</t>
+3. A genuine failure downloads nothing — never a malformed file.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-N1, S14-N2, S14-E1).</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-N1; S14-N2; S14-E1; §7)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-N1; S14-N2; S14-E1; §7)</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr"/>
@@ -8536,7 +8882,10 @@
         <is>
           <t>1. No file is produced — the server declines rather than generating a truncated file.
 2. An error toast reads exactly: "This report is too large to export. Narrow the date range or filters, then try again." (persists 120 seconds or until dismissed).
-3. Below the cap, a large Expanded View PDF still generates normally (many reps × many invoices is expected).</t>
+3. Below the cap, a large Expanded View PDF still generates normally (many reps × many invoices is expected).
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-E2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8585,12 +8934,14 @@
 2. The Summary PDF renders the header strip, no data rows, and a grand-totals row showing zeros for the money and Inv. Hrs columns and "—" for Margin %.
 3. The Expanded View PDF renders just the header strip with no per-rep blocks (it has no grand-totals row).
 4. Both CSVs generate a header-row-only file, still starting with the UTF-8 BOM.
-5. No special "empty" treatment or message appears inside the files.</t>
+5. No special "empty" treatment or message appears inside the files.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-E3).</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-E3)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-E3)</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr"/>
@@ -8635,12 +8986,14 @@
           <t>1. "Sales Representative Assignments" appears in the Report Name dropdown, appended at the BOTTOM of the list (additive — no existing entry moved or removed).
 2. Selecting it HIDES the date range picker.
 3. The dialog shows the note: "Snapshot of current sales representative assignments. Both active and inactive reps with assignments are listed."
-4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R1, S15-R2).</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>SV-8632 (specs/sbr-sales-by-representative.md Story 15 S15-R1; S15-R2)</t>
+          <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R1; S15-R2)</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr"/>
@@ -8682,11 +9035,13 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>1. The file downloads as "sales-representative-assignments.csv (the short form "rep" is gone from the file name — confirm the exact final file name in the build)".
+          <t>1. The file downloads as "sales-representative-assignments.csv" — the short form "rep" is gone from the file name.
 2. A success toast shows "Success" with the caption "Report downloaded." and auto-fades after 5 seconds.
 3. The CSV starts with a UTF-8 BOM and its headers, in order, are exactly: Customer Name, Sales Representative, Rep is active?.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
-5. Note for the tester: this file has only those three columns even if you have several locations in scope. It is a separate customer-to-representative list, not one of the report's four downloads, so it has no Location column - do not fail it for that.</t>
+5. Note for the tester: this file has only those three columns even if you have several locations in scope. It is a separate customer-to-representative list, not one of the report's four downloads, so it has no Location column - do not fail it for that.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R3, S15-R4, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -8735,12 +9090,14 @@
         <is>
           <t>1. Every customer with an assigned sales representative produces exactly ONE row (single-rep model: one rep per customer).
 2. Customers with no assigned rep are NOT included.
-3. Rows are sorted by customer name A→Z (primary), then rep name A→Z (secondary).</t>
+3. Rows are sorted by customer name A→Z (primary), then rep name A→Z (secondary).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R5, S15-R7, S15-R10).</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>SV-8632 (specs/sbr-sales-by-representative.md Story 15 S15-R5; S15-R7; S15-R10)</t>
+          <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R5; S15-R7; S15-R10)</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr"/>
@@ -8782,12 +9139,14 @@
         <is>
           <t>1. The staff-ACTIVE / toggle-off rep shows "Rep is active?" = "Yes" — the toggle does not drive this column.
 2. The staff-INACTIVE / toggle-on rep shows "Rep is active?" = "No".
-3. The value is always "Yes" or "No" (never "Deactivated" or another word).</t>
+3. The value is always "Yes" or "No" (never "Deactivated" or another word).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R6, S13-R11).</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>SV-8632 (specs/sbr-sales-by-representative.md Story 15 S15-R6; Story 13 S13-R11)</t>
+          <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R6; Story 13 S13-R11)</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr"/>
@@ -8831,12 +9190,14 @@
           <t>1. The customer still produces a row — the export never silently drops it.
 2. The "Sales Representative" name comes from the customer-side stored (denormalized) rep name, and "Rep is active?" = "No".
 3. When stored names differ across customers for the same rep (name drift), each customer's row uses its OWN stored name — drift never adds extra rows for a customer and never overwrites one customer's stored name with another's.
-4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R8, S15-R9).</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>SV-8632 (specs/sbr-sales-by-representative.md Story 15 S15-R8; S15-R9)</t>
+          <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R8; S15-R9)</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr"/>
@@ -8879,12 +9240,14 @@
       <c r="G174" s="2" t="inlineStr">
         <is>
           <t>1. With zero assigned customers, the CSV downloads with a header row and no data rows, and the dialog shows its empty-export warning: "There is no data to export for the selected report."
-2. On a generation failure, an error toast reads "An error occurred while exporting the report. Please try again." and auto-fades after 5 seconds.</t>
+2. On a generation failure, an error toast reads "An error occurred while exporting the report. Please try again." and auto-fades after 5 seconds.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R11, S15-N2).</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>SV-8632 (specs/sbr-sales-by-representative.md Story 15 S15-R11; S15-N2; §7)</t>
+          <t>SV-8632 (SBR spec v15 2026-07-29 Story 15 S15-R11; S15-N2; §7)</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr"/>
@@ -8930,7 +9293,9 @@
 2. The grand Totals indicator is NOT shown.
 3. The same message appears when no staff member has ever been credited — there is no separate "no reps configured" message; the report is contributor-driven.
 4. Whenever at least one rep row (or the Unassigned row) IS in the result set, the rep list renders and no empty/error message shows.
-5. In the empty state the toolbar — filters, column selector, and the ⋯ exports — stays visible and interactive; widening the range re-fetches and renders the matching reps normally.</t>
+5. In the empty state the toolbar — filters, column selector, and the ⋯ exports — stays visible and interactive; widening the range re-fetches and renders the matching reps normally.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S16-R1, S16-R2, S16-R3, S16-N1, S2-N1, S21-N2).</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -8964,7 +9329,8 @@
       </c>
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with data showing (use a slow/throttled connection if available to make the loading state observable).</t>
+          <t>1. You are on the report with data showing (use a slow/throttled connection if available to make the loading state observable).
+2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
       <c r="F176" s="2" t="inlineStr">
@@ -8979,12 +9345,14 @@
           <t>1. On the initial load and on every filter-triggered re-fetch, the table shows the standard reports loading indicator — a centered spinner over the data area.
 2. The grand Totals indicator is hidden during loading.
 3. The toolbar stays interactive so filters can be changed mid-load.
-4. A re-fetch replaces the previous data only when the new data returns — no flash of a blank table beyond the spinner overlay.</t>
+4. A re-fetch replaces the previous data only when the new data returns — no flash of a blank table beyond the spinner overlay.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S16-R4).</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>SV-8633 (specs/sbr-sales-by-representative.md Story 16 S16-R4)</t>
+          <t>SV-8633 (SBR spec v15 2026-07-29 Story 16 S16-R4)</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr"/>
@@ -9013,7 +9381,8 @@
       </c>
       <c r="E177" s="2" t="inlineStr">
         <is>
-          <t>1. You can force a load failure (for example, cut the network and change a filter) — if not forceable, mark Blocked with the reason.</t>
+          <t>1. You can force a load failure (for example, cut the network and change a filter) — if not forceable, mark Blocked with the reason.
+2. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
       <c r="F177" s="2" t="inlineStr">
@@ -9027,12 +9396,14 @@
         <is>
           <t>1. The data area shows the inline error message "Couldn't load the report. Please try again." with a "Retry" action.
 2. The filters and toolbar remain interactive, and the failure does NOT clear the filter selections.
-3. "Retry" re-runs the CURRENT request — the report loads with the same filters still applied.</t>
+3. "Retry" re-runs the CURRENT request — the report loads with the same filters still applied.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S16-R5).</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>SV-8633 (specs/sbr-sales-by-representative.md Story 16 S16-R5; §7)</t>
+          <t>SV-8633 (SBR spec v15 2026-07-29 Story 16 S16-R5; §7)</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr"/>
@@ -9075,12 +9446,14 @@
         <is>
           <t>1. Every toolbar control is visible and operable on touch.
 2. Below 1024px the toolbar controls stack vertically at full width; the ⋯ exports button — the first control of the action cluster — wraps to a partial row ABOVE the stacked controls.
-3. At 1024px and above the desktop layout applies.</t>
+3. At 1024px and above the desktop layout applies.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S17-R1, S17-R2, S17-R3).</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>SV-8634 (specs/sbr-sales-by-representative.md Story 17 S17-R1; S17-R2; S17-R3)</t>
+          <t>SV-8634 (SBR spec v15 2026-07-29 Story 17 S17-R1; S17-R2; S17-R3)</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr"/>
@@ -9123,12 +9496,14 @@
         <is>
           <t>1. The table scrolls horizontally to expose all columns; the pinned Subtotal column stays visible at the right edge throughout.
 2. The mobile external totals bar ("Totals" left, grand Subtotal right) sits below the table, OUTSIDE the horizontal scroll container — it does not scroll horizontally and is always fully visible.
-3. The chevron expands/collapses the rep on touch.</t>
+3. The chevron expands/collapses the rep on touch.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S17-R4, S17-R5, S10-R5).</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>SV-8634 (specs/sbr-sales-by-representative.md Story 17 S17-R4; S17-R5; Story 10 S10-R5 (mobile))</t>
+          <t>SV-8634 (SBR spec v15 2026-07-29 Story 17 S17-R4; S17-R5; Story 10 S10-R5 (mobile))</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr"/>
@@ -9157,7 +9532,8 @@
       </c>
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>1. The report is open on a touch device or touch emulation (under 1024px).</t>
+          <t>1. The report is open on a touch device or touch emulation (under 1024px).
+2. This test names exact colours or sizes. Use the browser's own developer tools: press F12, pick the element with the inspector, and read its colour or size from the "Styles" panel. There is nothing to install. If you cannot get a clear reading, mark this test Blocked rather than guessing.</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
@@ -9169,12 +9545,14 @@
       <c r="G180" s="2" t="inlineStr">
         <is>
           <t>1. Each of these interactive controls presents a touch target of at least 44×44 px.
-2. Hover-only tooltips are not shown on touch; the icons communicate the action and each icon-only control carries an accessible name.</t>
+2. Hover-only tooltips are not shown on touch; the icons communicate the action and each icon-only control carries an accessible name.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S17-R6, S17-N1, S18-R9).</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>SV-8634 (specs/sbr-sales-by-representative.md Story 17 S17-R6; S17-N1; Story 18 S18-R9)</t>
+          <t>SV-8634 (SBR spec v15 2026-07-29 Story 17 S17-R6; S17-N1; Story 18 S18-R9)</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr"/>
@@ -9208,23 +9586,28 @@
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
-          <t>1. Look at the toolbar's surface, padding, and how the title and the rightmost control line up with the table columns.
+          <t>1. Look at the toolbar strip, at the space between its controls and the edges of the strip, and at how the title and the rightmost control line up with the table columns.
 2. Look at the page background around the data area, the line between the toolbar and the column headers, and the table's side edges.
-3. Look at the header cells, the body cells, the pinned Subtotal cells, and the grand Totals indicator's surface.</t>
+3. Look at the header cells, the body cells, the pinned Subtotal cells, and the grand Totals indicator's surface.
+4. Open another report in the suite (for example Parts Velocity) side by side and compare.</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>1. The toolbar has a solid white background with padding 32px top / 24px bottom / 2rem left and right; the title's left edge aligns with the leftmost data column, and the rightmost toolbar control (the Location filter) aligns its right edge with the rightmost data column.
-2. The data area sits on the standard blue-grey page background with ZERO horizontal page padding — the toolbar and table run edge-to-edge against the side navigation.
+          <t>1. The toolbar has a solid white background and its controls sit clear of the edges rather than pressed up against them; the title's left edge lines up with the leftmost data column, and the rightmost toolbar control (the Location filter) lines its right edge up with the rightmost data column.
+2. The data area sits on the standard blue-grey page background and runs edge-to-edge against the side navigation — there is no strip of empty space down either side.
 3. A thin horizontal separator line sits between the toolbar and the column headers.
 4. Column-header cells and all body cells render on white; the pinned Subtotal column matches the row background (not a contrasting strip); the grand Totals indicator renders on the white card surface with a thin top border.
-5. Row types are differentiated by font weight and color, not background color. These rules apply unconditionally whenever the report is rendered.</t>
+5. Row types are told apart by how heavy and what colour their text is, not by a different background colour.
+6. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
+7. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the alignment look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this — 32px/24px toolbar padding, 2rem edge padding — are design-token values the design and engineering team check with their own tooling, not by hand.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S18-R1, S18-R2, S18-R3, S18-R4, S18-R5, S18-R7, S18-N1).</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>SV-8635 (specs/sbr-sales-by-representative.md Story 18 S18-R1; S18-R2; S18-R3; S18-R4; S18-R5; S18-R7.1–R7.6; S18-N1)</t>
+          <t>SV-8635 (SBR spec v15 2026-07-29 Story 18 S18-R1; S18-R2; S18-R3; S18-R4; S18-R5; S18-R7.1–R7.6; S18-N1)</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr"/>
@@ -9269,12 +9652,14 @@
           <t>1. The page, toolbar, header, body cells, and the grand Totals indicator switch to their dark equivalents.
 2. Status badges keep the same canonical payment-status color tokens and stay legible in both modes.
 3. Inv. Hrs green/red use the application's positive/negative tokens, mode-appropriate.
-4. PDFs always render in light-mode colors, even when downloaded from dark mode.</t>
+4. PDFs always render in light-mode colors, even when downloaded from dark mode.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S18-R8).</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>SV-8635 (specs/sbr-sales-by-representative.md Story 18 S18-R8)</t>
+          <t>SV-8635 (SBR spec v15 2026-07-29 Story 18 S18-R8)</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr"/>
@@ -9303,7 +9688,8 @@
       </c>
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with at least one rep row; a screen reader or the browser's accessibility inspector is available.</t>
+          <t>1. You are on the report with at least one rep row; a screen reader or the browser's accessibility inspector is available.
+2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
       <c r="F183" s="2" t="inlineStr">
@@ -9318,12 +9704,14 @@
 2. Column selector = "Show or hide columns".
 3. Per-row chevron = "Expand {rep name}" when collapsed / "Collapse {rep name}" when expanded.
 4. Header chevron = "Expand all reps" / "Collapse all reps".
-5. Dialog X = "Close".</t>
+5. Dialog X = "Close".
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S18-R9).</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>SV-8635 (specs/sbr-sales-by-representative.md Story 18 S18-R9)</t>
+          <t>SV-8635 (SBR spec v15 2026-07-29 Story 18 S18-R9)</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr"/>
@@ -9352,7 +9740,8 @@
       </c>
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with at least two rep rows; a screen reader or accessibility inspector is available.</t>
+          <t>1. You are on the report with at least two rep rows; a screen reader or accessibility inspector is available.
+2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
       <c r="F184" s="2" t="inlineStr">
@@ -9366,12 +9755,14 @@
         <is>
           <t>1. The row chevrons and the sortable column headers are keyboard-focusable and activate on Enter and on Space.
 2. A chevron exposes its expanded/collapsed state to assistive technology.
-3. A sortable header exposes its current sort state (unsorted / ascending / descending) to assistive technology.</t>
+3. A sortable header exposes its current sort state (unsorted / ascending / descending) to assistive technology.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S18-R10).</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>SV-8635 (specs/sbr-sales-by-representative.md Story 18 S18-R10)</t>
+          <t>SV-8635 (SBR spec v15 2026-07-29 Story 18 S18-R10)</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr"/>
@@ -9413,7 +9804,9 @@
         <is>
           <t>1. In BOTH light mode and dark mode the subdued-grey (N) count and the "(Inactive)" tag are easy to read against the surface behind them - the smaller text does not fade into the background.
 2. No information is conveyed by color alone: Inv. Hrs carries its +/- sign, status badges carry their text label, and links carry a hover/focus underline.
-3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can read the grey text easily in both modes, and only report it if you cannot. (The design rule behind this is WCAG AA contrast of at least 4.5:1, which the design and engineering team check with a contrast tool - not by hand.)</t>
+3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can read the grey text easily in both modes, and only report it if you cannot. (The design rule behind this is WCAG AA contrast of at least 4.5:1, which the design and engineering team check with a contrast tool - not by hand.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S18-R11, S18-R12).</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9464,12 +9857,14 @@
 2. The left panel includes the same "Sales Representative" selector on the Part Sale WO.
 3. The selector is NOT present on the imported Work Order.
 4. The selector is NOT present in History mode.
-5. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+5. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R1, S19-N1).</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>SV-8636 (specs/sbr-sales-by-representative.md Story 19 S19-R1; S19-N1)</t>
+          <t>SV-8636 (SBR spec v15 2026-07-29 Story 19 S19-R1; S19-N1)</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr"/>
@@ -9513,12 +9908,14 @@
           <t>1. The toggle-ON staff member is offered as a selectable rep.
 2. The toggle-OFF staff member is NOT offered as a new selection.
 3. The selector carries the accessible name "Sales Representative".
-4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R2, S19-R8).</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>SV-8636 (specs/sbr-sales-by-representative.md Story 19 S19-R2; S19-R8 — toggle entry path Settings -&gt; Staff -&gt; edit the staff member per the PRD companion video 2026-07-30 09:17-09:41; exact toggle label to confirm live in the build)</t>
+          <t>SV-8636 (SBR spec v15 2026-07-29 Story 19 S19-R2; S19-R8 — toggle entry path Settings -&gt; Staff -&gt; edit the staff member per the PRD companion video 2026-07-30 09:17-09:41; exact toggle label to confirm live in the build)</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr"/>
@@ -9561,12 +9958,14 @@
         <is>
           <t>1. The new Work Order opens with the Sales Representative field UNASSIGNED — it is not pre-filled at creation.
 2. Changing the Sales Representative persists immediately (save-on-change): the selection survives leaving and reopening the WO with no separate Save step.
-3. A new Part Sale WO also opens with the field unassigned.</t>
+3. A new Part Sale WO also opens with the field unassigned.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R3, S19-R4).</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>SV-8636 (specs/sbr-sales-by-representative.md Story 19 S19-R3; S19-R4)</t>
+          <t>SV-8636 (SBR spec v15 2026-07-29 Story 19 S19-R3; S19-R4)</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr"/>
@@ -9609,12 +10008,14 @@
           <t>1. On the Invoiced WO the Sales Representative selector is read-only (non-interactive) — the assignment cannot be changed.
 2. On the Paid WO the selector is also read-only.
 3. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
-4. Note for the tester: this field is only made read-only on the screen. If you find the sales rep can still be changed another way (through the back-end/API), that is expected — mark this test PASSED and do not raise it as a bug.</t>
+4. Note for the tester: this field is only made read-only on the screen. If you find the sales rep can still be changed another way (through the back-end/API), that is expected — mark this test PASSED and do not raise it as a bug.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R5).</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>SV-8636 (specs/sbr-sales-by-representative.md Story 19 S19-R5)</t>
+          <t>SV-8636 (SBR spec v15 2026-07-29 Story 19 S19-R5)</t>
         </is>
       </c>
       <c r="I189" s="2" t="inlineStr"/>
@@ -9658,12 +10059,14 @@
           <t>1. Invoice (a) is credited to the WO's Sales Representative.
 2. Invoice (b) falls back to the CUSTOMER's assigned rep.
 3. Invoice (c) is unassigned — it appears only under the "Unassigned" row.
-4. Changing WO (a)'s Sales Representative afterward does NOT retroactively alter the invoice already created from it — the invoice stays credited to the rep snapshotted at invoice creation.</t>
+4. Changing WO (a)'s Sales Representative afterward does NOT retroactively alter the invoice already created from it — the invoice stays credited to the rep snapshotted at invoice creation.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R6, S19-N2, S22-R3).</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>SV-8636 (specs/sbr-sales-by-representative.md Story 19 S19-R6; S19-N2; §3 Key Decisions (single-rep snapshot); Story 22 S22-R3)</t>
+          <t>SV-8636 (SBR spec v15 2026-07-29 Story 19 S19-R6; S19-N2; §3 Key Decisions (single-rep snapshot); Story 22 S22-R3)</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr"/>
@@ -9708,7 +10111,9 @@
           <t>1. The customer record's left-panel sidebar shows a single row labeled "Sales Representative" (the full word — the product owner explicitly corrected the short-form "Sales Representative" label here) with the customer's assigned rep.
 2. When no rep is assigned, the row renders "Unassigned".
 3. On the WO, the selector renders the bound rep's name with an "(Inactive)" indicator so the current assignment stays visible — but that rep is NOT offered as a new selection in the list.
-4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.</t>
+4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R7, S19-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -9743,7 +10148,8 @@
       <c r="E192" s="2" t="inlineStr">
         <is>
           <t>1. You are on the report with at least two rep rows, one with a large invoice count if seedable.
-2. The browser's network panel is open.</t>
+2. The browser's network panel is open.
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F192" s="2" t="inlineStr">
@@ -9757,12 +10163,14 @@
         <is>
           <t>1. Invoice detail rows are NOT delivered with the initial summary payload — the first expand of a rep triggers a server fetch for that rep's matching invoices, with a brief row-level loading indicator.
 2. A re-expand within the session does not necessarily re-fetch (the expansion state is session-preserved); no rep's details load before its first expand.
-3. When a rep's matching-invoice count is large, its detail rows are paginated per rep.</t>
+3. When a rep's matching-invoice count is large, its detail rows are paginated per rep.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R2).</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>SV-8624 (specs/sbr-sales-by-representative.md Story 6 S6-R2)</t>
+          <t>SV-8624 (SBR spec v15 2026-07-29 Story 6 S6-R2)</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr"/>
@@ -9791,7 +10199,8 @@
       </c>
       <c r="E193" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with several rep rows; the network panel is open.</t>
+          <t>1. You are on the report with several rep rows; the network panel is open.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F193" s="2" t="inlineStr">
@@ -9804,12 +10213,14 @@
         <is>
           <t>1. Each sort change triggers a server re-fetch of the rep summary rows in the requested order (a loading indicator shows during the fetch).
 2. The returned rows arrive already ordered by the requested column and direction — the client does not re-sort locally.
-3. Invoice detail rows continue to load lazily per rep on expand, unaffected by the sort mechanism.</t>
+3. Invoice detail rows continue to load lazily per rep on expand, unaffected by the sort mechanism.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R5).</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>SV-8628 (specs/sbr-sales-by-representative.md Story 11 S11-R5)</t>
+          <t>SV-8628 (SBR spec v15 2026-07-29 Story 11 S11-R5)</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr"/>
@@ -9838,7 +10249,8 @@
       </c>
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with several reps, at least one large enough that not all of its detail rows are loaded; the network panel is open.</t>
+          <t>1. You are on the report with several reps, at least one large enough that not all of its detail rows are loaded; the network panel is open.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
@@ -9851,12 +10263,14 @@
         <is>
           <t>1. The grand totals arrive WITH the summary payload — the client does not derive them by summing loaded rows.
 2. The totals cover EVERY matching non-reversed invoice across every rep, independent of which reps are expanded or how many detail rows are loaded.
-3. The on-screen grand Totals match the export's aggregate for the same filter set.</t>
+3. The on-screen grand Totals match the export's aggregate for the same filter set.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S10-R5).</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>SV-8627 (specs/sbr-sales-by-representative.md Story 10 S10-R5)</t>
+          <t>SV-8627 (SBR spec v15 2026-07-29 Story 10 S10-R5)</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr"/>
@@ -9885,7 +10299,8 @@
       </c>
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with filters and a column sort applied; at least one rep is left unexpanded; the network panel is open.</t>
+          <t>1. You are on the report with filters and a column sort applied; at least one rep is left unexpanded; the network panel is open.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F195" s="2" t="inlineStr">
@@ -9899,12 +10314,14 @@
         <is>
           <t>1. Each export is generated by the server, receiving the active filters and sort — the file's contents and order match the screen even for reps never expanded (not built from loaded screen data).
 2. A genuine server-side export failure produces NO file and shows the "Ooooops! An error occured" toast — never a malformed/partial file.
-3. An empty-but-loaded result still produces a valid file (header-row-only CSV / no-rows PDF).</t>
+3. An empty-but-loaded result still produces a valid file (header-row-only CSV / no-rows PDF).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R2a, S14-N2, S14-E3).</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-R2a; S14-N2; S14-E3)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-R2a; S14-N2; S14-E3)</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr"/>
@@ -9934,7 +10351,8 @@
       <c r="E196" s="2" t="inlineStr">
         <is>
           <t>1. A filter set producing more than 10,000 invoice detail rows exists or can be seeded — otherwise mark Blocked-Env with the reason.
-2. The network panel is open.</t>
+2. The network panel is open.
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F196" s="2" t="inlineStr">
@@ -9947,12 +10365,15 @@
         <is>
           <t>1. The server counts the rows against the 10,000-data-row cap and DECLINES to generate — the refusal happens pre-generation, observed in the export response.
 2. NO file (truncated or otherwise) is delivered; the client shows the specific too-large toast.
-3. A filter set just below the cap still generates a complete (possibly very large) PDF.</t>
+3. A filter set just below the cap still generates a complete (possibly very large) PDF.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-E2).</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>SV-8631 (specs/sbr-sales-by-representative.md Story 14 S14-E2)</t>
+          <t>SV-8631 (SBR spec v15 2026-07-29 Story 14 S14-E2)</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr"/>
@@ -9982,7 +10403,8 @@
       <c r="E197" s="2" t="inlineStr">
         <is>
           <t>1. A staff member is active with the sales-representative toggle on and at least one customer assigned (seed a throwaway ZZAUTOTEST assignment if needed).
-2. The network panel is open.</t>
+2. The network panel is open.
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F197" s="2" t="inlineStr">
@@ -9996,12 +10418,14 @@
         <is>
           <t>1. A precondition-check request runs FIRST, before any change is applied, returning the count of distinct customers currently assigned to that staff member as their sales representative, plus a flag indicating whether any assignments exist.
 2. The dialog's "{Staff Name} is the sales representative on {N} customer{s}." headline matches the returned count.
-3. No deactivation is committed by the pre-check itself — cancelling leaves the staff member's active status unchanged.</t>
+3. No deactivation is committed by the pre-check itself — cancelling leaves the staff member's active status unchanged.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R1, S13-R4).</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>SV-8630 (specs/sbr-sales-by-representative.md Story 13 S13-R1; S13-R4)</t>
+          <t>SV-8630 (SBR spec v15 2026-07-29 Story 13 S13-R1; S13-R4)</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr"/>
@@ -10045,7 +10469,9 @@
         <is>
           <t>1. A Parts section heading exists in the Reports navigation (this feature creates it - the application had no Parts reports before).
 2. Under Parts there is an entry labeled Parts Velocity; Inventory Value also lives under Parts. The order of the two inside the Parts section is not fixed — do not fail the test on which of them comes first.
-3. Clicking it opens the Parts Velocity report.</t>
+3. Clicking it opens the Parts Velocity report.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10093,12 +10519,14 @@
         <is>
           <t>1. The date range selector shows This Year.
 2. Report data loads automatically - you do not have to press anything to fetch it.
-3. Rows appear ranked by Demand, highest first (the default order).</t>
+3. Rows appear ranked by Demand, highest first (the default order).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-R2, S4-R6).</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>SV-8641 (specs/parts-velocity.md S1-R2; S4-R6)</t>
+          <t>SV-8641 (PV spec v4 2026-07-29 S1-R2; S4-R6)</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr"/>
@@ -10142,12 +10570,14 @@
         <is>
           <t>1. During the initial load, the table shows a loading indicator.
 2. During a filter change, the loading indicator shows again.
-3. The rows already on screen are replaced only when the new data comes back - the table does not blank out and rebuild mid-request.</t>
+3. The rows already on screen are replaced only when the new data comes back - the table does not blank out and rebuild mid-request.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-R3).</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>SV-8641 (specs/parts-velocity.md S1-R3)</t>
+          <t>SV-8641 (PV spec v4 2026-07-29 S1-R3)</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr"/>
@@ -10192,7 +10622,9 @@
         <is>
           <t>1. The report data loads and rows are shown.
 2. The export downloads successfully — both opening the report and exporting it are allowed by the same ordinary reports access.
-3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.</t>
+3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10238,12 +10670,14 @@
       <c r="G202" s="2" t="inlineStr">
         <is>
           <t>1. The user cannot reach the Reports section.
-2. The Parts Velocity navigation entry is not shown (this is the Reports section's own access control, not a report-specific rule).</t>
+2. The Parts Velocity navigation entry is not shown (this is the Reports section's own access control, not a report-specific rule).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-N1).</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>SV-8641 (specs/parts-velocity.md S1-N1)</t>
+          <t>SV-8641 (PV spec v4 2026-07-29 S1-N1)</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr"/>
@@ -10288,7 +10722,9 @@
           <t>1. The Parts Velocity entry is visible in the Reports navigation under Parts.
 2. Opening it shows the report data - not an access-denied screen.
 3. The export downloads.
-4. Note for the tester: for now ONE ordinary reports access opens all six of these new reports, and no report has a permission of its own. If an extra Parts or Inventory reports permission does exist and switching it OFF blocks this report or its export, that is wrong - mark this Failed and report it. If a separate per-report permission is ever added on purpose in a later release, this test will be updated first, so treat that as a planned change and not as a bug.</t>
+4. Note for the tester: for now ONE ordinary reports access opens all six of these new reports, and no report has a permission of its own. If an extra Parts or Inventory reports permission does exist and switching it OFF blocks this report or its export, that is wrong - mark this Failed and report it. If a separate per-report permission is ever added on purpose in a later release, this test will be updated first, so treat that as a planned change and not as a bug.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-N2, S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -10341,7 +10777,9 @@
 2. It is single-select and offers exactly three choices: Both, Inventory, and Special Order (special-order catalog parts that were never put into stock).
 3. On a first visit the default is Both.
 4. Both is an explicit selection returning inventory and Special Order rows together - a deliberate filter value, not the absence of a filter.
-5. Each selection immediately reloads the report limited to that type (no separate Apply step) - under Inventory every row's Type column reads Inventory; under Special Order every row's Type column reads Special Order; under Both, rows of both kinds appear.</t>
+5. Each selection immediately reloads the report limited to that type (no separate Apply step) - under Inventory every row's Type column reads Inventory; under Special Order every row's Type column reads Special Order; under Both, rows of both kinds appear.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R1, S3-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -10389,7 +10827,9 @@
           <t>1. The options are exactly: Today, Yesterday, This Week, Last Week, This Month, Last Month, This Year, Last Year, This Quarter, Last Quarter, Custom.
 2. There is NO 'All Time' option - the report always operates over a bounded date window (deliberate, per the spec's Out of Scope).
 3. Selecting a non-custom option immediately reloads the report data.
-4. The named ranges use the application's standard shared calendar boundaries (the same boundaries every report's date picker uses).</t>
+4. The named ranges use the application's standard shared calendar boundaries (the same boundaries every report's date picker uses).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R2).</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -10439,12 +10879,14 @@
           <t>1. A date picker opens requiring both a start and an end date.
 2. The report does not reload until both dates are valid; a start after the end is not accepted.
 3. With both valid dates selected, the data reloads for that range.
-4. A span wider than 366 days (counting both the start and end dates) is rejected - the selection is not applied.</t>
+4. A span wider than 366 days (counting both the start and end dates) is rejected - the selection is not applied.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R3).</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R3)</t>
+          <t>SV-8642 (PV spec v4 2026-07-29 S2-R3)</t>
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr"/>
@@ -10489,12 +10931,14 @@
           <t>1. Both filters allow selecting more than one value (multi-select).
 2. With categories selected, only parts in any of the selected categories are shown.
 3. With vendors selected, only parts supplied by any of the selected vendors are shown.
-4. Each change reloads the data from the server.</t>
+4. Each change reloads the data from the server.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R4, S2-R5, S2-R10).</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R4; S2-R5; S2-R10)</t>
+          <t>SV-8642 (PV spec v4 2026-07-29 S2-R4; S2-R5; S2-R10)</t>
         </is>
       </c>
       <c r="I207" s="2" t="inlineStr"/>
@@ -10540,12 +10984,14 @@
           <t>1. The search input is part of the report's toolbar (page-specific), separate from the global search bar.
 2. The part-number search matches despite the different letter case (case-insensitive 'contains' match).
 3. The description search returns rows whose description contains the word.
-4. Category and vendor names are NOT searched - use their dedicated filters instead (deliberate, to avoid false matches on common words).</t>
+4. Category and vendor names are NOT searched - use their dedicated filters instead (deliberate, to avoid false matches on common words).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R6).</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R6; §3 Key Decisions)</t>
+          <t>SV-8642 (PV spec v4 2026-07-29 S2-R6; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr"/>
@@ -10590,12 +11036,14 @@
         <is>
           <t>1. After steps 1-2 the part is still listed (it satisfies both filters).
 2. After step 3 the part disappears - a part must satisfy EVERY active filter to appear (AND logic, not OR).
-3. After step 4 the part is listed again.</t>
+3. After step 4 the part is listed again.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R7).</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R7)</t>
+          <t>SV-8642 (PV spec v4 2026-07-29 S2-R7)</t>
         </is>
       </c>
       <c r="I209" s="2" t="inlineStr"/>
@@ -10638,12 +11086,14 @@
         <is>
           <t>1. Each selection reloads the data from the server.
 2. Only inventory parts stocked in ANY of the selected bins are shown.
-3. The filter allows more than one bin (multi-select).</t>
+3. The filter allows more than one bin (multi-select).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R8).</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R8)</t>
+          <t>SV-8642 (PV spec v4 2026-07-29 S2-R8)</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr"/>
@@ -10686,7 +11136,9 @@
       <c r="G211" s="2" t="inlineStr">
         <is>
           <t>1. With any Bin filter active, ALL Special Order rows are excluded (they have no bin location).
-2. Special Order combined with any Bin filter yields an empty result showing the empty state - this is by design, not a defect.</t>
+2. Special Order combined with any Bin filter yields an empty result showing the empty state - this is by design, not a defect.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
@@ -10741,7 +11193,9 @@
 4. Each selection reloads the data scoped to the chosen set; 'All Locations' means all locations the user can ACCESS, never beyond - a location the user cannot access is never included.
 5. The location scope cascades through every metric like the other filters.
 6. With 'All Locations' active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
-7. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).</t>
+7. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -10787,7 +11241,9 @@
       <c r="G213" s="2" t="inlineStr">
         <is>
           <t>1. The server returns zero rows and the table shows the empty state.
-2. The empty-state label reads exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).</t>
+2. The empty-state label reads exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R11, S2-N1).</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -10837,12 +11293,14 @@
         <is>
           <t>1. The part with no category does not appear when any Category filter is active.
 2. The part with no vendor does not appear when any Vendor filter is active.
-3. The inventory part with no bin location does not appear when any Bin filter is active.</t>
+3. The inventory part with no bin location does not appear when any Bin filter is active.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-E1, S2-E2, S2-E3).</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-E1; S2-E2; S2-E3)</t>
+          <t>SV-8642 (PV spec v4 2026-07-29 S2-E1; S2-E2; S2-E3)</t>
         </is>
       </c>
       <c r="I214" s="2" t="inlineStr"/>
@@ -10884,7 +11342,9 @@
       <c r="G215" s="2" t="inlineStr">
         <is>
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
-2. For the user with access to two or more locations the Location filter IS shown.</t>
+2. For the user with access to two or more locations the Location filter IS shown.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-E4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
@@ -10929,8 +11389,7 @@
 3. Read the Location cell on the merged Special Order row.
 4. Open the column picker and look for Location in the list.
 5. Narrow to a single location and read the headers again.
-6. Change the selection between one location, several, and "All Locations", watching the filter control's width.
-7. With more than one location still selected, download the CSV and the PDF and read their columns from the left.</t>
+6. With more than one location still selected, download the CSV and the PDF and read their columns from the left.</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
@@ -10940,8 +11399,9 @@
 3. The merged Special Order row shows "Multiple", because it is summed across the selected locations.
 4. Location is NOT one of the 20 columns in the picker — it is managed by the location scope, not by you.
 5. With a single location in scope the Location column is hidden.
-6. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
-7. Both downloads include the Location column in the same position it holds on screen (leftmost, before Type), with the same values — each inventory row's own location, and "Multiple" on the merged Special Order row.</t>
+6. Both downloads include the Location column in the same position it holds on screen (leftmost, before Type), with the same values — each inventory row's own location, and "Multiple" on the merged Special Order row.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R12, S3-R10, S7-R8, S6-R11).</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -10989,12 +11449,14 @@
         <is>
           <t>1. The part appears as TWO inventory rows - one per selected location (an inventory part is a per-location stock record).
 2. Each row carries only that one location's On Hand, Min, and Max.
-3. On Hand / Min / Max are NEVER summed across locations.</t>
+3. On Hand / Min / Max are NEVER summed across locations.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R1a).</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (specs/parts-velocity.md S3-R1a; §3 Key Decisions)</t>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-R1a; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I217" s="2" t="inlineStr"/>
@@ -11038,12 +11500,14 @@
         <is>
           <t>1. The special-order part appears as a SINGLE row (one row per special-order part, merged across the selected locations).
 2. Its movement and profitability values are the SUM of the per-location values.
-3. Its inventory-only columns (On Hand, Turns / Yr, Min, Max) show — (em-dash), because special-order parts are not stocked.</t>
+3. Its inventory-only columns (On Hand, Turns / Yr, Min, Max) show — (em-dash), because special-order parts are not stocked.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R1a).</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (specs/parts-velocity.md S3-R1a; §3 Key Decisions)</t>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-R1a; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr"/>
@@ -11089,12 +11553,14 @@
           <t>1. Rows are ranked by Demand, descending - the most-active parts first.
 2. Inventory and special-order rows are ranked together in one list.
 3. Rows with equal Demand keep inventory-before-special-order order.
-4. The Demand header shows the descending sort indicator - this initial order IS the active sort (it is what the remembered view saves until you click another header).</t>
+4. The Demand header shows the descending sort indicator - this initial order IS the active sort (it is what the remembered view saves until you click another header).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R2).</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (specs/parts-velocity.md S3-R2)</t>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-R2)</t>
         </is>
       </c>
       <c r="I219" s="2" t="inlineStr"/>
@@ -11140,12 +11606,14 @@
           <t>1. The first click sorts that column ASCENDING; the header shows a direction indicator (an arrow).
 2. Clicking the active sort column again reverses the direction; the arrow flips.
 3. Null / — values are placed FIRST on ascending and LAST on descending.
-4. Every column is sortable; each header click re-fetches the data (server-resolved) and shows the first page of the re-sorted result; ties keep a stable order.</t>
+4. Every column is sortable; each header click re-fetches the data (server-resolved) and shows the first page of the re-sorted result; ties keep a stable order.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R3).</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (specs/parts-velocity.md S3-R3)</t>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-R3)</t>
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr"/>
@@ -11188,7 +11656,9 @@
         <is>
           <t>1. The header row is sticky - it stays visible while the body scrolls.
 2. The Type column shows each row's kind as plain text (no badge or chip styling): "Inventory" or "Special Order".
-3. ALL columns - header and cell data, including numbers and money - are left-aligned on screen. (The exports right-align numerics instead: a deliberate export-only difference.)</t>
+3. ALL columns - header and cell data, including numbers and money - are left-aligned on screen. (The exports right-align numerics instead: a deliberate export-only difference.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R4, S3-R5, S3-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11241,7 +11711,9 @@
 3. Demand shows exactly: "Number of separate transactions (work orders or parts sales) this part appeared on in the selected date range. Each transaction counts once, no matter how many units were sold on it."
 4. Turns/Yr shows exactly: "How many times you sell through this part in a year. Higher is better."
 5. The icon is focusable and exposes the same text to assistive technology; activating it does NOT trigger a column sort.
-6. No other column header carries an info icon.</t>
+6. No other column header carries an info icon.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R6).</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -11292,12 +11764,13 @@
           <t>1. Long Description, Category, and Vendor text is truncated with an ellipsis on screen.
 2. The full value shows on native hover (browser tooltip).
 3. Part # is NEVER truncated - on screen (and in the exports).
-4. The CSV export carries the full untruncated Description / Category / Vendor values.</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R7).</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (specs/parts-velocity.md S3-R7)</t>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-R7)</t>
         </is>
       </c>
       <c r="I223" s="2" t="inlineStr"/>
@@ -11333,21 +11806,20 @@
       <c r="F224" s="2" t="inlineStr">
         <is>
           <t>1. On the special-order row, read On Hand, Turns / Yr, Min, and Max.
-2. On the no-activity inventory row, read Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Demand, Revenue, and Margin.
-3. On the same row, read Unit Cost, Sell Price, Margin %, and Last Sale (assuming no billed units, no revenue, and no recorded sale ever).</t>
+2. On the no-activity inventory row, read Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Demand, Revenue, and Margin.</t>
         </is>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
           <t>1. On Hand, Turns / Yr, Min, and Max show — (em-dash) on special-order rows - always.
 2. The count metrics and money totals are NEVER null: Units Sold / Units Returned / Sold (WO) / Sold (Parts Sale) show 0.00, Demand shows 0, Revenue and Margin show $0.00.
-3. Unit Cost and Sell Price show — when billed units are zero or less; Margin % shows — when Revenue is zero or less; Last Sale shows — when the row has no recorded sale.
-4. Every null renders as the same — (em-dash) glyph, in the table and in all exports.</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R9, S5-R5).</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (specs/parts-velocity.md S3-R9; S5-R5)</t>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-R9; S5-R5)</t>
         </is>
       </c>
       <c r="I224" s="2" t="inlineStr"/>
@@ -11390,12 +11862,14 @@
         <is>
           <t>1. Part A does NOT appear - it fails all three keep-criteria (no movement, under one on hand, no revenue) so it carries nothing to act on.
 2. Part B DOES appear - a part with billed Revenue &gt; 0 is always kept even with no stock movement and no on-hand stock.
-3. (Special Order parts have no such rule: a never-requested special-order part simply produces no row.)</t>
+3. (Special Order parts have no such rule: a never-requested special-order part simply produces no row.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-N1).</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (specs/parts-velocity.md S3-N1)</t>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-N1)</t>
         </is>
       </c>
       <c r="I225" s="2" t="inlineStr"/>
@@ -11438,12 +11912,14 @@
         <is>
           <t>1. Part C shows Demand 1 (the reversal does not decrement the Demand count) with Units Sold 0.00 (the reversal nets the movement to zero).
 2. Part D shows a NEGATIVE Units Sold with a leading minus (e.g. -3.00) - negative movement is not floored to zero.
-3. A fully-reversed part with zero net movement, no on-hand stock, and no residual revenue would be excluded altogether (a Demand count alone does not keep a row).</t>
+3. A fully-reversed part with zero net movement, no on-hand stock, and no residual revenue would be excluded altogether (a Demand count alone does not keep a row).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-E1, S5-R5).</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (specs/parts-velocity.md S3-E1; S5-R5)</t>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-E1; S5-R5)</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr"/>
@@ -11485,12 +11961,14 @@
       <c r="G227" s="2" t="inlineStr">
         <is>
           <t>1. The picker lists all 20 available columns, each with a toggle: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
-2. No on-hand cost column is offered - the report computes one internally but it is never selectable and never displayed.</t>
+2. No on-hand cost column is offered - the report computes one internally but it is never selectable and never displayed.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R1, S4-R4, S5-R6).</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>SV-8644 (specs/parts-velocity.md S4-R1; S4-R4; S5-R6)</t>
+          <t>SV-8644 (PV spec v4 2026-07-29 S4-R1; S4-R4; S5-R6)</t>
         </is>
       </c>
       <c r="I227" s="2" t="inlineStr"/>
@@ -11531,7 +12009,9 @@
         <is>
           <t>1. With a single location in scope exactly these 14 columns show, in this left-to-right order: Type, Part #, Description, Category, Vendor, Units Sold, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand.
 2. The other 6 columns start hidden: Units Returned, Sold (WO), Sold (Parts Sale), Turns / Yr, Min, Max.
-3. When more than one location is in scope the automatic Location column shows as well, leftmost before Type — 15 columns. It is not part of the 14-column default set and is not in the column picker, so its presence is expected and is not a failure of this test.</t>
+3. When more than one location is in scope the automatic Location column shows as well, leftmost before Type — 15 columns. It is not part of the 14-column default set and is not in the column picker, so its presence is expected and is not a failure of this test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R2, S4-R3, S3-R10).</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11579,7 +12059,9 @@
         <is>
           <t>1. Each toggle takes effect immediately - the table re-renders without a page reload.
 2. Columns always render in the fixed canonical left-to-right order regardless of the order they were toggled on (with the automatic Location column, when shown, sitting leftmost before Type): Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
-3. So Units Returned slots in right after Units Sold, Turns/Yr after On Hand, and Min before Max - not appended at the end.</t>
+3. So Units Returned slots in right after Units Sold, Turns/Yr after On Hand, and Min before Max - not appended at the end.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R4, S4-R5, S3-R10).</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11628,12 +12110,14 @@
           <t>1. On return, every saved setting is restored: Type = Inventory, Last Month, the chosen category, the column set including Turns / Yr, and the Revenue-descending sort.
 2. The saved values are applied BEFORE the first data fetch - the report does not flash the defaults and then re-query.
 3. The saved values take precedence over the first-visit defaults (This Year / Both / active location / 14 columns / Demand-descending).
-4. The same holds after a full page reload.</t>
+4. The same holds after a full page reload.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R6, S1-R2).</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>SV-8644 (specs/parts-velocity.md S4-R6; S1-R2)</t>
+          <t>SV-8644 (PV spec v4 2026-07-29 S4-R6; S1-R2)</t>
         </is>
       </c>
       <c r="I230" s="2" t="inlineStr"/>
@@ -11675,12 +12159,14 @@
         <is>
           <t>1. The invalid saved value is NOT sent to the server.
 2. That one setting falls back to its default (e.g. the location falls back to the active location); the other saved settings still restore normally.
-3. The report loads without an error.</t>
+3. The report loads without an error.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R6).</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>SV-8644 (specs/parts-velocity.md S4-R6)</t>
+          <t>SV-8644 (PV spec v4 2026-07-29 S4-R6)</t>
         </is>
       </c>
       <c r="I231" s="2" t="inlineStr"/>
@@ -11722,12 +12208,14 @@
       <c r="G232" s="2" t="inlineStr">
         <is>
           <t>1. User 2 sees user 1's saved view (Type = Special Order, Last Quarter, the saved columns and sort).
-2. This is by design: storage is per browser, not tied to the account - there is no per-account separation.</t>
+2. This is by design: storage is per browser, not tied to the account - there is no per-account separation.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R6).</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>SV-8644 (specs/parts-velocity.md S4-R6)</t>
+          <t>SV-8644 (PV spec v4 2026-07-29 S4-R6)</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr"/>
@@ -11770,12 +12258,14 @@
         <is>
           <t>1. The picker enforces no minimum - all 20 columns can be switched off, leaving a grid with no data columns for the rest of the session.
 2. The export produces a file containing only the header/metadata rows and no data columns.
-3. On the next visit the all-hidden selection is NOT restored - the report falls back to the default 14-column set (the saved column selection returns to the last NON-EMPTY selection; all-hidden is the exception).</t>
+3. On the next visit the all-hidden selection is NOT restored - the report falls back to the default 14-column set (the saved column selection returns to the last NON-EMPTY selection; all-hidden is the exception).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-E1, S4-R6).</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>SV-8644 (specs/parts-velocity.md S4-E1; S4-R6)</t>
+          <t>SV-8644 (PV spec v4 2026-07-29 S4-E1; S4-R6)</t>
         </is>
       </c>
       <c r="I233" s="2" t="inlineStr"/>
@@ -11820,12 +12310,14 @@
           <t>1. After step 1, Units Sold increases by 5.00 (invoicing a work order adds the units sold - a stock-movement event).
 2. After step 2, Units Sold decreases by 2.00 (reversing/voiding an invoice adds stock back and is subtracted - Units Sold is net of invoice reversals).
 3. After step 3, Units Sold is UNCHANGED - part returns do not affect Units Sold (they feed Units Returned instead).
-4. Units Sold can be 0.00 or negative when reversals exceed sales.</t>
+4. Units Sold can be 0.00 or negative when reversals exceed sales.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R1, S5-R4).</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R1; S5-R4 (Units Sold; inventory); §4)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R1; S5-R4 (Units Sold; inventory); §4)</t>
         </is>
       </c>
       <c r="I234" s="2" t="inlineStr"/>
@@ -11868,12 +12360,14 @@
         <is>
           <t>1. Units Sold equals the total quantity across the part's in-window vendor requests (3 + 2 = 5.00 in the example), summed across the selected locations.
 2. The reversed/voided sale is EXCLUDED from the total (net of reversals).
-3. Only requests on work orders at status Invoiced or Paid count; the window is anchored to the work-order date.</t>
+3. Only requests on work orders at status Invoiced or Paid count; the window is anchored to the work-order date.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R2, S5-R4, S5-R4b).</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R2; S5-R4 (Units Sold; catalogue); S5-R4b)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R2; S5-R4 (Units Sold; catalogue); S5-R4b)</t>
         </is>
       </c>
       <c r="I235" s="2" t="inlineStr"/>
@@ -11919,12 +12413,14 @@
           <t>1. After step 1, Units Returned increases by 2.00 (the return record is counted when the return is initiated).
 2. After step 2, it increases by 1.00 more (a parts-sale credit also creates a part-return record).
 3. After step 3, it decreases by 2.00 - the column reflects the CURRENT state of return records (cancelled returns are excluded), not a snapshot.
-4. After step 4, Units Returned is UNCHANGED - invoice reversals are not returns (they affect Units Sold instead).</t>
+4. After step 4, Units Returned is UNCHANGED - invoice reversals are not returns (they affect Units Sold instead).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R3, S5-R4).</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R3; S5-R4 (Units Returned); §3 Key Decisions)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R3; S5-R4 (Units Returned); §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I236" s="2" t="inlineStr"/>
@@ -11971,12 +12467,14 @@
 2. In the previous window the return does not count (only the sale's own metrics do).
 3. Core-charge returns are EXCLUDED from Units Returned.
 4. Units Returned is independent of the work order's current invoice status.
-5. A part whose ONLY in-window event is a return (no sale, no stock, no revenue) produces no row at all - accepted behavior, the row axis is sales/stock activity.</t>
+5. A part whose ONLY in-window event is a return (no sale, no stock, no revenue) produces no row at all - accepted behavior, the row axis is sales/stock activity.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R3).</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R3)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R3)</t>
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr"/>
@@ -12021,12 +12519,14 @@
           <t>1. Sold (WO) shows the total part quantity on Service-type invoiced/paid work orders whose work-order date is in the window (4.00 in the example), net of reversed/voided sales.
 2. Sold (Parts Sale) shows the total on Parts-type invoiced/paid work orders (counter sales) in the window (3.00), net of reversed/voided sales.
 3. Both are windowed by the WORK-ORDER date (its end date) - with the range moved off those dates, both drop out.
-4. Both workflows feed the report - a parts sale is a separate workflow from a service work order but counts fully.</t>
+4. Both workflows feed the report - a parts sale is a separate workflow from a service work order but counts fully.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4).</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R4 (Sold via WO / Sold via Parts Sale); §5 Assumptions)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Sold via WO / Sold via Parts Sale); §5 Assumptions)</t>
         </is>
       </c>
       <c r="I238" s="2" t="inlineStr"/>
@@ -12072,12 +12572,14 @@
           <t>1. The inventory part's Demand is 2 - each stock-decrementing invoicing event counts ONCE no matter how many units were on it (1 unit and 10 units each count as one).
 2. After the reversal, Demand is STILL 2 - a reversal event neither adds to nor subtracts from the count (while Units Sold nets down).
 3. The special-order part's Demand is 2 - the count of its in-window vendor part requests.
-4. Demand is the report's default ranking signal (a whole number, never null - 0 when none).</t>
+4. Demand is the report's default ranking signal (a whole number, never null - 0 when none).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4).</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R4 (Demand); §4; §3 Key Decisions)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Demand); §4; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I239" s="2" t="inlineStr"/>
@@ -12125,12 +12627,14 @@
 2. It IS scoped to the selected location(s): with only location B selected, Last Sale reflects B's own most recent sale.
 3. Format is 'N days' (e.g. 42 days); a part with no recorded sale ever shows —.
 4. For a special-order part, the anchor is its most recent vendor-sourced invoiced/paid request.
-5. When the most recent sale is reversed, Last Sale re-anchors to the previous remaining sale (the day count grows accordingly); if no other sale remains it shows —.</t>
+5. When the most recent sale is reversed, Last Sale re-anchors to the previous remaining sale (the day count grows accordingly); if no other sale remains it shows —.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4, S5-R5).</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R4 (Last Sale); §4; S5-R5; tech-plan-2026-07-29 B3.1 (last-sale re-anchor on reversal — spec-silent))</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Last Sale); §4; S5-R5; tech-plan-2026-07-29 B3.1 (last-sale re-anchor on reversal — spec-silent))</t>
         </is>
       </c>
       <c r="I240" s="2" t="inlineStr"/>
@@ -12173,12 +12677,14 @@
         <is>
           <t>1. On Hand equals the part's CURRENT on-hand quantity at that row's location (never summed across locations).
 2. Min and Max show the stored minimum / maximum reorder thresholds for that location, as whole numbers (— when not set).
-3. Min and Max are READ-ONLY display columns - no edit control or slide-over opens; editing part attributes from this report is out of scope in this version.</t>
+3. Min and Max are READ-ONLY display columns - no edit control or slide-over opens; editing part attributes from this report is out of scope in this version.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4, S5-R5).</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R4 (On Hand / Min / Max); §2 Out of Scope; S5-R5)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (On Hand / Min / Max); §2 Out of Scope; S5-R5)</t>
         </is>
       </c>
       <c r="I241" s="2" t="inlineStr"/>
@@ -12225,12 +12731,15 @@
           <t>1. Part A's Turns / Yr matches the formula (two decimals, e.g. 24.33); the window is the whole-day span inclusive of both dates with a floor of 1 day.
 2. Part B shows 0.00 (renders 0.00 when On Hand is 0 - not an error, not —).
 3. Part C shows a NEGATIVE Turns / Yr with a leading minus (because Units Sold can be negative).
-4. Special Order rows always show — (not applicable).</t>
+4. Special Order rows always show — (not applicable).
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8819
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4).</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R4 (Turns / Yr); S5 Definitions (Window))</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Turns / Yr); S5 Definitions (Window))</t>
         </is>
       </c>
       <c r="I242" s="2" t="inlineStr"/>
@@ -12276,12 +12785,14 @@
 3. Unit Cost = COGS ÷ billed units; Sell Price = Revenue ÷ billed units.
 4. Margin % = (Revenue − COGS) ÷ Revenue × 100, shown to one decimal.
 5. All five are computed from the RAW (unrounded) Revenue / COGS / billed-units totals and rounded ONCE at the end - not built from already-rounded intermediates.
-6. The same formulas apply to inventory and special-order rows (for special-order, from the vendor part requests).</t>
+6. The same formulas apply to inventory and special-order rows (for special-order, from the vendor part requests).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4a).</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R4a; §4)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4a; §4)</t>
         </is>
       </c>
       <c r="I243" s="2" t="inlineStr"/>
@@ -12325,12 +12836,14 @@
         <is>
           <t>1. After the reversal, ALL the billed-line columns drop to reflect only the remaining sale - the reversed/voided sale is excluded from Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO), Sold (Parts Sale), and (for special-order) Units Sold.
 2. This netting is consistent with inventory Units Sold, which already nets reversals via the stock add-back.
-3. A voided sale therefore inflates NO column.</t>
+3. A voided sale therefore inflates NO column.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4b, S5-R4a).</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R4b; S5-R4a; §3 Key Decisions)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4b; S5-R4a; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I244" s="2" t="inlineStr"/>
@@ -12376,12 +12889,14 @@
           <t>1. Row 1: Unit Cost and Sell Price show — (billed units ≤ 0) while Revenue and Margin show dollar amounts AND Margin % is still computed from Revenue - a valid mixed row, not a defect.
 2. Row 2: Sell Price shows $0.00 (a number) while Margin % shows — (Revenue ≤ 0) - also valid.
 3. Row 3: Unit Cost, Sell Price, and Margin % all show — together - which happens ONLY when both billed units ≤ 0 AND Revenue ≤ 0.
-4. The three triggers are independent: Unit Cost/Sell Price null on billed units ≤ 0; Margin % null on Revenue ≤ 0.</t>
+4. The three triggers are independent: Unit Cost/Sell Price null on billed units ≤ 0; Margin % null on Revenue ≤ 0.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4a, S3-R9).</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R4a (null rules + mixed-row paragraph); S3-R9)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4a (null rules + mixed-row paragraph); S3-R9)</t>
         </is>
       </c>
       <c r="I245" s="2" t="inlineStr"/>
@@ -12425,12 +12940,14 @@
 2. Unit Cost, Sell Price, Revenue, Margin: currency with $, two decimals, thousands separators ($1,250.00); negatives with a leading minus and NO parentheses (-$45.00).
 3. Margin %: one decimal with a trailing % (33.8%); negatives with a leading minus, no + on positives (-8.4%).
 4. Demand: whole number. Min, Max: whole numbers (— when null). Last Sale: 'N days' (42 days), — when null.
-5. Rounding is half AWAY from zero: 8.45% displays 8.5% and -8.45% displays -8.5% (a tie rounds up in magnitude); this applies to all money and one-decimal values.</t>
+5. Rounding is half AWAY from zero: 8.45% displays 8.5% and -8.45% displays -8.5% (a tie rounds up in magnitude); this applies to all money and one-decimal values.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R5, S5-R7).</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R5; S5-R7 (rounding))</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R5; S5-R7 (rounding))</t>
         </is>
       </c>
       <c r="I246" s="2" t="inlineStr"/>
@@ -12473,12 +12990,14 @@
         <is>
           <t>1. The inventory core part does NOT appear in the report despite its activity and stock.
 2. The special-order core part does NOT appear either.
-3. Parts flagged as a core are excluded from both result sets by design.</t>
+3. Parts flagged as a core are excluded from both result sets by design.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R1, S5-R2).</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R1; S5-R2; §3 Key Decisions)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R1; S5-R2; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I247" s="2" t="inlineStr"/>
@@ -12523,12 +13042,14 @@
         <is>
           <t>1. On the inventory row, Units Sold (stock movement) DIFFERS from the billed units behind Revenue/Sell Price - this is CORRECT behavior, not a defect (the Units Sold tooltip calls it out).
 2. Sold (WO) + Sold (Parts Sale) together DO equal the billed-units basis (work orders are only Service- or Parts-type) - but neither equals the movement-based Units Sold.
-3. On the special-order row, everything reconciles: Units Sold = Sold (WO) + Sold (Parts Sale) = billed units (they share the vendor-request quantity as one source).</t>
+3. On the special-order row, everything reconciles: Units Sold = Sold (WO) + Sold (Parts Sale) = billed units (they share the vendor-request quantity as one source).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R7).</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5-R7; §3 Key Decisions)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R7; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I248" s="2" t="inlineStr"/>
@@ -12573,12 +13094,15 @@
           <t>1. In W1 (work-order date in window): the billed columns (Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO), Sold (Parts Sale)) count the sale, while inventory Units Sold / Demand do NOT (their movement event is outside W1).
 2. In W2 (movement date in window): Units Sold / Demand count it, the billed columns do not - the two anchors CAN differ for an inventory part and that is intended.
 3. The window is the whole-day span inclusive of BOTH the start and end dates, with a floor of 1 day - a single-day range (Today) computes normally (Window = 1 for the Turns / Yr divisor).
-4. Last Sale is not windowed at all (all-time).</t>
+4. Last Sale is not windowed at all (all-time).
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8819
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R7).</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (specs/parts-velocity.md S5 Definitions (Window / Work-order date); S5-R7)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5 Definitions (Window / Work-order date); S5-R7)</t>
         </is>
       </c>
       <c r="I249" s="2" t="inlineStr"/>
@@ -12626,7 +13150,9 @@
           <t>1. Units Sold reads exactly 2.50 — not 2.00, not 3.00, not blank and not a dash.
 2. It still reads exactly 2.50 after the sign-out and sign-back-in, which proves the part-of-a-unit quantity was really stored and not just shown once.
 3. On Hand has gone down by exactly 2.50 from what it was before the sale.
-4. No value anywhere on the row has been quietly rounded to a whole number.</t>
+4. No value anywhere on the row has been quietly rounded to a whole number.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R1, S5-R5).</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
@@ -12672,7 +13198,9 @@
       <c r="G251" s="2" t="inlineStr">
         <is>
           <t>1. The ⋯ overflow button sits leftmost in the toolbar's action cluster.
-2. The menu holds exactly two items, in this order: Download (PDF), then Download (CSV).</t>
+2. The menu holds exactly two items, in this order: Download (PDF), then Download (CSV).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R1).</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -12720,7 +13248,9 @@
         <is>
           <t>1. Both files contain only the rows matching the date range, type, category, vendor, bin, location, and search active at export time - not a full unfiltered dump.
 2. The exported rows match what the on-screen grid was showing.
-3. Each file (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).</t>
+3. Each file (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R2, S6-R11); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
@@ -12768,12 +13298,14 @@
         <is>
           <t>1. Both exports contain ONLY the currently enabled columns - the hidden ones are absent.
 2. Columns appear in the CANONICAL order (the fixed on-screen order) - the re-enabled Units Returned sits right after Units Sold, NOT appended at the end.
-3. The export mirrors the visible grid.</t>
+3. The export mirrors the visible grid.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R3, S4-R4).</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (specs/parts-velocity.md S6-R3; S4-R4)</t>
+          <t>SV-8646 (PV spec v4 2026-07-29 S6-R3; S4-R4)</t>
         </is>
       </c>
       <c r="I253" s="2" t="inlineStr"/>
@@ -12817,12 +13349,14 @@
         <is>
           <t>1. The default Demand-descending order is exported when the user has not chosen another column.
 2. Every column's sort is honored in the export - including Min and Max.
-3. The export renders the EXACT server order, including null placement (nulls first on ascending, last on descending) - the export and the on-screen grid match; there is no on-screen-vs-export null-sorting difference.</t>
+3. The export renders the EXACT server order, including null placement (nulls first on ascending, last on descending) - the export and the on-screen grid match; there is no on-screen-vs-export null-sorting difference.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R4, S3-R3).</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (specs/parts-velocity.md S6-R4; S3-R3)</t>
+          <t>SV-8646 (PV spec v4 2026-07-29 S6-R4; S3-R3)</t>
         </is>
       </c>
       <c r="I254" s="2" t="inlineStr"/>
@@ -12867,12 +13401,14 @@
 2. The PDF is formatted for A3 landscape and titled Parts Velocity.
 3. Description, Category, and Vendor are truncated to 18 characters in the PDF.
 4. Part # is NOT truncated.
-5. The shop logo shows at the top of the PDF when one is set. With no uploaded logo the PDF shows the bundled ShopView default logo instead of a blank space, the same as the other reports in this suite. The CSV never includes a logo.</t>
+5. The shop logo shows at the top of the PDF when one is set. With no uploaded logo the PDF shows the bundled ShopView default logo instead of a blank space, the same as the other reports in this suite. The CSV never includes a logo.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6).</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (specs/parts-velocity.md S6-R5; S6-R6 + same-logo-treatment for every report per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
+          <t>SV-8646 (PV spec v4 2026-07-29 S6-R5; S6-R6 + same-logo-treatment for every report per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
         </is>
       </c>
       <c r="I255" s="2" t="inlineStr"/>
@@ -12915,12 +13451,14 @@
         <is>
           <t>1. The file downloads as velocity-report.csv.
 2. The CSV carries the FULL, untruncated Description / Category / Vendor values (unlike the PDF's 18-character cut).
-3. Last Sale is a raw integer in the CSV (e.g. 42) - the 'N days' wording is PDF/on-screen only.</t>
+3. Last Sale is a raw integer in the CSV (e.g. 42) - the 'N days' wording is PDF/on-screen only.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6, S6-R8).</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (specs/parts-velocity.md S6-R5; S6-R6; S6-R8)</t>
+          <t>SV-8646 (PV spec v4 2026-07-29 S6-R5; S6-R6; S6-R8)</t>
         </is>
       </c>
       <c r="I256" s="2" t="inlineStr"/>
@@ -12956,20 +13494,20 @@
       <c r="F257" s="2" t="inlineStr">
         <is>
           <t>1. Download the CSV and locate the null cells.
-2. Download the PDF and locate the same cells.
-3. In the PDF, read a non-null Last Sale value.</t>
+2. Download the PDF and locate the same cells.</t>
         </is>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
           <t>1. A null value renders as — (em-dash) in BOTH the CSV and the PDF, in every nullable field: Unit Cost, Sell Price, Margin %, On Hand, Turns / Yr, Last Sale, Min, Max.
 2. Revenue, Margin, and the count metrics are never null in the exports either ($0.00 / 0.00 / 0).
-3. In the PDF, Last Sale renders as 'N days' (e.g. 42 days).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R7, S6-R8, S3-R9).</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (specs/parts-velocity.md S6-R7; S6-R8; S3-R9)</t>
+          <t>SV-8646 (PV spec v4 2026-07-29 S6-R7; S6-R8; S3-R9)</t>
         </is>
       </c>
       <c r="I257" s="2" t="inlineStr"/>
@@ -13013,12 +13551,14 @@
 2. In the PDF, the text columns (Part #, Description, Category, Vendor) are left-aligned.
 3. In the PDF, EVERY numeric and money column is right-aligned.
 4. This is a deliberate export-only treatment - the on-screen table is all-left-aligned; the difference is documented, not a defect.
-5. The CSV is plain data — the alignment assertions apply to the PDF only; how a spreadsheet displays the CSV is not part of this test.</t>
+5. The CSV is plain data — the alignment assertions apply to the PDF only; how a spreadsheet displays the CSV is not part of this test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R10, S3-R8).</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (specs/parts-velocity.md S6-R10; S3-R8)</t>
+          <t>SV-8646 (PV spec v4 2026-07-29 S6-R10; S3-R8)</t>
         </is>
       </c>
       <c r="I258" s="2" t="inlineStr"/>
@@ -13062,7 +13602,9 @@
         <is>
           <t>1. On success the toasts read exactly "Velocity report exported (CSV)" / "Velocity report exported (PDF)" and auto-fade — UPPERCASE (CSV)/(PDF).
 2. An error toast is shown on failure; when the server provides a message, that server message is shown.
-3. Otherwise the failure toast reads exactly: "Failed to export velocity report (csv)" or "Failed to export velocity report (pdf)" — lowercase (csv)/(pdf); the success/failure casing mix is the shipped wording, documented as-is (not a bug).</t>
+3. Otherwise the failure toast reads exactly: "Failed to export velocity report (csv)" or "Failed to export velocity report (pdf)" — lowercase (csv)/(pdf); the success/failure casing mix is the shipped wording, documented as-is (not a bug).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R9, S6-N1).</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
@@ -13112,12 +13654,15 @@
         <is>
           <t>1. Neither the CSV nor the PDF is produced — no download starts.
 2. A clear too-large message appears telling the user to narrow the date range or filters, then try again — the standard wording is "This report is too large to export. Narrow the date range or filters, then try again."
-3. After narrowing below the cap, the downloads work again.</t>
+3. After narrowing below the cap, the downloads work again.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (Story 6 exports).</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
-          <t>SV-8646 (specs/parts-velocity.md Story 6 exports — spec silent on a cap; tech-plan-2026-07-29 A3/FR-F4: suite-wide 10; 000-row export cap; locked by Chris 2026-07-21)</t>
+          <t>SV-8646 (PV spec v4 2026-07-29 Story 6 exports — spec silent on a cap; tech-plan-2026-07-29 A3/FR-F4: suite-wide 10; 000-row export cap; locked by Chris 2026-07-21)</t>
         </is>
       </c>
       <c r="I260" s="2" t="inlineStr"/>
@@ -13163,7 +13708,10 @@
           <t>1. The CSV downloads successfully at that size.
 2. The PDF also downloads successfully. If instead nothing downloads and a message appears saying something went wrong, that is a failure — record roughly how many rows were on screen.
 3. The small PDF downloads successfully, which shows the failure depends on size.
-4. Note for the tester: a very large view is refused politely with "This report is too large to export. Narrow the date range or filters, then try again." — that message is expected and is NOT this failure. This test is about a medium-sized view where the CSV works but the PDF errors.</t>
+4. Note for the tester: a very large view is refused politely with "This report is too large to export. Narrow the date range or filters, then try again." — that message is expected and is NOT this failure. This test is about a medium-sized view where the CSV works but the PDF errors.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (Story 6 exports).</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
@@ -13210,12 +13758,14 @@
         <is>
           <t>1. White card surfaces (toolbar + table cells) sit on the standard soft blue-grey page background (the application's two-tone report theme).
 2. There is NO card border-radius - the table runs edge to edge.
-3. The layout matches the application's other reports.</t>
+3. The layout matches the application's other reports.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S7-R1).</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
         <is>
-          <t>SV-8647 (specs/parts-velocity.md S7-R1; §2)</t>
+          <t>SV-8647 (PV spec v4 2026-07-29 S7-R1; §2)</t>
         </is>
       </c>
       <c r="I262" s="2" t="inlineStr"/>
@@ -13261,12 +13811,14 @@
 2. There is a thin dividing line between the toolbar and the column-header band, and the header band and the data cells are white.
 3. The first and last columns sit clear of the left and right edges of the table - the text is not touching the edge.
 4. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
-5. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this - 32px/24px toolbar padding, a 1px header border, 2rem edge padding - are design-token values the design and engineering team check with their own tooling, not by hand.)</t>
+5. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this - 32px/24px toolbar padding, a 1px header border, 2rem edge padding - are design-token values the design and engineering team check with their own tooling, not by hand.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S7-R2, S7-R3, S7-R4, S7-R5).</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
         <is>
-          <t>SV-8647 (specs/parts-velocity.md S7-R2; S7-R3; S7-R4; S7-R5)</t>
+          <t>SV-8647 (PV spec v4 2026-07-29 S7-R2; S7-R3; S7-R4; S7-R5)</t>
         </is>
       </c>
       <c r="I263" s="2" t="inlineStr"/>
@@ -13309,7 +13861,9 @@
         <is>
           <t>1. The report supports dark mode: page background, toolbar, and cells use their dark-mode equivalents.
 2. In BOTH light mode and dark mode the grey ⓘ info icon is clearly visible against the cell behind it - you can see it at a glance without leaning in, and it does not disappear into the background.
-3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes. Only report it if the icon is hard to see. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)</t>
+3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes. Only report it if the icon is hard to see. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S7-R6).</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
@@ -13344,7 +13898,8 @@
       <c r="E265" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Parts Velocity report with more rows in the result set than one page holds.
-2. Browser devtools (network tab) are open to observe the backend requests.</t>
+2. Browser devtools (network tab) are open to observe the backend requests.
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F265" s="2" t="inlineStr">
@@ -13357,12 +13912,14 @@
         <is>
           <t>1. The backend returns ONE page of rows at a time - the full result set is not shipped to the browser.
 2. Paging is resolved on the server: moving to another page issues a fresh backend request for that page.
-3. This keeps the report responsive at scale (organizations can carry 50-60k parts, multiplied across locations).</t>
+3. This keeps the report responsive at scale (organizations can carry 50-60k parts, multiplied across locations).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R10).</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md §2 (server-paginated); S2-R10)</t>
+          <t>SV-8642 (PV spec v4 2026-07-29 §2 (server-paginated); S2-R10)</t>
         </is>
       </c>
       <c r="I265" s="2" t="inlineStr"/>
@@ -13391,7 +13948,8 @@
       </c>
       <c r="E266" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Parts Velocity report with data loaded and the browser devtools network tab open.</t>
+          <t>1. You are on the Parts Velocity report with data loaded and the browser devtools network tab open.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F266" s="2" t="inlineStr">
@@ -13404,12 +13962,14 @@
         <is>
           <t>1. EACH change (Type, date range, Bin, Location, Category, Vendor, search) triggers a fresh server-side data load.
 2. There is no client-side-only narrowing - every filter or search change re-queries the server.
-3. Each change returns the FIRST page of the new result set.</t>
+3. Each change returns the FIRST page of the new result set.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R10).</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
-          <t>SV-8642 (specs/parts-velocity.md S2-R10)</t>
+          <t>SV-8642 (PV spec v4 2026-07-29 S2-R10)</t>
         </is>
       </c>
       <c r="I266" s="2" t="inlineStr"/>
@@ -13438,7 +13998,8 @@
       </c>
       <c r="E267" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Parts Velocity report with data loaded (including rows with null values in a sortable column) and the network tab open.</t>
+          <t>1. You are on the Parts Velocity report with data loaded (including rows with null values in a sortable column) and the network tab open.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F267" s="2" t="inlineStr">
@@ -13452,12 +14013,14 @@
         <is>
           <t>1. Each header click re-fetches the data from the server, ordered by the chosen column and direction, returning the first page of the re-sorted result set.
 2. Null values are placed FIRST on ascending and LAST on descending - as a server sort semantic, so the same order appears on screen and in the exports.
-3. Ties keep a stable order (no explicit secondary key).</t>
+3. Ties keep a stable order (no explicit secondary key).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R3).</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
-          <t>SV-8643 (specs/parts-velocity.md S3-R3)</t>
+          <t>SV-8643 (PV spec v4 2026-07-29 S3-R3)</t>
         </is>
       </c>
       <c r="I267" s="2" t="inlineStr"/>
@@ -13487,7 +14050,8 @@
       <c r="E268" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in as a user whose role has the ordinary reports access turned on and no other reports-related permission turned on.
-2. Browser devtools (network tab) are open.</t>
+2. Browser devtools (network tab) are open.
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F268" s="2" t="inlineStr">
@@ -13501,7 +14065,9 @@
           <t>1. The back end returns the report data - the request is not refused.
 2. The back end returns the export file - the request is not refused.
 3. Both requests succeed with only the ordinary reports access turned on - nothing else had to be enabled.
-4. Note for the tester: if the back end refuses either request for a user who has the ordinary reports access, mark this Failed and report it. If an extra Parts or Inventory reports permission exists in the system it must not change these results - for now it is hidden from the screen and enforces nothing. A per-report permission added on purpose in a later release is a planned change, not a bug, and this test will be updated first.</t>
+4. Note for the tester: if the back end refuses either request for a user who has the ordinary reports access, mark this Failed and report it. If an extra Parts or Inventory reports permission exists in the system it must not change these results - for now it is hidden from the screen and enforces nothing. A per-report permission added on purpose in a later release is a planned change, not a bug, and this test will be updated first.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-R4, S1-N2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -13537,7 +14103,8 @@
         <is>
           <t>1. The test company is connected to QuickBooks.
 2. The part-of-a-unit sale has been made and invoiced — a ZZAUTOTEST part sold in a quantity such as 2.5, at a known unit cost such as $10.00.
-3. You can sign in to that QuickBooks company and look at its journal entries.</t>
+3. You can sign in to that QuickBooks company and look at its journal entries.
+4. This test cannot be run without a company whose QuickBooks account is connected, because it checks what was sent to QuickBooks. If no QuickBooks-connected company is available, mark this test Blocked and say so — do not guess the result.</t>
         </is>
       </c>
       <c r="F269" s="2" t="inlineStr">
@@ -13554,7 +14121,9 @@
           <t>1. The QuickBooks amount is exactly the hand-worked figure to the cent — $25.00 for 2.5 at $10.00.
 2. It is NOT a whole-unit amount such as $20.00 or $30.00, and it is NOT a bigger, multiplied figure.
 3. The quantity behind the QuickBooks amount matches the Units Sold value on the report (2.50) — the two systems agree.
-4. No second or correcting journal entry is created to patch up a wrong amount.</t>
+4. No second or correcting journal entry is created to patch up a wrong amount.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and this point is not covered by any of the six report specifications — it comes from the engineering technical plan.</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -13603,7 +14172,9 @@
         <is>
           <t>1. The report is listed under the Performance group, labeled "Technician Utilization".
 2. Clicking it opens the report.
-3. The entry sits BELOW the pre-existing report links — Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency — the new reports are added below those items without moving or disturbing them.</t>
+3. The entry sits BELOW the pre-existing report links — Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency — the new reports are added below those items without moving or disturbing them.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R1).</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -13650,12 +14221,14 @@
       <c r="G271" s="2" t="inlineStr">
         <is>
           <t>1. Technician A has exactly ONE row.
-2. Technician B has NO row - only technicians with clocked time in the selected range at the selected location(s) appear.</t>
+2. Technician B has NO row - only technicians with clocked time in the selected range at the selected location(s) appear.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R2).</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (specs/technician-utilization.md S1-R2)</t>
+          <t>SV-8648 (TU spec v5 2026-07-29 S1-R2)</t>
         </is>
       </c>
       <c r="I271" s="2" t="inlineStr"/>
@@ -13697,7 +14270,9 @@
         <is>
           <t>1. The date range defaults to the current calendar month (the date picker's "This Month" preset).
 2. Because a range never extends past now, the current-month default effectively shows the month to date.
-3. The location filter defaults to the user's currently active location (the one in the application's global location switcher).</t>
+3. The location filter defaults to the user's currently active location (the one in the application's global location switcher).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R3, S1-R6, S9-R2).</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -13745,12 +14320,14 @@
         <is>
           <t>1. Each range change reloads the report's rows for the new range.
 2. A valid Custom range applies normally.
-3. A Custom span wider than 366 days (matching the largest preset) is rejected - it cannot be applied.</t>
+3. A Custom span wider than 366 days (matching the largest preset) is rejected - it cannot be applied.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R4, S1-R5).</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (specs/technician-utilization.md S1-R4; S1-R5)</t>
+          <t>SV-8648 (TU spec v5 2026-07-29 S1-R4; S1-R5)</t>
         </is>
       </c>
       <c r="I273" s="2" t="inlineStr"/>
@@ -13793,12 +14370,14 @@
         <is>
           <t>1. On the initial load and on every reload (date-range or location change), the data area shows the standard reports loading indicator.
 2. The existing rows are replaced only when the new data returns.
-3. The toolbar remains interactive during the load.</t>
+3. The toolbar remains interactive during the load.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R10).</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (specs/technician-utilization.md S1-R10)</t>
+          <t>SV-8648 (TU spec v5 2026-07-29 S1-R10)</t>
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr"/>
@@ -13844,12 +14423,14 @@
           <t>1. A record that crosses midnight is split by day - each day counts only its own hours; the midnight split is evaluated in the active workplace's time zone.
 2. A record that starts before the range (or ends after it) counts only the part inside the range.
 3. EVERY record is day-grouped and windowed in a SINGLE report-level time zone - the active workplace's - regardless of the location where it was clocked (a record's day, the current-month boundary, and the midnight split all use that one zone).
-4. This matches the Timesheet Activities report's single-time-zone grouping.</t>
+4. This matches the Timesheet Activities report's single-time-zone grouping.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R7).</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (specs/technician-utilization.md S1-R7; S1 context notes)</t>
+          <t>SV-8648 (TU spec v5 2026-07-29 S1-R7; S1 context notes)</t>
         </is>
       </c>
       <c r="I275" s="2" t="inlineStr"/>
@@ -13889,7 +14470,9 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>1. The Technician Utilization report does NOT appear in the navigation.</t>
+          <t>1. The Technician Utilization report does NOT appear in the navigation.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
@@ -13938,7 +14521,9 @@
         <is>
           <t>1. Instead of rows, the data area shows exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).
 2. The Summary row is hidden.
-3. Clearing every technician shows the SAME message and hides the Summary row — this version does not use distinct copy for genuinely-no-data vs a cleared filter.</t>
+3. Clearing every technician shows the SAME message and hides the Summary row — this version does not use distinct copy for genuinely-no-data vs a cleared filter.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-N2, S3-N1, S5-N1, S9-N2).</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
@@ -13991,7 +14576,9 @@
 3. WO Hours = time clocked directly to work orders; Internal Hours = time clocked to internal, non-billable activities.
 4. Internal Hours includes ALL internal time - including hours at a location with no configured labor rate.
 5. Hours show two decimal places with NO thousands separator (e.g. "107.70"), rounded from the unrounded hours using round-half-up (a tie rounds away from zero - 0.005 → 0.01).
-6. When more than one location is in scope the automatic Location column also appears, leftmost before Technician — it is not in the Column Selection control and its presence is expected.</t>
+6. When more than one location is in scope the automatic Location column also appears, leftmost before Technician — it is not in the Column Selection control and its presence is expected.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R1, S2-R2, S2-R3, S2-R4, S2-R5, S9-R9).</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -14037,12 +14624,14 @@
       <c r="G279" s="2" t="inlineStr">
         <is>
           <t>1. Utilization % = work-order hours as a percentage of total clocked hours, computed from the unrounded hours (not from the already-rounded displays).
-2. It shows one decimal place followed by a percent sign, rounded round-half-up (66.65% → 66.7%).</t>
+2. It shows one decimal place followed by a percent sign, rounded round-half-up (66.65% → 66.7%).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R6, S2-R7).</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-R6; S2-R7; §3)</t>
+          <t>SV-8649 (TU spec v5 2026-07-29 S2-R6; S2-R7; §3)</t>
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr"/>
@@ -14085,12 +14674,14 @@
         <is>
           <t>1. The internal-only technician shows "0.0%".
 2. No row shows more than 100% - work-order hours are always part of total clocked hours.
-3. The "—" (undefined, total = 0) state is unreachable on a rendered technician or day row, because only technicians with clocked time get rows.</t>
+3. The "—" (undefined, total = 0) state is unreachable on a rendered technician or day row, because only technicians with clocked time get rows.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-E1, S2-R7).</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-E1; S2-R7; S2 context note)</t>
+          <t>SV-8649 (TU spec v5 2026-07-29 S2-E1; S2-R7; S2 context note)</t>
         </is>
       </c>
       <c r="I280" s="2" t="inlineStr"/>
@@ -14135,12 +14726,14 @@
         <is>
           <t>1. Est. Lost Labor = the sum, per contributing location, of that location's default labor rate × the technician's internal hours clocked there - summed at full precision, with the technician's total rounded ONCE (round-half-up).
 2. In a single-location view it is simply that one location's rate × the technician's internal hours.
-3. The value shows as dollars with two decimals and commas between thousands (e.g. "$1,234.50").</t>
+3. The value shows as dollars with two decimals and commas between thousands (e.g. "$1,234.50").
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R8, S2-R9).</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-R8; S2-R9; §3)</t>
+          <t>SV-8649 (TU spec v5 2026-07-29 S2-R8; S2-R9; §3)</t>
         </is>
       </c>
       <c r="I281" s="2" t="inlineStr"/>
@@ -14186,7 +14779,9 @@
           <t>1. While Est. Lost Labor is shown, the column is pinned to the far right; its cells are bold and its header is bold, matching.
 2. The information icon shows exactly: "Internal hours valued at each location's default labor rate" — on hover, on keyboard focus, and on tap; it is dismissible.
 3. NO column header other than Est. Lost Labor shows the information icon.
-4. Est. Lost Labor can be turned OFF in the Column Selection control; when it is off the column, its bold styling and its information icon are all absent, and the report still works normally.</t>
+4. Est. Lost Labor can be turned OFF in the Column Selection control; when it is off the column, its bold styling and its information icon are all absent, and the report still works normally.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R10, S2-R11, S8-R4, S8-R6, S8-R7, S8-N1, S10-R3).</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14234,12 +14829,14 @@
         <is>
           <t>1. Technician A shows "$0.00" - there is nothing to value, regardless of whether the location has a rate configured.
 2. Technician B also shows "$0.00" - a configured rate of exactly $0.00 is a KNOWN rate that values the hours at $0.00, not "—".
-3. "$0.00" means 'the rate is known and there is nothing (or $0) to value' - a different state from "—" ('the rate is unknown').</t>
+3. "$0.00" means 'the rate is known and there is nothing (or $0) to value' - a different state from "—" ('the rate is unknown').
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-E2).</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-E2; §5 Assumptions; S2 context note)</t>
+          <t>SV-8649 (TU spec v5 2026-07-29 S2-E2; §5 Assumptions; S2 context note)</t>
         </is>
       </c>
       <c r="I283" s="2" t="inlineStr"/>
@@ -14268,7 +14865,8 @@
       </c>
       <c r="E284" s="2" t="inlineStr">
         <is>
-          <t>1. A technician's in-range internal hours were all clocked at location(s) with NO default labor rate configured (rate absent, not $0.00).</t>
+          <t>1. A technician's in-range internal hours were all clocked at location(s) with NO default labor rate configured (rate absent, not $0.00).
+2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
       <c r="F284" s="2" t="inlineStr">
@@ -14281,12 +14879,14 @@
         <is>
           <t>1. Est. Lost Labor shows "—" (an em-dash), NOT "$0.00" - the rate is unknown, so the value cannot be computed.
 2. The "—" cell carries the assistive-technology label "No default labor rate configured" (distinguishing it from "$0.00", which reads as its dollar value).
-3. The technician's Internal Hours column still shows all the internal hours (they are counted even though they cannot be valued).</t>
+3. The technician's Internal Hours column still shows all the internal hours (they are counted even though they cannot be valued).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-E3, S8-R11, S2-R4).</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-E3; S8-R11; S2-R4)</t>
+          <t>SV-8649 (TU spec v5 2026-07-29 S2-E3; S8-R11; S2-R4)</t>
         </is>
       </c>
       <c r="I284" s="2" t="inlineStr"/>
@@ -14329,12 +14929,14 @@
         <is>
           <t>1. Est. Lost Labor is the sum of the valued (rated-location) portions only - the unrated-location hours are excluded from the dollar amount.
 2. The amount shows as a normal "$X.XX" with NO partial-value indicator in this version - so the row's Est. Lost Labor values fewer hours than its Internal Hours column shows.
-3. This is a documented known limitation (a partial-value indicator is a possible follow-up) - expected behavior, not a defect.</t>
+3. This is a documented known limitation (a partial-value indicator is a possible follow-up) - expected behavior, not a defect.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-E4).</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-E4)</t>
+          <t>SV-8649 (TU spec v5 2026-07-29 S2-E4)</t>
         </is>
       </c>
       <c r="I285" s="2" t="inlineStr"/>
@@ -14363,7 +14965,8 @@
       </c>
       <c r="E286" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Technician Utilization report with several technician rows loaded.</t>
+          <t>1. You are on the Technician Utilization report with several technician rows loaded.
+2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
       <c r="F286" s="2" t="inlineStr">
@@ -14377,12 +14980,14 @@
         <is>
           <t>1. The technician rows are sorted by Technician name, A to Z.
 2. The Technician header shows the ascending sort indicator.
-3. The active sort header exposes its state to assistive technology (aria-sort = ascending on the Technician header; none on the others).</t>
+3. The active sort header exposes its state to assistive technology (aria-sort = ascending on the Technician header; none on the others).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R12, S8-R8, S8-R10).</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-R12; S8-R8; S8-R10)</t>
+          <t>SV-8649 (TU spec v5 2026-07-29 S2-R12; S8-R8; S8-R10)</t>
         </is>
       </c>
       <c r="I286" s="2" t="inlineStr"/>
@@ -14429,12 +15034,14 @@
 2. Clicking a column that is not the active sort sorts it ascending; clicking the active column again toggles to descending; further clicks only ever toggle ascending↔descending - there is NO third 'cleared' state.
 3. All six columns are sortable.
 4. Sorting is applied on screen to the loaded rows - NO reload/server request happens.
-5. Technicians tied in the sorted column are ordered by Technician name A to Z; two technicians sharing the same display name keep a stable order between renders.</t>
+5. Technicians tied in the sorted column are ordered by Technician name A to Z; two technicians sharing the same display name keep a stable order between renders.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R13, S2-R14).</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-R13; S2-R14)</t>
+          <t>SV-8649 (TU spec v5 2026-07-29 S2-R13; S2-R14)</t>
         </is>
       </c>
       <c r="I287" s="2" t="inlineStr"/>
@@ -14476,12 +15083,14 @@
       <c r="G288" s="2" t="inlineStr">
         <is>
           <t>1. After the reload, the rows are back to Technician name A to Z (the sort reset).
-2. On the return visit, the sort is again Technician A to Z - sort is NOT persisted (unlike the date range, technician selection, and location selection, which are).</t>
+2. On the return visit, the sort is again Technician A to Z - sort is NOT persisted (unlike the date range, technician selection, and location selection, which are).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R15).</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-R15; §3)</t>
+          <t>SV-8649 (TU spec v5 2026-07-29 S2-R15; §3)</t>
         </is>
       </c>
       <c r="I288" s="2" t="inlineStr"/>
@@ -14524,12 +15133,14 @@
         <is>
           <t>1. Only the technician rows reorder.
 2. The Summary row stays pinned at the bottom.
-3. Each technician's expanded day rows stay under that technician, still in date order (earliest to latest) - they do not re-sort by the clicked column.</t>
+3. Each technician's expanded day rows stay under that technician, still in date order (earliest to latest) - they do not re-sort by the clicked column.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R16).</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-R16)</t>
+          <t>SV-8649 (TU spec v5 2026-07-29 S2-R16)</t>
         </is>
       </c>
       <c r="I289" s="2" t="inlineStr"/>
@@ -14572,12 +15183,14 @@
         <is>
           <t>1. Rows whose Est. Lost Labor is "—" sort to the BOTTOM in BOTH ascending and descending order - they are never floated to the top by reversing direction.
 2. Among themselves, the "—" rows are ordered by Technician name A to Z.
-3. A "$0.00" value is a number, not "—" - it sorts as zero (lowest ascending, above only the — group).</t>
+3. A "$0.00" value is a number, not "—" - it sorts as zero (lowest ascending, above only the — group).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R17).</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
         <is>
-          <t>SV-8649 (specs/technician-utilization.md S2-R17)</t>
+          <t>SV-8649 (TU spec v5 2026-07-29 S2-R17)</t>
         </is>
       </c>
       <c r="I290" s="2" t="inlineStr"/>
@@ -14621,12 +15234,14 @@
           <t>1. A Summary row is pinned to the bottom of the report, labeled "Summary".
 2. It stays visible at the bottom while the rows scroll.
 3. It uses the same number formats as the technician rows.
-4. Its values carry NO label prefix such as "TOTAL:" or "AVG:".</t>
+4. Its values carry NO label prefix such as "TOTAL:" or "AVG:".
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S3-R1, S3-R2, S3-R6, S3-R7, S8-R5).</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
         <is>
-          <t>SV-8650 (specs/technician-utilization.md S3-R1; S3-R2; S3-R6; S3-R7; S8-R5)</t>
+          <t>SV-8650 (TU spec v5 2026-07-29 S3-R1; S3-R2; S3-R6; S3-R7; S8-R5)</t>
         </is>
       </c>
       <c r="I291" s="2" t="inlineStr"/>
@@ -14669,12 +15284,14 @@
         <is>
           <t>1. Each Summary hours value is the total of that column across the VISIBLE technicians, computed from unrounded hours and rounded once for display (round-half-up).
 2. Eye-summing the displayed rows MAY differ from the displayed Summary by 0.01 — one unit in the last decimal (these values are HOURS, not money) — expected in a compute-from-unrounded report, not a defect.
-3. With every technician selected, the Summary row equals the shop totals for the full date range at the selected location(s).</t>
+3. With every technician selected, the Summary row equals the shop totals for the full date range at the selected location(s).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S3-R3, S5-E1).</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
         <is>
-          <t>SV-8650 (specs/technician-utilization.md S3-R3; §3 context note; S5-E1)</t>
+          <t>SV-8650 (TU spec v5 2026-07-29 S3-R3; §3 context note; S5-E1)</t>
         </is>
       </c>
       <c r="I292" s="2" t="inlineStr"/>
@@ -14716,12 +15333,14 @@
       <c r="G293" s="2" t="inlineStr">
         <is>
           <t>1. The Summary Utilization % shows the WEIGHTED rate - the visible technicians' total work-order hours as a percentage of their total clocked hours, from unrounded hours (10.0% in the example).
-2. It is NOT the average of the per-technician percentages (not 50.0%).</t>
+2. It is NOT the average of the per-technician percentages (not 50.0%).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S3-R4).</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
-          <t>SV-8650 (specs/technician-utilization.md S3-R4)</t>
+          <t>SV-8650 (TU spec v5 2026-07-29 S3-R4)</t>
         </is>
       </c>
       <c r="I293" s="2" t="inlineStr"/>
@@ -14763,12 +15382,14 @@
         <is>
           <t>1. The Summary Est. Lost Labor is computed like a row but over all visible technicians' internal hours: rate × internal hours per contributing rated location, summed at full precision and rounded once.
 2. A visible technician whose value is "—" contributes NOTHING to the sum - so the Summary understates true lost labor whenever any visible technician is "—" or partially valued (documented, expected).
-3. The Summary shows "—" only when EVERY visible technician's Est. Lost Labor is "—".</t>
+3. The Summary shows "—" only when EVERY visible technician's Est. Lost Labor is "—".
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S3-R5).</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
-          <t>SV-8650 (specs/technician-utilization.md S3-R5)</t>
+          <t>SV-8650 (TU spec v5 2026-07-29 S3-R5)</t>
         </is>
       </c>
       <c r="I294" s="2" t="inlineStr"/>
@@ -14797,7 +15418,8 @@
       </c>
       <c r="E295" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Technician Utilization report with rows loaded.</t>
+          <t>1. You are on the Technician Utilization report with rows loaded.
+2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
       <c r="F295" s="2" t="inlineStr">
@@ -14811,12 +15433,14 @@
         <is>
           <t>1. Each technician row has a control to expand and collapse it.
 2. Its accessible name reflects the NEXT action, scoped to that technician: when collapsed it reads Expand, then that technician's name, then daily breakdown (for example: Expand John Smith's daily breakdown); when expanded it reads Collapse, then the same name and words.
-3. The control is keyboard-focusable, toggles on Enter and Space, and exposes its expanded/collapsed state to assistive technology.</t>
+3. The control is keyboard-focusable, toggles on Enter and Space, and exposes its expanded/collapsed state to assistive technology.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R1, S8-R12).</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
-          <t>SV-8651 (specs/technician-utilization.md S4-R1; S8-R12)</t>
+          <t>SV-8651 (TU spec v5 2026-07-29 S4-R1; S8-R12)</t>
         </is>
       </c>
       <c r="I295" s="2" t="inlineStr"/>
@@ -14863,7 +15487,9 @@
 2. The day rows are not there until you expand the row - they arrive at the moment you expand it (you may briefly see the standard loading indicator in that area), and the rest of the report does not reload.
 3. A day with no clocked time has NO row.
 4. With several locations selected, a day's row POOLS that day's hours across the selected locations - one day row per date, not one per location.
-5. Note for the tester: you do not need developer tools for this test - just watch the screen.</t>
+5. Note for the tester: you do not need developer tools for this test - just watch the screen.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R2, S4-N1, S9-R4).</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
@@ -14911,12 +15537,14 @@
         <is>
           <t>1. Each day row shows the same columns, in the same formats, as the technician row - with that day's values.
 2. The day's Est. Lost Labor is valued per location exactly like a technician row (that location's default labor rate × that day's internal hours there).
-3. Hours 2dp / Utilization one decimal + % / dollars with commas - all identical to the row formats, computed from unrounded values and rounded once.</t>
+3. Hours 2dp / Utilization one decimal + % / dollars with commas - all identical to the row formats, computed from unrounded values and rounded once.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R3, S2-R8).</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
-          <t>SV-8651 (specs/technician-utilization.md S4-R3; S2-R8; §3)</t>
+          <t>SV-8651 (TU spec v5 2026-07-29 S4-R3; S2-R8; §3)</t>
         </is>
       </c>
       <c r="I297" s="2" t="inlineStr"/>
@@ -14945,7 +15573,8 @@
       </c>
       <c r="E298" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Technician Utilization report with several technician rows loaded.</t>
+          <t>1. You are on the Technician Utilization report with several technician rows loaded.
+2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
       <c r="F298" s="2" t="inlineStr">
@@ -14961,12 +15590,14 @@
           <t>1. The control lives in the table's header row (Technician column) - NOT in the toolbar action cluster.
 2. If ANY row is collapsed, activating it expands ALL rows; only when EVERY row is already expanded does it collapse all rows (so step 3's activation re-expands the one collapsed row).
 3. Its accessible name reflects the next action: "Expand all technicians" when it will expand, "Collapse all technicians" when every row is already expanded.
-4. It is keyboard-focusable, toggles on Enter/Space, and exposes its state to assistive technology.</t>
+4. It is keyboard-focusable, toggles on Enter/Space, and exposes its state to assistive technology.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R4, S8-R12, S8-R3).</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
-          <t>SV-8651 (specs/technician-utilization.md S4-R4; S8-R12; S8-R3)</t>
+          <t>SV-8651 (TU spec v5 2026-07-29 S4-R4; S8-R12; S8-R3)</t>
         </is>
       </c>
       <c r="I298" s="2" t="inlineStr"/>
@@ -15009,12 +15640,14 @@
         <is>
           <t>1. After the reload (date-range or location change), all rows are collapsed - expansion state resets.
 2. On a fresh visit, all rows start collapsed - expansion is never persisted.
-3. Deselecting and re-selecting a technician (an on-screen operation) does NOT change the expansion state of the other rows - the expanded row stays expanded.</t>
+3. Deselecting and re-selecting a technician (an on-screen operation) does NOT change the expansion state of the other rows - the expanded row stays expanded.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R5).</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
-          <t>SV-8651 (specs/technician-utilization.md S4-R5)</t>
+          <t>SV-8651 (TU spec v5 2026-07-29 S4-R5)</t>
         </is>
       </c>
       <c r="I299" s="2" t="inlineStr"/>
@@ -15057,12 +15690,14 @@
         <is>
           <t>1. The toolbar has a filter labeled "Technician" that allows selecting more than one technician (when several are chosen its label reads, for example, "2 technicians").
 2. On the first visit, EVERY technician is selected.
-3. All technicians' rows are shown.</t>
+3. All technicians' rows are shown.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S5-R1, S5-R2).</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>SV-8652 (specs/technician-utilization.md S5-R1; S5-R2)</t>
+          <t>SV-8652 (TU spec v5 2026-07-29 S5-R1; S5-R2)</t>
         </is>
       </c>
       <c r="I300" s="2" t="inlineStr"/>
@@ -15108,7 +15743,9 @@
 2. The Summary row recalculates over the technicians that remain visible.
 3. The report does NOT reload - the technician filter works on screen only: the rows and the Summary update straight away, no loading indicator appears in the data area, and the date range does not change.
 4. Re-selecting the technician shows the row again (and the Summary recalculates back).
-5. Note for the tester: you do not need developer tools for this test - just watch the screen.</t>
+5. Note for the tester: you do not need developer tools for this test - just watch the screen.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S5-R3, S5-R4, S5-R5).</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
@@ -15158,12 +15795,14 @@
           <t>1. "Clear all" sets every currently-listed technician to deselected; "All technicians" selects all technicians at once.
 2. Selection is tracked as the set of DESELECTED technicians: a technician you have not deselected is selected by default.
 3. After step 3, your deselected technician STAYS deselected across the range change, while the newly-appearing technician is SELECTED (never explicitly deselected).
-4. After step 4, the newly-appearing technician is selected even though you had cleared all - "Clear all" only deselected the technicians listed at the time.</t>
+4. After step 4, the newly-appearing technician is selected even though you had cleared all - "Clear all" only deselected the technicians listed at the time.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S5-R6, S5-R7, S5-R8, S5-R9).</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>SV-8652 (specs/technician-utilization.md S5-R6; S5-R7; S5-R8; S5-R9)</t>
+          <t>SV-8652 (TU spec v5 2026-07-29 S5-R6; S5-R7; S5-R8; S5-R9)</t>
         </is>
       </c>
       <c r="I302" s="2" t="inlineStr"/>
@@ -15206,12 +15845,14 @@
         <is>
           <t>1. The two deselected technicians are STILL deselected on return - the deselected set is what persists (saved in this browser, not on the account).
 2. All other technicians - including any who appear for the first time - are selected.
-3. The saved date range and location selection are restored alongside.</t>
+3. The saved date range and location selection are restored alongside.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S5-R10, S1-R8).</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>SV-8652 (specs/technician-utilization.md S5-R10; S1-R8; §3)</t>
+          <t>SV-8652 (TU spec v5 2026-07-29 S5-R10; S1-R8; §3)</t>
         </is>
       </c>
       <c r="I303" s="2" t="inlineStr"/>
@@ -15254,12 +15895,14 @@
         <is>
           <t>1. Every technician row's Total Hours is rendered as a link (every rendered row has clocked time &gt; 0, so the link always applies).
 2. The link is distinguished by more than color - it carries an underline (or equivalent non-color affordance), is keyboard-focusable with a visible focus indicator, and activates on Enter.
-3. The Summary row's Total Hours value is NOT a link.</t>
+3. The Summary row's Total Hours value is NOT a link.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S6-R1, S6-N1, S8-R14).</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>SV-8653 (specs/technician-utilization.md S6-R1; S6-N1; S8-R14)</t>
+          <t>SV-8653 (TU spec v5 2026-07-29 S6-R1; S6-N1; S8-R14)</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr"/>
@@ -15302,12 +15945,14 @@
         <is>
           <t>1. The Timesheet Activities report opens in the SAME browser tab.
 2. It is already filtered to that technician.
-3. It uses the same date range that was active on the Technician Utilization report.</t>
+3. It uses the same date range that was active on the Technician Utilization report.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S6-R2, S6-R3, S6-R4).</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>SV-8653 (specs/technician-utilization.md S6-R2; S6-R3; S6-R4)</t>
+          <t>SV-8653 (TU spec v5 2026-07-29 S6-R2; S6-R3; S6-R4)</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr"/>
@@ -15351,12 +15996,14 @@
         <is>
           <t>1. The two totals MATCH exactly, to two decimals (these values are hours, not money) - both reports read the same clock records and round the same way (round-half-up, from unrounded values).
 2. Under this exact scope (same range, same single location, closed records) a mismatch IS a defect.
-3. The two documented scope differences (open clocks, multi-location drill-through) are covered by separate cases and are NOT defects.</t>
+3. The two documented scope differences (open clocks, multi-location drill-through) are covered by separate cases and are NOT defects.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R9).</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (specs/technician-utilization.md S1-R9; §2; §5 Assumptions)</t>
+          <t>SV-8648 (TU spec v5 2026-07-29 S1-R9; §2; §5 Assumptions)</t>
         </is>
       </c>
       <c r="I306" s="2" t="inlineStr"/>
@@ -15399,12 +16046,14 @@
         <is>
           <t>1. The open time is counted UP TO THE MOMENT THE REPORT LOADS - a fixed snapshot taken at load, not a value that keeps ticking on screen (matching how Timesheet Activities treats an open record).
 2. The two reports, loaded at different moments, MAY differ by the elapsed open time - this is a deliberate scope difference of the reconciliation guarantee, EXPECTED and NOT a defect.
-3. Reloading the Technician Utilization report takes a fresh snapshot (the value grows by the elapsed time).</t>
+3. Reloading the Technician Utilization report takes a fresh snapshot (the value grows by the elapsed time).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R9, S1-E1).</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (specs/technician-utilization.md S1-R9(a); S1-E1)</t>
+          <t>SV-8648 (TU spec v5 2026-07-29 S1-R9(a); S1-E1)</t>
         </is>
       </c>
       <c r="I307" s="2" t="inlineStr"/>
@@ -15448,12 +16097,14 @@
         <is>
           <t>1. The link passes the technician and the date range ONLY - it does NOT pass the location selection.
 2. Timesheet Activities opens for the user's currently active shop, so it shows one location's portion - it will differ from (or be disjoint with) the multi-location row value.
-3. This is a KNOWN drill-through limitation, EXPECTED and NOT a data defect (the same applies when the single selected location is not the active shop).</t>
+3. This is a KNOWN drill-through limitation, EXPECTED and NOT a data defect (the same applies when the single selected location is not the active shop).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S6-R6, S1-R9).</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
-          <t>SV-8653 (specs/technician-utilization.md S6-R6; S1-R9(b))</t>
+          <t>SV-8653 (TU spec v5 2026-07-29 S6-R6; S1-R9(b))</t>
         </is>
       </c>
       <c r="I308" s="2" t="inlineStr"/>
@@ -15494,12 +16145,14 @@
       <c r="G309" s="2" t="inlineStr">
         <is>
           <t>1. Timesheet Activities opens filtered to that technician.
-2. The date range covers ONLY that single day.</t>
+2. The date range covers ONLY that single day.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S6-R5).</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
         <is>
-          <t>SV-8653 (specs/technician-utilization.md S6-R5)</t>
+          <t>SV-8653 (TU spec v5 2026-07-29 S6-R5)</t>
         </is>
       </c>
       <c r="I309" s="2" t="inlineStr"/>
@@ -15541,7 +16194,9 @@
         <is>
           <t>1. The three-dot download menu sits LEFTMOST in the toolbar's action cluster, with the Column Selection control immediately after it.
 2. The menu holds: "Download Summary (PDF)", "Download Expanded View (PDF)", and "Download (CSV)".
-3. The labels match exactly - only the expanded option carries the word "View" (the shipped strings, documented as-is).</t>
+3. The labels match exactly - only the expanded option carries the word "View" (the shipped strings, documented as-is).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R1, S7-R2, S7-R3, S7-R4, S8-R2).</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15588,12 +16243,14 @@
         <is>
           <t>1. The Summary PDF shows the technician rows and the Summary row (no day rows); it downloads as "Technician-Utilization-Summary.pdf".
 2. The Expanded PDF shows the technician rows, EACH technician's per-day breakdown, and the Summary row; it downloads as "Technician-Utilization-Expanded.pdf".
-3. The PDF filenames are Title-Case as shipped.</t>
+3. The PDF filenames are Title-Case as shipped.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R5, S7-R6, S7-R12).</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (specs/technician-utilization.md S7-R5; S7-R6; S7-R12)</t>
+          <t>SV-8654 (TU spec v5 2026-07-29 S7-R5; S7-R6; S7-R12)</t>
         </is>
       </c>
       <c r="I311" s="2" t="inlineStr"/>
@@ -15636,12 +16293,14 @@
         <is>
           <t>1. The file downloads as "technician-utilization.csv" (lower-case as shipped, unlike the Title-Case PDFs).
 2. The CSV shows the technician rows and the Summary row - always this summary-level content; it does NOT vary by the summary/expanded choice (no day rows).
-3. Any value containing a comma (e.g. "$1,234.50") is wrapped in double quotes per standard CSV escaping, so the columns parse correctly.</t>
+3. Any value containing a comma (e.g. "$1,234.50") is wrapped in double quotes per standard CSV escaping, so the columns parse correctly.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R7, S7-R10, S7-R12).</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (specs/technician-utilization.md S7-R7; S7-R10; S7-R12)</t>
+          <t>SV-8654 (TU spec v5 2026-07-29 S7-R7; S7-R10; S7-R12)</t>
         </is>
       </c>
       <c r="I312" s="2" t="inlineStr"/>
@@ -15689,7 +16348,9 @@
 3. With every technician selected, the download covers all technicians for the range at the selected location(s).
 4. Every download (each PDF and the CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
 5. Every download also mirrors the columns currently shown on screen — a column hidden in the Column Selection control is absent from the files, and a re-shown column comes back.
-6. Note for the tester: when you have more than one location in scope, the files also carry a Location column even though it is not in the Column Selection control. That is correct - it appears by itself. With a single location in scope there is no Location column, and that is also correct.</t>
+6. Note for the tester: when you have more than one location in scope, the files also carry a Location column even though it is not in the Column Selection control. That is correct - it appears by itself. With a single location in scope there is no Location column, and that is also correct.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R8, S7-R9, S7-R10, S7-R13, S7-E1, S9-R8).</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -15737,12 +16398,14 @@
       <c r="G314" s="2" t="inlineStr">
         <is>
           <t>1. The downloaded files use the same column order and number formats as the on-screen report, including the "—" rendering for an unknown Est. Lost Labor.
-2. Rows in EVERY download are ordered by Technician name A to Z (the default order) - the on-screen column sort is client-side only and is NOT carried into the export.</t>
+2. Rows in EVERY download are ordered by Technician name A to Z (the default order) - the on-screen column sort is client-side only and is NOT carried into the export.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R10, S7-R10a).</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (specs/technician-utilization.md S7-R10; S7-R10a)</t>
+          <t>SV-8654 (TU spec v5 2026-07-29 S7-R10; S7-R10a)</t>
         </is>
       </c>
       <c r="I314" s="2" t="inlineStr"/>
@@ -15785,7 +16448,9 @@
         <is>
           <t>1. With an uploaded logo, BOTH PDF views show that logo at the top of the report.
 2. The CSV never includes the logo.
-3. With NO uploaded logo, the PDF views show the bundled ShopView logo instead — not a blank space and not an error.</t>
+3. With NO uploaded logo, the PDF views show the bundled ShopView logo instead — not a blank space and not an error.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R11, S7-N2, S7-N3).</t>
         </is>
       </c>
       <c r="H315" s="2" t="inlineStr">
@@ -15832,12 +16497,14 @@
       <c r="G316" s="2" t="inlineStr">
         <is>
           <t>1. Nothing happens: NO file downloads and NO message appears (not even an error).
-2. This silent no-op is the specified behavior for every download option when no technician is selected.</t>
+2. This silent no-op is the specified behavior for every download option when no technician is selected.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-N1).</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (specs/technician-utilization.md S7-N1; §7 context note)</t>
+          <t>SV-8654 (TU spec v5 2026-07-29 S7-N1; §7 context note)</t>
         </is>
       </c>
       <c r="I316" s="2" t="inlineStr"/>
@@ -15879,7 +16546,9 @@
       <c r="G317" s="2" t="inlineStr">
         <is>
           <t>1. When a download starts, a success notification reads exactly: "Download started".
-2. When a download fails, an error notification reads exactly: "Failed to download report".</t>
+2. When a download fails, an error notification reads exactly: "Failed to download report".
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (§7 notifications table, Story 7 has no S, §7 is the closing reference).</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr">
@@ -15929,12 +16598,15 @@
         <is>
           <t>1. Neither the CSV nor the PDF is produced — no download starts.
 2. A clear too-large message appears telling the user to narrow the date range or filters, then try again — the standard wording is "This report is too large to export. Narrow the date range or filters, then try again."
-3. After narrowing below the cap, the downloads work again.</t>
+3. After narrowing below the cap, the downloads work again.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (Story 7 exports).</t>
         </is>
       </c>
       <c r="H318" s="2" t="inlineStr">
         <is>
-          <t>SV-8654 (specs/technician-utilization.md Story 7 exports — spec silent on a cap; tech-plan-2026-07-29 A3/FR-F4: suite-wide 10; 000-row export cap; locked by Chris 2026-07-21)</t>
+          <t>SV-8654 (TU spec v5 2026-07-29 Story 7 exports — spec silent on a cap; tech-plan-2026-07-29 A3/FR-F4: suite-wide 10; 000-row export cap; locked by Chris 2026-07-21)</t>
         </is>
       </c>
       <c r="I318" s="2" t="inlineStr"/>
@@ -15980,12 +16652,14 @@
           <t>1. The toolbar has a location filter labeled "Location" - a multi-select and the RIGHTMOST control.
 2. It lists the locations the signed-in user has access to, plus an "All locations" option and a "Clear all" action. (If you only have access to one location, the "All locations" entry is not offered - you see "Clear all" and your one location.)
 3. "All locations" acts as a select-all shortcut: choosing it selects every accessible location; unchecking one location leaves the remaining specific locations selected - the selection is always the concrete set of checked locations.
-4. With more than one location selected, a Location column appears in the table and each row names its location - or reads "Multiple" for a technician whose hours span more than one of them. (Where that column sits on screen is checked by its own test.)</t>
+4. With more than one location selected, a Location column appears in the table and each row names its location - or reads "Multiple" for a technician whose hours span more than one of them. (Where that column sits on screen is checked by its own test.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H319" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (specs/technician-utilization.md S9-R1 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20; user ruling 2026-07-28: video overrides spec (video newer; last-update-wins))</t>
+          <t>SV-8656 (TU spec v5 2026-07-29 S9-R1 — per-row location identifier in All-Locations view ADDED per kickoff video P10 40:58-41:20; user ruling 2026-07-28: video overrides spec (video newer; last-update-wins))</t>
         </is>
       </c>
       <c r="I319" s="2" t="inlineStr"/>
@@ -16032,12 +16706,14 @@
 2. All metrics (technician rows, per-day rows, and the Summary) reflect only clock records at the selected location(s).
 3. The technician's hours are POOLED across the selected locations into ONE row (one row per technician, not one per location); per-day rows pool the same way.
 4. Scoping never goes beyond the user's accessible locations - a location the user cannot access is never included.
-5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).</t>
+5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R3, S9-R4, S9-R5).</t>
         </is>
       </c>
       <c r="H320" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (specs/technician-utilization.md S9-R3; S9-R4; S9-R5 + on-screen location-scope indicator per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
+          <t>SV-8656 (TU spec v5 2026-07-29 S9-R3; S9-R4; S9-R5 + on-screen location-scope indicator per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
         </is>
       </c>
       <c r="I320" s="2" t="inlineStr"/>
@@ -16079,12 +16755,14 @@
         <is>
           <t>1. Any saved location the user can no longer access is DROPPED from the restored selection; the remaining accessible locations restore normally.
 2. If the remaining set is empty, the report falls back to the user's currently active location (the first-visit default).
-3. The report loads without an error in both cases.</t>
+3. The report loads without an error in both cases.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R6, S1-R8, S9-R2).</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (specs/technician-utilization.md S9-R6; S1-R8; S9-R2)</t>
+          <t>SV-8656 (TU spec v5 2026-07-29 S9-R6; S1-R8; S9-R2)</t>
         </is>
       </c>
       <c r="I321" s="2" t="inlineStr"/>
@@ -16125,12 +16803,14 @@
       <c r="G322" s="2" t="inlineStr">
         <is>
           <t>1. The report falls back to the user's currently active location rather than showing nothing.
-2. Rows for the active location load normally.</t>
+2. Rows for the active location load normally.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R7).</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (specs/technician-utilization.md S9-R7)</t>
+          <t>SV-8656 (TU spec v5 2026-07-29 S9-R7)</t>
         </is>
       </c>
       <c r="I322" s="2" t="inlineStr"/>
@@ -16172,7 +16852,9 @@
       <c r="G323" s="2" t="inlineStr">
         <is>
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
-2. For the user with access to two or more locations the Location filter IS shown.</t>
+2. For the user with access to two or more locations the Location filter IS shown.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H323" s="2" t="inlineStr">
@@ -16220,8 +16902,7 @@
 5. Read the Location cell on the Summary row at the bottom.
 6. Open the Column Selection control and look for Location in the list.
 7. Narrow to a single location and read the headers again.
-8. Change the selection between one location, several, and "All Locations", watching the filter control's width.
-9. With more than one location still selected, download both PDF views and the CSV and read their columns from the left.</t>
+8. With more than one location still selected, download both PDF views and the CSV and read their columns from the left.</t>
         </is>
       </c>
       <c r="G324" s="2" t="inlineStr">
@@ -16233,8 +16914,9 @@
 5. The Summary row leaves the Location cell blank.
 6. Location is never listed in the Column Selection control — it follows the location scope on its own.
 7. With a single location in scope the Location column is hidden.
-8. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
-9. Every download — both PDF views and the CSV — includes the Location column in its on-screen leftmost position, carrying the same values you just read on screen.</t>
+8. Every download — both PDF views and the CSV — includes the Location column in its on-screen leftmost position, carrying the same values you just read on screen.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R9, S9-R10, S8-R15, S10-R4, S7-R13).</t>
         </is>
       </c>
       <c r="H324" s="2" t="inlineStr">
@@ -16269,7 +16951,8 @@
       <c r="E325" s="2" t="inlineStr">
         <is>
           <t>1. You are on the Technician Utilization report with rows loaded.
-2. This browser has never saved settings for this report (fresh visit), so every column is at its default.</t>
+2. This browser has never saved settings for this report (fresh visit), so every column is at its default.
+3. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
       <c r="F325" s="2" t="inlineStr">
@@ -16292,7 +16975,9 @@
 5. The Location column is never listed here — it appears on its own whenever more than one location is in scope.
 6. Turning a toggle off hides that column (header and cells) immediately, with no reload; turning it back on returns it to its usual place in the fixed left-to-right order — the remaining columns never reorder.
 7. Est. Lost Labor can now be hidden like any other column (it used to be always on).
-8. Your column choice is remembered in this browser and is still applied when you come back.</t>
+8. Your column choice is remembered in this browser and is still applied when you come back.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R5, S10-R6, S8-R16).</t>
         </is>
       </c>
       <c r="H325" s="2" t="inlineStr">
@@ -16340,7 +17025,9 @@
         <is>
           <t>1. The report uses an all-white table: white column headers and white data cells, with NO alternating row shading.
 2. The toolbar controls run, left to right: the three-dot download menu, the Column Selection control, the date-range picker, the technician filter, and the Location filter (rightmost).
-3. The expand/collapse-all control is NOT a toolbar control - it lives in the table header (in the Technician column).</t>
+3. The expand/collapse-all control is NOT a toolbar control - it lives in the table header (in the Technician column).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S8-R1, S8-R2, S8-R3).</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -16391,7 +17078,9 @@
           <t>1. The report supports dark mode: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and the "—" glyph are all clearly legible in dark mode.
 2. In BOTH light mode and dark mode the information icon is clearly visible against the background behind it - you can see it at a glance and it does not disappear into the background.
 3. The Total Hours link's non-color affordance and focus indicator apply in both modes.
-4. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes, and only report it if you cannot. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)</t>
+4. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes, and only report it if you cannot. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S8-R9, S8-R13, S8-R14).</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">
@@ -16425,7 +17114,8 @@
       </c>
       <c r="E328" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Technician Utilization report with rows loaded and browser devtools (network tab) open.</t>
+          <t>1. You are on the Technician Utilization report with rows loaded and browser devtools (network tab) open.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F328" s="2" t="inlineStr">
@@ -16439,12 +17129,14 @@
         <is>
           <t>1. The initial report payload does NOT ship the day rows.
 2. Expanding a technician row issues an on-demand backend request that returns that technician's per-day breakdown.
-3. Because expansion state resets (all collapsed) on any data reload, nothing is lost by the lazy loading - re-expanding fetches fresh day data.</t>
+3. Because expansion state resets (all collapsed) on any data reload, nothing is lost by the lazy loading - re-expanding fetches fresh day data.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R2, S4-R5).</t>
         </is>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
-          <t>SV-8651 (specs/technician-utilization.md S4-R2; S4-R5)</t>
+          <t>SV-8651 (TU spec v5 2026-07-29 S4-R2; S4-R5)</t>
         </is>
       </c>
       <c r="I328" s="2" t="inlineStr"/>
@@ -16473,7 +17165,8 @@
       </c>
       <c r="E329" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the Technician Utilization report with rows loaded and browser devtools (network tab) open.</t>
+          <t>1. You are on the Technician Utilization report with rows loaded and browser devtools (network tab) open.
+2. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox.</t>
         </is>
       </c>
       <c r="F329" s="2" t="inlineStr">
@@ -16489,12 +17182,14 @@
           <t>1. A date-range change triggers a fresh server load of the rows.
 2. A location change triggers a fresh server load scoped to the selected set.
 3. The technician filter causes NO server request - it works on screen only (hide/show + Summary recalculation).
-4. Column sorting causes NO server request - it is applied on screen to the loaded rows.</t>
+4. Column sorting causes NO server request - it is applied on screen to the loaded rows.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R5, S9-R3, S2-R13).</t>
         </is>
       </c>
       <c r="H329" s="2" t="inlineStr">
         <is>
-          <t>SV-8648 (specs/technician-utilization.md S1-R5; S9-R3; S5 context note; S2-R13; §3)</t>
+          <t>SV-8648 (TU spec v5 2026-07-29 S1-R5; S9-R3; S5 context note; S2-R13; §3)</t>
         </is>
       </c>
       <c r="I329" s="2" t="inlineStr"/>
@@ -16539,7 +17234,9 @@
         <is>
           <t>1. The reports navigation lists a report labeled "Work In Progress" under the Performance group, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency).
 2. Clicking it opens the Work In Progress report.
-3. The browser page title is exactly "Work In Progress - Report | ShopView" — a plain hyphen with one space on each side.</t>
+3. The browser page title is exactly "Work In Progress - Report | ShopView" — a plain hyphen with one space on each side.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-R1, S1-R5).</t>
         </is>
       </c>
       <c r="H330" s="2" t="inlineStr">
@@ -16588,7 +17285,9 @@
         <is>
           <t>1. Four tabs are shown, labeled in this order: "Approved - Partially Completed", "Approved - Not Started", "Completed", and "Estimates" - each followed by its count in brackets, for example "Completed (30)".
 2. The "Approved - Partially Completed" tab is selected by default on load.
-3. There is NO on-screen status filter — the four tabs take the place of a status filter (the tab a job lands in is derived from its status and whether any work has started).</t>
+3. There is NO on-screen status filter — the four tabs take the place of a status filter (the tab a job lands in is derived from its status and whether any work has started).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-R2, S1-R3).</t>
         </is>
       </c>
       <c r="H331" s="2" t="inlineStr">
@@ -16638,12 +17337,14 @@
         <is>
           <t>1. Each tab's label shows the count of work orders currently in that tab, in parentheses — for example, "Completed (22)".
 2. The count matches the number of work-order rows actually listed in that tab.
-3. A tab with no work orders shows "(0)".</t>
+3. A tab with no work orders shows "(0)".
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-R4, S2-N2).</t>
         </is>
       </c>
       <c r="H332" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (specs/wip-work-in-progress.md Story 1 S1-R4; Story 2 S2-N2 (count portion))</t>
+          <t>SV-8657 (WIP spec v6 2026-07-29 Story 1 S1-R4; Story 2 S2-N2 (count portion))</t>
         </is>
       </c>
       <c r="I332" s="2" t="inlineStr"/>
@@ -16685,12 +17386,14 @@
       <c r="G333" s="2" t="inlineStr">
         <is>
           <t>1. Only the four progress tabs exist — there is no Trend tab and no chart of work-in-progress dollars over time.
-2. No screen in the report reads or displays the nightly snapshot history.</t>
+2. No screen in the report reads or displays the nightly snapshot history.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R7).</t>
         </is>
       </c>
       <c r="H333" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (specs/wip-work-in-progress.md §2 Out of scope; §2 Known Limitations (v1); Story 11 S11-R7)</t>
+          <t>SV-8667 (WIP spec v6 2026-07-29 §2 Out of scope; §2 Known Limitations (v1); Story 11 S11-R7)</t>
         </is>
       </c>
       <c r="I333" s="2" t="inlineStr"/>
@@ -16732,12 +17435,14 @@
       <c r="G334" s="2" t="inlineStr">
         <is>
           <t>1. All five seeded work orders appear in the report — each one qualifies because it is a service work order, its status is one of Estimate, Approved, In Progress, Review, or Complete, and it belongs to a selected location.
-2. Each appears in the tab its status places it in (see the WIP — Tab Placement cases).</t>
+2. Each appears in the tab its status places it in (see the WIP — Tab Placement cases).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-R1).</t>
         </is>
       </c>
       <c r="H334" s="2" t="inlineStr">
         <is>
-          <t>SV-8658 (specs/wip-work-in-progress.md Story 2 S2-R1)</t>
+          <t>SV-8658 (WIP spec v6 2026-07-29 Story 2 S2-R1)</t>
         </is>
       </c>
       <c r="I334" s="2" t="inlineStr"/>
@@ -16782,12 +17487,14 @@
         <is>
           <t>1. The Invoiced and Paid work orders do not appear in any tab, any Totals row, the summary strip, or the download.
 2. The part-sale work order does not appear anywhere either.
-3. No excluded work order's money is counted in any figure.</t>
+3. No excluded work order's money is counted in any figure.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-R2, S2-R3).</t>
         </is>
       </c>
       <c r="H335" s="2" t="inlineStr">
         <is>
-          <t>SV-8658 (specs/wip-work-in-progress.md Story 2 S2-R2; S2-R3)</t>
+          <t>SV-8658 (WIP spec v6 2026-07-29 Story 2 S2-R2; S2-R3)</t>
         </is>
       </c>
       <c r="I335" s="2" t="inlineStr"/>
@@ -16830,12 +17537,14 @@
       <c r="G336" s="2" t="inlineStr">
         <is>
           <t>1. Each qualifying work order appears exactly once, in exactly one tab.
-2. The work order with nothing approved yet still appears (in the Estimates tab), with its earned and remaining both showing "$0.00".</t>
+2. The work order with nothing approved yet still appears (in the Estimates tab), with its earned and remaining both showing "$0.00".
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-R4).</t>
         </is>
       </c>
       <c r="H336" s="2" t="inlineStr">
         <is>
-          <t>SV-8658 (specs/wip-work-in-progress.md Story 2 S2-R4; §3 Key Decisions (every open job is listed))</t>
+          <t>SV-8658 (WIP spec v6 2026-07-29 Story 2 S2-R4; §3 Key Decisions (every open job is listed))</t>
         </is>
       </c>
       <c r="I336" s="2" t="inlineStr"/>
@@ -16878,12 +17587,14 @@
         <is>
           <t>1. While the report is loading, the data area shows the standard reports loading indicator.
 2. The existing rows are replaced only when the new data returns (the table does not go blank and stay blank mid-load).
-3. Both a date-range change and a location change reload the report's rows.</t>
+3. Both a date-range change and a location change reload the report's rows.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-R5, S2-R6).</t>
         </is>
       </c>
       <c r="H337" s="2" t="inlineStr">
         <is>
-          <t>SV-8658 (specs/wip-work-in-progress.md Story 2 S2-R5; S2-R6)</t>
+          <t>SV-8658 (WIP spec v6 2026-07-29 Story 2 S2-R5; S2-R6)</t>
         </is>
       </c>
       <c r="I337" s="2" t="inlineStr"/>
@@ -16929,7 +17640,9 @@
           <t>1. Each tab shows the standard reports no-data message "Empty bays, endless possibilities. Get Going!" in place of rows.
 2. No tab shows a Totals row.
 3. Every tab label count reads "(0)".
-4. When only one tab is empty, that tab shows the no-data message, no Totals row, and a "(0)" count while the populated tabs still show their rows normally.</t>
+4. When only one tab is empty, that tab shows the no-data message, no Totals row, and a "(0)" count while the populated tabs still show their rows normally.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-N1, S2-N2, S6-N1).</t>
         </is>
       </c>
       <c r="H338" s="2" t="inlineStr">
@@ -16977,12 +17690,14 @@
         <is>
           <t>1. The Estimate work order appears in the "Estimates" tab and nowhere else.
 2. The Complete work order appears in the "Completed" tab and nowhere else.
-3. The In Progress and Review work orders appear in the "Approved - partially completed" tab and nowhere else.</t>
+3. The In Progress and Review work orders appear in the "Approved - partially completed" tab and nowhere else.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S3-R1, S3-R2, S3-R3).</t>
         </is>
       </c>
       <c r="H339" s="2" t="inlineStr">
         <is>
-          <t>SV-8659 (specs/wip-work-in-progress.md Story 3 S3-R1; S3-R2; S3-R3)</t>
+          <t>SV-8659 (WIP spec v6 2026-07-29 Story 3 S3-R1; S3-R2; S3-R3)</t>
         </is>
       </c>
       <c r="I339" s="2" t="inlineStr"/>
@@ -17025,12 +17740,14 @@
         <is>
           <t>1. The Approved work order with clocked labor time appears in the "Approved - partially completed" tab.
 2. The Approved work order with a received part (and no clocked time) also appears in the "Approved - partially completed" tab — either kind of started work counts.
-3. The Approved work order with no clocked time and no received part appears in the "Approved - not started" tab and nowhere else.</t>
+3. The Approved work order with no clocked time and no received part appears in the "Approved - not started" tab and nowhere else.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S3-R4).</t>
         </is>
       </c>
       <c r="H340" s="2" t="inlineStr">
         <is>
-          <t>SV-8659 (specs/wip-work-in-progress.md Story 3 S3-R4 (started + not-started branches + context note))</t>
+          <t>SV-8659 (WIP spec v6 2026-07-29 Story 3 S3-R4 (started + not-started branches + context note))</t>
         </is>
       </c>
       <c r="I340" s="2" t="inlineStr"/>
@@ -17075,7 +17792,9 @@
         <is>
           <t>1. The columns appear in this order: WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total.
 2. WO #, Status, Customer, Asset, VIN, Location, and Advisor are left-aligned.
-3. Every other column (Days Open, Last Activity, and all money/number columns through Total) is right-aligned.</t>
+3. Every other column (Days Open, Last Activity, and all money/number columns through Total) is right-aligned.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R1, S4-R3, S4-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
       <c r="H341" s="2" t="inlineStr">
@@ -17124,7 +17843,9 @@
           <t>1. The visible columns on first visit are: WO #, Status, Customer, Asset, Advisor, Days Open, Earned, Remaining, and Total.
 2. Every other column (VIN, Location, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Inv. Hrs) is available in the column-selection control and off by default.
 3. Location IS offered in the column-selection control, between VIN and Advisor, and is off by default. Turning it on adds a Location column that names each job's location; turning it off removes it again.
-4. Note for the tester: the Location column does NOT appear on its own when you have more than one location selected - you have to switch it on yourself. That is what the build does today.</t>
+4. Note for the tester: the Location column does NOT appear on its own when you have more than one location selected - you have to switch it on yourself. That is what the build does today.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R2, S4-R3, S8-R3, S8-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
       <c r="H342" s="2" t="inlineStr">
@@ -17173,12 +17894,14 @@
         <is>
           <t>1. The WO # is shown as a link.
 2. Clicking it opens that work order in the SAME browser tab (not a new tab).
-3. The browser's back navigation returns you to the report.</t>
+3. The browser's back navigation returns you to the report.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R5).</t>
         </is>
       </c>
       <c r="H343" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R5 (+ context note))</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R5 (+ context note))</t>
         </is>
       </c>
       <c r="I343" s="2" t="inlineStr"/>
@@ -17221,7 +17944,9 @@
         <is>
           <t>1. Status is shown as a badge using the status's label: "Estimate", "Approved", "In progress", "Review", or "Complete".
 2. The badge is color-coded per the application's standard status colors.
-3. The label text is always present, so color is never the sole signal of the status.</t>
+3. The label text is always present, so color is never the sole signal of the status.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R6, S10-R8).</t>
         </is>
       </c>
       <c r="H344" s="2" t="inlineStr">
@@ -17272,7 +17997,9 @@
 2. When the asset has no VIN, the cell shows its Unit # instead; when it has no VIN or Unit #, it shows its plate instead.
 3. Note what the cell's second line shows now that the VIN is the main identifier (the older layout put the VIN on a muted second line) - the exact rendering is confirmed in the build; record what you see.
 4. The VIN column (off by default) shows the VIN on its own line as a separate, sortable column.
-5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.</t>
+5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R7, S4-R8, S4-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H345" s="2" t="inlineStr">
@@ -17319,12 +18046,14 @@
       <c r="G346" s="2" t="inlineStr">
         <is>
           <t>1. The Customer column shows the customer's company name.
-2. The cell is blank when no customer name exists.</t>
+2. The cell is blank when no customer name exists.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R11).</t>
         </is>
       </c>
       <c r="H346" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R11)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R11)</t>
         </is>
       </c>
       <c r="I346" s="2" t="inlineStr"/>
@@ -17368,12 +18097,14 @@
         <is>
           <t>1. Days Open is the whole number of days since the work order was created — elapsed time divided by 24 hours, floored, never negative — rendered as "X days".
 2. A same-day work order shows "0 days" and a one-day-old work order shows "1 days".
-3. The value is NOT grammatically pluralized: "1 days" (not "1 day") is the correct, expected rendering.</t>
+3. The value is NOT grammatically pluralized: "1 days" (not "1 day") is the correct, expected rendering.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R12).</t>
         </is>
       </c>
       <c r="H347" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R12; §2 Known Limitations (v1))</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R12; §2 Known Limitations (v1))</t>
         </is>
       </c>
       <c r="I347" s="2" t="inlineStr"/>
@@ -17418,12 +18149,14 @@
         <is>
           <t>1. A work order whose most recent activity was today shows "Today".
 2. Otherwise it shows "Xd ago" (for example "3d ago").
-3. A work order with no recorded activity shows "—".</t>
+3. A work order with no recorded activity shows "—".
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R13).</t>
         </is>
       </c>
       <c r="H348" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R13)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R13)</t>
         </is>
       </c>
       <c r="I348" s="2" t="inlineStr"/>
@@ -17468,12 +18201,14 @@
         <is>
           <t>1. Money values show a leading "$", two decimal places, and thousands separators — for example "$1,234.56".
 2. A negative value shows a leading minus before the "$" — for example "-$1,234.56".
-3. A genuine zero shows "$0.00".</t>
+3. A genuine zero shows "$0.00".
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R14).</t>
         </is>
       </c>
       <c r="H349" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R14)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R14)</t>
         </is>
       </c>
       <c r="I349" s="2" t="inlineStr"/>
@@ -17519,12 +18254,14 @@
         <is>
           <t>1. Labor Earned equals the share of the approved line's quoted labor value covered by the time clocked to it (in the example, $100.00).
 2. For the over-clocked line, Labor Earned never exceeds the full quoted value of that line ($400.00 in the example) — the earned share is capped at the quote per line.
-3. With several approved labor lines, Labor Earned is the sum of each line's capped earned share.</t>
+3. With several approved labor lines, Labor Earned is the sum of each line's capped earned share.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R15).</t>
         </is>
       </c>
       <c r="H350" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R15; §4 Terminology (Earned))</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R15; §4 Terminology (Earned))</t>
         </is>
       </c>
       <c r="I350" s="2" t="inlineStr"/>
@@ -17568,12 +18305,14 @@
       <c r="G351" s="2" t="inlineStr">
         <is>
           <t>1. Labor Remaining equals the total quoted value of the approved labor minus Labor Earned (in the example, $400.00 − $100.00 = $300.00).
-2. Labor Earned + Labor Remaining always equals the total quoted value of the approved labor.</t>
+2. Labor Earned + Labor Remaining always equals the total quoted value of the approved labor.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R16).</t>
         </is>
       </c>
       <c r="H351" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R16)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R16)</t>
         </is>
       </c>
       <c r="I351" s="2" t="inlineStr"/>
@@ -17617,12 +18356,14 @@
       <c r="G352" s="2" t="inlineStr">
         <is>
           <t>1. Parts Earned equals the sell value of the approved-line parts already received (in the example, $100.00).
-2. Parts not yet received contribute nothing to Parts Earned.</t>
+2. Parts not yet received contribute nothing to Parts Earned.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R17).</t>
         </is>
       </c>
       <c r="H352" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R17)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R17)</t>
         </is>
       </c>
       <c r="I352" s="2" t="inlineStr"/>
@@ -17667,12 +18408,14 @@
       <c r="G353" s="2" t="inlineStr">
         <is>
           <t>1. Parts Remaining equals the sell value of approved-line parts ordered but not yet received (in the example, $100.00).
-2. For the core-charge part, Parts Remaining values the outstanding quantity at its sell price INCLUDING the core charge.</t>
+2. For the core-charge part, Parts Remaining values the outstanding quantity at its sell price INCLUDING the core charge.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R18).</t>
         </is>
       </c>
       <c r="H353" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R18)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R18)</t>
         </is>
       </c>
       <c r="I353" s="2" t="inlineStr"/>
@@ -17720,12 +18463,14 @@
           <t>1. Earned equals Labor Earned plus Parts Earned.
 2. Remaining equals Labor Remaining plus Parts Remaining.
 3. Total equals Earned plus Remaining.
-4. The Total is NOT the work order's stored grand total — it excludes tax, fees, discounts, and non-approved lines, so a difference from the work order's own grand total is EXPECTED, not a data error.</t>
+4. The Total is NOT the work order's stored grand total — it excludes tax, fees, discounts, and non-approved lines, so a difference from the work order's own grand total is EXPECTED, not a data error.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R19, S4-R20, S4-R21).</t>
         </is>
       </c>
       <c r="H354" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R19; S4-R20; S4-R21; §3 Key Decisions)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R19; S4-R20; S4-R21; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I354" s="2" t="inlineStr"/>
@@ -17768,7 +18513,9 @@
       <c r="G355" s="2" t="inlineStr">
         <is>
           <t>1. The work order's Labor/Parts Earned, Labor/Parts Remaining, Earned, Remaining, and Total are unchanged.
-2. Only approved lines (line status authorized or complete) contribute to the report's money — not-yet-approved lines contribute nothing.</t>
+2. Only approved lines (line status authorized or complete) contribute to the report's money — not-yet-approved lines contribute nothing.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R15).</t>
         </is>
       </c>
       <c r="H355" s="2" t="inlineStr">
@@ -17818,12 +18565,14 @@
         <is>
           <t>1. Inv. Hrs shows the quoted labor hours minus the worked (clocked) labor hours across the approved lines, as a signed number with one decimal place — for example "+2.0" or "-14.0".
 2. On screen it is colored green when positive and red when negative; the overrun job shows a negative red value, the under-estimate job a positive green value.
-3. A value of exactly zero shows unsigned as "0.0" (never "+0.0" or blank) in the default text color.</t>
+3. A value of exactly zero shows unsigned as "0.0" (never "+0.0" or blank) in the default text color.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R23, S4-R24, S4-E2).</t>
         </is>
       </c>
       <c r="H356" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R23; S4-R24; S4-E2)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R23; S4-R24; S4-E2)</t>
         </is>
       </c>
       <c r="I356" s="2" t="inlineStr"/>
@@ -17866,12 +18615,14 @@
       <c r="G357" s="2" t="inlineStr">
         <is>
           <t>1. Every money column — Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, and Total — shows "$0.00".
-2. The row still appears in the Estimates tab (it is not hidden for having no value).</t>
+2. The row still appears in the Estimates tab (it is not hidden for having no value).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-E1, S2-R4).</t>
         </is>
       </c>
       <c r="H357" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-E1; Story 2 S2-R4)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-E1; Story 2 S2-R4)</t>
         </is>
       </c>
       <c r="I357" s="2" t="inlineStr"/>
@@ -17917,12 +18668,14 @@
         <is>
           <t>1. The running (not-yet-clocked-out) time counts toward Labor Earned — the line's earned share reflects the time clocked up to now, not only closed clock records.
 2. After more time accrues, a refresh shows a larger earned share for that line.
-3. Labor Earned never exceeds the line's full quoted value, no matter how long the clock keeps running — the per-line cap still applies.</t>
+3. Labor Earned never exceeds the line's full quoted value, no matter how long the clock keeps running — the per-line cap still applies.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R15).</t>
         </is>
       </c>
       <c r="H358" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R15; §4 Terminology (Earned) — spec silent on running clocks; tech-plan-2026-07-29 B1.2 open-clock policy)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R15; §4 Terminology (Earned) — spec silent on running clocks; tech-plan-2026-07-29 B1.2 open-clock policy)</t>
         </is>
       </c>
       <c r="I358" s="2" t="inlineStr"/>
@@ -17963,12 +18716,14 @@
       </c>
       <c r="G359" s="2" t="inlineStr">
         <is>
-          <t>1. The rows are sorted by Days Open, longest-open first (descending).</t>
+          <t>1. The rows are sorted by Days Open, longest-open first (descending).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R25).</t>
         </is>
       </c>
       <c r="H359" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R25)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R25)</t>
         </is>
       </c>
       <c r="I359" s="2" t="inlineStr"/>
@@ -18014,12 +18769,14 @@
           <t>1. The first click sorts the column ascending.
 2. The second click toggles it to descending.
 3. The third click returns to ascending — there is no third "cleared" state.
-4. Only one column sorts at a time: clicking another header replaces the previous sort.</t>
+4. Only one column sorts at a time: clicking another header replaces the previous sort.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R26).</t>
         </is>
       </c>
       <c r="H360" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R26)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R26)</t>
         </is>
       </c>
       <c r="I360" s="2" t="inlineStr"/>
@@ -18067,7 +18824,9 @@
 2. Days Open sorts by its day count.
 3. Status sorts by its displayed label.
 4. The Asset column sorts by the identifier it shows - the VIN, falling back to Unit #, then plate.
-5. WO #, Customer, Asset, VIN, Location, and Advisor sort as text.</t>
+5. WO #, Customer, Asset, VIN, Location, and Advisor sort as text.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R27, S4-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H361" s="2" t="inlineStr">
@@ -18116,12 +18875,14 @@
         <is>
           <t>1. Sorting reorders the rows within the active tab only.
 2. The Totals row stays pinned at the bottom, out of the sort.
-3. The other tab's order is not changed by the first tab's sort action.</t>
+3. The other tab's order is not changed by the first tab's sort action.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R28).</t>
         </is>
       </c>
       <c r="H362" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R28)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R28)</t>
         </is>
       </c>
       <c r="I362" s="2" t="inlineStr"/>
@@ -18163,7 +18924,9 @@
       <c r="G363" s="2" t="inlineStr">
         <is>
           <t>1. The strip shows seven figures, in this order: Total Earned, Total Remaining, Not Started, Started — Earned, Started — Remaining, Ready to Invoice, and Estimates.
-2. Every figure shows US-dollar currency with a leading "$", two decimals, and thousands separators.</t>
+2. Every figure shows US-dollar currency with a leading "$", two decimals, and thousands separators.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R1, S5-R10).</t>
         </is>
       </c>
       <c r="H363" s="2" t="inlineStr">
@@ -18211,12 +18974,14 @@
       <c r="G364" s="2" t="inlineStr">
         <is>
           <t>1. Total Earned is shown larger than the other figures and with a colored underline — it is the strip's hero figure.
-2. Total Earned equals Started — Earned plus Ready to Invoice, to the cent.</t>
+2. Total Earned equals Started — Earned plus Ready to Invoice, to the cent.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R2).</t>
         </is>
       </c>
       <c r="H364" s="2" t="inlineStr">
         <is>
-          <t>SV-8661 (specs/wip-work-in-progress.md Story 5 S5-R2)</t>
+          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R2)</t>
         </is>
       </c>
       <c r="I364" s="2" t="inlineStr"/>
@@ -18257,12 +19022,14 @@
       </c>
       <c r="G365" s="2" t="inlineStr">
         <is>
-          <t>1. Total Remaining equals Not Started plus Started — Remaining, to the cent.</t>
+          <t>1. Total Remaining equals Not Started plus Started — Remaining, to the cent.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R3).</t>
         </is>
       </c>
       <c r="H365" s="2" t="inlineStr">
         <is>
-          <t>SV-8661 (specs/wip-work-in-progress.md Story 5 S5-R3)</t>
+          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R3)</t>
         </is>
       </c>
       <c r="I365" s="2" t="inlineStr"/>
@@ -18307,12 +19074,14 @@
         <is>
           <t>1. Not Started equals the total approved value (earned + remaining) of the jobs in the "Approved - not started" tab.
 2. Started — Earned equals the total Earned of the jobs in the "Approved - partially completed" tab, and Started — Remaining equals that tab's total Remaining.
-3. Ready to Invoice equals the total Earned of the jobs in the "Completed" tab.</t>
+3. Ready to Invoice equals the total Earned of the jobs in the "Completed" tab.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R4, S5-R5, S5-R6, S5-R7).</t>
         </is>
       </c>
       <c r="H366" s="2" t="inlineStr">
         <is>
-          <t>SV-8661 (specs/wip-work-in-progress.md Story 5 S5-R4; S5-R5; S5-R6; S5-R7)</t>
+          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R4; S5-R5; S5-R6; S5-R7)</t>
         </is>
       </c>
       <c r="I366" s="2" t="inlineStr"/>
@@ -18356,12 +19125,14 @@
         <is>
           <t>1. The Estimates figure equals the total quoted value of the jobs in the Estimates tab.
 2. It is shown in a muted style.
-3. The Estimates figure is excluded from Total Earned and from Total Remaining.</t>
+3. The Estimates figure is excluded from Total Earned and from Total Remaining.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R8, S5-R9).</t>
         </is>
       </c>
       <c r="H367" s="2" t="inlineStr">
         <is>
-          <t>SV-8661 (specs/wip-work-in-progress.md Story 5 S5-R8; S5-R9)</t>
+          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R8; S5-R9)</t>
         </is>
       </c>
       <c r="I367" s="2" t="inlineStr"/>
@@ -18409,12 +19180,14 @@
 5. Started — Remaining — "Jobs in progress: the work still left to finish."
 6. Ready to Invoice — "Finished jobs, ready to bill the customer."
 7. Estimates — "Quotes the customer has not approved yet — not counted in the totals."
-8. Each explanation appears on hover, on keyboard focus, and on tap.</t>
+8. Each explanation appears on hover, on keyboard focus, and on tap.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R12).</t>
         </is>
       </c>
       <c r="H368" s="2" t="inlineStr">
         <is>
-          <t>SV-8661 (specs/wip-work-in-progress.md Story 5 S5-R12)</t>
+          <t>SV-8661 (WIP spec v6 2026-07-29 Story 5 S5-R12)</t>
         </is>
       </c>
       <c r="I368" s="2" t="inlineStr"/>
@@ -18458,12 +19231,14 @@
         <is>
           <t>1. Each tab's table has a Totals row pinned to the bottom, labeled "Totals" in its leftmost cell.
 2. The Totals row's Total cell is pinned far right and shown in bold, matching the column.
-3. The Totals row uses the same number formats as the data rows.</t>
+3. The Totals row uses the same number formats as the data rows.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S6-R1, S6-R4, S6-R5).</t>
         </is>
       </c>
       <c r="H369" s="2" t="inlineStr">
         <is>
-          <t>SV-8662 (specs/wip-work-in-progress.md Story 6 S6-R1; S6-R4; S6-R5)</t>
+          <t>SV-8662 (WIP spec v6 2026-07-29 Story 6 S6-R1; S6-R4; S6-R5)</t>
         </is>
       </c>
       <c r="I369" s="2" t="inlineStr"/>
@@ -18509,12 +19284,14 @@
           <t>1. The Totals row sums each visible money column across the tab's visible jobs, to the cent.
 2. The Totals row's Inv. Hrs shows the sum of the visible jobs' Inv. Hrs, in the same signed one-decimal format ("+2.0" / "-14.0" / "0.0").
 3. The Inv. Hrs total uses the same green (positive) / red (negative) / default (exactly 0.0) coloring as a data row.
-4. Note for the tester: the Inv. Hrs total can only be checked on screen. On this build a download that includes Inv. Hrs is refused, so do not try to verify this column from a file.</t>
+4. Note for the tester: the Inv. Hrs total can only be checked on screen. On this build a download that includes Inv. Hrs is refused, so do not try to verify this column from a file.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S6-R2, S6-R3).</t>
         </is>
       </c>
       <c r="H370" s="2" t="inlineStr">
         <is>
-          <t>SV-8662 (specs/wip-work-in-progress.md Story 6 S6-R2; S6-R3)</t>
+          <t>SV-8662 (WIP spec v6 2026-07-29 Story 6 S6-R2; S6-R3)</t>
         </is>
       </c>
       <c r="I370" s="2" t="inlineStr"/>
@@ -18558,12 +19335,14 @@
         <is>
           <t>1. The Advisor filter is a multi-select listing the advisors present in the loaded jobs.
 2. Selecting one or more advisors narrows the visible jobs to those advisors instantly, on screen only — no reload and no loading indicator.
-3. With two advisors selected, jobs for either advisor are shown.</t>
+3. With two advisors selected, jobs for either advisor are shown.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R1).</t>
         </is>
       </c>
       <c r="H371" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R1)</t>
+          <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R1)</t>
         </is>
       </c>
       <c r="I371" s="2" t="inlineStr"/>
@@ -18609,12 +19388,14 @@
           <t>1. With no customer selected, the filter reads "All customers", every job is shown, and no Clear action is offered.
 2. Typing narrows the option list (type-ahead); the options are the customers present in the loaded jobs.
 3. Selecting customers narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one customer is selected.
-4. Clear returns the filter to "All customers" and every job is shown again.</t>
+4. Clear returns the filter to "All customers" and every job is shown again.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R2, S7-R3).</t>
         </is>
       </c>
       <c r="H372" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R2; S7-R3)</t>
+          <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R2; S7-R3)</t>
         </is>
       </c>
       <c r="I372" s="2" t="inlineStr"/>
@@ -18661,7 +19442,9 @@
 2. Each option identifies the asset by its VIN, falling back to Unit #, then plate (the exact option text is confirmed in the build).
 3. The typed text matches against the asset's identifier - the VIN, and the Unit # where the asset has one (the exact fields matched are confirmed in the build).
 4. Selecting assets narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one asset is selected and returns the filter to "All assets".
-5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.</t>
+5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R4, S7-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H373" s="2" t="inlineStr">
@@ -18708,12 +19491,14 @@
         <is>
           <t>1. On a fresh visit the date range defaults to "This Week".
 2. The options offered are: "Today", "Yesterday", "This Week", "Last Week", "This Month", "Last Month", "This Year", "Last Year", "This Quarter", "Last Quarter", and "Custom".
-3. "All Time" is NOT offered.</t>
+3. "All Time" is NOT offered.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R6).</t>
         </is>
       </c>
       <c r="H374" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R6; §3 Key Decisions (date range defaults to This Week))</t>
+          <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R6; §3 Key Decisions (date range defaults to This Week))</t>
         </is>
       </c>
       <c r="I374" s="2" t="inlineStr"/>
@@ -18758,12 +19543,14 @@
           <t>1. Each preset (or Custom) filters the report to work orders whose CREATED date falls within the selected range — an open work order created outside the range is not listed.
 2. Changing the range reloads the report (the loading indicator shows).
 3. A range longer than about a year is refused with the message "Date range cannot be over one year." and the wider range is not loaded.
-4. Note for the tester: on this build the exact cut-off sits one day later than the specification says (a 367-day span is accepted, 368 is refused). Record what you see; the one-day difference is already known and is with the product owner.</t>
+4. Note for the tester: on this build the exact cut-off sits one day later than the specification says (a 367-day span is accepted, 368 is refused). Record what you see; the one-day difference is already known and is with the product owner.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R7, S7-R8).</t>
         </is>
       </c>
       <c r="H375" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R7; S7-R8)</t>
+          <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R7; S7-R8)</t>
         </is>
       </c>
       <c r="I375" s="2" t="inlineStr"/>
@@ -18812,7 +19599,9 @@
 2. On a first visit it defaults to the user's currently active location.
 3. Selecting one, several, or all locations reloads the report scoped to that set (rows from the added location appear).
 4. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
-5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's work orders.</t>
+5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's work orders.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R9, S7-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H376" s="2" t="inlineStr">
@@ -18861,12 +19650,14 @@
         <is>
           <t>1. Only the locations the user can access are offered — a location the user cannot access is never included in the scope.
 2. If the selection resolves to none, the report falls back to the user's currently active location rather than showing everything or erroring.
-3. A saved selection that no longer resolves also falls back to the active location.</t>
+3. A saved selection that no longer resolves also falls back to the active location.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R11, S8-R8).</t>
         </is>
       </c>
       <c r="H377" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R11; Story 8 S8-R8)</t>
+          <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R11; Story 8 S8-R8)</t>
         </is>
       </c>
       <c r="I377" s="2" t="inlineStr"/>
@@ -18910,12 +19701,14 @@
         <is>
           <t>1. A job must pass all three filters to remain visible (the filters combine with AND).
 2. The summary strip and each tab's Totals row recompute immediately from the still-visible jobs after every advisor, customer, or asset change — on screen, with no page reload.
-3. When the combination leaves no visible jobs, every tab shows the no-data message "Empty bays, endless possibilities. Get Going!" and no Totals row.</t>
+3. When the combination leaves no visible jobs, every tab shows the no-data message "Empty bays, endless possibilities. Get Going!" and no Totals row.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R12, S7-N1, S5-R11, S6-R6).</t>
         </is>
       </c>
       <c r="H378" s="2" t="inlineStr">
         <is>
-          <t>SV-8663 (specs/wip-work-in-progress.md Story 7 S7-R12; S7-N1; Story 5 S5-R11; Story 6 S6-R6; §3 Key Decisions)</t>
+          <t>SV-8663 (WIP spec v6 2026-07-29 Story 7 S7-R12; S7-N1; Story 5 S5-R11; Story 6 S6-R6; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I378" s="2" t="inlineStr"/>
@@ -18968,7 +19761,9 @@
 4. The column does not appear or disappear on its own when you change the location selection - it follows the column-selection toggle only.
 5. With the toggle off the Location column is not shown, whatever the location selection is.
 6. In both downloads the column is headed "Branch" (a known naming difference from the screen — do not raise it as a bug).
-7. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.</t>
+7. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
       <c r="H379" s="2" t="inlineStr">
@@ -19017,12 +19812,14 @@
         <is>
           <t>1. The icon button's tooltip reads "Column Selection".
 2. Toggling a column off hides it from the table; toggling it on shows it again.
-3. The Total column is always shown and cannot be turned off — it is not offered in the control at all.</t>
+3. The Total column is always shown and cannot be turned off — it is not offered in the control at all.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S8-R1, S8-R2).</t>
         </is>
       </c>
       <c r="H380" s="2" t="inlineStr">
         <is>
-          <t>SV-8664 (specs/wip-work-in-progress.md Story 8 S8-R1; S8-R2)</t>
+          <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R1; S8-R2)</t>
         </is>
       </c>
       <c r="I380" s="2" t="inlineStr"/>
@@ -19066,12 +19863,14 @@
         <is>
           <t>1. Whatever columns are shown, they always appear in the fixed left-to-right order (WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total) — the order you toggled them in never changes their position.
 2. Total is always the last column.
-3. The column selection applies to every tab at once — all four tabs show the same set of columns.</t>
+3. The column selection applies to every tab at once — all four tabs show the same set of columns.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S8-R5, S8-R6, S4-R1).</t>
         </is>
       </c>
       <c r="H381" s="2" t="inlineStr">
         <is>
-          <t>SV-8664 (specs/wip-work-in-progress.md Story 8 S8-R5; S8-R6; Story 4 S4-R1)</t>
+          <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R5; S8-R6; Story 4 S4-R1)</t>
         </is>
       </c>
       <c r="I381" s="2" t="inlineStr"/>
@@ -19115,12 +19914,14 @@
       <c r="G382" s="2" t="inlineStr">
         <is>
           <t>1. On return and after a reload, the report restores the saved date range, advisor selection, customer selection, asset selection, location selection, column selection, and active tab.
-2. In a different browser the report shows the defaults instead — the settings are saved per browser, not on the user's account.</t>
+2. In a different browser the report shows the defaults instead — the settings are saved per browser, not on the user's account.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S8-R7).</t>
         </is>
       </c>
       <c r="H382" s="2" t="inlineStr">
         <is>
-          <t>SV-8664 (specs/wip-work-in-progress.md Story 8 S8-R7; §3 Key Decisions (context note: per-browser persistence))</t>
+          <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R7; §3 Key Decisions (context note: per-browser persistence))</t>
         </is>
       </c>
       <c r="I382" s="2" t="inlineStr"/>
@@ -19162,12 +19963,14 @@
       <c r="G383" s="2" t="inlineStr">
         <is>
           <t>1. The report loads normally — the invalid saved value falls back to that setting's default rather than breaking the view.
-2. All other saved settings are still restored.</t>
+2. All other saved settings are still restored.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S8-R8).</t>
         </is>
       </c>
       <c r="H383" s="2" t="inlineStr">
         <is>
-          <t>SV-8664 (specs/wip-work-in-progress.md Story 8 S8-R8)</t>
+          <t>SV-8664 (WIP spec v6 2026-07-29 Story 8 S8-R8)</t>
         </is>
       </c>
       <c r="I383" s="2" t="inlineStr"/>
@@ -19210,12 +20013,14 @@
       <c r="G384" s="2" t="inlineStr">
         <is>
           <t>1. The menu holds the download options "Download (PDF)" and "Download (CSV)".
-2. Each option downloads a file of the current tab in the chosen format.</t>
+2. Each option downloads a file of the current tab in the chosen format.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R1).</t>
         </is>
       </c>
       <c r="H384" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R1)</t>
+          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R1)</t>
         </is>
       </c>
       <c r="I384" s="2" t="inlineStr"/>
@@ -19263,7 +20068,9 @@
 2. Both downloads honor the current date range and location filter, and include only the jobs left visible by the advisor, customer, and asset filters.
 3. Both downloads include a Totals row matching the on-screen Totals row for the tab.
 4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
-5. Note for the tester: the file carries the location column only when you have switched Location ON in the column-selection control - it does not appear just because you have more than one location selected. In the file it is headed "Branch", not "Location", and the asset column is headed "Unit". Both of those names are correct.</t>
+5. Note for the tester: the file carries the location column only when you have switched Location ON in the column-selection control - it does not appear just because you have more than one location selected. In the file it is headed "Branch", not "Location", and the asset column is headed "Unit". Both of those names are correct.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R2, S9-R3, S9-R4, S9-R10a, S7-R13, S9-E1).</t>
         </is>
       </c>
       <c r="H385" s="2" t="inlineStr">
@@ -19314,12 +20121,14 @@
         <is>
           <t>1. Money values use the same "$1,234.56" / "-$1,234.56" format as on screen; Inv. Hrs uses the same signed one-decimal format.
 2. In the CSV, a money value containing a comma (a thousands separator) is enclosed in double-quotes per standard CSV rules.
-3. A value without a comma is written unquoted.</t>
+3. A value without a comma is written unquoted.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R5, S9-R6).</t>
         </is>
       </c>
       <c r="H386" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R5; S9-R6)</t>
+          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R5; S9-R6)</t>
         </is>
       </c>
       <c r="I386" s="2" t="inlineStr"/>
@@ -19361,12 +20170,14 @@
       <c r="G387" s="2" t="inlineStr">
         <is>
           <t>1. In the PDF, Inv. Hrs keeps the green (positive) / red (negative) coloring.
-2. In the CSV, the Inv. Hrs column is monochrome — plain signed numbers with no color or markup.</t>
+2. In the CSV, the Inv. Hrs column is monochrome — plain signed numbers with no color or markup.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R7).</t>
         </is>
       </c>
       <c r="H387" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R7)</t>
+          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R7)</t>
         </is>
       </c>
       <c r="I387" s="2" t="inlineStr"/>
@@ -19409,12 +20220,14 @@
       <c r="G388" s="2" t="inlineStr">
         <is>
           <t>1. In the download, Days Open is the whole number of days as of the moment the file is generated.
-2. Because the screen computes Days Open live while the file freezes it at generation time, the file can legitimately show a day count one higher than the screen it was generated from — that difference is EXPECTED, not a defect.</t>
+2. Because the screen computes Days Open live while the file freezes it at generation time, the file can legitimately show a day count one higher than the screen it was generated from — that difference is EXPECTED, not a defect.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R8).</t>
         </is>
       </c>
       <c r="H388" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R8; Story 4 context note (Days Open live vs frozen))</t>
+          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R8; Story 4 context note (Days Open live vs frozen))</t>
         </is>
       </c>
       <c r="I388" s="2" t="inlineStr"/>
@@ -19457,7 +20270,9 @@
         <is>
           <t>1. The PDF is named "wip-2-report.pdf".
 2. The CSV is named "wip-2-report.csv".
-3. These exact names (including the "-2-") are the specified current behavior.</t>
+3. These exact names (including the "-2-") are the specified current behavior.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R9).</t>
         </is>
       </c>
       <c r="H389" s="2" t="inlineStr">
@@ -19507,7 +20322,9 @@
           <t>1. On screen the headers read "Asset" and "Location".
 2. In BOTH the PDF and the CSV, the same two columns are headed "Unit" and "Branch".
 3. This on-screen-vs-export label difference is the EXPECTED, documented v1 behavior.
-4. Note: the on-screen Asset cell now identifies the asset by its VIN (falling back to Unit #, then plate); whether the export header text changes from "Unit" is confirmed in the build - record what it shows, do not file a bug either way.</t>
+4. Note: the on-screen Asset cell now identifies the asset by its VIN (falling back to Unit #, then plate); whether the export header text changes from "Unit" is confirmed in the build - record what it shows, do not file a bug either way.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H390" s="2" t="inlineStr">
@@ -19554,12 +20371,14 @@
       <c r="G391" s="2" t="inlineStr">
         <is>
           <t>1. The PDF shows the shop logo at the top.
-2. The CSV never includes a logo (plain data only).</t>
+2. The CSV never includes a logo (plain data only).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R10).</t>
         </is>
       </c>
       <c r="H391" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R10)</t>
+          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R10)</t>
         </is>
       </c>
       <c r="I391" s="2" t="inlineStr"/>
@@ -19589,7 +20408,8 @@
       <c r="E392" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The report can be put in three states: rows present, no rows visible (filters leave nothing), and (if simulatable) a failing download, for example by disconnecting the network before the download.</t>
+2. The report can be put in three states: rows present, no rows visible (filters leave nothing), and (if simulatable) a failing download, for example by disconnecting the network before the download.
+3. To force the failure this test needs, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Offline" to cut the connection, or to "Slow 3G" to slow it down. There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
       <c r="F392" s="2" t="inlineStr">
@@ -19603,12 +20423,14 @@
         <is>
           <t>1. On a successful download, a success notification shows with the caption "Data exported successfully."
 2. When a download yields no rows, a warning notification shows titled "Empty export" with the caption "Export didn't yield any results".
-3. When a download fails, an error notification shows: "An error occurred while exporting the report. Please try again."</t>
+3. When a download fails, an error notification shows: "An error occurred while exporting the report. Please try again."
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R11, S9-R12, S9-R13).</t>
         </is>
       </c>
       <c r="H392" s="2" t="inlineStr">
         <is>
-          <t>SV-8665 (specs/wip-work-in-progress.md Story 9 S9-R11; S9-R12; S9-R13; §7 User Feedback Summary)</t>
+          <t>SV-8665 (WIP spec v6 2026-07-29 Story 9 S9-R11; S9-R12; S9-R13; §7 User Feedback Summary)</t>
         </is>
       </c>
       <c r="I392" s="2" t="inlineStr"/>
@@ -19652,7 +20474,9 @@
           <t>1. For both the CSV and the PDF: no file is generated and no download starts.
 2. An error toast is shown each time, reading exactly: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
 3. Below the cap the download works normally.
-4. Note for the tester: on this environment the biggest single tab holds about 114 work orders, so you cannot make this message appear here. Record that and move on.</t>
+4. Note for the tester: on this environment the biggest single tab holds about 114 work orders, so you cannot make this message appear here. Record that and move on.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (Story 9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H393" s="2" t="inlineStr">
@@ -19699,7 +20523,9 @@
       <c r="G394" s="2" t="inlineStr">
         <is>
           <t>1. Each tab uses an all-white table: white column headers and white data cells.
-2. There is no alternating row shading (no zebra striping).</t>
+2. There is no alternating row shading (no zebra striping).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R1).</t>
         </is>
       </c>
       <c r="H394" s="2" t="inlineStr">
@@ -19746,12 +20572,14 @@
       <c r="G395" s="2" t="inlineStr">
         <is>
           <t>1. The summary strip appears above the tabs.
-2. It is shown as a bold band delineated by a top and bottom rule — not as a row of separate cards.</t>
+2. It is shown as a bold band delineated by a top and bottom rule — not as a row of separate cards.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R2).</t>
         </is>
       </c>
       <c r="H395" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (specs/wip-work-in-progress.md Story 10 S10-R2)</t>
+          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R2)</t>
         </is>
       </c>
       <c r="I395" s="2" t="inlineStr"/>
@@ -19793,12 +20621,14 @@
       <c r="G396" s="2" t="inlineStr">
         <is>
           <t>1. The Total column header is bold and pinned to the far right, matching its cells.
-2. The Total column (header and cells, shown in bold) stays fixed to the right edge while the rest of the columns scroll underneath.</t>
+2. The Total column (header and cells, shown in bold) stays fixed to the right edge while the rest of the columns scroll underneath.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R22, S10-R3).</t>
         </is>
       </c>
       <c r="H396" s="2" t="inlineStr">
         <is>
-          <t>SV-8660 (specs/wip-work-in-progress.md Story 4 S4-R22; Story 10 S10-R3)</t>
+          <t>SV-8660 (WIP spec v6 2026-07-29 Story 4 S4-R22; Story 10 S10-R3)</t>
         </is>
       </c>
       <c r="I396" s="2" t="inlineStr"/>
@@ -19840,12 +20670,14 @@
       <c r="G397" s="2" t="inlineStr">
         <is>
           <t>1. The Totals row stays visible at the bottom while the rows scroll.
-2. The report fills the available height and only the active tab's table body scrolls — the page itself does not add a second scrollbar.</t>
+2. The report fills the available height and only the active tab's table body scrolls — the page itself does not add a second scrollbar.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R4, S10-R5).</t>
         </is>
       </c>
       <c r="H397" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (specs/wip-work-in-progress.md Story 10 S10-R4; S10-R5)</t>
+          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R4; S10-R5)</t>
         </is>
       </c>
       <c r="I397" s="2" t="inlineStr"/>
@@ -19889,12 +20721,14 @@
         <is>
           <t>1. The WO # link can receive keyboard focus.
 2. A visible focus indicator shows when it is focused.
-3. Activating it opens the work order (in the same browser tab).</t>
+3. Activating it opens the work order (in the same browser tab).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R6).</t>
         </is>
       </c>
       <c r="H398" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (specs/wip-work-in-progress.md Story 10 S10-R6)</t>
+          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R6)</t>
         </is>
       </c>
       <c r="I398" s="2" t="inlineStr"/>
@@ -19924,7 +20758,7 @@
       <c r="E399" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. The summary strip is visible; a screen reader (or the browser's accessibility inspector) is available.</t>
+2. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
       <c r="F399" s="2" t="inlineStr">
@@ -19938,12 +20772,14 @@
         <is>
           <t>1. Each information icon is reachable by keyboard focus.
 2. Its explanation is revealed on focus, not by hover alone.
-3. The explanation text is exposed to assistive technology.</t>
+3. The explanation text is exposed to assistive technology.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R7, S5-R12).</t>
         </is>
       </c>
       <c r="H399" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (specs/wip-work-in-progress.md Story 10 S10-R7; Story 5 S5-R12)</t>
+          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R7; Story 5 S5-R12)</t>
         </is>
       </c>
       <c r="I399" s="2" t="inlineStr"/>
@@ -19986,12 +20822,14 @@
       <c r="G400" s="2" t="inlineStr">
         <is>
           <t>1. The report supports dark mode.
-2. The table, the summary strip, the WO # link, the Inv. Hrs green/red coloring, and the two-line asset cell all use dark-mode-legible colors meeting contrast.</t>
+2. The table, the summary strip, the WO # link, the Inv. Hrs green/red coloring, and the two-line asset cell all use dark-mode-legible colors meeting contrast.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R9).</t>
         </is>
       </c>
       <c r="H400" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (specs/wip-work-in-progress.md Story 10 S10-R9)</t>
+          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R9)</t>
         </is>
       </c>
       <c r="I400" s="2" t="inlineStr"/>
@@ -20035,7 +20873,9 @@
         <is>
           <t>1. The report is listed and opens normally.
 2. The download works with the same permission — for now the one ordinary reports access covers the report and its downloads and no new permission is added for it.
-3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.</t>
+3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (Story 1 Prerequisites); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H401" s="2" t="inlineStr">
@@ -20081,7 +20921,9 @@
       </c>
       <c r="G402" s="2" t="inlineStr">
         <is>
-          <t>1. The report does not appear in the navigation for this user.</t>
+          <t>1. The report does not appear in the navigation for this user.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-N1).</t>
         </is>
       </c>
       <c r="H402" s="2" t="inlineStr">
@@ -20116,7 +20958,8 @@
       <c r="E403" s="2" t="inlineStr">
         <is>
           <t>1. Open work orders exist across the organization on the capture date.
-2. You can inspect the stored snapshot rows after the nightly capture runs (arrange the verification route with the developers).</t>
+2. You can inspect the stored snapshot rows after the nightly capture runs (arrange the verification route with the developers).
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
       <c r="F403" s="2" t="inlineStr">
@@ -20131,12 +20974,14 @@
         <is>
           <t>1. Once per day the system records one row per then-open work order — one row per work order per calendar date.
 2. The next day's capture adds a new row per open work order under the new date; a work order open on both days has one row for each date, never two rows for the same date.
-3. Re-running the capture for the SAME date replaces that date's rows — the day's existing rows are removed and re-recorded from current data, never duplicated.</t>
+3. Re-running the capture for the SAME date replaces that date's rows — the day's existing rows are removed and re-recorded from current data, never duplicated.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R1).</t>
         </is>
       </c>
       <c r="H403" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (specs/wip-work-in-progress.md Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs))</t>
+          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs))</t>
         </is>
       </c>
       <c r="I403" s="2" t="inlineStr"/>
@@ -20166,7 +21011,8 @@
       <c r="E404" s="2" t="inlineStr">
         <is>
           <t>1. At least one open work order with known status, location, and organization existed when the nightly capture ran.
-2. You can inspect that date's stored snapshot rows.</t>
+2. You can inspect that date's stored snapshot rows.
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
       <c r="F404" s="2" t="inlineStr">
@@ -20177,12 +21023,14 @@
       </c>
       <c r="G404" s="2" t="inlineStr">
         <is>
-          <t>1. The snapshot row captures, at minimum: the work order, its status, its Earned value, its Remaining value, the location and organization (copied from the work order), and the snapshot's calendar date.</t>
+          <t>1. The snapshot row captures, at minimum: the work order, its status, its Earned value, its Remaining value, the location and organization (copied from the work order), and the snapshot's calendar date.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R2).</t>
         </is>
       </c>
       <c r="H404" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (specs/wip-work-in-progress.md Story 11 S11-R2)</t>
+          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R2)</t>
         </is>
       </c>
       <c r="I404" s="2" t="inlineStr"/>
@@ -20212,7 +21060,8 @@
       <c r="E405" s="2" t="inlineStr">
         <is>
           <t>1. An open ZZAUTOTEST work order with known approved labor (partly clocked) and approved parts (partly received) exists and is left UNCHANGED across the capture.
-2. You can read the on-screen report on the capture date and the stored snapshot row afterward.</t>
+2. You can read the on-screen report on the capture date and the stored snapshot row afterward.
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
       <c r="F405" s="2" t="inlineStr">
@@ -20224,12 +21073,14 @@
       </c>
       <c r="G405" s="2" t="inlineStr">
         <is>
-          <t>1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation for both figures, so the two can never diverge for a given work order on the capture date.</t>
+          <t>1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation for both figures, so the two can never diverge for a given work order on the capture date.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R3).</t>
         </is>
       </c>
       <c r="H405" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (specs/wip-work-in-progress.md Story 11 S11-R3)</t>
+          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R3)</t>
         </is>
       </c>
       <c r="I405" s="2" t="inlineStr"/>
@@ -20260,7 +21111,8 @@
         <is>
           <t>1. Open service work orders exist at two or more different locations.
 2. An Invoiced (or Paid/Declined) work order and a part-sale work order also exist.
-3. You can inspect the capture date's snapshot rows.</t>
+3. You can inspect the capture date's snapshot rows.
+4. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
       <c r="F406" s="2" t="inlineStr">
@@ -20274,12 +21126,14 @@
         <is>
           <t>1. The captured set uses the same service-type and open-status conditions as the report (service work orders in Estimate, Approved, In Progress, Review, or Complete).
 2. The capture spans every location — there is no user-selected-location filter.
-3. Invoiced, Paid, and Declined work orders and part-sale work orders are not captured.</t>
+3. Invoiced, Paid, and Declined work orders and part-sale work orders are not captured.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R4, S2-R1).</t>
         </is>
       </c>
       <c r="H406" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (specs/wip-work-in-progress.md Story 11 S11-R4; Story 2 S2-R1 (first two conditions))</t>
+          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R4; Story 2 S2-R1 (first two conditions))</t>
         </is>
       </c>
       <c r="I406" s="2" t="inlineStr"/>
@@ -20309,7 +21163,8 @@
       <c r="E407" s="2" t="inlineStr">
         <is>
           <t>1. An open work order whose Earned/Remaining include non-round cent values (for example $123.45) existed at capture time.
-2. You can inspect the stored snapshot rows.</t>
+2. You can inspect the stored snapshot rows.
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
       <c r="F407" s="2" t="inlineStr">
@@ -20320,12 +21175,14 @@
       </c>
       <c r="G407" s="2" t="inlineStr">
         <is>
-          <t>1. Captured dollar values are stored to the cent — no rounding to whole dollars and no lost cents.</t>
+          <t>1. Captured dollar values are stored to the cent — no rounding to whole dollars and no lost cents.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R5).</t>
         </is>
       </c>
       <c r="H407" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (specs/wip-work-in-progress.md Story 11 S11-R5)</t>
+          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R5)</t>
         </is>
       </c>
       <c r="I407" s="2" t="inlineStr"/>
@@ -20355,7 +21212,8 @@
       <c r="E408" s="2" t="inlineStr">
         <is>
           <t>1. An open ZZAUTOTEST estimate with no approved line items existed at capture time.
-2. You can inspect the capture date's snapshot rows.</t>
+2. You can inspect the capture date's snapshot rows.
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
       <c r="F408" s="2" t="inlineStr">
@@ -20367,12 +21225,14 @@
       <c r="G408" s="2" t="inlineStr">
         <is>
           <t>1. The work order IS captured (not skipped).
-2. Its Earned is $0.00 and its Remaining is $0.00, matching what the report shows on screen for a job with nothing approved.</t>
+2. Its Earned is $0.00 and its Remaining is $0.00, matching what the report shows on screen for a job with nothing approved.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R6, S4-E1).</t>
         </is>
       </c>
       <c r="H408" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (specs/wip-work-in-progress.md Story 11 S11-R6; Story 4 S4-E1)</t>
+          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R6; Story 4 S4-E1)</t>
         </is>
       </c>
       <c r="I408" s="2" t="inlineStr"/>
@@ -20415,7 +21275,9 @@
       <c r="G409" s="2" t="inlineStr">
         <is>
           <t>1. The reports navigation lists a report labeled "Inventory Value" under the Parts group.
-2. Clicking it opens the Inventory Value report.</t>
+2. Clicking it opens the Inventory Value report.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S1-R1).</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
@@ -20463,12 +21325,14 @@
       <c r="G410" s="2" t="inlineStr">
         <is>
           <t>1. The report shows one row for each in-stock part at the selected location(s).
-2. The values are valued as of the resolved date (the current stock for a range reaching today, or the closest recorded nightly snapshot for an earlier date — see the IV — As-of Date &amp; Snapshots cases).</t>
+2. The values are valued as of the resolved date (the current stock for a range reaching today, or the closest recorded nightly snapshot for an earlier date — see the IV — As-of Date &amp; Snapshots cases).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S1-R2, S1-R6).</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
         <is>
-          <t>SV-8668 (specs/inventory-value.md Story 1 S1-R2; S1-R6)</t>
+          <t>SV-8668 (IV spec v3 2026-07-29 Story 1 S1-R2; S1-R6)</t>
         </is>
       </c>
       <c r="I410" s="2" t="inlineStr"/>
@@ -20510,7 +21374,9 @@
       <c r="G411" s="2" t="inlineStr">
         <is>
           <t>1. The date range defaults to the current calendar month.
-2. The location defaults to the user's currently active location.</t>
+2. The location defaults to the user's currently active location.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S1-R3, S7-R2).</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -20558,14 +21424,16 @@
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>1. The server returns one page of rows at a time; the user moves through pages with the reports suite's standard pagination control.
+          <t>1. The server returns one page of rows at a time rather than the whole list at once; further rows keep arriving as you scroll to the bottom.
 2. Changing any server-side filter (Date, Location, Category, Vendor), the part search, or the sort returns the FIRST page of the new result set - the list jumps back to the top.
-3. Note for the tester: on this build there are no numbered page controls on the screen - the rows load as you scroll. That is what you should see; record it and carry on with the checks above.</t>
+3. Note for the tester: on this build there are no numbered page controls on the screen - the rows load as you scroll. That is what you should see; record it and carry on with the checks above.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S1-R8).</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
         <is>
-          <t>SV-8668 (specs/inventory-value.md Story 1 S1-R8; §2 Scale and data model)</t>
+          <t>SV-8668 (IV spec v3 2026-07-29 Story 1 S1-R8; §2 Scale and data model)</t>
         </is>
       </c>
       <c r="I412" s="2" t="inlineStr"/>
@@ -20608,7 +21476,9 @@
       <c r="G413" s="2" t="inlineStr">
         <is>
           <t>1. In every case the report shows the standard reports no-data message "Empty bays, endless possibilities. Get Going!" instead of rows.
-2. No totals row is shown in any of the cases.</t>
+2. No totals row is shown in any of the cases.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S1-N2, S4-N1, S5-N1, S7-N2).</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -20658,12 +21528,14 @@
           <t>1. The normal, positive-quantity, non-core part appears as one row.
 2. The core-charge part is never listed — even with a positive quantity — and its value is not counted in the totals row.
 3. The zero-quantity and negative-quantity parts are not listed — only quantities greater than zero are valued.
-4. Only parts meeting BOTH conditions — not a core charge, and on-hand quantity greater than zero — are listed.</t>
+4. Only parts meeting BOTH conditions — not a core charge, and on-hand quantity greater than zero — are listed.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S2-R1, S2-R2, S2-N1, S2-N2).</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
         <is>
-          <t>SV-8669 (specs/inventory-value.md Story 2 S2-R1; S2-R2; S2-N1; S2-N2; §3 Key Decisions)</t>
+          <t>SV-8669 (IV spec v3 2026-07-29 Story 2 S2-R1; S2-R2; S2-N1; S2-N2; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I414" s="2" t="inlineStr"/>
@@ -20705,12 +21577,14 @@
       <c r="G415" s="2" t="inlineStr">
         <is>
           <t>1. The part appears twice — one row per location, each with that location's own quantity and values.
-2. The rows are NOT merged into one combined row; this is the documented v1 behavior.</t>
+2. The rows are NOT merged into one combined row; this is the documented v1 behavior.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S2-R3).</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
         <is>
-          <t>SV-8669 (specs/inventory-value.md Story 2 S2-R3; §2 Known Limitations (v1))</t>
+          <t>SV-8669 (IV spec v3 2026-07-29 Story 2 S2-R3; §2 Known Limitations (v1))</t>
         </is>
       </c>
       <c r="I415" s="2" t="inlineStr"/>
@@ -20751,12 +21625,14 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>1. The long-sitting part appears and its value is counted — every part currently holding positive, non-core stock contributes to the on-hand value, however long it has sat.</t>
+          <t>1. The long-sitting part appears and its value is counted — every part currently holding positive, non-core stock contributes to the on-hand value, however long it has sat.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3.</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
         <is>
-          <t>SV-8669 (specs/inventory-value.md Story 2 context note (no dead-stock exclusion))</t>
+          <t>SV-8669 (IV spec v3 2026-07-29 Story 2 context note (no dead-stock exclusion))</t>
         </is>
       </c>
       <c r="I416" s="2" t="inlineStr"/>
@@ -20799,12 +21675,14 @@
       <c r="G417" s="2" t="inlineStr">
         <is>
           <t>1. Unit Sell equals the part's fixed sell price.
-2. The pricing-matrix markup is NOT applied when a fixed sell price is set — the fixed price wins.</t>
+2. The pricing-matrix markup is NOT applied when a fixed sell price is set — the fixed price wins.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R5).</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
         <is>
-          <t>SV-8670 (specs/inventory-value.md Story 3 S3-R5 (fixed-price branch); §3 Key Decisions (unit sell resolved like the parts list))</t>
+          <t>SV-8670 (IV spec v3 2026-07-29 Story 3 S3-R5 (fixed-price branch); §3 Key Decisions (unit sell resolved like the parts list))</t>
         </is>
       </c>
       <c r="I417" s="2" t="inlineStr"/>
@@ -20846,12 +21724,14 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>1. Unit Sell equals the shop's pricing-matrix markup on cost for that part's category (the same way the parts list resolves it).</t>
+          <t>1. Unit Sell equals the shop's pricing-matrix markup on cost for that part's category (the same way the parts list resolves it).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R5).</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
         <is>
-          <t>SV-8670 (specs/inventory-value.md Story 3 S3-R5 (matrix branch); §5 Assumptions)</t>
+          <t>SV-8670 (IV spec v3 2026-07-29 Story 3 S3-R5 (matrix branch); §5 Assumptions)</t>
         </is>
       </c>
       <c r="I418" s="2" t="inlineStr"/>
@@ -20882,7 +21762,8 @@
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
 2. A ZZAUTOTEST in-stock part exists with a known unit cost, NO fixed sell price, and NO category.
-3. The Margin and Total Sell columns are turned on.</t>
+3. The Margin and Total Sell columns are turned on.
+4. Note for the tester: on this build a part cannot be saved without a category, so you may not be able to create the part described in step 2. If you cannot, mark this test Blocked and say so — do not guess the result.</t>
         </is>
       </c>
       <c r="F419" s="2" t="inlineStr">
@@ -20895,12 +21776,15 @@
       <c r="G419" s="2" t="inlineStr">
         <is>
           <t>1. A part with no category takes no markup, so its Unit Sell equals its Unit Cost.
-2. Such a part shows a Margin of $0.00 and a Margin % of 0.0% — the stock is valued at cost.</t>
+2. Such a part shows a Margin of $0.00 and a Margin % of 0.0% — the stock is valued at cost.
+3. Note for the tester: if no part without a category can be created or found, mark this test Blocked rather than Passed or Failed.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R5).</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
         <is>
-          <t>SV-8670 (specs/inventory-value.md Story 3 S3-R5 (no-category fallback) + context note; §5 Assumptions)</t>
+          <t>SV-8670 (IV spec v3 2026-07-29 Story 3 S3-R5 (no-category fallback) + context note; §5 Assumptions)</t>
         </is>
       </c>
       <c r="I419" s="2" t="inlineStr"/>
@@ -20944,12 +21828,14 @@
       <c r="G420" s="2" t="inlineStr">
         <is>
           <t>1. Total Sell equals the part's on-hand quantity × Unit Sell, shown as US-dollar currency.
-2. Total Cost equals the part's on-hand quantity × Unit Cost, shown as US-dollar currency.</t>
+2. Total Cost equals the part's on-hand quantity × Unit Cost, shown as US-dollar currency.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R6, S3-R7).</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
         <is>
-          <t>SV-8670 (specs/inventory-value.md Story 3 S3-R6; S3-R7; §4 Terminology)</t>
+          <t>SV-8670 (IV spec v3 2026-07-29 Story 3 S3-R6; S3-R7; §4 Terminology)</t>
         </is>
       </c>
       <c r="I420" s="2" t="inlineStr"/>
@@ -20993,12 +21879,14 @@
       <c r="G421" s="2" t="inlineStr">
         <is>
           <t>1. Margin equals Total Sell − Total Cost for the part's whole on-hand quantity, shown as US-dollar currency.
-2. Margin is the extended (total) margin, not the per-unit difference.</t>
+2. Margin is the extended (total) margin, not the per-unit difference.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R8).</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
         <is>
-          <t>SV-8670 (specs/inventory-value.md Story 3 S3-R8; §3 Key Decisions (extended margin); §4 Terminology)</t>
+          <t>SV-8670 (IV spec v3 2026-07-29 Story 3 S3-R8; §3 Key Decisions (extended margin); §4 Terminology)</t>
         </is>
       </c>
       <c r="I421" s="2" t="inlineStr"/>
@@ -21042,12 +21930,14 @@
         <is>
           <t>1. Margin % shows Margin as a percentage of Total Sell, to one decimal place followed by a percent sign — for example "39.7%".
 2. A Margin % that computes to a real number, including a negative one, shows its signed value.
-3. Margin % shows "—" when Total Sell is zero or negative (the percentage is undefined).</t>
+3. Margin % shows "—" when Total Sell is zero or negative (the percentage is undefined).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R9, S3-E3).</t>
         </is>
       </c>
       <c r="H422" s="2" t="inlineStr">
         <is>
-          <t>SV-8670 (specs/inventory-value.md Story 3 S3-R9; S3-E3)</t>
+          <t>SV-8670 (IV spec v3 2026-07-29 Story 3 S3-R9; S3-E3)</t>
         </is>
       </c>
       <c r="I422" s="2" t="inlineStr"/>
@@ -21092,7 +21982,9 @@
           <t>1. With a single location in scope the columns appear in this order: Part #, Description, Category, Vendor, Qty, Unit Cost, Unit Sell, Margin, Margin %, Total Sell, Total Cost.
 2. Part #, Description, Category, and Vendor are left-aligned.
 3. Every other column is right-aligned.
-4. Location is one of the columns in the column-selection control; when it is turned on the Location column appears between Vendor and Qty, left-aligned.</t>
+4. Location is one of the columns in the column-selection control; when it is turned on the Location column appears between Vendor and Qty, left-aligned.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R1, S3-R2, S7-R6); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
       <c r="H423" s="2" t="inlineStr">
@@ -21141,12 +22033,14 @@
         <is>
           <t>1. Qty shows the on-hand quantity to two decimal places, with no currency symbol; fractional quantities display correctly.
 2. Unit Cost and Unit Sell show per-unit prices as US-dollar currency.
-3. Money values show a leading "$", two decimal places, and thousands separators (for example "$1,234.56"); a negative value shows a leading minus before the "$" ("-$1,234.56"); a genuine zero shows "$0.00".</t>
+3. Money values show a leading "$", two decimal places, and thousands separators (for example "$1,234.56"); a negative value shows a leading minus before the "$" ("-$1,234.56"); a genuine zero shows "$0.00".
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R3, S3-R4, S3-R5, S3-R10).</t>
         </is>
       </c>
       <c r="H424" s="2" t="inlineStr">
         <is>
-          <t>SV-8670 (specs/inventory-value.md Story 3 S3-R3; S3-R4; S3-R5 (display); S3-R10; §4 Terminology (On-hand quantity))</t>
+          <t>SV-8670 (IV spec v3 2026-07-29 Story 3 S3-R3; S3-R4; S3-R5 (display); S3-R10; §4 Terminology (On-hand quantity))</t>
         </is>
       </c>
       <c r="I424" s="2" t="inlineStr"/>
@@ -21189,12 +22083,14 @@
         <is>
           <t>1. The Total Cost column is pinned to the far right of the row and shown in bold — it is the report's headline column.
 2. The Total Cost column header is bold and pinned, matching its cells.
-3. It stays fixed to the right edge while the other columns scroll underneath.</t>
+3. It stays fixed to the right edge while the other columns scroll underneath.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R11, S12-R4).</t>
         </is>
       </c>
       <c r="H425" s="2" t="inlineStr">
         <is>
-          <t>SV-8670 (specs/inventory-value.md Story 3 S3-R11; Story 12 S12-R4; §3 Key Decisions)</t>
+          <t>SV-8670 (IV spec v3 2026-07-29 Story 3 S3-R11; Story 12 S12-R4; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I425" s="2" t="inlineStr"/>
@@ -21238,7 +22134,9 @@
           <t>1. On first visit with a single location in scope the visible columns are: Part #, Description, Category, Vendor, Qty, Unit Cost, Unit Sell, Margin %, and Total Cost.
 2. The Margin and Total Sell columns are hidden by default.
 3. Both can be turned on from the column-selection control and then appear in their fixed positions.
-4. Location is one of the columns in the column-selection control; when it is turned on the Location column shows between Vendor and Qty.</t>
+4. Location is one of the columns in the column-selection control; when it is turned on the Location column shows between Vendor and Qty.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R12, S3-R13, S8-R3, S7-R6); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
       <c r="H426" s="2" t="inlineStr">
@@ -21288,12 +22186,14 @@
           <t>1. Category shows the part's category name; Vendor shows the part's vendor name.
 2. A part with no category shows an em dash ("—") in its Category cell.
 3. A part with no vendor shows an em dash ("—") in its Vendor cell.
-4. Note for the tester: on this build a part cannot be saved without a category, so you will not find a part whose Category cell shows "—". Check the Vendor half only.</t>
+4. Note for the tester: on this build a part cannot be saved without a category, so you will not find a part whose Category cell shows "—". Check the Vendor half only.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R14, S3-E1, S3-E2).</t>
         </is>
       </c>
       <c r="H427" s="2" t="inlineStr">
         <is>
-          <t>SV-8670 (specs/inventory-value.md Story 3 S3-R14; S3-E1; S3-E2)</t>
+          <t>SV-8670 (IV spec v3 2026-07-29 Story 3 S3-R14; S3-E1; S3-E2)</t>
         </is>
       </c>
       <c r="I427" s="2" t="inlineStr"/>
@@ -21302,7 +22202,7 @@
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>Totals row: Totals label, blank identity/per-unit cells, pinned bold Total Cost</t>
+          <t>Totals row: Total label, blank identity/per-unit cells, pinned bold Total Cost</t>
         </is>
       </c>
       <c r="B428" s="2" t="inlineStr">
@@ -21337,15 +22237,18 @@
       </c>
       <c r="G428" s="2" t="inlineStr">
         <is>
-          <t>1. A totals row is shown at the bottom, with the label "Totals" in the Part # column's cell.
+          <t>1. A totals row is shown at the bottom, with the label "Total" in the Part # column's cell. In the downloaded files the same row is labelled "Totals" — that difference is intended.
 2. The Description, Category, and Vendor cells are blank; the Unit Cost and Unit Sell cells are blank (a per-unit price has no meaningful sum).
 3. The totals-row Total Cost cell is pinned far right and bold, matching the column, and the row uses the same number formats as the data rows.
-4. The totals row stays visible at the bottom while the rows scroll.</t>
+4. The totals row stays visible at the bottom while the rows scroll.
+5. Note for the tester: if the label on screen reads "Totals" instead of "Total", mark this test Failed and report it — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S4-R1, S4-R4, S4-R5, S4-R6, S4-R7, S12-R5).</t>
         </is>
       </c>
       <c r="H428" s="2" t="inlineStr">
         <is>
-          <t>SV-8671 (specs/inventory-value.md Story 4 S4-R1; S4-R4; S4-R5; S4-R6; S4-R7; Story 12 S12-R5)</t>
+          <t>SV-8671 (IV spec v3 2026-07-29 Story 4 S4-R1; S4-R4; S4-R5; S4-R6; S4-R7; Story 12 S12-R5)</t>
         </is>
       </c>
       <c r="I428" s="2" t="inlineStr"/>
@@ -21393,12 +22296,14 @@
           <t>1. The totals row sums Qty, Margin, Total Sell, and Total Cost across the FULL filtered result set — every qualifying row for the current Date, Location, Category, Vendor, and part-search selection, not only the rows on the visible page.
 2. The totals are identical on every page (they do not change as you page).
 3. The hand-summed subset matches the server-computed totals to the cent.
-4. After each filter change the totals row recomputes on the server over the full filtered set, independent of which page is shown.</t>
+4. After each filter change the totals row recomputes on the server over the full filtered set, independent of which page is shown.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S4-R2, S4-R8, S6-R6).</t>
         </is>
       </c>
       <c r="H429" s="2" t="inlineStr">
         <is>
-          <t>SV-8671 (specs/inventory-value.md Story 4 S4-R2; S4-R8; Story 6 S6-R6; §2 Scale and data model; §4 Terminology (Filtered set))</t>
+          <t>SV-8671 (IV spec v3 2026-07-29 Story 4 S4-R2; S4-R8; Story 6 S6-R6; §2 Scale and data model; §4 Terminology (Filtered set))</t>
         </is>
       </c>
       <c r="I429" s="2" t="inlineStr"/>
@@ -21443,12 +22348,14 @@
         <is>
           <t>1. The totals-row Margin % equals total Margin ÷ total Total Sell × 100 (to one decimal place with a percent sign).
 2. It is NOT the average of the row percentages.
-3. It shows "—" when the total Total Sell is zero or negative.</t>
+3. It shows "—" when the total Total Sell is zero or negative.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S4-R3).</t>
         </is>
       </c>
       <c r="H430" s="2" t="inlineStr">
         <is>
-          <t>SV-8671 (specs/inventory-value.md Story 4 S4-R3)</t>
+          <t>SV-8671 (IV spec v3 2026-07-29 Story 4 S4-R3)</t>
         </is>
       </c>
       <c r="I430" s="2" t="inlineStr"/>
@@ -21490,12 +22397,14 @@
       <c r="G431" s="2" t="inlineStr">
         <is>
           <t>1. The control offers the standard presets: "Today", "Yesterday", "This Week", "Last Week", "This Month", "Last Month", "This Year", "Last Year", "This Quarter", "Last Quarter", and "Custom".
-2. "All Time" is NOT offered — because the report is valued as of a single date, an All-Time option would be meaningless; its absence is the documented v1 behavior.</t>
+2. "All Time" is NOT offered — because the report is valued as of a single date, an All-Time option would be meaningless; its absence is the documented v1 behavior.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S5-R1).</t>
         </is>
       </c>
       <c r="H431" s="2" t="inlineStr">
         <is>
-          <t>SV-8672 (specs/inventory-value.md Story 5 S5-R1; §2 Known Limitations (v1))</t>
+          <t>SV-8672 (IV spec v3 2026-07-29 Story 5 S5-R1; §2 Known Limitations (v1))</t>
         </is>
       </c>
       <c r="I431" s="2" t="inlineStr"/>
@@ -21539,12 +22448,15 @@
       <c r="G432" s="2" t="inlineStr">
         <is>
           <t>1. The report values inventory as of the END of the selected range.
-2. The date control is an "as of" anchor, not a created-date filter — narrowing it does not select "parts added in that range"; it shows the whole shelf as it stood on that date, so the part stocked before the range still appears.</t>
+2. The date control is an "as of" anchor, not a created-date filter — narrowing it does not select "parts added in that range"; it shows the whole shelf as it stood on that date, so the part stocked before the range still appears.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8820
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S5-R2).</t>
         </is>
       </c>
       <c r="H432" s="2" t="inlineStr">
         <is>
-          <t>SV-8672 (specs/inventory-value.md Story 5 S5-R2 (+ context note))</t>
+          <t>SV-8672 (IV spec v3 2026-07-29 Story 5 S5-R2 (+ context note))</t>
         </is>
       </c>
       <c r="I432" s="2" t="inlineStr"/>
@@ -21587,12 +22499,14 @@
       <c r="G433" s="2" t="inlineStr">
         <is>
           <t>1. The report values the current live stock — the values represent today.
-2. The part's row reflects today's changed quantity (not yesterday's snapshot), proving the live fallback is in use.</t>
+2. The part's row reflects today's changed quantity (not yesterday's snapshot), proving the live fallback is in use.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S5-R3).</t>
         </is>
       </c>
       <c r="H433" s="2" t="inlineStr">
         <is>
-          <t>SV-8672 (specs/inventory-value.md Story 5 S5-R3; §3 Key Decisions (live fallback for today))</t>
+          <t>SV-8672 (IV spec v3 2026-07-29 Story 5 S5-R3; §3 Key Decisions (live fallback for today))</t>
         </is>
       </c>
       <c r="I433" s="2" t="inlineStr"/>
@@ -21627,7 +22541,7 @@
       </c>
       <c r="F434" s="2" t="inlineStr">
         <is>
-          <t>1. Select a Custom range ending on the past recorded day.
+          <t>1. Open the date range picker and use the month calendar inside it to set a range ending on the past recorded day, then apply.
 2. Find the part and read its quantity and values.
 3. Compare them to what the part held on that recorded day (not today).</t>
         </is>
@@ -21635,12 +22549,15 @@
       <c r="G434" s="2" t="inlineStr">
         <is>
           <t>1. The report replays the closest recorded day on or before the end of the selected range.
-2. The part's row shows the quantity and values recorded for that day, not today's live stock.</t>
+2. The part's row shows the quantity and values recorded for that day, not today's live stock.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8820
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S5-R4).</t>
         </is>
       </c>
       <c r="H434" s="2" t="inlineStr">
         <is>
-          <t>SV-8672 (specs/inventory-value.md Story 5 S5-R4; §2 Relationship to nightly history)</t>
+          <t>SV-8672 (IV spec v3 2026-07-29 Story 5 S5-R4; §2 Relationship to nightly history)</t>
         </is>
       </c>
       <c r="I434" s="2" t="inlineStr"/>
@@ -21683,7 +22600,10 @@
       <c r="G435" s="2" t="inlineStr">
         <is>
           <t>1. When the displayed day is an earlier recorded day than the date asked for, the report shows an "As of" indicator naming the day actually shown.
-2. When the displayed day matches the date asked for (the common current-view case), the "As of" indicator is not shown — the date control already communicates the date.</t>
+2. When the displayed day matches the date asked for (the common current-view case), the "As of" indicator is not shown — the date control already communicates the date.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8820
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S5-R5, S5-R6).</t>
         </is>
       </c>
       <c r="H435" s="2" t="inlineStr">
@@ -21733,12 +22653,15 @@
         <is>
           <t>1. A Custom range lets the user pick a start and end date, and the report values as of the picked end date.
 2. A future end date cannot be chosen — the end date is capped at today.
-3. Changing the date range reloads the report (the loading indicator shows and the rows re-fetch).</t>
+3. Changing the date range reloads the report (the loading indicator shows and the rows re-fetch).
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8820
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S5-R7, S5-R8).</t>
         </is>
       </c>
       <c r="H436" s="2" t="inlineStr">
         <is>
-          <t>SV-8672 (specs/inventory-value.md Story 5 S5-R7; S5-R8)</t>
+          <t>SV-8672 (IV spec v3 2026-07-29 Story 5 S5-R7; S5-R8)</t>
         </is>
       </c>
       <c r="I436" s="2" t="inlineStr"/>
@@ -21780,12 +22703,14 @@
       <c r="G437" s="2" t="inlineStr">
         <is>
           <t>1. The report shows the empty state — there is no way to reconstruct inventory value for a date before recording began, because there is no historical backfill.
-2. This forward-capture-only behavior is the documented v1 boundary, not a defect.</t>
+2. This forward-capture-only behavior is the documented v1 boundary, not a defect.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S5-E1).</t>
         </is>
       </c>
       <c r="H437" s="2" t="inlineStr">
         <is>
-          <t>SV-8672 (specs/inventory-value.md Story 5 S5-E1; §2 Known Limitations (v1); §2 Out of scope)</t>
+          <t>SV-8672 (IV spec v3 2026-07-29 Story 5 S5-E1; §2 Known Limitations (v1); §2 Out of scope)</t>
         </is>
       </c>
       <c r="I437" s="2" t="inlineStr"/>
@@ -21830,12 +22755,14 @@
         <is>
           <t>1. The earlier recorded day still shows the category and vendor names AS THEY WERE RECORDED that day — a recorded day equals what the live report showed that day, even after the rename/delete.
 2. The rename/delete causes no blank Category/Vendor cells and no dropped rows on the recorded day.
-3. The live view (window reaching today) shows the NEW name for the renamed category.</t>
+3. The live view (window reaching today) shows the NEW name for the renamed category.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S11-R2, S5-R4).</t>
         </is>
       </c>
       <c r="H438" s="2" t="inlineStr">
         <is>
-          <t>SV-8678 (specs/inventory-value.md Story 11 S11-R2; Story 5 S5-R4; tech-plan-2026-07-29 B4.1 — names stored with the recorded rows on purpose)</t>
+          <t>SV-8678 (IV spec v3 2026-07-29 Story 11 S11-R2; Story 5 S5-R4; tech-plan-2026-07-29 B4.1 — names stored with the recorded rows on purpose)</t>
         </is>
       </c>
       <c r="I438" s="2" t="inlineStr"/>
@@ -21879,12 +22806,14 @@
         <is>
           <t>1. The toolbar has a Category filter labeled "Category" and a Vendor filter labeled "Vendor", each allowing one or more selections.
 2. Selecting one or more categories reloads the report to show only parts in the selected categories.
-3. Selecting one or more vendors reloads the report to show only parts supplied by the selected vendors.</t>
+3. Selecting one or more vendors reloads the report to show only parts supplied by the selected vendors.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S6-R1, S6-R2, S6-R3, S6-R4).</t>
         </is>
       </c>
       <c r="H439" s="2" t="inlineStr">
         <is>
-          <t>SV-8673 (specs/inventory-value.md Story 6 S6-R1; S6-R2; S6-R3; S6-R4)</t>
+          <t>SV-8673 (IV spec v3 2026-07-29 Story 6 S6-R1; S6-R2; S6-R3; S6-R4)</t>
         </is>
       </c>
       <c r="I439" s="2" t="inlineStr"/>
@@ -21919,7 +22848,7 @@
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
-          <t>1. Scroll well down the list, then select a Category and check where the list starts and which rows are listed.
+          <t>1. Scroll well down the list, then select a Category and check whether the list has jumped back to the top and which rows are now listed.
 2. Repeat with a Vendor selection.
 3. Repeat with a part search.
 4. Also change the date range, the location selection, and the sort — watching the data area each time.</t>
@@ -21927,14 +22856,16 @@
       </c>
       <c r="G440" s="2" t="inlineStr">
         <is>
-          <t>1. Each change re-queries the server and returns the first page of the new result set.
+          <t>1. Each change re-queries the server and the list jumps back to the top of the new set of rows.
 2. The filtering covers the ENTIRE data set — matching parts that were further down the list appear — not just a narrowing of the rows currently on screen.
-3. Every change — date range, location, Category, Vendor, part search, sort — reloads the rows from the server; while loading the standard reports loading indicator shows, and existing rows are replaced only when the new data returns.</t>
+3. Every change — date range, location, Category, Vendor, part search, sort — reloads the rows from the server; while loading the standard reports loading indicator shows, and existing rows are replaced only when the new data returns.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S6-R5, S1-R4, S1-R5, S1-R7, S1-R8).</t>
         </is>
       </c>
       <c r="H440" s="2" t="inlineStr">
         <is>
-          <t>SV-8673 (specs/inventory-value.md Story 6 S6-R5; Story 1 S1-R4; S1-R5; S1-R7; S1-R8)</t>
+          <t>SV-8673 (IV spec v3 2026-07-29 Story 6 S6-R5; Story 1 S1-R4; S1-R5; S1-R7; S1-R8)</t>
         </is>
       </c>
       <c r="I440" s="2" t="inlineStr"/>
@@ -21978,12 +22909,14 @@
         <is>
           <t>1. With no category selected, parts of all categories are shown.
 2. With no vendor selected, parts of all vendors are shown.
-3. With the part search empty, no search narrowing is applied.</t>
+3. With the part search empty, no search narrowing is applied.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S6-R7).</t>
         </is>
       </c>
       <c r="H441" s="2" t="inlineStr">
         <is>
-          <t>SV-8673 (specs/inventory-value.md Story 6 S6-R7)</t>
+          <t>SV-8673 (IV spec v3 2026-07-29 Story 6 S6-R7)</t>
         </is>
       </c>
       <c r="I441" s="2" t="inlineStr"/>
@@ -22029,12 +22962,14 @@
           <t>1. The search field is page-local, in the report's own toolbar — it is not the application's global search bar (the same toolbar-search pattern used elsewhere in the reports suite).
 2. The report narrows to parts whose part number OR description contains the entered text.
 3. Matching is case-insensitive.
-4. The search applies server-side (whole data set, first page returned); a no-match search shows the no-data message.</t>
+4. The search applies server-side (whole data set, first page returned); a no-match search shows the no-data message.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S6-R8, S6-R5).</t>
         </is>
       </c>
       <c r="H442" s="2" t="inlineStr">
         <is>
-          <t>SV-8673 (specs/inventory-value.md Story 6 S6-R8; S6-R5)</t>
+          <t>SV-8673 (IV spec v3 2026-07-29 Story 6 S6-R8; S6-R5)</t>
         </is>
       </c>
       <c r="I442" s="2" t="inlineStr"/>
@@ -22077,12 +23012,14 @@
       <c r="G443" s="2" t="inlineStr">
         <is>
           <t>1. A part must satisfy EVERY active filter and the search to appear — the Date range, Location, Category, Vendor, and part search combine with AND.
-2. The totals row matches the combined filtered set after each step.</t>
+2. The totals row matches the combined filtered set after each step.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S6-R9).</t>
         </is>
       </c>
       <c r="H443" s="2" t="inlineStr">
         <is>
-          <t>SV-8673 (specs/inventory-value.md Story 6 S6-R9)</t>
+          <t>SV-8673 (IV spec v3 2026-07-29 Story 6 S6-R9)</t>
         </is>
       </c>
       <c r="I443" s="2" t="inlineStr"/>
@@ -22127,7 +23064,9 @@
         <is>
           <t>1. The toolbar has a location filter labeled "Location" — a multi-select and the rightmost filter — listing the locations the signed-in user has access to, with an "All locations" / "Clear all" toggle.
 2. On a first visit it defaults to the user's currently active location.
-3. With "All locations" active you can tell which location each row's stock belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)</t>
+3. With "All locations" active you can tell which location each row's stock belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S7-R1, S7-R2, S12-R3); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
@@ -22176,12 +23115,14 @@
         <is>
           <t>1. Each selection change reloads the report scoped to the selected set.
 2. With both locations selected, parts from both appear (one row per part per location) and the totals cover both.
-3. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).</t>
+3. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S7-R3).</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
         <is>
-          <t>SV-8674 (specs/inventory-value.md Story 7 S7-R3 + on-screen location-scope indicator per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
+          <t>SV-8674 (IV spec v3 2026-07-29 Story 7 S7-R3 + on-screen location-scope indicator per Chris Ward group message 2026-07-29 (chris-update-2026-07-29/chris-message-2026-07-29.md; NEWEST source; last-update-wins))</t>
         </is>
       </c>
       <c r="I445" s="2" t="inlineStr"/>
@@ -22223,12 +23164,14 @@
       <c r="G446" s="2" t="inlineStr">
         <is>
           <t>1. Only the locations the user has access to are offered — a location the user cannot access is never included in the scope.
-2. If the requested location set resolves to none the user can access, the report falls back to the user's currently active location.</t>
+2. If the requested location set resolves to none the user can access, the report falls back to the user's currently active location.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S7-R4, S7-R5).</t>
         </is>
       </c>
       <c r="H446" s="2" t="inlineStr">
         <is>
-          <t>SV-8674 (specs/inventory-value.md Story 7 S7-R4; S7-R5)</t>
+          <t>SV-8674 (IV spec v3 2026-07-29 Story 7 S7-R4; S7-R5)</t>
         </is>
       </c>
       <c r="I446" s="2" t="inlineStr"/>
@@ -22270,7 +23213,9 @@
       <c r="G447" s="2" t="inlineStr">
         <is>
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's stock.
-2. For the user with access to two or more locations the Location filter IS shown.</t>
+2. For the user with access to two or more locations the Location filter IS shown.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S7-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H447" s="2" t="inlineStr">
@@ -22328,7 +23273,9 @@
 4. Location IS one of the columns offered in the column-selection control - its visibility follows that toggle, not the location selection.
 5. With the Location toggle off the column is not shown and the surrounding columns close up.
 6. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
-7. Both downloads include the Location column in the same position it holds on screen (between Vendor and Qty), naming each row's own location.</t>
+7. Both downloads include the Location column in the same position it holds on screen (between Vendor and Qty), naming each row's own location.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S7-R6, S7-R7, S3-R1, S12-R10, S10-R15); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
@@ -22377,12 +23324,14 @@
         <is>
           <t>1. The icon button's tooltip reads "Column Selection".
 2. Toggling a column off hides it from the table; toggling it on shows it again.
-3. The Total Cost column is always shown and cannot be turned off.</t>
+3. The Total Cost column is always shown and cannot be turned off.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S8-R1, S8-R2).</t>
         </is>
       </c>
       <c r="H449" s="2" t="inlineStr">
         <is>
-          <t>SV-8675 (specs/inventory-value.md Story 8 S8-R1; S8-R2)</t>
+          <t>SV-8675 (IV spec v3 2026-07-29 Story 8 S8-R1; S8-R2)</t>
         </is>
       </c>
       <c r="I449" s="2" t="inlineStr"/>
@@ -22424,7 +23373,9 @@
       <c r="G450" s="2" t="inlineStr">
         <is>
           <t>1. Whatever columns are shown, they appear in the fixed left-to-right order - with Location, when it is turned on in the column-selection control, between Vendor and Qty (Part #, Description, Category, Vendor, Qty, Unit Cost, Unit Sell, Margin, Margin %, Total Sell, Total Cost) - toggling visibility never reorders columns.
-2. Total Cost is always the last column.</t>
+2. Total Cost is always the last column.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S8-R4, S3-R1, S7-R6); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -22473,12 +23424,14 @@
       <c r="G451" s="2" t="inlineStr">
         <is>
           <t>1. On return and after a reload, the report restores the saved date range, category selection, vendor selection, part search text, location selection, column selection, and sort.
-2. In a different browser the report shows the defaults instead — persistence is per browser, not tied to the user's account.</t>
+2. In a different browser the report shows the defaults instead — persistence is per browser, not tied to the user's account.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S8-R5, S9-R5).</t>
         </is>
       </c>
       <c r="H451" s="2" t="inlineStr">
         <is>
-          <t>SV-8675 (specs/inventory-value.md Story 8 S8-R5 (+ context note); Story 9 S9-R5)</t>
+          <t>SV-8675 (IV spec v3 2026-07-29 Story 8 S8-R5 (+ context note); Story 9 S9-R5)</t>
         </is>
       </c>
       <c r="I451" s="2" t="inlineStr"/>
@@ -22520,12 +23473,14 @@
       <c r="G452" s="2" t="inlineStr">
         <is>
           <t>1. The report loads normally — the saved category or vendor that is no longer present in the data is dropped from the selection instead of breaking the view (the defensive-restore rule applied to the path these steps drive).
-2. All other saved settings are still restored.</t>
+2. All other saved settings are still restored.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S8-R6).</t>
         </is>
       </c>
       <c r="H452" s="2" t="inlineStr">
         <is>
-          <t>SV-8675 (specs/inventory-value.md Story 8 S8-R6)</t>
+          <t>SV-8675 (IV spec v3 2026-07-29 Story 8 S8-R6)</t>
         </is>
       </c>
       <c r="I452" s="2" t="inlineStr"/>
@@ -22567,12 +23522,14 @@
       <c r="G453" s="2" t="inlineStr">
         <is>
           <t>1. The rows are sorted by Total Cost, highest first (descending).
-2. The order holds across pages (page 2 continues below page 1's lowest value) — the server applies the default order over the full set.</t>
+2. The order holds across pages (page 2 continues below page 1's lowest value) — the server applies the default order over the full set.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S9-R1).</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
         <is>
-          <t>SV-8676 (specs/inventory-value.md Story 9 S9-R1; §3 Key Decisions (Total Cost default sort))</t>
+          <t>SV-8676 (IV spec v3 2026-07-29 Story 9 S9-R1; §3 Key Decisions (Total Cost default sort))</t>
         </is>
       </c>
       <c r="I453" s="2" t="inlineStr"/>
@@ -22617,12 +23574,14 @@
         <is>
           <t>1. Clicking a column that is not the active sort sorts it ascending; clicking the active sort column again toggles it to descending; there is no third "cleared" state.
 2. Each header click re-fetches the data from the server ordered by the chosen column and direction, returning the FIRST page of the re-sorted result set.
-3. Only one column sorts at a time.</t>
+3. Only one column sorts at a time.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S9-R2).</t>
         </is>
       </c>
       <c r="H454" s="2" t="inlineStr">
         <is>
-          <t>SV-8676 (specs/inventory-value.md Story 9 S9-R2)</t>
+          <t>SV-8676 (IV spec v3 2026-07-29 Story 9 S9-R2)</t>
         </is>
       </c>
       <c r="I454" s="2" t="inlineStr"/>
@@ -22665,12 +23624,14 @@
       <c r="G455" s="2" t="inlineStr">
         <is>
           <t>1. Money and numeric columns sort by their underlying value (so $1,100.00 is treated as more than $900.00, not compared as text).
-2. Text columns (Part #, Description, Category, Vendor) sort as text, case-insensitively ("apple" and "Apple" sort together).</t>
+2. Text columns (Part #, Description, Category, Vendor) sort as text, case-insensitively ("apple" and "Apple" sort together).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S9-R3).</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
         <is>
-          <t>SV-8676 (specs/inventory-value.md Story 9 S9-R3)</t>
+          <t>SV-8676 (IV spec v3 2026-07-29 Story 9 S9-R3)</t>
         </is>
       </c>
       <c r="I455" s="2" t="inlineStr"/>
@@ -22712,12 +23673,14 @@
       <c r="G456" s="2" t="inlineStr">
         <is>
           <t>1. Sorting reorders the data rows only; the totals row stays at the bottom.
-2. On return, the report restores the chosen sort (remembered per browser, Story 8).</t>
+2. On return, the report restores the chosen sort (remembered per browser, Story 8).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S9-R4, S9-R5).</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
         <is>
-          <t>SV-8676 (specs/inventory-value.md Story 9 S9-R4; S9-R5)</t>
+          <t>SV-8676 (IV spec v3 2026-07-29 Story 9 S9-R4; S9-R5)</t>
         </is>
       </c>
       <c r="I456" s="2" t="inlineStr"/>
@@ -22760,12 +23723,14 @@
       <c r="G457" s="2" t="inlineStr">
         <is>
           <t>1. The menu holds an option labeled "Download (PDF)" and an option labeled "Download (CSV)".
-2. Each option downloads a file of the current view in the chosen format.</t>
+2. Each option downloads a file of the current view in the chosen format.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S10-R1, S10-R2).</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
         <is>
-          <t>SV-8677 (specs/inventory-value.md Story 10 S10-R1; S10-R2)</t>
+          <t>SV-8677 (IV spec v3 2026-07-29 Story 10 S10-R1; S10-R2)</t>
         </is>
       </c>
       <c r="I457" s="2" t="inlineStr"/>
@@ -22813,7 +23778,9 @@
 2. Both downloads honor the current date, category, vendor, location, and part-search filters, and apply the current sort.
 3. Both downloads include a totals row labeled "Totals" matching the on-screen totals (the full-filtered-set totals).
 4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
-5. Note for the tester: the files carry the Location column when Location is turned ON in the column-selection control (it sits between Vendor and Qty). It does not appear just because you have more than one location selected.</t>
+5. Note for the tester: the files carry the Location column when Location is turned ON in the column-selection control (it sits between Vendor and Qty). It does not appear just because you have more than one location selected.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S10-R3, S10-R4, S10-R5, S10-R6, S10-R15); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -22861,7 +23828,9 @@
         <is>
           <t>1. Money uses two decimals and Margin % one decimal in both files; an undefined Margin % shows "—".
 2. In the CSV, money values are written as plain numbers with two decimals and NO thousands separators (so they parse cleanly in a spreadsheet).
-3. The PDF uses the same on-screen currency formatting with the "$" and thousands separators.</t>
+3. The PDF uses the same on-screen currency formatting with the "$" and thousands separators.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S10-R7).</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -22913,12 +23882,14 @@
           <t>1. The PDF header shows the report name "Inventory Value", the organization name, the selected period, and an "as of" line naming the day the values represent (or a message that no snapshot is available for the period).
 2. The PDF shows the shop logo at the top when one is set.
 3. The CSV never includes a logo.
-4. Note for the tester: the two files phrase the as-of line differently - the PDF reads "As of 2026-08-04" and the CSV's first line reads "As of: 2026-08-04" (with a colon). Both are correct; do not raise the difference.</t>
+4. Note for the tester: the two files phrase the as-of line differently - the PDF reads "As of 2026-08-04" and the CSV's first line reads "As of: 2026-08-04" (with a colon). Both are correct; do not raise the difference.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S10-R8, S10-R9).</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
         <is>
-          <t>SV-8677 (specs/inventory-value.md Story 10 S10-R8; S10-R9)</t>
+          <t>SV-8677 (IV spec v3 2026-07-29 Story 10 S10-R8; S10-R9)</t>
         </is>
       </c>
       <c r="I460" s="2" t="inlineStr"/>
@@ -22960,7 +23931,9 @@
       <c r="G461" s="2" t="inlineStr">
         <is>
           <t>1. The PDF is named "inventory-value-report.pdf".
-2. The CSV is named "inventory-value-report.csv".</t>
+2. The CSV is named "inventory-value-report.csv".
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S10-R10).</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -23009,12 +23982,14 @@
         <is>
           <t>1. The export contains the FULL filtered set — every qualifying row across all pages, not only the rows loaded in the browser.
 2. Parts from the later pages are present.
-3. The export is generated server-side against the current filters, part search, and sort — it is not built from the rows currently in the browser.</t>
+3. The export is generated server-side against the current filters, part search, and sort — it is not built from the rows currently in the browser.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S10-R11).</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
         <is>
-          <t>SV-8677 (specs/inventory-value.md Story 10 S10-R11)</t>
+          <t>SV-8677 (IV spec v3 2026-07-29 Story 10 S10-R11)</t>
         </is>
       </c>
       <c r="I462" s="2" t="inlineStr"/>
@@ -23059,12 +24034,15 @@
           <t>1. Neither the PDF nor the CSV is produced.
 2. The user sees the message: "This report is too large to export. Narrow the date range or filters, then try again." (a blocking notification; no file).
 3. After narrowing the filters below the cap, the download works again.
-4. Note for the tester: on this environment the biggest view you can build is about 9,275 rows, which is under the cap, so you cannot make this message appear here. If the PDF fails with a plain error instead, that is the separate timeout problem - see the Inventory Value export-notification case.</t>
+4. Note for the tester: on this environment the biggest view you can build is about 9,275 rows, which is under the cap, so you cannot make this message appear here. If the PDF fails with a plain error instead, that is the separate timeout problem - see the Inventory Value export-notification case.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S10-R12).</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
         <is>
-          <t>SV-8677 (specs/inventory-value.md Story 10 S10-R12; §7 User Feedback Summary)</t>
+          <t>SV-8677 (IV spec v3 2026-07-29 Story 10 S10-R12; §7 User Feedback Summary)</t>
         </is>
       </c>
       <c r="I463" s="2" t="inlineStr"/>
@@ -23110,12 +24088,15 @@
           <t>1. Success notifications read verbatim: "Inventory Value report exported (PDF)" and "Inventory Value report exported (CSV)".
 2. Failure notifications read verbatim: "Failed to export inventory value report (pdf)" and "Failed to export inventory value report (csv)".
 3. The lower-case "(pdf)"/"(csv)" on failure vs the upper-case success ones is the documented spec wording — expected, not a bug.
-4. Note for the tester: on this build a PDF download of a large view fails with a plain error - "An error occurred. We're sorry for this inconvenience, please try again a bit later later." - after roughly half a minute. It is a timeout, not the too-large-to-export message. Narrow the view with the part search or a single location and the PDF works. The CSV of the same view always works and is quick. Record the failure; it is a known problem, not a mistake you made.</t>
+4. Note for the tester: on this build a PDF download of a large view fails with a plain error - "An error occurred. We're sorry for this inconvenience, please try again a bit later later." - after roughly half a minute. It is a timeout, not the too-large-to-export message. Narrow the view with the part search or a single location and the PDF works. The CSV of the same view always works and is quick. Record the failure; it is a known problem, not a mistake you made.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S10-R13, S10-R14).</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
         <is>
-          <t>SV-8677 (specs/inventory-value.md Story 10 S10-R13; S10-R14; §7 User Feedback Summary)</t>
+          <t>SV-8677 (IV spec v3 2026-07-29 Story 10 S10-R13; S10-R14; §7 User Feedback Summary)</t>
         </is>
       </c>
       <c r="I464" s="2" t="inlineStr"/>
@@ -23159,10 +24140,14 @@
       <c r="G465" s="2" t="inlineStr">
         <is>
           <t>1. The narrowed PDF downloads successfully.
-2. On the whole list the PDF does not download. After roughly half a minute a plain error appears reading "An error occurred. We're sorry for this inconvenience, please try again a bit later later." — record that this happened and roughly how many rows were in the view.
+2. On the whole list the PDF either downloads successfully too, or is refused politely with the message "This report is too large to export. Narrow the date range or filters, then try again." Either of those is a pass.
 3. The CSV of that same whole list downloads successfully and quickly.
 4. Once the view is narrowed the PDF works again.
-5. Note for the tester: this is NOT the too-large-to-export message. If you see "This report is too large to export. Narrow the date range or filters, then try again." instead, that is the polite refusal working correctly and belongs to the export-cap test, not this one.</t>
+5. KNOWN PROBLEM at the time of writing: on the whole list the PDF did not download at all. After roughly half a minute a plain error appeared reading "An error occurred. We're sorry for this inconvenience, please try again a bit later later." If you still see that, mark this test Failed, note roughly how many rows were in the view, and refer to the reported problem — do not change the test.
+6. Note for the tester: the polite refusal message in item 2 is the correct behaviour. The plain error in item 5 is the problem being tracked. Tell the two apart by the wording.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S10-R11, S10-R12, S10-R14).</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -23210,7 +24195,9 @@
       <c r="G466" s="2" t="inlineStr">
         <is>
           <t>1. The table has white column headers and white data cells, with no alternating row shading.
-2. The table sits on the standard soft blue-grey report backdrop.</t>
+2. The table sits on the standard soft blue-grey report backdrop.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S12-R1).</t>
         </is>
       </c>
       <c r="H466" s="2" t="inlineStr">
@@ -23257,7 +24244,9 @@
       <c r="G467" s="2" t="inlineStr">
         <is>
           <t>1. In the toolbar, the three-dot download menu sits leftmost in the action cluster, followed by the Column Selection control.
-2. The toolbar filters run, left to right: the date-range control, the part search, the Category filter, the Vendor filter, and the Location filter (rightmost).</t>
+2. The toolbar filters run, left to right: the date-range control, the part search, the Category filter, the Vendor filter, and the Location filter (rightmost).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S12-R2, S12-R3).</t>
         </is>
       </c>
       <c r="H467" s="2" t="inlineStr">
@@ -23306,12 +24295,14 @@
         <is>
           <t>1. Long text values (Description, Category, Vendor) are truncated with an ellipsis when they overflow their column.
 2. The full value is available on hover.
-3. The Part # is never truncated.</t>
+3. The Part # is never truncated.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S12-R6).</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
         <is>
-          <t>SV-8679 (specs/inventory-value.md Story 12 S12-R6)</t>
+          <t>SV-8679 (IV spec v3 2026-07-29 Story 12 S12-R6)</t>
         </is>
       </c>
       <c r="I468" s="2" t="inlineStr"/>
@@ -23353,13 +24344,16 @@
       </c>
       <c r="G469" s="2" t="inlineStr">
         <is>
-          <t>1. The report supports dark mode.
-2. The page background, toolbar, cells, and the "—" glyph all use dark-mode-legible colors.</t>
+          <t>1. The report supports dark mode: the page background, the toolbar, and the table cells all switch to their dark equivalents rather than staying light.
+2. In dark mode you can read the toolbar text and the cell text at a glance, and the "—" glyph in an empty Category or Vendor cell is clearly visible against the dark cell behind it — it does not disappear into the background.
+3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether everything is easy to read in dark mode, and only report it if something is hard to see. (The exact colour values behind this are design-token values the design and engineering team check with their own tooling, not by hand.)
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S12-R7).</t>
         </is>
       </c>
       <c r="H469" s="2" t="inlineStr">
         <is>
-          <t>SV-8679 (specs/inventory-value.md Story 12 S12-R7)</t>
+          <t>SV-8679 (IV spec v3 2026-07-29 Story 12 S12-R7)</t>
         </is>
       </c>
       <c r="I469" s="2" t="inlineStr"/>
@@ -23389,8 +24383,8 @@
       <c r="E470" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. A screen reader or the browser's accessibility inspector is available.
-3. The Inventory Value report is open with rows loaded.</t>
+2. The Inventory Value report is open with rows loaded.
+3. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
       <c r="F470" s="2" t="inlineStr">
@@ -23404,12 +24398,14 @@
         <is>
           <t>1. The active sort direction is indicated visually on the header.
 2. Each sortable column header exposes its sort state to assistive technology (for example, ascending/descending/none).
-3. The exposed state updates when the direction toggles.</t>
+3. The exposed state updates when the direction toggles.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S12-R8).</t>
         </is>
       </c>
       <c r="H470" s="2" t="inlineStr">
         <is>
-          <t>SV-8679 (specs/inventory-value.md Story 12 S12-R8)</t>
+          <t>SV-8679 (IV spec v3 2026-07-29 Story 12 S12-R8)</t>
         </is>
       </c>
       <c r="I470" s="2" t="inlineStr"/>
@@ -23439,8 +24435,8 @@
       <c r="E471" s="2" t="inlineStr">
         <is>
           <t>1. You are signed in to the ShopView App on a desktop browser.
-2. A screen reader or the browser's accessibility inspector is available.
-3. The Inventory Value report is open.</t>
+2. The Inventory Value report is open.
+3. Part of this test checks what a blind user would hear, so you need a screen reader. On Windows install NVDA — it is free, from nvaccess.org. On a Mac use VoiceOver, which is already built in (Cmd+F5 turns it on and off). Alternatively the browser's developer tools (F12) have an "Accessibility" panel that shows the same names without you having to listen to anything.</t>
         </is>
       </c>
       <c r="F471" s="2" t="inlineStr">
@@ -23451,12 +24447,14 @@
       </c>
       <c r="G471" s="2" t="inlineStr">
         <is>
-          <t>1. Each icon-only control carries an accessible name exposed to assistive technology (it is not announced as an unnamed button).</t>
+          <t>1. Each icon-only control carries an accessible name exposed to assistive technology (it is not announced as an unnamed button).
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S12-R9).</t>
         </is>
       </c>
       <c r="H471" s="2" t="inlineStr">
         <is>
-          <t>SV-8679 (specs/inventory-value.md Story 12 S12-R9)</t>
+          <t>SV-8679 (IV spec v3 2026-07-29 Story 12 S12-R9)</t>
         </is>
       </c>
       <c r="I471" s="2" t="inlineStr"/>
@@ -23500,7 +24498,9 @@
         <is>
           <t>1. The report is listed and opens normally for a user holding the ordinary reports access.
 2. No additional report-specific permission is required — for now the one ordinary reports access covers all six of the new reports.
-3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.</t>
+3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (Story 1 Prerequisites); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H472" s="2" t="inlineStr">
@@ -23546,7 +24546,9 @@
       </c>
       <c r="G473" s="2" t="inlineStr">
         <is>
-          <t>1. The report does not appear in the navigation for this user.</t>
+          <t>1. The report does not appear in the navigation for this user.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S1-N1).</t>
         </is>
       </c>
       <c r="H473" s="2" t="inlineStr">
@@ -23582,7 +24584,8 @@
         <is>
           <t>1. In-stock, non-core parts exist at two or more locations, including a part with non-round cent values.
 2. A location with NO in-stock parts also exists.
-3. You can inspect the stored snapshot rows after the nightly capture runs (arrange the verification route with the developers).</t>
+3. You can inspect the stored snapshot rows after the nightly capture runs (arrange the verification route with the developers).
+4. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
       <c r="F474" s="2" t="inlineStr">
@@ -23596,12 +24599,14 @@
         <is>
           <t>1. Once per day, overnight, one row per then-in-stock, non-core part is recorded for every location across every organization, under that day's calendar date.
 2. Each row captures the part's identity (part, category, vendor), on-hand quantity, unit cost, unit sell, total cost, and total sell, stored to the cent.
-3. A location with no in-stock parts on the date simply has no rows for that date — this is valid, not an error.</t>
+3. A location with no in-stock parts on the date simply has no rows for that date — this is valid, not an error.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S11-R1, S11-R4).</t>
         </is>
       </c>
       <c r="H474" s="2" t="inlineStr">
         <is>
-          <t>SV-8678 (specs/inventory-value.md Story 11 S11-R1; S11-R4)</t>
+          <t>SV-8678 (IV spec v3 2026-07-29 Story 11 S11-R1; S11-R4)</t>
         </is>
       </c>
       <c r="I474" s="2" t="inlineStr"/>
@@ -23632,7 +24637,8 @@
         <is>
           <t>1. ZZAUTOTEST parts with known quantities, costs, and sell resolutions (fixed price, matrix markup, and no-category fallback) are in stock and left UNCHANGED across the capture.
 2. A core-charge part and a zero-quantity part also exist.
-3. You can read the live report on the capture date and the stored rows afterward.</t>
+3. You can read the live report on the capture date and the stored rows afterward.
+4. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
       <c r="F475" s="2" t="inlineStr">
@@ -23647,12 +24653,14 @@
         <is>
           <t>1. The captured parts use the same in-stock, non-core scope as the live report (Story 2) — the core-charge and zero-quantity parts are NOT captured.
 2. The captured values use the same valuation as the live report (Story 3), including the sell-price fallback chain.
-3. A recorded day equals what the live report would have shown that day — the as-of view of the captured date matches the noted live values.</t>
+3. A recorded day equals what the live report would have shown that day — the as-of view of the captured date matches the noted live values.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S11-R2).</t>
         </is>
       </c>
       <c r="H475" s="2" t="inlineStr">
         <is>
-          <t>SV-8678 (specs/inventory-value.md Story 11 S11-R2; §2 Relationship to nightly history)</t>
+          <t>SV-8678 (IV spec v3 2026-07-29 Story 11 S11-R2; §2 Relationship to nightly history)</t>
         </is>
       </c>
       <c r="I475" s="2" t="inlineStr"/>
@@ -23682,7 +24690,8 @@
       <c r="E476" s="2" t="inlineStr">
         <is>
           <t>1. A capture has already run for the current date.
-2. The capture can be re-run for that date (arrange with the developers).</t>
+2. The capture can be re-run for that date (arrange with the developers).
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
       <c r="F476" s="2" t="inlineStr">
@@ -23696,12 +24705,14 @@
         <is>
           <t>1. Re-running the capture for a date replaces that date's rows for each location — the existing rows for that location and date are removed, then re-inserted from current data.
 2. No duplicate rows exist for the same part, location, and date.
-3. The capture is idempotent and self-healing from current data.</t>
+3. The capture is idempotent and self-healing from current data.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S11-R3).</t>
         </is>
       </c>
       <c r="H476" s="2" t="inlineStr">
         <is>
-          <t>SV-8678 (specs/inventory-value.md Story 11 S11-R3)</t>
+          <t>SV-8678 (IV spec v3 2026-07-29 Story 11 S11-R3)</t>
         </is>
       </c>
       <c r="I476" s="2" t="inlineStr"/>
@@ -23731,7 +24742,8 @@
       <c r="E477" s="2" t="inlineStr">
         <is>
           <t>1. The date the first capture ran is known.
-2. Stock levels have changed since a past captured date.</t>
+2. Stock levels have changed since a past captured date.
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
       <c r="F477" s="2" t="inlineStr">
@@ -23745,12 +24757,14 @@
         <is>
           <t>1. No rows exist for dates before capture began — there is no backfill.
 2. A re-run always records current truth under the CURRENT date; it cannot reconstruct a past date.
-3. Past dates' stored rows are unchanged by a current re-run.</t>
+3. Past dates' stored rows are unchanged by a current re-run.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S11-R5, S5-E1).</t>
         </is>
       </c>
       <c r="H477" s="2" t="inlineStr">
         <is>
-          <t>SV-8678 (specs/inventory-value.md Story 11 S11-R5; Story 5 S5-E1)</t>
+          <t>SV-8678 (IV spec v3 2026-07-29 Story 11 S11-R5; Story 5 S5-E1)</t>
         </is>
       </c>
       <c r="I477" s="2" t="inlineStr"/>
@@ -23780,7 +24794,8 @@
       <c r="E478" s="2" t="inlineStr">
         <is>
           <t>1. Snapshot history exists (or is seeded/simulated with dev help) spanning both the 0–13-month band and the older-than-13-months band.
-2. The nightly capture (with its pruning) has run.</t>
+2. The nightly capture (with its pruning) has run.
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
       <c r="F478" s="2" t="inlineStr">
@@ -23794,12 +24809,14 @@
         <is>
           <t>1. For ages 0–13 months (measured from the current date), every daily capture is kept — full daily per-part detail, covering the report's longest date preset (366 days / This Year / Last Year) entirely at daily resolution.
 2. For ages older than 13 months, only the last capture of each calendar month is retained; the other daily captures in that band are pruned.
-3. Pruning runs as part of, or alongside, the nightly capture.</t>
+3. Pruning runs as part of, or alongside, the nightly capture.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S11-R6).</t>
         </is>
       </c>
       <c r="H478" s="2" t="inlineStr">
         <is>
-          <t>SV-8678 (specs/inventory-value.md Story 11 S11-R6)</t>
+          <t>SV-8678 (IV spec v3 2026-07-29 Story 11 S11-R6)</t>
         </is>
       </c>
       <c r="I478" s="2" t="inlineStr"/>
@@ -23829,7 +24846,8 @@
       <c r="E479" s="2" t="inlineStr">
         <is>
           <t>1. Thinned history exists (dates older than 13 months where only the monthly last-capture remains — dev-seeded if needed).
-2. The retained capture dates around the requested date are known.</t>
+2. The retained capture dates around the requested date are known.
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
       <c r="F479" s="2" t="inlineStr">
@@ -23843,12 +24861,14 @@
         <is>
           <t>1. The as-of resolution serves the thinned history unchanged: the report resolves to the nearest earlier retained capture ("closest recorded day on or before"), even when adjacent retained captures are up to a month apart.
 2. The "As of" indicator names the day actually shown.
-3. A requested date whose covering captures have all been pruned resolves to the nearest earlier retained capture, or shows the empty state if none remains.</t>
+3. A requested date whose covering captures have all been pruned resolves to the nearest earlier retained capture, or shows the empty state if none remains.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S11-E1, S11-R6, S5-R4, S5-R5, S5-N1).</t>
         </is>
       </c>
       <c r="H479" s="2" t="inlineStr">
         <is>
-          <t>SV-8678 (specs/inventory-value.md Story 11 S11-E1; S11-R6; Story 5 S5-R4; S5-R5; S5-N1)</t>
+          <t>SV-8678 (IV spec v3 2026-07-29 Story 11 S11-E1; S11-R6; Story 5 S5-R4; S5-R5; S5-N1)</t>
         </is>
       </c>
       <c r="I479" s="2" t="inlineStr"/>

--- a/testrail-import/report-suite-v1-testrail-import.xlsx
+++ b/testrail-import/report-suite-v1-testrail-import.xlsx
@@ -4268,7 +4268,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report in light mode on a desktop browser with dev tools available.</t>
+          <t>1. You are on the report in light mode on a desktop browser, with some data showing.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">

--- a/testrail-import/report-suite-v1-testrail-import.xlsx
+++ b/testrail-import/report-suite-v1-testrail-import.xlsx
@@ -7317,7 +7317,7 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>1. The dialog has a "Cancel" button (red outline) and an "X" close icon.
+          <t>1. The dialog has a "Cancel" button (grey) and an "X" close icon; the "Deactivate" button is the red one.
 2. Clicking "Cancel" closes the dialog; clicking the "X" icon closes the dialog.
 3. Pressing the "Esc" key does NOT close the dialog - it stays open (the app's general rule is that pop-ups do not close with the Esc key).
 4. Clicking outside the dialog does NOT close it.
@@ -7520,7 +7520,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>1. An error toast is shown: "Ooooops! An error occured" with the caption "For more information, please contact support. Include your request ID: [{request-id}] when reaching out for faster assistance." — it persists 120 seconds or until dismissed.
+          <t>1. An error toast is shown: "Ooooops! An error occurred" with the caption "For more information, please contact support. Include your request ID: [{request-id}] when reaching out for faster assistance." — it persists 120 seconds or until dismissed.
 2. The active status is unchanged.
 3. Each fresh dialog open requires a fresh confirmation entry — the input clears on open.
 ---
@@ -20530,7 +20530,7 @@
       </c>
       <c r="H394" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (specs/wip-work-in-progress.md Story 10 S10-R1)</t>
+          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R1)</t>
         </is>
       </c>
       <c r="I394" s="2" t="inlineStr"/>
@@ -21381,7 +21381,7 @@
       </c>
       <c r="H411" s="2" t="inlineStr">
         <is>
-          <t>SV-8668 (specs/inventory-value.md Story 1 S1-R3; Story 7 S7-R2)</t>
+          <t>SV-8668 (IV spec v3 2026-07-29 Story 1 S1-R3; Story 7 S7-R2)</t>
         </is>
       </c>
       <c r="I411" s="2" t="inlineStr"/>
@@ -22608,7 +22608,7 @@
       </c>
       <c r="H435" s="2" t="inlineStr">
         <is>
-          <t>SV-8672 (specs/inventory-value.md Story 5 S5-R5; S5-R6)</t>
+          <t>SV-8672 (IV spec v3 2026-07-29 Story 5 S5-R5; S5-R6)</t>
         </is>
       </c>
       <c r="I435" s="2" t="inlineStr"/>
@@ -23071,7 +23071,7 @@
       </c>
       <c r="H444" s="2" t="inlineStr">
         <is>
-          <t>SV-8674 (specs/inventory-value.md Story 7 S7-R1; S7-R2; Story 12 S12-R3 — per-row location identifier in All-locations view ADDED per kickoff video P10 40:58-41:20; user ruling 2026-07-28: video overrides spec (video newer; last-update-wins))</t>
+          <t>SV-8674 (IV spec v3 2026-07-29 Story 7 S7-R1; S7-R2; Story 12 S12-R3 — per-row location identifier in All-locations view ADDED per kickoff video P10 40:58-41:20; user ruling 2026-07-28: video overrides spec (video newer; last-update-wins))</t>
         </is>
       </c>
       <c r="I444" s="2" t="inlineStr"/>
@@ -23835,7 +23835,7 @@
       </c>
       <c r="H459" s="2" t="inlineStr">
         <is>
-          <t>SV-8677 (specs/inventory-value.md Story 10 S10-R7 (+ context note))</t>
+          <t>SV-8677 (IV spec v3 2026-07-29 Story 10 S10-R7 (+ context note))</t>
         </is>
       </c>
       <c r="I459" s="2" t="inlineStr"/>
@@ -24202,7 +24202,7 @@
       </c>
       <c r="H466" s="2" t="inlineStr">
         <is>
-          <t>SV-8679 (specs/inventory-value.md Story 12 S12-R1)</t>
+          <t>SV-8679 (IV spec v3 2026-07-29 Story 12 S12-R1)</t>
         </is>
       </c>
       <c r="I466" s="2" t="inlineStr"/>
@@ -24251,7 +24251,7 @@
       </c>
       <c r="H467" s="2" t="inlineStr">
         <is>
-          <t>SV-8679 (specs/inventory-value.md Story 12 S12-R2; S12-R3)</t>
+          <t>SV-8679 (IV spec v3 2026-07-29 Story 12 S12-R2; S12-R3)</t>
         </is>
       </c>
       <c r="I467" s="2" t="inlineStr"/>

--- a/testrail-import/report-suite-v1-testrail-import.xlsx
+++ b/testrail-import/report-suite-v1-testrail-import.xlsx
@@ -530,8 +530,6 @@
 4. The browser tab title reads "Sales By Customer - Report | ShopView".
 5. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-R1, S1-R3, S1-R4).</t>
         </is>
       </c>
@@ -839,8 +837,6 @@
 2. It offers eleven options, in this order: Today, Yesterday, This Week, Last Week, This Month, Last Month, This Year, Last Year, This Quarter, Last Quarter, Custom.
 3. There is no "All Time" option.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R1, S2-R2).</t>
         </is>
       </c>
@@ -891,8 +887,6 @@
 2. A range of 366 days or fewer applies normally.
 3. A range wider than 366 days cannot be applied — the report prevents the selection rather than loading the wider range.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R3, S2-R4, S2-N2).</t>
         </is>
       </c>
@@ -1049,8 +1043,6 @@
 4. Activating "All locations" selects every listed location at once; activating it again clears them all at once.
 5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's data.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R1, S4-R2, S4-R3); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -1164,8 +1156,6 @@
 6. With a single location in scope the Location column is hidden and the surrounding columns close up with no gap.
 7. Every one of the four downloads also contains the Location column, in the same position it holds on screen, showing the same values you just read: a location name on a row whose invoices are all at one location, "Multiple" on a row that aggregates more than one, and the invoice's own location on an invoice row. (Exactly where the column sits inside each file is confirmed in the build.)
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R12, S4-R12a, S4-R13, S20-R19).</t>
         </is>
       </c>
@@ -2178,8 +2168,6 @@
 4. For asset (d) (no VIN, Unit #, or plate), note what the label shows - what stands in when all three are missing is confirmed in the build (the older rule showed "Unknown Asset").
 5. Note whether the year/make/model text still appears anywhere in the row - the update says the VIN identifier REPLACES the year/make/model label; confirm the exact rendering in the build.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R7, S8-R8, S8-R9, S8-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -3538,8 +3526,6 @@
 3. When no logo is available at all, the logo column is not rendered and the text column fills the full width.
 4. The logo is embedded in the PDF (renders offline, not loaded from a network address).
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18).</t>
         </is>
       </c>
@@ -3746,8 +3732,6 @@
 4. All four files reflect exactly the filtered data shown on screen.
 5. With a single location in scope the Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When more than one location is in scope a Location column is added with the identifying columns, ahead of the money columns (the Summary files have no Date column for it to follow — confirm its exact position in the build).
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13).</t>
         </is>
       </c>
@@ -4132,8 +4116,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with data on screen.
-2. To slow the load enough to watch this, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Slow 3G". There is nothing to install. Set it back to "No throttling" when you finish.</t>
+          <t>1. You are on the report with data on screen.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -4152,14 +4135,13 @@
 3. The same empty state appears whichever filter caused it (date range, Product Type, or location).
 4. The header-row chevron is hidden when the table has no visible rows.
 5. With a narrowed customer selection and no data, the empty state shows but the selection is KEPT (not cleared) — when the filters change back, the selected customers reappear.
-6. While the table is still loading, the empty-state message is NOT shown (the loading state is shown instead); it appears only once loading has finished and there are zero customers.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1, S17-N1).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1).</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>SV-8615 (SBC spec v13 2026-07-31 Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1; Story 17 S17-N1)</t>
+          <t>SV-8615 (SBC spec v13 2026-07-31 Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1)</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -4314,8 +4296,6 @@
 4. The pinned Subtotal cell on any row uses that row's own background — never a contrasting strip.
 5. The three tree levels show by indentation: customer at the base, asset rows one level in (chevron and vehicle icon sit in from the customer), invoice rows one level deeper.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14).</t>
         </is>
       </c>
@@ -5071,8 +5051,6 @@
 2. The standard presets are offered: Today, Yesterday, This Week, This Month, Last Month, This Year, Last Year, This Quarter, Last Quarter, Custom.
 3. There is no "All Time" option (removed by the 2026-07-16 spec round).
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S2-R1, S2-R2).</t>
         </is>
       </c>
@@ -5577,8 +5555,6 @@
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -5641,8 +5617,6 @@
 7. With a single location in scope the Location column is hidden.
 8. All four downloads include the Location column in the same position it occupies on screen. In the Summary files a rep's row carries that rep's location and reads "Multiple" when the rep spans more than one location; in the Expanded View files each invoice row carries that invoice's own exact location.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-R7, S21-R8, S18-R13, S14-R20).</t>
         </is>
       </c>
@@ -8295,8 +8269,6 @@
 4. Subtotal is bolded across the header, the body rows, and the grand totals row; Inv. Hrs keeps its green/red/default coloring.
 5. The grand totals row reads "Totals" in the Rep cell and aggregates every summary row in the document (including the Unassigned row when Show Unassigned is on); its Margin % is RECOMPUTED as total Margin ÷ total Subtotal (shown "—" when that Subtotal is zero or below), never the sum or average of the rows' percentages.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R3, S14-R5, S14-R20, S2-R5).</t>
         </is>
       </c>
@@ -8351,8 +8323,6 @@
 5. Each block ends with a per-rep totals row — "Totals" in the Date cell; Invoice/Customer/Status blank; each metric aggregated; Margin % recomputed.
 6. There is NO grand-totals row across all reps at the end of the document.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R6, S14-R8, S14-R20, S6-R9).</t>
         </is>
       </c>
@@ -8609,8 +8579,6 @@
 6. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 7. When more than one location is in scope the file also carries a Location column, with the identifying columns ahead of the metric columns; a rep whose invoices span more than one location reads "Multiple". (This file has no Status column for it to follow — confirm its exact position in the build.)
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R15, S14-R18, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -8663,8 +8631,6 @@
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 5. When more than one location is in scope the file also carries a Location column immediately after Status — the position it holds on screen — and every row shows that invoice's own exact location, never "Multiple".
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R16, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -9844,8 +9810,6 @@
 4. The selector is NOT present in History mode.
 5. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R1, S19-N1).</t>
         </is>
       </c>
@@ -10100,8 +10064,6 @@
 3. On the WO, the selector renders the bound rep's name with an "(Inactive)" indicator so the current assignment stays visible — but that rep is NOT offered as a new selection in the list.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R7, S19-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -10818,8 +10780,6 @@
 3. Selecting a non-custom option immediately reloads the report data.
 4. The named ranges use the application's standard shared calendar boundaries (the same boundaries every report's date picker uses).
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R2).</t>
         </is>
       </c>
@@ -11335,8 +11295,6 @@
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-E4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -12516,14 +12474,13 @@
 2. After the reversal, Demand is STILL 2 - a reversal event neither adds to nor subtracts from the count (while Units Sold nets down).
 3. The special-order part's Demand is 2 - the count of its in-window vendor part requests.
 4. Demand is the report's default ranking signal (a whole number, never null - 0 when none).
-5. A part whose single in-window sale is invoiced and then fully reversed shows Demand 1 with Units Sold 0.00 — the Demand count is not decremented, while the movement nets to zero.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4, S3-E1).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4).</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Demand); §4; §3 Key Decisions; S3-E1)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Demand); §4; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr"/>
@@ -13347,8 +13304,6 @@
 4. Part # is NOT truncated.
 5. The shop logo shows at the top of the PDF when one is set. With no uploaded logo the PDF shows the bundled ShopView default logo instead of a blank space, the same as the other reports in this suite. The CSV never includes a logo.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6).</t>
         </is>
       </c>
@@ -13399,8 +13354,6 @@
 2. The CSV carries the FULL, untruncated Description / Category / Vendor values (unlike the PDF's 18-character cut).
 3. Last Sale is a raw integer in the CSV (e.g. 42) - the 'N days' wording is PDF/on-screen only.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6, S6-R8).</t>
         </is>
       </c>
@@ -16144,8 +16097,6 @@
 2. The menu holds: "Download Summary (PDF)", "Download Expanded View (PDF)", and "Download (CSV)".
 3. The labels match exactly - only the expanded option carries the word "View" (the shipped strings, documented as-is).
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R1, S7-R2, S7-R3, S7-R4, S8-R2).</t>
         </is>
       </c>
@@ -16195,8 +16146,6 @@
 2. The Expanded PDF shows the technician rows, EACH technician's per-day breakdown, and the Summary row; it downloads as "Technician-Utilization-Expanded.pdf".
 3. The PDF filenames are Title-Case as shipped.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R5, S7-R6, S7-R12).</t>
         </is>
       </c>
@@ -16402,8 +16351,6 @@
 2. The CSV never includes the logo.
 3. With NO uploaded logo, the PDF views show the bundled ShopView logo instead — not a blank space and not an error.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R11, S7-N2, S7-N3).</t>
         </is>
       </c>
@@ -16453,8 +16400,6 @@
           <t>1. Nothing happens: NO file downloads and NO message appears (not even an error).
 2. This silent no-op is the specified behavior for every download option when no technician is selected.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-N1).</t>
         </is>
       </c>
@@ -16712,14 +16657,13 @@
           <t>1. Any saved location the user can no longer access is DROPPED from the restored selection; the remaining accessible locations restore normally.
 2. If the remaining set is empty, the report falls back to the user's currently active location (the first-visit default).
 3. The report loads without an error in both cases.
-4. The same fallback happens when you deselect every location by hand in the Location filter — the report loads the currently active location's rows rather than showing nothing.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R6, S1-R8, S9-R2, S9-R7).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R6, S1-R8, S9-R2).</t>
         </is>
       </c>
       <c r="H319" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (TU spec v5 2026-07-29 S9-R6; S1-R8; S9-R2; S9-R7)</t>
+          <t>SV-8656 (TU spec v5 2026-07-29 S9-R6; S1-R8; S9-R2)</t>
         </is>
       </c>
       <c r="I319" s="2" t="inlineStr"/>
@@ -16763,8 +16707,6 @@
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -17197,14 +17139,13 @@
           <t>1. Four tabs are shown, labeled in this order: "Approved - Partially Completed", "Approved - Not Started", "Completed", and "Estimates" - each followed by its count in brackets, for example "Completed (30)".
 2. The "Approved - Partially Completed" tab is selected by default on load.
 3. There is NO on-screen status filter — the four tabs take the place of a status filter (the tab a job lands in is derived from its status and whether any work has started).
-4. Each tab's count matches the number of work-order rows actually listed in that tab.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-R2, S1-R3, S1-R4).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-R2, S1-R3).</t>
         </is>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (WIP spec v6 2026-07-29 Story 1 S1-R2; S1-R3; §3 Key Decisions (no on-screen status filter) — S1-R2 CLOSES the four tab labels and their order verbatim; so the closed list IS the requirement; Story 1 S1-R4)</t>
+          <t>SV-8657 (WIP spec v6 2026-07-29 Story 1 S1-R2; S1-R3; §3 Key Decisions (no on-screen status filter) — S1-R2 CLOSES the four tab labels and their order verbatim; so the closed list IS the requirement)</t>
         </is>
       </c>
       <c r="I328" s="2" t="inlineStr"/>
@@ -17654,8 +17595,6 @@
 2. WO #, Status, Customer, Asset, VIN, Location, and Advisor are left-aligned.
 3. Every other column (Days Open, Last Activity, and all money/number columns through Total) is right-aligned.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R1, S4-R3, S4-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
@@ -17707,8 +17646,6 @@
 3. Location IS offered in the column-selection control, between VIN and Advisor, and is off by default. Turning it on adds a Location column that names each job's location; turning it off removes it again.
 4. Note for the tester: the Location column does NOT appear on its own when you have more than one location selected - you have to switch it on yourself. That is what the build does today.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R2, S4-R3, S8-R3, S8-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
@@ -17863,8 +17800,6 @@
 4. The VIN column (off by default) shows the VIN on its own line as a separate, sortable column.
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R7, S4-R8, S4-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -18692,8 +18627,6 @@
 4. The Asset column sorts by the identifier it shows - the VIN, falling back to Unit #, then plate.
 5. WO #, Customer, Asset, VIN, Location, and Advisor sort as text.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R27, S4-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -18995,8 +18928,6 @@
 2. It is shown in a muted style.
 3. The Estimates figure is excluded from Total Earned and from Total Remaining.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R8, S5-R9).</t>
         </is>
       </c>
@@ -19314,8 +19245,6 @@
 4. Selecting assets narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one asset is selected and returns the filter to "All assets".
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R4, S7-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -19365,8 +19294,6 @@
 2. The options offered are: "Today", "Yesterday", "This Week", "Last Week", "This Month", "Last Month", "This Year", "Last Year", "This Quarter", "Last Quarter", and "Custom".
 3. "All Time" is NOT offered.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R6).</t>
         </is>
       </c>
@@ -19419,8 +19346,6 @@
 3. A range longer than about a year is refused with the message "Date range cannot be over one year." and the wider range is not loaded.
 4. Note for the tester: on this build the exact cut-off sits one day later than the specification says (a 367-day span is accepted, 368 is refused). Record what you see; the one-day difference is already known and is with the product owner.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R7, S7-R8).</t>
         </is>
       </c>
@@ -19477,8 +19402,6 @@
 4. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
 5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's work orders.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R9, S7-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -19641,8 +19564,6 @@
 6. In both downloads the column is headed "Branch" (a known naming difference from the screen — do not raise it as a bug).
 7. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
@@ -20204,8 +20125,6 @@
 3. This on-screen-vs-export label difference is the EXPECTED, documented v1 behavior.
 4. Note: the on-screen Asset cell now identifies the asset by its VIN (falling back to Unit #, then plate); whether the export header text changes from "Unit" is confirmed in the build - record what it shows, do not file a bug either way.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -20412,7 +20331,7 @@
       </c>
       <c r="H390" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R1)</t>
+          <t>SV-8666 (specs/wip-work-in-progress.md Story 10 S10-R1)</t>
         </is>
       </c>
       <c r="I390" s="2" t="inlineStr"/>
@@ -20857,14 +20776,13 @@
           <t>1. Once per day the system records one row per then-open work order — one row per work order per calendar date.
 2. The next day's capture adds a new row per open work order under the new date; a work order open on both days has one row for each date, never two rows for the same date.
 3. Re-running the capture for the SAME date replaces that date's rows — the day's existing rows are removed and re-recorded from current data, never duplicated.
-4. Each snapshot row captures, at minimum: the work order, its status, its Earned value, its Remaining value, the location and organization (copied from the work order), and the snapshot's calendar date.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R1, S11-R2).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R1).</t>
         </is>
       </c>
       <c r="H399" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs); Story 11 S11-R2)</t>
+          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs))</t>
         </is>
       </c>
       <c r="I399" s="2" t="inlineStr"/>
@@ -20895,8 +20813,7 @@
         <is>
           <t>1. An open ZZAUTOTEST work order with known approved labor (partly clocked) and approved parts (partly received) exists and is left UNCHANGED across the capture.
 2. You can read the on-screen report on the capture date and the stored snapshot row afterward.
-3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.
-4. The work order's Earned/Remaining include non-round cent values (for example $123.45), so lost cents would be visible.</t>
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
         </is>
       </c>
       <c r="F400" s="2" t="inlineStr">
@@ -20909,14 +20826,13 @@
       <c r="G400" s="2" t="inlineStr">
         <is>
           <t>1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation for both figures, so the two can never diverge for a given work order on the capture date.
-2. The captured dollar values are stored to the cent — no rounding to whole dollars and no lost cents.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R3, S11-R5).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R3).</t>
         </is>
       </c>
       <c r="H400" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R3; Story 11 S11-R5)</t>
+          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R3)</t>
         </is>
       </c>
       <c r="I400" s="2" t="inlineStr"/>
@@ -21168,7 +21084,7 @@
       </c>
       <c r="H405" s="2" t="inlineStr">
         <is>
-          <t>SV-8668 (IV spec v3 2026-07-29 Story 1 S1-R3; Story 7 S7-R2)</t>
+          <t>SV-8668 (specs/inventory-value.md Story 1 S1-R3; Story 7 S7-R2)</t>
         </is>
       </c>
       <c r="I405" s="2" t="inlineStr"/>
@@ -21316,14 +21232,13 @@
 2. The core-charge part is never listed — even with a positive quantity — and its value is not counted in the totals row.
 3. The zero-quantity and negative-quantity parts are not listed — only quantities greater than zero are valued.
 4. Only parts meeting BOTH conditions — not a core charge, and on-hand quantity greater than zero — are listed.
-5. A part that has sat without movement for a long time still appears and is still counted — there is no dead-stock exclusion; how long stock has sat makes no difference.
 ---
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S2-R1, S2-R2, S2-N1, S2-N2).</t>
         </is>
       </c>
       <c r="H408" s="2" t="inlineStr">
         <is>
-          <t>SV-8669 (IV spec v3 2026-07-29 Story 2 S2-R1; S2-R2; S2-N1; S2-N2; §3 Key Decisions; Story 2 context note (no dead-stock exclusion))</t>
+          <t>SV-8669 (IV spec v3 2026-07-29 Story 2 S2-R1; S2-R2; S2-N1; S2-N2; §3 Key Decisions)</t>
         </is>
       </c>
       <c r="I408" s="2" t="inlineStr"/>
@@ -21724,8 +21639,6 @@
 3. Every other column is right-aligned.
 4. Location is one of the columns in the column-selection control; when it is turned on the Location column appears between Vendor and Qty, left-aligned.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R1, S3-R2, S7-R6); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
@@ -21878,8 +21791,6 @@
 3. Both can be turned on from the column-selection control and then appear in their fixed positions.
 4. Location is one of the columns in the column-selection control; when it is turned on the Location column shows between Vendor and Qty.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R12, S3-R13, S8-R3, S7-R6); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
@@ -21986,14 +21897,13 @@
 3. The totals-row Total Cost cell is pinned far right and bold, matching the column, and the row uses the same number formats as the data rows.
 4. The totals row stays visible at the bottom while the rows scroll.
 5. Note for the tester: if the label on screen reads "Totals" instead of "Total", mark this test Failed and report it — do not change the test.
-6. Sorting by any column reorders the data rows only — the totals row stays at the bottom.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S4-R1, S4-R4, S4-R5, S4-R6, S4-R7, S12-R5, S9-R4).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S4-R1, S4-R4, S4-R5, S4-R6, S4-R7, S12-R5).</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
         <is>
-          <t>SV-8671 (IV spec v3 2026-07-29 Story 4 S4-R1; S4-R4; S4-R5; S4-R6; S4-R7; Story 12 S12-R5; Story 9 S9-R4)</t>
+          <t>SV-8671 (IV spec v3 2026-07-29 Story 4 S4-R1; S4-R4; S4-R5; S4-R6; S4-R7; Story 12 S12-R5)</t>
         </is>
       </c>
       <c r="I421" s="2" t="inlineStr"/>
@@ -22144,8 +22054,6 @@
           <t>1. The control offers the standard presets: "Today", "Yesterday", "This Week", "Last Week", "This Month", "Last Month", "This Year", "Last Year", "This Quarter", "Last Quarter", and "Custom".
 2. "All Time" is NOT offered — because the report is valued as of a single date, an All-Time option would be meaningless; its absence is the documented v1 behavior.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S5-R1).</t>
         </is>
       </c>
@@ -22299,8 +22207,6 @@
 2. The part's row shows the quantity and values recorded for that day, not today's live stock.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8820
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S5-R4).</t>
         </is>
       </c>
@@ -22357,7 +22263,7 @@
       </c>
       <c r="H428" s="2" t="inlineStr">
         <is>
-          <t>SV-8672 (IV spec v3 2026-07-29 Story 5 S5-R5; S5-R6)</t>
+          <t>SV-8672 (specs/inventory-value.md Story 5 S5-R5; S5-R6)</t>
         </is>
       </c>
       <c r="I428" s="2" t="inlineStr"/>
@@ -22820,7 +22726,7 @@
       </c>
       <c r="H437" s="2" t="inlineStr">
         <is>
-          <t>SV-8674 (IV spec v3 2026-07-29 Story 7 S7-R1; S7-R2; Story 12 S12-R3 — per-row location identifier in All-locations view ADDED per kickoff video P10 40:58-41:20; user ruling 2026-07-28: video overrides spec (video newer; last-update-wins))</t>
+          <t>SV-8674 (specs/inventory-value.md Story 7 S7-R1; S7-R2; Story 12 S12-R3 — per-row location identifier in All-locations view ADDED per kickoff video P10 40:58-41:20; user ruling 2026-07-28: video overrides spec (video newer; last-update-wins))</t>
         </is>
       </c>
       <c r="I437" s="2" t="inlineStr"/>
@@ -22964,8 +22870,6 @@
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's stock.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S7-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -23026,8 +22930,6 @@
 6. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
 7. Both downloads include the Location column in the same position it holds on screen (between Vendor and Qty), naming each row's own location.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S7-R6, S7-R7, S3-R1, S12-R10, S10-R15); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
@@ -23128,8 +23030,6 @@
           <t>1. Whatever columns are shown, they appear in the fixed left-to-right order - with Location, when it is turned on in the column-selection control, between Vendor and Qty (Part #, Description, Category, Vendor, Qty, Unit Cost, Unit Sell, Margin, Margin %, Total Sell, Total Cost) - toggling visibility never reorders columns.
 2. Total Cost is always the last column.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S8-R4, S3-R1, S7-R6); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
@@ -23486,8 +23386,6 @@
 4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
 5. Note for the tester: the files carry the Location column when Location is turned ON in the column-selection control (it sits between Vendor and Qty). It does not appear just because you have more than one location selected.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S10-R3, S10-R4, S10-R5, S10-R6, S10-R15); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
@@ -23543,7 +23441,7 @@
       </c>
       <c r="H451" s="2" t="inlineStr">
         <is>
-          <t>SV-8677 (IV spec v3 2026-07-29 Story 10 S10-R7 (+ context note))</t>
+          <t>SV-8677 (specs/inventory-value.md Story 10 S10-R7 (+ context note))</t>
         </is>
       </c>
       <c r="I451" s="2" t="inlineStr"/>
@@ -23592,8 +23490,6 @@
 3. The CSV never includes a logo.
 4. Note for the tester: the two files phrase the as-of line differently - the PDF reads "As of 2026-08-04" and the CSV's first line reads "As of: 2026-08-04" (with a colon). Both are correct; do not raise the difference.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S10-R8, S10-R9).</t>
         </is>
       </c>
@@ -23912,7 +23808,7 @@
       </c>
       <c r="H458" s="2" t="inlineStr">
         <is>
-          <t>SV-8679 (IV spec v3 2026-07-29 Story 12 S12-R1)</t>
+          <t>SV-8679 (specs/inventory-value.md Story 12 S12-R1)</t>
         </is>
       </c>
       <c r="I458" s="2" t="inlineStr"/>
@@ -23961,7 +23857,7 @@
       </c>
       <c r="H459" s="2" t="inlineStr">
         <is>
-          <t>SV-8679 (IV spec v3 2026-07-29 Story 12 S12-R2; S12-R3)</t>
+          <t>SV-8679 (specs/inventory-value.md Story 12 S12-R2; S12-R3)</t>
         </is>
       </c>
       <c r="I459" s="2" t="inlineStr"/>
@@ -24416,16 +24312,13 @@
           <t>1. Re-running the capture for a date replaces that date's rows for each location — the existing rows for that location and date are removed, then re-inserted from current data.
 2. No duplicate rows exist for the same part, location, and date.
 3. The capture is idempotent and self-healing from current data.
-4. No rows exist for dates before capture began — there is no backfill.
-5. A re-run always records current truth under the CURRENT date; it cannot reconstruct a past date.
-6. A past date's stored rows are unchanged by a current re-run.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S11-R3, S11-R5, S5-E1).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S11-R3).</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
         <is>
-          <t>SV-8678 (IV spec v3 2026-07-29 Story 11 S11-R3; Story 11 S11-R5; Story 5 S5-E1)</t>
+          <t>SV-8678 (IV spec v3 2026-07-29 Story 11 S11-R3)</t>
         </is>
       </c>
       <c r="I468" s="2" t="inlineStr"/>

--- a/testrail-import/report-suite-v1-testrail-import.xlsx
+++ b/testrail-import/report-suite-v1-testrail-import.xlsx
@@ -530,6 +530,8 @@
 4. The browser tab title reads "Sales By Customer - Report | ShopView".
 5. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-R1, S1-R3, S1-R4).</t>
         </is>
       </c>
@@ -837,6 +839,8 @@
 2. It offers eleven options, in this order: Today, Yesterday, This Week, Last Week, This Month, Last Month, This Year, Last Year, This Quarter, Last Quarter, Custom.
 3. There is no "All Time" option.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R1, S2-R2).</t>
         </is>
       </c>
@@ -887,6 +891,8 @@
 2. A range of 366 days or fewer applies normally.
 3. A range wider than 366 days cannot be applied — the report prevents the selection rather than loading the wider range.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R3, S2-R4, S2-N2).</t>
         </is>
       </c>
@@ -1043,6 +1049,8 @@
 4. Activating "All locations" selects every listed location at once; activating it again clears them all at once.
 5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's data.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R1, S4-R2, S4-R3); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -1156,6 +1164,8 @@
 6. With a single location in scope the Location column is hidden and the surrounding columns close up with no gap.
 7. Every one of the four downloads also contains the Location column, in the same position it holds on screen, showing the same values you just read: a location name on a row whose invoices are all at one location, "Multiple" on a row that aggregates more than one, and the invoice's own location on an invoice row. (Exactly where the column sits inside each file is confirmed in the build.)
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R12, S4-R12a, S4-R13, S20-R19).</t>
         </is>
       </c>
@@ -2168,6 +2178,8 @@
 4. For asset (d) (no VIN, Unit #, or plate), note what the label shows - what stands in when all three are missing is confirmed in the build (the older rule showed "Unknown Asset").
 5. Note whether the year/make/model text still appears anywhere in the row - the update says the VIN identifier REPLACES the year/make/model label; confirm the exact rendering in the build.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R7, S8-R8, S8-R9, S8-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -3526,6 +3538,8 @@
 3. When no logo is available at all, the logo column is not rendered and the text column fills the full width.
 4. The logo is embedded in the PDF (renders offline, not loaded from a network address).
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18).</t>
         </is>
       </c>
@@ -3732,6 +3746,8 @@
 4. All four files reflect exactly the filtered data shown on screen.
 5. With a single location in scope the Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When more than one location is in scope a Location column is added with the identifying columns, ahead of the money columns (the Summary files have no Date column for it to follow — confirm its exact position in the build).
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13).</t>
         </is>
       </c>
@@ -4116,7 +4132,8 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>1. You are on the report with data on screen.</t>
+          <t>1. You are on the report with data on screen.
+2. To slow the load enough to watch this, use the browser's own developer tools: press F12, open the "Network" tab, and switch the throttling dropdown (it normally reads "No throttling") to "Slow 3G". There is nothing to install. Set it back to "No throttling" when you finish.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -4135,13 +4152,14 @@
 3. The same empty state appears whichever filter caused it (date range, Product Type, or location).
 4. The header-row chevron is hidden when the table has no visible rows.
 5. With a narrowed customer selection and no data, the empty state shows but the selection is KEPT (not cleared) — when the filters change back, the selected customers reappear.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1).</t>
+6. While the table is still loading, the empty-state message is NOT shown (the loading state is shown instead); it appears only once loading has finished and there are zero customers.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1, S17-N1).</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>SV-8615 (SBC spec v13 2026-07-31 Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1)</t>
+          <t>SV-8615 (SBC spec v13 2026-07-31 Story 17 S17-R1; S17-R2; S17-R3; S17-E1; Story 2 S2-N1; Story 3 S3-N1; Story 4 S4-N2; Story 8 S8-N1; Story 17 S17-N1)</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr"/>
@@ -4296,6 +4314,8 @@
 4. The pinned Subtotal cell on any row uses that row's own background — never a contrasting strip.
 5. The three tree levels show by indentation: customer at the base, asset rows one level in (chevron and vehicle icon sit in from the customer), invoice rows one level deeper.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14).</t>
         </is>
       </c>
@@ -5051,6 +5071,8 @@
 2. The standard presets are offered: Today, Yesterday, This Week, This Month, Last Month, This Year, Last Year, This Quarter, Last Quarter, Custom.
 3. There is no "All Time" option (removed by the 2026-07-16 spec round).
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S2-R1, S2-R2).</t>
         </is>
       </c>
@@ -5555,6 +5577,8 @@
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -5617,6 +5641,8 @@
 7. With a single location in scope the Location column is hidden.
 8. All four downloads include the Location column in the same position it occupies on screen. In the Summary files a rep's row carries that rep's location and reads "Multiple" when the rep spans more than one location; in the Expanded View files each invoice row carries that invoice's own exact location.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-R7, S21-R8, S18-R13, S14-R20).</t>
         </is>
       </c>
@@ -8269,6 +8295,8 @@
 4. Subtotal is bolded across the header, the body rows, and the grand totals row; Inv. Hrs keeps its green/red/default coloring.
 5. The grand totals row reads "Totals" in the Rep cell and aggregates every summary row in the document (including the Unassigned row when Show Unassigned is on); its Margin % is RECOMPUTED as total Margin ÷ total Subtotal (shown "—" when that Subtotal is zero or below), never the sum or average of the rows' percentages.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R3, S14-R5, S14-R20, S2-R5).</t>
         </is>
       </c>
@@ -8323,6 +8351,8 @@
 5. Each block ends with a per-rep totals row — "Totals" in the Date cell; Invoice/Customer/Status blank; each metric aggregated; Margin % recomputed.
 6. There is NO grand-totals row across all reps at the end of the document.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R6, S14-R8, S14-R20, S6-R9).</t>
         </is>
       </c>
@@ -8579,6 +8609,8 @@
 6. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 7. When more than one location is in scope the file also carries a Location column, with the identifying columns ahead of the metric columns; a rep whose invoices span more than one location reads "Multiple". (This file has no Status column for it to follow — confirm its exact position in the build.)
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R15, S14-R18, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -8631,6 +8663,8 @@
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 5. When more than one location is in scope the file also carries a Location column immediately after Status — the position it holds on screen — and every row shows that invoice's own exact location, never "Multiple".
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R16, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -9810,6 +9844,8 @@
 4. The selector is NOT present in History mode.
 5. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R1, S19-N1).</t>
         </is>
       </c>
@@ -10064,6 +10100,8 @@
 3. On the WO, the selector renders the bound rep's name with an "(Inactive)" indicator so the current assignment stays visible — but that rep is NOT offered as a new selection in the list.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R7, S19-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -10780,6 +10818,8 @@
 3. Selecting a non-custom option immediately reloads the report data.
 4. The named ranges use the application's standard shared calendar boundaries (the same boundaries every report's date picker uses).
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R2).</t>
         </is>
       </c>
@@ -11295,6 +11335,8 @@
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-E4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -12474,13 +12516,14 @@
 2. After the reversal, Demand is STILL 2 - a reversal event neither adds to nor subtracts from the count (while Units Sold nets down).
 3. The special-order part's Demand is 2 - the count of its in-window vendor part requests.
 4. Demand is the report's default ranking signal (a whole number, never null - 0 when none).
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4).</t>
+5. A part whose single in-window sale is invoiced and then fully reversed shows Demand 1 with Units Sold 0.00 — the Demand count is not decremented, while the movement nets to zero.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4, S3-E1).</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Demand); §4; §3 Key Decisions)</t>
+          <t>SV-8645 (PV spec v4 2026-07-29 S5-R4 (Demand); §4; §3 Key Decisions; S3-E1)</t>
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr"/>
@@ -13304,6 +13347,8 @@
 4. Part # is NOT truncated.
 5. The shop logo shows at the top of the PDF when one is set. With no uploaded logo the PDF shows the bundled ShopView default logo instead of a blank space, the same as the other reports in this suite. The CSV never includes a logo.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6).</t>
         </is>
       </c>
@@ -13354,6 +13399,8 @@
 2. The CSV carries the FULL, untruncated Description / Category / Vendor values (unlike the PDF's 18-character cut).
 3. Last Sale is a raw integer in the CSV (e.g. 42) - the 'N days' wording is PDF/on-screen only.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6, S6-R8).</t>
         </is>
       </c>
@@ -16097,6 +16144,8 @@
 2. The menu holds: "Download Summary (PDF)", "Download Expanded View (PDF)", and "Download (CSV)".
 3. The labels match exactly - only the expanded option carries the word "View" (the shipped strings, documented as-is).
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R1, S7-R2, S7-R3, S7-R4, S8-R2).</t>
         </is>
       </c>
@@ -16146,6 +16195,8 @@
 2. The Expanded PDF shows the technician rows, EACH technician's per-day breakdown, and the Summary row; it downloads as "Technician-Utilization-Expanded.pdf".
 3. The PDF filenames are Title-Case as shipped.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R5, S7-R6, S7-R12).</t>
         </is>
       </c>
@@ -16351,6 +16402,8 @@
 2. The CSV never includes the logo.
 3. With NO uploaded logo, the PDF views show the bundled ShopView logo instead — not a blank space and not an error.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R11, S7-N2, S7-N3).</t>
         </is>
       </c>
@@ -16400,6 +16453,8 @@
           <t>1. Nothing happens: NO file downloads and NO message appears (not even an error).
 2. This silent no-op is the specified behavior for every download option when no technician is selected.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-N1).</t>
         </is>
       </c>
@@ -16657,13 +16712,14 @@
           <t>1. Any saved location the user can no longer access is DROPPED from the restored selection; the remaining accessible locations restore normally.
 2. If the remaining set is empty, the report falls back to the user's currently active location (the first-visit default).
 3. The report loads without an error in both cases.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R6, S1-R8, S9-R2).</t>
+4. The same fallback happens when you deselect every location by hand in the Location filter — the report loads the currently active location's rows rather than showing nothing.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R6, S1-R8, S9-R2, S9-R7).</t>
         </is>
       </c>
       <c r="H319" s="2" t="inlineStr">
         <is>
-          <t>SV-8656 (TU spec v5 2026-07-29 S9-R6; S1-R8; S9-R2)</t>
+          <t>SV-8656 (TU spec v5 2026-07-29 S9-R6; S1-R8; S9-R2; S9-R7)</t>
         </is>
       </c>
       <c r="I319" s="2" t="inlineStr"/>
@@ -16707,6 +16763,8 @@
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -17139,13 +17197,14 @@
           <t>1. Four tabs are shown, labeled in this order: "Approved - Partially Completed", "Approved - Not Started", "Completed", and "Estimates" - each followed by its count in brackets, for example "Completed (30)".
 2. The "Approved - Partially Completed" tab is selected by default on load.
 3. There is NO on-screen status filter — the four tabs take the place of a status filter (the tab a job lands in is derived from its status and whether any work has started).
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-R2, S1-R3).</t>
+4. Each tab's count matches the number of work-order rows actually listed in that tab.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-R2, S1-R3, S1-R4).</t>
         </is>
       </c>
       <c r="H328" s="2" t="inlineStr">
         <is>
-          <t>SV-8657 (WIP spec v6 2026-07-29 Story 1 S1-R2; S1-R3; §3 Key Decisions (no on-screen status filter) — S1-R2 CLOSES the four tab labels and their order verbatim; so the closed list IS the requirement)</t>
+          <t>SV-8657 (WIP spec v6 2026-07-29 Story 1 S1-R2; S1-R3; §3 Key Decisions (no on-screen status filter) — S1-R2 CLOSES the four tab labels and their order verbatim; so the closed list IS the requirement; Story 1 S1-R4)</t>
         </is>
       </c>
       <c r="I328" s="2" t="inlineStr"/>
@@ -17595,6 +17654,8 @@
 2. WO #, Status, Customer, Asset, VIN, Location, and Advisor are left-aligned.
 3. Every other column (Days Open, Last Activity, and all money/number columns through Total) is right-aligned.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R1, S4-R3, S4-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
@@ -17646,6 +17707,8 @@
 3. Location IS offered in the column-selection control, between VIN and Advisor, and is off by default. Turning it on adds a Location column that names each job's location; turning it off removes it again.
 4. Note for the tester: the Location column does NOT appear on its own when you have more than one location selected - you have to switch it on yourself. That is what the build does today.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R2, S4-R3, S8-R3, S8-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
@@ -17800,6 +17863,8 @@
 4. The VIN column (off by default) shows the VIN on its own line as a separate, sortable column.
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R7, S4-R8, S4-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -18627,6 +18692,8 @@
 4. The Asset column sorts by the identifier it shows - the VIN, falling back to Unit #, then plate.
 5. WO #, Customer, Asset, VIN, Location, and Advisor sort as text.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R27, S4-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -18928,6 +18995,8 @@
 2. It is shown in a muted style.
 3. The Estimates figure is excluded from Total Earned and from Total Remaining.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R8, S5-R9).</t>
         </is>
       </c>
@@ -19245,6 +19314,8 @@
 4. Selecting assets narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one asset is selected and returns the filter to "All assets".
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R4, S7-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -19294,6 +19365,8 @@
 2. The options offered are: "Today", "Yesterday", "This Week", "Last Week", "This Month", "Last Month", "This Year", "Last Year", "This Quarter", "Last Quarter", and "Custom".
 3. "All Time" is NOT offered.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R6).</t>
         </is>
       </c>
@@ -19346,6 +19419,8 @@
 3. A range longer than about a year is refused with the message "Date range cannot be over one year." and the wider range is not loaded.
 4. Note for the tester: on this build the exact cut-off sits one day later than the specification says (a 367-day span is accepted, 368 is refused). Record what you see; the one-day difference is already known and is with the product owner.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R7, S7-R8).</t>
         </is>
       </c>
@@ -19402,6 +19477,8 @@
 4. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
 5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's work orders.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R9, S7-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -19564,6 +19641,8 @@
 6. In both downloads the column is headed "Branch" (a known naming difference from the screen — do not raise it as a bug).
 7. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
@@ -20125,6 +20204,8 @@
 3. This on-screen-vs-export label difference is the EXPECTED, documented v1 behavior.
 4. Note: the on-screen Asset cell now identifies the asset by its VIN (falling back to Unit #, then plate); whether the export header text changes from "Unit" is confirmed in the build - record what it shows, do not file a bug either way.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -20331,7 +20412,7 @@
       </c>
       <c r="H390" s="2" t="inlineStr">
         <is>
-          <t>SV-8666 (specs/wip-work-in-progress.md Story 10 S10-R1)</t>
+          <t>SV-8666 (WIP spec v6 2026-07-29 Story 10 S10-R1)</t>
         </is>
       </c>
       <c r="I390" s="2" t="inlineStr"/>
@@ -20776,13 +20857,15 @@
           <t>1. Once per day the system records one row per then-open work order — one row per work order per calendar date.
 2. The next day's capture adds a new row per open work order under the new date; a work order open on both days has one row for each date, never two rows for the same date.
 3. Re-running the capture for the SAME date replaces that date's rows — the day's existing rows are removed and re-recorded from current data, never duplicated.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R1).</t>
+4. Each snapshot row captures, at minimum: the work order, its status, its Earned value, its Remaining value, the location and organization (copied from the work order), and the snapshot's calendar date.
+---
+Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R1, S11-R2).</t>
         </is>
       </c>
       <c r="H399" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs))</t>
+          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R1; tech-plan-2026-07-29 B1.2 (idempotent re-run — WIP spec Story 11 is silent on re-runs); Story 11 S11-R2)</t>
         </is>
       </c>
       <c r="I399" s="2" t="inlineStr"/>
@@ -20813,7 +20896,8 @@
         <is>
           <t>1. An open ZZAUTOTEST work order with known approved labor (partly clocked) and approved parts (partly received) exists and is left UNCHANGED across the capture.
 2. You can read the on-screen report on the capture date and the stored snapshot row afterward.
-3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.</t>
+3. To see the information this test asks for you need the browser's own developer tools: press F12 (or Ctrl+Shift+I; on a Mac Cmd+Option+I) and open the "Network" tab, then reload the page. There is nothing to install — it is built into Chrome, Edge and Firefox. Where a check also asks you to confirm what is stored on the server, ask a developer to read it back for you — that part cannot be seen from the browser.
+4. The work order's Earned/Remaining include non-round cent values (for example $123.45), so lost cents would be visible.</t>
         </is>
       </c>
       <c r="F400" s="2" t="inlineStr">
@@ -20826,13 +20910,15 @@
       <c r="G400" s="2" t="inlineStr">
         <is>
           <t>1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation for both figures, so the two can never diverge for a given work order on the capture date.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R3).</t>
+2. The captured dollar values are stored to the cent — no rounding to whole dollars and no lost cents.
+---
+Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R3, S11-R5).</t>
         </is>
       </c>
       <c r="H400" s="2" t="inlineStr">
         <is>
-          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R3)</t>
+          <t>SV-8667 (WIP spec v6 2026-07-29 Story 11 S11-R3; Story 11 S11-R5)</t>
         </is>
       </c>
       <c r="I400" s="2" t="inlineStr"/>
@@ -20880,6 +20966,7 @@
 2. The capture spans every location — there is no user-selected-location filter.
 3. Invoiced, Paid, and Declined work orders and part-sale work orders are not captured.
 ---
+Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R4, S2-R1).</t>
         </is>
       </c>
@@ -20930,6 +21017,7 @@
           <t>1. The work order IS captured (not skipped).
 2. Its Earned is $0.00 and its Remaining is $0.00, matching what the report shows on screen for a job with nothing approved.
 ---
+Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R6, S4-E1).</t>
         </is>
       </c>
@@ -21084,7 +21172,7 @@
       </c>
       <c r="H405" s="2" t="inlineStr">
         <is>
-          <t>SV-8668 (specs/inventory-value.md Story 1 S1-R3; Story 7 S7-R2)</t>
+          <t>SV-8668 (IV spec v3 2026-07-29 Story 1 S1-R3; Story 7 S7-R2)</t>
         </is>
       </c>
       <c r="I405" s="2" t="inlineStr"/>
@@ -21232,13 +21320,14 @@
 2. The core-charge part is never listed — even with a positive quantity — and its value is not counted in the totals row.
 3. The zero-quantity and negative-quantity parts are not listed — only quantities greater than zero are valued.
 4. Only parts meeting BOTH conditions — not a core charge, and on-hand quantity greater than zero — are listed.
+5. A part that has sat without movement for a long time still appears and is still counted — there is no dead-stock exclusion; how long stock has sat makes no difference.
 ---
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S2-R1, S2-R2, S2-N1, S2-N2).</t>
         </is>
       </c>
       <c r="H408" s="2" t="inlineStr">
         <is>
-          <t>SV-8669 (IV spec v3 2026-07-29 Story 2 S2-R1; S2-R2; S2-N1; S2-N2; §3 Key Decisions)</t>
+          <t>SV-8669 (IV spec v3 2026-07-29 Story 2 S2-R1; S2-R2; S2-N1; S2-N2; §3 Key Decisions; Story 2 context note (no dead-stock exclusion))</t>
         </is>
       </c>
       <c r="I408" s="2" t="inlineStr"/>
@@ -21639,6 +21728,8 @@
 3. Every other column is right-aligned.
 4. Location is one of the columns in the column-selection control; when it is turned on the Location column appears between Vendor and Qty, left-aligned.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R1, S3-R2, S7-R6); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
@@ -21791,6 +21882,8 @@
 3. Both can be turned on from the column-selection control and then appear in their fixed positions.
 4. Location is one of the columns in the column-selection control; when it is turned on the Location column shows between Vendor and Qty.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R12, S3-R13, S8-R3, S7-R6); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
@@ -21897,13 +21990,14 @@
 3. The totals-row Total Cost cell is pinned far right and bold, matching the column, and the row uses the same number formats as the data rows.
 4. The totals row stays visible at the bottom while the rows scroll.
 5. Note for the tester: if the label on screen reads "Totals" instead of "Total", mark this test Failed and report it — do not change the test.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S4-R1, S4-R4, S4-R5, S4-R6, S4-R7, S12-R5).</t>
+6. Sorting by any column reorders the data rows only — the totals row stays at the bottom.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S4-R1, S4-R4, S4-R5, S4-R6, S4-R7, S12-R5, S9-R4).</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
         <is>
-          <t>SV-8671 (IV spec v3 2026-07-29 Story 4 S4-R1; S4-R4; S4-R5; S4-R6; S4-R7; Story 12 S12-R5)</t>
+          <t>SV-8671 (IV spec v3 2026-07-29 Story 4 S4-R1; S4-R4; S4-R5; S4-R6; S4-R7; Story 12 S12-R5; Story 9 S9-R4)</t>
         </is>
       </c>
       <c r="I421" s="2" t="inlineStr"/>
@@ -22054,6 +22148,8 @@
           <t>1. The control offers the standard presets: "Today", "Yesterday", "This Week", "Last Week", "This Month", "Last Month", "This Year", "Last Year", "This Quarter", "Last Quarter", and "Custom".
 2. "All Time" is NOT offered — because the report is valued as of a single date, an All-Time option would be meaningless; its absence is the documented v1 behavior.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S5-R1).</t>
         </is>
       </c>
@@ -22207,6 +22303,8 @@
 2. The part's row shows the quantity and values recorded for that day, not today's live stock.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8820
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S5-R4).</t>
         </is>
       </c>
@@ -22263,7 +22361,7 @@
       </c>
       <c r="H428" s="2" t="inlineStr">
         <is>
-          <t>SV-8672 (specs/inventory-value.md Story 5 S5-R5; S5-R6)</t>
+          <t>SV-8672 (IV spec v3 2026-07-29 Story 5 S5-R5; S5-R6)</t>
         </is>
       </c>
       <c r="I428" s="2" t="inlineStr"/>
@@ -22726,7 +22824,7 @@
       </c>
       <c r="H437" s="2" t="inlineStr">
         <is>
-          <t>SV-8674 (specs/inventory-value.md Story 7 S7-R1; S7-R2; Story 12 S12-R3 — per-row location identifier in All-locations view ADDED per kickoff video P10 40:58-41:20; user ruling 2026-07-28: video overrides spec (video newer; last-update-wins))</t>
+          <t>SV-8674 (IV spec v3 2026-07-29 Story 7 S7-R1; S7-R2; Story 12 S12-R3 — per-row location identifier in All-locations view ADDED per kickoff video P10 40:58-41:20; user ruling 2026-07-28: video overrides spec (video newer; last-update-wins))</t>
         </is>
       </c>
       <c r="I437" s="2" t="inlineStr"/>
@@ -22870,6 +22968,8 @@
           <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's stock.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S7-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
@@ -22930,6 +23030,8 @@
 6. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
 7. Both downloads include the Location column in the same position it holds on screen (between Vendor and Qty), naming each row's own location.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S7-R6, S7-R7, S3-R1, S12-R10, S10-R15); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
@@ -23030,6 +23132,8 @@
           <t>1. Whatever columns are shown, they appear in the fixed left-to-right order - with Location, when it is turned on in the column-selection control, between Vendor and Qty (Part #, Description, Category, Vendor, Qty, Unit Cost, Unit Sell, Margin, Margin %, Total Sell, Total Cost) - toggling visibility never reorders columns.
 2. Total Cost is always the last column.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S8-R4, S3-R1, S7-R6); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
@@ -23386,6 +23490,9 @@
 4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
 5. Note for the tester: the files carry the Location column when Location is turned ON in the column-selection control (it sits between Vendor and Qty). It does not appear just because you have more than one location selected.
 ---
+Note for the tester: on this build the spreadsheet file ignores the columns you picked and puts them in a different order from the screen, so point 1 above will not match. That difference is already written up and a decision on it is pending - record what you see and carry on; you do not need to raise it again.
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S10-R3, S10-R4, S10-R5, S10-R6, S10-R15); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
@@ -23436,12 +23543,14 @@
 2. In the CSV, money values are written as plain numbers with two decimals and NO thousands separators (so they parse cleanly in a spreadsheet).
 3. The PDF uses the same on-screen currency formatting with the "$" and thousands separators.
 ---
+On this build the money in the spreadsheet file comes out as "$11,176.88" - with a dollar sign and a comma - instead of the plain number described in point 2 above.
+Known and accepted: the product behaves this way on purpose for now. Do not raise this as a new problem.
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S10-R7).</t>
         </is>
       </c>
       <c r="H451" s="2" t="inlineStr">
         <is>
-          <t>SV-8677 (specs/inventory-value.md Story 10 S10-R7 (+ context note))</t>
+          <t>SV-8677 (IV spec v3 2026-07-29 Story 10 S10-R7 (+ context note))</t>
         </is>
       </c>
       <c r="I451" s="2" t="inlineStr"/>
@@ -23490,6 +23599,8 @@
 3. The CSV never includes a logo.
 4. Note for the tester: the two files phrase the as-of line differently - the PDF reads "As of 2026-08-04" and the CSV's first line reads "As of: 2026-08-04" (with a colon). Both are correct; do not raise the difference.
 ---
+DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
+The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S10-R8, S10-R9).</t>
         </is>
       </c>
@@ -23808,7 +23919,7 @@
       </c>
       <c r="H458" s="2" t="inlineStr">
         <is>
-          <t>SV-8679 (specs/inventory-value.md Story 12 S12-R1)</t>
+          <t>SV-8679 (IV spec v3 2026-07-29 Story 12 S12-R1)</t>
         </is>
       </c>
       <c r="I458" s="2" t="inlineStr"/>
@@ -23857,7 +23968,7 @@
       </c>
       <c r="H459" s="2" t="inlineStr">
         <is>
-          <t>SV-8679 (specs/inventory-value.md Story 12 S12-R2; S12-R3)</t>
+          <t>SV-8679 (IV spec v3 2026-07-29 Story 12 S12-R2; S12-R3)</t>
         </is>
       </c>
       <c r="I459" s="2" t="inlineStr"/>
@@ -24312,13 +24423,16 @@
           <t>1. Re-running the capture for a date replaces that date's rows for each location — the existing rows for that location and date are removed, then re-inserted from current data.
 2. No duplicate rows exist for the same part, location, and date.
 3. The capture is idempotent and self-healing from current data.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S11-R3).</t>
+4. No rows exist for dates before capture began — there is no backfill.
+5. A re-run always records current truth under the CURRENT date; it cannot reconstruct a past date.
+6. A past date's stored rows are unchanged by a current re-run.
+---
+This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S11-R3, S11-R5, S5-E1).</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
         <is>
-          <t>SV-8678 (IV spec v3 2026-07-29 Story 11 S11-R3)</t>
+          <t>SV-8678 (IV spec v3 2026-07-29 Story 11 S11-R3; Story 11 S11-R5; Story 5 S5-E1)</t>
         </is>
       </c>
       <c r="I468" s="2" t="inlineStr"/>
@@ -24365,6 +24479,7 @@
 2. For ages older than 13 months, only the last capture of each calendar month is retained; the other daily captures in that band are pruned.
 3. Pruning runs as part of, or alongside, the nightly capture.
 ---
+Note for the tester: this one needs records going back more than a year, and this test system only holds a few days of records so far. If there is nothing old enough to look at, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S11-R6).</t>
         </is>
       </c>
@@ -24417,6 +24532,7 @@
 2. The "As of" indicator names the day actually shown.
 3. A requested date whose covering captures have all been pruned resolves to the nearest earlier retained capture, or shows the empty state if none remains.
 ---
+Note for the tester: this one needs records going back more than a year, and this test system only holds a few days of records so far. If there is nothing old enough to look at, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S11-E1, S11-R6, S5-R4, S5-R5, S5-N1).</t>
         </is>
       </c>

--- a/testrail-import/report-suite-v1-testrail-import.xlsx
+++ b/testrail-import/report-suite-v1-testrail-import.xlsx
@@ -23597,7 +23597,7 @@
           <t>1. The PDF header shows the report name "Inventory Value", the organization name, the selected period, and an "as of" line naming the day the values represent (or a message that no snapshot is available for the period).
 2. The PDF shows the shop logo at the top when one is set.
 3. The CSV never includes a logo.
-4. Note for the tester: the two files phrase the as-of line differently - the PDF reads "As of 2026-08-04" and the CSV's first line reads "As of: 2026-08-04" (with a colon). Both are correct; do not raise the difference.
+4. Note for the tester: the two files phrase the as-of line differently - the PDF reads "As of 2026-08-04", and in the spreadsheet it is one of the short summary lines that sit above the column headings, reading "As of: 2026-08-04" (with a colon). Both are correct; do not raise the difference, and do not count the summary lines - more of them may be added.
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx

--- a/testrail-import/report-suite-v1-testrail-import.xlsx
+++ b/testrail-import/report-suite-v1-testrail-import.xlsx
@@ -12676,7 +12676,6 @@
 2. Part B shows 0.00 (renders 0.00 when On Hand is 0 - not an error, not —).
 3. Part C shows a NEGATIVE Turns / Yr with a leading minus (because Units Sold can be negative).
 4. Special Order rows always show — (not applicable).
-Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8819
 ---
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4).</t>
         </is>
@@ -13039,7 +13038,6 @@
 2. In W2 (movement date in window): Units Sold / Demand count it, the billed columns do not - the two anchors CAN differ for an inventory part and that is intended.
 3. The window is the whole-day span inclusive of BOTH the start and end dates, with a floor of 1 day - a single-day range (Today) computes normally (Window = 1 for the Turns / Yr divisor).
 4. Last Sale is not windowed at all (all-time).
-Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8819
 ---
 This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R7).</t>
         </is>

--- a/testrail-import/report-suite-v1-testrail-import.xlsx
+++ b/testrail-import/report-suite-v1-testrail-import.xlsx
@@ -532,7 +532,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-R1, S1-R3, S1-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S1-R1, S1-R3, S1-R4).</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -583,7 +583,7 @@
 3. Ordinary reports access alone is enough — this report does NOT need a permission of its own.
 4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S1-R2).</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -635,7 +635,7 @@
 3. The gate is the ordinary reports access — there is no separate Sales By Customer permission to remove.
 4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S1-N1).</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
           <t>1. The destination page shows the application's standard access-denied state.
 2. Pressing back returns you to the Sales By Customer report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S9-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S9-N2).</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
 3. A requested location the user does not have access to is ignored — the report does NOT widen to the whole organization.
 4. The report data never includes invoices from a location the user does not have access to.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R7, S4-R8, S4-R9, S4-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S4-R7, S4-R8, S4-R9, S4-N1).</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
 2. The only reports permission offered is the ordinary reports access, and that one covers all six of the new reports.
 3. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S1-R2).</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -841,7 +841,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R1, S2-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S2-R1, S2-R2).</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -893,7 +893,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R3, S2-R4, S2-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S2-R3, S2-R4, S2-N2).</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
           <t>1. The chosen date range value is written into the page link.
 2. Opening that link in a browser with no saved view for this report restores the sender's date range.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R6, S2-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S2-R6, S2-R9).</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
 4. With "Parts &amp; Service" selected, no product-type filter is applied — both S and P invoices are included and counts/totals cover both.
 5. The whole invoice is classified by its number prefix — there is no per-line-item split.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6).</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R1, S4-R2, S4-R3); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S4-R1, S4-R2, S4-R3); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
 4. With "All locations" active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
 5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R5, S4-R6); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S4-R5, S4-R6); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S4-R12, S4-R12a, S4-R13, S20-R19).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S4-R12, S4-R12a, S4-R13, S20-R19).</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1217,7 +1217,7 @@
 3. Before typing, the dropdown shows the pinned all/clear control at the top and a "Search customers…" hint; individual customers are revealed by typing.
 4. The hint yields to the typed query while you are searching.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R1, S18-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R1, S18-R2).</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1268,7 +1268,7 @@
 2. The list is scoped to the active date range, Product Type, and location.
 3. A selected customer is shown with a checkmark.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R2).</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
 3. The control is pinned to the top of the dropdown in both states.
 4. After "Clear all": the report shows the empty-state message "No sales data found for the selected filters.", the totals row shows zeros, and the collapsed label reads "None."
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R3, S18-N1, S17-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R3, S18-N1, S17-E1).</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1373,7 +1373,7 @@
 3. The all-customers state is an explicit state — while it is active, any customer that appears later (new data) is included automatically.
 4. After the filter change the filter stays in the all-customers state (label still "All customers") and every customer matching the new filters is included — including the newly-appearing one, with no manual re-selection.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R4, S18-R5, S18-R9, S18-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R4, S18-R5, S18-R9, S18-E1).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1425,7 +1425,7 @@
 3. With more than one selected the label reads "N selected" where N is the number of selected customers (for example "3 selected").
 4. While typing, the field shows the query text instead of the summary label; the summary label returns when the query is cleared or the field loses focus.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R5).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1475,7 +1475,7 @@
 2. The table refreshes as a fresh first page of results.
 3. The totals row updates to cover only the selected customers' matching invoices.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R5, S18-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R5, S18-R11).</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1526,7 +1526,7 @@
 3. Customer C (newly present) is NOT auto-selected and is not shown.
 4. The Customer filter selection itself is not cleared by the date change.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R9, S18-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R9, S18-E1).</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
 4. The count reflects the active date range, Product Type, and location — it drops when the range is narrowed; it is not a lifetime count.
 5. Note for the tester: you do not need to measure anything and you do not need any tool for item 3. Just say whether the count looks the right size and is easy to read, and only report it if it looks obviously wrong. (The exact colour and weight behind this are design-token values the design and engineering team check with their own tooling.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-R1, S7-R2, S7-R3, S7-R4, S7-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-R1, S7-R2, S7-R3, S7-R4, S7-R5).</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1627,7 +1627,7 @@
         <is>
           <t>1. The customer is not shown — there are no zero-value placeholder rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-N1).</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1682,7 +1682,7 @@
 6. Each chevron toggles back to collapsed on a second activation.
 7. Collapsing customer A does not affect customer B's expansion; each asset's expansion state is likewise independent.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R1, S8-R2, S8-R5, S8-R5a, S8-R5b, S8-R5c, S8-R15).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R1, S8-R2, S8-R5, S8-R5a, S8-R5b, S8-R5c, S8-R15).</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
 2. Each detail row shows the invoice number (as a link), the invoice date, and the per-invoice Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, and Subtotal.
 3. The invoice date shows in the format "Mon DD YYYY" — for example, May 14 2026.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R4, S8-R12, S8-R12a, S20-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R4, S8-R12, S8-R12a, S20-R14).</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
           <t>1. Invoices referencing the same vehicle record (same vehicle id) group into ONE asset row — no duplicate rows for the same vehicle.
 2. An older invoice with no vehicle id on file groups by the invoice's own stored vehicle snapshot instead.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R3).</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1829,7 +1829,7 @@
 2. The no-vehicle work collects under a single row labeled "Parts Sales," always sorted last among that customer's assets.
 3. Changing the column sort does not change the asset order — assets stay A→Z with "Parts Sales" last.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R6, S8-R6a, S10-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R6, S8-R6a, S10-R6).</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
 2. Clicking it expands every customer on the current page in one action — it acts on the currently visible customers only, not the whole result set.
 3. With all visible customers expanded, the icon switches to "collapse" and the tooltip reads "Collapse all"; clicking collapses them all.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R16, S8-R17, S8-R18, S8-R19).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R16, S8-R17, S8-R18, S8-R19).</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
 2. A change that re-fetches customer rows (date range, Product Type, location, Customer selection, or sort) collapses all expanded rows.
 3. While the re-fetch is in flight the table shows the standard loading state; when it clears, the page shows the first page of the newly ordered set — the customers on the page can change.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R20, S8-R21, S10-R8a, S10-R8b, S10-R8c).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R20, S8-R21, S10-R8a, S10-R8b, S10-R8c).</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
           <t>1. The single-invoice asset expands and shows exactly one invoice detail row.
 2. Customer B shows a single "Parts Sales" row and no vehicle rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-E1, S8-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-E1, S8-E2).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2025,7 +2025,7 @@
         <is>
           <t>1. The no-vehicle S invoice appears under that customer's "Parts Sales" row — the bucket collects work by the ABSENCE of a vehicle, not by the invoice-number prefix.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-E3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-E3).</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2076,7 +2076,7 @@
 2. It is excluded from the customer's "(N)" count and from every row total, regardless of the Product Type filter.
 3. The customer/asset totals drop by exactly that invoice's amounts.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-R7, S7-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-R7, S7-N2).</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
 4. A customer summary row reads as heavier than the invoice rows under it, and its Subtotal cell is the heaviest cell on that row.
 5. Note for the tester: you do not need to measure anything and you do not need any tool for item 4. Just say whether the summary row stands out from the invoice rows and whether its Subtotal looks the boldest, and only report it if it looks obviously wrong. (The exact weights behind this are design-token values the design and engineering team check with their own tooling.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-R8, S7-R9, S7-R10, S7-R15, S7-R16).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-R8, S7-R9, S7-R10, S7-R15, S7-R16).</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R7, S8-R8, S8-R9, S8-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R7, S8-R8, S8-R9, S8-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2229,7 +2229,7 @@
           <t>1. The duplicate labels are suffixed " (#1)" and " (#2)" (and so on for more duplicates).
 2. The numbering is fixed and repeatable — after a reload the same vehicle keeps the same number.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R11).</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
 2. A service invoice opens the associated work order's Finance tab.
 3. A parts invoice opens the associated part sale's Part Requests tab.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S9-R1, S9-R2, S9-R2a, S9-R2b).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S9-R1, S9-R2, S9-R2a, S9-R2b).</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2329,7 +2329,7 @@
 2. Pressing back returns to the report with its filters, sort, and columns restored exactly as set.
 3. Expanded rows are shown collapsed again — expansion is not restored (this is the specified behavior, not a defect).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S9-R3, S9-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S9-R3, S9-R4).</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
 3. The link has no underline at rest, on hover, or after it has been clicked.
 4. The link never recolors to the browser's visited-link (purple) color.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S9-R5, S9-R6, S9-R7, S9-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S9-R5, S9-R6, S9-R7, S9-R8).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2428,7 +2428,7 @@
           <t>1. The destination page shows the application's standard "not found" state.
 2. Pressing back returns you to the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S9-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S9-N1).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
 2. Text columns sort alphabetically; numeric columns sort by value (not as text).
 3. Sorting reorders only the customer summary rows — asset rows keep their own order (A→Z with "Parts Sales" last) and invoice rows keep their order under their asset.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S10-R1, S10-R2, S10-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S10-R1, S10-R2, S10-R6).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2529,7 +2529,7 @@
           <t>1. On first load, rows are ordered by Customer name, ascending, case-insensitive (a lower-case "acme" sorts by letter, not after all capitals).
 2. Clicking a column header replaces the default with that column's sort.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S10-R4, S10-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S10-R4, S10-R7).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
           <t>1. Ascending: the em-dash (missing) row sorts to the bottom.
 2. Descending: the em-dash row sorts to the top.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S10-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S10-R3).</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2625,7 +2625,7 @@
           <t>1. Customer rows order by each customer's most recent invoice date in the current view.
 2. The Date cells on customer rows stay blank — the sort still works.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S10-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S10-R5).</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
 3. Labor Margin = Labor Invoiced minus labor cost; Parts Margin = Parts Invoiced minus parts cost.
 4. Margin = Labor Margin + Parts Margin — it does NOT include any Shop Supplies amount (shop supplies add to Subtotal but add no profit to Margin).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-R6, S11-R1, S4-R12, S20-R19).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-R6, S11-R1, S4-R12, S20-R19).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2727,7 +2727,7 @@
 3. Margin % is monochrome — no green or red coloring.
 4. The same calculation and format apply to customer rows, asset rows, and invoice rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S7-R11, S7-R12, S7-R13, S7-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-R11, S7-R12, S7-R13, S7-R14).</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2779,7 +2779,7 @@
 5. A zero/break-even value shows 0.0 in the default text color.
 6. The same calculation, label, format, and coloring apply on customer, asset, and invoice rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S12-R1, S12-R2, S12-R3, S12-R4, S12-R5, S12-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S12-R1, S12-R2, S12-R3, S12-R4, S12-R5, S12-R6).</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
 2. A value that rounds to 0.0 (for example +0.04) is shown as 0.0 in the default text color (not +0.0 in green).
 3. A negative value shows a minus sign and one decimal — for example, -0.5.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S12-N1, S12-E1, S12-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S12-N1, S12-E1, S12-E2).</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
 2. A customer's asset subtotals sum exactly to the customer's row total.
 3. This holds for every financial column, not only Subtotal.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R13).</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
 3. Subtotal values are shown in bold on the header, on every customer, asset and invoice row, and on the totals row.
 4. Check it still holds after two changes: narrow the date range so fewer rows match, then sort by a different column. Subtotal stays the rightmost column, stays pinned, and stays bold both times.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S11-R1, S11-R2, S11-R3, S11-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S11-R1, S11-R2, S11-R3, S11-N1).</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
           <t>1. The totals row is computed over the full set of customers matching the active filters (date range, Product Type, location, Customer filter).
 2. The totals do not change when you move between pages — they never reflect only the visible page.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R6).</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3030,7 +3030,7 @@
 4. With no saved selection, all nine toggleable columns default to visible.
 5. Note for the tester: there is no Location toggle in this panel. That is correct - the Location column appears by itself when you have more than one location in scope, so it is never something you switch on here.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S13-R1, S13-R2, S13-R3, S13-R4, S13-R7, S4-R12, S4-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S13-R1, S13-R2, S13-R3, S13-R4, S13-R7, S4-R12, S4-R13).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3080,7 +3080,7 @@
 2. The Customer and Subtotal columns and the chevron control column do NOT appear in the toggle list and are always present.
 3. All nine columns can be hidden — nothing blocks the last toggle; the table still renders the Customer and Subtotal columns and the totals row still shows its Subtotal.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S13-R5, S13-R6, S13-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S13-R5, S13-R6, S13-N1).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3130,7 +3130,7 @@
 2. The menu items read, in order: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)" - and there is NO "Print" item anywhere in the menu.
 3. There are no separate always-visible export buttons - all exports live behind this one menu.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R1, S14-R2, S15-R1, S15-R2, S20-R16); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R1, S14-R2, S15-R1, S15-R2, S20-R16); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
 4. The file is plain comma-separated text with a .csv extension that opens as rows and columns in a spreadsheet — not an .xlsx workbook and not a JSON file.
 5. The two PDF downloads follow the same names with a .pdf extension — for example, sales-by-customer-summary-this_month.pdf and sales-by-customer-expanded-custom.pdf.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R14, S14-R15, S15-R6); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R14, S14-R15, S15-R6); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3238,7 +3238,7 @@
 6. Work with no vehicle appears as an asset row named "Parts Sales".
 7. The file carries a "Locations:" line naming the location or locations the report was scoped to, or "All locations" when every location you can access is selected — as a leading line above the column headers.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R5, S14-R6, S14-R7, S14-R8, S14-R13, S4-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R5, S14-R6, S14-R7, S14-R8, S14-R13, S4-R13).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3287,8 +3287,10 @@
 2. Dates export as mm-dd-yyyy — for example, 05-14-2026.
 3. Currency values are plain numbers with no dollar sign and no thousands separators.
 4. The CSV has no color; the signed Inv. Hrs value still conveys direction.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R9, S14-R10, S14-R11, S14-R12, S14-R13).</t>
+On this build the money in the spreadsheet file comes out as "$224.92" - with a dollar sign, and with a comma as well once the value passes a thousand - instead of the plain number described in point 3 above.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8823
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R9, S14-R10, S14-R11, S14-R12, S14-R13).</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3338,7 +3340,7 @@
 2. When every customer is selected, the export contains the full set of customers under those filters.
 3. The chosen date range and Product Type are reflected in both exports.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R7, S3-R7, S4-R10, S14-R3, S15-R3, S18-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S2-R7, S3-R7, S4-R10, S14-R3, S15-R3, S18-R7).</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3389,7 +3391,7 @@
 2. If a CSV download fails, an error toast is shown: "CSV export failed." (dismissed by the user).
 3. If a PDF download fails, the toast reads "PDF export failed." — identical behaviour, different wording.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-E1, S14-N1, S15-E1, S15-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-E1, S14-N1, S15-E1, S15-N1).</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3437,7 +3439,7 @@
           <t>1. The PDF is A4 landscape using the application's standard font; the page margins look uniform on all sides. (The spec's exact 25px margin needs a PDF inspector — check the number only if you have one; otherwise uniform margins pass.)
 2. The footer has a centered "Software Powered by ShopView" label and a right-aligned page number "Page X of Y."
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S15-R5, S15-R6, S15-R7, S15-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S15-R5, S15-R6, S15-R7, S15-R8).</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3487,7 +3489,7 @@
 3. The header date range shows start and end in the format "Mon D, YYYY," joined by an em dash - for example, "May 1, 2026 - May 31, 2026" - and always shows both dates (every range is bounded).
 4. The header also carries a "Locations:" line naming the location(s) the report was scoped to (exact placement within the header is confirmed in the build).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S15-R7, S15-R8, S15-R9, S15-R10, S15-R11, S15-R14, S4-R13); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S15-R7, S15-R8, S15-R9, S15-R10, S15-R11, S15-R14, S4-R13); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3540,7 +3542,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18).</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3594,7 +3596,7 @@
 6. Inv. Hrs uses the same signs and coloring as on screen, with green rendered as #21ba45 and red as #c10015.
 7. The PDF header title reads "Sales By Customer Report" on the Summary and Expanded versions alike — which version you have is told by the file name and the contents, not by a different title.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S15-R5, S15-R13, S15-R19, S15-R20, S15-R21, S15-R22, S15-R23, S15-R24, S4-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S15-R5, S15-R13, S15-R19, S15-R20, S15-R21, S15-R22, S15-R23, S15-R24, S4-R13).</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3646,7 +3648,7 @@
 4. Below the cap the export succeeds normally.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R16, S15-R25, S14-R14, S15-R22); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R16, S15-R25, S14-R14, S15-R22); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3694,7 +3696,7 @@
           <t>1. The export still downloads — no error and no warning is shown.
 2. The file contains the column headers and a totals row of zeros, with no data rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R10).</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3748,7 +3750,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13).</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3797,7 +3799,7 @@
           <t>1. The saved view is restored: the date range, the Product Type, the location selection, the Customer filter selection, the sort column and direction, and the visible columns.
 2. On load, the report shows the restored view immediately — the default view is never shown first and then replaced.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S6-R1, S6-R2, S6-R4, S2-R8, S3-R8, S4-R11, S10-R9, S13-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-R1, S6-R2, S6-R4, S2-R8, S3-R8, S4-R11, S10-R9, S13-R8).</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3848,7 +3850,7 @@
 3. The scroll position is not restored.
 4. This is the specified behavior (expansion is treated as fresh each visit), not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S6-R3, S8-R22).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-R3, S8-R22).</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3898,7 +3900,7 @@
 2. No error appears and the report loads normally.
 3. Per the spec, the same discard-to-default applies to an unknown date range, a sort column that no longer exists, or a column set that does not match the current columns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S6-R5, S6-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-R5, S6-R6).</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3946,7 +3948,7 @@
           <t>1. The other report keeps its own defaults/saved view — the Sales By Customer settings do not leak into it.
 2. Sales By Customer still restores its own saved view.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S6-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-R7).</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4000,7 +4002,7 @@
 5. Sort = Customer name ascending.
 6. All nine toggleable columns visible.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S6-N1, S2-R5, S4-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-N1, S2-R5, S4-R4).</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4049,7 +4051,7 @@
           <t>1. The saved view is applied (Last Month) and the link value is ignored.
 2. This is intentional: a shared link restores the sender's range only for a recipient who has no saved range of their own.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S2-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S2-R9).</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4098,7 +4100,7 @@
           <t>1. Scenario A: the filter restores to the all-customers state and the report shows every present customer — including the customer that appeared since the state was saved.
 2. Scenario B: still-present saved ids are re-selected; a saved id no longer present is dropped (a stale saved id never forces an empty view); a customer that appeared since the set was saved is NOT auto-selected.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R8).</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4154,7 +4156,7 @@
 5. With a narrowed customer selection and no data, the empty state shows but the selection is KEPT (not cleared) — when the filters change back, the selected customers reappear.
 6. While the table is still loading, the empty-state message is NOT shown (the loading state is shown instead); it appears only once loading has finished and there are zero customers.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1, S17-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1, S17-N1).</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4203,7 +4205,7 @@
           <t>1. An error toast is shown: "An error occurred while fetching the report data."
 2. The toast auto-fades after 5 seconds.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (§7 User Feedback Summary).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (§7 User Feedback Summary).</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4261,7 +4263,7 @@
 8. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 9. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing, the alignment and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this — 32px/24px toolbar padding, a 1px header border, 2rem edge padding, a 24px arrow — are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S20-R1, S20-R2, S20-R3, S20-R4, S20-R5, S20-R6, S20-R7, S20-R12, S20-R13, S20-R15, S20-R17).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S20-R1, S20-R2, S20-R3, S20-R4, S20-R5, S20-R6, S20-R7, S20-R12, S20-R13, S20-R15, S20-R17).</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4316,7 +4318,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14).</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4364,7 +4366,7 @@
           <t>1. In dark mode every visual rule applies with the dark equivalent of each color (dark background, dark surfaces).
 2. The PDF export always renders in light-mode colors regardless of the user's app mode.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S20-R18).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S20-R18).</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4414,7 +4416,7 @@
 2. Below 1024px the toolbar uses two rows: the action controls (overflow menu and column selector) on the first row, and the filter dropdowns on the second row, stacked at full width.
 3. At 1024px and above the toolbar uses the desktop single-row layout.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S21-R1, S21-R2, S21-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S21-R1, S21-R2, S21-R3).</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4464,7 +4466,7 @@
 2. The chevron expand and collapse control on each row works on touch.
 3. The invoice number link opens the invoice in the same tab, the same as on desktop.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S21-R4, S21-R5, S21-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S21-R4, S21-R5, S21-R6).</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4516,7 +4518,7 @@
 2. The first expand of a customer triggers a server fetch for that customer's asset and invoice rows.
 3. Expand-all triggers at most one drill-down fetch per not-yet-expanded customer on the current page — a bounded number never exceeding the page size; it does not fetch customers beyond the current page or the whole result set.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S8-R14, S8-R16).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R14, S8-R16).</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4568,7 +4570,7 @@
 3. The ordering is not done by re-shuffling rows already in the browser.
 4. A sort request naming a column the report does not offer is safely refused or ignored — never an error page or a crash; sorting works only on the report's own columns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S10-R8, S10-R8b).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S10-R8, S10-R8b).</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4619,7 +4621,7 @@
 2. As you type, the browser fetches matching customers from the server — case-insensitive "contains" matching on the name, scoped to the active date range, Product Type, and location — and lists the returned customers.
 3. The all-customers state is stored as an explicit state (a flag), not an enumeration of the fetched ids.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R2, S18-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R2, S18-R4).</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4670,7 +4672,7 @@
 2. Changing the Customer selection re-fetches the matching customers as a fresh first page.
 3. The totals are computed on the server over the full set of matching customers — they arrive with the data and do not change as you page.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S18-R6, S18-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R6, S18-R11).</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4720,7 +4722,7 @@
 2. Over the cap, the server does not generate the file (the request comes back as a refusal, not a file) and the browser starts no download — the count the cap checks is the count the file would contain, against the same filters and sort as the screen.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S14-R3, S14-R14, S15-R3, S15-R22).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R3, S14-R14, S15-R3, S15-R22).</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4777,7 +4779,7 @@
 4. For that same user, the export request is refused with HTTP 403 as well — no file is produced.
 5. Note for the tester: one single permission controls all four of these. If you find the report data refused but the export allowed (or the other way round), that is a failure — record both response codes.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Customer report specification version 13 (S1-R2, S1-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S1-R2, S1-N1).</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4830,7 +4832,7 @@
 4. The page title reads "Sales By Representative".
 5. The browser tab title reads "Sales By Representative - Report | ShopView".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S1-R1, S1-R2, S1-R3, S1-R4, S1-R5, S1-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R1, S1-R2, S1-R3, S1-R4, S1-R5, S1-R6).</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4878,7 +4880,7 @@
           <t>1. The full "Sales By Representative" label renders without crowding against the entry's edges and without truncation.
 2. The label is not shortened to fit — the fix is the entry's horizontal padding, not the name.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S1-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R7).</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -4925,7 +4927,7 @@
         <is>
           <t>1. "Sales By Representative" appears in the Performance group for this user — the entry is visible to every user who can see any other report in the same group.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S1-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R1).</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -4976,7 +4978,7 @@
 2. The report (and its ⋯ export menu) is not reachable.
 3. The Export Reports dialog and the Sales Representative Assignments download are not reachable.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S1-N1, S14-N3, S15-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-N1, S14-N3, S15-N1).</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5022,7 +5024,7 @@
         <is>
           <t>1. The staff-editing surface is not reachable, so the deactivation flow (and its warning dialog) cannot be reached.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N1).</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5073,7 +5075,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S2-R1, S2-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S2-R1, S2-R2).</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5121,7 +5123,7 @@
           <t>1. A custom range within the cap applies normally via the date-picker dialog.
 2. A custom selection whose span exceeds 366 days is not accepted — the picker holds you to a range of 366 days or fewer.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S2-R3, S2-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S2-R3, S2-R6).</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5171,7 +5173,7 @@
 2. The date used is the invoice's own date — the value shown in the Date column.
 3. The chosen date range is reflected in both PDF exports' header strips.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S2-R5, S2-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S2-R5, S2-R8).</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5225,7 +5227,7 @@
 4. "Parts &amp; Service" applies no product-type filter — both appear again.
 5. Each change re-fetches and re-renders the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6, S3-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6, S3-R7).</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5276,7 +5278,7 @@
 3. "All Statuses" is the default on first load.
 4. Changing the selection re-fetches and re-renders the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S4-R1, S4-R2, S4-R3, S4-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R1, S4-R2, S4-R3, S4-R5).</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5328,7 +5330,7 @@
 3. "Unpaid" includes only the unpaid invoice.
 4. The filter matches on the mapped display value, the same mapping the status badge uses — prepaid is the only state whose display value depends on the balance owed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S4-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R4).</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5380,7 +5382,7 @@
 3. Parts-only leg: rep A disappears; rep B's summary totals, detail rows, grand Totals, and (N) count reflect only the matching (P) invoices.
 4. Unpaid leg: rep C disappears; rep D's figures reflect only the Unpaid invoices.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S4-R7, S4-R6, S4-N1, S3-R8, S3-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R7, S4-R6, S4-N1, S3-R8, S3-N1).</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5427,7 +5429,7 @@
           <t>1. The invoice shows its FULL invoiced amounts (its full Subtotal) — payments are not netted out.
 2. Filtering to "Unpaid" or "Partially Paid" changes which invoices are included, never the amounts shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S4-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R8).</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5475,7 +5477,7 @@
           <t>1. The location filter is the rightmost control in the toolbar.
 2. It is a multi-select listing the locations the user has access to, plus an "All Locations" option.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-R1, S18-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-R1, S18-R7).</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5529,7 +5531,7 @@
 4. With "All Locations" active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
 5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-R3, S21-R4, S21-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-R3, S21-R4, S21-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5579,7 +5581,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5643,7 +5645,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S21-R7, S21-R8, S18-R13, S14-R20).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-R7, S21-R8, S18-R13, S14-R20).</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -5694,7 +5696,7 @@
 3. The number of contributing invoices shows in parentheses after the rep's name, in a smaller, subdued grey font — e.g., Mary Smith (12) — and is always at least 1.
 4. A staff member with no matching invoice does not appear regardless of toggle state or historical activity.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S5-R1, S5-R4, S5-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R1, S5-R4, S5-N1).</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -5747,7 +5749,7 @@
 4. Rep summary rows are bold (700) so they read as parent rows; detail rows use the default weight (400) — row type is distinguished by font weight, not background color.
 5. Every row renders exactly the report's column count with blanks in position — a cell with nothing to show is blank, never shifted or wrapped (a drifted row is a defect). The grand Totals indicator is exempt: the desktop Totals row merges the four leading identifier columns; the mobile bar is not a table row.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S5-R2, S5-R3, S5-R6, S5-R8, S5-R10, S5-N2, S6-R4, S18-R4, S18-R6a, S21-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R2, S5-R3, S5-R6, S5-R8, S5-R10, S5-N2, S6-R4, S18-R4, S18-R6a, S21-R7).</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -5799,7 +5801,7 @@
 3. For a deleted staff record, the display name and sort position come from the denormalized rep-name snapshot on the rep's most recent matching invoice (by invoice date, ties by invoice number), so the row still shows a historical name and sorts correctly.
 4. The grand Totals stay reconciled to the period's invoices — no revenue silently disappears.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S5-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R9).</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -5848,7 +5850,7 @@
 2. Each detail row shows, left to right: the invoice's date, the invoice number, the customer name, the payment status badge, and the per-invoice values for Inv. Hrs and the money columns.
 3. A rep with a single matching invoice can still be expanded — one detail row is shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R1, S6-R2, S6-R3, S6-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R1, S6-R2, S6-R3, S6-E1).</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5898,7 +5900,7 @@
 2. Clicking expands every visible rep in one action; with every rep expanded the glyph switches to "collapse."
 3. A second activation collapses them all.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R5, S6-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R5, S6-R6).</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5946,7 +5948,7 @@
           <t>1. Every invoice appears under exactly one rep (the rep credited at invoicing time) or under the Unassigned row — never under two rows.
 2. The sum of all (N) counts equals the number of matching invoices.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R7).</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5996,7 +5998,7 @@
 2. When a filter change removes a rep, the rep and its expansion state are gone; when a later change brings the rep back, the row renders collapsed (it does not auto-re-expand).
 3. A full page reload resets all expansion.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R8, S6-N1, S23-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R8, S6-N1, S23-R2).</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6046,7 +6048,7 @@
 3. If both the date and the numeric portion tie (e.g., P100 and S100 same day), P (Parts) sorts before S (Service).
 4. This order is independent of the rep-row column sort (which reorders summary rows only).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R9, S11-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R9, S11-R2).</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6098,7 +6100,7 @@
 3. The mapping is: paid → Paid; overpaid → Paid; prepaid with zero balance → Paid; prepaid with a balance owed → Partially Paid; partially_paid → Partially Paid; unpaid → Unpaid.
 4. Badges are vertically centered in their cells; on rep summary rows the Status cell is blank; the badge's text is the accessible label — status is never conveyed by color alone.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S8-R1, S8-R2, S8-R4, S8-R5, S8-R6, S8-N1, S18-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S8-R1, S8-R2, S8-R4, S8-R5, S8-R6, S8-N1, S18-R6).</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6147,7 +6149,7 @@
 2. The badges use the same canonical payment-status color tokens as the invoice list, consistent app-wide.
 3. The treatment stays legible and consistent in both light and dark mode.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S8-R3, S18-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S8-R3, S18-R8).</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6195,7 +6197,7 @@
           <t>1. The column heading reads "Inv. Hrs" (verbatim, including the period after "Inv").
 2. The value equals the billed labor hours minus the technician clocked hours, rounded half-up to one decimal.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S9-R1, S9-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R1, S9-R2).</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6248,7 +6250,7 @@
 3. The rep-summary/totals value equals round(sum of unrounded per-invoice deltas).
 4. A value that rounds to 0.0 (e.g., +0.04) shows 0.0 in the default color — not +0.0 in green; negative values always use an explicit minus and one decimal (e.g., -0.5).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S9-R3, S9-R4, S9-R5, S9-R6, S9-E1, S9-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R3, S9-R4, S9-R5, S9-R6, S9-E1, S9-E2).</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6296,7 +6298,7 @@
           <t>1. The invoice with neither billed labor hours nor clocked hours shows Inv. Hrs 0.0 in the default color — never blank, "N/A," or "—".
 2. The invoice with clocked hours but no billed labor line shows the resulting NEGATIVE delta in red (e.g., -3.0) — the worked-but-unbilled signal is not suppressed to 0.0.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S9-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-N1).</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6346,7 +6348,7 @@
 2. It renders "—" when Subtotal ≤ 0 — never "0.0%" or a divide-by-zero result.
 3. On every rolled-up row (rep summary rows and every totals row) Margin % is RECOMPUTED from that row-set's total Margin and total Subtotal — never the sum or average of the child percentages.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S10-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5).</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6396,7 +6398,7 @@
 3. Labor Margin = Labor Invoiced − labor cost; Parts Margin = Parts Invoiced − parts cost; Margin = Labor Margin + Parts Margin.
 4. The same values appear everywhere the numbers show (screen, and later the exports).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S5-R2, S21-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R2, S21-R7).</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6444,7 +6446,7 @@
           <t>1. Negative dollar values render in accounting-convention parentheses — ($1,234.56) — on screen, across every money column (Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Subtotal).
 2. Inv. Hrs (a signed time value) and Margin % (a signed percentage) are excluded — they use a leading minus, not parentheses.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (§3 Key Decisions accounting parentheses).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (§3 Key Decisions accounting parentheses).</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6492,7 +6494,7 @@
 2. Rolled-up values are computed from UNROUNDED components and then rounded, so a totals cell may differ from the eye-summed displayed rows by one unit in the last decimal.
 3. That one-unit difference is EXPECTED behavior per the spec — it must NOT be filed as a calculation defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (§3 half).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (§3 half).</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6542,7 +6544,7 @@
 2. The billed SELL values (Labor, Parts, Subtotal) stay unchanged — a clock edit never rewrites what was billed.
 3. The figures tied to worked time move together consistently (Margin uses the labor cost behind the worked hours, so it may change too) — nothing is left stale.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S9-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R2).</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6596,7 +6598,7 @@
 4. The pinned column matches the row's background color (white on body rows) — not a contrasting strip.
 5. The column-header row stays stuck to the top during vertical scroll; the Subtotal header cell stays visible in BOTH axes (top while scrolling down, pinned right while scrolling sideways).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R6, S10-N1, S18-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R6, S10-N1, S18-R7).</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6649,7 +6651,7 @@
 4. Money uses accounting parentheses for negatives; Margin % is recomputed; values are round(sum of unrounded).
 5. The indicator is present whenever at least one summary row exists, and hidden during loading and in the empty state.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S10-R5, S10-N1, S16-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5, S10-N1, S16-R4).</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6700,7 +6702,7 @@
 3. During vertical page scroll it sits after the table in normal flow (not pinned to the viewport bottom).
 4. It uses the white card surface with a thin top border.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S10-R5, S17-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5, S17-R4).</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -6749,7 +6751,7 @@
 2. The identifier columns (Date, Invoice, Customer, Status) do not respond to header clicks.
 3. The Date header carries the expand/collapse-all chevron, not a sort affordance.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R1, S11-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R1, S11-R6).</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -6796,7 +6798,7 @@
           <t>1. Rows render in A→Z order by display name, case-insensitive.
 2. There are NO active/inactive tiers — an "(Inactive)" rep sorts by name among the others, not grouped separately.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R4).</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6848,7 +6850,7 @@
 3. There is no third "cleared" state — the third click returns to ascending.
 4. Via the column headers there is no way back to A→Z; the A→Z default shows only when a session carries no valid saved financial sort.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R5, S23-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R5, S23-R5).</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -6897,7 +6899,7 @@
 2. Invoice detail rows stay grouped under their parent rep, keeping their own newest-first order.
 3. The Unassigned row stays pinned to the top regardless of sort.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R2, S22-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R2, S22-R4).</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -6945,7 +6947,7 @@
           <t>1. Reps with equal values in the sorted column retain the default A→Z order between them.
 2. A Margin % cell rendered "—" (undefined) sorts as zero.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R7).</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -6995,7 +6997,7 @@
 2. Activating it navigates the CURRENT tab to the underlying invoice (work order or parts sale) — never a new tab.
 3. The customer name is likewise a clickable link that navigates the current tab to the customer's record.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S12-R1, S12-R2, S12-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R1, S12-R2, S12-R3).</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -7045,7 +7047,7 @@
 2. Back-navigation does not trigger a full report reload.
 3. This is deliberately different from a page reload, which restores persisted filters/columns/sort but resets expansion and scroll.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S12-R3a, S23-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R3a, S23-R2).</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -7096,7 +7098,7 @@
 3. Both hold in light and dark mode and across return visits.
 4. Underlined-at-rest links, browser-blue customer names, purple post-click links, and new-tab destinations are all defects.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S12-R4, S12-R5, S12-R6, S12-N3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R4, S12-R5, S12-R6, S12-N3).</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7144,7 +7146,7 @@
           <t>1. The tab navigates to the application's standard not-found/access-denied state.
 2. Pressing back still returns to the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S12-N1, S12-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-N1, S12-N2).</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7194,7 +7196,7 @@
 2. The body shows "{Staff Name} is the sales representative on {N} customer{s}." — singular for N=1 ("1 customer"), plural otherwise ("3 customers") — followed by the reassurance line "Their customer assignments will stay where they are."
 3. Focus is trapped within the dialog while open and returns to the invoking control on dismiss.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R1, S13-R3, S13-R4, S13-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R1, S13-R3, S13-R4, S13-R12).</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7246,7 +7248,7 @@
 3. While disabled, hovering it shows the tooltip "Type YES above to enable."
 4. Pressing Enter while valid submits.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R6, S13-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R6, S13-R7).</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7300,7 +7302,7 @@
 4. Clicking outside the dialog does NOT close it.
 5. When the dialog closes via Cancel or X, the staff member's active status is unchanged - no deactivation happens.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R8).</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7350,7 +7352,7 @@
 3. Customer assignments are NOT modified — every customer stays assigned to this rep; denormalized rep names and past invoice snapshots are preserved.
 4. Deactivation never forces reassignment, blocks on assignments, or auto-reassigns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R9, S13-R10, S13-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R9, S13-R10, S13-E1).</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7400,7 +7402,7 @@
 2. In the Sales Representative Assignments CSV the rep's customers show "Rep is active?" = "No" — that column is driven by staff-active status, not the toggle.
 3. In the report the rep still appears with credit intact; the "(Inactive)" marker appears only if the sales-representative TOGGLE is off (a separate flag from staff-active status).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R11, S15-R6, S5-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R11, S15-R6, S5-R9).</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7451,7 +7453,7 @@
 3. After reactivation the assignments re-surface immediately with no extra action.
 4. Deactivating a sales representative with NO customer assignments applies silently — no warning dialog.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R2, S13-N2, S13-N3, S13-E3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R2, S13-N2, S13-N3, S13-E3).</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7501,7 +7503,7 @@
 2. The active status is unchanged.
 3. Each fresh dialog open requires a fresh confirmation entry — the input clears on open.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-N5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N5).</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7550,7 +7552,7 @@
           <t>1. The system NEVER silently deactivates — the warning dialog still opens (fallback), so the type-to-confirm gate still applies.
 2. Because the customer count is unavailable, the dialog OMITS the count headline and shows only the reassurance line "Their customer assignments will stay where they are." above the "Type YES to confirm" gate.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-N4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N4).</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7598,7 +7600,7 @@
           <t>1. A "Show Unassigned" toggle sits between the column selector and the date range picker; it is OFF by default.
 2. While off, invoices with no assigned rep contribute to nothing — no row, and not counted in any total.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S22-R1, S22-R2, S18-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-R1, S22-R2, S18-R7).</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7650,7 +7652,7 @@
 3. Toggling re-renders the report and recomputes the grand Totals to include or exclude the Unassigned row accordingly.
 4. The Unassigned row shows the same metric columns and (N) count as any rep summary row, is expandable to its contributing invoices, is included in the grand Totals, and never carries an "(Inactive)" tag.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S22-R3, S22-R4, S22-R5, S22-R6, S6-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-R3, S22-R4, S22-R5, S22-R6, S6-R1).</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7699,7 +7701,7 @@
           <t>1. With the toggle on but no matching unassigned invoices, no Unassigned row is shown — an empty Unassigned row is never rendered; with no rep rows either, the empty state applies.
 2. Turning the toggle off removes the expanded row; turning it back on renders it collapsed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S22-N1, S6-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-N1, S6-N2).</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7753,7 +7755,7 @@
 4. With all seven metric columns hidden the table still renders the five always-on columns and the grand Totals indicator — no empty or error state.
 5. Note for the tester: if you have more than one location in scope you will also see a Location column on the table that is in neither list. That is correct - it appears by itself and is not something you can switch on or off here.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S20-R1, S20-R2, S20-R3, S20-R6, S20-N1, S21-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R1, S20-R2, S20-R3, S20-R6, S20-N1, S21-R7).</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7801,7 +7803,7 @@
           <t>1. The toggle takes effect immediately — no confirm step.
 2. Hiding a metric column removes it from rep summary rows, invoice detail rows, and the grand Totals indicator simultaneously; showing restores it everywhere at once.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S20-R4, S20-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R4, S20-R7).</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7848,7 +7850,7 @@
         <is>
           <t>1. All four downloads include ALL metric columns regardless of the on-screen column selector state.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S20-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R8).</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7896,7 +7898,7 @@
           <t>1. Hiding the active sort column does not clear the sort — rows stay ordered by the now-hidden metric until another sort is chosen or the A→Z default is restored.
 2. Showing the column again reveals the sort indicator on it.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S20-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R9).</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -7945,7 +7947,7 @@
           <t>1. Every setting is restored: date range (including the custom start/end), product type, invoice status, location, Show Unassigned, column visibility, and the active column sort (column + direction).
 2. The settings are restored BEFORE the first data fetch — the report does not fetch defaults first and then re-fetch.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S23-R1, S20-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R1, S20-R5).</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7993,7 +7995,7 @@
           <t>1. All rows render collapsed and the scroll position resets.
 2. This is the specified behavior (only back-navigation from a drilldown restores expansion/scroll), not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S23-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R2).</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8042,7 +8044,7 @@
 2. No error occurs — a stale saved setting can never cause an error or an invalid request.
 3. Per the spec the same applies to a range or sort column that no longer exists and to a hidden-but-sorted column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S23-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R3).</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8090,7 +8092,7 @@
           <t>1. Date range = This Month; Product Type = "Parts &amp; Service"; Invoice Status = "All Statuses"; Location = your currently active location only (the one location you are working in); Show Unassigned = off; all seven metric columns visible; sort = the A→Z default.
 2. Clearing browser storage fully returns the report to first-visit defaults — no server-side profile brings the old settings back.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S23-R4, S23-N1, S2-R4, S2-R7, S21-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R4, S23-N1, S2-R4, S2-R7, S21-R2).</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8138,7 +8140,7 @@
           <t>1. The report restores to the A→Z default order by rep display name.
 2. No financial column shows a sort indicator — the saved "no financial sort" state restores as A→Z, not as an arbitrary column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S23-R5, S11-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R5, S11-R4).</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -8187,7 +8189,7 @@
           <t>1. The menu lists exactly four actions: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", and "Download Expanded View (CSV)".
 2. No other entries appear in the menu.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R1, S17-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R1, S17-R3).</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8242,7 +8244,7 @@
 4. The Unassigned row (Show Unassigned on) is pinned first, ahead of the sorted reps.
 5. Every file (all four downloads, PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R2, S14-R2a, S14-R20, S21-R6, S22-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R2, S14-R2a, S14-R20, S21-R6, S22-R4).</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -8297,7 +8299,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R3, S14-R5, S14-R20, S2-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R3, S14-R5, S14-R20, S2-R5).</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8353,7 +8355,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R6, S14-R8, S14-R20, S6-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R6, S14-R8, S14-R20, S6-R9).</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8402,7 +8404,7 @@
 2. In the PDF, the long number is cut to its first 18 characters followed by an ellipsis (the ellipsis is not counted toward the 18).
 3. In the PDF, the 18-character-or-shorter number shows in full with no ellipsis.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R7).</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -8453,7 +8455,7 @@
 2. A footer reading "Software Powered by ShopView" appears on EVERY page of both PDFs.
 3. With no configured logo, the logo region falls back to the default ShopView logo and the PDF still generates normally.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R3a, S14-R4, S14-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R3a, S14-R4, S14-R11).</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -8503,7 +8505,7 @@
 2. The on-screen (N) invoice count does NOT appear next to any rep name in either PDF.
 3. The "(Inactive)" tag DOES render on toggled-off contributors' names in both PDFs; other rep names render plainly.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R9, S14-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R9, S14-R10).</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8554,7 +8556,7 @@
 2. Column widths are fixed for the worst case regardless of tier — the layout never breaks and no value overflows or wraps its column.
 3. Both PDF formats adapt the same way.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R12, S14-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R12, S14-R13).</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -8611,7 +8613,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R15, S14-R18, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R15, S14-R18, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -8665,7 +8667,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R16, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R16, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -8716,8 +8718,10 @@
 4. The "Sales Representative" name carries the "(Inactive)" tag when applicable; the on-screen (N) count is NOT embedded in the name.
 5. Text fields are quoted per standard CSV escaping; both CSVs are monochrome (Inv. Hrs conveys direction only by its sign).
 6. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
----
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R17).</t>
+On this build the money in the spreadsheet file comes out as "$1,979.40" - with a dollar sign and a comma - instead of the plain number described in point 1 above.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8823
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R17).</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -8769,7 +8773,7 @@
 3. With the toggle OFF: no Unassigned row and no unassigned invoices appear in ANY of the four files.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R19, S22-R2, S22-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R19, S22-R2, S22-R4).</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8820,7 +8824,7 @@
 2. A failed download shows the error toast "Ooooops! An error occured" (the typo is as-shipped) — it persists 120 seconds or until dismissed.
 3. A genuine failure downloads nothing — never a malformed file.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-N1, S14-N2, S14-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-N1, S14-N2, S14-E1).</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -8870,7 +8874,7 @@
 3. Below the cap, a large Expanded View PDF still generates normally (many reps × many invoices is expected).
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-E2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -8921,7 +8925,7 @@
 4. Both CSVs generate a header-row-only file, still starting with the UTF-8 BOM.
 5. No special "empty" treatment or message appears inside the files.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-E3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E3).</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8973,7 +8977,7 @@
 3. The dialog shows the note: "Snapshot of current sales representative assignments. Both active and inactive reps with assignments are listed."
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R1, S15-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R1, S15-R2).</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -9026,7 +9030,7 @@
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 5. Note for the tester: this file has only those three columns even if you have several locations in scope. It is a separate customer-to-representative list, not one of the report's four downloads, so it has no Location column - do not fail it for that.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R3, S15-R4, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R3, S15-R4, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -9077,7 +9081,7 @@
 2. Customers with no assigned rep are NOT included.
 3. Rows are sorted by customer name A→Z (primary), then rep name A→Z (secondary).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R5, S15-R7, S15-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R5, S15-R7, S15-R10).</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9126,7 +9130,7 @@
 2. The staff-INACTIVE / toggle-on rep shows "Rep is active?" = "No".
 3. The value is always "Yes" or "No" (never "Deactivated" or another word).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R6, S13-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R6, S13-R11).</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9177,7 +9181,7 @@
 3. When stored names differ across customers for the same rep (name drift), each customer's row uses its OWN stored name — drift never adds extra rows for a customer and never overwrites one customer's stored name with another's.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R8, S15-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R8, S15-R9).</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -9227,7 +9231,7 @@
           <t>1. With zero assigned customers, the CSV downloads with a header row and no data rows, and the dialog shows its empty-export warning: "There is no data to export for the selected report."
 2. On a generation failure, an error toast reads "An error occurred while exporting the report. Please try again." and auto-fades after 5 seconds.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S15-R11, S15-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R11, S15-N2).</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -9280,7 +9284,7 @@
 4. Whenever at least one rep row (or the Unassigned row) IS in the result set, the rep list renders and no empty/error message shows.
 5. In the empty state the toolbar — filters, column selector, and the ⋯ exports — stays visible and interactive; widening the range re-fetches and renders the matching reps normally.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S16-R1, S16-R2, S16-R3, S16-N1, S2-N1, S21-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R1, S16-R2, S16-R3, S16-N1, S2-N1, S21-N2).</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9332,7 +9336,7 @@
 3. The toolbar stays interactive so filters can be changed mid-load.
 4. A re-fetch replaces the previous data only when the new data returns — no flash of a blank table beyond the spinner overlay.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S16-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R4).</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9383,7 +9387,7 @@
 2. The filters and toolbar remain interactive, and the failure does NOT clear the filter selections.
 3. "Retry" re-runs the CURRENT request — the report loads with the same filters still applied.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S16-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R5).</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9433,7 +9437,7 @@
 2. Below 1024px the toolbar controls stack vertically at full width; the ⋯ exports button — the first control of the action cluster — wraps to a partial row ABOVE the stacked controls.
 3. At 1024px and above the desktop layout applies.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S17-R1, S17-R2, S17-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R1, S17-R2, S17-R3).</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9483,7 +9487,7 @@
 2. The mobile external totals bar ("Totals" left, grand Subtotal right) sits below the table, OUTSIDE the horizontal scroll container — it does not scroll horizontally and is always fully visible.
 3. The chevron expands/collapses the rep on touch.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S17-R4, S17-R5, S10-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R4, S17-R5, S10-R5).</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -9532,7 +9536,7 @@
           <t>1. Each of these interactive controls presents a touch target of at least 44×44 px.
 2. Hover-only tooltips are not shown on touch; the icons communicate the action and each icon-only control carries an accessible name.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S17-R6, S17-N1, S18-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R6, S17-N1, S18-R9).</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -9587,7 +9591,7 @@
 6. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 7. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the alignment look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this — 32px/24px toolbar padding, 2rem edge padding — are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S18-R1, S18-R2, S18-R3, S18-R4, S18-R5, S18-R7, S18-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R1, S18-R2, S18-R3, S18-R4, S18-R5, S18-R7, S18-N1).</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -9639,7 +9643,7 @@
 3. Inv. Hrs green/red use the application's positive/negative tokens, mode-appropriate.
 4. PDFs always render in light-mode colors, even when downloaded from dark mode.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S18-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R8).</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
@@ -9691,7 +9695,7 @@
 4. Header chevron = "Expand all reps" / "Collapse all reps".
 5. Dialog X = "Close".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S18-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R9).</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
@@ -9742,7 +9746,7 @@
 2. A chevron exposes its expanded/collapsed state to assistive technology.
 3. A sortable header exposes its current sort state (unsorted / ascending / descending) to assistive technology.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S18-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R10).</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
@@ -9791,7 +9795,7 @@
 2. No information is conveyed by color alone: Inv. Hrs carries its +/- sign, status badges carry their text label, and links carry a hover/focus underline.
 3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can read the grey text easily in both modes, and only report it if you cannot. (The design rule behind this is WCAG AA contrast of at least 4.5:1, which the design and engineering team check with a contrast tool - not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S18-R11, S18-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R11, S18-R12).</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
@@ -9846,7 +9850,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R1, S19-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R1, S19-N1).</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9897,7 +9901,7 @@
 3. The selector carries the accessible name "Sales Representative".
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R2, S19-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R2, S19-R8).</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -9947,7 +9951,7 @@
 2. Changing the Sales Representative persists immediately (save-on-change): the selection survives leaving and reopening the WO with no separate Save step.
 3. A new Part Sale WO also opens with the field unassigned.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R3, S19-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R3, S19-R4).</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -9997,7 +10001,7 @@
 3. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 4. Note for the tester: this field is only made read-only on the screen. If you find the sales rep can still be changed another way (through the back-end/API), that is expected — mark this test PASSED and do not raise it as a bug.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R5).</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -10048,7 +10052,7 @@
 3. Invoice (c) is unassigned — it appears only under the "Unassigned" row.
 4. Changing WO (a)'s Sales Representative afterward does NOT retroactively alter the invoice already created from it — the invoice stays credited to the rep snapshotted at invoice creation.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R6, S19-N2, S22-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R6, S19-N2, S22-R3).</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -10102,7 +10106,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S19-R7, S19-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R7, S19-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
@@ -10154,7 +10158,7 @@
 2. A re-expand within the session does not necessarily re-fetch (the expansion state is session-preserved); no rep's details load before its first expand.
 3. When a rep's matching-invoice count is large, its detail rows are paginated per rep.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S6-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R2).</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10204,7 +10208,7 @@
 2. The returned rows arrive already ordered by the requested column and direction — the client does not re-sort locally.
 3. Invoice detail rows continue to load lazily per rep on expand, unaffected by the sort mechanism.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S11-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R5).</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -10254,7 +10258,7 @@
 2. The totals cover EVERY matching non-reversed invoice across every rep, independent of which reps are expanded or how many detail rows are loaded.
 3. The on-screen grand Totals match the export's aggregate for the same filter set.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S10-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5).</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
@@ -10305,7 +10309,7 @@
 2. A genuine server-side export failure produces NO file and shows the "Ooooops! An error occured" toast — never a malformed/partial file.
 3. An empty-but-loaded result still produces a valid file (header-row-only CSV / no-rows PDF).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-R2a, S14-N2, S14-E3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R2a, S14-N2, S14-E3).</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -10357,7 +10361,7 @@
 3. A filter set just below the cap still generates a complete (possibly very large) PDF.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S14-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E2).</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -10409,7 +10413,7 @@
 2. The dialog's "{Staff Name} is the sales representative on {N} customer{s}." headline matches the returned count.
 3. No deactivation is committed by the pre-check itself — cancelling leaves the staff member's active status unchanged.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Sales By Representative report specification version 15 (S13-R1, S13-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R1, S13-R4).</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10460,7 +10464,7 @@
 2. Under Parts there is an entry labeled Parts Velocity; Inventory Value also lives under Parts. The order of the two inside the Parts section is not fixed — do not fail the test on which of them comes first.
 3. Clicking it opens the Parts Velocity report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10510,7 +10514,7 @@
 2. Report data loads automatically - you do not have to press anything to fetch it.
 3. Rows appear ranked by Demand, highest first (the default order).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-R2, S4-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-R2, S4-R6).</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10561,7 +10565,7 @@
 2. During a filter change, the loading indicator shows again.
 3. The rows already on screen are replaced only when the new data comes back - the table does not blank out and rebuild mid-request.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-R3).</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10613,7 +10617,7 @@
 2. The export downloads successfully — both opening the report and exporting it are allowed by the same ordinary reports access.
 3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -10661,7 +10665,7 @@
           <t>1. The user cannot reach the Reports section.
 2. The Parts Velocity navigation entry is not shown (this is the Reports section's own access control, not a report-specific rule).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-N1).</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10713,7 +10717,7 @@
 3. The export downloads.
 4. Note for the tester: for now ONE ordinary reports access opens all six of these new reports, and no report has a permission of its own. If an extra Parts or Inventory reports permission does exist and switching it OFF blocks this report or its export, that is wrong - mark this Failed and report it. If a separate per-report permission is ever added on purpose in a later release, this test will be updated first, so treat that as a planned change and not as a bug.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-N2, S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-N2, S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -10768,7 +10772,7 @@
 4. Both is an explicit selection returning inventory and Special Order rows together - a deliberate filter value, not the absence of a filter.
 5. Each selection immediately reloads the report limited to that type (no separate Apply step) - under Inventory every row's Type column reads Inventory; under Special Order every row's Type column reads Special Order; under Both, rows of both kinds appear.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R1, S3-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R1, S3-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -10820,7 +10824,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R2).</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -10872,7 +10876,7 @@
 3. With both valid dates selected, the data reloads for that range.
 4. A span wider than 366 days (counting both the start and end dates) is rejected - the selection is not applied.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R3).</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -10924,7 +10928,7 @@
 3. With vendors selected, only parts supplied by any of the selected vendors are shown.
 4. Each change reloads the data from the server.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R4, S2-R5, S2-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R4, S2-R5, S2-R10).</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -10977,7 +10981,7 @@
 3. The description search returns rows whose description contains the word.
 4. Category and vendor names are NOT searched - use their dedicated filters instead (deliberate, to avoid false matches on common words).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R6).</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -11029,7 +11033,7 @@
 2. After step 3 the part disappears - a part must satisfy EVERY active filter to appear (AND logic, not OR).
 3. After step 4 the part is listed again.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R7).</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -11079,7 +11083,7 @@
 2. Only inventory parts stocked in ANY of the selected bins are shown.
 3. The filter allows more than one bin (multi-select).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R8).</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
@@ -11129,7 +11133,7 @@
           <t>1. With any Bin filter active, ALL Special Order rows are excluded (they have no bin location).
 2. Special Order combined with any Bin filter yields an empty result showing the empty state - this is by design, not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -11186,7 +11190,7 @@
 6. With 'All Locations' active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
 7. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
@@ -11234,7 +11238,7 @@
           <t>1. The server returns zero rows and the table shows the empty state.
 2. The empty-state label reads exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R11, S2-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R11, S2-N1).</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -11286,7 +11290,7 @@
 2. The part with no vendor does not appear when any Vendor filter is active.
 3. The inventory part with no bin location does not appear when any Bin filter is active.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-E1, S2-E2, S2-E3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-E1, S2-E2, S2-E3).</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -11337,7 +11341,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-E4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-E4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
@@ -11394,7 +11398,7 @@
 5. With a single location in scope the Location column is hidden.
 6. Both downloads include the Location column in the same position it holds on screen (leftmost, before Type), with the same values — each inventory row's own location, and "Multiple" on the merged Special Order row.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R12, S3-R10, S7-R8, S6-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R12, S3-R10, S7-R8, S6-R11).</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
@@ -11444,7 +11448,7 @@
 2. Each row carries only that one location's On Hand, Min, and Max.
 3. On Hand / Min / Max are NEVER summed across locations.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R1a).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R1a).</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -11495,7 +11499,7 @@
 2. Its movement and profitability values are the SUM of the per-location values.
 3. Its inventory-only columns (On Hand, Turns / Yr, Min, Max) show — (em-dash), because special-order parts are not stocked.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R1a).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R1a).</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -11548,7 +11552,7 @@
 3. Rows with equal Demand keep inventory-before-special-order order.
 4. The Demand header shows the descending sort indicator - this initial order IS the active sort (it is what the remembered view saves until you click another header).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R2).</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11601,7 +11605,7 @@
 3. Null / — values are placed FIRST on ascending and LAST on descending.
 4. Every column is sortable; each header click re-fetches the data (server-resolved) and shows the first page of the re-sorted result; ties keep a stable order.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R3).</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -11651,7 +11655,7 @@
 2. The Type column shows each row's kind as plain text (no badge or chip styling): "Inventory" or "Special Order".
 3. ALL columns - header and cell data, including numbers and money - are left-aligned on screen. (The exports right-align numerics instead: a deliberate export-only difference.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R4, S3-R5, S3-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R4, S3-R5, S3-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11706,7 +11710,7 @@
 5. The icon is focusable and exposes the same text to assistive technology; activating it does NOT trigger a column sort.
 6. No other column header carries an info icon.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R6).</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11758,7 +11762,7 @@
 2. The full value shows on native hover (browser tooltip).
 3. Part # is NEVER truncated - on screen (and in the exports).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R7).</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -11807,7 +11811,7 @@
           <t>1. On Hand, Turns / Yr, Min, and Max show — (em-dash) on special-order rows - always.
 2. The count metrics and money totals are NEVER null: Units Sold / Units Returned / Sold (WO) / Sold (Parts Sale) show 0.00, Demand shows 0, Revenue and Margin show $0.00.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R9, S5-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R9, S5-R5).</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
@@ -11857,7 +11861,7 @@
 2. Part B DOES appear - a part with billed Revenue &gt; 0 is always kept even with no stock movement and no on-hand stock.
 3. (Special Order parts have no such rule: a never-requested special-order part simply produces no row.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-N1).</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -11906,7 +11910,7 @@
           <t>1. The picker lists all 20 available columns, each with a toggle: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
 2. No on-hand cost column is offered - the report computes one internally but it is never selectable and never displayed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R1, S4-R4, S5-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-R1, S4-R4, S5-R6).</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11954,7 +11958,7 @@
 2. The other 6 columns start hidden: Units Returned, Sold (WO), Sold (Parts Sale), Turns / Yr, Min, Max.
 3. When more than one location is in scope the automatic Location column shows as well, leftmost before Type — 15 columns. It is not part of the 14-column default set and is not in the column picker, so its presence is expected and is not a failure of this test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R2, S4-R3, S3-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-R2, S4-R3, S3-R10).</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -12004,7 +12008,7 @@
 2. Columns always render in the fixed canonical left-to-right order regardless of the order they were toggled on (with the automatic Location column, when shown, sitting leftmost before Type): Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
 3. So Units Returned slots in right after Units Sold, Turns/Yr after On Hand, and Min before Max - not appended at the end.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R4, S4-R5, S3-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-R4, S4-R5, S3-R10).</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -12055,7 +12059,7 @@
 3. The saved values take precedence over the first-visit defaults (This Year / Both / active location / 14 columns / Demand-descending).
 4. The same holds after a full page reload.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R6, S1-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-R6, S1-R2).</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -12104,7 +12108,7 @@
 2. That one setting falls back to its default (e.g. the location falls back to the active location); the other saved settings still restore normally.
 3. The report loads without an error.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-R6).</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -12153,7 +12157,7 @@
           <t>1. User 2 sees user 1's saved view (Type = Special Order, Last Quarter, the saved columns and sort).
 2. This is by design: storage is per browser, not tied to the account - there is no per-account separation.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-R6).</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -12203,7 +12207,7 @@
 2. The export produces a file containing only the header/metadata rows and no data columns.
 3. On the next visit the all-hidden selection is NOT restored - the report falls back to the default 14-column set (the saved column selection returns to the last NON-EMPTY selection; all-hidden is the exception).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S4-E1, S4-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-E1, S4-R6).</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -12255,7 +12259,7 @@
 3. After step 3, Units Sold is UNCHANGED - part returns do not affect Units Sold (they feed Units Returned instead).
 4. Units Sold can be 0.00 or negative when reversals exceed sales.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R1, S5-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R1, S5-R4).</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -12305,7 +12309,7 @@
 2. The reversed/voided sale is EXCLUDED from the total (net of reversals).
 3. Only requests on work orders at status Invoiced or Paid count; the window is anchored to the work-order date.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R2, S5-R4, S5-R4b).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R2, S5-R4, S5-R4b).</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -12358,7 +12362,7 @@
 3. After step 3, it decreases by 2.00 - the column reflects the CURRENT state of return records (cancelled returns are excluded), not a snapshot.
 4. After step 4, Units Returned is UNCHANGED - invoice reversals are not returns (they affect Units Sold instead).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R3, S5-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R3, S5-R4).</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -12412,7 +12416,7 @@
 4. Units Returned is independent of the work order's current invoice status.
 5. A part whose ONLY in-window event is a return (no sale, no stock, no revenue) produces no row at all - accepted behavior, the row axis is sales/stock activity.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R3).</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -12464,7 +12468,7 @@
 3. Both are windowed by the WORK-ORDER date (its end date) - with the range moved off those dates, both drop out.
 4. Both workflows feed the report - a parts sale is a separate workflow from a service work order but counts fully.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4).</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
@@ -12518,7 +12522,7 @@
 4. Demand is the report's default ranking signal (a whole number, never null - 0 when none).
 5. A part whose single in-window sale is invoiced and then fully reversed shows Demand 1 with Units Sold 0.00 — the Demand count is not decremented, while the movement nets to zero.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4, S3-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4, S3-E1).</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -12573,7 +12577,7 @@
 4. For a special-order part, the anchor is its most recent vendor-sourced invoiced/paid request.
 5. When the most recent sale is reversed, Last Sale re-anchors to the previous remaining sale (the day count grows accordingly); if no other sale remains it shows —.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4, S5-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4, S5-R5).</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -12623,7 +12627,7 @@
 2. Min and Max show the stored minimum / maximum reorder thresholds for that location, as whole numbers (— when not set).
 3. Min and Max are READ-ONLY display columns - no edit control or slide-over opens; editing part attributes from this report is out of scope in this version.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4, S5-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4, S5-R5).</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
@@ -12677,7 +12681,7 @@
 3. Part C shows a NEGATIVE Turns / Yr with a leading minus (because Units Sold can be negative).
 4. Special Order rows always show — (not applicable).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4).</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
@@ -12730,7 +12734,7 @@
 5. All five are computed from the RAW (unrounded) Revenue / COGS / billed-units totals and rounded ONCE at the end - not built from already-rounded intermediates.
 6. The same formulas apply to inventory and special-order rows (for special-order, from the vendor part requests).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4a).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4a).</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
@@ -12781,7 +12785,7 @@
 2. This netting is consistent with inventory Units Sold, which already nets reversals via the stock add-back.
 3. A voided sale therefore inflates NO column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4b, S5-R4a).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4b, S5-R4a).</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
@@ -12834,7 +12838,7 @@
 3. Row 3: Unit Cost, Sell Price, and Margin % all show — together - which happens ONLY when both billed units ≤ 0 AND Revenue ≤ 0.
 4. The three triggers are independent: Unit Cost/Sell Price null on billed units ≤ 0; Margin % null on Revenue ≤ 0.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R4a, S3-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4a, S3-R9).</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
@@ -12885,7 +12889,7 @@
 4. Demand: whole number. Min, Max: whole numbers (— when null). Last Sale: 'N days' (42 days), — when null.
 5. Rounding is half AWAY from zero: 8.45% displays 8.5% and -8.45% displays -8.5% (a tie rounds up in magnitude); this applies to all money and one-decimal values.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R5, S5-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R5, S5-R7).</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
@@ -12935,7 +12939,7 @@
 2. The special-order core part does NOT appear either.
 3. Parts flagged as a core are excluded from both result sets by design.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R1, S5-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R1, S5-R2).</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -12987,7 +12991,7 @@
 2. Sold (WO) + Sold (Parts Sale) together DO equal the billed-units basis (work orders are only Service- or Parts-type) - but neither equals the movement-based Units Sold.
 3. On the special-order row, everything reconciles: Units Sold = Sold (WO) + Sold (Parts Sale) = billed units (they share the vendor-request quantity as one source).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R7).</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
@@ -13039,7 +13043,7 @@
 3. The window is the whole-day span inclusive of BOTH the start and end dates, with a floor of 1 day - a single-day range (Today) computes normally (Window = 1 for the Turns / Yr divisor).
 4. Last Sale is not windowed at all (all-time).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R7).</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
@@ -13094,7 +13098,7 @@
 3. On Hand has gone down by exactly 2.50 from what it was before the sale.
 4. No value anywhere on the row has been quietly rounded to a whole number.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S5-R1, S5-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R1, S5-R5).</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -13142,7 +13146,7 @@
           <t>1. The ⋯ overflow button sits leftmost in the toolbar's action cluster.
 2. The menu holds exactly two items, in this order: Download (PDF), then Download (CSV).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R1).</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
@@ -13192,7 +13196,7 @@
 2. The exported rows match what the on-screen grid was showing.
 3. Each file (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R2, S6-R11); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R2, S6-R11); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
@@ -13242,7 +13246,7 @@
 2. Columns appear in the CANONICAL order (the fixed on-screen order) - the re-enabled Units Returned sits right after Units Sold, NOT appended at the end.
 3. The export mirrors the visible grid.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R3, S4-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R3, S4-R4).</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -13293,7 +13297,7 @@
 2. Every column's sort is honored in the export - including Min and Max.
 3. The export renders the EXACT server order, including null placement (nulls first on ascending, last on descending) - the export and the on-screen grid match; there is no on-screen-vs-export null-sorting difference.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R4, S3-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R4, S3-R3).</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
@@ -13347,7 +13351,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6).</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
@@ -13399,7 +13403,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6, S6-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6, S6-R8).</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -13448,7 +13452,7 @@
           <t>1. A null value renders as — (em-dash) in BOTH the CSV and the PDF, in every nullable field: Unit Cost, Sell Price, Margin %, On Hand, Turns / Yr, Last Sale, Min, Max.
 2. Revenue, Margin, and the count metrics are never null in the exports either ($0.00 / 0.00 / 0).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R7, S6-R8, S3-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R7, S6-R8, S3-R9).</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -13499,7 +13503,7 @@
 4. This is a deliberate export-only treatment - the on-screen table is all-left-aligned; the difference is documented, not a defect.
 5. The CSV is plain data — the alignment assertions apply to the PDF only; how a spreadsheet displays the CSV is not part of this test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R10, S3-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R10, S3-R8).</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -13550,7 +13554,7 @@
 2. An error toast is shown on failure; when the server provides a message, that server message is shown.
 3. Otherwise the failure toast reads exactly: "Failed to export velocity report (csv)" or "Failed to export velocity report (pdf)" — lowercase (csv)/(pdf); the success/failure casing mix is the shipped wording, documented as-is (not a bug).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S6-R9, S6-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R9, S6-N1).</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -13603,7 +13607,7 @@
 3. After narrowing below the cap, the downloads work again.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (Story 6 exports).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (Story 6 exports).</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -13657,7 +13661,7 @@
 4. Note for the tester: a very large view is refused politely with "This report is too large to export. Narrow the date range or filters, then try again." — that message is expected and is NOT this failure. This test is about a medium-sized view where the CSV works but the PDF errors.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (Story 6 exports).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (Story 6 exports).</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
@@ -13706,7 +13710,7 @@
 2. There is NO card border-radius - the table runs edge to edge.
 3. The layout matches the application's other reports.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S7-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S7-R1).</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -13759,7 +13763,7 @@
 4. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 5. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this - 32px/24px toolbar padding, a 1px header border, 2rem edge padding - are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S7-R2, S7-R3, S7-R4, S7-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S7-R2, S7-R3, S7-R4, S7-R5).</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
@@ -13809,7 +13813,7 @@
 2. In BOTH light mode and dark mode the grey ⓘ info icon is clearly visible against the cell behind it - you can see it at a glance without leaning in, and it does not disappear into the background.
 3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes. Only report it if the icon is hard to see. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S7-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S7-R6).</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
@@ -13860,7 +13864,7 @@
 2. Paging is resolved on the server: moving to another page issues a fresh backend request for that page.
 3. This keeps the report responsive at scale (organizations can carry 50-60k parts, multiplied across locations).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R10).</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
@@ -13910,7 +13914,7 @@
 2. There is no client-side-only narrowing - every filter or search change re-queries the server.
 3. Each change returns the FIRST page of the new result set.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S2-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R10).</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
@@ -13961,7 +13965,7 @@
 2. Null values are placed FIRST on ascending and LAST on descending - as a server sort semantic, so the same order appears on screen and in the exports.
 3. Ties keep a stable order (no explicit secondary key).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S3-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R3).</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
@@ -14013,7 +14017,7 @@
 3. Both requests succeed with only the ordinary reports access turned on - nothing else had to be enabled.
 4. Note for the tester: if the back end refuses either request for a user who has the ordinary reports access, mark this Failed and report it. If an extra Parts or Inventory reports permission exists in the system it must not change these results - for now it is hidden from the screen and enforces nothing. A per-report permission added on purpose in a later release is a planned change, not a bug, and this test will be updated first.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Parts Velocity report specification version 4 (S1-R4, S1-N2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-R4, S1-N2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
@@ -14069,7 +14073,7 @@
 3. The quantity behind the QuickBooks amount matches the Units Sold value on the report (2.50) — the two systems agree.
 4. No second or correcting journal entry is created to patch up a wrong amount.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and this point is not covered by any of the six report specifications — it comes from the engineering technical plan.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and this point is not covered by any of the six report specifications — it comes from the engineering technical plan.</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -14120,7 +14124,7 @@
 2. Clicking it opens the report.
 3. The entry sits BELOW the pre-existing report links — Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency — the new reports are added below those items without moving or disturbing them.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R1).</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -14169,7 +14173,7 @@
           <t>1. Technician A has exactly ONE row.
 2. Technician B has NO row - only technicians with clocked time in the selected range at the selected location(s) appear.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R2).</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -14218,7 +14222,7 @@
 2. Because a range never extends past now, the current-month default effectively shows the month to date.
 3. The location filter defaults to the user's currently active location (the one in the application's global location switcher).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R3, S1-R6, S9-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R3, S1-R6, S9-R2).</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -14268,7 +14272,7 @@
 2. A valid Custom range applies normally.
 3. A Custom span wider than 366 days (matching the largest preset) is rejected - it cannot be applied.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R4, S1-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R4, S1-R5).</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
@@ -14318,7 +14322,7 @@
 2. The existing rows are replaced only when the new data returns.
 3. The toolbar remains interactive during the load.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R10).</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -14371,7 +14375,7 @@
 3. EVERY record is day-grouped and windowed in a SINGLE report-level time zone - the active workplace's - regardless of the location where it was clocked (a record's day, the current-month boundary, and the midnight split all use that one zone).
 4. This matches the Timesheet Activities report's single-time-zone grouping.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R7).</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -14418,7 +14422,7 @@
         <is>
           <t>1. The Technician Utilization report does NOT appear in the navigation.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -14469,7 +14473,7 @@
 2. The Summary row is hidden.
 3. Clearing every technician shows the SAME message and hides the Summary row — this version does not use distinct copy for genuinely-no-data vs a cleared filter.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-N2, S3-N1, S5-N1, S9-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-N2, S3-N1, S5-N1, S9-N2).</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
@@ -14524,7 +14528,7 @@
 5. Hours show two decimal places with NO thousands separator (e.g. "107.70"), rounded from the unrounded hours using round-half-up (a tie rounds away from zero - 0.005 → 0.01).
 6. When more than one location is in scope the automatic Location column also appears, leftmost before Technician — it is not in the Column Selection control and its presence is expected.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R1, S2-R2, S2-R3, S2-R4, S2-R5, S9-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R1, S2-R2, S2-R3, S2-R4, S2-R5, S9-R9).</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
@@ -14572,7 +14576,7 @@
           <t>1. Utilization % = work-order hours as a percentage of total clocked hours, computed from the unrounded hours (not from the already-rounded displays).
 2. It shows one decimal place followed by a percent sign, rounded round-half-up (66.65% → 66.7%).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R6, S2-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R6, S2-R7).</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
@@ -14622,7 +14626,7 @@
 2. No row shows more than 100% - work-order hours are always part of total clocked hours.
 3. The "—" (undefined, total = 0) state is unreachable on a rendered technician or day row, because only technicians with clocked time get rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-E1, S2-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E1, S2-R7).</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -14674,7 +14678,7 @@
 2. In a single-location view it is simply that one location's rate × the technician's internal hours.
 3. The value shows as dollars with two decimals and commas between thousands (e.g. "$1,234.50").
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R8, S2-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R8, S2-R9).</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
@@ -14727,7 +14731,7 @@
 3. NO column header other than Est. Lost Labor shows the information icon.
 4. Est. Lost Labor can be turned OFF in the Column Selection control; when it is off the column, its bold styling and its information icon are all absent, and the report still works normally.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R10, S2-R11, S8-R4, S8-R6, S8-R7, S8-N1, S10-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R10, S2-R11, S8-R4, S8-R6, S8-R7, S8-N1, S10-R3).</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
@@ -14777,7 +14781,7 @@
 2. Technician B also shows "$0.00" - a configured rate of exactly $0.00 is a KNOWN rate that values the hours at $0.00, not "—".
 3. "$0.00" means 'the rate is known and there is nothing (or $0) to value' - a different state from "—" ('the rate is unknown').
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E2).</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -14827,7 +14831,7 @@
 2. The "—" cell carries the assistive-technology label "No default labor rate configured" (distinguishing it from "$0.00", which reads as its dollar value).
 3. The technician's Internal Hours column still shows all the internal hours (they are counted even though they cannot be valued).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-E3, S8-R11, S2-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E3, S8-R11, S2-R4).</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14877,7 +14881,7 @@
 2. The amount shows as a normal "$X.XX" with NO partial-value indicator in this version - so the row's Est. Lost Labor values fewer hours than its Internal Hours column shows.
 3. This is a documented known limitation (a partial-value indicator is a possible follow-up) - expected behavior, not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-E4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E4).</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -14928,7 +14932,7 @@
 2. The Technician header shows the ascending sort indicator.
 3. The active sort header exposes its state to assistive technology (aria-sort = ascending on the Technician header; none on the others).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R12, S8-R8, S8-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R12, S8-R8, S8-R10).</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -14982,7 +14986,7 @@
 4. Sorting is applied on screen to the loaded rows - NO reload/server request happens.
 5. Technicians tied in the sorted column are ordered by Technician name A to Z; two technicians sharing the same display name keep a stable order between renders.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R13, S2-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R13, S2-R14).</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -15031,7 +15035,7 @@
           <t>1. After the reload, the rows are back to Technician name A to Z (the sort reset).
 2. On the return visit, the sort is again Technician A to Z - sort is NOT persisted (unlike the date range, technician selection, and location selection, which are).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R15).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R15).</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -15081,7 +15085,7 @@
 2. The Summary row stays pinned at the bottom.
 3. Each technician's expanded day rows stay under that technician, still in date order (earliest to latest) - they do not re-sort by the clicked column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R16).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R16).</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15131,7 +15135,7 @@
 2. Among themselves, the "—" rows are ordered by Technician name A to Z.
 3. A "$0.00" value is a number, not "—" - it sorts as zero (lowest ascending, above only the — group).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S2-R17).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R17).</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -15182,7 +15186,7 @@
 3. It uses the same number formats as the technician rows.
 4. Its values carry NO label prefix such as "TOTAL:" or "AVG:".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S3-R1, S3-R2, S3-R6, S3-R7, S8-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R1, S3-R2, S3-R6, S3-R7, S8-R5).</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
@@ -15232,7 +15236,7 @@
 2. Eye-summing the displayed rows MAY differ from the displayed Summary by 0.01 — one unit in the last decimal (these values are HOURS, not money) — expected in a compute-from-unrounded report, not a defect.
 3. With every technician selected, the Summary row equals the shop totals for the full date range at the selected location(s).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S3-R3, S5-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R3, S5-E1).</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
@@ -15281,7 +15285,7 @@
           <t>1. The Summary Utilization % shows the WEIGHTED rate - the visible technicians' total work-order hours as a percentage of their total clocked hours, from unrounded hours (10.0% in the example).
 2. It is NOT the average of the per-technician percentages (not 50.0%).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S3-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R4).</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
@@ -15330,7 +15334,7 @@
 2. A visible technician whose value is "—" contributes NOTHING to the sum - so the Summary understates true lost labor whenever any visible technician is "—" or partially valued (documented, expected).
 3. The Summary shows "—" only when EVERY visible technician's Est. Lost Labor is "—".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S3-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R5).</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
@@ -15381,7 +15385,7 @@
 2. Its accessible name reflects the NEXT action, scoped to that technician: when collapsed it reads Expand, then that technician's name, then daily breakdown (for example: Expand John Smith's daily breakdown); when expanded it reads Collapse, then the same name and words.
 3. The control is keyboard-focusable, toggles on Enter and Space, and exposes its expanded/collapsed state to assistive technology.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R1, S8-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R1, S8-R12).</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
@@ -15435,7 +15439,7 @@
 4. With several locations selected, a day's row POOLS that day's hours across the selected locations - one day row per date, not one per location.
 5. Note for the tester: you do not need developer tools for this test - just watch the screen.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R2, S4-N1, S9-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R2, S4-N1, S9-R4).</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
@@ -15485,7 +15489,7 @@
 2. The day's Est. Lost Labor is valued per location exactly like a technician row (that location's default labor rate × that day's internal hours there).
 3. Hours 2dp / Utilization one decimal + % / dollars with commas - all identical to the row formats, computed from unrounded values and rounded once.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R3, S2-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R3, S2-R8).</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
@@ -15538,7 +15542,7 @@
 3. Its accessible name reflects the next action: "Expand all technicians" when it will expand, "Collapse all technicians" when every row is already expanded.
 4. It is keyboard-focusable, toggles on Enter/Space, and exposes its state to assistive technology.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R4, S8-R12, S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R4, S8-R12, S8-R3).</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
@@ -15588,7 +15592,7 @@
 2. On a fresh visit, all rows start collapsed - expansion is never persisted.
 3. Deselecting and re-selecting a technician (an on-screen operation) does NOT change the expansion state of the other rows - the expanded row stays expanded.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R5).</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
@@ -15638,7 +15642,7 @@
 2. On the first visit, EVERY technician is selected.
 3. All technicians' rows are shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S5-R1, S5-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R1, S5-R2).</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
@@ -15691,7 +15695,7 @@
 4. Re-selecting the technician shows the row again (and the Summary recalculates back).
 5. Note for the tester: you do not need developer tools for this test - just watch the screen.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S5-R3, S5-R4, S5-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R3, S5-R4, S5-R5).</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -15743,7 +15747,7 @@
 3. After step 3, your deselected technician STAYS deselected across the range change, while the newly-appearing technician is SELECTED (never explicitly deselected).
 4. After step 4, the newly-appearing technician is selected even though you had cleared all - "Clear all" only deselected the technicians listed at the time.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S5-R6, S5-R7, S5-R8, S5-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R6, S5-R7, S5-R8, S5-R9).</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
@@ -15793,7 +15797,7 @@
 2. All other technicians - including any who appear for the first time - are selected.
 3. The saved date range and location selection are restored alongside.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S5-R10, S1-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R10, S1-R8).</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
@@ -15843,7 +15847,7 @@
 2. The link is distinguished by more than color - it carries an underline (or equivalent non-color affordance), is keyboard-focusable with a visible focus indicator, and activates on Enter.
 3. The Summary row's Total Hours value is NOT a link.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S6-R1, S6-N1, S8-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R1, S6-N1, S8-R14).</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -15893,7 +15897,7 @@
 2. It is already filtered to that technician.
 3. It uses the same date range that was active on the Technician Utilization report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S6-R2, S6-R3, S6-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R2, S6-R3, S6-R4).</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
@@ -15944,7 +15948,7 @@
 2. Under this exact scope (same range, same single location, closed records) a mismatch IS a defect.
 3. The two documented scope differences (open clocks, multi-location drill-through) are covered by separate cases and are NOT defects.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R9).</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
@@ -15994,7 +15998,7 @@
 2. The two reports, loaded at different moments, MAY differ by the elapsed open time - this is a deliberate scope difference of the reconciliation guarantee, EXPECTED and NOT a defect.
 3. Reloading the Technician Utilization report takes a fresh snapshot (the value grows by the elapsed time).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R9, S1-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R9, S1-E1).</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -16045,7 +16049,7 @@
 2. Timesheet Activities opens for the user's currently active shop, so it shows one location's portion - it will differ from (or be disjoint with) the multi-location row value.
 3. This is a KNOWN drill-through limitation, EXPECTED and NOT a data defect (the same applies when the single selected location is not the active shop).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S6-R6, S1-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R6, S1-R9).</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
@@ -16093,7 +16097,7 @@
           <t>1. Timesheet Activities opens filtered to that technician.
 2. The date range covers ONLY that single day.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S6-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R5).</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -16144,7 +16148,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R1, S7-R2, S7-R3, S7-R4, S8-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R1, S7-R2, S7-R3, S7-R4, S8-R2).</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -16195,7 +16199,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R5, S7-R6, S7-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R5, S7-R6, S7-R12).</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -16245,7 +16249,7 @@
 2. The CSV shows the technician rows and the Summary row - always this summary-level content; it does NOT vary by the summary/expanded choice (no day rows).
 3. Any value containing a comma (e.g. "$1,234.50") is wrapped in double quotes per standard CSV escaping, so the columns parse correctly.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R7, S7-R10, S7-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R7, S7-R10, S7-R12).</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -16300,7 +16304,7 @@
 5. Every download also mirrors the columns currently shown on screen — a column hidden in the Column Selection control is absent from the files, and a re-shown column comes back.
 6. Note for the tester: when you have more than one location in scope, the files also carry a Location column even though it is not in the Column Selection control. That is correct - it appears by itself. With a single location in scope there is no Location column, and that is also correct.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R8, S7-R9, S7-R10, S7-R13, S7-E1, S9-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R8, S7-R9, S7-R10, S7-R13, S7-E1, S9-R8).</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -16350,7 +16354,7 @@
           <t>1. The downloaded files use the same column order and number formats as the on-screen report, including the "—" rendering for an unknown Est. Lost Labor.
 2. Rows in EVERY download are ordered by Technician name A to Z (the default order) - the on-screen column sort is client-side only and is NOT carried into the export.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R10, S7-R10a).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R10, S7-R10a).</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
@@ -16402,7 +16406,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-R11, S7-N2, S7-N3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R11, S7-N2, S7-N3).</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -16453,7 +16457,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S7-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-N1).</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -16502,7 +16506,7 @@
           <t>1. When a download starts, a success notification reads exactly: "Download started".
 2. When a download fails, an error notification reads exactly: "Failed to download report".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (§7 notifications table, Story 7 has no S, §7 is the closing reference).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (§7 notifications table, Story 7 has no S, §7 is the closing reference).</t>
         </is>
       </c>
       <c r="H315" s="2" t="inlineStr">
@@ -16555,7 +16559,7 @@
 3. After narrowing below the cap, the downloads work again.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (Story 7 exports).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (Story 7 exports).</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
@@ -16608,7 +16612,7 @@
 3. "All locations" acts as a select-all shortcut: choosing it selects every accessible location; unchecking one location leaves the remaining specific locations selected - the selection is always the concrete set of checked locations.
 4. With more than one location selected, a Location column appears in the table and each row names its location - or reads "Multiple" for a technician whose hours span more than one of them. (Where that column sits on screen is checked by its own test.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr">
@@ -16662,7 +16666,7 @@
 4. Scoping never goes beyond the user's accessible locations - a location the user cannot access is never included.
 5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R3, S9-R4, S9-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R3, S9-R4, S9-R5).</t>
         </is>
       </c>
       <c r="H318" s="2" t="inlineStr">
@@ -16712,7 +16716,7 @@
 3. The report loads without an error in both cases.
 4. The same fallback happens when you deselect every location by hand in the Location filter — the report loads the currently active location's rows rather than showing nothing.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R6, S1-R8, S9-R2, S9-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R6, S1-R8, S9-R2, S9-R7).</t>
         </is>
       </c>
       <c r="H319" s="2" t="inlineStr">
@@ -16763,7 +16767,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H320" s="2" t="inlineStr">
@@ -16825,7 +16829,7 @@
 7. With a single location in scope the Location column is hidden.
 8. Every download — both PDF views and the CSV — includes the Location column in its on-screen leftmost position, carrying the same values you just read on screen.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S9-R9, S9-R10, S8-R15, S10-R4, S7-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R9, S9-R10, S8-R15, S10-R4, S7-R13).</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -16886,7 +16890,7 @@
 7. Est. Lost Labor can now be hidden like any other column (it used to be always on).
 8. Your column choice is remembered in this browser and is still applied when you come back.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R5, S10-R6, S8-R16).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R5, S10-R6, S8-R16).</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16936,7 +16940,7 @@
 2. The toolbar controls run, left to right: the three-dot download menu, the Column Selection control, the date-range picker, the technician filter, and the Location filter (rightmost).
 3. The expand/collapse-all control is NOT a toolbar control - it lives in the table header (in the Technician column).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S8-R1, S8-R2, S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S8-R1, S8-R2, S8-R3).</t>
         </is>
       </c>
       <c r="H323" s="2" t="inlineStr">
@@ -16989,7 +16993,7 @@
 3. The Total Hours link's non-color affordance and focus indicator apply in both modes.
 4. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes, and only report it if you cannot. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S8-R9, S8-R13, S8-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S8-R9, S8-R13, S8-R14).</t>
         </is>
       </c>
       <c r="H324" s="2" t="inlineStr">
@@ -17040,7 +17044,7 @@
 2. Expanding a technician row issues an on-demand backend request that returns that technician's per-day breakdown.
 3. Because expansion state resets (all collapsed) on any data reload, nothing is lost by the lazy loading - re-expanding fetches fresh day data.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S4-R2, S4-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R2, S4-R5).</t>
         </is>
       </c>
       <c r="H325" s="2" t="inlineStr">
@@ -17093,7 +17097,7 @@
 3. The technician filter causes NO server request - it works on screen only (hide/show + Summary recalculation).
 4. Column sorting causes NO server request - it is applied on screen to the loaded rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Technician Utilization report specification version 5 (S1-R5, S9-R3, S2-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R5, S9-R3, S2-R13).</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -17145,7 +17149,7 @@
 2. Clicking it opens the Work In Progress report.
 3. The browser page title is exactly "Work In Progress - Report | ShopView" — a plain hyphen with one space on each side.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-R1, S1-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S1-R1, S1-R5).</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">
@@ -17197,7 +17201,7 @@
 3. There is NO on-screen status filter — the four tabs take the place of a status filter (the tab a job lands in is derived from its status and whether any work has started).
 4. Each tab's count matches the number of work-order rows actually listed in that tab.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-R2, S1-R3, S1-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S1-R2, S1-R3, S1-R4).</t>
         </is>
       </c>
       <c r="H328" s="2" t="inlineStr">
@@ -17246,7 +17250,7 @@
           <t>1. Only the four progress tabs exist — there is no Trend tab and no chart of work-in-progress dollars over time.
 2. No screen in the report reads or displays the nightly snapshot history.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R7).</t>
         </is>
       </c>
       <c r="H329" s="2" t="inlineStr">
@@ -17295,7 +17299,7 @@
           <t>1. All five seeded work orders appear in the report — each one qualifies because it is a service work order, its status is one of Estimate, Approved, In Progress, Review, or Complete, and it belongs to a selected location.
 2. Each appears in the tab its status places it in (see the WIP — Tab Placement cases).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R1).</t>
         </is>
       </c>
       <c r="H330" s="2" t="inlineStr">
@@ -17347,7 +17351,7 @@
 2. The part-sale work order does not appear anywhere either.
 3. No excluded work order's money is counted in any figure.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-R2, S2-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R2, S2-R3).</t>
         </is>
       </c>
       <c r="H331" s="2" t="inlineStr">
@@ -17397,7 +17401,7 @@
           <t>1. Each qualifying work order appears exactly once, in exactly one tab.
 2. The work order with nothing approved yet still appears (in the Estimates tab), with its earned and remaining both showing "$0.00".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R4).</t>
         </is>
       </c>
       <c r="H332" s="2" t="inlineStr">
@@ -17447,7 +17451,7 @@
 2. The existing rows are replaced only when the new data returns (the table does not go blank and stay blank mid-load).
 3. Both a date-range change and a location change reload the report's rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-R5, S2-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R5, S2-R6).</t>
         </is>
       </c>
       <c r="H333" s="2" t="inlineStr">
@@ -17500,7 +17504,7 @@
 3. Every tab label count reads "(0)".
 4. When only one tab is empty, that tab shows the no-data message, no Totals row, and a "(0)" count while the populated tabs still show their rows normally.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S2-N1, S2-N2, S6-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-N1, S2-N2, S6-N1).</t>
         </is>
       </c>
       <c r="H334" s="2" t="inlineStr">
@@ -17550,7 +17554,7 @@
 2. The Complete work order appears in the "Completed" tab and nowhere else.
 3. The In Progress and Review work orders appear in the "Approved - partially completed" tab and nowhere else.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S3-R1, S3-R2, S3-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S3-R1, S3-R2, S3-R3).</t>
         </is>
       </c>
       <c r="H335" s="2" t="inlineStr">
@@ -17600,7 +17604,7 @@
 2. The Approved work order with a received part (and no clocked time) also appears in the "Approved - partially completed" tab — either kind of started work counts.
 3. The Approved work order with no clocked time and no received part appears in the "Approved - not started" tab and nowhere else.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S3-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S3-R4).</t>
         </is>
       </c>
       <c r="H336" s="2" t="inlineStr">
@@ -17654,7 +17658,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R1, S4-R3, S4-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R1, S4-R3, S4-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
       <c r="H337" s="2" t="inlineStr">
@@ -17707,7 +17711,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R2, S4-R3, S8-R3, S8-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R2, S4-R3, S8-R3, S8-R4); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
       <c r="H338" s="2" t="inlineStr">
@@ -17758,7 +17762,7 @@
 2. Clicking it opens that work order in the SAME browser tab (not a new tab).
 3. The browser's back navigation returns you to the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R5).</t>
         </is>
       </c>
       <c r="H339" s="2" t="inlineStr">
@@ -17808,7 +17812,7 @@
 2. The badge is color-coded per the application's standard status colors.
 3. The label text is always present, so color is never the sole signal of the status.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R6, S10-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R6, S10-R8).</t>
         </is>
       </c>
       <c r="H340" s="2" t="inlineStr">
@@ -17863,7 +17867,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R7, S4-R8, S4-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R7, S4-R8, S4-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H341" s="2" t="inlineStr">
@@ -17912,7 +17916,7 @@
           <t>1. The Customer column shows the customer's company name.
 2. The cell is blank when no customer name exists.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R11).</t>
         </is>
       </c>
       <c r="H342" s="2" t="inlineStr">
@@ -17963,7 +17967,7 @@
 2. A same-day work order shows "0 days" and a one-day-old work order shows "1 days".
 3. The value is NOT grammatically pluralized: "1 days" (not "1 day") is the correct, expected rendering.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R12).</t>
         </is>
       </c>
       <c r="H343" s="2" t="inlineStr">
@@ -18015,7 +18019,7 @@
 2. Otherwise it shows "Xd ago" (for example "3d ago").
 3. A work order with no recorded activity shows "—".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R13).</t>
         </is>
       </c>
       <c r="H344" s="2" t="inlineStr">
@@ -18067,7 +18071,7 @@
 2. A negative value shows a leading minus before the "$" — for example "-$1,234.56".
 3. A genuine zero shows "$0.00".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R14).</t>
         </is>
       </c>
       <c r="H345" s="2" t="inlineStr">
@@ -18120,7 +18124,7 @@
 2. For the over-clocked line, Labor Earned never exceeds the full quoted value of that line ($400.00 in the example) — the earned share is capped at the quote per line.
 3. With several approved labor lines, Labor Earned is the sum of each line's capped earned share.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R15).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R15).</t>
         </is>
       </c>
       <c r="H346" s="2" t="inlineStr">
@@ -18171,7 +18175,7 @@
           <t>1. Labor Remaining equals the total quoted value of the approved labor minus Labor Earned (in the example, $400.00 − $100.00 = $300.00).
 2. Labor Earned + Labor Remaining always equals the total quoted value of the approved labor.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R16).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R16).</t>
         </is>
       </c>
       <c r="H347" s="2" t="inlineStr">
@@ -18222,7 +18226,7 @@
           <t>1. Parts Earned equals the sell value of the approved-line parts already received (in the example, $100.00).
 2. Parts not yet received contribute nothing to Parts Earned.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R17).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R17).</t>
         </is>
       </c>
       <c r="H348" s="2" t="inlineStr">
@@ -18274,7 +18278,7 @@
           <t>1. Parts Remaining equals the sell value of approved-line parts ordered but not yet received (in the example, $100.00).
 2. For the core-charge part, Parts Remaining values the outstanding quantity at its sell price INCLUDING the core charge.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R18).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R18).</t>
         </is>
       </c>
       <c r="H349" s="2" t="inlineStr">
@@ -18329,7 +18333,7 @@
 3. Total equals Earned plus Remaining.
 4. The Total is NOT the work order's stored grand total — it excludes tax, fees, discounts, and non-approved lines, so a difference from the work order's own grand total is EXPECTED, not a data error.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R19, S4-R20, S4-R21).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R19, S4-R20, S4-R21).</t>
         </is>
       </c>
       <c r="H350" s="2" t="inlineStr">
@@ -18379,7 +18383,7 @@
           <t>1. The work order's Labor/Parts Earned, Labor/Parts Remaining, Earned, Remaining, and Total are unchanged.
 2. Only approved lines (line status authorized or complete) contribute to the report's money — not-yet-approved lines contribute nothing.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R15).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R15).</t>
         </is>
       </c>
       <c r="H351" s="2" t="inlineStr">
@@ -18431,7 +18435,7 @@
 2. On screen it is colored green when positive and red when negative; the overrun job shows a negative red value, the under-estimate job a positive green value.
 3. A value of exactly zero shows unsigned as "0.0" (never "+0.0" or blank) in the default text color.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R23, S4-R24, S4-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R23, S4-R24, S4-E2).</t>
         </is>
       </c>
       <c r="H352" s="2" t="inlineStr">
@@ -18481,7 +18485,7 @@
           <t>1. Every money column — Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, and Total — shows "$0.00".
 2. The row still appears in the Estimates tab (it is not hidden for having no value).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-E1, S2-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-E1, S2-R4).</t>
         </is>
       </c>
       <c r="H353" s="2" t="inlineStr">
@@ -18534,7 +18538,7 @@
 2. After more time accrues, a refresh shows a larger earned share for that line.
 3. Labor Earned never exceeds the line's full quoted value, no matter how long the clock keeps running — the per-line cap still applies.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R15).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R15).</t>
         </is>
       </c>
       <c r="H354" s="2" t="inlineStr">
@@ -18582,7 +18586,7 @@
         <is>
           <t>1. The rows are sorted by Days Open, longest-open first (descending).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R25).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R25).</t>
         </is>
       </c>
       <c r="H355" s="2" t="inlineStr">
@@ -18635,7 +18639,7 @@
 3. The third click returns to ascending — there is no third "cleared" state.
 4. Only one column sorts at a time: clicking another header replaces the previous sort.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R26).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R26).</t>
         </is>
       </c>
       <c r="H356" s="2" t="inlineStr">
@@ -18692,7 +18696,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R27, S4-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R27, S4-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H357" s="2" t="inlineStr">
@@ -18743,7 +18747,7 @@
 2. The Totals row stays pinned at the bottom, out of the sort.
 3. The other tab's order is not changed by the first tab's sort action.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R28).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R28).</t>
         </is>
       </c>
       <c r="H358" s="2" t="inlineStr">
@@ -18792,7 +18796,7 @@
           <t>1. The strip shows seven figures, in this order: Total Earned, Total Remaining, Not Started, Started — Earned, Started — Remaining, Ready to Invoice, and Estimates.
 2. Every figure shows US-dollar currency with a leading "$", two decimals, and thousands separators.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R1, S5-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R1, S5-R10).</t>
         </is>
       </c>
       <c r="H359" s="2" t="inlineStr">
@@ -18842,7 +18846,7 @@
           <t>1. Total Earned is shown larger than the other figures and with a colored underline — it is the strip's hero figure.
 2. Total Earned equals Started — Earned plus Ready to Invoice, to the cent.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R2).</t>
         </is>
       </c>
       <c r="H360" s="2" t="inlineStr">
@@ -18890,7 +18894,7 @@
         <is>
           <t>1. Total Remaining equals Not Started plus Started — Remaining, to the cent.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R3).</t>
         </is>
       </c>
       <c r="H361" s="2" t="inlineStr">
@@ -18942,7 +18946,7 @@
 2. Started — Earned equals the total Earned of the jobs in the "Approved - partially completed" tab, and Started — Remaining equals that tab's total Remaining.
 3. Ready to Invoice equals the total Earned of the jobs in the "Completed" tab.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R4, S5-R5, S5-R6, S5-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R4, S5-R5, S5-R6, S5-R7).</t>
         </is>
       </c>
       <c r="H362" s="2" t="inlineStr">
@@ -18995,7 +18999,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R8, S5-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R8, S5-R9).</t>
         </is>
       </c>
       <c r="H363" s="2" t="inlineStr">
@@ -19050,7 +19054,7 @@
 7. Estimates — "Quotes the customer has not approved yet — not counted in the totals."
 8. Each explanation appears on hover, on keyboard focus, and on tap.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S5-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R12).</t>
         </is>
       </c>
       <c r="H364" s="2" t="inlineStr">
@@ -19101,7 +19105,7 @@
 2. The Totals row's Total cell is pinned far right and shown in bold, matching the column.
 3. The Totals row uses the same number formats as the data rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S6-R1, S6-R4, S6-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S6-R1, S6-R4, S6-R5).</t>
         </is>
       </c>
       <c r="H365" s="2" t="inlineStr">
@@ -19154,7 +19158,7 @@
 3. The Inv. Hrs total uses the same green (positive) / red (negative) / default (exactly 0.0) coloring as a data row.
 4. Note for the tester: the Inv. Hrs total can only be checked on screen. On this build a download that includes Inv. Hrs is refused, so do not try to verify this column from a file.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S6-R2, S6-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S6-R2, S6-R3).</t>
         </is>
       </c>
       <c r="H366" s="2" t="inlineStr">
@@ -19205,7 +19209,7 @@
 2. Selecting one or more advisors narrows the visible jobs to those advisors instantly, on screen only — no reload and no loading indicator.
 3. With two advisors selected, jobs for either advisor are shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R1).</t>
         </is>
       </c>
       <c r="H367" s="2" t="inlineStr">
@@ -19258,7 +19262,7 @@
 3. Selecting customers narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one customer is selected.
 4. Clear returns the filter to "All customers" and every job is shown again.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R2, S7-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R2, S7-R3).</t>
         </is>
       </c>
       <c r="H368" s="2" t="inlineStr">
@@ -19314,7 +19318,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R4, S7-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R4, S7-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H369" s="2" t="inlineStr">
@@ -19365,7 +19369,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R6).</t>
         </is>
       </c>
       <c r="H370" s="2" t="inlineStr">
@@ -19419,7 +19423,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R7, S7-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R7, S7-R8).</t>
         </is>
       </c>
       <c r="H371" s="2" t="inlineStr">
@@ -19477,7 +19481,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R9, S7-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R9, S7-R10); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H372" s="2" t="inlineStr">
@@ -19528,7 +19532,7 @@
 2. If the selection resolves to none, the report falls back to the user's currently active location rather than showing everything or erroring.
 3. A saved selection that no longer resolves also falls back to the active location.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R11, S8-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R11, S8-R8).</t>
         </is>
       </c>
       <c r="H373" s="2" t="inlineStr">
@@ -19579,7 +19583,7 @@
 2. The summary strip and each tab's Totals row recompute immediately from the still-visible jobs after every advisor, customer, or asset change — on screen, with no page reload.
 3. When the combination leaves no visible jobs, every tab shows the no-data message "Empty bays, endless possibilities. Get Going!" and no Totals row.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R12, S7-N1, S5-R11, S6-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R12, S7-N1, S5-R11, S6-R6).</t>
         </is>
       </c>
       <c r="H374" s="2" t="inlineStr">
@@ -19641,7 +19645,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
       <c r="H375" s="2" t="inlineStr">
@@ -19692,7 +19696,7 @@
 2. Toggling a column off hides it from the table; toggling it on shows it again.
 3. The Total column is always shown and cannot be turned off — it is not offered in the control at all.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S8-R1, S8-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R1, S8-R2).</t>
         </is>
       </c>
       <c r="H376" s="2" t="inlineStr">
@@ -19743,7 +19747,7 @@
 2. Total is always the last column.
 3. The column selection applies to every tab at once — all four tabs show the same set of columns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S8-R5, S8-R6, S4-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R5, S8-R6, S4-R1).</t>
         </is>
       </c>
       <c r="H377" s="2" t="inlineStr">
@@ -19794,7 +19798,7 @@
           <t>1. On return and after a reload, the report restores the saved date range, advisor selection, customer selection, asset selection, location selection, column selection, and active tab.
 2. In a different browser the report shows the defaults instead — the settings are saved per browser, not on the user's account.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S8-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R7).</t>
         </is>
       </c>
       <c r="H378" s="2" t="inlineStr">
@@ -19843,7 +19847,7 @@
           <t>1. The report loads normally — the invalid saved value falls back to that setting's default rather than breaking the view.
 2. All other saved settings are still restored.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S8-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R8).</t>
         </is>
       </c>
       <c r="H379" s="2" t="inlineStr">
@@ -19893,7 +19897,7 @@
           <t>1. The menu holds the download options "Download (PDF)" and "Download (CSV)".
 2. Each option downloads a file of the current tab in the chosen format.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R1).</t>
         </is>
       </c>
       <c r="H380" s="2" t="inlineStr">
@@ -19948,7 +19952,7 @@
 4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
 5. Note for the tester: the file carries the location column only when you have switched Location ON in the column-selection control - it does not appear just because you have more than one location selected. In the file it is headed "Branch", not "Location", and the asset column is headed "Unit". Both of those names are correct.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R2, S9-R3, S9-R4, S9-R10a, S7-R13, S9-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R2, S9-R3, S9-R4, S9-R10a, S7-R13, S9-E1).</t>
         </is>
       </c>
       <c r="H381" s="2" t="inlineStr">
@@ -20001,7 +20005,7 @@
 2. In the CSV, a money value containing a comma (a thousands separator) is enclosed in double-quotes per standard CSV rules.
 3. A value without a comma is written unquoted.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R5, S9-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R5, S9-R6).</t>
         </is>
       </c>
       <c r="H382" s="2" t="inlineStr">
@@ -20050,7 +20054,7 @@
           <t>1. In the PDF, Inv. Hrs keeps the green (positive) / red (negative) coloring.
 2. In the CSV, the Inv. Hrs column is monochrome — plain signed numbers with no color or markup.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R7).</t>
         </is>
       </c>
       <c r="H383" s="2" t="inlineStr">
@@ -20100,7 +20104,7 @@
           <t>1. In the download, Days Open is the whole number of days as of the moment the file is generated.
 2. Because the screen computes Days Open live while the file freezes it at generation time, the file can legitimately show a day count one higher than the screen it was generated from — that difference is EXPECTED, not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R8).</t>
         </is>
       </c>
       <c r="H384" s="2" t="inlineStr">
@@ -20150,7 +20154,7 @@
 2. The CSV is named "wip-2-report.csv".
 3. These exact names (including the "-2-") are the specified current behavior.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R9).</t>
         </is>
       </c>
       <c r="H385" s="2" t="inlineStr">
@@ -20204,7 +20208,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H386" s="2" t="inlineStr">
@@ -20253,7 +20257,7 @@
           <t>1. The PDF shows the shop logo at the top.
 2. The CSV never includes a logo (plain data only).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R10).</t>
         </is>
       </c>
       <c r="H387" s="2" t="inlineStr">
@@ -20305,7 +20309,7 @@
 2. When a download yields no rows, a warning notification shows titled "Empty export" with the caption "Export didn't yield any results".
 3. When a download fails, an error notification shows: "An error occurred while exporting the report. Please try again."
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S9-R11, S9-R12, S9-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R11, S9-R12, S9-R13).</t>
         </is>
       </c>
       <c r="H388" s="2" t="inlineStr">
@@ -20356,7 +20360,7 @@
 3. Below the cap the download works normally.
 4. Note for the tester: on this environment the biggest single tab holds about 114 work orders, so you cannot make this message appear here. Record that and move on.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (Story 9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (Story 9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H389" s="2" t="inlineStr">
@@ -20405,7 +20409,7 @@
           <t>1. Each tab uses an all-white table: white column headers and white data cells.
 2. There is no alternating row shading (no zebra striping).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R1).</t>
         </is>
       </c>
       <c r="H390" s="2" t="inlineStr">
@@ -20454,7 +20458,7 @@
           <t>1. The summary strip appears above the tabs.
 2. It is shown as a bold band delineated by a top and bottom rule — not as a row of separate cards.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R2).</t>
         </is>
       </c>
       <c r="H391" s="2" t="inlineStr">
@@ -20503,7 +20507,7 @@
           <t>1. The Total column header is bold and pinned to the far right, matching its cells.
 2. The Total column (header and cells, shown in bold) stays fixed to the right edge while the rest of the columns scroll underneath.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S4-R22, S10-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R22, S10-R3).</t>
         </is>
       </c>
       <c r="H392" s="2" t="inlineStr">
@@ -20552,7 +20556,7 @@
           <t>1. The Totals row stays visible at the bottom while the rows scroll.
 2. The report fills the available height and only the active tab's table body scrolls — the page itself does not add a second scrollbar.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R4, S10-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R4, S10-R5).</t>
         </is>
       </c>
       <c r="H393" s="2" t="inlineStr">
@@ -20603,7 +20607,7 @@
 2. A visible focus indicator shows when it is focused.
 3. Activating it opens the work order (in the same browser tab).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R6).</t>
         </is>
       </c>
       <c r="H394" s="2" t="inlineStr">
@@ -20654,7 +20658,7 @@
 2. Its explanation is revealed on focus, not by hover alone.
 3. The explanation text is exposed to assistive technology.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R7, S5-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R7, S5-R12).</t>
         </is>
       </c>
       <c r="H395" s="2" t="inlineStr">
@@ -20704,7 +20708,7 @@
           <t>1. The report supports dark mode.
 2. The table, the summary strip, the WO # link, the Inv. Hrs green/red coloring, and the two-line asset cell all use dark-mode-legible colors meeting contrast.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S10-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R9).</t>
         </is>
       </c>
       <c r="H396" s="2" t="inlineStr">
@@ -20755,7 +20759,7 @@
 2. The download works with the same permission — for now the one ordinary reports access covers the report and its downloads and no new permission is added for it.
 3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (Story 1 Prerequisites); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (Story 1 Prerequisites); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H397" s="2" t="inlineStr">
@@ -20803,7 +20807,7 @@
         <is>
           <t>1. The report does not appear in the navigation for this user.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S1-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S1-N1).</t>
         </is>
       </c>
       <c r="H398" s="2" t="inlineStr">
@@ -20858,7 +20862,7 @@
 4. Each snapshot row captures, at minimum: the work order, its status, its Earned value, its Remaining value, the location and organization (copied from the work order), and the snapshot's calendar date.
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R1, S11-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R1, S11-R2).</t>
         </is>
       </c>
       <c r="H399" s="2" t="inlineStr">
@@ -20911,7 +20915,7 @@
 2. The captured dollar values are stored to the cent — no rounding to whole dollars and no lost cents.
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R3, S11-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R3, S11-R5).</t>
         </is>
       </c>
       <c r="H400" s="2" t="inlineStr">
@@ -20965,7 +20969,7 @@
 3. Invoiced, Paid, and Declined work orders and part-sale work orders are not captured.
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R4, S2-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R4, S2-R1).</t>
         </is>
       </c>
       <c r="H401" s="2" t="inlineStr">
@@ -21016,7 +21020,7 @@
 2. Its Earned is $0.00 and its Remaining is $0.00, matching what the report shows on screen for a job with nothing approved.
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Work In Progress report specification version 6 (S11-R6, S4-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R6, S4-E1).</t>
         </is>
       </c>
       <c r="H402" s="2" t="inlineStr">
@@ -21066,7 +21070,7 @@
           <t>1. The reports navigation lists a report labeled "Inventory Value" under the Parts group.
 2. Clicking it opens the Inventory Value report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S1-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S1-R1).</t>
         </is>
       </c>
       <c r="H403" s="2" t="inlineStr">
@@ -21116,7 +21120,7 @@
           <t>1. The report shows one row for each in-stock part at the selected location(s).
 2. The values are valued as of the resolved date (the current stock for a range reaching today, or the closest recorded nightly snapshot for an earlier date — see the IV — As-of Date &amp; Snapshots cases).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S1-R2, S1-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S1-R2, S1-R6).</t>
         </is>
       </c>
       <c r="H404" s="2" t="inlineStr">
@@ -21165,7 +21169,7 @@
           <t>1. The date range defaults to the current calendar month.
 2. The location defaults to the user's currently active location.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S1-R3, S7-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S1-R3, S7-R2).</t>
         </is>
       </c>
       <c r="H405" s="2" t="inlineStr">
@@ -21217,7 +21221,7 @@
 2. Changing any server-side filter (Date, Location, Category, Vendor), the part search, or the sort returns the FIRST page of the new result set - the list jumps back to the top.
 3. Note for the tester: on this build there are no numbered page controls on the screen - the rows load as you scroll. That is what you should see; record it and carry on with the checks above.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S1-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S1-R8).</t>
         </is>
       </c>
       <c r="H406" s="2" t="inlineStr">
@@ -21267,7 +21271,7 @@
           <t>1. In every case the report shows the standard reports no-data message "Empty bays, endless possibilities. Get Going!" instead of rows.
 2. No totals row is shown in any of the cases.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S1-N2, S4-N1, S5-N1, S7-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S1-N2, S4-N1, S5-N1, S7-N2).</t>
         </is>
       </c>
       <c r="H407" s="2" t="inlineStr">
@@ -21320,7 +21324,7 @@
 4. Only parts meeting BOTH conditions — not a core charge, and on-hand quantity greater than zero — are listed.
 5. A part that has sat without movement for a long time still appears and is still counted — there is no dead-stock exclusion; how long stock has sat makes no difference.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S2-R1, S2-R2, S2-N1, S2-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S2-R1, S2-R2, S2-N1, S2-N2).</t>
         </is>
       </c>
       <c r="H408" s="2" t="inlineStr">
@@ -21369,7 +21373,7 @@
           <t>1. The part appears twice — one row per location, each with that location's own quantity and values.
 2. The rows are NOT merged into one combined row; this is the documented v1 behavior.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S2-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S2-R3).</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
@@ -21419,7 +21423,7 @@
           <t>1. Unit Sell equals the part's fixed sell price.
 2. The pricing-matrix markup is NOT applied when a fixed sell price is set — the fixed price wins.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R5).</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
@@ -21468,7 +21472,7 @@
         <is>
           <t>1. Unit Sell equals the shop's pricing-matrix markup on cost for that part's category (the same way the parts list resolves it).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R5).</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -21521,7 +21525,7 @@
 2. Such a part shows a Margin of $0.00 and a Margin % of 0.0% — the stock is valued at cost.
 3. Note for the tester: if no part without a category can be created or found, mark this test Blocked rather than Passed or Failed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R5).</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -21572,7 +21576,7 @@
           <t>1. Total Sell equals the part's on-hand quantity × Unit Sell, shown as US-dollar currency.
 2. Total Cost equals the part's on-hand quantity × Unit Cost, shown as US-dollar currency.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R6, S3-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R6, S3-R7).</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -21623,7 +21627,7 @@
           <t>1. Margin equals Total Sell − Total Cost for the part's whole on-hand quantity, shown as US-dollar currency.
 2. Margin is the extended (total) margin, not the per-unit difference.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R8).</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -21674,7 +21678,7 @@
 2. A Margin % that computes to a real number, including a negative one, shows its signed value.
 3. Margin % shows "—" when Total Sell is zero or negative (the percentage is undefined).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R9, S3-E3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R9, S3-E3).</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -21728,7 +21732,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R1, S3-R2, S7-R6); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R1, S3-R2, S7-R6); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -21779,7 +21783,7 @@
 2. Unit Cost and Unit Sell show per-unit prices as US-dollar currency.
 3. Money values show a leading "$", two decimal places, and thousands separators (for example "$1,234.56"); a negative value shows a leading minus before the "$" ("-$1,234.56"); a genuine zero shows "$0.00".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R3, S3-R4, S3-R5, S3-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R3, S3-R4, S3-R5, S3-R10).</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -21829,7 +21833,7 @@
 2. The Total Cost column header is bold and pinned, matching its cells.
 3. It stays fixed to the right edge while the other columns scroll underneath.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R11, S12-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R11, S12-R4).</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -21882,7 +21886,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R12, S3-R13, S8-R3, S7-R6); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R12, S3-R13, S8-R3, S7-R6); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
@@ -21934,7 +21938,7 @@
 3. A part with no vendor shows an em dash ("—") in its Vendor cell.
 4. Note for the tester: on this build a part cannot be saved without a category, so you will not find a part whose Category cell shows "—". Check the Vendor half only.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S3-R14, S3-E1, S3-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R14, S3-E1, S3-E2).</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -21990,7 +21994,7 @@
 5. Note for the tester: if the label on screen reads "Totals" instead of "Total", mark this test Failed and report it — do not change the test.
 6. Sorting by any column reorders the data rows only — the totals row stays at the bottom.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S4-R1, S4-R4, S4-R5, S4-R6, S4-R7, S12-R5, S9-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S4-R1, S4-R4, S4-R5, S4-R6, S4-R7, S12-R5, S9-R4).</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
@@ -22045,7 +22049,7 @@
 3. The hand-summed subset matches the server-computed totals to the cent.
 4. After each filter change the totals row recomputes on the server over the full filtered set, independent of which page is shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S4-R2, S4-R8, S6-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S4-R2, S4-R8, S6-R6).</t>
         </is>
       </c>
       <c r="H422" s="2" t="inlineStr">
@@ -22097,7 +22101,7 @@
 2. It is NOT the average of the row percentages.
 3. It shows "—" when the total Total Sell is zero or negative.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S4-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S4-R3).</t>
         </is>
       </c>
       <c r="H423" s="2" t="inlineStr">
@@ -22148,7 +22152,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S5-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S5-R1).</t>
         </is>
       </c>
       <c r="H424" s="2" t="inlineStr">
@@ -22200,7 +22204,7 @@
 2. The date control is an "as of" anchor, not a created-date filter — narrowing it does not select "parts added in that range"; it shows the whole shelf as it stood on that date, so the part stocked before the range still appears.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8820
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S5-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S5-R2).</t>
         </is>
       </c>
       <c r="H425" s="2" t="inlineStr">
@@ -22250,7 +22254,7 @@
           <t>1. The report values the current live stock — the values represent today.
 2. The part's row reflects today's changed quantity (not yesterday's snapshot), proving the live fallback is in use.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S5-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S5-R3).</t>
         </is>
       </c>
       <c r="H426" s="2" t="inlineStr">
@@ -22303,7 +22307,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S5-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S5-R4).</t>
         </is>
       </c>
       <c r="H427" s="2" t="inlineStr">
@@ -22354,7 +22358,7 @@
 2. When the displayed day matches the date asked for (the common current-view case), the "As of" indicator is not shown — the date control already communicates the date.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8820
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S5-R5, S5-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S5-R5, S5-R6).</t>
         </is>
       </c>
       <c r="H428" s="2" t="inlineStr">
@@ -22407,7 +22411,7 @@
 3. Changing the date range reloads the report (the loading indicator shows and the rows re-fetch).
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8820
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S5-R7, S5-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S5-R7, S5-R8).</t>
         </is>
       </c>
       <c r="H429" s="2" t="inlineStr">
@@ -22456,7 +22460,7 @@
           <t>1. The report shows the empty state — there is no way to reconstruct inventory value for a date before recording began, because there is no historical backfill.
 2. This forward-capture-only behavior is the documented v1 boundary, not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S5-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S5-E1).</t>
         </is>
       </c>
       <c r="H430" s="2" t="inlineStr">
@@ -22508,7 +22512,7 @@
 2. The rename/delete causes no blank Category/Vendor cells and no dropped rows on the recorded day.
 3. The live view (window reaching today) shows the NEW name for the renamed category.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S11-R2, S5-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S11-R2, S5-R4).</t>
         </is>
       </c>
       <c r="H431" s="2" t="inlineStr">
@@ -22559,7 +22563,7 @@
 2. Selecting one or more categories reloads the report to show only parts in the selected categories.
 3. Selecting one or more vendors reloads the report to show only parts supplied by the selected vendors.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S6-R1, S6-R2, S6-R3, S6-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S6-R1, S6-R2, S6-R3, S6-R4).</t>
         </is>
       </c>
       <c r="H432" s="2" t="inlineStr">
@@ -22611,7 +22615,7 @@
 2. The filtering covers the ENTIRE data set — matching parts that were further down the list appear — not just a narrowing of the rows currently on screen.
 3. Every change — date range, location, Category, Vendor, part search, sort — reloads the rows from the server; while loading the standard reports loading indicator shows, and existing rows are replaced only when the new data returns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S6-R5, S1-R4, S1-R5, S1-R7, S1-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S6-R5, S1-R4, S1-R5, S1-R7, S1-R8).</t>
         </is>
       </c>
       <c r="H433" s="2" t="inlineStr">
@@ -22662,7 +22666,7 @@
 2. With no vendor selected, parts of all vendors are shown.
 3. With the part search empty, no search narrowing is applied.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S6-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S6-R7).</t>
         </is>
       </c>
       <c r="H434" s="2" t="inlineStr">
@@ -22715,7 +22719,7 @@
 3. Matching is case-insensitive.
 4. The search applies server-side (whole data set, first page returned); a no-match search shows the no-data message.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S6-R8, S6-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S6-R8, S6-R5).</t>
         </is>
       </c>
       <c r="H435" s="2" t="inlineStr">
@@ -22765,7 +22769,7 @@
           <t>1. A part must satisfy EVERY active filter and the search to appear — the Date range, Location, Category, Vendor, and part search combine with AND.
 2. The totals row matches the combined filtered set after each step.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S6-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S6-R9).</t>
         </is>
       </c>
       <c r="H436" s="2" t="inlineStr">
@@ -22817,7 +22821,7 @@
 2. On a first visit it defaults to the user's currently active location.
 3. With "All locations" active you can tell which location each row's stock belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S7-R1, S7-R2, S12-R3); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S7-R1, S7-R2, S12-R3); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H437" s="2" t="inlineStr">
@@ -22868,7 +22872,7 @@
 2. With both locations selected, parts from both appear (one row per part per location) and the totals cover both.
 3. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S7-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S7-R3).</t>
         </is>
       </c>
       <c r="H438" s="2" t="inlineStr">
@@ -22917,7 +22921,7 @@
           <t>1. Only the locations the user has access to are offered — a location the user cannot access is never included in the scope.
 2. If the requested location set resolves to none the user can access, the report falls back to the user's currently active location.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S7-R4, S7-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S7-R4, S7-R5).</t>
         </is>
       </c>
       <c r="H439" s="2" t="inlineStr">
@@ -22968,7 +22972,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S7-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S7-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H440" s="2" t="inlineStr">
@@ -23030,7 +23034,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S7-R6, S7-R7, S3-R1, S12-R10, S10-R15); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S7-R6, S7-R7, S3-R1, S12-R10, S10-R15); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
       <c r="H441" s="2" t="inlineStr">
@@ -23081,7 +23085,7 @@
 2. Toggling a column off hides it from the table; toggling it on shows it again.
 3. The Total Cost column is always shown and cannot be turned off.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S8-R1, S8-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S8-R1, S8-R2).</t>
         </is>
       </c>
       <c r="H442" s="2" t="inlineStr">
@@ -23132,7 +23136,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S8-R4, S3-R1, S7-R6); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S8-R4, S3-R1, S7-R6); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
         </is>
       </c>
       <c r="H443" s="2" t="inlineStr">
@@ -23183,7 +23187,7 @@
           <t>1. On return and after a reload, the report restores the saved date range, category selection, vendor selection, part search text, location selection, column selection, and sort.
 2. In a different browser the report shows the defaults instead — persistence is per browser, not tied to the user's account.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S8-R5, S9-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S8-R5, S9-R5).</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
@@ -23232,7 +23236,7 @@
           <t>1. The report loads normally — the saved category or vendor that is no longer present in the data is dropped from the selection instead of breaking the view (the defensive-restore rule applied to the path these steps drive).
 2. All other saved settings are still restored.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S8-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S8-R6).</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -23281,7 +23285,7 @@
           <t>1. The rows are sorted by Total Cost, highest first (descending).
 2. The order holds across pages (page 2 continues below page 1's lowest value) — the server applies the default order over the full set.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S9-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S9-R1).</t>
         </is>
       </c>
       <c r="H446" s="2" t="inlineStr">
@@ -23333,7 +23337,7 @@
 2. Each header click re-fetches the data from the server ordered by the chosen column and direction, returning the FIRST page of the re-sorted result set.
 3. Only one column sorts at a time.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S9-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S9-R2).</t>
         </is>
       </c>
       <c r="H447" s="2" t="inlineStr">
@@ -23383,7 +23387,7 @@
           <t>1. Money and numeric columns sort by their underlying value (so $1,100.00 is treated as more than $900.00, not compared as text).
 2. Text columns (Part #, Description, Category, Vendor) sort as text, case-insensitively ("apple" and "Apple" sort together).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S9-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S9-R3).</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
@@ -23433,7 +23437,7 @@
           <t>1. The menu holds an option labeled "Download (PDF)" and an option labeled "Download (CSV)".
 2. Each option downloads a file of the current view in the chosen format.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S10-R1, S10-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S10-R1, S10-R2).</t>
         </is>
       </c>
       <c r="H449" s="2" t="inlineStr">
@@ -23487,11 +23491,12 @@
 3. Both downloads include a totals row labeled "Totals" matching the on-screen totals (the full-filtered-set totals).
 4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
 5. Note for the tester: the files carry the Location column when Location is turned ON in the column-selection control (it sits between Vendor and Qty). It does not appear just because you have more than one location selected.
----
-Note for the tester: on this build the spreadsheet file ignores the columns you picked and puts them in a different order from the screen, so point 1 above will not match. That difference is already written up and a decision on it is pending - record what you see and carry on; you do not need to raise it again.
+On this build the spreadsheet file ignores the columns you picked and puts them in a different order from the screen, so point 1 above will not match - record what you see and carry on.
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8823
+---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S10-R3, S10-R4, S10-R5, S10-R6, S10-R15); on this point that specification currently states otherwise and a product decision is still awaited, so treat the behaviour described above as what the build does today.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S10-R3, S10-R4, S10-R5, S10-R6, S10-R15).</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -23540,10 +23545,10 @@
           <t>1. Money uses two decimals and Margin % one decimal in both files; an undefined Margin % shows "—".
 2. In the CSV, money values are written as plain numbers with two decimals and NO thousands separators (so they parse cleanly in a spreadsheet).
 3. The PDF uses the same on-screen currency formatting with the "$" and thousands separators.
----
 On this build the money in the spreadsheet file comes out as "$11,176.88" - with a dollar sign and a comma - instead of the plain number described in point 2 above.
-Known and accepted: the product behaves this way on purpose for now. Do not raise this as a new problem.
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S10-R7).</t>
+Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8823
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S10-R7).</t>
         </is>
       </c>
       <c r="H451" s="2" t="inlineStr">
@@ -23599,7 +23604,7 @@
 ---
 DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
 The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S10-R8, S10-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S10-R8, S10-R9).</t>
         </is>
       </c>
       <c r="H452" s="2" t="inlineStr">
@@ -23648,7 +23653,7 @@
           <t>1. The PDF is named "inventory-value-report.pdf".
 2. The CSV is named "inventory-value-report.csv".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S10-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S10-R10).</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
@@ -23699,7 +23704,7 @@
 2. Parts from the later pages are present.
 3. The export is generated server-side against the current filters, part search, and sort — it is not built from the rows currently in the browser.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S10-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S10-R11).</t>
         </is>
       </c>
       <c r="H454" s="2" t="inlineStr">
@@ -23752,7 +23757,7 @@
 4. Note for the tester: on this environment the biggest view you can build is about 9,275 rows, which is under the cap, so you cannot make this message appear here. If the PDF fails with a plain error instead, that is the separate timeout problem - see the Inventory Value export-notification case.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S10-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S10-R12).</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
@@ -23806,7 +23811,7 @@
 4. Note for the tester: on this build a PDF download of a large view fails with a plain error - "An error occurred. We're sorry for this inconvenience, please try again a bit later later." - after roughly half a minute. It is a timeout, not the too-large-to-export message. Narrow the view with the part search or a single location and the PDF works. The CSV of the same view always works and is quick. Record the failure; it is a known problem, not a mistake you made.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S10-R13, S10-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S10-R13, S10-R14).</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -23862,7 +23867,7 @@
 6. Note for the tester: the polite refusal message in item 2 is the correct behaviour. The plain error in item 5 is the problem being tracked. Tell the two apart by the wording.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S10-R11, S10-R12, S10-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S10-R11, S10-R12, S10-R14).</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -23912,7 +23917,7 @@
           <t>1. The table has white column headers and white data cells, with no alternating row shading.
 2. The table sits on the standard soft blue-grey report backdrop.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S12-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S12-R1).</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -23961,7 +23966,7 @@
           <t>1. In the toolbar, the three-dot download menu sits leftmost in the action cluster, followed by the Column Selection control.
 2. The toolbar filters run, left to right: the date-range control, the part search, the Category filter, the Vendor filter, and the Location filter (rightmost).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S12-R2, S12-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S12-R2, S12-R3).</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -24012,7 +24017,7 @@
 2. The full value is available on hover.
 3. The Part # is never truncated.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S12-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S12-R6).</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -24063,7 +24068,7 @@
 2. In dark mode you can read the toolbar text and the cell text at a glance, and the "—" glyph in an empty Category or Vendor cell is clearly visible against the dark cell behind it — it does not disappear into the background.
 3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether everything is easy to read in dark mode, and only report it if something is hard to see. (The exact colour values behind this are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S12-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S12-R7).</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -24115,7 +24120,7 @@
 2. Each sortable column header exposes its sort state to assistive technology (for example, ascending/descending/none).
 3. The exposed state updates when the direction toggles.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S12-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S12-R8).</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -24164,7 +24169,7 @@
         <is>
           <t>1. Each icon-only control carries an accessible name exposed to assistive technology (it is not announced as an unnamed button).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S12-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S12-R9).</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
@@ -24215,7 +24220,7 @@
 2. No additional report-specific permission is required — for now the one ordinary reports access covers all six of the new reports.
 3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (Story 1 Prerequisites); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (Story 1 Prerequisites); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -24263,7 +24268,7 @@
         <is>
           <t>1. The report does not appear in the navigation for this user.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S1-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S1-N1).</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -24316,7 +24321,7 @@
 2. Each row captures the part's identity (part, category, vendor), on-hand quantity, unit cost, unit sell, total cost, and total sell, stored to the cent.
 3. A location with no in-stock parts on the date simply has no rows for that date — this is valid, not an error.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S11-R1, S11-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S11-R1, S11-R4).</t>
         </is>
       </c>
       <c r="H466" s="2" t="inlineStr">
@@ -24370,7 +24375,7 @@
 2. The captured values use the same valuation as the live report (Story 3), including the sell-price fallback chain.
 3. A recorded day equals what the live report would have shown that day — the as-of view of the captured date matches the noted live values.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S11-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S11-R2).</t>
         </is>
       </c>
       <c r="H467" s="2" t="inlineStr">
@@ -24425,7 +24430,7 @@
 5. A re-run always records current truth under the CURRENT date; it cannot reconstruct a past date.
 6. A past date's stored rows are unchanged by a current re-run.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S11-R3, S11-R5, S5-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S11-R3, S11-R5, S5-E1).</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
@@ -24478,7 +24483,7 @@
 3. Pruning runs as part of, or alongside, the nightly capture.
 ---
 Note for the tester: this one needs records going back more than a year, and this test system only holds a few days of records so far. If there is nothing old enough to look at, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S11-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S11-R6).</t>
         </is>
       </c>
       <c r="H469" s="2" t="inlineStr">
@@ -24531,7 +24536,7 @@
 3. A requested date whose covering captures have all been pruned resolves to the nearest earlier retained capture, or shows the empty state if none remains.
 ---
 Note for the tester: this one needs records going back more than a year, and this test system only holds a few days of records so far. If there is nothing old enough to look at, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
-This is the expected behaviour as per the build tested on 8/4/2026, and as per the Inventory Value report specification version 3 (S11-E1, S11-R6, S5-R4, S5-R5, S5-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S11-E1, S11-R6, S5-R4, S5-R5, S5-N1).</t>
         </is>
       </c>
       <c r="H470" s="2" t="inlineStr">

--- a/testrail-import/report-suite-v1-testrail-import.xlsx
+++ b/testrail-import/report-suite-v1-testrail-import.xlsx
@@ -524,15 +524,15 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1. "Sales By Customer" is listed in the Performance group of the Reports left-side navigation, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency) — the new reports are added below those items without moving them.
+          <t xml:space="preserve">1. "Sales By Customer" is listed in the Performance group of the Reports left-side navigation, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency) — the new reports are added below those items without moving them.
 2. Clicking it opens the Sales By Customer report in the main content area.
 3. The page title reads "Sales By Customer."
 4. The browser tab title reads "Sales By Customer - Report | ShopView".
-5. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
----
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S1-R1, S1-R3, S1-R4).</t>
+5. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S1-R1, S1-R3, S1-R4).
+AUTOMATION: HOLD - waiting on an answer from the product owner
+</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -578,12 +578,14 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1. The "Sales By Customer" entry is visible in the Reports navigation.
+          <t xml:space="preserve">1. The "Sales By Customer" entry is visible in the Reports navigation.
 2. The report opens and shows its data.
 3. Ordinary reports access alone is enough — this report does NOT need a permission of its own.
-4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S1-R2).</t>
+4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S1-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -630,12 +632,14 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1. "Sales By Customer" does not appear in the Reports navigation.
+          <t xml:space="preserve">1. "Sales By Customer" does not appear in the Reports navigation.
 2. Opening the report by direct link does not show the report (the application blocks it with its standard access-denied handling).
 3. The gate is the ordinary reports access — there is no separate Sales By Customer permission to remove.
-4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S1-N1).</t>
+4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S1-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -682,10 +686,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1. The destination page shows the application's standard access-denied state.
+          <t xml:space="preserve">1. The destination page shows the application's standard access-denied state.
 2. Pressing back returns you to the Sales By Customer report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S9-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S9-N2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -734,12 +740,14 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1. The administrator's filter lists every location in the organization.
+          <t xml:space="preserve">1. The administrator's filter lists every location in the organization.
 2. The non-administrator's filter lists only the locations assigned to them.
 3. A requested location the user does not have access to is ignored — the report does NOT widen to the whole organization.
 4. The report data never includes invoices from a location the user does not have access to.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S4-R7, S4-R8, S4-R9, S4-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S4-R7, S4-R8, S4-R9, S4-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -786,11 +794,13 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1. There is NO "Sales By Customer" permission anywhere in the list for an administrator to switch on or off.
+          <t xml:space="preserve">1. There is NO "Sales By Customer" permission anywhere in the list for an administrator to switch on or off.
 2. The only reports permission offered is the ordinary reports access, and that one covers all six of the new reports.
-3. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed but switching it on or off changes nothing at all, that part is expected for now — just report that it is still visible.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S1-R2).</t>
+3. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S1-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -835,11 +845,13 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1. A date range picker is visible in the report toolbar.
+          <t xml:space="preserve">1. A date range picker is visible in the report toolbar.
 3. The named periods use the application's standard shared calendar boundaries - this is one shared chooser used by all six reports.
 3. There is no "All Time" option.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Customer report specification version 13 (S2-R1, S2-R2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Customer report specification version 14 (S2-R1, S2-R2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -885,11 +897,13 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1. The date range picker shows a month calendar inside it — that is how a custom start and end date are chosen on this build. There is no separate "Custom" item to choose.
+          <t xml:space="preserve">1. The date range picker shows a month calendar inside it — that is how a custom start and end date are chosen. There is no separate "Custom" item to choose.
 2. A range of 366 days or fewer applies normally.
 3. A range wider than 366 days cannot be applied — the report prevents the selection rather than loading the wider range.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Customer report specification version 13 (S2-R3, S2-R4, S2-N2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Customer report specification version 14 (S2-R3, S2-R4, S2-N2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -935,10 +949,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1. The chosen date range value is written into the page link.
+          <t xml:space="preserve">1. The chosen date range value is written into the page link.
 2. Opening that link in a browser with no saved view for this report restores the sender's date range.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S2-R6, S2-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S2-R6, S2-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -986,13 +1002,15 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1. The dropdown offers exactly three options, in this order: "Parts &amp; Service," "Parts only," "Service only" — with "Parts &amp; Service" selected by default on first load.
+          <t xml:space="preserve">1. The dropdown offers exactly three options, in this order: "Parts &amp; Service," "Parts only," "Service only" — with "Parts &amp; Service" selected by default on first load.
 2. Under "Service only," every invoice shown has a number starting with S; parts invoices are gone and all counts/totals reflect only S invoices.
 3. Under "Parts only," every invoice shown has a number starting with P; service invoices are gone and all counts/totals reflect only P invoices.
 4. With "Parts &amp; Service" selected, no product-type filter is applied — both S and P invoices are included and counts/totals cover both.
 5. The whole invoice is classified by its number prefix — there is no per-line-item split.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1039,13 +1057,15 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1. The location filter is the rightmost filter in the toolbar.
+          <t xml:space="preserve">1. The location filter is the rightmost filter in the toolbar.
 2. It lists the locations the signed-in user has access to.
 3. An "All locations" option is pinned to the top.
 4. Activating "All locations" selects every listed location at once; activating it again clears them all at once.
 5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's data.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S4-R1, S4-R2, S4-R3). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S4-R1, S4-R2, S4-R3). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1093,13 +1113,14 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1. With one or more locations selected, the report includes only data from those locations.
+          <t xml:space="preserve">1. With one or more locations selected, the report includes only data from those locations.
 2. Adding a second location adds that location's invoices to the rows and totals.
 3. With "All locations," the report includes data from every location the user has access to.
-4. With "All locations" active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
-5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S4-R5, S4-R6); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+4. With "All locations" active you can tell which location each row's data belongs to — a location label or marking is shown.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S4-R5, S4-R6); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1150,18 +1171,19 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1. With more than one location in scope a Location column is shown, positioned immediately after the Date column.
+          <t xml:space="preserve">1. With more than one location in scope a Location column is shown, positioned immediately after the Date column.
 2. A customer or asset row whose invoices are all at one location shows that location's name.
 3. A customer or asset row whose invoices come from more than one location shows "Multiple".
 4. An invoice row always shows its own exact location — never "Multiple".
 5. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all.
 6. With a single location in scope the Location column is hidden and the surrounding columns close up with no gap.
-7. Every one of the four downloads also contains the Location column, in the same position it holds on screen, showing the same values you just read: a location name on a row whose invoices are all at one location, "Multiple" on a row that aggregates more than one, and the invoice's own location on an invoice row. (Exactly where the column sits inside each file is confirmed in the build.)
+7. Every one of the four downloads also contains the Location column, in the same position it holds on screen, showing the same values you just read: a location name on a row whose invoices are all at one location, "Multiple" on a row that aggregates more than one, and the invoice's own location on an invoice row.
 Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
 ---
-DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Customer report specification version 13 (S4-R12, S4-R12a, S4-R13, S20-R19) differs, his decision is the authority.</t>
+---
+This is the expected behaviour as per the Sales By Customer report specification version 14 (S4-R12, S4-R12a, S4-R13, S20-R19), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1207,12 +1229,14 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1. A Customer filter labeled "Customer" sits between the Product Type filter and the Location filter.
+          <t xml:space="preserve">1. A Customer filter labeled "Customer" sits between the Product Type filter and the Location filter.
 2. The control carries a search (magnifier) icon marking it as searchable.
 3. Before typing, the dropdown shows the pinned all/clear control at the top and a "Search customers…" hint; individual customers are revealed by typing.
 4. The hint yields to the typed query while you are searching.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R1, S18-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R1, S18-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1259,11 +1283,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1. As you type, customers whose names contain the typed text appear in the list — matching is case-insensitive and matches anywhere in the name (a "contains" match, not starts-with).
+          <t xml:space="preserve">1. As you type, customers whose names contain the typed text appear in the list — matching is case-insensitive and matches anywhere in the name (a "contains" match, not starts-with).
 2. The list is scoped to the active date range, Product Type, and location.
 3. A selected customer is shown with a checkmark.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1309,12 +1335,14 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1. In the all-customers state the pinned control reads "Clear all"; activating it clears the selection to an empty set.
+          <t xml:space="preserve">1. In the all-customers state the pinned control reads "Clear all"; activating it clears the selection to an empty set.
 2. When the filter is NOT in the all-customers state the pinned control reads "All customers"; activating it puts the filter back in the all-customers state.
 3. The control is pinned to the top of the dropdown in both states.
 4. After "Clear all": the report shows the empty-state message "No sales data found for the selected filters.", the totals row shows zeros, and the collapsed label reads "None."
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R3, S18-N1, S17-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R3, S18-N1, S17-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1363,12 +1391,14 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1. The Customer filter's collapsed label reads "All customers."
+          <t xml:space="preserve">1. The Customer filter's collapsed label reads "All customers."
 2. The report shows every customer matching the other active filters.
 3. The all-customers state is an explicit state — while it is active, any customer that appears later (new data) is included automatically.
 4. After the filter change the filter stays in the all-customers state (label still "All customers") and every customer matching the new filters is included — including the newly-appearing one, with no manual re-selection.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R4, S18-R5, S18-R9, S18-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R4, S18-R5, S18-R9, S18-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1415,12 +1445,14 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1. With an empty selection the collapsed label reads "None."
+          <t xml:space="preserve">1. With an empty selection the collapsed label reads "None."
 2. With exactly one customer selected the label shows that customer's name.
 3. With more than one selected the label reads "N selected" where N is the number of selected customers (for example "3 selected").
 4. While typing, the field shows the query text instead of the summary label; the summary label returns when the query is cleared or the field loses focus.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1466,11 +1498,13 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1. The report shows only the two selected customers.
+          <t xml:space="preserve">1. The report shows only the two selected customers.
 2. The table refreshes as a fresh first page of results.
 3. The totals row updates to cover only the selected customers' matching invoices.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R5, S18-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R5, S18-R11).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1516,12 +1550,14 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1. Customer A (still present in the new results) stays selected and is shown.
+          <t xml:space="preserve">1. Customer A (still present in the new results) stays selected and is shown.
 2. Customer B (no longer present) is dropped from the selection and not shown; it must be re-selected to appear if it later returns.
 3. Customer C (newly present) is NOT auto-selected and is not shown.
 4. The Customer filter selection itself is not cleared by the date change.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R9, S18-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R9, S18-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1568,13 +1604,15 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1. The customer occupies exactly one summary row at the top level of the table.
+          <t xml:space="preserve">1. The customer occupies exactly one summary row at the top level of the table.
 2. The customer's name is shown at the start of the row, followed by the number of contributing invoices in parentheses — for example, Acme Corp (5).
 3. The count is the same size as the customer name next to it, in a slightly softer grey, and is easy to read.
 4. The count reflects the active date range, Product Type, and location — it drops when the range is narrowed; it is not a lifetime count.
 5. Note for the tester: you do not need to measure anything and you do not need any tool for item 3. Just say whether the count looks the right size and is easy to read, and only report it if it looks obviously wrong. (The exact colour and weight behind this are design-token values the design and engineering team check with their own tooling.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-R1, S7-R2, S7-R3, S7-R4, S7-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-R1, S7-R2, S7-R3, S7-R4, S7-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1620,9 +1658,11 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1. The customer is not shown — there are no zero-value placeholder rows.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-N1).</t>
+          <t xml:space="preserve">1. The customer is not shown — there are no zero-value placeholder rows.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1669,7 +1709,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1. The customer's asset rows appear beneath the summary row — one row per vehicle the customer's invoices were done on.
+          <t xml:space="preserve">1. The customer's asset rows appear beneath the summary row — one row per vehicle the customer's invoices were done on.
 2. Each asset row shows a vehicle icon, the asset label, and the asset's invoice count in parentheses.
 3. Each asset row shows the same financial columns as the customer row, rolled up for that asset.
 4. The Date cell is blank on asset rows.
@@ -1677,7 +1717,9 @@
 6. Each chevron toggles back to collapsed on a second activation.
 7. Collapsing customer A does not affect customer B's expansion; each asset's expansion state is likewise independent.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R1, S8-R2, S8-R5, S8-R5a, S8-R5b, S8-R5c, S8-R15).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R1, S8-R2, S8-R5, S8-R5a, S8-R5b, S8-R5c, S8-R15).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1722,11 +1764,13 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1. The invoice detail rows for that asset appear, indented one level deeper than the asset row.
+          <t xml:space="preserve">1. The invoice detail rows for that asset appear, indented one level deeper than the asset row.
 2. Each detail row shows the invoice number (as a link), the invoice date, and the per-invoice Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, and Subtotal.
 3. The invoice date shows in the format "Mon DD YYYY" — for example, May 14 2026.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R4, S8-R12, S8-R12a, S20-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R4, S8-R12, S8-R12a, S20-R14).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1772,10 +1816,12 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1. Invoices referencing the same vehicle record (same vehicle id) group into ONE asset row — no duplicate rows for the same vehicle.
+          <t xml:space="preserve">1. Invoices referencing the same vehicle record (same vehicle id) group into ONE asset row — no duplicate rows for the same vehicle.
 2. An older invoice with no vehicle id on file groups by the invoice's own stored vehicle snapshot instead.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1820,11 +1866,13 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1. The customer's real asset rows are ordered A→Z by their label, case-insensitive.
+          <t xml:space="preserve">1. The customer's real asset rows are ordered A→Z by their label, case-insensitive.
 2. The no-vehicle work collects under a single row labeled "Parts Sales," always sorted last among that customer's assets.
 3. Changing the column sort does not change the asset order — assets stay A→Z with "Parts Sales" last.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R6, S8-R6a, S10-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R6, S8-R6a, S10-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1870,11 +1918,13 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1. With at least one visible customer collapsed, the header chevron shows the "expand" icon and its tooltip reads "Expand all."
+          <t xml:space="preserve">1. With at least one visible customer collapsed, the header chevron shows the "expand" icon and its tooltip reads "Expand all."
 2. Clicking it expands every customer on the current page in one action — it acts on the currently visible customers only, not the whole result set.
 3. With all visible customers expanded, the icon switches to "collapse" and the tooltip reads "Collapse all"; clicking collapses them all.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R16, S8-R17, S8-R18, S8-R19).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R16, S8-R17, S8-R18, S8-R19).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1921,11 +1971,13 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1. Typing in the Customer filter's type-ahead only narrows the dropdown list — the expanded table rows stay expanded.
+          <t xml:space="preserve">1. Typing in the Customer filter's type-ahead only narrows the dropdown list — the expanded table rows stay expanded.
 2. A change that re-fetches customer rows (date range, Product Type, location, Customer selection, or sort) collapses all expanded rows.
 3. While the re-fetch is in flight the table shows the standard loading state; when it clears, the page shows the first page of the newly ordered set — the customers on the page can change.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R20, S8-R21, S10-R8a, S10-R8b, S10-R8c).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R20, S8-R21, S10-R8a, S10-R8b, S10-R8c).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1970,10 +2022,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1. The single-invoice asset expands and shows exactly one invoice detail row.
+          <t xml:space="preserve">1. The single-invoice asset expands and shows exactly one invoice detail row.
 2. Customer B shows a single "Parts Sales" row and no vehicle rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-E1, S8-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-E1, S8-E2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2018,9 +2072,11 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1. The no-vehicle S invoice appears under that customer's "Parts Sales" row — the bucket collects work by the ABSENCE of a vehicle, not by the invoice-number prefix.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-E3).</t>
+          <t xml:space="preserve">1. The no-vehicle S invoice appears under that customer's "Parts Sales" row — the bucket collects work by the ABSENCE of a vehicle, not by the invoice-number prefix.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-E3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2067,11 +2123,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1. The reversed/voided invoice never appears as an invoice row.
+          <t xml:space="preserve">1. The reversed/voided invoice never appears as an invoice row.
 2. It is excluded from the customer's "(N)" count and from every row total, regardless of the Product Type filter.
 3. The customer/asset totals drop by exactly that invoice's amounts.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-R7, S7-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-R7, S7-N2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2117,13 +2175,15 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1. Every row type — customer, asset, invoice, totals — renders the same columns in the same left-to-right order.
+          <t xml:space="preserve">1. Every row type — customer, asset, invoice, totals — renders the same columns in the same left-to-right order.
 2. A cell with no value for its row (for example the Date cell on a customer or asset row) is left blank and keeps its column position; no value moves into another column.
 3. The Date cell on the customer summary row is blank.
 4. A customer summary row reads as heavier than the invoice rows under it, and its Subtotal cell is the heaviest cell on that row.
 5. Note for the tester: you do not need to measure anything and you do not need any tool for item 4. Just say whether the summary row stands out from the invoice rows and whether its Subtotal looks the boldest, and only report it if it looks obviously wrong. (The exact weights behind this are design-token values the design and engineering team check with their own tooling.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-R8, S7-R9, S7-R10, S7-R15, S7-R16).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-R8, S7-R9, S7-R10, S7-R15, S7-R16).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2167,13 +2227,15 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1. Asset (a) is identified by its VIN.
+          <t xml:space="preserve">1. Asset (a) is identified by its VIN.
 2. Asset (b) (no VIN) is identified by its Unit # instead.
 3. Asset (c) (no VIN or Unit #) is identified by its plate instead.
-4. For asset (d) (no VIN, Unit #, or plate), note what the label shows - what stands in when all three are missing is confirmed in the build (the older rule showed "Unknown Asset").
+4. For asset (d) (no VIN, Unit #, or plate), the label reads "Unknown Asset" when all three are missing.
 5. Note whether the year/make/model text still appears anywhere in the row - the update says the VIN identifier REPLACES the year/make/model label; confirm the exact rendering in the build.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R7, S8-R8, S8-R9, S8-R10). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R7, S8-R8, S8-R9, S8-R10). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2219,10 +2281,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1. The duplicate labels are suffixed " (#1)" and " (#2)" (and so on for more duplicates).
+          <t xml:space="preserve">1. The duplicate labels are suffixed " (#1)" and " (#2)" (and so on for more duplicates).
 2. The numbering is fixed and repeatable — after a reload the same vehicle keeps the same number.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R11).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2267,11 +2331,13 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1. Each invoice number on a detail row is a clickable link that opens in the SAME browser tab (no new tab).
+          <t xml:space="preserve">1. Each invoice number on a detail row is a clickable link that opens in the SAME browser tab (no new tab).
 2. A service invoice opens the associated work order's Finance tab.
 3. A parts invoice opens the associated part sale's Part Requests tab.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S9-R1, S9-R2, S9-R2a, S9-R2b).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S9-R1, S9-R2, S9-R2a, S9-R2b).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2318,11 +2384,13 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1. Before navigating, the active date range and Product Type are written to the page link.
+          <t xml:space="preserve">1. Before navigating, the active date range and Product Type are written to the page link.
 2. Pressing back returns to the report with its filters, sort, and columns restored exactly as set.
 3. Expanded rows are shown collapsed again — expansion is not restored (this is the specified behavior, not a defect).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S9-R3, S9-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S9-R3, S9-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2367,12 +2435,14 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1. The customer name on the summary row is plain text, not a link.
+          <t xml:space="preserve">1. The customer name on the summary row is plain text, not a link.
 2. The invoice number link is shown in the application's primary color at rest, on hover, and after it has been clicked.
 3. The link has no underline at rest, on hover, or after it has been clicked.
 4. The link never recolors to the browser's visited-link (purple) color.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S9-R5, S9-R6, S9-R7, S9-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S9-R5, S9-R6, S9-R7, S9-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2418,10 +2488,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1. The destination page shows the application's standard "not found" state.
+          <t xml:space="preserve">1. The destination page shows the application's standard "not found" state.
 2. Pressing back returns you to the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S9-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S9-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -2469,11 +2541,13 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>1. Every column is sortable except the chevron column.
+          <t xml:space="preserve">1. Every column is sortable except the chevron column.
 2. Text columns sort alphabetically; numeric columns sort by value (not as text).
 3. Sorting reorders only the customer summary rows — asset rows keep their own order (A→Z with "Parts Sales" last) and invoice rows keep their order under their asset.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S10-R1, S10-R2, S10-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S10-R1, S10-R2, S10-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -2519,10 +2593,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1. On first load, rows are ordered by Customer name, ascending, case-insensitive (a lower-case "acme" sorts by letter, not after all capitals).
+          <t xml:space="preserve">1. On first load, rows are ordered by Customer name, ascending, case-insensitive (a lower-case "acme" sorts by letter, not after all capitals).
 2. Clicking a column header replaces the default with that column's sort.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S10-R4, S10-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S10-R4, S10-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -2567,10 +2643,12 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1. Ascending: the em-dash (missing) row sorts to the bottom.
+          <t xml:space="preserve">1. Ascending: the em-dash (missing) row sorts to the bottom.
 2. Descending: the em-dash row sorts to the top.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S10-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S10-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2615,10 +2693,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1. Customer rows order by each customer's most recent invoice date in the current view.
+          <t xml:space="preserve">1. Customer rows order by each customer's most recent invoice date in the current view.
 2. The Date cells on customer rows stay blank — the sort still works.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S10-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S10-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -2664,12 +2744,14 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1. The financial columns appear in this order: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin % — with Subtotal as the rightmost column.
+          <t xml:space="preserve">1. The financial columns appear in this order: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin % — with Subtotal as the rightmost column.
 2. Subtotal = Labor Invoiced + Parts Invoiced + Shop Supplies, before tax.
 3. Labor Margin = Labor Invoiced minus labor cost; Parts Margin = Parts Invoiced minus parts cost.
 4. Margin = Labor Margin + Parts Margin — it does NOT include any Shop Supplies amount (shop supplies add to Subtotal but add no profit to Margin).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-R6, S11-R1, S4-R12, S20-R19).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-R6, S11-R1, S4-R12, S20-R19).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2715,12 +2797,14 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>1. Margin % shows the row's Margin divided by its Subtotal, times 100, to one decimal with a percent sign — for example, 64.7%.
+          <t xml:space="preserve">1. Margin % shows the row's Margin divided by its Subtotal, times 100, to one decimal with a percent sign — for example, 64.7%.
 2. When the row's Subtotal is zero or below, the Margin % cell shows an em dash (—).
 3. Margin % is monochrome — no green or red coloring.
 4. The same calculation and format apply to customer rows, asset rows, and invoice rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S7-R11, S7-R12, S7-R13, S7-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-R11, S7-R12, S7-R13, S7-R14).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2765,14 +2849,16 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>1. The column heading reads "Inv. Hrs" (including the period after "Inv").
+          <t xml:space="preserve">1. The column heading reads "Inv. Hrs" (including the period after "Inv").
 2. The value is hours invoiced minus hours worked, rounded to one decimal.
 3. A positive value shows a leading + sign in the application's standard positive (green) color — for example, +1.5.
 4. A negative value shows a leading - sign in the standard negative (red) color — for example, -1.5.
 5. A zero/break-even value shows 0.0 in the default text color.
 6. The same calculation, label, format, and coloring apply on customer, asset, and invoice rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S12-R1, S12-R2, S12-R3, S12-R4, S12-R5, S12-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S12-R1, S12-R2, S12-R3, S12-R4, S12-R5, S12-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2817,11 +2903,13 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1. A customer, asset, or invoice with no labor shows 0.0 in the default color — never blank, "N/A," an em dash, or omitted.
+          <t xml:space="preserve">1. A customer, asset, or invoice with no labor shows 0.0 in the default color — never blank, "N/A," an em dash, or omitted.
 2. A value that rounds to 0.0 (for example +0.04) is shown as 0.0 in the default text color (not +0.0 in green).
 3. A negative value shows a minus sign and one decimal — for example, -0.5.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S12-N1, S12-E1, S12-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S12-N1, S12-E1, S12-E2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2867,11 +2955,13 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>1. An asset's invoice subtotals sum exactly to that asset's row total.
+          <t xml:space="preserve">1. An asset's invoice subtotals sum exactly to that asset's row total.
 2. A customer's asset subtotals sum exactly to the customer's row total.
 3. This holds for every financial column, not only Subtotal.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R13).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2917,12 +3007,14 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1. Subtotal is the rightmost column in the table.
+          <t xml:space="preserve">1. Subtotal is the rightmost column in the table.
 2. It stays visible pinned at the right edge while the table scrolls horizontally.
 3. Subtotal values are shown in bold on the header, on every customer, asset and invoice row, and on the totals row.
 4. Check it still holds after two changes: narrow the date range so fewer rows match, then sort by a different column. Subtotal stays the rightmost column, stays pinned, and stays bold both times.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S11-R1, S11-R2, S11-R3, S11-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S11-R1, S11-R2, S11-R3, S11-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2968,10 +3060,12 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>1. The totals row is computed over the full set of customers matching the active filters (date range, Product Type, location, Customer filter).
+          <t xml:space="preserve">1. The totals row is computed over the full set of customers matching the active filters (date range, Product Type, location, Customer filter).
 2. The totals do not change when you move between pages — they never reflect only the visible page.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -3017,13 +3111,16 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1. The column selector is a separate control next to the overflow menu — it is not an item inside the overflow menu.
+          <t xml:space="preserve">1. The column selector is a separate control next to the overflow menu — it is not an item inside the overflow menu.
 2. Hovering it shows the tooltip "Column Selection."
 3. The panel lists nine toggles, in order: Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %.
 4. With no saved selection, all nine toggleable columns default to visible.
-5. Note for the tester: there is no Location toggle in this panel. That is correct - the Location column appears by itself when you have more than one location in scope, so it is never something you switch on here.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S13-R1, S13-R2, S13-R3, S13-R4, S13-R7, S4-R12, S4-R13).</t>
+5. Note for the tester: this panel lists nine toggles and no Location toggle. The specification is currently inconsistent on this one point - one requirement says a Location toggle should be here for anyone who can reach more than one branch, while the list of nine does not include it. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Sales By Customer report specification version 14 (S13-R1, S13-R2, S13-R3, S13-R4, S13-R7, S4-R12, S4-R13), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -3069,11 +3166,13 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1. Turning a toggle off hides that column's header and all its body cells together; turning it on restores both together.
+          <t xml:space="preserve">1. Turning a toggle off hides that column's header and all its body cells together; turning it on restores both together.
 2. The Customer and Subtotal columns and the chevron control column do NOT appear in the toggle list and are always present.
 3. All nine columns can be hidden — nothing blocks the last toggle; the table still renders the Customer and Subtotal columns and the totals row still shows its Subtotal.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S13-R5, S13-R6, S13-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S13-R5, S13-R6, S13-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -3126,8 +3225,8 @@
 3. No Location column shows on the table either, because this person only ever has one location in view.
 4. Note for the tester: this test is about someone who only has ACCESS to one location. That is a different person from someone who can reach several locations but has picked just one. Do not mix the two up - they are separate tests, and the second one is still waiting on an answer from the product owner.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. In his own words the location column selector "should not appear if the user doesn't satisfy" having access to multiple locations. Nothing in the Sales By Customer report specification version 13 covers this, so his answers are the only basis for it, and it has not been checked on a build yet.
-AUTOMATION: HOLD - nobody has run this test yet, and it needs a sign-in that has access to exactly one location.
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. In his own words the location column selector "should not appear if the user doesn't satisfy" having access to multiple locations. Nothing in the Sales By Customer report specification version 14 covers this, so his answers are the only basis for it, and it has not been checked on a build yet.
+AUTOMATION: HOLD - waiting on an answer from the product owner
 </t>
         </is>
       </c>
@@ -3174,11 +3273,13 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>1. The overflow (export) menu is the leftmost control in the toolbar's action area and is the application's standard overflow-menu control.
+          <t xml:space="preserve">1. The overflow (export) menu is the leftmost control in the toolbar's action area and is the application's standard overflow-menu control.
 2. The menu items read, in order: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)" - and there is NO "Print" item anywhere in the menu.
 3. There are no separate always-visible export buttons - all exports live behind this one menu.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R1, S14-R2, S15-R1, S15-R2, S20-R16); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-R1, S14-R2, S15-R1, S15-R2, S20-R16); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -3226,13 +3327,15 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>1. The Summary file name is sales-by-customer-summary-{range}.csv and the Expanded file name is sales-by-customer-expanded-{range}.csv — so the file says which version it is.
-2. {range} follows the period you picked, using the nine periods the chooser actually offers: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Record the exact word the file uses for each - the mapping is confirmed in the build.
+          <t xml:space="preserve">1. The Summary file name is sales-by-customer-summary-{range}.csv and the Expanded file name is sales-by-customer-expanded-{range}.csv — so the file says which version it is.
+2. {range} follows the period you picked, using the nine periods the chooser actually offers: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. The specification gives the word for each period, so check the file against it.
 3. For a range you built yourself on the calendar, record what the file name uses in place of a period name - the exact wording is confirmed in the build.
 4. The file is plain comma-separated text with a .csv extension that opens as rows and columns in a spreadsheet — not an .xlsx workbook and not a JSON file.
 5. The two PDF downloads follow the same names with a .pdf extension — for example, sales-by-customer-summary-this_month.pdf and sales-by-customer-expanded-custom.pdf.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Customer report specification version 13 (S14-R14, S14-R15, S15-R6) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Customer report specification version 14 (S14-R14, S14-R15, S15-R6) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3278,7 +3381,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>1. With a single location in scope the Expanded View CSV has these thirteen columns in this exact order: Customer, Asset, Invoice #, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal. When more than one location is in scope the file also carries a Location column — immediately after Date, the position it holds on screen — making fourteen.
+          <t xml:space="preserve">1. With a single location in scope the Expanded View CSV has these thirteen columns in this exact order: Customer, Asset, Invoice #, Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal. When more than one location is in scope the file also carries a Location column — immediately after Date, the position it holds on screen — making fourteen.
 2. A customer row fills the Customer cell and leaves Asset, Invoice # and Date blank.
 3. An asset row leaves Customer blank, fills Asset, and leaves Invoice # and Date blank.
 4. An invoice row leaves Customer and Asset blank and fills Invoice # and Date.
@@ -3286,7 +3389,9 @@
 6. Work with no vehicle appears as an asset row named "Parts Sales".
 7. The file carries a "Locations:" line naming the location or locations the report was scoped to, or "All locations" when every location you can access is selected — as a leading line above the column headers.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R5, S14-R6, S14-R7, S14-R8, S14-R13, S4-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-R5, S14-R6, S14-R7, S14-R8, S14-R13, S4-R13).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -3331,14 +3436,16 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>1. Margin % is a plain number to one decimal with no percent sign (for example, 64.7); it is EMPTY when the row's Subtotal is zero or below.
+          <t xml:space="preserve">1. Margin % is a plain number to one decimal with no percent sign (for example, 64.7); it is EMPTY when the row's Subtotal is zero or below.
 2. Dates export as mm-dd-yyyy — for example, 05-14-2026.
 3. Currency values are plain numbers with no dollar sign and no thousands separators.
 4. The CSV has no color; the signed Inv. Hrs value still conveys direction.
 On this build the money in the spreadsheet file comes out as "$224.92" - with a dollar sign, and with a comma as well once the value passes a thousand - instead of the plain number described in point 3 above.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8823
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R9, S14-R10, S14-R11, S14-R12, S14-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-R9, S14-R10, S14-R11, S14-R12, S14-R13).
+AUTOMATION: READY - EXPECT FAIL (SV-8823)
+</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3384,11 +3491,13 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>1. Each export contains exactly the customers matching the active filters — the selected customers, within the active date range, Product Type, and location — in the active sort order.
+          <t xml:space="preserve">1. Each export contains exactly the customers matching the active filters — the selected customers, within the active date range, Product Type, and location — in the active sort order.
 2. When every customer is selected, the export contains the full set of customers under those filters.
 3. The chosen date range and Product Type are reflected in both exports.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S2-R7, S3-R7, S4-R10, S14-R3, S15-R3, S18-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S2-R7, S3-R7, S4-R10, S14-R3, S15-R3, S18-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3435,11 +3544,13 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>1. While a download is in progress, ONLY that menu item shows a loading state and is non-interactive; the other three items are unaffected.
+          <t xml:space="preserve">1. While a download is in progress, ONLY that menu item shows a loading state and is non-interactive; the other three items are unaffected.
 2. If a CSV download fails, an error toast is shown: "CSV export failed." (dismissed by the user).
 3. If a PDF download fails, the toast reads "PDF export failed." — identical behaviour, different wording.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-E1, S14-N1, S15-E1, S15-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-E1, S14-N1, S15-E1, S15-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3484,10 +3595,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>1. The PDF is A4 landscape using the application's standard font; the page margins look uniform on all sides. (The spec's exact 25px margin needs a PDF inspector — check the number only if you have one; otherwise uniform margins pass.)
+          <t xml:space="preserve">1. The PDF is A4 landscape using the application's standard font; the page margins look uniform on all sides. (The spec's exact 25px margin needs a PDF inspector — check the number only if you have one; otherwise uniform margins pass.)
 2. The footer has a centered "Software Powered by ShopView" label and a right-aligned page number "Page X of Y."
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S15-R5, S15-R6, S15-R7, S15-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S15-R5, S15-R6, S15-R7, S15-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3532,12 +3645,14 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>1. The header is two columns: a text block on the left (70% width) and the organization logo on the right (30% width).
+          <t xml:space="preserve">1. The header is two columns: a text block on the left (70% width) and the organization logo on the right (30% width).
 2. The text block shows the report title "Sales By Customer Report"; the organization name; the date range; and the filter summary line "Product Type: {value}" where value is "Parts &amp; Service," "Parts only," or "Service only."
 3. The header date range shows start and end in the format "Mon D, YYYY," joined by an em dash - for example, "May 1, 2026 - May 31, 2026" - and always shows both dates (every range is bounded).
-4. The header also carries a "Locations:" line naming the location(s) the report was scoped to (exact placement within the header is confirmed in the build).
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S15-R7, S15-R8, S15-R9, S15-R10, S15-R11, S15-R14, S4-R13); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+4. The header also carries a "Locations:" line naming the location(s) the report was scoped to.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S15-R7, S15-R8, S15-R9, S15-R10, S15-R11, S15-R14, S4-R13); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3583,13 +3698,15 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>1. With an uploaded logo, that logo appears pinned to the top-right, scaled to fit its area without distortion.
+          <t xml:space="preserve">1. With an uploaded logo, that logo appears pinned to the top-right, scaled to fit its area without distortion.
 2. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space.
 3. When no logo is printed, the logo column is not rendered and the text column fills the full width.
 4. The logo is embedded in the PDF (renders offline, not loaded from a network address).
 Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Customer report specification version 13 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18) differs, his decision is the authority.</t>
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Customer report specification version 14 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18) differs, his decision is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -3635,7 +3752,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>1. The Expanded View PDF's body table has the same columns, in the same order and with the same labels, as the Expanded View CSV — thirteen with a single location in scope, plus the Location column after Date when more than one location is in scope — including the Asset column — and shows the full Customer, then Asset, then Invoice breakdown, one block per customer.
+          <t xml:space="preserve">1. The Expanded View PDF's body table has the same columns, in the same order and with the same labels, as the Expanded View CSV — thirteen with a single location in scope, plus the Location column after Date when more than one location is in scope — including the Asset column — and shows the full Customer, then Asset, then Invoice breakdown, one block per customer.
 2. Body dates show as "Mon DD YYYY" - for example, "May 14 2026."
 3. The Date cell is blank on customer rows and on asset rows, matching the screen.
 4. Margin % shows an em dash when the row's Subtotal is zero or below.
@@ -3643,7 +3760,9 @@
 6. Inv. Hrs uses the same signs and coloring as on screen, with green rendered as #21ba45 and red as #c10015.
 7. The PDF header title reads "Sales By Customer Report" on the Summary and Expanded versions alike — which version you have is told by the file name and the contents, not by a different title.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S15-R5, S15-R13, S15-R19, S15-R20, S15-R21, S15-R22, S15-R23, S15-R24, S4-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S15-R5, S15-R13, S15-R19, S15-R20, S15-R21, S15-R22, S15-R23, S15-R24, S4-R13).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3689,13 +3808,15 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>1. For both CSV and PDF: no file is generated and no download starts.
+          <t xml:space="preserve">1. For both CSV and PDF: no file is generated and no download starts.
 2. An error toast is shown each time: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
 3. The cap counts customer rows plus invoice rows (not the header or totals row) against the active date range, Product Type, location, Customer filter, and sort.
 4. Below the cap the export succeeds normally.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R16, S15-R25, S14-R14, S15-R22); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-R16, S15-R25, S14-R14, S15-R22); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY - EXPECT FAIL (SV-8818)
+</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3740,10 +3861,12 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>1. The export still downloads — no error and no warning is shown.
+          <t xml:space="preserve">1. The export still downloads — no error and no warning is shown.
 2. The file contains the column headers and a totals row of zeros, with no data rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3789,13 +3912,15 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>1. The menu offers exactly four items: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)".
+          <t xml:space="preserve">1. The menu offers exactly four items: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)".
 2. Each Summary file gives ONE row per customer, without the asset or invoice detail rows.
 3. Each Expanded View file contains the full Customer, then Asset, then Invoice breakdown.
 4. All four files reflect exactly the filtered data shown on screen.
 5. With a single location in scope the Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When more than one location is in scope a Location column is added immediately after the Customer name and before the money columns.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. The Sales By Customer report specification version 13 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13) is silent on this point, and it has not yet been confirmed on a build.</t>
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. The Sales By Customer report specification version 14 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13) is silent on this point, and it has not yet been confirmed on a build.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3852,8 +3977,8 @@
 4. All six reports behave the same way.
 5. Note for the tester: step 2 is the difficult part. If you cannot get the organization into that state, mark this test Blocked and say so plainly - do not guess the answer.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. His words are: "Use the company's own uploaded logo. If a logo is set but fails to load, fall back to the built-in ShopView logo. If no logo is uploaded, print no logo and let the text fill the space." This DIFFERS from the Sales By Customer report specification version 13 (S15-R17), which shows the built-in ShopView logo when no logo has been uploaded rather than when an uploaded one fails to load, and we have taken his newer decision as the one that prevails. It has not been checked on a build yet.
-AUTOMATION: HOLD - nobody has run this test yet, and it needs an organization whose logo is set but will not load, which a tester cannot always produce.
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. His words are: "Use the company's own uploaded logo. If a logo is set but fails to load, fall back to the built-in ShopView logo. If no logo is uploaded, print no logo and let the text fill the space." This DIFFERS from the Sales By Customer report specification version 14 (S15-R17), which shows the built-in ShopView logo when no logo has been uploaded rather than when an uploaded one fails to load, and we have taken his newer decision as the one that prevails. It has not been checked on a build yet.
+AUTOMATION: HOLD - nobody has run this test yet; it needs one live check of a logo that fails to load
 </t>
         </is>
       </c>
@@ -3896,10 +4021,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>1. The saved view is restored: the date range, the Product Type, the location selection, the Customer filter selection, the sort column and direction, and the visible columns.
+          <t xml:space="preserve">1. The saved view is restored: the date range, the Product Type, the location selection, the Customer filter selection, the sort column and direction, and the visible columns.
 2. On load, the report shows the restored view immediately — the default view is never shown first and then replaced.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-R1, S6-R2, S6-R4, S2-R8, S3-R8, S4-R11, S10-R9, S13-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S6-R1, S6-R2, S6-R4, S2-R8, S3-R8, S4-R11, S10-R9, S13-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3945,12 +4072,14 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>1. The type-ahead search text is gone (only the resulting customer selection is saved).
+          <t xml:space="preserve">1. The type-ahead search text is gone (only the resulting customer selection is saved).
 2. All rows are collapsed — reloading clears all expansion state.
 3. The scroll position is not restored.
 4. This is the specified behavior (expansion is treated as fresh each visit), not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-R3, S8-R22).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S6-R3, S8-R22).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3996,11 +4125,13 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>1. The stale saved location is discarded and the location setting uses its default (your active location) instead.
+          <t xml:space="preserve">1. The stale saved location is discarded and the location setting uses its default (your active location) instead.
 2. No error appears and the report loads normally.
 3. Per the spec, the same discard-to-default applies to an unknown date range, a sort column that no longer exists, or a column set that does not match the current columns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-R5, S6-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S6-R5, S6-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4045,10 +4176,12 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>1. The other report keeps its own defaults/saved view — the Sales By Customer settings do not leak into it.
+          <t xml:space="preserve">1. The other report keeps its own defaults/saved view — the Sales By Customer settings do not leak into it.
 2. Sales By Customer still restores its own saved view.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S6-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -4095,14 +4228,16 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>1. Date range = This Month (nothing saved and no range in the page link).
+          <t xml:space="preserve">1. Date range = This Month (nothing saved and no range in the page link).
 2. Product Type = "Parts &amp; Service."
 3. Location = the single location you are currently working in (your active location) — not all locations.
 4. Customer filter = all customers selected (label "All customers").
 5. Sort = Customer name ascending.
 6. All nine toggleable columns visible.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S6-N1, S2-R5, S4-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S6-N1, S2-R5, S4-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -4148,10 +4283,12 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>1. The saved view is applied (Last Month) and the link value is ignored.
+          <t xml:space="preserve">1. The saved view is applied (Last Month) and the link value is ignored.
 2. This is intentional: a shared link restores the sender's range only for a recipient who has no saved range of their own.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S2-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S2-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4197,10 +4334,12 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>1. Scenario A: the filter restores to the all-customers state and the report shows every present customer — including the customer that appeared since the state was saved.
+          <t xml:space="preserve">1. Scenario A: the filter restores to the all-customers state and the report shows every present customer — including the customer that appeared since the state was saved.
 2. Scenario B: still-present saved ids are re-selected; a saved id no longer present is dropped (a stale saved id never forces an empty view); a customer that appeared since the set was saved is NOT auto-selected.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -4249,14 +4388,16 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>1. The table body shows the message "No sales data found for the selected filters." where customer rows would appear — not in the toolbar, the totals row, or a modal.
+          <t xml:space="preserve">1. The table body shows the message "No sales data found for the selected filters." where customer rows would appear — not in the toolbar, the totals row, or a modal.
 2. The toolbar stays visible and interactive (all filters including the Customer filter, and the action controls), so you can adjust filters without leaving the page.
 3. The same empty state appears whichever filter caused it (date range, Product Type, or location).
 4. The header-row chevron is hidden when the table has no visible rows.
 5. With a narrowed customer selection and no data, the empty state shows but the selection is KEPT (not cleared) — when the filters change back, the selected customers reappear.
 6. While the table is still loading, the empty-state message is NOT shown (the loading state is shown instead); it appears only once loading has finished and there are zero customers.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1, S17-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1, S17-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -4302,10 +4443,12 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>1. An error toast is shown: "An error occurred while fetching the report data."
+          <t xml:space="preserve">1. An error toast is shown: "An error occurred while fetching the report data."
 2. The toast auto-fades after 5 seconds.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (§7 User Feedback Summary).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (§7 User Feedback Summary).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -4353,7 +4496,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>1. The page background behind the data area is the standard soft blue-grey used across the suite, and the page itself has no border of empty space around it.
+          <t xml:space="preserve">1. The page background behind the data area is the standard soft blue-grey used across the suite, and the page itself has no border of empty space around it.
 2. The toolbar strip is white, its controls sit clear of the edges rather than pressed up against them, it sits flush against the top of the page with no gap, and the table reaches the left and right edges next to the side navigation.
 3. The left edge of the title lines up with the leftmost column of data, and the right edge of the action cluster lines up with the rightmost column.
 4. A thin dividing line separates the toolbar from the column headers.
@@ -4363,7 +4506,9 @@
 8. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 9. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing, the alignment and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this — 32px/24px toolbar padding, a 1px header border, 2rem edge padding, a 24px arrow — are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S20-R1, S20-R2, S20-R3, S20-R4, S20-R5, S20-R6, S20-R7, S20-R12, S20-R13, S20-R15, S20-R17).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S20-R1, S20-R2, S20-R3, S20-R4, S20-R5, S20-R6, S20-R7, S20-R12, S20-R13, S20-R15, S20-R17).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -4410,15 +4555,15 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>1. Column-header cells and customer summary rows use the white surface (#ffffff).
+          <t xml:space="preserve">1. Column-header cells and customer summary rows use the white surface (#ffffff).
 2. Asset rows and invoice rows use the blue-grey background (#f9fafb).
 3. The totals row uses the white surface with a top border and bold text (white on purpose, matching Technician Efficiency).
 4. The pinned Subtotal cell on any row uses that row's own background — never a contrasting strip.
 5. The three tree levels show by indentation: customer at the base, asset rows one level in (chevron and vehicle icon sit in from the customer), invoice rows one level deeper.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14).
+AUTOMATION: HOLD - waiting on an answer from the product owner
+</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -4463,10 +4608,12 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>1. In dark mode every visual rule applies with the dark equivalent of each color (dark background, dark surfaces).
+          <t xml:space="preserve">1. In dark mode every visual rule applies with the dark equivalent of each color (dark background, dark surfaces).
 2. The PDF export always renders in light-mode colors regardless of the user's app mode.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S20-R18).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S20-R18).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4512,11 +4659,13 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>1. Every toolbar control is visible and works on touch.
+          <t xml:space="preserve">1. Every toolbar control is visible and works on touch.
 2. Below 1024px the toolbar uses two rows: the action controls (overflow menu and column selector) on the first row, and the filter dropdowns on the second row, stacked at full width.
 3. At 1024px and above the toolbar uses the desktop single-row layout.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S21-R1, S21-R2, S21-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S21-R1, S21-R2, S21-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -4562,11 +4711,13 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>1. The data table scrolls sideways to show all columns, and the pinned Subtotal column stays visible during that scroll.
+          <t xml:space="preserve">1. The data table scrolls sideways to show all columns, and the pinned Subtotal column stays visible during that scroll.
 2. The chevron expand and collapse control on each row works on touch.
 3. The invoice number link opens the invoice in the same tab, the same as on desktop.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S21-R4, S21-R5, S21-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S21-R4, S21-R5, S21-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4614,11 +4765,13 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>1. Customer summary rows load WITHOUT the asset/invoice detail — the drill-down data is not preloaded.
+          <t xml:space="preserve">1. Customer summary rows load WITHOUT the asset/invoice detail — the drill-down data is not preloaded.
 2. The first expand of a customer triggers a server fetch for that customer's asset and invoice rows.
 3. Expand-all triggers at most one drill-down fetch per not-yet-expanded customer on the current page — a bounded number never exceeding the page size; it does not fetch customers beyond the current page or the whole result set.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S8-R14, S8-R16).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R14, S8-R16).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4665,12 +4818,14 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>1. Clicking a column header issues a server request that returns the customer rows ordered by that column.
+          <t xml:space="preserve">1. Clicking a column header issues a server request that returns the customer rows ordered by that column.
 2. The full filtered set is re-ordered and re-paginated on the server — the response is the first page of results in the new order, so page membership can change.
 3. The ordering is not done by re-shuffling rows already in the browser.
 4. A sort request naming a column the report does not offer is safely refused or ignored — never an error page or a crash; sorting works only on the report's own columns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S10-R8, S10-R8b).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S10-R8, S10-R8b).
+AUTOMATION: HOLD - this part of the report is not built yet
+</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4717,11 +4872,13 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>1. The dropdown does not load the full customer list into the browser up front.
+          <t xml:space="preserve">1. The dropdown does not load the full customer list into the browser up front.
 2. As you type, the browser fetches matching customers from the server — case-insensitive "contains" matching on the name, scoped to the active date range, Product Type, and location — and lists the returned customers.
 3. The all-customers state is stored as an explicit state (a flag), not an enumeration of the fetched ids.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R2, S18-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R2, S18-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4768,11 +4925,13 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>1. Customer rows arrive page by page from the server (server-paginated), not as one full client-side list.
+          <t xml:space="preserve">1. Customer rows arrive page by page from the server (server-paginated), not as one full client-side list.
 2. Changing the Customer selection re-fetches the matching customers as a fresh first page.
 3. The totals are computed on the server over the full set of matching customers — they arrive with the data and do not change as you page.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S18-R6, S18-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R6, S18-R11).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4818,11 +4977,13 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>1. The CSV and PDF are generated on the server from the active date range, Product Type, location, Customer filter, and sort — not assembled from the rows already loaded in the browser.
+          <t xml:space="preserve">1. The CSV and PDF are generated on the server from the active date range, Product Type, location, Customer filter, and sort — not assembled from the rows already loaded in the browser.
 2. Over the cap, the server does not generate the file (the request comes back as a refusal, not a file) and the browser starts no download — the count the cap checks is the count the file would contain, against the same filters and sort as the screen.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S14-R3, S14-R14, S15-R3, S15-R22).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-R3, S14-R14, S15-R3, S15-R22).
+AUTOMATION: READY - EXPECT FAIL (SV-8818)
+</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -4873,13 +5034,15 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>1. For the user WITH ordinary reports access, the report's data request succeeds (HTTP 200) and the report fills with rows.
+          <t xml:space="preserve">1. For the user WITH ordinary reports access, the report's data request succeeds (HTTP 200) and the report fills with rows.
 2. For that same user, the export request also succeeds (HTTP 200) and a file is produced.
 3. For the user WITHOUT reports access, the data request is refused with HTTP 403 and a message reading "Access denied." — no report data comes back.
 4. For that same user, the export request is refused with HTTP 403 as well — no file is produced.
 5. Note for the tester: one single permission controls all four of these. If you find the report data refused but the export allowed (or the other way round), that is a failure — record both response codes.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 13 (S1-R2, S1-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S1-R2, S1-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -4926,13 +5089,15 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>1. "Sales By Representative" appears in the Performance group, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency) — the label is the full word "Representative," not a "Rep" shorthand. It need not be the very last entry: the other new reports (Technician Utilization, Work In Progress, Sales By Customer) are added in the same below-the-anchors block, in no set order.
+          <t xml:space="preserve">1. "Sales By Representative" appears in the Performance group, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency) — the label is the full word "Representative," not a "Rep" shorthand. It need not be the very last entry: the other new reports (Technician Utilization, Work In Progress, Sales By Customer) are added in the same below-the-anchors block, in no set order.
 2. The rest of the navigation matches the previous release: no existing entry is moved, replaced, or reordered — if you can compare against production or an earlier build, the only difference is the added entry.
 3. Selecting the entry opens the report in the main content area.
 4. The page title reads "Sales By Representative".
 5. The browser tab title reads "Sales By Representative - Report | ShopView".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R1, S1-R2, S1-R3, S1-R4, S1-R5, S1-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R1, S1-R2, S1-R3, S1-R4, S1-R5, S1-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -4977,10 +5142,12 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>1. The full "Sales By Representative" label renders without crowding against the entry's edges and without truncation.
+          <t xml:space="preserve">1. The full "Sales By Representative" label renders without crowding against the entry's edges and without truncation.
 2. The label is not shortened to fit — the fix is the entry's horizontal padding, not the name.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -5025,9 +5192,11 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>1. "Sales By Representative" appears in the Performance group for this user — the entry is visible to every user who can see any other report in the same group.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R1).</t>
+          <t xml:space="preserve">1. "Sales By Representative" appears in the Performance group for this user — the entry is visible to every user who can see any other report in the same group.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5074,11 +5243,13 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>1. The entire Reports navigation — including the "Sales By Representative" entry — is not shown.
+          <t xml:space="preserve">1. The entire Reports navigation — including the "Sales By Representative" entry — is not shown.
 2. The report (and its ⋯ export menu) is not reachable.
 3. The Export Reports dialog and the Sales Representative Assignments download are not reachable.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-N1, S14-N3, S15-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-N1, S14-N3, S15-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -5122,9 +5293,11 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>1. The staff-editing surface is not reachable, so the deactivation flow (and its warning dialog) cannot be reached.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N1).</t>
+          <t xml:space="preserve">1. The staff-editing surface is not reachable, so the deactivation flow (and its warning dialog) cannot be reached.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5169,11 +5342,13 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>1. A date range picker is visible in the report toolbar.
+          <t xml:space="preserve">1. A date range picker is visible in the report toolbar.
 2. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
 3. The named periods use the application's standard shared calendar boundaries - this is one shared chooser used by all six reports.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Representative report specification version 15 (S2-R1, S2-R2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Representative report specification version 15 (S2-R1, S2-R2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5218,10 +5393,12 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>1. A custom range within the cap applies normally via the date-picker dialog.
+          <t xml:space="preserve">1. A custom range within the cap applies normally via the date-picker dialog.
 2. A custom selection whose span exceeds 366 days is not accepted — the picker holds you to a range of 366 days or fewer.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S2-R3, S2-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S2-R3, S2-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5267,11 +5444,13 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>1. The invoices dated on the start and end dates are INCLUDED (inclusive endpoints); the invoice outside the range is excluded.
+          <t xml:space="preserve">1. The invoices dated on the start and end dates are INCLUDED (inclusive endpoints); the invoice outside the range is excluded.
 2. The date used is the invoice's own date — the value shown in the Date column.
 3. The chosen date range is reflected in both PDF exports' header strips.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S2-R5, S2-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S2-R5, S2-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5319,13 +5498,15 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>1. The dropdown offers exactly three options: "Parts &amp; Service," "Parts only," "Service only" — with "Parts &amp; Service" as the default on first load.
+          <t xml:space="preserve">1. The dropdown offers exactly three options: "Parts &amp; Service," "Parts only," "Service only" — with "Parts &amp; Service" as the default on first load.
 2. "Parts only" includes only invoices whose number starts with P.
 3. "Service only" includes only invoices whose number starts with S.
 4. "Parts &amp; Service" applies no product-type filter — both appear again.
 5. Each change re-fetches and re-renders the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6, S3-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6, S3-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5371,12 +5552,14 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>1. An "Invoice Status" dropdown is visible in the toolbar.
+          <t xml:space="preserve">1. An "Invoice Status" dropdown is visible in the toolbar.
 2. It offers exactly four options: "All Statuses," "Unpaid," "Partially Paid," "Paid."
 3. "All Statuses" is the default on first load.
 4. Changing the selection re-fetches and re-renders the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R1, S4-R2, S4-R3, S4-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R1, S4-R2, S4-R3, S4-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -5423,12 +5606,14 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>1. "Paid" includes the paid, the overpaid, AND the prepaid-with-zero-balance invoices.
+          <t xml:space="preserve">1. "Paid" includes the paid, the overpaid, AND the prepaid-with-zero-balance invoices.
 2. "Partially Paid" includes the partially-paid AND the prepaid-with-a-balance-owed invoices.
 3. "Unpaid" includes only the unpaid invoice.
 4. The filter matches on the mapped display value, the same mapping the status badge uses — prepaid is the only state whose display value depends on the balance owed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -5475,12 +5660,14 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>1. Only invoices matching ALL active filters contribute — every metric reflects the intersection; an invoice failing any single filter contributes nothing anywhere.
+          <t xml:space="preserve">1. Only invoices matching ALL active filters contribute — every metric reflects the intersection; an invoice failing any single filter contributes nothing anywhere.
 2. A rep appears only if at least one invoice matches all active filters.
 3. Parts-only leg: rep A disappears; rep B's summary totals, detail rows, grand Totals, and (N) count reflect only the matching (P) invoices.
 4. Unpaid leg: rep C disappears; rep D's figures reflect only the Unpaid invoices.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R7, S4-R6, S4-N1, S3-R8, S3-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R7, S4-R6, S4-N1, S3-R8, S3-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5524,10 +5711,12 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>1. The invoice shows its FULL invoiced amounts (its full Subtotal) — payments are not netted out.
+          <t xml:space="preserve">1. The invoice shows its FULL invoiced amounts (its full Subtotal) — payments are not netted out.
 2. Filtering to "Unpaid" or "Partially Paid" changes which invoices are included, never the amounts shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -5572,10 +5761,12 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>1. The location filter is the rightmost control in the toolbar.
+          <t xml:space="preserve">1. The location filter is the rightmost control in the toolbar.
 2. It is a multi-select listing the locations the user has access to, plus an "All Locations" option.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-R1, S18-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-R1, S18-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -5623,13 +5814,14 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>1. With only Y selected, rep A disappears (no matching invoice at Y); rep B's metrics reflect only Y invoices — an invoice's location is that of its originating work order / parts sale.
+          <t xml:space="preserve">1. With only Y selected, rep A disappears (no matching invoice at Y); rep B's metrics reflect only Y invoices — an invoice's location is that of its originating work order / parts sale.
 2. Changing the selection re-fetches and re-renders scoped to the chosen set.
 3. "All Locations" means all locations the user can access — location Z's data is never included.
-4. With "All Locations" active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
-5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-R3, S21-R4, S21-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+4. With "All Locations" active you can tell which location each row's data belongs to — a location label or marking is shown.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-R3, S21-R4, S21-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -5674,10 +5866,12 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
+          <t xml:space="preserve">1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-N1). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-N1). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -5730,7 +5924,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>1. With more than one location in scope a Location column is shown, positioned immediately after the Status column and before Inv. Hrs.
+          <t xml:space="preserve">1. With more than one location in scope a Location column is shown, positioned immediately after the Status column and before Inv. Hrs.
 2. A rep summary row whose invoices are all at one location shows that location's name.
 3. A rep summary row whose invoices span more than one location shows "Multiple".
 4. An invoice detail row shows that invoice's own exact location — never "Multiple".
@@ -5738,12 +5932,14 @@
 6. The pinned Subtotal column is still rightmost — the Location column never displaces it.
 7. With a single location in scope the Location column is hidden.
 8. All four downloads include the Location column in the same position it occupies on screen. In the Summary files a rep's row carries that rep's location and reads "Multiple" when the rep spans more than one location; in the Expanded View files each invoice row carries that invoice's own exact location.
-Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all.
 Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
----
-DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Representative report specification version 15 (S21-R7, S21-R8, S18-R13, S14-R20) differs, his decision is the authority.</t>
+The Location column is not in the column-selection dropdown — that dropdown holds the seven metric columns only — and you cannot switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
+Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Sales By Representative report specification version 15 (S21-R7, S21-R8, S18-R13, S14-R20), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -5789,12 +5985,14 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>1. Rep A occupies exactly one summary row.
+          <t xml:space="preserve">1. Rep A occupies exactly one summary row.
 2. Reps B and C do not appear — there are no blank placeholder rows, and a reversed invoice never satisfies the contributor gate.
 3. The number of contributing invoices shows in parentheses after the rep's name, in a smaller, subdued grey font — e.g., Mary Smith (12) — and is always at least 1.
 4. A staff member with no matching invoice does not appear regardless of toggle state or historical activity.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R1, S5-R4, S5-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R1, S5-R4, S5-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -5841,13 +6039,15 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>1. With a single location in scope the columns appear left to right: Date, Invoice, Customer, Status, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal (12 columns). When more than one location is in scope the automatic Location column is added immediately after Status, making 13.
+          <t xml:space="preserve">1. With a single location in scope the columns appear left to right: Date, Invoice, Customer, Status, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal (12 columns). When more than one location is in scope the automatic Location column is added immediately after Status, making 13.
 2. On a rep summary row the Date cell holds the chevron control followed by the rep's display name ("First Last"); the date value is intentionally blank.
 3. The Invoice, Customer, and Status cells are blank on summary rows; the metric cells carry the rep's totals across all matching invoices.
 4. Rep summary rows are bold (700) so they read as parent rows; detail rows use the default weight (400) — row type is distinguished by font weight, not background color.
 5. Every row renders exactly the report's column count with blanks in position — a cell with nothing to show is blank, never shifted or wrapped (a drifted row is a defect). The grand Totals indicator is exempt: the desktop Totals row merges the four leading identifier columns; the mobile bar is not a table row.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R2, S5-R3, S5-R6, S5-R8, S5-R10, S5-N2, S6-R4, S18-R4, S18-R6a, S21-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R2, S5-R3, S5-R6, S5-R8, S5-R10, S5-N2, S6-R4, S18-R4, S18-R6a, S21-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -5894,12 +6094,14 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>1. Rep A still appears with credit intact; the name is followed by a subdued "(Inactive)" tag — e.g., Mary Smith (Inactive) (12) — in the same muted grey as the count.
+          <t xml:space="preserve">1. Rep A still appears with credit intact; the name is followed by a subdued "(Inactive)" tag — e.g., Mary Smith (Inactive) (12) — in the same muted grey as the count.
 2. The tag is display-only: metrics, A→Z position, and expandability are unchanged; a rep whose toggle is on shows no tag.
 3. For a deleted staff record, the display name and sort position come from the denormalized rep-name snapshot on the rep's most recent matching invoice (by invoice date, ties by invoice number), so the row still shows a historical name and sorts correctly.
 4. The grand Totals stay reconciled to the period's invoices — no revenue silently disappears.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -5944,11 +6146,13 @@
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>1. The rep's matching invoices appear as detail rows beneath the summary row; a brief row-level loading indicator shows while they load on the first expand.
+          <t xml:space="preserve">1. The rep's matching invoices appear as detail rows beneath the summary row; a brief row-level loading indicator shows while they load on the first expand.
 2. Each detail row shows, left to right: the invoice's date, the invoice number, the customer name, the payment status badge, and the per-invoice values for Inv. Hrs and the money columns.
 3. A rep with a single matching invoice can still be expanded — one detail row is shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R1, S6-R2, S6-R3, S6-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R1, S6-R2, S6-R3, S6-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
@@ -5994,11 +6198,13 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>1. With at least one rep collapsed the header chevron shows the "expand" glyph.
+          <t xml:space="preserve">1. With at least one rep collapsed the header chevron shows the "expand" glyph.
 2. Clicking expands every visible rep in one action; with every rep expanded the glyph switches to "collapse."
 3. A second activation collapses them all.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R5, S6-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R5, S6-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -6043,10 +6249,12 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>1. Every invoice appears under exactly one rep (the rep credited at invoicing time) or under the Unassigned row — never under two rows.
+          <t xml:space="preserve">1. Every invoice appears under exactly one rep (the rep credited at invoicing time) or under the Unassigned row — never under two rows.
 2. The sum of all (N) counts equals the number of matching invoices.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -6092,11 +6300,13 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>1. Expanded state is preserved across filter and sort changes within the same session.
+          <t xml:space="preserve">1. Expanded state is preserved across filter and sort changes within the same session.
 2. When a filter change removes a rep, the rep and its expansion state are gone; when a later change brings the rep back, the row renders collapsed (it does not auto-re-expand).
 3. A full page reload resets all expansion.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R8, S6-N1, S23-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R8, S6-N1, S23-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -6141,12 +6351,14 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>1. Detail rows order by invoice date descending (newest first).
+          <t xml:space="preserve">1. Detail rows order by invoice date descending (newest first).
 2. Date ties break by invoice number ascending by the numeric portion after the P/S prefix — numeric, not alphabetical, so S999 precedes S1000.
 3. If both the date and the numeric portion tie (e.g., P100 and S100 same day), P (Parts) sorts before S (Service).
 4. This order is independent of the rep-row column sort (which reorders summary rows only).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R9, S11-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R9, S11-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6193,12 +6405,14 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>1. The Status column sits immediately after the Customer column. With a single location in scope the next column to its right is Inv. Hrs; when more than one location is in scope the automatic Location column is inserted immediately after Status, so Inv. Hrs then follows Location.
+          <t xml:space="preserve">1. The Status column sits immediately after the Customer column. With a single location in scope the next column to its right is Inv. Hrs; when more than one location is in scope the automatic Location column is inserted immediately after Status, so Inv. Hrs then follows Location.
 2. Every detail row renders a small colored badge reading "Paid," "Partially Paid," or "Unpaid" — badge rendering is unconditional on detail rows.
 3. The mapping is: paid → Paid; overpaid → Paid; prepaid with zero balance → Paid; prepaid with a balance owed → Partially Paid; partially_paid → Partially Paid; unpaid → Unpaid.
 4. Badges are vertically centered in their cells; on rep summary rows the Status cell is blank; the badge's text is the accessible label — status is never conveyed by color alone.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S8-R1, S8-R2, S8-R4, S8-R5, S8-R6, S8-N1, S18-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S8-R1, S8-R2, S8-R4, S8-R5, S8-R6, S8-N1, S18-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6243,11 +6457,13 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>1. Paid = dark teal text on light teal; Partially Paid = dark orange on light orange; Unpaid = dark red on light red.
+          <t xml:space="preserve">1. Paid = dark teal text on light teal; Partially Paid = dark orange on light orange; Unpaid = dark red on light red.
 2. The badges use the same canonical payment-status color tokens as the invoice list, consistent app-wide.
 3. The treatment stays legible and consistent in both light and dark mode.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S8-R3, S18-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S8-R3, S18-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6292,10 +6508,12 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>1. The column heading reads "Inv. Hrs" (verbatim, including the period after "Inv").
+          <t xml:space="preserve">1. The column heading reads "Inv. Hrs" (verbatim, including the period after "Inv").
 2. The value equals the billed labor hours minus the technician clocked hours, rounded half-up to one decimal.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R1, S9-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R1, S9-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -6343,12 +6561,14 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>1. Positive values show a leading + in green (e.g., +1.5); negative values a leading - in red (e.g., -1.5); zero/break-even shows 0.0 in the default text color.
+          <t xml:space="preserve">1. Positive values show a leading + in green (e.g., +1.5); negative values a leading - in red (e.g., -1.5); zero/break-even shows 0.0 in the default text color.
 2. The same calculation, label, format, and coloring apply to rep summary rows, invoice detail rows, and the totals row.
 3. The rep-summary/totals value equals round(sum of unrounded per-invoice deltas).
 4. A value that rounds to 0.0 (e.g., +0.04) shows 0.0 in the default color — not +0.0 in green; negative values always use an explicit minus and one decimal (e.g., -0.5).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R3, S9-R4, S9-R5, S9-R6, S9-E1, S9-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R3, S9-R4, S9-R5, S9-R6, S9-E1, S9-E2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6393,10 +6613,12 @@
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>1. The invoice with neither billed labor hours nor clocked hours shows Inv. Hrs 0.0 in the default color — never blank, "N/A," or "—".
+          <t xml:space="preserve">1. The invoice with neither billed labor hours nor clocked hours shows Inv. Hrs 0.0 in the default color — never blank, "N/A," or "—".
 2. The invoice with clocked hours but no billed labor line shows the resulting NEGATIVE delta in red (e.g., -3.0) — the worked-but-unbilled signal is not suppressed to 0.0.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
@@ -6442,11 +6664,13 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>1. Margin % = Margin ÷ Subtotal × 100, to one decimal with a trailing % — e.g., 45.2%; a negative renders -8.4% (leading minus, no parentheses, no + on positives).
+          <t xml:space="preserve">1. Margin % = Margin ÷ Subtotal × 100, to one decimal with a trailing % — e.g., 45.2%; a negative renders -8.4% (leading minus, no parentheses, no + on positives).
 2. It renders "—" when Subtotal ≤ 0 — never "0.0%" or a divide-by-zero result.
 3. On every rolled-up row (rep summary rows and every totals row) Margin % is RECOMPUTED from that row-set's total Margin and total Subtotal — never the sum or average of the child percentages.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6491,12 +6715,14 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>1. The labels read exactly: Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
+          <t xml:space="preserve">1. The labels read exactly: Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 2. Subtotal = Labor Invoiced + Parts Invoiced, BEFORE tax.
 3. Labor Margin = Labor Invoiced − labor cost; Parts Margin = Parts Invoiced − parts cost; Margin = Labor Margin + Parts Margin.
 4. The same values appear everywhere the numbers show (screen, and later the exports).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R2, S21-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R2, S21-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6541,10 +6767,12 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>1. Negative dollar values render in accounting-convention parentheses — ($1,234.56) — on screen, across every money column (Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Subtotal).
+          <t xml:space="preserve">1. Negative dollar values render in accounting-convention parentheses — ($1,234.56) — on screen, across every money column (Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Subtotal).
 2. Inv. Hrs (a signed time value) and Margin % (a signed percentage) are excluded — they use a leading minus, not parentheses.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (§3 Key Decisions accounting parentheses).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (§3 Key Decisions accounting parentheses).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6588,11 +6816,13 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>1. All displayed values round half-up (away from zero) at their stated precision — money to cents; Inv. Hrs and Margin % to one decimal.
+          <t xml:space="preserve">1. All displayed values round half-up (away from zero) at their stated precision — money to cents; Inv. Hrs and Margin % to one decimal.
 2. Rolled-up values are computed from UNROUNDED components and then rounded, so a totals cell may differ from the eye-summed displayed rows by one unit in the last decimal.
 3. That one-unit difference is EXPECTED behavior per the spec — it must NOT be filed as a calculation defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (§3 half).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (§3 half).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6638,11 +6868,13 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>1. The worked-hours side updates — Inv. Hrs (hours invoiced minus hours worked) reflects the edited clock time after the reload.
+          <t xml:space="preserve">1. The worked-hours side updates — Inv. Hrs (hours invoiced minus hours worked) reflects the edited clock time after the reload.
 2. The billed SELL values (Labor, Parts, Subtotal) stay unchanged — a clock edit never rewrites what was billed.
 3. The figures tied to worked time move together consistently (Margin uses the labor cost behind the worked hours, so it may change too) — nothing is left stale.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6690,13 +6922,15 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>1. Subtotal is the rightmost column on every row type.
+          <t xml:space="preserve">1. Subtotal is the rightmost column on every row type.
 2. On screen it is pinned to the right edge and stays visible during horizontal scroll on every rep summary and invoice detail row.
 3. Subtotal values are bold across the header, every summary row, every detail row, and the grand Totals indicator.
 4. The pinned column matches the row's background color (white on body rows) — not a contrasting strip.
 5. The column-header row stays stuck to the top during vertical scroll; the Subtotal header cell stays visible in BOTH axes (top while scrolling down, pinned right while scrolling sideways).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R6, S10-N1, S18-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R6, S10-N1, S18-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -6743,13 +6977,15 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>1. A Totals row is the last row inside the table, sticky at the bottom of the scroll area, on the white card surface with a thin top border.
+          <t xml:space="preserve">1. A Totals row is the last row inside the table, sticky at the bottom of the scroll area, on the white card surface with a thin top border.
 2. Its first cell is a single merged cell spanning the four leading identifier columns (Date, Invoice, Customer, Status) labeled "Totals," followed by a cell per metric column and its own pinned Subtotal cell.
 3. The grand totals cover the FULL filtered result set — every matching non-reversed invoice across every rep, independent of which reps are expanded or loaded.
 4. Money uses accounting parentheses for negatives; Margin % is recomputed; values are round(sum of unrounded).
 5. The indicator is present whenever at least one summary row exists, and hidden during loading and in the empty state.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5, S10-N1, S16-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5, S10-N1, S16-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -6795,12 +7031,14 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>1. A simplified external totals bar sits directly below the table, outside its horizontal scroll container, showing "Totals" on the left and the grand Subtotal on the right (no other metrics).
+          <t xml:space="preserve">1. A simplified external totals bar sits directly below the table, outside its horizontal scroll container, showing "Totals" on the left and the grand Subtotal on the right (no other metrics).
 2. It does not scroll horizontally — it is always fully visible across.
 3. During vertical page scroll it sits after the table in normal flow (not pinned to the viewport bottom).
 4. It uses the white card surface with a thin top border.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5, S17-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5, S17-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -6845,11 +7083,13 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>1. Each financial column responds to a header click and reorders the rep rows.
+          <t xml:space="preserve">1. Each financial column responds to a header click and reorders the rep rows.
 2. The identifier columns (Date, Invoice, Customer, Status) do not respond to header clicks.
 3. The Date header carries the expand/collapse-all chevron, not a sort affordance.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R1, S11-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R1, S11-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -6893,10 +7133,12 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>1. Rows render in A→Z order by display name, case-insensitive.
+          <t xml:space="preserve">1. Rows render in A→Z order by display name, case-insensitive.
 2. There are NO active/inactive tiers — an "(Inactive)" rep sorts by name among the others, not grouped separately.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -6943,12 +7185,14 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>1. The first click sorts Subtotal ASCENDING and shows an ascending direction indicator on the header.
+          <t xml:space="preserve">1. The first click sorts Subtotal ASCENDING and shows an ascending direction indicator on the header.
 2. The second click toggles to DESCENDING.
 3. There is no third "cleared" state — the third click returns to ascending.
 4. Via the column headers there is no way back to A→Z; the A→Z default shows only when a session carries no valid saved financial sort.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R5, S23-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R5, S23-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -6993,11 +7237,13 @@
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
-          <t>1. Only the rep summary rows reorder.
+          <t xml:space="preserve">1. Only the rep summary rows reorder.
 2. Invoice detail rows stay grouped under their parent rep, keeping their own newest-first order.
 3. The Unassigned row stays pinned to the top regardless of sort.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R2, S22-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R2, S22-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H129" s="2" t="inlineStr">
@@ -7042,10 +7288,12 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>1. Reps with equal values in the sorted column retain the default A→Z order between them.
+          <t xml:space="preserve">1. Reps with equal values in the sorted column retain the default A→Z order between them.
 2. A Margin % cell rendered "—" (undefined) sorts as zero.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -7091,11 +7339,13 @@
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>1. Each invoice number is a clickable link.
+          <t xml:space="preserve">1. Each invoice number is a clickable link.
 2. Activating it navigates the CURRENT tab to the underlying invoice (work order or parts sale) — never a new tab.
 3. The customer name is likewise a clickable link that navigates the current tab to the customer's record.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R1, S12-R2, S12-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R1, S12-R2, S12-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H131" s="2" t="inlineStr">
@@ -7141,11 +7391,13 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>1. Back returns to the report with ALL state intact — date range, product type, invoice status, location, Show Unassigned, every rep's expansion state, and scroll position — exactly as they were.
+          <t xml:space="preserve">1. Back returns to the report with ALL state intact — date range, product type, invoice status, location, Show Unassigned, every rep's expansion state, and scroll position — exactly as they were.
 2. Back-navigation does not trigger a full report reload.
 3. This is deliberately different from a page reload, which restores persisted filters/columns/sort but resets expansion and scroll.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R3a, S23-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R3a, S23-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -7191,12 +7443,14 @@
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>1. Invoice-number link: theme-primary color, no underline at rest; an underline appears on hover and on keyboard focus (visible focus indicator); it never recolors to browser-purple after a click.
+          <t xml:space="preserve">1. Invoice-number link: theme-primary color, no underline at rest; an underline appears on hover and on keyboard focus (visible focus indicator); it never recolors to browser-purple after a click.
 2. Customer-name link: inherits the cell's body text color (never theme-blue), no underline at rest; underline on hover and keyboard focus; never browser-purple.
 3. Both hold in light and dark mode and across return visits.
 4. Underlined-at-rest links, browser-blue customer names, purple post-click links, and new-tab destinations are all defects.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R4, S12-R5, S12-R6, S12-N3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R4, S12-R5, S12-R6, S12-N3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H133" s="2" t="inlineStr">
@@ -7241,10 +7495,12 @@
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>1. The tab navigates to the application's standard not-found/access-denied state.
+          <t xml:space="preserve">1. The tab navigates to the application's standard not-found/access-denied state.
 2. Pressing back still returns to the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-N1, S12-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-N1, S12-N2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H134" s="2" t="inlineStr">
@@ -7290,11 +7546,13 @@
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>1. A warning dialog titled "Deactivate {Staff Name}?" opens BEFORE any change is applied; the deactivation does not commit until confirmed.
+          <t xml:space="preserve">1. A warning dialog titled "Deactivate {Staff Name}?" opens BEFORE any change is applied; the deactivation does not commit until confirmed.
 2. The body shows "{Staff Name} is the sales representative on {N} customer{s}." — singular for N=1 ("1 customer"), plural otherwise ("3 customers") — followed by the reassurance line "Their customer assignments will stay where they are."
 3. Focus is trapped within the dialog while open and returns to the invoking control on dismiss.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R1, S13-R3, S13-R4, S13-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R1, S13-R3, S13-R4, S13-R12).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -7341,12 +7599,14 @@
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>1. Below the reassurance copy, instruction text reads "Type YES to confirm" (with "YES" emphasized) above a single auto-focused text input.
+          <t xml:space="preserve">1. Below the reassurance copy, instruction text reads "Type YES to confirm" (with "YES" emphasized) above a single auto-focused text input.
 2. The primary "Deactivate" button is disabled until the input matches the confirmation word case-insensitively, ignoring leading/trailing whitespace — yes, YES, Yes (and padded variants) all enable it; "no" does not.
 3. While disabled, hovering it shows the tooltip "Type YES above to enable."
 4. Pressing Enter while valid submits.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R6, S13-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R6, S13-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H136" s="2" t="inlineStr">
@@ -7394,13 +7654,15 @@
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>1. The dialog has a "Cancel" button (grey) and an "X" close icon; the "Deactivate" button is the red one.
+          <t xml:space="preserve">1. The dialog has a "Cancel" button (grey) and an "X" close icon; the "Deactivate" button is the red one.
 2. Clicking "Cancel" closes the dialog; clicking the "X" icon closes the dialog.
 3. Pressing the "Esc" key does NOT close the dialog - it stays open (the app's general rule is that pop-ups do not close with the Esc key).
 4. Clicking outside the dialog does NOT close it.
 5. When the dialog closes via Cancel or X, the staff member's active status is unchanged - no deactivation happens.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -7445,12 +7707,14 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>1. The "Deactivate" button enters the standard in-flight loading state (non-interactive, in-progress indicator); the dialog stays open and the Cancel and X controls are non-interactive during the request (pressing the "Esc" key never closes the dialog at any time).
+          <t xml:space="preserve">1. The "Deactivate" button enters the standard in-flight loading state (non-interactive, in-progress indicator); the dialog stays open and the Cancel and X controls are non-interactive during the request (pressing the "Esc" key never closes the dialog at any time).
 2. On success the dialog closes and the change applies.
 3. Customer assignments are NOT modified — every customer stays assigned to this rep; denormalized rep names and past invoice snapshots are preserved.
 4. Deactivation never forces reassignment, blocks on assignments, or auto-reassigns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R9, S13-R10, S13-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R9, S13-R10, S13-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7496,11 +7760,13 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>1. The sales-representative toggle state is unchanged by the deactivation flow.
+          <t xml:space="preserve">1. The sales-representative toggle state is unchanged by the deactivation flow.
 2. In the Sales Representative Assignments CSV the rep's customers show "Rep is active?" = "No" — that column is driven by staff-active status, not the toggle.
 3. In the report the rep still appears with credit intact; the "(Inactive)" marker appears only if the sales-representative TOGGLE is off (a separate flag from staff-active status).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R11, S15-R6, S5-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R11, S15-R6, S5-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7546,12 +7812,14 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>1. For a staff member without the sales-representative toggle, the precondition check is skipped and no warning is shown.
+          <t xml:space="preserve">1. For a staff member without the sales-representative toggle, the precondition check is skipped and no warning is shown.
 2. Reactivation never shows the warning dialog (the flow does not apply to an already-inactive member).
 3. After reactivation the assignments re-surface immediately with no extra action.
 4. Deactivating a sales representative with NO customer assignments applies silently — no warning dialog.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R2, S13-N2, S13-N3, S13-E3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R2, S13-N2, S13-N3, S13-E3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7597,11 +7865,13 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>1. An error toast is shown: "Ooooops! An error occurred" with the caption "For more information, please contact support. Include your request ID: [{request-id}] when reaching out for faster assistance." — it persists 120 seconds or until dismissed.
+          <t xml:space="preserve">1. An error toast is shown: "Ooooops! An error occurred" with the caption "For more information, please contact support. Include your request ID: [{request-id}] when reaching out for faster assistance." — it persists 120 seconds or until dismissed.
 2. The active status is unchanged.
 3. Each fresh dialog open requires a fresh confirmation entry — the input clears on open.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -7647,10 +7917,12 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>1. The system NEVER silently deactivates — the warning dialog still opens (fallback), so the type-to-confirm gate still applies.
+          <t xml:space="preserve">1. The system NEVER silently deactivates — the warning dialog still opens (fallback), so the type-to-confirm gate still applies.
 2. Because the customer count is unavailable, the dialog OMITS the count headline and shows only the reassurance line "Their customer assignments will stay where they are." above the "Type YES to confirm" gate.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7695,10 +7967,12 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>1. A "Show Unassigned" toggle sits between the column selector and the date range picker; it is OFF by default.
+          <t xml:space="preserve">1. A "Show Unassigned" toggle sits between the column selector and the date range picker; it is OFF by default.
 2. While off, invoices with no assigned rep contribute to nothing — no row, and not counted in any total.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-R1, S22-R2, S18-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-R1, S22-R2, S18-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -7745,12 +8019,14 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>1. A single summary row labeled "Unassigned" (verbatim) rolls up every matching invoice that has no assigned rep, respecting all other active filters.
+          <t xml:space="preserve">1. A single summary row labeled "Unassigned" (verbatim) rolls up every matching invoice that has no assigned rep, respecting all other active filters.
 2. The row is pinned to the TOP of the table, above the A→Z reps, and stays pinned regardless of sort.
 3. Toggling re-renders the report and recomputes the grand Totals to include or exclude the Unassigned row accordingly.
 4. The Unassigned row shows the same metric columns and (N) count as any rep summary row, is expandable to its contributing invoices, is included in the grand Totals, and never carries an "(Inactive)" tag.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-R3, S22-R4, S22-R5, S22-R6, S6-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-R3, S22-R4, S22-R5, S22-R6, S6-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7796,10 +8072,12 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>1. With the toggle on but no matching unassigned invoices, no Unassigned row is shown — an empty Unassigned row is never rendered; with no rep rows either, the empty state applies.
+          <t xml:space="preserve">1. With the toggle on but no matching unassigned invoices, no Unassigned row is shown — an empty Unassigned row is never rendered; with no rep rows either, the empty state applies.
 2. Turning the toggle off removes the expanded row; turning it back on renders it collapsed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-N1, S6-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-N1, S6-N2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7847,13 +8125,15 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>1. The dropdown lists the seven toggleable metric columns, each with a toggle switch: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %.
+          <t xml:space="preserve">1. The dropdown lists the seven toggleable metric columns, each with a toggle switch: Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %.
 2. On first visit all seven metric columns are visible.
 3. The five always-visible columns (Date, Invoice, Customer, Status, Subtotal) do not appear in the dropdown and cannot be hidden.
 4. With all seven metric columns hidden the table still renders the five always-on columns and the grand Totals indicator — no empty or error state.
 5. Note for the tester: if you have more than one location in scope you will also see a Location column on the table that is in neither list. That is correct - it appears by itself and is not something you can switch on or off here.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R1, S20-R2, S20-R3, S20-R6, S20-N1, S21-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R1, S20-R2, S20-R3, S20-R6, S20-N1, S21-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7898,10 +8178,12 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>1. The toggle takes effect immediately — no confirm step.
+          <t xml:space="preserve">1. The toggle takes effect immediately — no confirm step.
 2. Hiding a metric column removes it from rep summary rows, invoice detail rows, and the grand Totals indicator simultaneously; showing restores it everywhere at once.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R4, S20-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R4, S20-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -7946,9 +8228,11 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>1. All four downloads include ALL metric columns regardless of the on-screen column selector state.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R8).</t>
+          <t xml:space="preserve">1. All four downloads include ALL metric columns regardless of the on-screen column selector state.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -7993,10 +8277,12 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>1. Hiding the active sort column does not clear the sort — rows stay ordered by the now-hidden metric until another sort is chosen or the A→Z default is restored.
+          <t xml:space="preserve">1. Hiding the active sort column does not clear the sort — rows stay ordered by the now-hidden metric until another sort is chosen or the A→Z default is restored.
 2. Showing the column again reveals the sort indicator on it.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -8042,10 +8328,12 @@
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
-          <t>1. Every setting is restored: date range (including the custom start/end), product type, invoice status, location, Show Unassigned, column visibility, and the active column sort (column + direction).
+          <t xml:space="preserve">1. Every setting is restored: date range (including the custom start/end), product type, invoice status, location, Show Unassigned, column visibility, and the active column sort (column + direction).
 2. The settings are restored BEFORE the first data fetch — the report does not fetch defaults first and then re-fetch.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R1, S20-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R1, S20-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr">
@@ -8090,10 +8378,12 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>1. All rows render collapsed and the scroll position resets.
+          <t xml:space="preserve">1. All rows render collapsed and the scroll position resets.
 2. This is the specified behavior (only back-navigation from a drilldown restores expansion/scroll), not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8138,11 +8428,13 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>1. The no-longer-valid location falls back to the default (your active location) rather than being sent to the server.
+          <t xml:space="preserve">1. The no-longer-valid location falls back to the default (your active location) rather than being sent to the server.
 2. No error occurs — a stale saved setting can never cause an error or an invalid request.
 3. Per the spec the same applies to a range or sort column that no longer exists and to a hidden-but-sorted column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -8187,10 +8479,12 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>1. Date range = This Month; Product Type = "Parts &amp; Service"; Invoice Status = "All Statuses"; Location = your currently active location only (the one location you are working in); Show Unassigned = off; all seven metric columns visible; sort = the A→Z default.
+          <t xml:space="preserve">1. Date range = This Month; Product Type = "Parts &amp; Service"; Invoice Status = "All Statuses"; Location = your currently active location only (the one location you are working in); Show Unassigned = off; all seven metric columns visible; sort = the A→Z default.
 2. Clearing browser storage fully returns the report to first-visit defaults — no server-side profile brings the old settings back.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R4, S23-N1, S2-R4, S2-R7, S21-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R4, S23-N1, S2-R4, S2-R7, S21-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8235,10 +8529,12 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>1. The report restores to the A→Z default order by rep display name.
+          <t xml:space="preserve">1. The report restores to the A→Z default order by rep display name.
 2. No financial column shows a sort indicator — the saved "no financial sort" state restores as A→Z, not as an arbitrary column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R5, S11-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R5, S11-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -8284,10 +8580,12 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>1. The menu lists exactly four actions: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", and "Download Expanded View (CSV)".
+          <t xml:space="preserve">1. The menu lists exactly four actions: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", and "Download Expanded View (CSV)".
 2. No other entries appear in the menu.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R1, S17-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R1, S17-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -8336,13 +8634,15 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>1. Every file contains only the reps/invoices matching ALL the active filters (date range, product type, invoice status, location, Show Unassigned).
+          <t xml:space="preserve">1. Every file contains only the reps/invoices matching ALL the active filters (date range, product type, invoice status, location, Show Unassigned).
 2. The files reflect the FULL result set for those filters — a collapsed (never-expanded) rep's invoices still appear in the Expanded View files; on-screen expansion state does not matter.
 3. Rep rows appear in the report's currently-active order — the active column sort if one is set, otherwise the A→Z default.
 4. The Unassigned row (Show Unassigned on) is pinned first, ahead of the sorted reps.
-5. Every file (all four downloads, PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R2, S14-R2a, S14-R20, S21-R6, S22-R4).</t>
+5. Every file (all four downloads, PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R2, S14-R2a, S14-R20, S21-R6, S22-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -8389,13 +8689,15 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>1. The PDF is A4 portrait, edge-to-edge, with a header strip on the first page showing the workplace name and address, the organization logo, the report title "Sales By Representative," and the selected date range.
+          <t xml:space="preserve">1. The PDF is A4 portrait, edge-to-edge, with a header strip on the first page showing the workplace name and address, the organization logo, the report title "Sales By Representative," and the selected date range.
 2. There is one rolled-up row per rep, in the report's currently-active order; a toggled-off contributor's name carries the "(Inactive)" tag.
 3. With a single location in scope the columns are: Rep / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal. When more than one location is in scope a Location column is added immediately after the Representative name and before the money columns, and a rep who spans more than one location reads "Multiple".
 4. Subtotal is bolded across the header, the body rows, and the grand totals row; Inv. Hrs keeps its green/red/default coloring.
 5. The grand totals row reads "Totals" in the Rep cell and aggregates every summary row in the document (including the Unassigned row when Show Unassigned is on); its Margin % is RECOMPUTED as total Margin ÷ total Subtotal (shown "—" when that Subtotal is zero or below), never the sum or average of the rows' percentages.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. The Sales By Representative report specification version 15 (S14-R3, S14-R5, S14-R20, S2-R5) is silent on this point, and it has not yet been confirmed on a build.</t>
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. The Sales By Representative report specification version 15 (S14-R3, S14-R5, S14-R20, S2-R5) is silent on this point, and it has not yet been confirmed on a build.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -8442,14 +8744,16 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>1. There is one page-block per rep, in the report's currently-active order, with a page break before each new rep after the first.
+          <t xml:space="preserve">1. There is one page-block per rep, in the report's currently-active order, with a page break before each new rep after the first.
 2. Each block shows the header strip (workplace name and address, organization logo, title "Sales By Representative," the selected date range), the rep's name, and a per-invoice table with columns: Date / Invoice / Customer / Status / (Location, only when more than one location is in scope, carrying that invoice's own location) / Inv. Hrs / Labor Invoiced / Labor Margin / Parts Invoiced / Parts Margin / Margin / Margin % / Subtotal.
 3. The Status column renders the same colored badge as on screen, vertically centered.
 4. Invoices are ordered newest first (the same order as the on-screen expansion: invoice date descending, numeric invoice-number tie-break).
 5. Each block ends with a per-rep totals row — "Totals" in the Date cell; Invoice/Customer/Status blank; each metric aggregated; Margin % recomputed.
 6. There is NO grand-totals row across all reps at the end of the document.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R6, S14-R8, S14-R20, S6-R9). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R6, S14-R8, S14-R20, S6-R9). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -8494,11 +8798,13 @@
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>1. On screen, both invoice numbers show in full — never truncated.
+          <t xml:space="preserve">1. On screen, both invoice numbers show in full — never truncated.
 2. In the PDF, the long number is cut to its first 18 characters followed by an ellipsis (the ellipsis is not counted toward the 18).
 3. In the PDF, the 18-character-or-shorter number shows in full with no ellipsis.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H159" s="2" t="inlineStr">
@@ -8545,12 +8851,15 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>1. The files are named exactly "sales-by-representative-summary.pdf" and "sales-by-representative-expanded.pdf".
+          <t xml:space="preserve">1. The files are named exactly "sales-by-representative-summary.pdf" and "sales-by-representative-expanded.pdf".
 2. A footer reading "Software Powered by ShopView" appears on EVERY page of both PDFs.
 3. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space. The PDF still generates normally either way.
 ---
 Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Representative report specification version 15 (S14-R3a, S14-R4, S14-R11) differs, his decision is the authority.</t>
+---
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Representative report specification version 15 (S14-R3a, S14-R4, S14-R11) differs, his decision is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -8596,11 +8905,13 @@
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
-          <t>1. Negative dollar values render in accounting parentheses — for example ($1,234.56) — in both PDFs, with no extra color treatment.
+          <t xml:space="preserve">1. Negative dollar values render in accounting parentheses — for example ($1,234.56) — in both PDFs, with no extra color treatment.
 2. The on-screen (N) invoice count does NOT appear next to any rep name in either PDF.
 3. The "(Inactive)" tag DOES render on toggled-off contributors' names in both PDFs; other rep names render plainly.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R9, S14-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R9, S14-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
@@ -8647,11 +8958,13 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>1. As the longest positive dollar value in the document grows past each length bracket, the PDF body text visibly steps DOWN in size — the relative step-downs are the pass criterion for this manual test.
+          <t xml:space="preserve">1. As the longest positive dollar value in the document grows past each length bracket, the PDF body text visibly steps DOWN in size — the relative step-downs are the pass criterion for this manual test.
 2. Column widths are fixed for the worst case regardless of tier — the layout never breaks and no value overflows or wraps its column.
 3. Both PDF formats adapt the same way.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R12, S14-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R12, S14-R13).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -8698,7 +9011,7 @@
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
-          <t>1. The file is named "sales-by-representative-summary.csv" and starts with a UTF-8 BOM.
+          <t xml:space="preserve">1. The file is named "sales-by-representative-summary.csv" and starts with a UTF-8 BOM.
 2. With a single location in scope the headers, in order, are: Representative, # Invoices, # Customers, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal. On this build only nine of them arrive - Representative, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal - because # Invoices, # Customers, Hrs Worked and Hrs Invoiced are missing by mistake. Record what you see; the four missing columns are with the developers.
 3. There is one header row plus one row per rep in the current filtered view, in the report's currently-active order.
 4. "# Invoices" equals the on-screen (N); "# Customers" counts distinct customers across those invoices (de-duplicated across locations when several are selected).
@@ -8706,7 +9019,9 @@
 6. Note for the tester: the heading in this file reads simply "Representative". The product owner has confirmed that is correct and not slang, so do not fail the test for it.
 7. When more than one location is in scope the file also carries a Location column, immediately after the Representative name and before the money columns; a rep whose invoices span more than one location reads "Multiple".
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Representative report specification version 15 (S14-R15, S14-R18, S14-R20) differs, his decision is the authority.</t>
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Representative report specification version 15 (S14-R15, S14-R18, S14-R20) differs, his decision is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
@@ -8752,13 +9067,15 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>1. The file is named "sales-by-representative-expanded.csv" and starts with a UTF-8 BOM.
+          <t xml:space="preserve">1. The file is named "sales-by-representative-expanded.csv" and starts with a UTF-8 BOM.
 2. With a single location in scope the headers, in order, are: Representative, Date, Invoice #, Customer, Status, Hrs Worked, Hrs Invoiced, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Margin %, Subtotal.
 3. There is one header row plus one row per invoice, flattened across all reps in the report's currently-active order, for the current filtered view.
 4. Note for the tester: the heading in this file reads simply "Representative". The product owner has confirmed that is correct and not slang, so do not fail the test for it.
 5. When more than one location is in scope the file also carries a Location column immediately after Status — the position it holds on screen — and every row shows that invoice's own exact location, never "Multiple".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Representative report specification version 15 (S14-R16, S14-R20) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Representative report specification version 15 (S14-R16, S14-R20) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8803,7 +9120,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>1. Numeric columns are plain numbers — NO currency symbol, thousands separators, or parentheses; a negative uses a leading minus (for example, -1234.56).
+          <t xml:space="preserve">1. Numeric columns are plain numbers — NO currency symbol, thousands separators, or parentheses; a negative uses a leading minus (for example, -1234.56).
 2. Money values carry two decimals; Hrs Worked / Hrs Invoiced / Inv. Hrs carry their full stored precision; Inv. Hrs keeps its leading + or - sign.
 3. Margin % is a plain number to one decimal (for example, 45.2) with no % sign, and the cell is EMPTY where Margin % is undefined (Subtotal ≤ 0).
 4. The "Sales Representative" name carries the "(Inactive)" tag when applicable; the on-screen (N) count is NOT embedded in the name.
@@ -8812,7 +9129,9 @@
 On this build the money in the spreadsheet file comes out as "$1,979.40" - with a dollar sign and a comma - instead of the plain number described in point 1 above.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8823
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R17).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R17).
+AUTOMATION: READY - EXPECT FAIL (SV-8823)
+</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -8859,12 +9178,14 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>1. With the toggle ON: the Summary PDF and Summary CSV each carry one rolled-up row whose Rep / "Sales Representative" cell reads the literal "Unassigned", sorted to the top; the Expanded CSV rows for those invoices carry "Sales Representative" = "Unassigned"; the Expanded View PDF has its own TOP page-block titled "Unassigned".
+          <t xml:space="preserve">1. With the toggle ON: the Summary PDF and Summary CSV each carry one rolled-up row whose Rep / "Sales Representative" cell reads the literal "Unassigned", sorted to the top; the Expanded CSV rows for those invoices carry "Sales Representative" = "Unassigned"; the Expanded View PDF has its own TOP page-block titled "Unassigned".
 2. The Summary PDF grand-totals row aggregates across all summary rows INCLUDING Unassigned; in the Summary CSV the Unassigned row is simply one of the data rows (no totals row exists).
 3. With the toggle OFF: no Unassigned row and no unassigned invoices appear in ANY of the four files.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R19, S22-R2, S22-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R19, S22-R2, S22-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -8911,11 +9232,13 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>1. While a PDF is generating, the action shows a loading state and is non-interactive until the file is delivered.
+          <t xml:space="preserve">1. While a PDF is generating, the action shows a loading state and is non-interactive until the file is delivered.
 2. A failed download shows the error toast "Ooooops! An error occured" (the typo is as-shipped) — it persists 120 seconds or until dismissed.
 3. A genuine failure downloads nothing — never a malformed file.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-N1, S14-N2, S14-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-N1, S14-N2, S14-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8960,12 +9283,14 @@
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
-          <t>1. No file is produced — the server declines rather than generating a truncated file.
+          <t xml:space="preserve">1. No file is produced — the server declines rather than generating a truncated file.
 2. An error toast reads exactly: "This report is too large to export. Narrow the date range or filters, then try again." (persists 120 seconds or until dismissed).
 3. Below the cap, a large Expanded View PDF still generates normally (many reps × many invoices is expected).
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY - EXPECT FAIL (SV-8818)
+</t>
         </is>
       </c>
       <c r="H168" s="2" t="inlineStr">
@@ -9010,13 +9335,15 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>1. All four downloads produce a FILE, not an error.
+          <t xml:space="preserve">1. All four downloads produce a FILE, not an error.
 2. The Summary PDF renders the header strip, no data rows, and a grand-totals row showing zeros for the money and Inv. Hrs columns and "—" for Margin %.
 3. The Expanded View PDF renders just the header strip with no per-rep blocks (it has no grand-totals row).
 4. Both CSVs generate a header-row-only file, still starting with the UTF-8 BOM.
 5. No special "empty" treatment or message appears inside the files.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -9063,12 +9390,14 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>1. "Sales Representative Assignments" appears in the Report Name dropdown, appended at the BOTTOM of the list (additive — no existing entry moved or removed).
+          <t xml:space="preserve">1. "Sales Representative Assignments" appears in the Report Name dropdown, appended at the BOTTOM of the list (additive — no existing entry moved or removed).
 2. Selecting it HIDES the date range picker.
 3. The dialog shows the note: "Snapshot of current sales representative assignments. Both active and inactive reps with assignments are listed."
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R1, S15-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R1, S15-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9115,13 +9444,15 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>1. The file downloads as "sales-representative-assignments.csv" — the short form "rep" is gone from the file name.
+          <t xml:space="preserve">1. The file downloads as "sales-representative-assignments.csv" — the short form "rep" is gone from the file name.
 2. A success toast shows "Success" with the caption "Report downloaded." and auto-fades after 5 seconds.
 3. The CSV starts with a UTF-8 BOM and its headers, in order, are exactly: Customer Name, Sales Representative, Rep is active?.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 5. Note for the tester: this file has only those three columns even if you have several locations in scope. It is a separate customer-to-representative list, not one of the report's four downloads, so it has no Location column - do not fail it for that.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R3, S15-R4, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R3, S15-R4, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -9168,11 +9499,13 @@
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>1. Every customer with an assigned sales representative produces exactly ONE row (single-rep model: one rep per customer).
+          <t xml:space="preserve">1. Every customer with an assigned sales representative produces exactly ONE row (single-rep model: one rep per customer).
 2. Customers with no assigned rep are NOT included.
 3. Rows are sorted by customer name A→Z (primary), then rep name A→Z (secondary).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R5, S15-R7, S15-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R5, S15-R7, S15-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr">
@@ -9217,11 +9550,13 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>1. The staff-ACTIVE / toggle-off rep shows "Rep is active?" = "Yes" — the toggle does not drive this column.
+          <t xml:space="preserve">1. The staff-ACTIVE / toggle-off rep shows "Rep is active?" = "Yes" — the toggle does not drive this column.
 2. The staff-INACTIVE / toggle-on rep shows "Rep is active?" = "No".
 3. The value is always "Yes" or "No" (never "Deactivated" or another word).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R6, S13-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R6, S13-R11).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -9267,12 +9602,14 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>1. The customer still produces a row — the export never silently drops it.
+          <t xml:space="preserve">1. The customer still produces a row — the export never silently drops it.
 2. The "Sales Representative" name comes from the customer-side stored (denormalized) rep name, and "Rep is active?" = "No".
 3. When stored names differ across customers for the same rep (name drift), each customer's row uses its OWN stored name — drift never adds extra rows for a customer and never overwrites one customer's stored name with another's.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R8, S15-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R8, S15-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9319,10 +9656,12 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>1. With zero assigned customers, the CSV downloads with a header row and no data rows, and the dialog shows its empty-export warning: "There is no data to export for the selected report."
+          <t xml:space="preserve">1. With zero assigned customers, the CSV downloads with a header row and no data rows, and the dialog shows its empty-export warning: "There is no data to export for the selected report."
 2. On a generation failure, an error toast reads "An error occurred while exporting the report. Please try again." and auto-fades after 5 seconds.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R11, S15-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R11, S15-N2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9369,13 +9708,15 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>1. The table shows no data rows and the empty-state message "No sales activity matches the current filters."
+          <t xml:space="preserve">1. The table shows no data rows and the empty-state message "No sales activity matches the current filters."
 2. The grand Totals indicator is NOT shown.
 3. The same message appears when no staff member has ever been credited — there is no separate "no reps configured" message; the report is contributor-driven.
 4. Whenever at least one rep row (or the Unassigned row) IS in the result set, the rep list renders and no empty/error message shows.
 5. In the empty state the toolbar — filters, column selector, and the ⋯ exports — stays visible and interactive; widening the range re-fetches and renders the matching reps normally.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R1, S16-R2, S16-R3, S16-N1, S2-N1, S21-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R1, S16-R2, S16-R3, S16-N1, S2-N1, S21-N2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9422,12 +9763,14 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>1. On the initial load and on every filter-triggered re-fetch, the table shows the standard reports loading indicator — a centered spinner over the data area.
+          <t xml:space="preserve">1. On the initial load and on every filter-triggered re-fetch, the table shows the standard reports loading indicator — a centered spinner over the data area.
 2. The grand Totals indicator is hidden during loading.
 3. The toolbar stays interactive so filters can be changed mid-load.
 4. A re-fetch replaces the previous data only when the new data returns — no flash of a blank table beyond the spinner overlay.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9474,11 +9817,13 @@
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
-          <t>1. The data area shows the inline error message "Couldn't load the report. Please try again." with a "Retry" action.
+          <t xml:space="preserve">1. The data area shows the inline error message "Couldn't load the report. Please try again." with a "Retry" action.
 2. The filters and toolbar remain interactive, and the failure does NOT clear the filter selections.
 3. "Retry" re-runs the CURRENT request — the report loads with the same filters still applied.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H178" s="2" t="inlineStr">
@@ -9524,11 +9869,13 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>1. Every toolbar control is visible and operable on touch.
+          <t xml:space="preserve">1. Every toolbar control is visible and operable on touch.
 2. Below 1024px the toolbar controls stack vertically at full width; the ⋯ exports button — the first control of the action cluster — wraps to a partial row ABOVE the stacked controls.
 3. At 1024px and above the desktop layout applies.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R1, S17-R2, S17-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R1, S17-R2, S17-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
@@ -9574,11 +9921,13 @@
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
-          <t>1. The table scrolls horizontally to expose all columns; the pinned Subtotal column stays visible at the right edge throughout.
+          <t xml:space="preserve">1. The table scrolls horizontally to expose all columns; the pinned Subtotal column stays visible at the right edge throughout.
 2. The mobile external totals bar ("Totals" left, grand Subtotal right) sits below the table, OUTSIDE the horizontal scroll container — it does not scroll horizontally and is always fully visible.
 3. The chevron expands/collapses the rep on touch.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R4, S17-R5, S10-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R4, S17-R5, S10-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr">
@@ -9624,10 +9973,12 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>1. Each of these interactive controls presents a touch target of at least 44×44 px.
+          <t xml:space="preserve">1. Each of these interactive controls presents a touch target of at least 44×44 px.
 2. Hover-only tooltips are not shown on touch; the icons communicate the action and each icon-only control carries an accessible name.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R6, S17-N1, S18-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R6, S17-N1, S18-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
@@ -9674,7 +10025,7 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>1. The toolbar has a solid white background and its controls sit clear of the edges rather than pressed up against them; the title's left edge lines up with the leftmost data column, and the rightmost toolbar control (the Location filter) lines its right edge up with the rightmost data column.
+          <t xml:space="preserve">1. The toolbar has a solid white background and its controls sit clear of the edges rather than pressed up against them; the title's left edge lines up with the leftmost data column, and the rightmost toolbar control (the Location filter) lines its right edge up with the rightmost data column.
 2. The data area sits on the standard blue-grey page background and runs edge-to-edge against the side navigation — there is no strip of empty space down either side.
 3. A thin horizontal separator line sits between the toolbar and the column headers.
 4. Column-header cells and all body cells render on white; the pinned Subtotal column matches the row background (not a contrasting strip); the grand Totals indicator renders on the white card surface with a thin top border.
@@ -9682,7 +10033,9 @@
 6. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 7. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the alignment look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this — 32px/24px toolbar padding, 2rem edge padding — are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R1, S18-R2, S18-R3, S18-R4, S18-R5, S18-R7, S18-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R1, S18-R2, S18-R3, S18-R4, S18-R5, S18-R7, S18-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
@@ -9729,12 +10082,14 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>1. The page, toolbar, header, body cells, and the grand Totals indicator switch to their dark equivalents.
+          <t xml:space="preserve">1. The page, toolbar, header, body cells, and the grand Totals indicator switch to their dark equivalents.
 2. Status badges keep the same canonical payment-status color tokens and stay legible in both modes.
 3. Inv. Hrs green/red use the application's positive/negative tokens, mode-appropriate.
 4. PDFs always render in light-mode colors, even when downloaded from dark mode.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
@@ -9780,13 +10135,15 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>1. ⋯ exports = "Report actions".
+          <t xml:space="preserve">1. ⋯ exports = "Report actions".
 2. Column selector = "Show or hide columns".
 3. Per-row chevron = "Expand {rep name}" when collapsed / "Collapse {rep name}" when expanded.
 4. Header chevron = "Expand all reps" / "Collapse all reps".
 5. Dialog X = "Close".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
@@ -9833,11 +10190,13 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>1. The row chevrons and the sortable column headers are keyboard-focusable and activate on Enter and on Space.
+          <t xml:space="preserve">1. The row chevrons and the sortable column headers are keyboard-focusable and activate on Enter and on Space.
 2. A chevron exposes its expanded/collapsed state to assistive technology.
 3. A sortable header exposes its current sort state (unsorted / ascending / descending) to assistive technology.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
@@ -9882,11 +10241,13 @@
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>1. In BOTH light mode and dark mode the subdued-grey (N) count and the "(Inactive)" tag are easy to read against the surface behind them - the smaller text does not fade into the background.
+          <t xml:space="preserve">1. In BOTH light mode and dark mode the subdued-grey (N) count and the "(Inactive)" tag are easy to read against the surface behind them - the smaller text does not fade into the background.
 2. No information is conveyed by color alone: Inv. Hrs carries its +/- sign, status badges carry their text label, and links carry a hover/focus underline.
 3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can read the grey text easily in both modes, and only report it if you cannot. (The design rule behind this is WCAG AA contrast of at least 4.5:1, which the design and engineering team check with a contrast tool - not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R11, S18-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R11, S18-R12).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr">
@@ -9933,15 +10294,15 @@
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>1. The left panel includes a "Sales Representative" selector on the standard Work Order.
+          <t xml:space="preserve">1. The left panel includes a "Sales Representative" selector on the standard Work Order.
 2. The left panel includes the same "Sales Representative" selector on the Part Sale WO.
 3. The selector is NOT present on the imported Work Order.
 4. The selector is NOT present in History mode.
 5. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R1, S19-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R1, S19-N1).
+AUTOMATION: HOLD - waiting on an answer from the product owner
+</t>
         </is>
       </c>
       <c r="H187" s="2" t="inlineStr">
@@ -9987,12 +10348,14 @@
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>1. The toggle-ON staff member is offered as a selectable rep.
+          <t xml:space="preserve">1. The toggle-ON staff member is offered as a selectable rep.
 2. The toggle-OFF staff member is NOT offered as a new selection.
 3. The selector carries the accessible name "Sales Representative".
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R2, S19-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R2, S19-R8).
+AUTOMATION: HOLD - this part of the report is not built yet
+</t>
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr">
@@ -10038,11 +10401,13 @@
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>1. The new Work Order opens with the Sales Representative field UNASSIGNED — it is not pre-filled at creation.
+          <t xml:space="preserve">1. The new Work Order opens with the Sales Representative field UNASSIGNED — it is not pre-filled at creation.
 2. Changing the Sales Representative persists immediately (save-on-change): the selection survives leaving and reopening the WO with no separate Save step.
 3. A new Part Sale WO also opens with the field unassigned.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R3, S19-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R3, S19-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H189" s="2" t="inlineStr">
@@ -10087,12 +10452,14 @@
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>1. On the Invoiced WO the Sales Representative selector is read-only (non-interactive) — the assignment cannot be changed.
+          <t xml:space="preserve">1. On the Invoiced WO the Sales Representative selector is read-only (non-interactive) — the assignment cannot be changed.
 2. On the Paid WO the selector is also read-only.
 3. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 4. Note for the tester: this field is only made read-only on the screen. If you find the sales rep can still be changed another way (through the back-end/API), that is expected — mark this test PASSED and do not raise it as a bug.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H190" s="2" t="inlineStr">
@@ -10138,12 +10505,14 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>1. Invoice (a) is credited to the WO's Sales Representative.
+          <t xml:space="preserve">1. Invoice (a) is credited to the WO's Sales Representative.
 2. Invoice (b) falls back to the CUSTOMER's assigned rep.
 3. Invoice (c) is unassigned — it appears only under the "Unassigned" row.
 4. Changing WO (a)'s Sales Representative afterward does NOT retroactively alter the invoice already created from it — the invoice stays credited to the rep snapshotted at invoice creation.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R6, S19-N2, S22-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R6, S19-N2, S22-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10190,14 +10559,14 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>1. The customer record's left-panel sidebar shows a single row labeled "Sales Representative" (the full word — the product owner explicitly corrected the short-form "Sales Representative" label here) with the customer's assigned rep.
+          <t xml:space="preserve">1. The customer record's left-panel sidebar shows a single row labeled "Sales Representative" (the full word — the product owner explicitly corrected the short-form "Sales Representative" label here) with the customer's assigned rep.
 2. When no rep is assigned, the row renders "Unassigned".
 3. On the WO, the selector renders the bound rep's name with an "(Inactive)" indicator so the current assignment stays visible — but that rep is NOT offered as a new selection in the list.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R7, S19-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R7, S19-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: HOLD - waiting on an answer from the product owner
+</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -10245,11 +10614,13 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>1. Invoice detail rows are NOT delivered with the initial summary payload — the first expand of a rep triggers a server fetch for that rep's matching invoices, with a brief row-level loading indicator.
+          <t xml:space="preserve">1. Invoice detail rows are NOT delivered with the initial summary payload — the first expand of a rep triggers a server fetch for that rep's matching invoices, with a brief row-level loading indicator.
 2. A re-expand within the session does not necessarily re-fetch (the expansion state is session-preserved); no rep's details load before its first expand.
 3. When a rep's matching-invoice count is large, its detail rows are paginated per rep.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
@@ -10295,11 +10666,13 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>1. Each sort change triggers a server re-fetch of the rep summary rows in the requested order (a loading indicator shows during the fetch).
+          <t xml:space="preserve">1. Each sort change triggers a server re-fetch of the rep summary rows in the requested order (a loading indicator shows during the fetch).
 2. The returned rows arrive already ordered by the requested column and direction — the client does not re-sort locally.
 3. Invoice detail rows continue to load lazily per rep on expand, unaffected by the sort mechanism.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -10345,11 +10718,13 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>1. The grand totals arrive WITH the summary payload — the client does not derive them by summing loaded rows.
+          <t xml:space="preserve">1. The grand totals arrive WITH the summary payload — the client does not derive them by summing loaded rows.
 2. The totals cover EVERY matching non-reversed invoice across every rep, independent of which reps are expanded or how many detail rows are loaded.
 3. The on-screen grand Totals match the export's aggregate for the same filter set.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
@@ -10396,11 +10771,13 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>1. Each export is generated by the server, receiving the active filters and sort — the file's contents and order match the screen even for reps never expanded (not built from loaded screen data).
+          <t xml:space="preserve">1. Each export is generated by the server, receiving the active filters and sort — the file's contents and order match the screen even for reps never expanded (not built from loaded screen data).
 2. A genuine server-side export failure produces NO file and shows the "Ooooops! An error occured" toast — never a malformed/partial file.
 3. An empty-but-loaded result still produces a valid file (header-row-only CSV / no-rows PDF).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R2a, S14-N2, S14-E3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R2a, S14-N2, S14-E3).
+AUTOMATION: HOLD - this part of the report is not built yet
+</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
@@ -10447,12 +10824,14 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>1. The server counts the rows against the 10,000-data-row cap and DECLINES to generate — the refusal happens pre-generation, observed in the export response.
+          <t xml:space="preserve">1. The server counts the rows against the 10,000-data-row cap and DECLINES to generate — the refusal happens pre-generation, observed in the export response.
 2. NO file (truncated or otherwise) is delivered; the client shows the specific too-large toast.
 3. A filter set just below the cap still generates a complete (possibly very large) PDF.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E2).
+AUTOMATION: READY - EXPECT FAIL (SV-8818)
+</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10500,11 +10879,13 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>1. A precondition-check request runs FIRST, before any change is applied, returning the count of distinct customers currently assigned to that staff member as their sales representative, plus a flag indicating whether any assignments exist.
+          <t xml:space="preserve">1. A precondition-check request runs FIRST, before any change is applied, returning the count of distinct customers currently assigned to that staff member as their sales representative, plus a flag indicating whether any assignments exist.
 2. The dialog's "{Staff Name} is the sales representative on {N} customer{s}." headline matches the returned count.
 3. No deactivation is committed by the pre-check itself — cancelling leaves the staff member's active status unchanged.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R1, S13-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R1, S13-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
@@ -10551,11 +10932,13 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>1. A Parts section heading exists in the Reports navigation (this feature creates it - the application had no Parts reports before).
+          <t xml:space="preserve">1. A Parts section heading exists in the Reports navigation (this feature creates it - the application had no Parts reports before).
 2. Under Parts there is an entry labeled Parts Velocity; Inventory Value also lives under Parts. The order of the two inside the Parts section is not fixed — do not fail the test on which of them comes first.
 3. Clicking it opens the Parts Velocity report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
@@ -10601,11 +10984,13 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>1. The date range selector shows This Year.
+          <t xml:space="preserve">1. The date range selector shows This Year.
 2. Report data loads automatically - you do not have to press anything to fetch it.
 3. Rows appear ranked by Demand, highest first (the default order).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-R2, S4-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-R2, S4-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
@@ -10652,11 +11037,13 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>1. During the initial load, the table shows a loading indicator.
+          <t xml:space="preserve">1. During the initial load, the table shows a loading indicator.
 2. During a filter change, the loading indicator shows again.
 3. The rows already on screen are replaced only when the new data comes back - the table does not blank out and rebuild mid-request.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10704,11 +11091,13 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>1. The report data loads and rows are shown.
+          <t xml:space="preserve">1. The report data loads and rows are shown.
 2. The export downloads successfully — both opening the report and exporting it are allowed by the same ordinary reports access.
-3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+3. Note for the tester: the specification allows ONE ordinary reports access for all six of these new reports and no per-report permission. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -10753,10 +11142,12 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>1. The user cannot reach the Reports section.
+          <t xml:space="preserve">1. The user cannot reach the Reports section.
 2. The Parts Velocity navigation entry is not shown (this is the Reports section's own access control, not a report-specific rule).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -10803,12 +11194,14 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>1. The Parts Velocity entry is visible in the Reports navigation under Parts.
+          <t xml:space="preserve">1. The Parts Velocity entry is visible in the Reports navigation under Parts.
 2. Opening it shows the report data - not an access-denied screen.
 3. The export downloads.
-4. Note for the tester: for now ONE ordinary reports access opens all six of these new reports, and no report has a permission of its own. If an extra Parts or Inventory reports permission does exist and switching it OFF blocks this report or its export, that is wrong - mark this Failed and report it. If a separate per-report permission is ever added on purpose in a later release, this test will be updated first, so treat that as a planned change and not as a bug.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-N2, S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+4. Note for the tester: the specification allows ONE ordinary reports access for all six of these new reports and no per-report permission. If an extra Parts or Inventory reports permission does exist and switching it OFF blocks this report or its export, that is wrong - mark this Failed and report it. If a separate per-report permission is ever added on purpose in a later release, this test will be updated first, so treat that as a planned change and not as a bug.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-N2, S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -10857,13 +11250,15 @@
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
-          <t>1. The Type filter is the first control in the filter row.
+          <t xml:space="preserve">1. The Type filter is the first control in the filter row.
 2. It is single-select and offers exactly three choices: Both, Inventory, and Special Order (special-order catalog parts that were never put into stock).
 3. On a first visit the default is Both.
 4. Both is an explicit selection returning inventory and Special Order rows together - a deliberate filter value, not the absence of a filter.
 5. Each selection immediately reloads the report limited to that type (no separate Apply step) - under Inventory every row's Type column reads Inventory; under Special Order every row's Type column reads Special Order; under Both, rows of both kinds appear.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R1, S3-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R1, S3-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H205" s="2" t="inlineStr">
@@ -10908,12 +11303,14 @@
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
-          <t>1. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
+          <t xml:space="preserve">1. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
 2. The report always operates over a bounded date window, which is why no All-Time period is offered.
 3. Selecting a non-custom option immediately reloads the report data.
 4. The named ranges use the application's standard shared calendar boundaries (the same boundaries every report's date picker uses).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Parts Velocity report specification version 4 (S2-R2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Parts Velocity report specification version 5 (S2-R2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr">
@@ -10960,12 +11357,14 @@
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>1. A date picker opens requiring both a start and an end date.
+          <t xml:space="preserve">1. A date picker opens requiring both a start and an end date.
 2. The report does not reload until both dates are valid; a start after the end is not accepted.
 3. With both valid dates selected, the data reloads for that range.
 4. A span wider than 366 days (counting both the start and end dates) is rejected - the selection is not applied.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H207" s="2" t="inlineStr">
@@ -11012,12 +11411,14 @@
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>1. Both filters allow selecting more than one value (multi-select).
+          <t xml:space="preserve">1. Both filters allow selecting more than one value (multi-select).
 2. With categories selected, only parts in any of the selected categories are shown.
 3. With vendors selected, only parts supplied by any of the selected vendors are shown.
 4. Each change reloads the data from the server.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R4, S2-R5, S2-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R4, S2-R5, S2-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr">
@@ -11065,12 +11466,14 @@
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>1. The search input is part of the report's toolbar (page-specific), separate from the global search bar.
+          <t xml:space="preserve">1. The search input is part of the report's toolbar (page-specific), separate from the global search bar.
 2. The part-number search matches despite the different letter case (case-insensitive 'contains' match).
 3. The description search returns rows whose description contains the word.
 4. Category and vendor names are NOT searched - use their dedicated filters instead (deliberate, to avoid false matches on common words).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H209" s="2" t="inlineStr">
@@ -11118,11 +11521,13 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>1. After steps 1-2 the part is still listed (it satisfies both filters).
+          <t xml:space="preserve">1. After steps 1-2 the part is still listed (it satisfies both filters).
 2. After step 3 the part disappears - a part must satisfy EVERY active filter to appear (AND logic, not OR).
 3. After step 4 the part is listed again.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -11168,11 +11573,13 @@
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
-          <t>1. Each selection reloads the data from the server.
+          <t xml:space="preserve">1. Each selection reloads the data from the server.
 2. Only inventory parts stocked in ANY of the selected bins are shown.
 3. The filter allows more than one bin (multi-select).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H211" s="2" t="inlineStr">
@@ -11219,10 +11626,12 @@
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
-          <t>1. With any Bin filter active, ALL Special Order rows are excluded (they have no bin location).
+          <t xml:space="preserve">1. With any Bin filter active, ALL Special Order rows are excluded (they have no bin location).
 2. Special Order combined with any Bin filter yields an empty result showing the empty state - this is by design, not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr">
@@ -11271,15 +11680,16 @@
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
-          <t>1. The Location filter is the rightmost control in the filter row and is multi-select.
+          <t xml:space="preserve">1. The Location filter is the rightmost control in the filter row and is multi-select.
 2. On a first visit it defaults to the user's currently active location (the one in the global location switcher).
 3. The list holds the locations the signed-in user has access to, plus an 'All Locations' option.
 4. Each selection reloads the data scoped to the chosen set; 'All Locations' means all locations the user can ACCESS, never beyond - a location the user cannot access is never included.
 5. The location scope cascades through every metric like the other filters.
-6. With 'All Locations' active you can tell which location each row's data belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
-7. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+6. With 'All Locations' active you can tell which location each row's data belongs to — a location label or marking is shown.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H213" s="2" t="inlineStr">
@@ -11324,10 +11734,12 @@
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
-          <t>1. The server returns zero rows and the table shows the empty state.
+          <t xml:space="preserve">1. The server returns zero rows and the table shows the empty state.
 2. The empty-state label reads exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R11, S2-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R11, S2-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H214" s="2" t="inlineStr">
@@ -11375,11 +11787,13 @@
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>1. The part with no category does not appear when any Category filter is active.
+          <t xml:space="preserve">1. The part with no category does not appear when any Category filter is active.
 2. The part with no vendor does not appear when any Vendor filter is active.
 3. The inventory part with no bin location does not appear when any Bin filter is active.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-E1, S2-E2, S2-E3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-E1, S2-E2, S2-E3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H215" s="2" t="inlineStr">
@@ -11425,10 +11839,12 @@
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
+          <t xml:space="preserve">1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-E4). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-E4). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr">
@@ -11478,17 +11894,20 @@
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>1. With more than one location in scope a Location column is shown as the LEFTMOST column, before Type.
+          <t xml:space="preserve">1. With more than one location in scope a Location column is shown as the LEFTMOST column, before Type.
 2. Each inventory row shows its own location's name (an inventory row is one part at one location).
 3. The merged Special Order row shows "Multiple", because it is summed across the selected locations.
-4. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all.
-5. With a single location in scope the Location column is hidden.
-6. Both downloads include the Location column in the same position it holds on screen (leftmost, before Type), with the same values — each inventory row's own location, and "Multiple" on the merged Special Order row.
+4. With a single location in scope the Location column is hidden.
+5. Both downloads include the Location column in the same position it holds on screen (leftmost, before Type), with the same values — each inventory row's own location, and "Multiple" on the merged Special Order row.
 ---
 Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
-DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Parts Velocity report specification version 4 (S2-R12, S3-R10, S7-R8, S6-R11) differs, his decision is the authority.</t>
+The Location column is not one of the columns in the column-selection control and you cannot switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
+Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Parts Velocity report specification version 5 (S2-R12, S3-R10, S7-R8, S6-R11), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H217" s="2" t="inlineStr">
@@ -11534,11 +11953,13 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>1. The part appears as TWO inventory rows - one per selected location (an inventory part is a per-location stock record).
+          <t xml:space="preserve">1. The part appears as TWO inventory rows - one per selected location (an inventory part is a per-location stock record).
 2. Each row carries only that one location's On Hand, Min, and Max.
 3. On Hand / Min / Max are NEVER summed across locations.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R1a).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R1a).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11585,11 +12006,13 @@
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>1. The special-order part appears as a SINGLE row (one row per special-order part, merged across the selected locations).
+          <t xml:space="preserve">1. The special-order part appears as a SINGLE row (one row per special-order part, merged across the selected locations).
 2. Its movement and profitability values are the SUM of the per-location values.
 3. Its inventory-only columns (On Hand, Turns / Yr, Min, Max) show — (em-dash), because special-order parts are not stocked.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R1a).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R1a).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H219" s="2" t="inlineStr">
@@ -11637,12 +12060,14 @@
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
-          <t>1. Rows are ranked by Demand, descending - the most-active parts first.
+          <t xml:space="preserve">1. Rows are ranked by Demand, descending - the most-active parts first.
 2. Inventory and special-order rows are ranked together in one list.
 3. Rows with equal Demand keep inventory-before-special-order order.
 4. The Demand header shows the descending sort indicator - this initial order IS the active sort (it is what the remembered view saves until you click another header).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr">
@@ -11690,12 +12115,14 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>1. The first click sorts that column ASCENDING; the header shows a direction indicator (an arrow).
+          <t xml:space="preserve">1. The first click sorts that column ASCENDING; the header shows a direction indicator (an arrow).
 2. Clicking the active sort column again reverses the direction; the arrow flips.
 3. Null / — values are placed FIRST on ascending and LAST on descending.
 4. Every column is sortable; each header click re-fetches the data (server-resolved) and shows the first page of the re-sorted result; ties keep a stable order.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11741,11 +12168,13 @@
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
-          <t>1. The header row is sticky - it stays visible while the body scrolls.
+          <t xml:space="preserve">1. The header row is sticky - it stays visible while the body scrolls.
 2. The Type column shows each row's kind as plain text (no badge or chip styling): "Inventory" or "Special Order".
 3. ALL columns - header and cell data, including numbers and money - are left-aligned on screen. (The exports right-align numerics instead: a deliberate export-only difference.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R4, S3-R5, S3-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R4, S3-R5, S3-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H222" s="2" t="inlineStr">
@@ -11793,14 +12222,16 @@
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
-          <t>1. Each of the three headers carries a grey info icon, shown always (not hover-to-reveal) whenever its column is visible; the Turns/Yr icon appears only once that column is enabled.
+          <t xml:space="preserve">1. Each of the three headers carries a grey info icon, shown always (not hover-to-reveal) whenever its column is visible; the Turns/Yr icon appears only once that column is enabled.
 2. Units Sold shows exactly: "Units taken out of inventory stock on invoiced work orders in this date range. This is stock movement, so it can differ from the units billed behind Revenue and Sell Price."
 3. Demand shows exactly: "Number of separate transactions (work orders or parts sales) this part appeared on in the selected date range. Each transaction counts once, no matter how many units were sold on it."
 4. Turns/Yr shows exactly: "How many times you sell through this part in a year. Higher is better."
 5. The icon is focusable and exposes the same text to assistive technology; activating it does NOT trigger a column sort.
 6. No other column header carries an info icon.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H223" s="2" t="inlineStr">
@@ -11848,11 +12279,13 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>1. Long Description, Category, and Vendor text is truncated with an ellipsis on screen.
+          <t xml:space="preserve">1. Long Description, Category, and Vendor text is truncated with an ellipsis on screen.
 2. The full value shows on native hover (browser tooltip).
 3. Part # is NEVER truncated - on screen (and in the exports).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -11898,10 +12331,12 @@
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
-          <t>1. On Hand, Turns / Yr, Min, and Max show — (em-dash) on special-order rows - always.
+          <t xml:space="preserve">1. On Hand, Turns / Yr, Min, and Max show — (em-dash) on special-order rows - always.
 2. The count metrics and money totals are NEVER null: Units Sold / Units Returned / Sold (WO) / Sold (Parts Sale) show 0.00, Demand shows 0, Revenue and Margin show $0.00.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R9, S5-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R9, S5-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H225" s="2" t="inlineStr">
@@ -11947,11 +12382,13 @@
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>1. Part A does NOT appear - it fails all three keep-criteria (no movement, under one on hand, no revenue) so it carries nothing to act on.
+          <t xml:space="preserve">1. Part A does NOT appear - it fails all three keep-criteria (no movement, under one on hand, no revenue) so it carries nothing to act on.
 2. Part B DOES appear - a part with billed Revenue &gt; 0 is always kept even with no stock movement and no on-hand stock.
 3. (Special Order parts have no such rule: a never-requested special-order part simply produces no row.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr">
@@ -11997,10 +12434,12 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>1. The picker lists all 20 available columns, each with a toggle: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
+          <t xml:space="preserve">1. The picker lists all 20 available columns, each with a toggle: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
 2. No on-hand cost column is offered - the report computes one internally but it is never selectable and never displayed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-R1, S4-R4, S5-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-R1, S4-R4, S5-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H227" s="2" t="inlineStr">
@@ -12044,13 +12483,15 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>1. With a single location in scope exactly these 14 columns show, in this left-to-right order: Type, Part #, Description, Category, Vendor, Units Sold, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand.
+          <t xml:space="preserve">1. With a single location in scope exactly these 14 columns show, in this left-to-right order: Type, Part #, Description, Category, Vendor, Units Sold, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand.
 2. The other 6 columns start hidden: Units Returned, Sold (WO), Sold (Parts Sale), Turns / Yr, Min, Max.
-3. When more than one location is selected the Location column shows as well, leftmost before Type — 15 columns. It is already switched on for you; you do not have to turn it on, and you can switch it off again. It is not part of the 14-column default set, so its presence is expected and is not a failure of this test.
----
-DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
-This is the expected behaviour as per the Parts Velocity report specification version 4 (S4-R2, S4-R3, S3-R10) for the 14 default columns and the 6 hidden ones. The part about the Location column follows Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; his decision differs from what this case said before, which stated the Location column is not in the column picker, and we have taken his later decision as the one that prevails.</t>
+3. When more than one location is in scope the Location column shows as well, leftmost before Type — 15 columns. It is not one of the columns in the column-selection control and you cannot switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope. It is not part of the 14-column default set, so its presence is expected and is not a failure of this test.
+Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Parts Velocity report specification version 5 (S3-R10), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -12096,11 +12537,13 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>1. Each toggle takes effect immediately - the table re-renders without a page reload.
+          <t xml:space="preserve">1. Each toggle takes effect immediately - the table re-renders without a page reload.
 2. Columns always render in the fixed canonical left-to-right order regardless of the order they were toggled on (with the automatic Location column, when shown, sitting leftmost before Type): Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
 3. So Units Returned slots in right after Units Sold, Turns/Yr after On Hand, and Min before Max - not appended at the end.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-R4, S4-R5, S3-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-R4, S4-R5, S3-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -12146,12 +12589,14 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>1. On return, every saved setting is restored: Type = Inventory, Last Month, the chosen category, the column set including Turns / Yr, and the Revenue-descending sort.
+          <t xml:space="preserve">1. On return, every saved setting is restored: Type = Inventory, Last Month, the chosen category, the column set including Turns / Yr, and the Revenue-descending sort.
 2. The saved values are applied BEFORE the first data fetch - the report does not flash the defaults and then re-query.
 3. The saved values take precedence over the first-visit defaults (This Year / Both / active location / 14 columns / Demand-descending).
 4. The same holds after a full page reload.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-R6, S1-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-R6, S1-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -12196,11 +12641,13 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>1. The invalid saved value is NOT sent to the server.
+          <t xml:space="preserve">1. The invalid saved value is NOT sent to the server.
 2. That one setting falls back to its default (e.g. the location falls back to the active location); the other saved settings still restore normally.
 3. The report loads without an error.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -12246,10 +12693,12 @@
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
-          <t>1. User 2 sees user 1's saved view (Type = Special Order, Last Quarter, the saved columns and sort).
+          <t xml:space="preserve">1. User 2 sees user 1's saved view (Type = Special Order, Last Quarter, the saved columns and sort).
 2. This is by design: storage is per browser, not tied to the account - there is no per-account separation.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H232" s="2" t="inlineStr">
@@ -12295,11 +12744,13 @@
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
-          <t>1. The picker enforces no minimum - all 20 columns can be switched off, leaving a grid with no data columns for the rest of the session.
+          <t xml:space="preserve">1. The picker enforces no minimum - all 20 columns can be switched off, leaving a grid with no data columns for the rest of the session.
 2. The export produces a file containing only the header/metadata rows and no data columns.
 3. On the next visit the all-hidden selection is NOT restored - the report falls back to the default 14-column set (the saved column selection returns to the last NON-EMPTY selection; all-hidden is the exception).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S4-E1, S4-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-E1, S4-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H233" s="2" t="inlineStr">
@@ -12346,12 +12797,14 @@
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
-          <t>1. After step 1, Units Sold increases by 5.00 (invoicing a work order adds the units sold - a stock-movement event).
+          <t xml:space="preserve">1. After step 1, Units Sold increases by 5.00 (invoicing a work order adds the units sold - a stock-movement event).
 2. After step 2, Units Sold decreases by 2.00 (reversing/voiding an invoice adds stock back and is subtracted - Units Sold is net of invoice reversals).
 3. After step 3, Units Sold is UNCHANGED - part returns do not affect Units Sold (they feed Units Returned instead).
 4. Units Sold can be 0.00 or negative when reversals exceed sales.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R1, S5-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R1, S5-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H234" s="2" t="inlineStr">
@@ -12397,11 +12850,13 @@
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
-          <t>1. Units Sold equals the total quantity across the part's in-window vendor requests (3 + 2 = 5.00 in the example), summed across the selected locations.
+          <t xml:space="preserve">1. Units Sold equals the total quantity across the part's in-window vendor requests (3 + 2 = 5.00 in the example), summed across the selected locations.
 2. The reversed/voided sale is EXCLUDED from the total (net of reversals).
 3. Only requests on work orders at status Invoiced or Paid count; the window is anchored to the work-order date.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R2, S5-R4, S5-R4b).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R2, S5-R4, S5-R4b).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H235" s="2" t="inlineStr">
@@ -12449,12 +12904,14 @@
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>1. After step 1, Units Returned increases by 2.00 (the return record is counted when the return is initiated).
+          <t xml:space="preserve">1. After step 1, Units Returned increases by 2.00 (the return record is counted when the return is initiated).
 2. After step 2, it increases by 1.00 more (a parts-sale credit also creates a part-return record).
 3. After step 3, it decreases by 2.00 - the column reflects the CURRENT state of return records (cancelled returns are excluded), not a snapshot.
 4. After step 4, Units Returned is UNCHANGED - invoice reversals are not returns (they affect Units Sold instead).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R3, S5-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R3, S5-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H236" s="2" t="inlineStr">
@@ -12502,13 +12959,15 @@
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>1. The return counts in the window of its INITIATION date - so it appears in the current window even though the sale was earlier (a return and its originating sale can fall in different report windows; each uses its own natural event date).
+          <t xml:space="preserve">1. The return counts in the window of its INITIATION date - so it appears in the current window even though the sale was earlier (a return and its originating sale can fall in different report windows; each uses its own natural event date).
 2. In the previous window the return does not count (only the sale's own metrics do).
 3. Core-charge returns are EXCLUDED from Units Returned.
 4. Units Returned is independent of the work order's current invoice status.
-5. A part whose ONLY in-window event is a return (no sale, no stock, no revenue) produces no row at all - accepted behavior, the row axis is sales/stock activity.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R3).</t>
+5. A part whose ONLY in-window event is a return (no sale, no stock, no revenue) produces no row at all - the rows of this report are built from sales and stock activity, so a return on its own does not create one.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H237" s="2" t="inlineStr">
@@ -12555,12 +13014,14 @@
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>1. Sold (WO) shows the total part quantity on Service-type invoiced/paid work orders whose work-order date is in the window (4.00 in the example), net of reversed/voided sales.
+          <t xml:space="preserve">1. Sold (WO) shows the total part quantity on Service-type invoiced/paid work orders whose work-order date is in the window (4.00 in the example), net of reversed/voided sales.
 2. Sold (Parts Sale) shows the total on Parts-type invoiced/paid work orders (counter sales) in the window (3.00), net of reversed/voided sales.
 3. Both are windowed by the WORK-ORDER date (its end date) - with the range moved off those dates, both drop out.
 4. Both workflows feed the report - a parts sale is a separate workflow from a service work order but counts fully.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr">
@@ -12608,13 +13069,15 @@
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>1. The inventory part's Demand is 2 - each stock-decrementing invoicing event counts ONCE no matter how many units were on it (1 unit and 10 units each count as one).
+          <t xml:space="preserve">1. The inventory part's Demand is 2 - each stock-decrementing invoicing event counts ONCE no matter how many units were on it (1 unit and 10 units each count as one).
 2. After the reversal, Demand is STILL 2 - a reversal event neither adds to nor subtracts from the count (while Units Sold nets down).
 3. The special-order part's Demand is 2 - the count of its in-window vendor part requests.
 4. Demand is the report's default ranking signal (a whole number, never null - 0 when none).
 5. A part whose single in-window sale is invoiced and then fully reversed shows Demand 1 with Units Sold 0.00 — the Demand count is not decremented, while the movement nets to zero.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4, S3-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4, S3-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H239" s="2" t="inlineStr">
@@ -12663,13 +13126,15 @@
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>1. Last Sale shows the whole days between today and the part's most recent sale measured over ALL-TIME history - it IGNORES the selected date range (e.g. '42 days' even though the range is This Month).
+          <t xml:space="preserve">1. Last Sale shows the whole days between today and the part's most recent sale measured over ALL-TIME history - it IGNORES the selected date range (e.g. '42 days' even though the range is This Month).
 2. It IS scoped to the selected location(s): with only location B selected, Last Sale reflects B's own most recent sale.
 3. Format is 'N days' (e.g. 42 days); a part with no recorded sale ever shows —.
 4. For a special-order part, the anchor is its most recent vendor-sourced invoiced/paid request.
 5. When the most recent sale is reversed, Last Sale re-anchors to the previous remaining sale (the day count grows accordingly); if no other sale remains it shows —.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4, S5-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4, S5-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr">
@@ -12715,11 +13180,13 @@
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>1. On Hand equals the part's CURRENT on-hand quantity at that row's location (never summed across locations).
+          <t xml:space="preserve">1. On Hand equals the part's CURRENT on-hand quantity at that row's location (never summed across locations).
 2. Min and Max show the stored minimum / maximum reorder thresholds for that location, as whole numbers (— when not set).
 3. Min and Max are READ-ONLY display columns - no edit control or slide-over opens; editing part attributes from this report is out of scope in this version.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4, S5-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4, S5-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H241" s="2" t="inlineStr">
@@ -12768,12 +13235,14 @@
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>1. Part A's Turns / Yr matches the formula (two decimals, e.g. 24.33); the window is the whole-day span inclusive of both dates with a floor of 1 day.
+          <t xml:space="preserve">1. Part A's Turns / Yr matches the formula (two decimals, e.g. 24.33); the window is the whole-day span inclusive of both dates with a floor of 1 day.
 2. Part B shows 0.00 (renders 0.00 when On Hand is 0 - not an error, not —).
 3. Part C shows a NEGATIVE Turns / Yr with a leading minus (because Units Sold can be negative).
 4. Special Order rows always show — (not applicable).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H242" s="2" t="inlineStr">
@@ -12819,14 +13288,16 @@
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>1. Revenue = the summed billed sell amount (each line's stored sell price × quantity) in the window.
+          <t xml:space="preserve">1. Revenue = the summed billed sell amount (each line's stored sell price × quantity) in the window.
 2. Margin = Revenue − COGS (the summed billed cost captured at billing time).
 3. Unit Cost = COGS ÷ billed units; Sell Price = Revenue ÷ billed units.
 4. Margin % = (Revenue − COGS) ÷ Revenue × 100, shown to one decimal.
 5. All five are computed from the RAW (unrounded) Revenue / COGS / billed-units totals and rounded ONCE at the end - not built from already-rounded intermediates.
 6. The same formulas apply to inventory and special-order rows (for special-order, from the vendor part requests).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4a).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4a).
+AUTOMATION: HOLD - this part of the report is not built yet
+</t>
         </is>
       </c>
       <c r="H243" s="2" t="inlineStr">
@@ -12873,11 +13344,13 @@
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
-          <t>1. After the reversal, ALL the billed-line columns drop to reflect only the remaining sale - the reversed/voided sale is excluded from Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO), Sold (Parts Sale), and (for special-order) Units Sold.
+          <t xml:space="preserve">1. After the reversal, ALL the billed-line columns drop to reflect only the remaining sale - the reversed/voided sale is excluded from Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO), Sold (Parts Sale), and (for special-order) Units Sold.
 2. This netting is consistent with inventory Units Sold, which already nets reversals via the stock add-back.
 3. A voided sale therefore inflates NO column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4b, S5-R4a).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4b, S5-R4a).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H244" s="2" t="inlineStr">
@@ -12925,12 +13398,14 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>1. Row 1: Unit Cost and Sell Price show — (billed units ≤ 0) while Revenue and Margin show dollar amounts AND Margin % is still computed from Revenue - a valid mixed row, not a defect.
+          <t xml:space="preserve">1. Row 1: Unit Cost and Sell Price show — (billed units ≤ 0) while Revenue and Margin show dollar amounts AND Margin % is still computed from Revenue - a valid mixed row, not a defect.
 2. Row 2: Sell Price shows $0.00 (a number) while Margin % shows — (Revenue ≤ 0) - also valid.
 3. Row 3: Unit Cost, Sell Price, and Margin % all show — together - which happens ONLY when both billed units ≤ 0 AND Revenue ≤ 0.
 4. The three triggers are independent: Unit Cost/Sell Price null on billed units ≤ 0; Margin % null on Revenue ≤ 0.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R4a, S3-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4a, S3-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -12975,13 +13450,15 @@
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
-          <t>1. Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), On Hand, Turns / Yr: two decimals with thousands separators (1,250.00); negatives with a leading minus (-3.00).
+          <t xml:space="preserve">1. Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), On Hand, Turns / Yr: two decimals with thousands separators (1,250.00); negatives with a leading minus (-3.00).
 2. Unit Cost, Sell Price, Revenue, Margin: currency with $, two decimals, thousands separators ($1,250.00); negatives with a leading minus and NO parentheses (-$45.00).
 3. Margin %: one decimal with a trailing % (33.8%); negatives with a leading minus, no + on positives (-8.4%).
 4. Demand: whole number. Min, Max: whole numbers (— when null). Last Sale: 'N days' (42 days), — when null.
 5. Rounding is half AWAY from zero: 8.45% displays 8.5% and -8.45% displays -8.5% (a tie rounds up in magnitude); this applies to all money and one-decimal values.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R5, S5-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R5, S5-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr">
@@ -13027,11 +13504,13 @@
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
-          <t>1. The inventory core part does NOT appear in the report despite its activity and stock.
+          <t xml:space="preserve">1. The inventory core part does NOT appear in the report despite its activity and stock.
 2. The special-order core part does NOT appear either.
 3. Parts flagged as a core are excluded from both result sets by design.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R1, S5-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R1, S5-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H247" s="2" t="inlineStr">
@@ -13079,11 +13558,13 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>1. On the inventory row, Units Sold (stock movement) DIFFERS from the billed units behind Revenue/Sell Price - this is CORRECT behavior, not a defect (the Units Sold tooltip calls it out).
+          <t xml:space="preserve">1. On the inventory row, Units Sold (stock movement) DIFFERS from the billed units behind Revenue/Sell Price - this is CORRECT behavior, not a defect (the Units Sold tooltip calls it out).
 2. Sold (WO) + Sold (Parts Sale) together DO equal the billed-units basis (work orders are only Service- or Parts-type) - but neither equals the movement-based Units Sold.
 3. On the special-order row, everything reconciles: Units Sold = Sold (WO) + Sold (Parts Sale) = billed units (they share the vendor-request quantity as one source).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -13130,12 +13611,14 @@
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
-          <t>1. In W1 (work-order date in window): the billed columns (Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO), Sold (Parts Sale)) count the sale, while inventory Units Sold / Demand do NOT (their movement event is outside W1).
+          <t xml:space="preserve">1. In W1 (work-order date in window): the billed columns (Revenue, Margin, Unit Cost, Sell Price, Margin %, Sold (WO), Sold (Parts Sale)) count the sale, while inventory Units Sold / Demand do NOT (their movement event is outside W1).
 2. In W2 (movement date in window): Units Sold / Demand count it, the billed columns do not - the two anchors CAN differ for an inventory part and that is intended.
 3. The window is the whole-day span inclusive of BOTH the start and end dates, with a floor of 1 day - a single-day range (Today) computes normally (Window = 1 for the Turns / Yr divisor).
 4. Last Sale is not windowed at all (all-time).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H249" s="2" t="inlineStr">
@@ -13185,12 +13668,14 @@
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
-          <t>1. Units Sold reads exactly 2.50 — not 2.00, not 3.00, not blank and not a dash.
+          <t xml:space="preserve">1. Units Sold reads exactly 2.50 — not 2.00, not 3.00, not blank and not a dash.
 2. It still reads exactly 2.50 after the sign-out and sign-back-in, which proves the part-of-a-unit quantity was really stored and not just shown once.
 3. On Hand has gone down by exactly 2.50 from what it was before the sale.
 4. No value anywhere on the row has been quietly rounded to a whole number.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S5-R1, S5-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R1, S5-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H250" s="2" t="inlineStr">
@@ -13235,10 +13720,12 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>1. The ⋯ overflow button sits leftmost in the toolbar's action cluster.
+          <t xml:space="preserve">1. The ⋯ overflow button sits leftmost in the toolbar's action cluster.
 2. The menu holds exactly two items, in this order: Download (PDF), then Download (CSV).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -13284,11 +13771,13 @@
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
-          <t>1. Both files contain only the rows matching the date range, type, category, vendor, bin, location, and search active at export time - not a full unfiltered dump.
+          <t xml:space="preserve">1. Both files contain only the rows matching the date range, type, category, vendor, bin, location, and search active at export time - not a full unfiltered dump.
 2. The exported rows match what the on-screen grid was showing.
-3. Each file (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R2, S6-R11); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+3. Each file (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R2, S6-R11); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H252" s="2" t="inlineStr">
@@ -13334,11 +13823,13 @@
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
-          <t>1. Both exports contain ONLY the currently enabled columns - the hidden ones are absent.
+          <t xml:space="preserve">1. Both exports contain ONLY the currently enabled columns - the hidden ones are absent.
 2. Columns appear in the CANONICAL order (the fixed on-screen order) - the re-enabled Units Returned sits right after Units Sold, NOT appended at the end.
 3. The export mirrors the visible grid.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R3, S4-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R3, S4-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H253" s="2" t="inlineStr">
@@ -13385,11 +13876,13 @@
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
-          <t>1. The default Demand-descending order is exported when the user has not chosen another column.
+          <t xml:space="preserve">1. The default Demand-descending order is exported when the user has not chosen another column.
 2. Every column's sort is honored in the export - including Min and Max.
 3. The export renders the EXACT server order, including null placement (nulls first on ascending, last on descending) - the export and the on-screen grid match; there is no on-screen-vs-export null-sorting difference.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R4, S3-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R4, S3-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H254" s="2" t="inlineStr">
@@ -13435,14 +13928,16 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>1. The file downloads as velocity-report.pdf.
+          <t xml:space="preserve">1. The file downloads as velocity-report.pdf.
 2. The PDF is formatted for A3 landscape and titled Parts Velocity.
 3. Description, Category, and Vendor are truncated to 18 characters in the PDF.
 4. Part # is NOT truncated.
 5. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space. The CSV never includes a logo.
 Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Parts Velocity report specification version 4 (S6-R5, S6-R6) differs, his decision is the authority.</t>
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Parts Velocity report specification version 5 (S6-R5, S6-R6) differs, his decision is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -13488,11 +13983,13 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>1. The file downloads as velocity-report.csv.
+          <t xml:space="preserve">1. The file downloads as velocity-report.csv.
 2. The CSV carries the FULL, untruncated Description / Category / Vendor values (unlike the PDF's 18-character cut).
 3. Last Sale is a raw integer in the CSV (e.g. 42) - the 'N days' wording is PDF/on-screen only.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R5, S6-R6, S6-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R5, S6-R6, S6-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -13538,10 +14035,12 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>1. A null value renders as — (em-dash) in BOTH the CSV and the PDF, in every nullable field: Unit Cost, Sell Price, Margin %, On Hand, Turns / Yr, Last Sale, Min, Max.
+          <t xml:space="preserve">1. A null value renders as — (em-dash) in BOTH the CSV and the PDF, in every nullable field: Unit Cost, Sell Price, Margin %, On Hand, Turns / Yr, Last Sale, Min, Max.
 2. Revenue, Margin, and the count metrics are never null in the exports either ($0.00 / 0.00 / 0).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R7, S6-R8, S3-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R7, S6-R8, S3-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -13586,13 +14085,15 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>1. In the PDF, the Type column is CENTERED.
+          <t xml:space="preserve">1. In the PDF, the Type column is CENTERED.
 2. In the PDF, the text columns (Part #, Description, Category, Vendor) are left-aligned.
 3. In the PDF, EVERY numeric and money column is right-aligned.
 4. This is a deliberate export-only treatment - the on-screen table is all-left-aligned; the difference is documented, not a defect.
 5. The CSV is plain data — the alignment assertions apply to the PDF only; how a spreadsheet displays the CSV is not part of this test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R10, S3-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R10, S3-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -13639,11 +14140,13 @@
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
-          <t>1. On success the toasts read exactly "Velocity report exported (CSV)" / "Velocity report exported (PDF)" and auto-fade — UPPERCASE (CSV)/(PDF).
+          <t xml:space="preserve">1. On success the toasts read exactly "Velocity report exported (CSV)" / "Velocity report exported (PDF)" and auto-fade — UPPERCASE (CSV)/(PDF).
 2. An error toast is shown on failure; when the server provides a message, that server message is shown.
-3. Otherwise the failure toast reads exactly: "Failed to export velocity report (csv)" or "Failed to export velocity report (pdf)" — lowercase (csv)/(pdf); the success/failure casing mix is the shipped wording, documented as-is (not a bug).
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S6-R9, S6-N1).</t>
+3. Otherwise the failure toast reads exactly: "Failed to export velocity report (csv)" or "Failed to export velocity report (pdf)" — lowercase (csv)/(pdf); the success/failure casing mix is the specified wording (not a bug).
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R9, S6-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H259" s="2" t="inlineStr">
@@ -13691,12 +14194,14 @@
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
-          <t>1. Neither the CSV nor the PDF is produced — no download starts.
+          <t xml:space="preserve">1. Neither the CSV nor the PDF is produced — no download starts.
 2. A clear too-large message appears telling the user to narrow the date range or filters, then try again — the standard wording is "This report is too large to export. Narrow the date range or filters, then try again."
 3. After narrowing below the cap, the downloads work again.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (Story 6 exports).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (Story 6 exports).
+AUTOMATION: READY - EXPECT FAIL (SV-8818)
+</t>
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr">
@@ -13744,13 +14249,15 @@
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
-          <t>1. The CSV downloads successfully at that size.
+          <t xml:space="preserve">1. The CSV downloads successfully at that size.
 2. The PDF also downloads successfully. If instead nothing downloads and a message appears saying something went wrong, that is a failure — record roughly how many rows were on screen.
 3. The small PDF downloads successfully, which shows the failure depends on size.
 4. Note for the tester: a very large view is refused politely with "This report is too large to export. Narrow the date range or filters, then try again." — that message is expected and is NOT this failure. This test is about a medium-sized view where the CSV works but the PDF errors.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (Story 6 exports).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (Story 6 exports).
+AUTOMATION: READY - EXPECT FAIL (SV-8818)
+</t>
         </is>
       </c>
       <c r="H261" s="2" t="inlineStr">
@@ -13795,11 +14302,13 @@
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
-          <t>1. White card surfaces (toolbar + table cells) sit on the standard soft blue-grey page background (the application's two-tone report theme).
+          <t xml:space="preserve">1. White card surfaces (toolbar + table cells) sit on the standard soft blue-grey page background (the application's two-tone report theme).
 2. There is NO card border-radius - the table runs edge to edge.
 3. The layout matches the application's other reports.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S7-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S7-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr">
@@ -13846,13 +14355,15 @@
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
-          <t>1. The toolbar strip is white (dark in dark mode), and its controls sit clear of the edges rather than pressed up against them.
+          <t xml:space="preserve">1. The toolbar strip is white (dark in dark mode), and its controls sit clear of the edges rather than pressed up against them.
 2. There is a thin dividing line between the toolbar and the column-header band, and the header band and the data cells are white.
 3. The first and last columns sit clear of the left and right edges of the table - the text is not touching the edge.
 4. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 5. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this - 32px/24px toolbar padding, a 1px header border, 2rem edge padding - are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S7-R2, S7-R3, S7-R4, S7-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S7-R2, S7-R3, S7-R4, S7-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H263" s="2" t="inlineStr">
@@ -13898,11 +14409,13 @@
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
-          <t>1. The report supports dark mode: page background, toolbar, and cells use their dark-mode equivalents.
+          <t xml:space="preserve">1. The report supports dark mode: page background, toolbar, and cells use their dark-mode equivalents.
 2. In BOTH light mode and dark mode the grey ⓘ info icon is clearly visible against the cell behind it - you can see it at a glance without leaning in, and it does not disappear into the background.
 3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes. Only report it if the icon is hard to see. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S7-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S7-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H264" s="2" t="inlineStr">
@@ -13949,11 +14462,13 @@
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
-          <t>1. The backend returns ONE page of rows at a time - the full result set is not shipped to the browser.
+          <t xml:space="preserve">1. The backend returns ONE page of rows at a time - the full result set is not shipped to the browser.
 2. Paging is resolved on the server: moving to another page issues a fresh backend request for that page.
 3. This keeps the report responsive at scale (organizations can carry 50-60k parts, multiplied across locations).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H265" s="2" t="inlineStr">
@@ -13999,11 +14514,13 @@
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
-          <t>1. EACH change (Type, date range, Bin, Location, Category, Vendor, search) triggers a fresh server-side data load.
+          <t xml:space="preserve">1. EACH change (Type, date range, Bin, Location, Category, Vendor, search) triggers a fresh server-side data load.
 2. There is no client-side-only narrowing - every filter or search change re-queries the server.
 3. Each change returns the FIRST page of the new result set.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S2-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H266" s="2" t="inlineStr">
@@ -14050,11 +14567,13 @@
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
-          <t>1. Each header click re-fetches the data from the server, ordered by the chosen column and direction, returning the first page of the re-sorted result set.
+          <t xml:space="preserve">1. Each header click re-fetches the data from the server, ordered by the chosen column and direction, returning the first page of the re-sorted result set.
 2. Null values are placed FIRST on ascending and LAST on descending - as a server sort semantic, so the same order appears on screen and in the exports.
 3. Ties keep a stable order (no explicit secondary key).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S3-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H267" s="2" t="inlineStr">
@@ -14101,12 +14620,14 @@
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
-          <t>1. The back end returns the report data - the request is not refused.
+          <t xml:space="preserve">1. The back end returns the report data - the request is not refused.
 2. The back end returns the export file - the request is not refused.
 3. Both requests succeed with only the ordinary reports access turned on - nothing else had to be enabled.
-4. Note for the tester: if the back end refuses either request for a user who has the ordinary reports access, mark this Failed and report it. If an extra Parts or Inventory reports permission exists in the system it must not change these results - for now it is hidden from the screen and enforces nothing. A per-report permission added on purpose in a later release is a planned change, not a bug, and this test will be updated first.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 4 (S1-R4, S1-N2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+4. Note for the tester: if the back end refuses either request for a user who has the ordinary reports access, mark this Failed and report it. If an extra Parts or Inventory reports permission exists in the system it must not change these results - the specification allows no per-report permission at all. A per-report permission added on purpose in a later release is a planned change, not a bug, and this test will be updated first.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-R4, S1-N2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr">
@@ -14157,12 +14678,14 @@
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
-          <t>1. The QuickBooks amount is exactly the hand-worked figure to the cent — $25.00 for 2.5 at $10.00.
+          <t xml:space="preserve">1. The QuickBooks amount is exactly the hand-worked figure to the cent — $25.00 for 2.5 at $10.00.
 2. It is NOT a whole-unit amount such as $20.00 or $30.00, and it is NOT a bigger, multiplied figure.
 3. The quantity behind the QuickBooks amount matches the Units Sold value on the report (2.50) — the two systems agree.
 4. No second or correcting journal entry is created to patch up a wrong amount.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and this point is not covered by any of the six report specifications — it comes from the engineering technical plan.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and this point is not covered by any of the six report specifications — it comes from the engineering technical plan.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H269" s="2" t="inlineStr">
@@ -14209,11 +14732,13 @@
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
-          <t>1. The report is listed under the Performance group, labeled "Technician Utilization".
+          <t xml:space="preserve">1. The report is listed under the Performance group, labeled "Technician Utilization".
 2. Clicking it opens the report.
 3. The entry sits BELOW the pre-existing report links — Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency — the new reports are added below those items without moving or disturbing them.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H270" s="2" t="inlineStr">
@@ -14259,10 +14784,12 @@
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
-          <t>1. Technician A has exactly ONE row.
+          <t xml:space="preserve">1. Technician A has exactly ONE row.
 2. Technician B has NO row - only technicians with clocked time in the selected range at the selected location(s) appear.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H271" s="2" t="inlineStr">
@@ -14307,11 +14834,13 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>1. The date range defaults to the current calendar month (the date picker's "This Month" preset).
+          <t xml:space="preserve">1. The date range defaults to the current calendar month (the date picker's "This Month" preset).
 2. Because a range never extends past now, the current-month default effectively shows the month to date.
 3. The location filter defaults to the user's currently active location (the one in the application's global location switcher).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R3, S1-R6, S9-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R3, S1-R6, S9-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -14357,11 +14886,13 @@
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
-          <t>1. Each range change reloads the report's rows for the new range.
+          <t xml:space="preserve">1. Each range change reloads the report's rows for the new range.
 2. A valid Custom range applies normally.
 3. A Custom span wider than 366 days (matching the largest preset) is rejected - it cannot be applied.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R4, S1-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R4, S1-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H273" s="2" t="inlineStr">
@@ -14407,11 +14938,13 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>1. On the initial load and on every reload (date-range or location change), the data area shows the standard reports loading indicator.
+          <t xml:space="preserve">1. On the initial load and on every reload (date-range or location change), the data area shows the standard reports loading indicator.
 2. The existing rows are replaced only when the new data returns.
 3. The toolbar remains interactive during the load.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
@@ -14459,12 +14992,14 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>1. A record that crosses midnight is split by day - each day counts only its own hours; the midnight split is evaluated in the active workplace's time zone.
+          <t xml:space="preserve">1. A record that crosses midnight is split by day - each day counts only its own hours; the midnight split is evaluated in the active workplace's time zone.
 2. A record that starts before the range (or ends after it) counts only the part inside the range.
 3. EVERY record is day-grouped and windowed in a SINGLE report-level time zone - the active workplace's - regardless of the location where it was clocked (a record's day, the current-month boundary, and the midnight split all use that one zone).
 4. This matches the Timesheet Activities report's single-time-zone grouping.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
@@ -14509,9 +15044,11 @@
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
-          <t>1. The Technician Utilization report does NOT appear in the navigation.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+          <t xml:space="preserve">1. The Technician Utilization report does NOT appear in the navigation.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr">
@@ -14558,11 +15095,13 @@
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
-          <t>1. Instead of rows, the data area shows exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).
+          <t xml:space="preserve">1. Instead of rows, the data area shows exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).
 2. The Summary row is hidden.
 3. Clearing every technician shows the SAME message and hides the Summary row — this version does not use distinct copy for genuinely-no-data vs a cleared filter.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-N2, S3-N1, S5-N1, S9-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-N2, S3-N1, S5-N1, S9-N2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H277" s="2" t="inlineStr">
@@ -14610,15 +15149,21 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>1. With a single location in scope the headers appear in exactly this order: Technician, Total Hours, WO Hours, Internal Hours, Utilization %, Est. Lost Labor.
+          <t xml:space="preserve">1. With a single location in scope the headers appear in exactly this order: Technician, Total Hours, WO Hours, Internal Hours, Utilization %, Est. Lost Labor.
 2. Total Hours = all time the technician was clocked in for the range.
 3. WO Hours = time clocked directly to work orders; Internal Hours = time clocked to internal, non-billable activities.
 4. Internal Hours includes ALL internal time - including hours at a location with no configured labor rate.
 5. Hours show two decimal places with NO thousands separator (e.g. "107.70"), rounded from the unrounded hours using round-half-up (a tie rounds away from zero - 0.005 → 0.01).
-6. When more than one location is in scope the Location column also appears, leftmost before Technician. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all.
+6. When more than one location is in scope the Location column also appears, leftmost before Technician.
 ---
 Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Technician Utilization report specification version 5 (S2-R1, S2-R2, S2-R3, S2-R4, S2-R5, S9-R9) differs, his decision is the authority.</t>
+The Location column is never listed in the column-selection control and you cannot switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
+Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Technician Utilization report specification version 5 (S2-R1, S2-R2, S2-R3, S2-R4, S2-R5, S9-R9), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -14663,10 +15208,12 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>1. Utilization % = work-order hours as a percentage of total clocked hours, computed from the unrounded hours (not from the already-rounded displays).
+          <t xml:space="preserve">1. Utilization % = work-order hours as a percentage of total clocked hours, computed from the unrounded hours (not from the already-rounded displays).
 2. It shows one decimal place followed by a percent sign, rounded round-half-up (66.65% → 66.7%).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R6, S2-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R6, S2-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
@@ -14712,11 +15259,13 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>1. The internal-only technician shows "0.0%".
+          <t xml:space="preserve">1. The internal-only technician shows "0.0%".
 2. No row shows more than 100% - work-order hours are always part of total clocked hours.
 3. The "—" (undefined, total = 0) state is unreachable on a rendered technician or day row, because only technicians with clocked time get rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E1, S2-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E1, S2-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
@@ -14764,11 +15313,13 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>1. Est. Lost Labor = the sum, per contributing location, of that location's default labor rate × the technician's internal hours clocked there - summed at full precision, with the technician's total rounded ONCE (round-half-up).
+          <t xml:space="preserve">1. Est. Lost Labor = the sum, per contributing location, of that location's default labor rate × the technician's internal hours clocked there - summed at full precision, with the technician's total rounded ONCE (round-half-up).
 2. In a single-location view it is simply that one location's rate × the technician's internal hours.
 3. The value shows as dollars with two decimals and commas between thousands (e.g. "$1,234.50").
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R8, S2-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R8, S2-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
@@ -14816,12 +15367,14 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>1. While Est. Lost Labor is shown, the column is pinned to the far right; its cells are bold and its header is bold, matching.
+          <t xml:space="preserve">1. While Est. Lost Labor is shown, the column is pinned to the far right; its cells are bold and its header is bold, matching.
 2. The information icon shows exactly: "Internal hours valued at each location's default labor rate" — on hover, on keyboard focus, and on tap; it is dismissible.
 3. NO column header other than Est. Lost Labor shows the information icon.
 4. Est. Lost Labor can be turned OFF in the Column Selection control; when it is off the column, its bold styling and its information icon are all absent, and the report still works normally.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R10, S2-R11, S8-R4, S8-R6, S8-R7, S8-N1, S10-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R10, S2-R11, S8-R4, S8-R6, S8-R7, S8-N1, S10-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14867,11 +15420,13 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>1. Technician A shows "$0.00" - there is nothing to value, regardless of whether the location has a rate configured.
+          <t xml:space="preserve">1. Technician A shows "$0.00" - there is nothing to value, regardless of whether the location has a rate configured.
 2. Technician B also shows "$0.00" - a configured rate of exactly $0.00 is a KNOWN rate that values the hours at $0.00, not "—".
 3. "$0.00" means 'the rate is known and there is nothing (or $0) to value' - a different state from "—" ('the rate is unknown').
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -14917,11 +15472,13 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>1. Est. Lost Labor shows "—" (an em-dash), NOT "$0.00" - the rate is unknown, so the value cannot be computed.
+          <t xml:space="preserve">1. Est. Lost Labor shows "—" (an em-dash), NOT "$0.00" - the rate is unknown, so the value cannot be computed.
 2. The "—" cell carries the assistive-technology label "No default labor rate configured" (distinguishing it from "$0.00", which reads as its dollar value).
 3. The technician's Internal Hours column still shows all the internal hours (they are counted even though they cannot be valued).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E3, S8-R11, S2-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E3, S8-R11, S2-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -14967,11 +15524,13 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>1. Est. Lost Labor is the sum of the valued (rated-location) portions only - the unrated-location hours are excluded from the dollar amount.
+          <t xml:space="preserve">1. Est. Lost Labor is the sum of the valued (rated-location) portions only - the unrated-location hours are excluded from the dollar amount.
 2. The amount shows as a normal "$X.XX" with NO partial-value indicator in this version - so the row's Est. Lost Labor values fewer hours than its Internal Hours column shows.
 3. This is a documented known limitation (a partial-value indicator is a possible follow-up) - expected behavior, not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -15018,11 +15577,13 @@
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
-          <t>1. The technician rows are sorted by Technician name, A to Z.
+          <t xml:space="preserve">1. The technician rows are sorted by Technician name, A to Z.
 2. The Technician header shows the ascending sort indicator.
 3. The active sort header exposes its state to assistive technology (aria-sort = ascending on the Technician header; none on the others).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R12, S8-R8, S8-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R12, S8-R8, S8-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr">
@@ -15070,13 +15631,15 @@
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
-          <t>1. Because Technician-ascending is the active sort on load, the FIRST click on the Technician header sorts it DESCENDING (Z to A).
+          <t xml:space="preserve">1. Because Technician-ascending is the active sort on load, the FIRST click on the Technician header sorts it DESCENDING (Z to A).
 2. Clicking a column that is not the active sort sorts it ascending; clicking the active column again toggles to descending; further clicks only ever toggle ascending↔descending - there is NO third 'cleared' state.
 3. All six columns are sortable.
 4. Sorting is applied on screen to the loaded rows - NO reload/server request happens.
 5. Technicians tied in the sorted column are ordered by Technician name A to Z; two technicians sharing the same display name keep a stable order between renders.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R13, S2-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R13, S2-R14).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H287" s="2" t="inlineStr">
@@ -15122,10 +15685,12 @@
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
-          <t>1. After the reload, the rows are back to Technician name A to Z (the sort reset).
+          <t xml:space="preserve">1. After the reload, the rows are back to Technician name A to Z (the sort reset).
 2. On the return visit, the sort is again Technician A to Z - sort is NOT persisted (unlike the date range, technician selection, and location selection, which are).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R15).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R15).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H288" s="2" t="inlineStr">
@@ -15171,11 +15736,13 @@
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
-          <t>1. Only the technician rows reorder.
+          <t xml:space="preserve">1. Only the technician rows reorder.
 2. The Summary row stays pinned at the bottom.
 3. Each technician's expanded day rows stay under that technician, still in date order (earliest to latest) - they do not re-sort by the clicked column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R16).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R16).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H289" s="2" t="inlineStr">
@@ -15221,11 +15788,13 @@
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
-          <t>1. Rows whose Est. Lost Labor is "—" sort to the BOTTOM in BOTH ascending and descending order - they are never floated to the top by reversing direction.
+          <t xml:space="preserve">1. Rows whose Est. Lost Labor is "—" sort to the BOTTOM in BOTH ascending and descending order - they are never floated to the top by reversing direction.
 2. Among themselves, the "—" rows are ordered by Technician name A to Z.
 3. A "$0.00" value is a number, not "—" - it sorts as zero (lowest ascending, above only the — group).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R17).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R17).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr">
@@ -15271,12 +15840,14 @@
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
-          <t>1. A Summary row is pinned to the bottom of the report, labeled "Summary".
+          <t xml:space="preserve">1. A Summary row is pinned to the bottom of the report, labeled "Summary".
 2. It stays visible at the bottom while the rows scroll.
 3. It uses the same number formats as the technician rows.
 4. Its values carry NO label prefix such as "TOTAL:" or "AVG:".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R1, S3-R2, S3-R6, S3-R7, S8-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R1, S3-R2, S3-R6, S3-R7, S8-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H291" s="2" t="inlineStr">
@@ -15322,11 +15893,13 @@
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
-          <t>1. Each Summary hours value is the total of that column across the VISIBLE technicians, computed from unrounded hours and rounded once for display (round-half-up).
+          <t xml:space="preserve">1. Each Summary hours value is the total of that column across the VISIBLE technicians, computed from unrounded hours and rounded once for display (round-half-up).
 2. Eye-summing the displayed rows MAY differ from the displayed Summary by 0.01 — one unit in the last decimal (these values are HOURS, not money) — expected in a compute-from-unrounded report, not a defect.
 3. With every technician selected, the Summary row equals the shop totals for the full date range at the selected location(s).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R3, S5-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R3, S5-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H292" s="2" t="inlineStr">
@@ -15372,10 +15945,12 @@
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
-          <t>1. The Summary Utilization % shows the WEIGHTED rate - the visible technicians' total work-order hours as a percentage of their total clocked hours, from unrounded hours (10.0% in the example).
+          <t xml:space="preserve">1. The Summary Utilization % shows the WEIGHTED rate - the visible technicians' total work-order hours as a percentage of their total clocked hours, from unrounded hours (10.0% in the example).
 2. It is NOT the average of the per-technician percentages (not 50.0%).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H293" s="2" t="inlineStr">
@@ -15420,11 +15995,13 @@
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
-          <t>1. The Summary Est. Lost Labor is computed like a row but over all visible technicians' internal hours: rate × internal hours per contributing rated location, summed at full precision and rounded once.
+          <t xml:space="preserve">1. The Summary Est. Lost Labor is computed like a row but over all visible technicians' internal hours: rate × internal hours per contributing rated location, summed at full precision and rounded once.
 2. A visible technician whose value is "—" contributes NOTHING to the sum - so the Summary understates true lost labor whenever any visible technician is "—" or partially valued (documented, expected).
 3. The Summary shows "—" only when EVERY visible technician's Est. Lost Labor is "—".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S3-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H294" s="2" t="inlineStr">
@@ -15471,11 +16048,13 @@
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
-          <t>1. Each technician row has a control to expand and collapse it.
+          <t xml:space="preserve">1. Each technician row has a control to expand and collapse it.
 2. Its accessible name reflects the NEXT action, scoped to that technician: when collapsed it reads Expand, then that technician's name, then daily breakdown (for example: Expand John Smith's daily breakdown); when expanded it reads Collapse, then the same name and words.
 3. The control is keyboard-focusable, toggles on Enter and Space, and exposes its expanded/collapsed state to assistive technology.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R1, S8-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R1, S8-R12).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H295" s="2" t="inlineStr">
@@ -15523,13 +16102,15 @@
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
-          <t>1. One row appears for each day the technician clocked time in the range, in date order from earliest to latest.
+          <t xml:space="preserve">1. One row appears for each day the technician clocked time in the range, in date order from earliest to latest.
 2. The day rows are not there until you expand the row - they arrive at the moment you expand it (you may briefly see the standard loading indicator in that area), and the rest of the report does not reload.
 3. A day with no clocked time has NO row.
 4. With several locations selected, a day's row POOLS that day's hours across the selected locations - one day row per date, not one per location.
 5. Note for the tester: you do not need developer tools for this test - just watch the screen.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R2, S4-N1, S9-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R2, S4-N1, S9-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H296" s="2" t="inlineStr">
@@ -15575,11 +16156,13 @@
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
-          <t>1. Each day row shows the same columns, in the same formats, as the technician row - with that day's values.
+          <t xml:space="preserve">1. Each day row shows the same columns, in the same formats, as the technician row - with that day's values.
 2. The day's Est. Lost Labor is valued per location exactly like a technician row (that location's default labor rate × that day's internal hours there).
 3. Hours 2dp / Utilization one decimal + % / dollars with commas - all identical to the row formats, computed from unrounded values and rounded once.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R3, S2-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R3, S2-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H297" s="2" t="inlineStr">
@@ -15627,12 +16210,14 @@
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
-          <t>1. The control lives in the table's header row (Technician column) - NOT in the toolbar action cluster.
+          <t xml:space="preserve">1. The control lives in the table's header row (Technician column) - NOT in the toolbar action cluster.
 2. If ANY row is collapsed, activating it expands ALL rows; only when EVERY row is already expanded does it collapse all rows (so step 3's activation re-expands the one collapsed row).
 3. Its accessible name reflects the next action: "Expand all technicians" when it will expand, "Collapse all technicians" when every row is already expanded.
 4. It is keyboard-focusable, toggles on Enter/Space, and exposes its state to assistive technology.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R4, S8-R12, S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R4, S8-R12, S8-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H298" s="2" t="inlineStr">
@@ -15678,11 +16263,13 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>1. After the reload (date-range or location change), all rows are collapsed - expansion state resets.
+          <t xml:space="preserve">1. After the reload (date-range or location change), all rows are collapsed - expansion state resets.
 2. On a fresh visit, all rows start collapsed - expansion is never persisted.
 3. Deselecting and re-selecting a technician (an on-screen operation) does NOT change the expansion state of the other rows - the expanded row stays expanded.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -15728,11 +16315,13 @@
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
-          <t>1. The toolbar has a filter labeled "Technician" that allows selecting more than one technician (when several are chosen its label reads, for example, "2 technicians").
+          <t xml:space="preserve">1. The toolbar has a filter labeled "Technician" that allows selecting more than one technician (when several are chosen its label reads, for example, "2 technicians").
 2. On the first visit, EVERY technician is selected.
 3. All technicians' rows are shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R1, S5-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R1, S5-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H300" s="2" t="inlineStr">
@@ -15779,13 +16368,15 @@
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
-          <t>1. The deselected technician's row is hidden.
+          <t xml:space="preserve">1. The deselected technician's row is hidden.
 2. The Summary row recalculates over the technicians that remain visible.
 3. The report does NOT reload - the technician filter works on screen only: the rows and the Summary update straight away, no loading indicator appears in the data area, and the date range does not change.
 4. Re-selecting the technician shows the row again (and the Summary recalculates back).
 5. Note for the tester: you do not need developer tools for this test - just watch the screen.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R3, S5-R4, S5-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R3, S5-R4, S5-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H301" s="2" t="inlineStr">
@@ -15832,12 +16423,14 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>1. "Clear all" sets every currently-listed technician to deselected; "All technicians" selects all technicians at once.
+          <t xml:space="preserve">1. "Clear all" sets every currently-listed technician to deselected; "All technicians" selects all technicians at once.
 2. Selection is tracked as the set of DESELECTED technicians: a technician you have not deselected is selected by default.
 3. After step 3, your deselected technician STAYS deselected across the range change, while the newly-appearing technician is SELECTED (never explicitly deselected).
 4. After step 4, the newly-appearing technician is selected even though you had cleared all - "Clear all" only deselected the technicians listed at the time.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R6, S5-R7, S5-R8, S5-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R6, S5-R7, S5-R8, S5-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -15883,11 +16476,13 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>1. The two deselected technicians are STILL deselected on return - the deselected set is what persists (saved in this browser, not on the account).
+          <t xml:space="preserve">1. The two deselected technicians are STILL deselected on return - the deselected set is what persists (saved in this browser, not on the account).
 2. All other technicians - including any who appear for the first time - are selected.
 3. The saved date range and location selection are restored alongside.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R10, S1-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S5-R10, S1-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
@@ -15933,11 +16528,13 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>1. Every technician row's Total Hours is rendered as a link (every rendered row has clocked time &gt; 0, so the link always applies).
+          <t xml:space="preserve">1. Every technician row's Total Hours is rendered as a link (every rendered row has clocked time &gt; 0, so the link always applies).
 2. The link is distinguished by more than color - it carries an underline (or equivalent non-color affordance), is keyboard-focusable with a visible focus indicator, and activates on Enter.
 3. The Summary row's Total Hours value is NOT a link.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R1, S6-N1, S8-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R1, S6-N1, S8-R14).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
@@ -15983,11 +16580,13 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>1. The Timesheet Activities report opens in the SAME browser tab.
+          <t xml:space="preserve">1. The Timesheet Activities report opens in the SAME browser tab.
 2. It is already filtered to that technician.
 3. It uses the same date range that was active on the Technician Utilization report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R2, S6-R3, S6-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R2, S6-R3, S6-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -16034,11 +16633,13 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>1. The two totals MATCH exactly, to two decimals (these values are hours, not money) - both reports read the same clock records and round the same way (round-half-up, from unrounded values).
+          <t xml:space="preserve">1. The two totals MATCH exactly, to two decimals (these values are hours, not money) - both reports read the same clock records and round the same way (round-half-up, from unrounded values).
 2. Under this exact scope (same range, same single location, closed records) a mismatch IS a defect.
 3. The two documented scope differences (open clocks, multi-location drill-through) are covered by separate cases and are NOT defects.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
@@ -16084,11 +16685,13 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>1. The open time is counted UP TO THE MOMENT THE REPORT LOADS - a fixed snapshot taken at load, not a value that keeps ticking on screen (matching how Timesheet Activities treats an open record).
+          <t xml:space="preserve">1. The open time is counted UP TO THE MOMENT THE REPORT LOADS - a fixed snapshot taken at load, not a value that keeps ticking on screen (matching how Timesheet Activities treats an open record).
 2. The two reports, loaded at different moments, MAY differ by the elapsed open time - this is a deliberate scope difference of the reconciliation guarantee, EXPECTED and NOT a defect.
 3. Reloading the Technician Utilization report takes a fresh snapshot (the value grows by the elapsed time).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R9, S1-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R9, S1-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
@@ -16135,11 +16738,13 @@
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
-          <t>1. The link passes the technician and the date range ONLY - it does NOT pass the location selection.
+          <t xml:space="preserve">1. The link passes the technician and the date range ONLY - it does NOT pass the location selection.
 2. Timesheet Activities opens for the user's currently active shop, so it shows one location's portion - it will differ from (or be disjoint with) the multi-location row value.
 3. This is a KNOWN drill-through limitation, EXPECTED and NOT a data defect (the same applies when the single selected location is not the active shop).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R6, S1-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R6, S1-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H308" s="2" t="inlineStr">
@@ -16184,10 +16789,12 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>1. Timesheet Activities opens filtered to that technician.
+          <t xml:space="preserve">1. Timesheet Activities opens filtered to that technician.
 2. The date range covers ONLY that single day.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S6-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -16232,11 +16839,13 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>1. The three-dot download menu sits LEFTMOST in the toolbar's action cluster, with the Column Selection control immediately after it.
+          <t xml:space="preserve">1. The three-dot download menu sits LEFTMOST in the toolbar's action cluster, with the Column Selection control immediately after it.
 2. The menu holds four items, worded exactly as they are on Sales By Customer and Sales By Representative: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)" and "Download Expanded View (CSV)".
 3. Note for the tester: on this build the four items are worded more briefly - "Summary (PDF)", "Summary (CSV)", "Expanded (PDF)" and "Expanded (CSV)" - without the word "Download". The product owner has decided they must match the other two reports, so record what you see; the change is with the developers.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Technician Utilization report specification version 5 (S7-R1, S7-R2, S7-R3, S7-R4, S8-R2) differs, his decision is the authority.</t>
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Technician Utilization report specification version 5 (S7-R1, S7-R2, S7-R3, S7-R4, S8-R2) differs, his decision is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -16281,11 +16890,13 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>1. The Summary PDF shows the technician rows and the Summary row (no day rows); it downloads as "Technician-Utilization-Summary.pdf".
+          <t xml:space="preserve">1. The Summary PDF shows the technician rows and the Summary row (no day rows); it downloads as "Technician-Utilization-Summary.pdf".
 2. The Expanded PDF shows the technician rows, EACH technician's per-day breakdown, and the Summary row; it downloads as "Technician-Utilization-Expanded.pdf".
 3. The PDF filenames are Title-Case as shipped.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R5, S7-R6, S7-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R5, S7-R6, S7-R12).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -16331,11 +16942,13 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>1. The file downloads as "technician-utilization.csv" (lower-case as shipped, unlike the Title-Case PDFs).
+          <t xml:space="preserve">1. The file downloads as "technician-utilization.csv" (lower-case as shipped, unlike the Title-Case PDFs).
 2. The CSV shows the technician rows and the Summary row - always this summary-level content; it does NOT vary by the summary/expanded choice (no day rows).
 3. Any value containing a comma (e.g. "$1,234.50") is wrapped in double quotes per standard CSV escaping, so the columns parse correctly.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R7, S7-R10, S7-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R7, S7-R10, S7-R12).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">
@@ -16383,17 +16996,21 @@
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
-          <t>1. Every download includes ONLY the technicians currently selected in the technician filter - the deselected technician is absent from all three files.
+          <t xml:space="preserve">1. Every download includes ONLY the technicians currently selected in the technician filter - the deselected technician is absent from all three files.
 2. Every download covers the location(s) currently selected in the location filter and the date range currently active on the report.
 3. With every technician selected, the download covers all technicians for the range at the selected location(s).
-4. Every download (each PDF and the CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
+4. Every download (each PDF and the CSV) carries a "Locations:" line naming the location(s) the report was scoped to.
 5. Every download also mirrors the columns currently shown on screen — a column hidden in the Column Selection control is absent from the files, and a re-shown column comes back.
-6. Note for the tester: when more than one location is in scope the files also carry a Location column. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all. With a single location in scope there is no Location column in the files.
+6. Note for the tester: when more than one location is in scope the files also carry a Location column. With a single location in scope there is no Location column in the files.
 ---
 Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
-DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Technician Utilization report specification version 5 (S7-R8, S7-R9, S7-R10, S7-R13, S7-E1, S9-R8) differs, his decision is the authority.</t>
+The Location column is never listed in the column-selection control and you cannot switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
+Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Technician Utilization report specification version 5 (S7-R8, S7-R9, S7-R10, S7-R13, S7-E1, S9-R8), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H313" s="2" t="inlineStr">
@@ -16440,10 +17057,12 @@
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
-          <t>1. The downloaded files use the same column order and number formats as the on-screen report, including the "—" rendering for an unknown Est. Lost Labor.
+          <t xml:space="preserve">1. The downloaded files use the same column order and number formats as the on-screen report, including the "—" rendering for an unknown Est. Lost Labor.
 2. Rows in EVERY download are ordered by Technician name A to Z (the default order) - the on-screen column sort is client-side only and is NOT carried into the export.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R10, S7-R10a).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-R10, S7-R10a).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H314" s="2" t="inlineStr">
@@ -16489,12 +17108,14 @@
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
-          <t>1. With an uploaded logo, BOTH PDF views show that logo at the top of the report.
+          <t xml:space="preserve">1. With an uploaded logo, BOTH PDF views show that logo at the top of the report.
 2. The CSV never includes the logo.
 3. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space.
 Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Technician Utilization report specification version 5 (S7-R11, S7-N2, S7-N3) differs, his decision is the authority.</t>
+This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Technician Utilization report specification version 5 (S7-R11, S7-N2, S7-N3) differs, his decision is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H315" s="2" t="inlineStr">
@@ -16540,11 +17161,13 @@
       </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
-          <t>1. Nothing happens: NO file downloads and NO message appears (not even an error).
+          <t xml:space="preserve">1. Nothing happens: NO file downloads and NO message appears (not even an error).
 2. This silent no-op is the specified behavior for every download option when no technician is selected.
 Known issue: the product does not currently do this — on the build tested, choosing a download with no technician selected still started the download and showed a success message. That is a fault for a developer to fix, not a decision for the product owner. No developer ticket has been raised for it yet, so this test will fail until it is fixed — record what you see and leave the test as it is.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S7-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H316" s="2" t="inlineStr">
@@ -16590,10 +17213,12 @@
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
-          <t>1. When a download starts, a success notification reads exactly: "Download started".
+          <t xml:space="preserve">1. When a download starts, a success notification reads exactly: "Download started".
 2. When a download fails, an error notification reads exactly: "Failed to download report".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (§7 notifications table, Story 7 has no S, §7 is the closing reference).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (§7 notifications table, Story 7 has no S, §7 is the closing reference).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H317" s="2" t="inlineStr">
@@ -16641,12 +17266,14 @@
       </c>
       <c r="G318" s="2" t="inlineStr">
         <is>
-          <t>1. Neither the CSV nor the PDF is produced — no download starts.
+          <t xml:space="preserve">1. Neither the CSV nor the PDF is produced — no download starts.
 2. A clear too-large message appears telling the user to narrow the date range or filters, then try again — the standard wording is "This report is too large to export. Narrow the date range or filters, then try again."
 3. After narrowing below the cap, the downloads work again.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (Story 7 exports).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (Story 7 exports).
+AUTOMATION: READY - EXPECT FAIL (SV-8818)
+</t>
         </is>
       </c>
       <c r="H318" s="2" t="inlineStr">
@@ -16701,7 +17328,7 @@
 5. Note for the tester: write down the exact file name each option gives you. Names for two separate spreadsheet files have never been written down anywhere, so we are collecting them, not checking them - do not fail this test over a file name.
 ---
 This is the expected behaviour as per the Technician Utilization report specification version 5 (S7-R7), which says the spreadsheet always holds the technician rows and the Summary row and does not change with the Summary or Expanded choice. The test exists at all because of Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true - he asked this report's download menu to match Sales By Customer and Sales By Representative, which each offer a spreadsheet for both views, whereas that specification describes only one spreadsheet download. That his answer leaves the menu with four options is our reading of his words and he has not confirmed it. It has not been checked on a build yet.
-AUTOMATION: HOLD - the build does not offer two spreadsheet options yet, and the product owner has not confirmed that it should.
+AUTOMATION: HOLD - the two spreadsheet downloads do not exist yet and the product owner has not confirmed them
 </t>
         </is>
       </c>
@@ -16746,12 +17373,14 @@
       </c>
       <c r="G320" s="2" t="inlineStr">
         <is>
-          <t>1. The toolbar has a location filter labeled "Location" - a multi-select and the RIGHTMOST control.
+          <t xml:space="preserve">1. The toolbar has a location filter labeled "Location" - a multi-select and the RIGHTMOST control.
 2. It lists the locations the signed-in user has access to, plus an "All locations" option and a "Clear all" action. (If you only have access to one location, the "All locations" entry is not offered - you see "Clear all" and your one location.)
 3. "All locations" acts as a select-all shortcut: choosing it selects every accessible location; unchecking one location leaves the remaining specific locations selected - the selection is always the concrete set of checked locations.
 4. With more than one location selected, a Location column appears in the table and each row names its location - or reads "Multiple" for a technician whose hours span more than one of them. (Where that column sits on screen is checked by its own test.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: HOLD - this part of the report is not built yet
+</t>
         </is>
       </c>
       <c r="H320" s="2" t="inlineStr">
@@ -16799,13 +17428,14 @@
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
-          <t>1. Selecting one, several, or all locations RELOADS the report scoped to that set (unlike the technician filter, which is on-screen only).
+          <t xml:space="preserve">1. Selecting one, several, or all locations RELOADS the report scoped to that set (unlike the technician filter, which is on-screen only).
 2. All metrics (technician rows, per-day rows, and the Summary) reflect only clock records at the selected location(s).
 3. The technician's hours are POOLED across the selected locations into ONE row (one row per technician, not one per location); per-day rows pool the same way.
 4. Scoping never goes beyond the user's accessible locations - a location the user cannot access is never included.
-5. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R3, S9-R4, S9-R5).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R3, S9-R4, S9-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H321" s="2" t="inlineStr">
@@ -16850,12 +17480,14 @@
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
-          <t>1. Any saved location the user can no longer access is DROPPED from the restored selection; the remaining accessible locations restore normally.
+          <t xml:space="preserve">1. Any saved location the user can no longer access is DROPPED from the restored selection; the remaining accessible locations restore normally.
 2. If the remaining set is empty, the report falls back to the user's currently active location (the first-visit default).
 3. The report loads without an error in both cases.
 4. The same fallback happens when you deselect every location by hand in the Location filter — the report loads the currently active location's rows rather than showing nothing.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R6, S1-R8, S9-R2, S9-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-R6, S1-R8, S9-R2, S9-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H322" s="2" t="inlineStr">
@@ -16901,10 +17533,12 @@
       </c>
       <c r="G323" s="2" t="inlineStr">
         <is>
-          <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
+          <t xml:space="preserve">1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-N1). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S9-N1). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H323" s="2" t="inlineStr">
@@ -16957,19 +17591,22 @@
       </c>
       <c r="G324" s="2" t="inlineStr">
         <is>
-          <t>1. With more than one location in scope a Location column is shown as the LEFTMOST column, before Technician.
+          <t xml:space="preserve">1. With more than one location in scope a Location column is shown as the LEFTMOST column, before Technician.
 2. A technician whose hours were all clocked at one location shows that location's name.
 3. A technician whose hours span more than one selected location shows "Multiple".
 4. An expanded day row shows the exact location when that day's hours were all at one location, and "Multiple" when the day spans more than one.
 5. The Summary row leaves the Location cell blank.
-6. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all.
-7. With a single location in scope the Location column is hidden.
-8. Every download — both PDF views and the CSV — includes the Location column in its on-screen leftmost position, carrying the same values you just read on screen.
+6. With a single location in scope the Location column is hidden.
+7. Every download — both PDF views and the CSV — includes the Location column in its on-screen leftmost position, carrying the same values you just read on screen.
 ---
 Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
-DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Technician Utilization report specification version 5 (S9-R9, S9-R10, S8-R15, S10-R4, S7-R13) differs, his decision is the authority.</t>
+The Location column is never listed in the column-selection control and you cannot switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
+Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Technician Utilization report specification version 5 (S9-R9, S9-R10, S8-R15, S10-R4, S7-R13), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H324" s="2" t="inlineStr">
@@ -17021,8 +17658,8 @@
       </c>
       <c r="G325" s="2" t="inlineStr">
         <is>
-          <t>1. The control is an icon button whose tooltip reads "Column Selection", sitting immediately after the three-dot download menu in the toolbar.
-2. Because the button shows an icon and no text, it still carries a name that assistive technology reads out — it is not left unnamed. (The exact wording is confirmed in the build.)
+          <t xml:space="preserve">1. The control is an icon button whose tooltip reads "Column Selection", sitting immediately after the three-dot download menu in the toolbar.
+2. Because the button shows an icon and no text, it still carries a name that assistive technology reads out — it is not left unnamed.
 3. The list offers five toggles — Total Hours, WO Hours, Internal Hours, Utilization % and Est. Lost Labor — and all five are on by default.
 4. Technician is always shown and cannot be turned off (it is not offered as a toggle).
 5. The Location column is never listed here — it appears on its own whenever more than one location is in scope.
@@ -17030,7 +17667,9 @@
 7. Est. Lost Labor can now be hidden like any other column (it used to be always on).
 8. Your column choice is remembered in this browser and is still applied when you come back.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R5, S10-R6, S8-R16).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R5, S10-R6, S8-R16).
+AUTOMATION: HOLD - this part of the report is not built yet
+</t>
         </is>
       </c>
       <c r="H325" s="2" t="inlineStr">
@@ -17076,11 +17715,13 @@
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
-          <t>1. The report uses an all-white table: white column headers and white data cells, with NO alternating row shading.
+          <t xml:space="preserve">1. The report uses an all-white table: white column headers and white data cells, with NO alternating row shading.
 2. The toolbar controls run, left to right: the three-dot download menu, the Column Selection control, the date-range picker, the technician filter, and the Location filter (rightmost).
 3. The expand/collapse-all control is NOT a toolbar control - it lives in the table header (in the Technician column).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S8-R1, S8-R2, S8-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S8-R1, S8-R2, S8-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H326" s="2" t="inlineStr">
@@ -17128,12 +17769,14 @@
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
-          <t>1. The report supports dark mode: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and the "—" glyph are all clearly legible in dark mode.
+          <t xml:space="preserve">1. The report supports dark mode: page background, toolbar, cells, the Total Hours link, the information icon, the sort indicator, and the "—" glyph are all clearly legible in dark mode.
 2. In BOTH light mode and dark mode the information icon is clearly visible against the background behind it - you can see it at a glance and it does not disappear into the background.
 3. The Total Hours link's non-color affordance and focus indicator apply in both modes.
 4. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes, and only report it if you cannot. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S8-R9, S8-R13, S8-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S8-R9, S8-R13, S8-R14).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H327" s="2" t="inlineStr">
@@ -17180,11 +17823,13 @@
       </c>
       <c r="G328" s="2" t="inlineStr">
         <is>
-          <t>1. The initial report payload does NOT ship the day rows.
+          <t xml:space="preserve">1. The initial report payload does NOT ship the day rows.
 2. Expanding a technician row issues an on-demand backend request that returns that technician's per-day breakdown.
 3. Because expansion state resets (all collapsed) on any data reload, nothing is lost by the lazy loading - re-expanding fetches fresh day data.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R2, S4-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S4-R2, S4-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H328" s="2" t="inlineStr">
@@ -17232,12 +17877,14 @@
       </c>
       <c r="G329" s="2" t="inlineStr">
         <is>
-          <t>1. A date-range change triggers a fresh server load of the rows.
+          <t xml:space="preserve">1. A date-range change triggers a fresh server load of the rows.
 2. A location change triggers a fresh server load scoped to the selected set.
 3. The technician filter causes NO server request - it works on screen only (hide/show + Summary recalculation).
 4. Column sorting causes NO server request - it is applied on screen to the loaded rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R5, S9-R3, S2-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R5, S9-R3, S2-R13).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H329" s="2" t="inlineStr">
@@ -17285,11 +17932,13 @@
       </c>
       <c r="G330" s="2" t="inlineStr">
         <is>
-          <t>1. The reports navigation lists a report labeled "Work In Progress" under the Performance group, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency).
+          <t xml:space="preserve">1. The reports navigation lists a report labeled "Work In Progress" under the Performance group, BELOW the pre-existing entries (Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency).
 2. Clicking it opens the Work In Progress report.
 3. The browser page title is exactly "Work In Progress - Report | ShopView" — a plain hyphen with one space on each side.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S1-R1, S1-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S1-R1, S1-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H330" s="2" t="inlineStr">
@@ -17336,12 +17985,14 @@
       </c>
       <c r="G331" s="2" t="inlineStr">
         <is>
-          <t>1. Four tabs are shown, labeled in this order: "Approved - Partially Completed", "Approved - Not Started", "Completed", and "Estimates" - each followed by its count in brackets, for example "Completed (30)".
+          <t xml:space="preserve">1. Four tabs are shown, labeled in this order: "Approved - Partially Completed", "Approved - Not Started", "Completed", and "Estimates" - each followed by its count in brackets, for example "Completed (30)".
 2. The "Approved - Partially Completed" tab is selected by default on load.
 3. There is NO on-screen status filter — the four tabs take the place of a status filter (the tab a job lands in is derived from its status and whether any work has started).
 4. Each tab's count matches the number of work-order rows actually listed in that tab.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S1-R2, S1-R3, S1-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S1-R2, S1-R3, S1-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H331" s="2" t="inlineStr">
@@ -17387,10 +18038,12 @@
       </c>
       <c r="G332" s="2" t="inlineStr">
         <is>
-          <t>1. Only the four progress tabs exist — there is no Trend tab and no chart of work-in-progress dollars over time.
+          <t xml:space="preserve">1. Only the four progress tabs exist — there is no Trend tab and no chart of work-in-progress dollars over time.
 2. No screen in the report reads or displays the nightly snapshot history.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H332" s="2" t="inlineStr">
@@ -17436,10 +18089,12 @@
       </c>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t>1. All five seeded work orders appear in the report — each one qualifies because it is a service work order, its status is one of Estimate, Approved, In Progress, Review, or Complete, and it belongs to a selected location.
+          <t xml:space="preserve">1. All five seeded work orders appear in the report — each one qualifies because it is a service work order, its status is one of Estimate, Approved, In Progress, Review, or Complete, and it belongs to a selected location.
 2. Each appears in the tab its status places it in (see the WIP — Tab Placement cases).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H333" s="2" t="inlineStr">
@@ -17487,11 +18142,13 @@
       </c>
       <c r="G334" s="2" t="inlineStr">
         <is>
-          <t>1. The Invoiced and Paid work orders do not appear in any tab, any Totals row, the summary strip, or the download.
+          <t xml:space="preserve">1. The Invoiced and Paid work orders do not appear in any tab, any Totals row, the summary strip, or the download.
 2. The part-sale work order does not appear anywhere either.
 3. No excluded work order's money is counted in any figure.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R2, S2-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R2, S2-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H334" s="2" t="inlineStr">
@@ -17538,10 +18195,12 @@
       </c>
       <c r="G335" s="2" t="inlineStr">
         <is>
-          <t>1. Each qualifying work order appears exactly once, in exactly one tab.
+          <t xml:space="preserve">1. Each qualifying work order appears exactly once, in exactly one tab.
 2. The work order with nothing approved yet still appears (in the Estimates tab), with its earned and remaining both showing "$0.00".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H335" s="2" t="inlineStr">
@@ -17587,11 +18246,13 @@
       </c>
       <c r="G336" s="2" t="inlineStr">
         <is>
-          <t>1. While the report is loading, the data area shows the standard reports loading indicator.
+          <t xml:space="preserve">1. While the report is loading, the data area shows the standard reports loading indicator.
 2. The existing rows are replaced only when the new data returns (the table does not go blank and stay blank mid-load).
 3. Both a date-range change and a location change reload the report's rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R5, S2-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-R5, S2-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H336" s="2" t="inlineStr">
@@ -17639,12 +18300,14 @@
       </c>
       <c r="G337" s="2" t="inlineStr">
         <is>
-          <t>1. Each tab shows the standard reports no-data message "Empty bays, endless possibilities. Get Going!" in place of rows.
+          <t xml:space="preserve">1. Each tab shows the standard reports no-data message "Empty bays, endless possibilities. Get Going!" in place of rows.
 2. No tab shows a Totals row.
 3. Every tab label count reads "(0)".
 4. When only one tab is empty, that tab shows the no-data message, no Totals row, and a "(0)" count while the populated tabs still show their rows normally.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-N1, S2-N2, S6-N1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S2-N1, S2-N2, S6-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H337" s="2" t="inlineStr">
@@ -17690,11 +18353,13 @@
       </c>
       <c r="G338" s="2" t="inlineStr">
         <is>
-          <t>1. The Estimate work order appears in the "Estimates" tab and nowhere else.
+          <t xml:space="preserve">1. The Estimate work order appears in the "Estimates" tab and nowhere else.
 2. The Complete work order appears in the "Completed" tab and nowhere else.
 3. The In Progress and Review work orders appear in the "Approved - partially completed" tab and nowhere else.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S3-R1, S3-R2, S3-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S3-R1, S3-R2, S3-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H338" s="2" t="inlineStr">
@@ -17740,11 +18405,13 @@
       </c>
       <c r="G339" s="2" t="inlineStr">
         <is>
-          <t>1. The Approved work order with clocked labor time appears in the "Approved - partially completed" tab.
+          <t xml:space="preserve">1. The Approved work order with clocked labor time appears in the "Approved - partially completed" tab.
 2. The Approved work order with a received part (and no clocked time) also appears in the "Approved - partially completed" tab — either kind of started work counts.
 3. The Approved work order with no clocked time and no received part appears in the "Approved - not started" tab and nowhere else.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S3-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S3-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H339" s="2" t="inlineStr">
@@ -17792,11 +18459,13 @@
       </c>
       <c r="G340" s="2" t="inlineStr">
         <is>
-          <t>1. The columns appear in this order: WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total.
+          <t xml:space="preserve">1. The columns appear in this order: WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total.
 2. WO #, Status, Customer, Asset, VIN, Location, and Advisor are left-aligned.
 3. Every other column (Days Open, Last Activity, and all money/number columns through Total) is right-aligned.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R1, S4-R3, S4-R4). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R1, S4-R3, S4-R4). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H340" s="2" t="inlineStr">
@@ -17842,14 +18511,16 @@
       </c>
       <c r="G341" s="2" t="inlineStr">
         <is>
-          <t>1. The visible columns on first visit are: WO #, Status, Customer, Asset, Advisor, Days Open, Earned, Remaining, and Total.
-2. Every other column (VIN, Location, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Inv. Hrs) is available in the column-selection control and off by default.
-3. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all. When it is on, the Location column sits between VIN and Advisor and names each job's location.
-4. Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
----
-DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Work In Progress report specification version 6 (S4-R2, S4-R3, S8-R3, S8-R4) differs, his decision is the authority.</t>
+          <t xml:space="preserve">1. The visible columns on first visit are: WO #, Status, Customer, Asset, Advisor, Days Open, Earned, Remaining, and Total.
+2. Every other column (VIN, Location, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Inv. Hrs) is available in the column-selection control and off by default. When it is on, the Location column sits between VIN and Advisor and names each job's location.
+3. Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
+The Location column is not offered in the column-selection control and you do not switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
+Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Work In Progress report specification version 6 (S4-R2, S4-R3, S8-R3, S8-R4), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H341" s="2" t="inlineStr">
@@ -17896,11 +18567,13 @@
       </c>
       <c r="G342" s="2" t="inlineStr">
         <is>
-          <t>1. The WO # is shown as a link.
+          <t xml:space="preserve">1. The WO # is shown as a link.
 2. Clicking it opens that work order in the SAME browser tab (not a new tab).
 3. The browser's back navigation returns you to the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H342" s="2" t="inlineStr">
@@ -17946,11 +18619,13 @@
       </c>
       <c r="G343" s="2" t="inlineStr">
         <is>
-          <t>1. Status is shown as a badge using the status's label: "Estimate", "Approved", "In progress", "Review", or "Complete".
+          <t xml:space="preserve">1. Status is shown as a badge using the status's label: "Estimate", "Approved", "In progress", "Review", or "Complete".
 2. The badge is color-coded per the application's standard status colors.
 3. The label text is always present, so color is never the sole signal of the status.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R6, S10-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R6, S10-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H343" s="2" t="inlineStr">
@@ -17997,13 +18672,15 @@
       </c>
       <c r="G344" s="2" t="inlineStr">
         <is>
-          <t>1. The Asset cell is a two-line cell: the Unit # on the first line in bold, with the VIN underneath in a smaller, muted style.
+          <t xml:space="preserve">1. The Asset cell is a two-line cell: the Unit # on the first line in bold, with the VIN underneath in a smaller, muted style.
 2. When the work order has no Unit #, the first line reads "(no unit #)"; when it has no VIN, the second line reads "— no VIN —". Nothing else stands in for a missing value - there is no further fallback.
-3. The product owner has confirmed this two-line layout is correct for this report and is already built, so the unit number leading is the expected result - do not raise it.
+3. The specification requires this two-line layout for this report, with the unit number leading, and the product owner confirmed it - do not raise it.
 4. The VIN column (off by default) shows the VIN on its own line as a separate, sortable column.
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R7, S4-R8, S4-R10) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R7, S4-R8, S4-R10) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H344" s="2" t="inlineStr">
@@ -18049,10 +18726,12 @@
       </c>
       <c r="G345" s="2" t="inlineStr">
         <is>
-          <t>1. The Customer column shows the customer's company name.
+          <t xml:space="preserve">1. The Customer column shows the customer's company name.
 2. The cell is blank when no customer name exists.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R11).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H345" s="2" t="inlineStr">
@@ -18099,11 +18778,13 @@
       </c>
       <c r="G346" s="2" t="inlineStr">
         <is>
-          <t>1. Days Open is the whole number of days since the work order was created — elapsed time divided by 24 hours, floored, never negative — rendered as "X days".
+          <t xml:space="preserve">1. Days Open is the whole number of days since the work order was created — elapsed time divided by 24 hours, floored, never negative — rendered as "X days".
 2. A same-day work order shows "0 days" and a one-day-old work order shows "1 days".
 3. The value is NOT grammatically pluralized: "1 days" (not "1 day") is the correct, expected rendering.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R12).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H346" s="2" t="inlineStr">
@@ -18151,11 +18832,13 @@
       </c>
       <c r="G347" s="2" t="inlineStr">
         <is>
-          <t>1. A work order whose most recent activity was today shows "Today".
+          <t xml:space="preserve">1. A work order whose most recent activity was today shows "Today".
 2. Otherwise it shows "Xd ago" (for example "3d ago").
 3. A work order with no recorded activity shows "—".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R13).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H347" s="2" t="inlineStr">
@@ -18203,11 +18886,13 @@
       </c>
       <c r="G348" s="2" t="inlineStr">
         <is>
-          <t>1. Money values show a leading "$", two decimal places, and thousands separators — for example "$1,234.56".
+          <t xml:space="preserve">1. Money values show a leading "$", two decimal places, and thousands separators — for example "$1,234.56".
 2. A negative value shows a leading minus before the "$" — for example "-$1,234.56".
 3. A genuine zero shows "$0.00".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R14).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H348" s="2" t="inlineStr">
@@ -18256,11 +18941,13 @@
       </c>
       <c r="G349" s="2" t="inlineStr">
         <is>
-          <t>1. Labor Earned equals the share of the approved line's quoted labor value covered by the time clocked to it (in the example, $100.00).
+          <t xml:space="preserve">1. Labor Earned equals the share of the approved line's quoted labor value covered by the time clocked to it (in the example, $100.00).
 2. For the over-clocked line, Labor Earned never exceeds the full quoted value of that line ($400.00 in the example) — the earned share is capped at the quote per line.
 3. With several approved labor lines, Labor Earned is the sum of each line's capped earned share.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R15).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R15).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H349" s="2" t="inlineStr">
@@ -18308,10 +18995,12 @@
       </c>
       <c r="G350" s="2" t="inlineStr">
         <is>
-          <t>1. Labor Remaining equals the total quoted value of the approved labor minus Labor Earned (in the example, $400.00 − $100.00 = $300.00).
+          <t xml:space="preserve">1. Labor Remaining equals the total quoted value of the approved labor minus Labor Earned (in the example, $400.00 − $100.00 = $300.00).
 2. Labor Earned + Labor Remaining always equals the total quoted value of the approved labor.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R16).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R16).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H350" s="2" t="inlineStr">
@@ -18359,10 +19048,12 @@
       </c>
       <c r="G351" s="2" t="inlineStr">
         <is>
-          <t>1. Parts Earned equals the sell value of the approved-line parts already received (in the example, $100.00).
+          <t xml:space="preserve">1. Parts Earned equals the sell value of the approved-line parts already received (in the example, $100.00).
 2. Parts not yet received contribute nothing to Parts Earned.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R17).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R17).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H351" s="2" t="inlineStr">
@@ -18411,10 +19102,12 @@
       </c>
       <c r="G352" s="2" t="inlineStr">
         <is>
-          <t>1. Parts Remaining equals the sell value of approved-line parts ordered but not yet received (in the example, $100.00).
+          <t xml:space="preserve">1. Parts Remaining equals the sell value of approved-line parts ordered but not yet received (in the example, $100.00).
 2. For the core-charge part, Parts Remaining values the outstanding quantity at its sell price INCLUDING the core charge.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R18).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R18).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H352" s="2" t="inlineStr">
@@ -18464,12 +19157,14 @@
       </c>
       <c r="G353" s="2" t="inlineStr">
         <is>
-          <t>1. Earned equals Labor Earned plus Parts Earned.
+          <t xml:space="preserve">1. Earned equals Labor Earned plus Parts Earned.
 2. Remaining equals Labor Remaining plus Parts Remaining.
 3. Total equals Earned plus Remaining.
 4. The Total is NOT the work order's stored grand total — it excludes tax, fees, discounts, and non-approved lines, so a difference from the work order's own grand total is EXPECTED, not a data error.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R19, S4-R20, S4-R21).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R19, S4-R20, S4-R21).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H353" s="2" t="inlineStr">
@@ -18516,10 +19211,12 @@
       </c>
       <c r="G354" s="2" t="inlineStr">
         <is>
-          <t>1. The work order's Labor/Parts Earned, Labor/Parts Remaining, Earned, Remaining, and Total are unchanged.
+          <t xml:space="preserve">1. The work order's Labor/Parts Earned, Labor/Parts Remaining, Earned, Remaining, and Total are unchanged.
 2. Only approved lines (line status authorized or complete) contribute to the report's money — not-yet-approved lines contribute nothing.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R15).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R15).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H354" s="2" t="inlineStr">
@@ -18567,11 +19264,13 @@
       </c>
       <c r="G355" s="2" t="inlineStr">
         <is>
-          <t>1. Inv. Hrs shows the quoted labor hours minus the worked (clocked) labor hours across the approved lines, as a signed number with one decimal place — for example "+2.0" or "-14.0".
+          <t xml:space="preserve">1. Inv. Hrs shows the quoted labor hours minus the worked (clocked) labor hours across the approved lines, as a signed number with one decimal place — for example "+2.0" or "-14.0".
 2. On screen it is colored green when positive and red when negative; the overrun job shows a negative red value, the under-estimate job a positive green value.
 3. A value of exactly zero shows unsigned as "0.0" (never "+0.0" or blank) in the default text color.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R23, S4-R24, S4-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R23, S4-R24, S4-E2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H355" s="2" t="inlineStr">
@@ -18618,10 +19317,12 @@
       </c>
       <c r="G356" s="2" t="inlineStr">
         <is>
-          <t>1. Every money column — Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, and Total — shows "$0.00".
+          <t xml:space="preserve">1. Every money column — Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, and Total — shows "$0.00".
 2. The row still appears in the Estimates tab (it is not hidden for having no value).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-E1, S2-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-E1, S2-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H356" s="2" t="inlineStr">
@@ -18670,11 +19371,13 @@
       </c>
       <c r="G357" s="2" t="inlineStr">
         <is>
-          <t>1. The running (not-yet-clocked-out) time counts toward Labor Earned — the line's earned share reflects the time clocked up to now, not only closed clock records.
+          <t xml:space="preserve">1. The running (not-yet-clocked-out) time counts toward Labor Earned — the line's earned share reflects the time clocked up to now, not only closed clock records.
 2. After more time accrues, a refresh shows a larger earned share for that line.
 3. Labor Earned never exceeds the line's full quoted value, no matter how long the clock keeps running — the per-line cap still applies.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R15).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R15).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H357" s="2" t="inlineStr">
@@ -18720,9 +19423,11 @@
       </c>
       <c r="G358" s="2" t="inlineStr">
         <is>
-          <t>1. The rows are sorted by Days Open, longest-open first (descending).
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R25).</t>
+          <t xml:space="preserve">1. The rows are sorted by Days Open, longest-open first (descending).
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R25).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H358" s="2" t="inlineStr">
@@ -18770,12 +19475,14 @@
       </c>
       <c r="G359" s="2" t="inlineStr">
         <is>
-          <t>1. The first click sorts the column ascending.
+          <t xml:space="preserve">1. The first click sorts the column ascending.
 2. The second click toggles it to descending.
 3. The third click returns to ascending — there is no third "cleared" state.
 4. Only one column sorts at a time: clicking another header replaces the previous sort.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R26).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R26).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H359" s="2" t="inlineStr">
@@ -18824,13 +19531,15 @@
       </c>
       <c r="G360" s="2" t="inlineStr">
         <is>
-          <t>1. Money and numeric columns sort by their underlying numeric value (so $1,100.00 is treated as more than $900.00, not compared as text).
+          <t xml:space="preserve">1. Money and numeric columns sort by their underlying numeric value (so $1,100.00 is treated as more than $900.00, not compared as text).
 2. Days Open sorts by its day count.
 3. Status sorts by its displayed label.
 4. The Asset column sorts by the Unit #.
 5. WO #, Customer, Asset, VIN, Location, and Advisor sort as text.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R9, S4-R27) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R9, S4-R27) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H360" s="2" t="inlineStr">
@@ -18877,11 +19586,13 @@
       </c>
       <c r="G361" s="2" t="inlineStr">
         <is>
-          <t>1. Sorting reorders the rows within the active tab only.
+          <t xml:space="preserve">1. Sorting reorders the rows within the active tab only.
 2. The Totals row stays pinned at the bottom, out of the sort.
 3. The other tab's order is not changed by the first tab's sort action.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R28).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R28).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H361" s="2" t="inlineStr">
@@ -18927,10 +19638,12 @@
       </c>
       <c r="G362" s="2" t="inlineStr">
         <is>
-          <t>1. The strip shows seven figures, in this order: Total Earned, Total Remaining, Not Started, Started — Earned, Started — Remaining, Ready to Invoice, and Estimates.
+          <t xml:space="preserve">1. The strip shows seven figures, in this order: Total Earned, Total Remaining, Not Started, Started — Earned, Started — Remaining, Ready to Invoice, and Estimates.
 2. Every figure shows US-dollar currency with a leading "$", two decimals, and thousands separators.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R1, S5-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R1, S5-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H362" s="2" t="inlineStr">
@@ -18977,10 +19690,12 @@
       </c>
       <c r="G363" s="2" t="inlineStr">
         <is>
-          <t>1. Total Earned is shown larger than the other figures and with a colored underline — it is the strip's hero figure.
+          <t xml:space="preserve">1. Total Earned is shown larger than the other figures and with a colored underline — it is the strip's hero figure.
 2. Total Earned equals Started — Earned plus Ready to Invoice, to the cent.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H363" s="2" t="inlineStr">
@@ -19026,9 +19741,11 @@
       </c>
       <c r="G364" s="2" t="inlineStr">
         <is>
-          <t>1. Total Remaining equals Not Started plus Started — Remaining, to the cent.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R3).</t>
+          <t xml:space="preserve">1. Total Remaining equals Not Started plus Started — Remaining, to the cent.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H364" s="2" t="inlineStr">
@@ -19076,11 +19793,13 @@
       </c>
       <c r="G365" s="2" t="inlineStr">
         <is>
-          <t>1. Not Started equals the total approved value (earned + remaining) of the jobs in the "Approved - not started" tab.
+          <t xml:space="preserve">1. Not Started equals the total approved value (earned + remaining) of the jobs in the "Approved - not started" tab.
 2. Started — Earned equals the total Earned of the jobs in the "Approved - partially completed" tab, and Started — Remaining equals that tab's total Remaining.
 3. Ready to Invoice equals the total Earned of the jobs in the "Completed" tab.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R4, S5-R5, S5-R6, S5-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R4, S5-R5, S5-R6, S5-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H365" s="2" t="inlineStr">
@@ -19127,12 +19846,14 @@
       </c>
       <c r="G366" s="2" t="inlineStr">
         <is>
-          <t>1. The Estimates figure equals the total quoted value of the jobs in the Estimates tab.
+          <t xml:space="preserve">1. The Estimates figure equals the total quoted value of the jobs in the Estimates tab.
 2. It is shown in a muted style.
 3. The Estimates figure is excluded from Total Earned and from Total Remaining.
 Known issue: the product does not currently do this — on the build tested, the Estimates figure read $0.00 even though the Estimates tab held jobs, because the product is showing the approved value instead of the quoted value. That is a fault for a developer to fix, not a decision for the product owner. No developer ticket has been raised for it yet, so this test will fail until it is fixed — record what you see and leave the test as it is.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R8, S5-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R8, S5-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H366" s="2" t="inlineStr">
@@ -19178,7 +19899,7 @@
       </c>
       <c r="G367" s="2" t="inlineStr">
         <is>
-          <t>1. Total Earned — "Work you have already done but have not billed yet — the money waiting to be collected."
+          <t xml:space="preserve">1. Total Earned — "Work you have already done but have not billed yet — the money waiting to be collected."
 2. Total Remaining — "Approved work you still have to do — the money that comes in once it is finished."
 3. Not Started — "Approved jobs nobody has started yet. The full amount is still ahead."
 4. Started — Earned — "Jobs in progress: the work already done but not billed yet."
@@ -19187,7 +19908,9 @@
 7. Estimates — "Quotes the customer has not approved yet — not counted in the totals."
 8. Each explanation appears on hover, on keyboard focus, and on tap.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S5-R12).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H367" s="2" t="inlineStr">
@@ -19234,11 +19957,13 @@
       </c>
       <c r="G368" s="2" t="inlineStr">
         <is>
-          <t>1. Each tab's table has a Totals row pinned to the bottom, labeled "Totals" in its leftmost cell.
+          <t xml:space="preserve">1. Each tab's table has a Totals row pinned to the bottom, labeled "Totals" in its leftmost cell.
 2. The Totals row's Total cell is pinned far right and shown in bold, matching the column.
 3. The Totals row uses the same number formats as the data rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S6-R1, S6-R4, S6-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S6-R1, S6-R4, S6-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H368" s="2" t="inlineStr">
@@ -19286,12 +20011,14 @@
       </c>
       <c r="G369" s="2" t="inlineStr">
         <is>
-          <t>1. The Totals row sums each visible money column across the tab's visible jobs, to the cent.
+          <t xml:space="preserve">1. The Totals row sums each visible money column across the tab's visible jobs, to the cent.
 2. The Totals row's Inv. Hrs shows the sum of the visible jobs' Inv. Hrs, in the same signed one-decimal format ("+2.0" / "-14.0" / "0.0").
 3. The Inv. Hrs total uses the same green (positive) / red (negative) / default (exactly 0.0) coloring as a data row.
 4. Note for the tester: the Inv. Hrs total can only be checked on screen. On this build a download that includes Inv. Hrs is refused, so do not try to verify this column from a file.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S6-R2, S6-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S6-R2, S6-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H369" s="2" t="inlineStr">
@@ -19338,11 +20065,13 @@
       </c>
       <c r="G370" s="2" t="inlineStr">
         <is>
-          <t>1. The Advisor filter is a multi-select listing the advisors present in the loaded jobs.
+          <t xml:space="preserve">1. The Advisor filter is a multi-select listing the advisors present in the loaded jobs.
 2. Selecting one or more advisors narrows the visible jobs to those advisors instantly, on screen only — no reload and no loading indicator.
 3. With two advisors selected, jobs for either advisor are shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H370" s="2" t="inlineStr">
@@ -19390,12 +20119,14 @@
       </c>
       <c r="G371" s="2" t="inlineStr">
         <is>
-          <t>1. With no customer selected, the filter reads "All customers", every job is shown, and no Clear action is offered.
+          <t xml:space="preserve">1. With no customer selected, the filter reads "All customers", every job is shown, and no Clear action is offered.
 2. Typing narrows the option list (type-ahead); the options are the customers present in the loaded jobs.
 3. Selecting customers narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one customer is selected.
 4. Clear returns the filter to "All customers" and every job is shown again.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R2, S7-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R2, S7-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H371" s="2" t="inlineStr">
@@ -19443,13 +20174,15 @@
       </c>
       <c r="G372" s="2" t="inlineStr">
         <is>
-          <t>1. With no asset selected, the filter reads "All assets" and every job is shown.
+          <t xml:space="preserve">1. With no asset selected, the filter reads "All assets" and every job is shown.
 2. Each option shows both the asset's Unit # and its VIN.
 3. Text you type matches against either the Unit # or the VIN - a match on either one brings the asset up.
 4. Selecting assets narrows the visible jobs on screen only (no reload); a single "Clear" action appears once at least one asset is selected and returns the filter to "All assets".
 5. Note for the tester: the field is labelled VIN. For assets that are not vehicles (for example a generator), this is the unit's serial number.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R4, S7-R5) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R4, S7-R5) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H372" s="2" t="inlineStr">
@@ -19494,11 +20227,13 @@
       </c>
       <c r="G373" s="2" t="inlineStr">
         <is>
-          <t>1. On a fresh visit the date range defaults to "This Week".
+          <t xml:space="preserve">1. On a fresh visit the date range defaults to "This Week".
 2. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
 3. The named periods use the application's standard shared calendar boundaries - this is one shared chooser used by all six reports.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Work In Progress report specification version 6 (S7-R6) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Work In Progress report specification version 6 (S7-R6) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H373" s="2" t="inlineStr">
@@ -19545,14 +20280,14 @@
       </c>
       <c r="G374" s="2" t="inlineStr">
         <is>
-          <t>1. Each preset (or Custom) filters the report to work orders whose CREATED date falls within the selected range — an open work order created outside the range is not listed.
+          <t xml:space="preserve">1. Each preset (or Custom) filters the report to work orders whose CREATED date falls within the selected range — an open work order created outside the range is not listed.
 2. Changing the range reloads the report (the loading indicator shows).
 3. A range longer than about a year is refused with the message "Date range cannot be over one year." and the wider range is not loaded.
 4. Note for the tester: on this build the exact cut-off sits one day later than the specification says (a 367-day span is accepted, 368 is refused). Record what you see; the one-day difference is already known and is with the product owner.
 ---
-DO NOT AUTOMATE YET: this behaviour is waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/chris-consolidated-2026-08-04/Report-Suite_Questions-and-Decisions-for-Chris-Ward_2026-08-04.xlsx
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R7, S7-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R7, S7-R8).
+AUTOMATION: HOLD - waiting on an answer from the product owner
+</t>
         </is>
       </c>
       <c r="H374" s="2" t="inlineStr">
@@ -19602,13 +20337,14 @@
       </c>
       <c r="G375" s="2" t="inlineStr">
         <is>
-          <t>1. The Location filter is the rightmost toolbar filter, a multi-select listing the locations the signed-in user can access, with an "All locations" / "Clear all" toggle.
+          <t xml:space="preserve">1. The Location filter is the rightmost toolbar filter, a multi-select listing the locations the signed-in user can access, with an "All locations" / "Clear all" toggle.
 2. On a first visit it defaults to the user's currently active location.
 3. Selecting one, several, or all locations reloads the report scoped to that set (rows from the added location appear).
-4. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
-5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's work orders.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R9, S7-R10). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+4. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's work orders.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R9, S7-R10). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H375" s="2" t="inlineStr">
@@ -19655,11 +20391,13 @@
       </c>
       <c r="G376" s="2" t="inlineStr">
         <is>
-          <t>1. Only the locations the user can access are offered — a location the user cannot access is never included in the scope.
+          <t xml:space="preserve">1. Only the locations the user can access are offered — a location the user cannot access is never included in the scope.
 2. If the selection resolves to none, the report falls back to the user's currently active location rather than showing everything or erroring.
 3. A saved selection that no longer resolves also falls back to the active location.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R11, S8-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R11, S8-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H376" s="2" t="inlineStr">
@@ -19706,11 +20444,13 @@
       </c>
       <c r="G377" s="2" t="inlineStr">
         <is>
-          <t>1. A job must pass all three filters to remain visible (the filters combine with AND).
+          <t xml:space="preserve">1. A job must pass all three filters to remain visible (the filters combine with AND).
 2. The summary strip and each tab's Totals row recompute immediately from the still-visible jobs after every advisor, customer, or asset change — on screen, with no page reload.
 3. When the combination leaves no visible jobs, every tab shows the no-data message "Empty bays, endless possibilities. Get Going!" and no Totals row.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R12, S7-N1, S5-R11, S6-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S7-R12, S7-N1, S5-R11, S6-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H377" s="2" t="inlineStr">
@@ -19762,17 +20502,20 @@
       </c>
       <c r="G378" s="2" t="inlineStr">
         <is>
-          <t>1. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all. When it is on, the Location column sits between VIN and Advisor, left-aligned.
-2. Each row names its own work order's location.
-3. NO row ever shows "Multiple" — a work order belongs to exactly one location, and this report has no grouped or drill-down rows.
-4. Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
-5. With the toggle off the Location column is not shown, whatever the location selection is.
-6. In both downloads the column is headed "Branch" (a known naming difference from the screen — do not raise it as a bug).
-7. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
----
-DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Work In Progress report specification version 6 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a) differs, his decision is the authority.</t>
+          <t xml:space="preserve"> When it is on, the Location column sits between VIN and Advisor, left-aligned.
+1. Each row names its own work order's location.
+2. NO row ever shows "Multiple" — a work order belongs to exactly one location, and this report has no grouped or drill-down rows.
+3. Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
+4. With the toggle off the Location column is not shown, whatever the location selection is.
+5. In both downloads the column is headed "Branch" (a known naming difference from the screen — do not raise it as a bug).
+6. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
+The Location column is not offered in the column-selection control and you do not switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
+Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Work In Progress report specification version 6 (S7-R13, S7-R14, S4-R3, S9-E1, S10-R5a), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H378" s="2" t="inlineStr">
@@ -19819,11 +20562,13 @@
       </c>
       <c r="G379" s="2" t="inlineStr">
         <is>
-          <t>1. The icon button's tooltip reads "Column Selection".
+          <t xml:space="preserve">1. The icon button's tooltip reads "Column Selection".
 2. Toggling a column off hides it from the table; toggling it on shows it again.
 3. The Total column is always shown and cannot be turned off — it is not offered in the control at all.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R1, S8-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R1, S8-R2).
+AUTOMATION: HOLD - this part of the report is not built yet
+</t>
         </is>
       </c>
       <c r="H379" s="2" t="inlineStr">
@@ -19870,11 +20615,13 @@
       </c>
       <c r="G380" s="2" t="inlineStr">
         <is>
-          <t>1. Whatever columns are shown, they always appear in the fixed left-to-right order (WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total) — the order you toggled them in never changes their position.
+          <t xml:space="preserve">1. Whatever columns are shown, they always appear in the fixed left-to-right order (WO #, Status, Customer, Asset, VIN, Location, Advisor, Days Open, Last Activity, Labor Earned, Labor Remaining, Parts Earned, Parts Remaining, Earned, Remaining, Inv. Hrs, Total) — the order you toggled them in never changes their position.
 2. Total is always the last column.
 3. The column selection applies to every tab at once — all four tabs show the same set of columns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R5, S8-R6, S4-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R5, S8-R6, S4-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H380" s="2" t="inlineStr">
@@ -19922,10 +20669,12 @@
       </c>
       <c r="G381" s="2" t="inlineStr">
         <is>
-          <t>1. On return and after a reload, the report restores the saved date range, advisor selection, customer selection, asset selection, location selection, column selection, and active tab.
+          <t xml:space="preserve">1. On return and after a reload, the report restores the saved date range, advisor selection, customer selection, asset selection, location selection, column selection, and active tab.
 2. In a different browser the report shows the defaults instead — the settings are saved per browser, not on the user's account.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H381" s="2" t="inlineStr">
@@ -19971,10 +20720,12 @@
       </c>
       <c r="G382" s="2" t="inlineStr">
         <is>
-          <t>1. The report loads normally — the invalid saved value falls back to that setting's default rather than breaking the view.
+          <t xml:space="preserve">1. The report loads normally — the invalid saved value falls back to that setting's default rather than breaking the view.
 2. All other saved settings are still restored.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S8-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H382" s="2" t="inlineStr">
@@ -20029,7 +20780,7 @@
 4. Everything else is remembered exactly as before - the other column choices, the date range, the filters and the tab you were on. Turning Location on or off changes nothing else.
 ---
 This is the expected behaviour as per the Work In Progress report specification version 6 (S8-R7), which says the report remembers the column selection in the user's browser and puts it back on the next visit. Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, is what makes Location a column you can switch on and off at all, and it does not say whether that choice is remembered - so this test applies the existing written rule about remembered column choices to the new switch. It has not been checked on a build yet.
-AUTOMATION: HOLD - nobody has run this test yet, and the product owner has not confirmed that a hand-made Location choice is remembered.
+AUTOMATION: HOLD - waiting on an answer from the product owner
 </t>
         </is>
       </c>
@@ -20073,10 +20824,12 @@
       </c>
       <c r="G384" s="2" t="inlineStr">
         <is>
-          <t>1. The menu holds the download options "Download (PDF)" and "Download (CSV)".
+          <t xml:space="preserve">1. The menu holds the download options "Download (PDF)" and "Download (CSV)".
 2. Each option downloads a file of the current tab in the chosen format.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H384" s="2" t="inlineStr">
@@ -20125,14 +20878,20 @@
       </c>
       <c r="G385" s="2" t="inlineStr">
         <is>
-          <t>1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total last. One exception on this build: if you turn Inv. Hrs on, the download is refused - that column cannot be exported yet.
+          <t xml:space="preserve">1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total last. One exception on this build: if you turn Inv. Hrs on, the download is refused - that column cannot be exported yet.
 2. Both downloads honor the current date range and location filter, and include only the jobs left visible by the advisor, customer, and asset filters.
 3. Both downloads include a Totals row matching the on-screen Totals row for the tab.
-4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
-5. Note for the tester: the file carries the Location column whenever it is showing on screen. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all. In the file it is headed "Branch", not "Location".
+4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to.
+5. Note for the tester: the file carries the Location column whenever it is showing on screen. In the file it is headed "Branch", not "Location".
 ---
 Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Work In Progress report specification version 6 (S9-R2, S9-R3, S9-R4, S9-R10a, S7-R13, S9-E1) differs, his decision is the authority.</t>
+The Location column is not offered in the column-selection control and you do not switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
+Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Work In Progress report specification version 6 (S9-R2, S9-R3, S9-R4, S9-R10a, S7-R13, S9-E1), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H385" s="2" t="inlineStr">
@@ -20181,11 +20940,13 @@
       </c>
       <c r="G386" s="2" t="inlineStr">
         <is>
-          <t>1. Money values use the same "$1,234.56" / "-$1,234.56" format as on screen; Inv. Hrs uses the same signed one-decimal format.
+          <t xml:space="preserve">1. Money values use the same "$1,234.56" / "-$1,234.56" format as on screen; Inv. Hrs uses the same signed one-decimal format.
 2. In the CSV, a money value containing a comma (a thousands separator) is enclosed in double-quotes per standard CSV rules.
 3. A value without a comma is written unquoted.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R5, S9-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R5, S9-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H386" s="2" t="inlineStr">
@@ -20231,10 +20992,12 @@
       </c>
       <c r="G387" s="2" t="inlineStr">
         <is>
-          <t>1. In the PDF, Inv. Hrs keeps the green (positive) / red (negative) coloring.
+          <t xml:space="preserve">1. In the PDF, Inv. Hrs keeps the green (positive) / red (negative) coloring.
 2. In the CSV, the Inv. Hrs column is monochrome — plain signed numbers with no color or markup.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H387" s="2" t="inlineStr">
@@ -20281,10 +21044,12 @@
       </c>
       <c r="G388" s="2" t="inlineStr">
         <is>
-          <t>1. In the download, Days Open is the whole number of days as of the moment the file is generated.
+          <t xml:space="preserve">1. In the download, Days Open is the whole number of days as of the moment the file is generated.
 2. Because the screen computes Days Open live while the file freezes it at generation time, the file can legitimately show a day count one higher than the screen it was generated from — that difference is EXPECTED, not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H388" s="2" t="inlineStr">
@@ -20330,11 +21095,13 @@
       </c>
       <c r="G389" s="2" t="inlineStr">
         <is>
-          <t>1. The PDF is named "wip-2-report.pdf".
+          <t xml:space="preserve">1. The PDF is named "wip-2-report.pdf".
 2. The CSV is named "wip-2-report.csv".
 3. These exact names (including the "-2-") are the specified current behavior.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H389" s="2" t="inlineStr">
@@ -20381,12 +21148,14 @@
       </c>
       <c r="G390" s="2" t="inlineStr">
         <is>
-          <t>1. On screen the headers read "Asset" and "Location".
+          <t xml:space="preserve">1. On screen the headers read "Asset" and "Location".
 2. In BOTH the PDF and the CSV, the same two columns are headed "Unit" and "Branch".
 3. This on-screen-vs-export label difference is the EXPECTED, documented v1 behavior.
 4. The on-screen Asset cell leads with the Unit #, which is what the export header "Unit" already reflects - so no header change is expected here.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-E1) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-E1) - the build and that specification agree. Chris Ward confirmed it again on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It differs from an earlier answer he gave us on 29 July 2026, which we now know was given against a question that described this report incorrectly; we follow his latest word, which agrees with the specification.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H390" s="2" t="inlineStr">
@@ -20432,10 +21201,12 @@
       </c>
       <c r="G391" s="2" t="inlineStr">
         <is>
-          <t>1. The PDF shows the shop logo at the top.
+          <t xml:space="preserve">1. The PDF shows the shop logo at the top.
 2. The CSV never includes a logo (plain data only).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H391" s="2" t="inlineStr">
@@ -20483,11 +21254,13 @@
       </c>
       <c r="G392" s="2" t="inlineStr">
         <is>
-          <t>1. On a successful download, a success notification shows with the caption "Data exported successfully."
+          <t xml:space="preserve">1. On a successful download, a success notification shows with the caption "Data exported successfully."
 2. When a download yields no rows, a warning notification shows titled "Empty export" with the caption "Export didn't yield any results".
 3. When a download fails, an error notification shows: "An error occurred while exporting the report. Please try again."
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R11, S9-R12, S9-R13).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S9-R11, S9-R12, S9-R13).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H392" s="2" t="inlineStr">
@@ -20533,12 +21306,14 @@
       </c>
       <c r="G393" s="2" t="inlineStr">
         <is>
-          <t>1. For both the CSV and the PDF: no file is generated and no download starts.
+          <t xml:space="preserve">1. For both the CSV and the PDF: no file is generated and no download starts.
 2. An error toast is shown each time, reading exactly: "This report is too large to export. Narrow the date range or filters, then try again." (dismissed by the user).
 3. Below the cap the download works normally.
 4. Note for the tester: on this environment the biggest single tab holds about 114 work orders, so you cannot make this message appear here. Record that and move on.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (Story 9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (Story 9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H393" s="2" t="inlineStr">
@@ -20584,10 +21359,12 @@
       </c>
       <c r="G394" s="2" t="inlineStr">
         <is>
-          <t>1. Each tab uses an all-white table: white column headers and white data cells.
+          <t xml:space="preserve">1. Each tab uses an all-white table: white column headers and white data cells.
 2. There is no alternating row shading (no zebra striping).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H394" s="2" t="inlineStr">
@@ -20633,10 +21410,12 @@
       </c>
       <c r="G395" s="2" t="inlineStr">
         <is>
-          <t>1. The summary strip appears above the tabs.
+          <t xml:space="preserve">1. The summary strip appears above the tabs.
 2. It is shown as a bold band delineated by a top and bottom rule — not as a row of separate cards.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H395" s="2" t="inlineStr">
@@ -20682,10 +21461,12 @@
       </c>
       <c r="G396" s="2" t="inlineStr">
         <is>
-          <t>1. The Total column header is bold and pinned to the far right, matching its cells.
+          <t xml:space="preserve">1. The Total column header is bold and pinned to the far right, matching its cells.
 2. The Total column (header and cells, shown in bold) stays fixed to the right edge while the rest of the columns scroll underneath.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R22, S10-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S4-R22, S10-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H396" s="2" t="inlineStr">
@@ -20731,10 +21512,12 @@
       </c>
       <c r="G397" s="2" t="inlineStr">
         <is>
-          <t>1. The Totals row stays visible at the bottom while the rows scroll.
+          <t xml:space="preserve">1. The Totals row stays visible at the bottom while the rows scroll.
 2. The report fills the available height and only the active tab's table body scrolls — the page itself does not add a second scrollbar.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R4, S10-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R4, S10-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H397" s="2" t="inlineStr">
@@ -20781,11 +21564,13 @@
       </c>
       <c r="G398" s="2" t="inlineStr">
         <is>
-          <t>1. The WO # link can receive keyboard focus.
+          <t xml:space="preserve">1. The WO # link can receive keyboard focus.
 2. A visible focus indicator shows when it is focused.
 3. Activating it opens the work order (in the same browser tab).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H398" s="2" t="inlineStr">
@@ -20832,11 +21617,13 @@
       </c>
       <c r="G399" s="2" t="inlineStr">
         <is>
-          <t>1. Each information icon is reachable by keyboard focus.
+          <t xml:space="preserve">1. Each information icon is reachable by keyboard focus.
 2. Its explanation is revealed on focus, not by hover alone.
 3. The explanation text is exposed to assistive technology.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R7, S5-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R7, S5-R12).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H399" s="2" t="inlineStr">
@@ -20883,10 +21670,12 @@
       </c>
       <c r="G400" s="2" t="inlineStr">
         <is>
-          <t>1. The report supports dark mode.
+          <t xml:space="preserve">1. The report supports dark mode.
 2. The table, the summary strip, the WO # link, the Inv. Hrs green/red coloring, and the two-line asset cell all use dark-mode-legible colors meeting contrast.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S10-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H400" s="2" t="inlineStr">
@@ -20933,11 +21722,13 @@
       </c>
       <c r="G401" s="2" t="inlineStr">
         <is>
-          <t>1. The report is listed and opens normally.
-2. The download works with the same permission — for now the one ordinary reports access covers the report and its downloads and no new permission is added for it.
-3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (Story 1 Prerequisites); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+          <t xml:space="preserve">1. The report is listed and opens normally.
+2. The download works with the same permission — the specification allows the one ordinary reports access to cover the report and its downloads, with no new permission for it.
+3. Note for the tester: the specification allows ONE ordinary reports access for all six of these new reports and no per-report permission. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (Story 1 Prerequisites); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H401" s="2" t="inlineStr">
@@ -20983,9 +21774,11 @@
       </c>
       <c r="G402" s="2" t="inlineStr">
         <is>
-          <t>1. The report does not appear in the navigation for this user.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S1-N1).</t>
+          <t xml:space="preserve">1. The report does not appear in the navigation for this user.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S1-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H402" s="2" t="inlineStr">
@@ -21034,13 +21827,16 @@
       </c>
       <c r="G403" s="2" t="inlineStr">
         <is>
-          <t>1. Once per day the system records one row per then-open work order — one row per work order per calendar date.
+          <t xml:space="preserve">1. Once per day the system records one row per then-open work order — one row per work order per calendar date.
 2. The next day's capture adds a new row per open work order under the new date; a work order open on both days has one row for each date, never two rows for the same date.
 3. Re-running the capture for the SAME date replaces that date's rows — the day's existing rows are removed and re-recorded from current data, never duplicated.
 4. Each snapshot row captures, at minimum: the work order, its status, its Earned value, its Remaining value, the location and organization (copied from the work order), and the snapshot's calendar date.
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R1, S11-R2).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R1, S11-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H403" s="2" t="inlineStr">
@@ -21089,11 +21885,14 @@
       </c>
       <c r="G404" s="2" t="inlineStr">
         <is>
-          <t>1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation for both figures, so the two can never diverge for a given work order on the capture date.
+          <t xml:space="preserve">1. The captured Earned equals the on-screen Earned and the captured Remaining equals the on-screen Remaining, to the cent — the snapshot uses the identical computation for both figures, so the two can never diverge for a given work order on the capture date.
 2. The captured dollar values are stored to the cent — no rounding to whole dollars and no lost cents.
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R3, S11-R5).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R3, S11-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H404" s="2" t="inlineStr">
@@ -21142,12 +21941,15 @@
       </c>
       <c r="G405" s="2" t="inlineStr">
         <is>
-          <t>1. The captured set uses the same service-type and open-status conditions as the report (service work orders in Estimate, Approved, In Progress, Review, or Complete).
+          <t xml:space="preserve">1. The captured set uses the same service-type and open-status conditions as the report (service work orders in Estimate, Approved, In Progress, Review, or Complete).
 2. The capture spans every location — there is no user-selected-location filter.
 3. Invoiced, Paid, and Declined work orders and part-sale work orders are not captured.
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R4, S2-R1).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R4, S2-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H405" s="2" t="inlineStr">
@@ -21194,11 +21996,14 @@
       </c>
       <c r="G406" s="2" t="inlineStr">
         <is>
-          <t>1. The work order IS captured (not skipped).
+          <t xml:space="preserve">1. The work order IS captured (not skipped).
 2. Its Earned is $0.00 and its Remaining is $0.00, matching what the report shows on screen for a job with nothing approved.
 ---
 Note for the tester: you cannot check this one from any screen. These figures are written each night by a background process, and nothing in the report reads them back in this version. If you cannot see the figures anywhere, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R6, S4-E1).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Work In Progress report specification version 6 (S11-R6, S4-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H406" s="2" t="inlineStr">
@@ -21245,10 +22050,12 @@
       </c>
       <c r="G407" s="2" t="inlineStr">
         <is>
-          <t>1. The reports navigation lists a report labeled "Inventory Value" under the Parts group.
+          <t xml:space="preserve">1. The reports navigation lists a report labeled "Inventory Value" under the Parts group.
 2. Clicking it opens the Inventory Value report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S1-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S1-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H407" s="2" t="inlineStr">
@@ -21295,10 +22102,12 @@
       </c>
       <c r="G408" s="2" t="inlineStr">
         <is>
-          <t>1. The report shows one row for each in-stock part at the selected location(s).
+          <t xml:space="preserve">1. The report shows one row for each in-stock part at the selected location(s).
 2. The values are valued as of the resolved date (the current stock for a range reaching today, or the closest recorded nightly snapshot for an earlier date — see the IV — As-of Date &amp; Snapshots cases).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S1-R2, S1-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S1-R2, S1-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H408" s="2" t="inlineStr">
@@ -21344,10 +22153,12 @@
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
-          <t>1. The date range defaults to the current calendar month.
+          <t xml:space="preserve">1. The date range defaults to the current calendar month.
 2. The location defaults to the user's currently active location.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S1-R3, S7-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S1-R3, S7-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H409" s="2" t="inlineStr">
@@ -21395,11 +22206,13 @@
       </c>
       <c r="G410" s="2" t="inlineStr">
         <is>
-          <t>1. The server returns one page of rows at a time rather than the whole list at once; further rows keep arriving as you scroll to the bottom.
+          <t xml:space="preserve">1. The server returns one page of rows at a time rather than the whole list at once; further rows keep arriving as you scroll to the bottom.
 2. Changing any server-side filter (Date, Location, Category, Vendor), the part search, or the sort returns the FIRST page of the new result set - the list jumps back to the top.
-3. Note for the tester: on this build there are no numbered page controls on the screen - the rows load as you scroll. That is what you should see; record it and carry on with the checks above.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S1-R8).</t>
+3. Note for the tester: on the build tested there were no numbered page controls on the screen - the rows loaded as you scrolled. That is a difference from the specification, which asks for the reports suite's standard page controls. Record what you see and carry on.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S1-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H410" s="2" t="inlineStr">
@@ -21446,10 +22259,12 @@
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
-          <t>1. In every case the report shows the standard reports no-data message "Empty bays, endless possibilities. Get Going!" instead of rows.
+          <t xml:space="preserve">1. In every case the report shows the standard reports no-data message "Empty bays, endless possibilities. Get Going!" instead of rows.
 2. No totals row is shown in any of the cases.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S1-N2, S4-N1, S5-N1, S7-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S1-N2, S4-N1, S5-N1, S7-N2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H411" s="2" t="inlineStr">
@@ -21496,13 +22311,15 @@
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
-          <t>1. The normal, positive-quantity, non-core part appears as one row.
+          <t xml:space="preserve">1. The normal, positive-quantity, non-core part appears as one row.
 2. The core-charge part is never listed — even with a positive quantity — and its value is not counted in the totals row.
 3. The zero-quantity and negative-quantity parts are not listed — only quantities greater than zero are valued.
 4. Only parts meeting BOTH conditions — not a core charge, and on-hand quantity greater than zero — are listed.
 5. A part that has sat without movement for a long time still appears and is still counted — there is no dead-stock exclusion; how long stock has sat makes no difference.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S2-R1, S2-R2, S2-N1, S2-N2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S2-R1, S2-R2, S2-N1, S2-N2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H412" s="2" t="inlineStr">
@@ -21548,10 +22365,12 @@
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
-          <t>1. The part appears twice — one row per location, each with that location's own quantity and values.
+          <t xml:space="preserve">1. The part appears twice — one row per location, each with that location's own quantity and values.
 2. The rows are NOT merged into one combined row; this is the documented v1 behavior.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S2-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S2-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H413" s="2" t="inlineStr">
@@ -21598,10 +22417,12 @@
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
-          <t>1. Unit Sell equals the part's fixed sell price.
+          <t xml:space="preserve">1. Unit Sell equals the part's fixed sell price.
 2. The pricing-matrix markup is NOT applied when a fixed sell price is set — the fixed price wins.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H414" s="2" t="inlineStr">
@@ -21648,9 +22469,11 @@
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
-          <t>1. Unit Sell equals the shop's pricing-matrix markup on cost for that part's category (the same way the parts list resolves it).
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R5).</t>
+          <t xml:space="preserve">1. Unit Sell equals the shop's pricing-matrix markup on cost for that part's category (the same way the parts list resolves it).
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H415" s="2" t="inlineStr">
@@ -21699,11 +22522,13 @@
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
-          <t>1. A part with no category takes no markup, so its Unit Sell equals its Unit Cost.
+          <t xml:space="preserve">1. A part with no category takes no markup, so its Unit Sell equals its Unit Cost.
 2. Such a part shows a Margin of $0.00 and a Margin % of 0.0% — the stock is valued at cost.
 3. Note for the tester: if no part without a category can be created or found, mark this test Blocked rather than Passed or Failed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H416" s="2" t="inlineStr">
@@ -21751,10 +22576,12 @@
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
-          <t>1. Total Sell equals the part's on-hand quantity × Unit Sell, shown as US-dollar currency.
+          <t xml:space="preserve">1. Total Sell equals the part's on-hand quantity × Unit Sell, shown as US-dollar currency.
 2. Total Cost equals the part's on-hand quantity × Unit Cost, shown as US-dollar currency.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R6, S3-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R6, S3-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H417" s="2" t="inlineStr">
@@ -21802,10 +22629,12 @@
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
-          <t>1. Margin equals Total Sell − Total Cost for the part's whole on-hand quantity, shown as US-dollar currency.
+          <t xml:space="preserve">1. Margin equals Total Sell − Total Cost for the part's whole on-hand quantity, shown as US-dollar currency.
 2. Margin is the extended (total) margin, not the per-unit difference.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H418" s="2" t="inlineStr">
@@ -21852,11 +22681,13 @@
       </c>
       <c r="G419" s="2" t="inlineStr">
         <is>
-          <t>1. Margin % shows Margin as a percentage of Total Sell, to one decimal place followed by a percent sign — for example "39.7%".
+          <t xml:space="preserve">1. Margin % shows Margin as a percentage of Total Sell, to one decimal place followed by a percent sign — for example "39.7%".
 2. A Margin % that computes to a real number, including a negative one, shows its signed value.
 3. Margin % shows "—" when Total Sell is zero or negative (the percentage is undefined).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R9, S3-E3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R9, S3-E3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H419" s="2" t="inlineStr">
@@ -21903,15 +22734,17 @@
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
-          <t>1. With a single location in scope the columns appear in this order: Part #, Description, Category, Vendor, Qty, Unit Cost, Unit Sell, Margin, Margin %, Total Sell, Total Cost.
+          <t xml:space="preserve">1. With a single location in scope the columns appear in this order: Part #, Description, Category, Vendor, Qty, Unit Cost, Unit Sell, Margin, Margin %, Total Sell, Total Cost.
 2. Part #, Description, Category, and Vendor are left-aligned.
-3. Every other column is right-aligned.
-4. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all. When it is on, the Location column appears between Vendor and Qty, left-aligned.
+3. Every other column is right-aligned. When it is on, the Location column appears between Vendor and Qty, left-aligned.
 Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
----
-DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Inventory Value report specification version 3 (S3-R1, S3-R2, S7-R6) differs, his decision is the authority.</t>
+The Location column is not one of the columns offered in the column-selection control and you cannot switch it on or off: it follows the location scope by itself — shown when more than one location is in scope, hidden when a single location is in scope.
+Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Inventory Value report specification version 3 (S3-R1, S3-R2, S7-R6), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H420" s="2" t="inlineStr">
@@ -21958,11 +22791,13 @@
       </c>
       <c r="G421" s="2" t="inlineStr">
         <is>
-          <t>1. Qty shows the on-hand quantity to two decimal places, with no currency symbol; fractional quantities display correctly.
+          <t xml:space="preserve">1. Qty shows the on-hand quantity to two decimal places, with no currency symbol; fractional quantities display correctly.
 2. Unit Cost and Unit Sell show per-unit prices as US-dollar currency.
 3. Money values show a leading "$", two decimal places, and thousands separators (for example "$1,234.56"); a negative value shows a leading minus before the "$" ("-$1,234.56"); a genuine zero shows "$0.00".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R3, S3-R4, S3-R5, S3-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R3, S3-R4, S3-R5, S3-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H421" s="2" t="inlineStr">
@@ -22008,11 +22843,13 @@
       </c>
       <c r="G422" s="2" t="inlineStr">
         <is>
-          <t>1. The Total Cost column is pinned to the far right of the row and shown in bold — it is the report's headline column.
+          <t xml:space="preserve">1. The Total Cost column is pinned to the far right of the row and shown in bold — it is the report's headline column.
 2. The Total Cost column header is bold and pinned, matching its cells.
 3. It stays fixed to the right edge while the other columns scroll underneath.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R11, S12-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R11, S12-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H422" s="2" t="inlineStr">
@@ -22058,15 +22895,17 @@
       </c>
       <c r="G423" s="2" t="inlineStr">
         <is>
-          <t>1. On first visit with a single location in scope the visible columns are: Part #, Description, Category, Vendor, Qty, Unit Cost, Unit Sell, Margin %, and Total Cost.
+          <t xml:space="preserve">1. On first visit with a single location in scope the visible columns are: Part #, Description, Category, Vendor, Qty, Unit Cost, Unit Sell, Margin %, and Total Cost.
 2. The Margin and Total Sell columns are hidden by default.
-3. Both can be turned on from the column-selection control and then appear in their fixed positions.
-4. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all. When it is on, the Location column shows between Vendor and Qty.
+3. Both can be turned on from the column-selection control and then appear in their fixed positions. When it is on, the Location column shows between Vendor and Qty.
 Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
----
-DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Inventory Value report specification version 3 (S3-R12, S3-R13, S8-R3, S7-R6) differs, his decision is the authority.</t>
+The Location column is not one of the columns offered in the column-selection control and you cannot switch it on or off: it follows the location scope by itself — shown when more than one location is in scope, hidden when a single location is in scope.
+Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Inventory Value report specification version 3 (S3-R12, S3-R13, S8-R3, S7-R6), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H423" s="2" t="inlineStr">
@@ -22113,12 +22952,14 @@
       </c>
       <c r="G424" s="2" t="inlineStr">
         <is>
-          <t>1. Category shows the part's category name; Vendor shows the part's vendor name.
+          <t xml:space="preserve">1. Category shows the part's category name; Vendor shows the part's vendor name.
 2. A part with no category shows an em dash ("—") in its Category cell.
 3. A part with no vendor shows an em dash ("—") in its Vendor cell.
 4. Note for the tester: on this build a part cannot be saved without a category, so you will not find a part whose Category cell shows "—". Check the Vendor half only.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R14, S3-E1, S3-E2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S3-R14, S3-E1, S3-E2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H424" s="2" t="inlineStr">
@@ -22167,14 +23008,16 @@
       </c>
       <c r="G425" s="2" t="inlineStr">
         <is>
-          <t>1. A totals row is shown at the bottom, with the label "Total" in the Part # column's cell. In the downloaded files the same row is labelled "Totals" — that difference is intended.
+          <t xml:space="preserve">1. A totals row is shown at the bottom, with the label "Total" in the Part # column's cell. In the downloaded files the same row is labelled "Totals" — that difference is intended.
 2. The Description, Category, and Vendor cells are blank; the Unit Cost and Unit Sell cells are blank (a per-unit price has no meaningful sum).
 3. The totals-row Total Cost cell is pinned far right and bold, matching the column, and the row uses the same number formats as the data rows.
 4. The totals row stays visible at the bottom while the rows scroll.
 5. Note for the tester: if the label on screen reads "Totals" instead of "Total", mark this test Failed and report it — do not change the test.
 6. Sorting by any column reorders the data rows only — the totals row stays at the bottom.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S4-R1, S4-R4, S4-R5, S4-R6, S4-R7, S12-R5, S9-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S4-R1, S4-R4, S4-R5, S4-R6, S4-R7, S12-R5, S9-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H425" s="2" t="inlineStr">
@@ -22224,12 +23067,14 @@
       </c>
       <c r="G426" s="2" t="inlineStr">
         <is>
-          <t>1. The totals row sums Qty, Margin, Total Sell, and Total Cost across the FULL filtered result set — every qualifying row for the current Date, Location, Category, Vendor, and part-search selection, not only the rows on the visible page.
+          <t xml:space="preserve">1. The totals row sums Qty, Margin, Total Sell, and Total Cost across the FULL filtered result set — every qualifying row for the current Date, Location, Category, Vendor, and part-search selection, not only the rows on the visible page.
 2. The totals are identical on every page (they do not change as you page).
 3. The hand-summed subset matches the server-computed totals to the cent.
 4. After each filter change the totals row recomputes on the server over the full filtered set, independent of which page is shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S4-R2, S4-R8, S6-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S4-R2, S4-R8, S6-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H426" s="2" t="inlineStr">
@@ -22277,11 +23122,13 @@
       </c>
       <c r="G427" s="2" t="inlineStr">
         <is>
-          <t>1. The totals-row Margin % equals total Margin ÷ total Total Sell × 100 (to one decimal place with a percent sign).
+          <t xml:space="preserve">1. The totals-row Margin % equals total Margin ÷ total Total Sell × 100 (to one decimal place with a percent sign).
 2. It is NOT the average of the row percentages.
 3. It shows "—" when the total Total Sell is zero or negative.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S4-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S4-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H427" s="2" t="inlineStr">
@@ -22327,10 +23174,12 @@
       </c>
       <c r="G428" s="2" t="inlineStr">
         <is>
-          <t>1. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
+          <t xml:space="preserve">1. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
 2. Because the report is valued as of a single date, an All-Time period would be meaningless; its absence is the documented behaviour.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Inventory Value report specification version 3 (S5-R1) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Inventory Value report specification version 3 (S5-R1) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H428" s="2" t="inlineStr">
@@ -22378,11 +23227,13 @@
       </c>
       <c r="G429" s="2" t="inlineStr">
         <is>
-          <t>1. The report values inventory as of the END of the selected range.
+          <t xml:space="preserve">1. The report values inventory as of the END of the selected range.
 2. The date control is an "as of" anchor, not a created-date filter — narrowing it does not select "parts added in that range"; it shows the whole shelf as it stood on that date, so the part stocked before the range still appears.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8820
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S5-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S5-R2).
+AUTOMATION: READY - EXPECT FAIL (SV-8820)
+</t>
         </is>
       </c>
       <c r="H429" s="2" t="inlineStr">
@@ -22429,10 +23280,12 @@
       </c>
       <c r="G430" s="2" t="inlineStr">
         <is>
-          <t>1. The report values the current live stock — the values represent today.
+          <t xml:space="preserve">1. The report values the current live stock — the values represent today.
 2. The part's row reflects today's changed quantity (not yesterday's snapshot), proving the live fallback is in use.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S5-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S5-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H430" s="2" t="inlineStr">
@@ -22479,11 +23332,13 @@
       </c>
       <c r="G431" s="2" t="inlineStr">
         <is>
-          <t>1. The report replays the closest recorded day on or before the end of the selected range.
+          <t xml:space="preserve">1. The report replays the closest recorded day on or before the end of the selected range.
 2. The part's row shows the quantity and values recorded for that day, not today's live stock.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8820
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S5-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S5-R4).
+AUTOMATION: READY - EXPECT FAIL (SV-8820)
+</t>
         </is>
       </c>
       <c r="H431" s="2" t="inlineStr">
@@ -22530,11 +23385,13 @@
       </c>
       <c r="G432" s="2" t="inlineStr">
         <is>
-          <t>1. When the displayed day is an earlier recorded day than the date asked for, the report shows an "As of" indicator naming the day actually shown.
+          <t xml:space="preserve">1. When the displayed day is an earlier recorded day than the date asked for, the report shows an "As of" indicator naming the day actually shown.
 2. When the displayed day matches the date asked for (the common current-view case), the "As of" indicator is not shown — the date control already communicates the date.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8820
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S5-R5, S5-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S5-R5, S5-R6).
+AUTOMATION: READY - EXPECT FAIL (SV-8820)
+</t>
         </is>
       </c>
       <c r="H432" s="2" t="inlineStr">
@@ -22582,12 +23439,14 @@
       </c>
       <c r="G433" s="2" t="inlineStr">
         <is>
-          <t>1. A Custom range lets the user pick a start and end date, and the report values as of the picked end date.
+          <t xml:space="preserve">1. A Custom range lets the user pick a start and end date, and the report values as of the picked end date.
 2. A future end date cannot be chosen — the end date is capped at today.
 3. Changing the date range reloads the report (the loading indicator shows and the rows re-fetch).
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8820
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S5-R7, S5-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S5-R7, S5-R8).
+AUTOMATION: READY - EXPECT FAIL (SV-8820)
+</t>
         </is>
       </c>
       <c r="H433" s="2" t="inlineStr">
@@ -22633,10 +23492,12 @@
       </c>
       <c r="G434" s="2" t="inlineStr">
         <is>
-          <t>1. The report shows the empty state — there is no way to reconstruct inventory value for a date before recording began, because there is no historical backfill.
+          <t xml:space="preserve">1. The report shows the empty state — there is no way to reconstruct inventory value for a date before recording began, because there is no historical backfill.
 2. This forward-capture-only behavior is the documented v1 boundary, not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S5-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S5-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H434" s="2" t="inlineStr">
@@ -22684,11 +23545,13 @@
       </c>
       <c r="G435" s="2" t="inlineStr">
         <is>
-          <t>1. The earlier recorded day still shows the category and vendor names AS THEY WERE RECORDED that day — a recorded day equals what the live report showed that day, even after the rename/delete.
+          <t xml:space="preserve">1. The earlier recorded day still shows the category and vendor names AS THEY WERE RECORDED that day — a recorded day equals what the live report showed that day, even after the rename/delete.
 2. The rename/delete causes no blank Category/Vendor cells and no dropped rows on the recorded day.
 3. The live view (window reaching today) shows the NEW name for the renamed category.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S11-R2, S5-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S11-R2, S5-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H435" s="2" t="inlineStr">
@@ -22735,11 +23598,13 @@
       </c>
       <c r="G436" s="2" t="inlineStr">
         <is>
-          <t>1. The toolbar has a Category filter labeled "Category" and a Vendor filter labeled "Vendor", each allowing one or more selections.
+          <t xml:space="preserve">1. The toolbar has a Category filter labeled "Category" and a Vendor filter labeled "Vendor", each allowing one or more selections.
 2. Selecting one or more categories reloads the report to show only parts in the selected categories.
 3. Selecting one or more vendors reloads the report to show only parts supplied by the selected vendors.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S6-R1, S6-R2, S6-R3, S6-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S6-R1, S6-R2, S6-R3, S6-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H436" s="2" t="inlineStr">
@@ -22787,11 +23652,13 @@
       </c>
       <c r="G437" s="2" t="inlineStr">
         <is>
-          <t>1. Each change re-queries the server and the list jumps back to the top of the new set of rows.
+          <t xml:space="preserve">1. Each change re-queries the server and the list jumps back to the top of the new set of rows.
 2. The filtering covers the ENTIRE data set — matching parts that were further down the list appear — not just a narrowing of the rows currently on screen.
 3. Every change — date range, location, Category, Vendor, part search, sort — reloads the rows from the server; while loading the standard reports loading indicator shows, and existing rows are replaced only when the new data returns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S6-R5, S1-R4, S1-R5, S1-R7, S1-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S6-R5, S1-R4, S1-R5, S1-R7, S1-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H437" s="2" t="inlineStr">
@@ -22838,11 +23705,13 @@
       </c>
       <c r="G438" s="2" t="inlineStr">
         <is>
-          <t>1. With no category selected, parts of all categories are shown.
+          <t xml:space="preserve">1. With no category selected, parts of all categories are shown.
 2. With no vendor selected, parts of all vendors are shown.
 3. With the part search empty, no search narrowing is applied.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S6-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S6-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H438" s="2" t="inlineStr">
@@ -22890,12 +23759,14 @@
       </c>
       <c r="G439" s="2" t="inlineStr">
         <is>
-          <t>1. The search field is page-local, in the report's own toolbar — it is not the application's global search bar (the same toolbar-search pattern used elsewhere in the reports suite).
+          <t xml:space="preserve">1. The search field is page-local, in the report's own toolbar — it is not the application's global search bar (the same toolbar-search pattern used elsewhere in the reports suite).
 2. The report narrows to parts whose part number OR description contains the entered text.
 3. Matching is case-insensitive.
 4. The search applies server-side (whole data set, first page returned); a no-match search shows the no-data message.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S6-R8, S6-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S6-R8, S6-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H439" s="2" t="inlineStr">
@@ -22942,10 +23813,12 @@
       </c>
       <c r="G440" s="2" t="inlineStr">
         <is>
-          <t>1. A part must satisfy EVERY active filter and the search to appear — the Date range, Location, Category, Vendor, and part search combine with AND.
+          <t xml:space="preserve">1. A part must satisfy EVERY active filter and the search to appear — the Date range, Location, Category, Vendor, and part search combine with AND.
 2. The totals row matches the combined filtered set after each step.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S6-R9).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S6-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H440" s="2" t="inlineStr">
@@ -22993,11 +23866,13 @@
       </c>
       <c r="G441" s="2" t="inlineStr">
         <is>
-          <t>1. The toolbar has a location filter labeled "Location" — a multi-select and the rightmost filter — listing the locations the signed-in user has access to, with an "All locations" / "Clear all" toggle.
+          <t xml:space="preserve">1. The toolbar has a location filter labeled "Location" — a multi-select and the rightmost filter — listing the locations the signed-in user has access to, with an "All locations" / "Clear all" toggle.
 2. On a first visit it defaults to the user's currently active location.
-3. With "All locations" active you can tell which location each row's stock belongs to — a location label or marking is shown. (Exactly where and how it appears is confirmed in the build.)
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S7-R1, S7-R2, S12-R3); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+3. With "All locations" active you can tell which location each row's stock belongs to — a location label or marking is shown.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S7-R1, S7-R2, S12-R3); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H441" s="2" t="inlineStr">
@@ -23044,11 +23919,12 @@
       </c>
       <c r="G442" s="2" t="inlineStr">
         <is>
-          <t>1. Each selection change reloads the report scoped to the selected set.
+          <t xml:space="preserve">1. Each selection change reloads the report scoped to the selected set.
 2. With both locations selected, parts from both appear (one row per part per location) and the totals cover both.
-3. The page itself shows which location(s) the report is currently scoped to (the new on-screen scope indicator - exactly where and how it appears is confirmed in the build).
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S7-R3).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S7-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H442" s="2" t="inlineStr">
@@ -23094,10 +23970,12 @@
       </c>
       <c r="G443" s="2" t="inlineStr">
         <is>
-          <t>1. Only the locations the user has access to are offered — a location the user cannot access is never included in the scope.
+          <t xml:space="preserve">1. Only the locations the user has access to are offered — a location the user cannot access is never included in the scope.
 2. If the requested location set resolves to none the user can access, the report falls back to the user's currently active location.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S7-R4, S7-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S7-R4, S7-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H443" s="2" t="inlineStr">
@@ -23143,10 +24021,12 @@
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
-          <t>1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's stock.
+          <t xml:space="preserve">1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's stock.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S7-N1). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S7-N1). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H444" s="2" t="inlineStr">
@@ -23198,18 +24078,20 @@
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
-          <t>1. With Location turned on in the column-selection control, a Location column is shown, inserted between Vendor and Qty.
+          <t xml:space="preserve">1. With Location turned on in the column-selection control, a Location column is shown, inserted between Vendor and Qty.
 2. Each row names the location that row's stock is held at.
 3. NO row ever shows "Multiple" — each row is one part at one location.
-4. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all.
-5. With the Location toggle off the column is not shown and the surrounding columns close up.
-6. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
-7. Both downloads include the Location column in the same position it holds on screen (between Vendor and Qty), naming each row's own location.
+4. With the Location toggle off the column is not shown and the surrounding columns close up.
+5. The Location filter control keeps the same width whichever label it shows — one location, several, or "All locations" — so the toolbar does not shift as you change the selection.
+6. Both downloads include the Location column in the same position it holds on screen (between Vendor and Qty), naming each row's own location.
 Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
----
-DO NOT AUTOMATE YET: part of this behaviour is still waiting on an answer from the product owner. Automating it now could lock in the wrong behaviour.
-The open question is in: Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx — https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Inventory Value report specification version 3 (S7-R6, S7-R7, S3-R1, S12-R10, S10-R15) differs, his decision is the authority.</t>
+The Location column is not one of the columns offered in the column-selection control and you cannot switch it on or off: it follows the location scope by itself — shown when more than one location is in scope, hidden when a single location is in scope.
+Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Inventory Value report specification version 3 (S7-R6, S7-R7, S3-R1, S12-R10, S10-R15), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H445" s="2" t="inlineStr">
@@ -23256,11 +24138,13 @@
       </c>
       <c r="G446" s="2" t="inlineStr">
         <is>
-          <t>1. The icon button's tooltip reads "Column Selection".
+          <t xml:space="preserve">1. The icon button's tooltip reads "Column Selection".
 2. Toggling a column off hides it from the table; toggling it on shows it again.
 3. The Total Cost column is always shown and cannot be turned off.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S8-R1, S8-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S8-R1, S8-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H446" s="2" t="inlineStr">
@@ -23306,10 +24190,12 @@
       </c>
       <c r="G447" s="2" t="inlineStr">
         <is>
-          <t>1. Whatever columns are shown, they appear in the fixed left-to-right order - with Location, when it is turned on in the column-selection control, between Vendor and Qty (Part #, Description, Category, Vendor, Qty, Unit Cost, Unit Sell, Margin, Margin %, Total Sell, Total Cost) - toggling visibility never reorders columns.
+          <t xml:space="preserve">1. Whatever columns are shown, they appear in the fixed left-to-right order - with Location, when it is turned on in the column-selection control, between Vendor and Qty (Part #, Description, Category, Vendor, Qty, Unit Cost, Unit Sell, Margin, Margin %, Total Sell, Total Cost) - toggling visibility never reorders columns.
 2. Total Cost is always the last column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S8-R4, S3-R1, S7-R6). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S8-R4, S3-R1, S7-R6). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H447" s="2" t="inlineStr">
@@ -23357,10 +24243,12 @@
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
-          <t>1. On return and after a reload, the report restores the saved date range, category selection, vendor selection, part search text, location selection, column selection, and sort.
+          <t xml:space="preserve">1. On return and after a reload, the report restores the saved date range, category selection, vendor selection, part search text, location selection, column selection, and sort.
 2. In a different browser the report shows the defaults instead — persistence is per browser, not tied to the user's account.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S8-R5, S9-R5).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S8-R5, S9-R5).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H448" s="2" t="inlineStr">
@@ -23406,10 +24294,12 @@
       </c>
       <c r="G449" s="2" t="inlineStr">
         <is>
-          <t>1. The report loads normally — the saved category or vendor that is no longer present in the data is dropped from the selection instead of breaking the view (the defensive-restore rule applied to the path these steps drive).
+          <t xml:space="preserve">1. The report loads normally — the saved category or vendor that is no longer present in the data is dropped from the selection instead of breaking the view (the defensive-restore rule applied to the path these steps drive).
 2. All other saved settings are still restored.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S8-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S8-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H449" s="2" t="inlineStr">
@@ -23455,10 +24345,12 @@
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
-          <t>1. The rows are sorted by Total Cost, highest first (descending).
+          <t xml:space="preserve">1. The rows are sorted by Total Cost, highest first (descending).
 2. The order holds across pages (page 2 continues below page 1's lowest value) — the server applies the default order over the full set.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S9-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S9-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H450" s="2" t="inlineStr">
@@ -23506,11 +24398,13 @@
       </c>
       <c r="G451" s="2" t="inlineStr">
         <is>
-          <t>1. Clicking a column that is not the active sort sorts it ascending; clicking the active sort column again toggles it to descending; there is no third "cleared" state.
+          <t xml:space="preserve">1. Clicking a column that is not the active sort sorts it ascending; clicking the active sort column again toggles it to descending; there is no third "cleared" state.
 2. Each header click re-fetches the data from the server ordered by the chosen column and direction, returning the FIRST page of the re-sorted result set.
 3. Only one column sorts at a time.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S9-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S9-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H451" s="2" t="inlineStr">
@@ -23557,10 +24451,12 @@
       </c>
       <c r="G452" s="2" t="inlineStr">
         <is>
-          <t>1. Money and numeric columns sort by their underlying value (so $1,100.00 is treated as more than $900.00, not compared as text).
+          <t xml:space="preserve">1. Money and numeric columns sort by their underlying value (so $1,100.00 is treated as more than $900.00, not compared as text).
 2. Text columns (Part #, Description, Category, Vendor) sort as text, case-insensitively ("apple" and "Apple" sort together).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S9-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S9-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H452" s="2" t="inlineStr">
@@ -23607,10 +24503,12 @@
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
-          <t>1. The menu holds an option labeled "Download (PDF)" and an option labeled "Download (CSV)".
+          <t xml:space="preserve">1. The menu holds an option labeled "Download (PDF)" and an option labeled "Download (CSV)".
 2. Each option downloads a file of the current view in the chosen format.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S10-R1, S10-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S10-R1, S10-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H453" s="2" t="inlineStr">
@@ -23659,16 +24557,21 @@
       </c>
       <c r="G454" s="2" t="inlineStr">
         <is>
-          <t>1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total Cost last.
+          <t xml:space="preserve">1. Both downloads include only the columns currently shown, in the same left-to-right order as the screen, with Total Cost last.
 2. Both downloads honor the current date, category, vendor, location, and part-search filters, and apply the current sort.
 3. Both downloads include a totals row labeled "Totals" matching the on-screen totals (the full-filtered-set totals).
-4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to (exact position in the file is confirmed in the build).
-5. Note for the tester: the files carry the Location column whenever it is showing on screen (it sits between Vendor and Qty). Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all.
+4. Each download (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to.
+5. Note for the tester: the files carry the Location column whenever it is showing on screen (it sits between Vendor and Qty).
 On this build the spreadsheet file ignores the columns you picked and puts them in a different order from the screen, so point 1 above will not match - record what you see and carry on.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8823
 Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
----
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Inventory Value report specification version 3 (S10-R3, S10-R4, S10-R5, S10-R6, S10-R15) differs, his decision is the authority.</t>
+The Location column is not one of the columns offered in the column-selection control and you cannot switch it on or off: it follows the location scope by itself — shown when more than one location is in scope, hidden when a single location is in scope.
+Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
+---
+---
+This is the expected behaviour as per the Inventory Value report specification version 3 (S10-R3, S10-R4, S10-R5, S10-R6, S10-R15), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+</t>
         </is>
       </c>
       <c r="H454" s="2" t="inlineStr">
@@ -23714,13 +24617,15 @@
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
-          <t>1. Money uses two decimals and Margin % one decimal in both files; an undefined Margin % shows "—".
+          <t xml:space="preserve">1. Money uses two decimals and Margin % one decimal in both files; an undefined Margin % shows "—".
 2. In the CSV, money values are written as plain numbers with two decimals and NO thousands separators (so they parse cleanly in a spreadsheet).
 3. The PDF uses the same on-screen currency formatting with the "$" and thousands separators.
 On this build the money in the spreadsheet file comes out as "$11,176.88" - with a dollar sign and a comma - instead of the plain number described in point 2 above.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8823
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S10-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S10-R7).
+AUTOMATION: READY - EXPECT FAIL (SV-8823)
+</t>
         </is>
       </c>
       <c r="H455" s="2" t="inlineStr">
@@ -23769,12 +24674,14 @@
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
-          <t>1. The PDF header shows the report name "Inventory Value", the organization name, the selected period, and an "as of" line naming the day the values represent (or a message that no snapshot is available for the period).
+          <t xml:space="preserve">1. The PDF header shows the report name "Inventory Value", the organization name, the selected period, and an "as of" line naming the day the values represent (or a message that no snapshot is available for the period).
 2. The PDF shows the shop logo at the top when one is set.
 3. The CSV never includes a logo.
 4. Note for the tester: the two files phrase the as-of line differently - the PDF reads "As of 2026-08-04", and in the spreadsheet it is one of the short summary lines that sit above the column headings, reading "As of: 2026-08-04" (with a colon). Both are correct; do not raise the difference, and do not count the summary lines - more of them may be added.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Inventory Value report specification version 3 (S10-R8, S10-R9) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Inventory Value report specification version 3 (S10-R8, S10-R9) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H456" s="2" t="inlineStr">
@@ -23820,10 +24727,12 @@
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
-          <t>1. The PDF is named "inventory-value-report.pdf".
+          <t xml:space="preserve">1. The PDF is named "inventory-value-report.pdf".
 2. The CSV is named "inventory-value-report.csv".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S10-R10).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S10-R10).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H457" s="2" t="inlineStr">
@@ -23870,11 +24779,13 @@
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
-          <t>1. The export contains the FULL filtered set — every qualifying row across all pages, not only the rows loaded in the browser.
+          <t xml:space="preserve">1. The export contains the FULL filtered set — every qualifying row across all pages, not only the rows loaded in the browser.
 2. Parts from the later pages are present.
 3. The export is generated server-side against the current filters, part search, and sort — it is not built from the rows currently in the browser.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S10-R11).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S10-R11).
+AUTOMATION: HOLD - this part of the report is not built yet
+</t>
         </is>
       </c>
       <c r="H458" s="2" t="inlineStr">
@@ -23921,13 +24832,15 @@
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
-          <t>1. Neither the PDF nor the CSV is produced.
+          <t xml:space="preserve">1. Neither the PDF nor the CSV is produced.
 2. The user sees the message: "This report is too large to export. Narrow the date range or filters, then try again." (a blocking notification; no file).
 3. After narrowing the filters below the cap, the download works again.
 4. Note for the tester: on this environment the biggest view you can build is about 9,275 rows, which is under the cap, so you cannot make this message appear here. If the PDF fails with a plain error instead, that is the separate timeout problem - see the Inventory Value export-notification case.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S10-R12).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S10-R12).
+AUTOMATION: READY - EXPECT FAIL (SV-8818)
+</t>
         </is>
       </c>
       <c r="H459" s="2" t="inlineStr">
@@ -23975,13 +24888,15 @@
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
-          <t>1. Success notifications read verbatim: "Inventory Value report exported (PDF)" and "Inventory Value report exported (CSV)".
+          <t xml:space="preserve">1. Success notifications read verbatim: "Inventory Value report exported (PDF)" and "Inventory Value report exported (CSV)".
 2. Failure notifications read verbatim: "Failed to export inventory value report (pdf)" and "Failed to export inventory value report (csv)".
 3. The lower-case "(pdf)"/"(csv)" on failure vs the upper-case success ones is the documented spec wording — expected, not a bug.
 4. Note for the tester: on this build a PDF download of a large view fails with a plain error - "An error occurred. We're sorry for this inconvenience, please try again a bit later later." - after roughly half a minute. It is a timeout, not the too-large-to-export message. Narrow the view with the part search or a single location and the PDF works. The CSV of the same view always works and is quick. Record the failure; it is a known problem, not a mistake you made.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S10-R13, S10-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S10-R13, S10-R14).
+AUTOMATION: READY - EXPECT FAIL (SV-8818)
+</t>
         </is>
       </c>
       <c r="H460" s="2" t="inlineStr">
@@ -24029,7 +24944,7 @@
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
-          <t>1. The narrowed PDF downloads successfully.
+          <t xml:space="preserve">1. The narrowed PDF downloads successfully.
 2. On the whole list the PDF either downloads successfully too, or is refused politely with the message "This report is too large to export. Narrow the date range or filters, then try again." Either of those is a pass.
 3. The CSV of that same whole list downloads successfully and quickly.
 4. Once the view is narrowed the PDF works again.
@@ -24037,7 +24952,9 @@
 6. Note for the tester: the polite refusal message in item 2 is the correct behaviour. The plain error in item 5 is the problem being tracked. Tell the two apart by the wording.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S10-R11, S10-R12, S10-R14).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S10-R11, S10-R12, S10-R14).
+AUTOMATION: READY - EXPECT FAIL (SV-8818)
+</t>
         </is>
       </c>
       <c r="H461" s="2" t="inlineStr">
@@ -24084,10 +25001,12 @@
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
-          <t>1. The table has white column headers and white data cells, with no alternating row shading.
+          <t xml:space="preserve">1. The table has white column headers and white data cells, with no alternating row shading.
 2. The table sits on the standard soft blue-grey report backdrop.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S12-R1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S12-R1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H462" s="2" t="inlineStr">
@@ -24133,10 +25052,12 @@
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
-          <t>1. In the toolbar, the three-dot download menu sits leftmost in the action cluster, followed by the Column Selection control.
+          <t xml:space="preserve">1. In the toolbar, the three-dot download menu sits leftmost in the action cluster, followed by the Column Selection control.
 2. The toolbar filters run, left to right: the date-range control, the part search, the Category filter, the Vendor filter, and the Location filter (rightmost).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S12-R2, S12-R3).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S12-R2, S12-R3).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H463" s="2" t="inlineStr">
@@ -24183,11 +25104,13 @@
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
-          <t>1. Long text values (Description, Category, Vendor) are truncated with an ellipsis when they overflow their column.
+          <t xml:space="preserve">1. Long text values (Description, Category, Vendor) are truncated with an ellipsis when they overflow their column.
 2. The full value is available on hover.
 3. The Part # is never truncated.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S12-R6).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S12-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H464" s="2" t="inlineStr">
@@ -24234,11 +25157,13 @@
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
-          <t>1. The report supports dark mode: the page background, the toolbar, and the table cells all switch to their dark equivalents rather than staying light.
+          <t xml:space="preserve">1. The report supports dark mode: the page background, the toolbar, and the table cells all switch to their dark equivalents rather than staying light.
 2. In dark mode you can read the toolbar text and the cell text at a glance, and the "—" glyph in an empty Category or Vendor cell is clearly visible against the dark cell behind it — it does not disappear into the background.
 3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether everything is easy to read in dark mode, and only report it if something is hard to see. (The exact colour values behind this are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S12-R7).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S12-R7).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H465" s="2" t="inlineStr">
@@ -24286,11 +25211,13 @@
       </c>
       <c r="G466" s="2" t="inlineStr">
         <is>
-          <t>1. The active sort direction is indicated visually on the header.
+          <t xml:space="preserve">1. The active sort direction is indicated visually on the header.
 2. Each sortable column header exposes its sort state to assistive technology (for example, ascending/descending/none).
 3. The exposed state updates when the direction toggles.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S12-R8).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S12-R8).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H466" s="2" t="inlineStr">
@@ -24337,9 +25264,11 @@
       </c>
       <c r="G467" s="2" t="inlineStr">
         <is>
-          <t>1. Each icon-only control carries an accessible name exposed to assistive technology (it is not announced as an unnamed button).
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S12-R9).</t>
+          <t xml:space="preserve">1. Each icon-only control carries an accessible name exposed to assistive technology (it is not announced as an unnamed button).
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S12-R9).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H467" s="2" t="inlineStr">
@@ -24386,11 +25315,13 @@
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
-          <t>1. The report is listed and opens normally for a user holding the ordinary reports access.
-2. No additional report-specific permission is required — for now the one ordinary reports access covers all six of the new reports.
-3. Note for the tester: for now ONE ordinary reports access opens all six of these new reports; none of them has a permission of its own. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (Story 1 Prerequisites); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.</t>
+          <t xml:space="preserve">1. The report is listed and opens normally for a user holding the ordinary reports access.
+2. No additional report-specific permission is required — the specification allows the one ordinary reports access to cover all six of the new reports.
+3. Note for the tester: the specification allows ONE ordinary reports access for all six of these new reports and no per-report permission. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (Story 1 Prerequisites); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H468" s="2" t="inlineStr">
@@ -24436,9 +25367,11 @@
       </c>
       <c r="G469" s="2" t="inlineStr">
         <is>
-          <t>1. The report does not appear in the navigation for this user.
----
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S1-N1).</t>
+          <t xml:space="preserve">1. The report does not appear in the navigation for this user.
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S1-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H469" s="2" t="inlineStr">
@@ -24487,11 +25420,13 @@
       </c>
       <c r="G470" s="2" t="inlineStr">
         <is>
-          <t>1. Once per day, overnight, one row per then-in-stock, non-core part is recorded for every location across every organization, under that day's calendar date.
+          <t xml:space="preserve">1. Once per day, overnight, one row per then-in-stock, non-core part is recorded for every location across every organization, under that day's calendar date.
 2. Each row captures the part's identity (part, category, vendor), on-hand quantity, unit cost, unit sell, total cost, and total sell, stored to the cent.
 3. A location with no in-stock parts on the date simply has no rows for that date — this is valid, not an error.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S11-R1, S11-R4).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S11-R1, S11-R4).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H470" s="2" t="inlineStr">
@@ -24541,11 +25476,13 @@
       </c>
       <c r="G471" s="2" t="inlineStr">
         <is>
-          <t>1. The captured parts use the same in-stock, non-core scope as the live report (Story 2) — the core-charge and zero-quantity parts are NOT captured.
+          <t xml:space="preserve">1. The captured parts use the same in-stock, non-core scope as the live report (Story 2) — the core-charge and zero-quantity parts are NOT captured.
 2. The captured values use the same valuation as the live report (Story 3), including the sell-price fallback chain.
 3. A recorded day equals what the live report would have shown that day — the as-of view of the captured date matches the noted live values.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S11-R2).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S11-R2).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H471" s="2" t="inlineStr">
@@ -24593,14 +25530,16 @@
       </c>
       <c r="G472" s="2" t="inlineStr">
         <is>
-          <t>1. Re-running the capture for a date replaces that date's rows for each location — the existing rows for that location and date are removed, then re-inserted from current data.
+          <t xml:space="preserve">1. Re-running the capture for a date replaces that date's rows for each location — the existing rows for that location and date are removed, then re-inserted from current data.
 2. No duplicate rows exist for the same part, location, and date.
 3. The capture is idempotent and self-healing from current data.
 4. No rows exist for dates before capture began — there is no backfill.
 5. A re-run always records current truth under the CURRENT date; it cannot reconstruct a past date.
 6. A past date's stored rows are unchanged by a current re-run.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S11-R3, S11-R5, S5-E1).</t>
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S11-R3, S11-R5, S5-E1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H472" s="2" t="inlineStr">
@@ -24648,12 +25587,15 @@
       </c>
       <c r="G473" s="2" t="inlineStr">
         <is>
-          <t>1. For ages 0–13 months (measured from the current date), every daily capture is kept — full daily per-part detail, covering the report's longest date preset (366 days / This Year / Last Year) entirely at daily resolution.
+          <t xml:space="preserve">1. For ages 0–13 months (measured from the current date), every daily capture is kept — full daily per-part detail, covering the report's longest date preset (366 days / This Year / Last Year) entirely at daily resolution.
 2. For ages older than 13 months, only the last capture of each calendar month is retained; the other daily captures in that band are pruned.
 3. Pruning runs as part of, or alongside, the nightly capture.
 ---
 Note for the tester: this one needs records going back more than a year, and this test system only holds a few days of records so far. If there is nothing old enough to look at, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S11-R6).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S11-R6).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H473" s="2" t="inlineStr">
@@ -24701,12 +25643,15 @@
       </c>
       <c r="G474" s="2" t="inlineStr">
         <is>
-          <t>1. The as-of resolution serves the thinned history unchanged: the report resolves to the nearest earlier retained capture ("closest recorded day on or before"), even when adjacent retained captures are up to a month apart.
+          <t xml:space="preserve">1. The as-of resolution serves the thinned history unchanged: the report resolves to the nearest earlier retained capture ("closest recorded day on or before"), even when adjacent retained captures are up to a month apart.
 2. The "As of" indicator names the day actually shown.
 3. A requested date whose covering captures have all been pruned resolves to the nearest earlier retained capture, or shows the empty state if none remains.
 ---
 Note for the tester: this one needs records going back more than a year, and this test system only holds a few days of records so far. If there is nothing old enough to look at, mark this test BLOCKED - do not mark it failed, and do not raise it as a problem.
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S11-E1, S11-R6, S5-R4, S5-R5, S5-N1).</t>
+---
+This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Inventory Value report specification version 3 (S11-E1, S11-R6, S5-R4, S5-R5, S5-N1).
+AUTOMATION: READY
+</t>
         </is>
       </c>
       <c r="H474" s="2" t="inlineStr">

--- a/testrail-import/report-suite-v1-testrail-import.xlsx
+++ b/testrail-import/report-suite-v1-testrail-import.xlsx
@@ -530,7 +530,8 @@
 4. The browser tab title reads "Sales By Customer - Report | ShopView".
 5. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S1-R1, S1-R3, S1-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S1-R1, S1-R3, S1-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - waiting on an answer from the product owner
 </t>
         </is>
@@ -583,7 +584,8 @@
 3. Ordinary reports access alone is enough — this report does NOT need a permission of its own.
 4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S1-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S1-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -637,7 +639,8 @@
 3. The gate is the ordinary reports access — there is no separate Sales By Customer permission to remove.
 4. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S1-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S1-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -689,7 +692,8 @@
           <t xml:space="preserve">1. The destination page shows the application's standard access-denied state.
 2. Pressing back returns you to the Sales By Customer report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S9-N2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S9-N2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -745,7 +749,8 @@
 3. A requested location the user does not have access to is ignored — the report does NOT widen to the whole organization.
 4. The report data never includes invoices from a location the user does not have access to.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S4-R7, S4-R8, S4-R9, S4-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S4-R7, S4-R8, S4-R9, S4-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -798,7 +803,8 @@
 2. The only reports permission offered is the ordinary reports access, and that one covers all six of the new reports.
 3. Note for the tester: the product owner has ruled that every report in this suite opens with the ordinary reports access, and the written description now says the same. If the build still demands a separate Sales By Customer permission, mark this test Failed and report it against the change already raised with the developers — do not change the test. You may also find a "Sales By Customer" permission still listed for an administrator to switch on and off: that should have been hidden from the screen, so please report that too. If it is listed at all, that is a difference from the specification — report that it is still visible.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S1-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S1-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -849,7 +855,8 @@
 3. The named periods use the application's standard shared calendar boundaries - this is one shared chooser used by all six reports.
 3. There is no "All Time" option.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Customer report specification version 14 (S2-R1, S2-R2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Customer report specification version 14 (S2-R1, S2-R2) says something different, his decision is the later word and is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -901,7 +908,8 @@
 2. A range of 366 days or fewer applies normally.
 3. A range wider than 366 days cannot be applied — the report prevents the selection rather than loading the wider range.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Customer report specification version 14 (S2-R3, S2-R4, S2-N2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Customer report specification version 14 (S2-R3, S2-R4, S2-N2) says something different, his decision is the later word and is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -952,7 +960,8 @@
           <t xml:space="preserve">1. The chosen date range value is written into the page link.
 2. Opening that link in a browser with no saved view for this report restores the sender's date range.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S2-R6, S2-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S2-R6, S2-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1008,7 +1017,8 @@
 4. With "Parts &amp; Service" selected, no product-type filter is applied — both S and P invoices are included and counts/totals cover both.
 5. The whole invoice is classified by its number prefix — there is no per-line-item split.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1063,7 +1073,8 @@
 4. Activating "All locations" selects every listed location at once; activating it again clears them all at once.
 5. For a user with access to only one location the Location filter is NOT shown at all — the report simply shows that one location's data.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S4-R1, S4-R2, S4-R3). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S4-R1, S4-R2, S4-R3). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1118,7 +1129,8 @@
 3. With "All locations," the report includes data from every location the user has access to.
 4. With "All locations" active you can tell which location each row's data belongs to — a location label or marking is shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S4-R5, S4-R6); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S4-R5, S4-R6); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1175,14 +1187,13 @@
 2. A customer or asset row whose invoices are all at one location shows that location's name.
 3. A customer or asset row whose invoices come from more than one location shows "Multiple".
 4. An invoice row always shows its own exact location — never "Multiple".
-5. Location is one of the columns in the column-selection control, and with more than one location SELECTED it is already switched on for you - you do not have to turn it on. You can still switch it off. If the signed-in person only has access to ONE location, Location is not offered in the column-selection list at all.
-6. With a single location in scope the Location column is hidden and the surrounding columns close up with no gap.
+5. If the signed-in person only has access to ONE location, no Location column is shown to them at all and Location is not offered in their column-selection list.
+6. When the Location column is not shown, the surrounding columns close up with no gap.
 7. Every one of the four downloads also contains the Location column, in the same position it holds on screen, showing the same values you just read: a location name on a row whose invoices are all at one location, "Multiple" on a row that aggregates more than one, and the invoice's own location on an invoice row.
-Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
----
----
-This is the expected behaviour as per the Sales By Customer report specification version 14 (S4-R12, S4-R12a, S4-R13, S20-R19), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+---
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S4-R12, S4-R12a, S4-R13, S20-R19). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: one requirement says it is shown by default and can be toggled there, and the list of toggleable columns in another does not include it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
+AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
 </t>
         </is>
       </c>
@@ -1234,7 +1245,8 @@
 3. Before typing, the dropdown shows the pinned all/clear control at the top and a "Search customers…" hint; individual customers are revealed by typing.
 4. The hint yields to the typed query while you are searching.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R1, S18-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R1, S18-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1287,7 +1299,8 @@
 2. The list is scoped to the active date range, Product Type, and location.
 3. A selected customer is shown with a checkmark.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1340,7 +1353,8 @@
 3. The control is pinned to the top of the dropdown in both states.
 4. After "Clear all": the report shows the empty-state message "No sales data found for the selected filters.", the totals row shows zeros, and the collapsed label reads "None."
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R3, S18-N1, S17-E1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R3, S18-N1, S17-E1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1396,7 +1410,8 @@
 3. The all-customers state is an explicit state — while it is active, any customer that appears later (new data) is included automatically.
 4. After the filter change the filter stays in the all-customers state (label still "All customers") and every customer matching the new filters is included — including the newly-appearing one, with no manual re-selection.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R4, S18-R5, S18-R9, S18-E1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R4, S18-R5, S18-R9, S18-E1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1450,7 +1465,8 @@
 3. With more than one selected the label reads "N selected" where N is the number of selected customers (for example "3 selected").
 4. While typing, the field shows the query text instead of the summary label; the summary label returns when the query is cleared or the field loses focus.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1502,7 +1518,8 @@
 2. The table refreshes as a fresh first page of results.
 3. The totals row updates to cover only the selected customers' matching invoices.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R5, S18-R11).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R5, S18-R11).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1555,7 +1572,8 @@
 3. Customer C (newly present) is NOT auto-selected and is not shown.
 4. The Customer filter selection itself is not cleared by the date change.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R9, S18-E1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R9, S18-E1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1610,7 +1628,8 @@
 4. The count reflects the active date range, Product Type, and location — it drops when the range is narrowed; it is not a lifetime count.
 5. Note for the tester: you do not need to measure anything and you do not need any tool for item 3. Just say whether the count looks the right size and is easy to read, and only report it if it looks obviously wrong. (The exact colour and weight behind this are design-token values the design and engineering team check with their own tooling.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-R1, S7-R2, S7-R3, S7-R4, S7-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S7-R1, S7-R2, S7-R3, S7-R4, S7-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1660,7 +1679,8 @@
         <is>
           <t xml:space="preserve">1. The customer is not shown — there are no zero-value placeholder rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S7-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1717,7 +1737,8 @@
 6. Each chevron toggles back to collapsed on a second activation.
 7. Collapsing customer A does not affect customer B's expansion; each asset's expansion state is likewise independent.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R1, S8-R2, S8-R5, S8-R5a, S8-R5b, S8-R5c, S8-R15).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R1, S8-R2, S8-R5, S8-R5a, S8-R5b, S8-R5c, S8-R15).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1768,7 +1789,8 @@
 2. Each detail row shows the invoice number (as a link), the invoice date, and the per-invoice Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, and Subtotal.
 3. The invoice date shows in the format "Mon DD YYYY" — for example, May 14 2026.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R4, S8-R12, S8-R12a, S20-R14).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R4, S8-R12, S8-R12a, S20-R14).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1819,7 +1841,8 @@
           <t xml:space="preserve">1. Invoices referencing the same vehicle record (same vehicle id) group into ONE asset row — no duplicate rows for the same vehicle.
 2. An older invoice with no vehicle id on file groups by the invoice's own stored vehicle snapshot instead.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1870,7 +1893,8 @@
 2. The no-vehicle work collects under a single row labeled "Parts Sales," always sorted last among that customer's assets.
 3. Changing the column sort does not change the asset order — assets stay A→Z with "Parts Sales" last.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R6, S8-R6a, S10-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R6, S8-R6a, S10-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1922,7 +1946,8 @@
 2. Clicking it expands every customer on the current page in one action — it acts on the currently visible customers only, not the whole result set.
 3. With all visible customers expanded, the icon switches to "collapse" and the tooltip reads "Collapse all"; clicking collapses them all.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R16, S8-R17, S8-R18, S8-R19).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R16, S8-R17, S8-R18, S8-R19).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -1975,7 +2000,8 @@
 2. A change that re-fetches customer rows (date range, Product Type, location, Customer selection, or sort) collapses all expanded rows.
 3. While the re-fetch is in flight the table shows the standard loading state; when it clears, the page shows the first page of the newly ordered set — the customers on the page can change.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R20, S8-R21, S10-R8a, S10-R8b, S10-R8c).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R20, S8-R21, S10-R8a, S10-R8b, S10-R8c).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2025,7 +2051,8 @@
           <t xml:space="preserve">1. The single-invoice asset expands and shows exactly one invoice detail row.
 2. Customer B shows a single "Parts Sales" row and no vehicle rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-E1, S8-E2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-E1, S8-E2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2074,7 +2101,8 @@
         <is>
           <t xml:space="preserve">1. The no-vehicle S invoice appears under that customer's "Parts Sales" row — the bucket collects work by the ABSENCE of a vehicle, not by the invoice-number prefix.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-E3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-E3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2127,7 +2155,8 @@
 2. It is excluded from the customer's "(N)" count and from every row total, regardless of the Product Type filter.
 3. The customer/asset totals drop by exactly that invoice's amounts.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-R7, S7-N2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S7-R7, S7-N2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2181,7 +2210,8 @@
 4. A customer summary row reads as heavier than the invoice rows under it, and its Subtotal cell is the heaviest cell on that row.
 5. Note for the tester: you do not need to measure anything and you do not need any tool for item 4. Just say whether the summary row stands out from the invoice rows and whether its Subtotal looks the boldest, and only report it if it looks obviously wrong. (The exact weights behind this are design-token values the design and engineering team check with their own tooling.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-R8, S7-R9, S7-R10, S7-R15, S7-R16).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S7-R8, S7-R9, S7-R10, S7-R15, S7-R16).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2233,7 +2263,8 @@
 4. For asset (d) (no VIN, Unit #, or plate), the label reads "Unknown Asset" when all three are missing.
 5. Note whether the year/make/model text still appears anywhere in the row - the update says the VIN identifier REPLACES the year/make/model label; confirm the exact rendering in the build.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R7, S8-R8, S8-R9, S8-R10). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R7, S8-R8, S8-R9, S8-R10). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2284,7 +2315,8 @@
           <t xml:space="preserve">1. The duplicate labels are suffixed " (#1)" and " (#2)" (and so on for more duplicates).
 2. The numbering is fixed and repeatable — after a reload the same vehicle keeps the same number.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R11).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R11).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2335,7 +2367,8 @@
 2. A service invoice opens the associated work order's Finance tab.
 3. A parts invoice opens the associated part sale's Part Requests tab.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S9-R1, S9-R2, S9-R2a, S9-R2b).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S9-R1, S9-R2, S9-R2a, S9-R2b).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2388,7 +2421,8 @@
 2. Pressing back returns to the report with its filters, sort, and columns restored exactly as set.
 3. Expanded rows are shown collapsed again — expansion is not restored (this is the specified behavior, not a defect).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S9-R3, S9-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S9-R3, S9-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2440,7 +2474,8 @@
 3. The link has no underline at rest, on hover, or after it has been clicked.
 4. The link never recolors to the browser's visited-link (purple) color.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S9-R5, S9-R6, S9-R7, S9-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S9-R5, S9-R6, S9-R7, S9-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2491,7 +2526,8 @@
           <t xml:space="preserve">1. The destination page shows the application's standard "not found" state.
 2. Pressing back returns you to the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S9-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S9-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2545,7 +2581,8 @@
 2. Text columns sort alphabetically; numeric columns sort by value (not as text).
 3. Sorting reorders only the customer summary rows — asset rows keep their own order (A→Z with "Parts Sales" last) and invoice rows keep their order under their asset.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S10-R1, S10-R2, S10-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S10-R1, S10-R2, S10-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2596,7 +2633,8 @@
           <t xml:space="preserve">1. On first load, rows are ordered by Customer name, ascending, case-insensitive (a lower-case "acme" sorts by letter, not after all capitals).
 2. Clicking a column header replaces the default with that column's sort.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S10-R4, S10-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S10-R4, S10-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2646,7 +2684,8 @@
           <t xml:space="preserve">1. Ascending: the em-dash (missing) row sorts to the bottom.
 2. Descending: the em-dash row sorts to the top.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S10-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S10-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2696,7 +2735,8 @@
           <t xml:space="preserve">1. Customer rows order by each customer's most recent invoice date in the current view.
 2. The Date cells on customer rows stay blank — the sort still works.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S10-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S10-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2749,7 +2789,8 @@
 3. Labor Margin = Labor Invoiced minus labor cost; Parts Margin = Parts Invoiced minus parts cost.
 4. Margin = Labor Margin + Parts Margin — it does NOT include any Shop Supplies amount (shop supplies add to Subtotal but add no profit to Margin).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-R6, S11-R1, S4-R12, S20-R19).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S7-R6, S11-R1, S4-R12, S20-R19).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2802,7 +2843,8 @@
 3. Margin % is monochrome — no green or red coloring.
 4. The same calculation and format apply to customer rows, asset rows, and invoice rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S7-R11, S7-R12, S7-R13, S7-R14).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S7-R11, S7-R12, S7-R13, S7-R14).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2856,7 +2898,8 @@
 5. A zero/break-even value shows 0.0 in the default text color.
 6. The same calculation, label, format, and coloring apply on customer, asset, and invoice rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S12-R1, S12-R2, S12-R3, S12-R4, S12-R5, S12-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S12-R1, S12-R2, S12-R3, S12-R4, S12-R5, S12-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2907,7 +2950,8 @@
 2. A value that rounds to 0.0 (for example +0.04) is shown as 0.0 in the default text color (not +0.0 in green).
 3. A negative value shows a minus sign and one decimal — for example, -0.5.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S12-N1, S12-E1, S12-E2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S12-N1, S12-E1, S12-E2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -2959,7 +3003,8 @@
 2. A customer's asset subtotals sum exactly to the customer's row total.
 3. This holds for every financial column, not only Subtotal.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R13).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R13).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3012,7 +3057,8 @@
 3. Subtotal values are shown in bold on the header, on every customer, asset and invoice row, and on the totals row.
 4. Check it still holds after two changes: narrow the date range so fewer rows match, then sort by a different column. Subtotal stays the rightmost column, stays pinned, and stays bold both times.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S11-R1, S11-R2, S11-R3, S11-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S11-R1, S11-R2, S11-R3, S11-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3063,7 +3109,8 @@
           <t xml:space="preserve">1. The totals row is computed over the full set of customers matching the active filters (date range, Product Type, location, Customer filter).
 2. The totals do not change when you move between pages — they never reflect only the visible page.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3115,11 +3162,11 @@
 2. Hovering it shows the tooltip "Column Selection."
 3. The panel lists nine toggles, in order: Date, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %.
 4. With no saved selection, all nine toggleable columns default to visible.
-5. Note for the tester: this panel lists nine toggles and no Location toggle. The specification is currently inconsistent on this one point - one requirement says a Location toggle should be here for anyone who can reach more than one branch, while the list of nine does not include it. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
----
----
-This is the expected behaviour as per the Sales By Customer report specification version 14 (S13-R1, S13-R2, S13-R3, S13-R4, S13-R7, S4-R12, S4-R13), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+5. Note for the tester: this panel lists nine toggles and no Location toggle. The specification is currently inconsistent on this one point - one requirement says a Location toggle should be here for anyone who can reach more than one branch, while the list of nine does not include it. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+---
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S13-R1, S13-R2, S13-R3, S13-R4, S13-R7, S4-R12, S4-R13). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: one requirement says it is shown by default and can be toggled there, and the list of toggleable columns in another does not include it. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
+AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
 </t>
         </is>
       </c>
@@ -3170,7 +3217,8 @@
 2. The Customer and Subtotal columns and the chevron control column do NOT appear in the toggle list and are always present.
 3. All nine columns can be hidden — nothing blocks the last toggle; the table still renders the Customer and Subtotal columns and the totals row still shows its Subtotal.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S13-R5, S13-R6, S13-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S13-R5, S13-R6, S13-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3225,8 +3273,9 @@
 3. No Location column shows on the table either, because this person only ever has one location in view.
 4. Note for the tester: this test is about someone who only has ACCESS to one location. That is a different person from someone who can reach several locations but has picked just one. Do not mix the two up - they are separate tests, and the second one is still waiting on an answer from the product owner.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. In his own words the location column selector "should not appear if the user doesn't satisfy" having access to multiple locations. Nothing in the Sales By Customer report specification version 14 covers this, so his answers are the only basis for it, and it has not been checked on a build yet.
-AUTOMATION: HOLD - waiting on an answer from the product owner
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S4-R12), which states that a user with access to a single location is never shown the Location column and that it never appears in their column selector; the Technician Utilization report specification version 6 (S10-R4) and the Work In Progress report specification version 7 (S4-R3) say the same, and on the other three reports the written description keeps the column out of that list for everyone, so the result is the same for all six. Chris Ward asked for this in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This has not yet been checked against a build.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -3277,7 +3326,8 @@
 2. The menu items read, in order: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", "Download Expanded View (CSV)" - and there is NO "Print" item anywhere in the menu.
 3. There are no separate always-visible export buttons - all exports live behind this one menu.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-R1, S14-R2, S15-R1, S15-R2, S20-R16); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S14-R1, S14-R2, S15-R1, S15-R2, S20-R16).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3328,12 +3378,13 @@
       <c r="G55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">1. The Summary file name is sales-by-customer-summary-{range}.csv and the Expanded file name is sales-by-customer-expanded-{range}.csv — so the file says which version it is.
-2. {range} follows the period you picked, using the nine periods the chooser actually offers: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. The specification gives the word for each period, so check the file against it.
-3. For a range you built yourself on the calendar, record what the file name uses in place of a period name - the exact wording is confirmed in the build.
+2. {range} follows the period you picked, using the nine periods the chooser actually offers: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. The written description gives the word for eight of them - this_week, last_week, this_month, last_month, this_year, last_year, this_quarter, last_quarter - so check the file against those. It does not give a word for Last 12 Months, so for that one record what you see rather than judging it right or wrong.
+3. For a range you built yourself on the calendar the file name uses the word custom in place of a period name - for example sales-by-customer-summary-custom.csv.
 4. The file is plain comma-separated text with a .csv extension that opens as rows and columns in a spreadsheet — not an .xlsx workbook and not a JSON file.
 5. The two PDF downloads follow the same names with a .pdf extension — for example, sales-by-customer-summary-this_month.pdf and sales-by-customer-expanded-custom.pdf.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Customer report specification version 14 (S14-R14, S14-R15, S15-R6) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Customer report specification version 14 (S14-R14, S14-R15, S15-R6) says something different, his decision is the later word and is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3389,7 +3440,8 @@
 6. Work with no vehicle appears as an asset row named "Parts Sales".
 7. The file carries a "Locations:" line naming the location or locations the report was scoped to, or "All locations" when every location you can access is selected — as a leading line above the column headers.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-R5, S14-R6, S14-R7, S14-R8, S14-R13, S4-R13).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S14-R5, S14-R6, S14-R7, S14-R8, S14-R13, S4-R13).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3443,7 +3495,8 @@
 On this build the money in the spreadsheet file comes out as "$224.92" - with a dollar sign, and with a comma as well once the value passes a thousand - instead of the plain number described in point 3 above.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8823
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-R9, S14-R10, S14-R11, S14-R12, S14-R13).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S14-R9, S14-R10, S14-R11, S14-R12, S14-R13).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8823)
 </t>
         </is>
@@ -3495,7 +3548,8 @@
 2. When every customer is selected, the export contains the full set of customers under those filters.
 3. The chosen date range and Product Type are reflected in both exports.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S2-R7, S3-R7, S4-R10, S14-R3, S15-R3, S18-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S2-R7, S3-R7, S4-R10, S14-R3, S15-R3, S18-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3548,7 +3602,8 @@
 2. If a CSV download fails, an error toast is shown: "CSV export failed." (dismissed by the user).
 3. If a PDF download fails, the toast reads "PDF export failed." — identical behaviour, different wording.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-E1, S14-N1, S15-E1, S15-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S14-E1, S14-N1, S15-E1, S15-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3598,7 +3653,8 @@
           <t xml:space="preserve">1. The PDF is A4 landscape using the application's standard font; the page margins look uniform on all sides. (The spec's exact 25px margin needs a PDF inspector — check the number only if you have one; otherwise uniform margins pass.)
 2. The footer has a centered "Software Powered by ShopView" label and a right-aligned page number "Page X of Y."
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S15-R5, S15-R6, S15-R7, S15-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S15-R5, S15-R6, S15-R7, S15-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3650,7 +3706,8 @@
 3. The header date range shows start and end in the format "Mon D, YYYY," joined by an em dash - for example, "May 1, 2026 - May 31, 2026" - and always shows both dates (every range is bounded).
 4. The header also carries a "Locations:" line naming the location(s) the report was scoped to.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S15-R7, S15-R8, S15-R9, S15-R10, S15-R11, S15-R14, S4-R13); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S15-R7, S15-R8, S15-R9, S15-R10, S15-R11, S15-R14, S4-R13); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3704,7 +3761,8 @@
 4. The logo is embedded in the PDF (renders offline, not loaded from a network address).
 Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Customer report specification version 14 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18) differs, his decision is the authority.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; where the Sales By Customer report specification version 14 (S15-R12, S15-R13, S15-R14, S15-R15, S15-R16, S15-R17, S15-R18) differs, his decision is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026, which does not yet match it - that change is with the developers.
 AUTOMATION: READY
 </t>
         </is>
@@ -3760,7 +3818,8 @@
 6. Inv. Hrs uses the same signs and coloring as on screen, with green rendered as #21ba45 and red as #c10015.
 7. The PDF header title reads "Sales By Customer Report" on the Summary and Expanded versions alike — which version you have is told by the file name and the contents, not by a different title.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S15-R5, S15-R13, S15-R19, S15-R20, S15-R21, S15-R22, S15-R23, S15-R24, S4-R13).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S15-R5, S15-R13, S15-R19, S15-R20, S15-R21, S15-R22, S15-R23, S15-R24, S4-R13).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3814,7 +3873,8 @@
 4. Below the cap the export succeeds normally.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-R16, S15-R25, S14-R14, S15-R22); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S14-R16, S15-R25, S14-R14, S15-R22); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8818)
 </t>
         </is>
@@ -3864,7 +3924,8 @@
           <t xml:space="preserve">1. The export still downloads — no error and no warning is shown.
 2. The file contains the column headers and a totals row of zeros, with no data rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R10).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R10).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -3918,7 +3979,8 @@
 4. All four files reflect exactly the filtered data shown on screen.
 5. With a single location in scope the Summary files have these ten columns in this exact order: Customer, Inv. Hrs, Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Shop Supplies, Margin, Margin %, Subtotal — no Asset, Invoice # or Date columns. When more than one location is in scope a Location column is added immediately after the Customer name and before the money columns.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. The Sales By Customer report specification version 14 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13) is silent on this point, and it has not yet been confirmed on a build.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. the Sales By Customer report specification version 14 (S14-R1, S14-R2, S14-R4, S15-R1, S15-R2, S15-R4, S15-R5, S4-R13) is silent on this point, so his answers are the only basis for it.
+This has not yet been checked against a build.
 AUTOMATION: READY
 </t>
         </is>
@@ -3977,12 +4039,17 @@
 4. All six reports behave the same way.
 5. Note for the tester: step 2 is the difficult part. If you cannot get the organization into that state, mark this test Blocked and say so plainly - do not guess the answer.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. His words are: "Use the company's own uploaded logo. If a logo is set but fails to load, fall back to the built-in ShopView logo. If no logo is uploaded, print no logo and let the text fill the space." This DIFFERS from the Sales By Customer report specification version 14 (S15-R17), which shows the built-in ShopView logo when no logo has been uploaded rather than when an uploaded one fails to load, and we have taken his newer decision as the one that prevails. It has not been checked on a build yet.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. His words are: "Use the company's own uploaded logo. If a logo is set but fails to load, fall back to the built-in ShopView logo. If no logo is uploaded, print no logo and let the text fill the space." This DIFFERS from the Sales By Customer report specification version 14 (S15-R17), which shows the built-in ShopView logo when no logo has been uploaded rather than when an uploaded one fails to load, and we have taken his newer decision as the one that prevails.
+This has not yet been checked against a build.
 AUTOMATION: HOLD - nobody has run this test yet; it needs one live check of a logo that fails to load
 </t>
         </is>
       </c>
-      <c r="H67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>SV-8613 (SBC spec v13 2026-07-31 Story 15 S15-R17 and S15-R18 - the logo order and the no-logo layout; the set-but-fails-to-load step is Chris Ward's answer T3-4 option C of 2026-08-05 alone)</t>
+        </is>
+      </c>
       <c r="I67" s="2" t="inlineStr"/>
       <c r="J67" s="2" t="inlineStr"/>
     </row>
@@ -4024,7 +4091,8 @@
           <t xml:space="preserve">1. The saved view is restored: the date range, the Product Type, the location selection, the Customer filter selection, the sort column and direction, and the visible columns.
 2. On load, the report shows the restored view immediately — the default view is never shown first and then replaced.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S6-R1, S6-R2, S6-R4, S2-R8, S3-R8, S4-R11, S10-R9, S13-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S6-R1, S6-R2, S6-R4, S2-R8, S3-R8, S4-R11, S10-R9, S13-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4077,7 +4145,8 @@
 3. The scroll position is not restored.
 4. This is the specified behavior (expansion is treated as fresh each visit), not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S6-R3, S8-R22).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S6-R3, S8-R22).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4129,7 +4198,8 @@
 2. No error appears and the report loads normally.
 3. Per the spec, the same discard-to-default applies to an unknown date range, a sort column that no longer exists, or a column set that does not match the current columns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S6-R5, S6-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S6-R5, S6-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4179,7 +4249,8 @@
           <t xml:space="preserve">1. The other report keeps its own defaults/saved view — the Sales By Customer settings do not leak into it.
 2. Sales By Customer still restores its own saved view.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S6-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S6-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4235,7 +4306,8 @@
 5. Sort = Customer name ascending.
 6. All nine toggleable columns visible.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S6-N1, S2-R5, S4-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S6-N1, S2-R5, S4-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4286,7 +4358,8 @@
           <t xml:space="preserve">1. The saved view is applied (Last Month) and the link value is ignored.
 2. This is intentional: a shared link restores the sender's range only for a recipient who has no saved range of their own.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S2-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S2-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4337,7 +4410,8 @@
           <t xml:space="preserve">1. Scenario A: the filter restores to the all-customers state and the report shows every present customer — including the customer that appeared since the state was saved.
 2. Scenario B: still-present saved ids are re-selected; a saved id no longer present is dropped (a stale saved id never forces an empty view); a customer that appeared since the set was saved is NOT auto-selected.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4395,7 +4469,8 @@
 5. With a narrowed customer selection and no data, the empty state shows but the selection is KEPT (not cleared) — when the filters change back, the selected customers reappear.
 6. While the table is still loading, the empty-state message is NOT shown (the loading state is shown instead); it appears only once loading has finished and there are zero customers.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1, S17-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S17-R1, S17-R2, S17-R3, S17-E1, S2-N1, S3-N1, S4-N2, S8-N1, S17-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4446,7 +4521,8 @@
           <t xml:space="preserve">1. An error toast is shown: "An error occurred while fetching the report data."
 2. The toast auto-fades after 5 seconds.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (§7 User Feedback Summary).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (§7 User Feedback Summary).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4506,7 +4582,8 @@
 8. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 9. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing, the alignment and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this — 32px/24px toolbar padding, a 1px header border, 2rem edge padding, a 24px arrow — are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S20-R1, S20-R2, S20-R3, S20-R4, S20-R5, S20-R6, S20-R7, S20-R12, S20-R13, S20-R15, S20-R17).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S20-R1, S20-R2, S20-R3, S20-R4, S20-R5, S20-R6, S20-R7, S20-R12, S20-R13, S20-R15, S20-R17).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4561,8 +4638,9 @@
 4. The pinned Subtotal cell on any row uses that row's own background — never a contrasting strip.
 5. The three tree levels show by indentation: customer at the base, asset rows one level in (chevron and vehicle icon sit in from the customer), invoice rows one level deeper.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14).
-AUTOMATION: HOLD - waiting on an answer from the product owner
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S20-R8, S20-R9, S20-R10, S20-R11, S20-R14).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -4611,7 +4689,8 @@
           <t xml:space="preserve">1. In dark mode every visual rule applies with the dark equivalent of each color (dark background, dark surfaces).
 2. The PDF export always renders in light-mode colors regardless of the user's app mode.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S20-R18).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S20-R18).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4663,7 +4742,8 @@
 2. Below 1024px the toolbar uses two rows: the action controls (overflow menu and column selector) on the first row, and the filter dropdowns on the second row, stacked at full width.
 3. At 1024px and above the toolbar uses the desktop single-row layout.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S21-R1, S21-R2, S21-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S21-R1, S21-R2, S21-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4715,7 +4795,8 @@
 2. The chevron expand and collapse control on each row works on touch.
 3. The invoice number link opens the invoice in the same tab, the same as on desktop.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S21-R4, S21-R5, S21-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S21-R4, S21-R5, S21-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4769,7 +4850,8 @@
 2. The first expand of a customer triggers a server fetch for that customer's asset and invoice rows.
 3. Expand-all triggers at most one drill-down fetch per not-yet-expanded customer on the current page — a bounded number never exceeding the page size; it does not fetch customers beyond the current page or the whole result set.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S8-R14, S8-R16).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S8-R14, S8-R16).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4823,7 +4905,8 @@
 3. The ordering is not done by re-shuffling rows already in the browser.
 4. A sort request naming a column the report does not offer is safely refused or ignored — never an error page or a crash; sorting works only on the report's own columns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S10-R8, S10-R8b).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S10-R8, S10-R8b).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - this part of the report is not built yet
 </t>
         </is>
@@ -4876,7 +4959,8 @@
 2. As you type, the browser fetches matching customers from the server — case-insensitive "contains" matching on the name, scoped to the active date range, Product Type, and location — and lists the returned customers.
 3. The all-customers state is stored as an explicit state (a flag), not an enumeration of the fetched ids.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R2, S18-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R2, S18-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4929,7 +5013,8 @@
 2. Changing the Customer selection re-fetches the matching customers as a fresh first page.
 3. The totals are computed on the server over the full set of matching customers — they arrive with the data and do not change as you page.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S18-R6, S18-R11).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S18-R6, S18-R11).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -4981,7 +5066,8 @@
 2. Over the cap, the server does not generate the file (the request comes back as a refusal, not a file) and the browser starts no download — the count the cap checks is the count the file would contain, against the same filters and sort as the screen.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S14-R3, S14-R14, S15-R3, S15-R22).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S14-R3, S14-R14, S15-R3, S15-R22).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8818)
 </t>
         </is>
@@ -5040,7 +5126,8 @@
 4. For that same user, the export request is refused with HTTP 403 as well — no file is produced.
 5. Note for the tester: one single permission controls all four of these. If you find the report data refused but the export allowed (or the other way round), that is a failure — record both response codes.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Customer report specification version 14 (S1-R2, S1-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Customer report specification version 14 (S1-R2, S1-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5095,7 +5182,8 @@
 4. The page title reads "Sales By Representative".
 5. The browser tab title reads "Sales By Representative - Report | ShopView".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R1, S1-R2, S1-R3, S1-R4, S1-R5, S1-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S1-R1, S1-R2, S1-R3, S1-R4, S1-R5, S1-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5145,7 +5233,8 @@
           <t xml:space="preserve">1. The full "Sales By Representative" label renders without crowding against the entry's edges and without truncation.
 2. The label is not shortened to fit — the fix is the entry's horizontal padding, not the name.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S1-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5194,7 +5283,8 @@
         <is>
           <t xml:space="preserve">1. "Sales By Representative" appears in the Performance group for this user — the entry is visible to every user who can see any other report in the same group.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-R1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S1-R1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5247,7 +5337,8 @@
 2. The report (and its ⋯ export menu) is not reachable.
 3. The Export Reports dialog and the Sales Representative Assignments download are not reachable.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S1-N1, S14-N3, S15-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S1-N1, S14-N3, S15-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5295,7 +5386,8 @@
         <is>
           <t xml:space="preserve">1. The staff-editing surface is not reachable, so the deactivation flow (and its warning dialog) cannot be reached.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5346,7 +5438,8 @@
 2. The chooser offers nine ready-made periods, in this order: Last 12 Months, This Year, Last Year, This Quarter, Last Quarter, This Month, Last Month, This Week, Last Week. Beside them it shows a month calendar you click dates on to build your own range, a live readout of how many days the range covers, and an Apply button. There is no "Today", no "Yesterday" and no item called "Custom" - you build your own range on the calendar instead. There is no "All Time" option.
 3. The named periods use the application's standard shared calendar boundaries - this is one shared chooser used by all six reports.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Representative report specification version 15 (S2-R1, S2-R2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Representative report specification version 16 (S2-R1, S2-R2) says something different, his decision is the later word and is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5396,7 +5489,8 @@
           <t xml:space="preserve">1. A custom range within the cap applies normally via the date-picker dialog.
 2. A custom selection whose span exceeds 366 days is not accepted — the picker holds you to a range of 366 days or fewer.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S2-R3, S2-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S2-R3, S2-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5448,7 +5542,8 @@
 2. The date used is the invoice's own date — the value shown in the Date column.
 3. The chosen date range is reflected in both PDF exports' header strips.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S2-R5, S2-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S2-R5, S2-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5504,7 +5599,8 @@
 4. "Parts &amp; Service" applies no product-type filter — both appear again.
 5. Each change re-fetches and re-renders the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6, S3-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S3-R1, S3-R2, S3-R3, S3-R4, S3-R5, S3-R6, S3-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5557,7 +5653,8 @@
 3. "All Statuses" is the default on first load.
 4. Changing the selection re-fetches and re-renders the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R1, S4-R2, S4-R3, S4-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S4-R1, S4-R2, S4-R3, S4-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5611,7 +5708,8 @@
 3. "Unpaid" includes only the unpaid invoice.
 4. The filter matches on the mapped display value, the same mapping the status badge uses — prepaid is the only state whose display value depends on the balance owed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S4-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5665,7 +5763,8 @@
 3. Parts-only leg: rep A disappears; rep B's summary totals, detail rows, grand Totals, and (N) count reflect only the matching (P) invoices.
 4. Unpaid leg: rep C disappears; rep D's figures reflect only the Unpaid invoices.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R7, S4-R6, S4-N1, S3-R8, S3-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S4-R7, S4-R6, S4-N1, S3-R8, S3-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5714,7 +5813,8 @@
           <t xml:space="preserve">1. The invoice shows its FULL invoiced amounts (its full Subtotal) — payments are not netted out.
 2. Filtering to "Unpaid" or "Partially Paid" changes which invoices are included, never the amounts shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S4-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S4-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5764,7 +5864,8 @@
           <t xml:space="preserve">1. The location filter is the rightmost control in the toolbar.
 2. It is a multi-select listing the locations the user has access to, plus an "All Locations" option.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-R1, S18-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S21-R1, S18-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5819,7 +5920,8 @@
 3. "All Locations" means all locations the user can access — location Z's data is never included.
 4. With "All Locations" active you can tell which location each row's data belongs to — a location label or marking is shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-R3, S21-R4, S21-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S21-R3, S21-R4, S21-R5); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5869,7 +5971,8 @@
           <t xml:space="preserve">1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S21-N1). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S21-N1). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -5930,15 +6033,13 @@
 4. An invoice detail row shows that invoice's own exact location — never "Multiple".
 5. The Unassigned summary row follows the same rule as any rep summary row.
 6. The pinned Subtotal column is still rightmost — the Location column never displaces it.
-7. With a single location in scope the Location column is hidden.
+7. With only one location involved the Location column is not shown.
 8. All four downloads include the Location column in the same position it occupies on screen. In the Summary files a rep's row carries that rep's location and reads "Multiple" when the rep spans more than one location; in the Expanded View files each invoice row carries that invoice's own exact location.
-Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
-The Location column is not in the column-selection dropdown — that dropdown holds the seven metric columns only — and you cannot switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
-Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
----
----
-This is the expected behaviour as per the Sales By Representative report specification version 15 (S21-R7, S21-R8, S18-R13, S14-R20), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. For this report the two statements are that the column-selection dropdown holds the seven metric columns only, and that Location is one of the columns you can switch on and off there. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+---
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S21-R7, S21-R8, S18-R13, S14-R20). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: its summary says it can be toggled there, while the requirement that governs the column says it appears only when the view spans more than one location and the dropdown holds the seven metric columns only. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
+AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
 </t>
         </is>
       </c>
@@ -5990,7 +6091,8 @@
 3. The number of contributing invoices shows in parentheses after the rep's name, in a smaller, subdued grey font — e.g., Mary Smith (12) — and is always at least 1.
 4. A staff member with no matching invoice does not appear regardless of toggle state or historical activity.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R1, S5-R4, S5-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S5-R1, S5-R4, S5-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6045,7 +6147,8 @@
 4. Rep summary rows are bold (700) so they read as parent rows; detail rows use the default weight (400) — row type is distinguished by font weight, not background color.
 5. Every row renders exactly the report's column count with blanks in position — a cell with nothing to show is blank, never shifted or wrapped (a drifted row is a defect). The grand Totals indicator is exempt: the desktop Totals row merges the four leading identifier columns; the mobile bar is not a table row.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R2, S5-R3, S5-R6, S5-R8, S5-R10, S5-N2, S6-R4, S18-R4, S18-R6a, S21-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S5-R2, S5-R3, S5-R6, S5-R8, S5-R10, S5-N2, S6-R4, S18-R4, S18-R6a, S21-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6099,7 +6202,8 @@
 3. For a deleted staff record, the display name and sort position come from the denormalized rep-name snapshot on the rep's most recent matching invoice (by invoice date, ties by invoice number), so the row still shows a historical name and sorts correctly.
 4. The grand Totals stay reconciled to the period's invoices — no revenue silently disappears.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S5-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6150,7 +6254,8 @@
 2. Each detail row shows, left to right: the invoice's date, the invoice number, the customer name, the payment status badge, and the per-invoice values for Inv. Hrs and the money columns.
 3. A rep with a single matching invoice can still be expanded — one detail row is shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R1, S6-R2, S6-R3, S6-E1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S6-R1, S6-R2, S6-R3, S6-E1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6202,7 +6307,8 @@
 2. Clicking expands every visible rep in one action; with every rep expanded the glyph switches to "collapse."
 3. A second activation collapses them all.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R5, S6-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S6-R5, S6-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6252,7 +6358,8 @@
           <t xml:space="preserve">1. Every invoice appears under exactly one rep (the rep credited at invoicing time) or under the Unassigned row — never under two rows.
 2. The sum of all (N) counts equals the number of matching invoices.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S6-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6304,7 +6411,8 @@
 2. When a filter change removes a rep, the rep and its expansion state are gone; when a later change brings the rep back, the row renders collapsed (it does not auto-re-expand).
 3. A full page reload resets all expansion.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R8, S6-N1, S23-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S6-R8, S6-N1, S23-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6356,7 +6464,8 @@
 3. If both the date and the numeric portion tie (e.g., P100 and S100 same day), P (Parts) sorts before S (Service).
 4. This order is independent of the rep-row column sort (which reorders summary rows only).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R9, S11-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S6-R9, S11-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6410,7 +6519,8 @@
 3. The mapping is: paid → Paid; overpaid → Paid; prepaid with zero balance → Paid; prepaid with a balance owed → Partially Paid; partially_paid → Partially Paid; unpaid → Unpaid.
 4. Badges are vertically centered in their cells; on rep summary rows the Status cell is blank; the badge's text is the accessible label — status is never conveyed by color alone.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S8-R1, S8-R2, S8-R4, S8-R5, S8-R6, S8-N1, S18-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S8-R1, S8-R2, S8-R4, S8-R5, S8-R6, S8-N1, S18-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6461,7 +6571,8 @@
 2. The badges use the same canonical payment-status color tokens as the invoice list, consistent app-wide.
 3. The treatment stays legible and consistent in both light and dark mode.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S8-R3, S18-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S8-R3, S18-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6511,7 +6622,8 @@
           <t xml:space="preserve">1. The column heading reads "Inv. Hrs" (verbatim, including the period after "Inv").
 2. The value equals the billed labor hours minus the technician clocked hours, rounded half-up to one decimal.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R1, S9-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S9-R1, S9-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6566,7 +6678,8 @@
 3. The rep-summary/totals value equals round(sum of unrounded per-invoice deltas).
 4. A value that rounds to 0.0 (e.g., +0.04) shows 0.0 in the default color — not +0.0 in green; negative values always use an explicit minus and one decimal (e.g., -0.5).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R3, S9-R4, S9-R5, S9-R6, S9-E1, S9-E2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S9-R3, S9-R4, S9-R5, S9-R6, S9-E1, S9-E2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6616,7 +6729,8 @@
           <t xml:space="preserve">1. The invoice with neither billed labor hours nor clocked hours shows Inv. Hrs 0.0 in the default color — never blank, "N/A," or "—".
 2. The invoice with clocked hours but no billed labor line shows the resulting NEGATIVE delta in red (e.g., -3.0) — the worked-but-unbilled signal is not suppressed to 0.0.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S9-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6668,7 +6782,8 @@
 2. It renders "—" when Subtotal ≤ 0 — never "0.0%" or a divide-by-zero result.
 3. On every rolled-up row (rep summary rows and every totals row) Margin % is RECOMPUTED from that row-set's total Margin and total Subtotal — never the sum or average of the child percentages.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S10-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6720,7 +6835,8 @@
 3. Labor Margin = Labor Invoiced − labor cost; Parts Margin = Parts Invoiced − parts cost; Margin = Labor Margin + Parts Margin.
 4. The same values appear everywhere the numbers show (screen, and later the exports).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S5-R2, S21-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S5-R2, S21-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6770,7 +6886,8 @@
           <t xml:space="preserve">1. Negative dollar values render in accounting-convention parentheses — ($1,234.56) — on screen, across every money column (Labor Invoiced, Labor Margin, Parts Invoiced, Parts Margin, Margin, Subtotal).
 2. Inv. Hrs (a signed time value) and Margin % (a signed percentage) are excluded — they use a leading minus, not parentheses.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (§3 Key Decisions accounting parentheses).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (§3 Key Decisions accounting parentheses).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6820,7 +6937,8 @@
 2. Rolled-up values are computed from UNROUNDED components and then rounded, so a totals cell may differ from the eye-summed displayed rows by one unit in the last decimal.
 3. That one-unit difference is EXPECTED behavior per the spec — it must NOT be filed as a calculation defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (§3 half).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (§3 half).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6872,7 +6990,8 @@
 2. The billed SELL values (Labor, Parts, Subtotal) stay unchanged — a clock edit never rewrites what was billed.
 3. The figures tied to worked time move together consistently (Margin uses the labor cost behind the worked hours, so it may change too) — nothing is left stale.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S9-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S9-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6928,7 +7047,8 @@
 4. The pinned column matches the row's background color (white on body rows) — not a contrasting strip.
 5. The column-header row stays stuck to the top during vertical scroll; the Subtotal header cell stays visible in BOTH axes (top while scrolling down, pinned right while scrolling sideways).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R6, S10-N1, S18-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S10-R1, S10-R2, S10-R3, S10-R4, S10-R6, S10-N1, S18-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -6983,7 +7103,8 @@
 4. Money uses accounting parentheses for negatives; Margin % is recomputed; values are round(sum of unrounded).
 5. The indicator is present whenever at least one summary row exists, and hidden during loading and in the empty state.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5, S10-N1, S16-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S10-R5, S10-N1, S16-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7036,7 +7157,8 @@
 3. During vertical page scroll it sits after the table in normal flow (not pinned to the viewport bottom).
 4. It uses the white card surface with a thin top border.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5, S17-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S10-R5, S17-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7087,7 +7209,8 @@
 2. The identifier columns (Date, Invoice, Customer, Status) do not respond to header clicks.
 3. The Date header carries the expand/collapse-all chevron, not a sort affordance.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R1, S11-R6).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S11-R1, S11-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7136,7 +7259,8 @@
           <t xml:space="preserve">1. Rows render in A→Z order by display name, case-insensitive.
 2. There are NO active/inactive tiers — an "(Inactive)" rep sorts by name among the others, not grouped separately.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S11-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7190,7 +7314,8 @@
 3. There is no third "cleared" state — the third click returns to ascending.
 4. Via the column headers there is no way back to A→Z; the A→Z default shows only when a session carries no valid saved financial sort.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R5, S23-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S11-R5, S23-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7241,7 +7366,8 @@
 2. Invoice detail rows stay grouped under their parent rep, keeping their own newest-first order.
 3. The Unassigned row stays pinned to the top regardless of sort.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R2, S22-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S11-R2, S22-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7291,7 +7417,8 @@
           <t xml:space="preserve">1. Reps with equal values in the sorted column retain the default A→Z order between them.
 2. A Margin % cell rendered "—" (undefined) sorts as zero.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S11-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7343,7 +7470,8 @@
 2. Activating it navigates the CURRENT tab to the underlying invoice (work order or parts sale) — never a new tab.
 3. The customer name is likewise a clickable link that navigates the current tab to the customer's record.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R1, S12-R2, S12-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S12-R1, S12-R2, S12-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7395,7 +7523,8 @@
 2. Back-navigation does not trigger a full report reload.
 3. This is deliberately different from a page reload, which restores persisted filters/columns/sort but resets expansion and scroll.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R3a, S23-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S12-R3a, S23-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7448,7 +7577,8 @@
 3. Both hold in light and dark mode and across return visits.
 4. Underlined-at-rest links, browser-blue customer names, purple post-click links, and new-tab destinations are all defects.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-R4, S12-R5, S12-R6, S12-N3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S12-R4, S12-R5, S12-R6, S12-N3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7498,7 +7628,8 @@
           <t xml:space="preserve">1. The tab navigates to the application's standard not-found/access-denied state.
 2. Pressing back still returns to the report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S12-N1, S12-N2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S12-N1, S12-N2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7550,7 +7681,8 @@
 2. The body shows "{Staff Name} is the sales representative on {N} customer{s}." — singular for N=1 ("1 customer"), plural otherwise ("3 customers") — followed by the reassurance line "Their customer assignments will stay where they are."
 3. Focus is trapped within the dialog while open and returns to the invoking control on dismiss.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R1, S13-R3, S13-R4, S13-R12).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-R1, S13-R3, S13-R4, S13-R12).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7604,7 +7736,8 @@
 3. While disabled, hovering it shows the tooltip "Type YES above to enable."
 4. Pressing Enter while valid submits.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R6, S13-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-R6, S13-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7660,7 +7793,8 @@
 4. Clicking outside the dialog does NOT close it.
 5. When the dialog closes via Cancel or X, the staff member's active status is unchanged - no deactivation happens.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7712,7 +7846,8 @@
 3. Customer assignments are NOT modified — every customer stays assigned to this rep; denormalized rep names and past invoice snapshots are preserved.
 4. Deactivation never forces reassignment, blocks on assignments, or auto-reassigns.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R9, S13-R10, S13-E1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-R9, S13-R10, S13-E1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7764,7 +7899,8 @@
 2. In the Sales Representative Assignments CSV the rep's customers show "Rep is active?" = "No" — that column is driven by staff-active status, not the toggle.
 3. In the report the rep still appears with credit intact; the "(Inactive)" marker appears only if the sales-representative TOGGLE is off (a separate flag from staff-active status).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R11, S15-R6, S5-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-R11, S15-R6, S5-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7817,7 +7953,8 @@
 3. After reactivation the assignments re-surface immediately with no extra action.
 4. Deactivating a sales representative with NO customer assignments applies silently — no warning dialog.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R2, S13-N2, S13-N3, S13-E3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-R2, S13-N2, S13-N3, S13-E3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7869,7 +8006,8 @@
 2. The active status is unchanged.
 3. Each fresh dialog open requires a fresh confirmation entry — the input clears on open.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-N5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7920,7 +8058,8 @@
           <t xml:space="preserve">1. The system NEVER silently deactivates — the warning dialog still opens (fallback), so the type-to-confirm gate still applies.
 2. Because the customer count is unavailable, the dialog OMITS the count headline and shows only the reassurance line "Their customer assignments will stay where they are." above the "Type YES to confirm" gate.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-N4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-N4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -7970,7 +8109,8 @@
           <t xml:space="preserve">1. A "Show Unassigned" toggle sits between the column selector and the date range picker; it is OFF by default.
 2. While off, invoices with no assigned rep contribute to nothing — no row, and not counted in any total.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-R1, S22-R2, S18-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S22-R1, S22-R2, S18-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8024,7 +8164,8 @@
 3. Toggling re-renders the report and recomputes the grand Totals to include or exclude the Unassigned row accordingly.
 4. The Unassigned row shows the same metric columns and (N) count as any rep summary row, is expandable to its contributing invoices, is included in the grand Totals, and never carries an "(Inactive)" tag.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-R3, S22-R4, S22-R5, S22-R6, S6-R1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S22-R3, S22-R4, S22-R5, S22-R6, S6-R1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8075,7 +8216,8 @@
           <t xml:space="preserve">1. With the toggle on but no matching unassigned invoices, no Unassigned row is shown — an empty Unassigned row is never rendered; with no rep rows either, the empty state applies.
 2. Turning the toggle off removes the expanded row; turning it back on renders it collapsed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S22-N1, S6-N2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S22-N1, S6-N2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8131,7 +8273,8 @@
 4. With all seven metric columns hidden the table still renders the five always-on columns and the grand Totals indicator — no empty or error state.
 5. Note for the tester: if you have more than one location in scope you will also see a Location column on the table that is in neither list. That is correct - it appears by itself and is not something you can switch on or off here.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R1, S20-R2, S20-R3, S20-R6, S20-N1, S21-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S20-R1, S20-R2, S20-R3, S20-R6, S20-N1, S21-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8181,7 +8324,8 @@
           <t xml:space="preserve">1. The toggle takes effect immediately — no confirm step.
 2. Hiding a metric column removes it from rep summary rows, invoice detail rows, and the grand Totals indicator simultaneously; showing restores it everywhere at once.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R4, S20-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S20-R4, S20-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8230,7 +8374,8 @@
         <is>
           <t xml:space="preserve">1. All four downloads include ALL metric columns regardless of the on-screen column selector state.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S20-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8280,7 +8425,8 @@
           <t xml:space="preserve">1. Hiding the active sort column does not clear the sort — rows stay ordered by the now-hidden metric until another sort is chosen or the A→Z default is restored.
 2. Showing the column again reveals the sort indicator on it.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S20-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S20-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8331,7 +8477,8 @@
           <t xml:space="preserve">1. Every setting is restored: date range (including the custom start/end), product type, invoice status, location, Show Unassigned, column visibility, and the active column sort (column + direction).
 2. The settings are restored BEFORE the first data fetch — the report does not fetch defaults first and then re-fetch.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R1, S20-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S23-R1, S20-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8381,7 +8528,8 @@
           <t xml:space="preserve">1. All rows render collapsed and the scroll position resets.
 2. This is the specified behavior (only back-navigation from a drilldown restores expansion/scroll), not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S23-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8432,7 +8580,8 @@
 2. No error occurs — a stale saved setting can never cause an error or an invalid request.
 3. Per the spec the same applies to a range or sort column that no longer exists and to a hidden-but-sorted column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S23-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8482,7 +8631,8 @@
           <t xml:space="preserve">1. Date range = This Month; Product Type = "Parts &amp; Service"; Invoice Status = "All Statuses"; Location = your currently active location only (the one location you are working in); Show Unassigned = off; all seven metric columns visible; sort = the A→Z default.
 2. Clearing browser storage fully returns the report to first-visit defaults — no server-side profile brings the old settings back.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R4, S23-N1, S2-R4, S2-R7, S21-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S23-R4, S23-N1, S2-R4, S2-R7, S21-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8532,7 +8682,8 @@
           <t xml:space="preserve">1. The report restores to the A→Z default order by rep display name.
 2. No financial column shows a sort indicator — the saved "no financial sort" state restores as A→Z, not as an arbitrary column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S23-R5, S11-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S23-R5, S11-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8583,7 +8734,8 @@
           <t xml:space="preserve">1. The menu lists exactly four actions: "Download Summary (PDF)", "Download Expanded View (PDF)", "Download Summary (CSV)", and "Download Expanded View (CSV)".
 2. No other entries appear in the menu.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R1, S17-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R1, S17-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8640,7 +8792,8 @@
 4. The Unassigned row (Show Unassigned on) is pinned first, ahead of the sorted reps.
 5. Every file (all four downloads, PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R2, S14-R2a, S14-R20, S21-R6, S22-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R2, S14-R2a, S14-R20, S21-R6, S22-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8695,7 +8848,8 @@
 4. Subtotal is bolded across the header, the body rows, and the grand totals row; Inv. Hrs keeps its green/red/default coloring.
 5. The grand totals row reads "Totals" in the Rep cell and aggregates every summary row in the document (including the Unassigned row when Show Unassigned is on); its Margin % is RECOMPUTED as total Margin ÷ total Subtotal (shown "—" when that Subtotal is zero or below), never the sum or average of the rows' percentages.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. The Sales By Representative report specification version 15 (S14-R3, S14-R5, S14-R20, S2-R5) is silent on this point, and it has not yet been confirmed on a build.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. the Sales By Representative report specification version 16 (S14-R3, S14-R5, S14-R20, S2-R5) is silent on this point, so his answers are the only basis for it.
+This has not yet been checked against a build.
 AUTOMATION: READY
 </t>
         </is>
@@ -8751,7 +8905,8 @@
 5. Each block ends with a per-rep totals row — "Totals" in the Date cell; Invoice/Customer/Status blank; each metric aggregated; Margin % recomputed.
 6. There is NO grand-totals row across all reps at the end of the document.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R6, S14-R8, S14-R20, S6-R9). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R6, S14-R8, S14-R20, S6-R9). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8802,7 +8957,8 @@
 2. In the PDF, the long number is cut to its first 18 characters followed by an ellipsis (the ellipsis is not counted toward the 18).
 3. In the PDF, the 18-character-or-shorter number shows in full with no ellipsis.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R7).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8857,7 +9013,8 @@
 ---
 Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Representative report specification version 15 (S14-R3a, S14-R4, S14-R11) differs, his decision is the authority.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; where the Sales By Representative report specification version 16 (S14-R3a, S14-R4, S14-R11) differs, his decision is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026, which does not yet match it - that change is with the developers.
 AUTOMATION: READY
 </t>
         </is>
@@ -8909,7 +9066,8 @@
 2. The on-screen (N) invoice count does NOT appear next to any rep name in either PDF.
 3. The "(Inactive)" tag DOES render on toggled-off contributors' names in both PDFs; other rep names render plainly.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R9, S14-R10).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R9, S14-R10).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -8962,7 +9120,8 @@
 2. Column widths are fixed for the worst case regardless of tier — the layout never breaks and no value overflows or wraps its column.
 3. Both PDF formats adapt the same way.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R12, S14-R13).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R12, S14-R13).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -9019,7 +9178,8 @@
 6. Note for the tester: the heading in this file reads simply "Representative". The product owner has confirmed that is correct and not slang, so do not fail the test for it.
 7. When more than one location is in scope the file also carries a Location column, immediately after the Representative name and before the money columns; a rep whose invoices span more than one location reads "Multiple".
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Sales By Representative report specification version 15 (S14-R15, S14-R18, S14-R20) differs, his decision is the authority.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; where the Sales By Representative report specification version 16 (S14-R15, S14-R18, S14-R20) differs, his decision is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026, which does not yet match it - that change is with the developers.
 AUTOMATION: READY
 </t>
         </is>
@@ -9073,7 +9233,8 @@
 4. Note for the tester: the heading in this file reads simply "Representative". The product owner has confirmed that is correct and not slang, so do not fail the test for it.
 5. When more than one location is in scope the file also carries a Location column immediately after Status — the position it holds on screen — and every row shows that invoice's own exact location, never "Multiple".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Sales By Representative report specification version 15 (S14-R16, S14-R20) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Sales By Representative report specification version 16 (S14-R16, S14-R20) says something different, his decision is the later word and is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -9129,7 +9290,8 @@
 On this build the money in the spreadsheet file comes out as "$1,979.40" - with a dollar sign and a comma - instead of the plain number described in point 1 above.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8823
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R17).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R17).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8823)
 </t>
         </is>
@@ -9183,7 +9345,8 @@
 3. With the toggle OFF: no Unassigned row and no unassigned invoices appear in ANY of the four files.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R19, S22-R2, S22-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R19, S22-R2, S22-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -9236,7 +9399,8 @@
 2. A failed download shows the error toast "Ooooops! An error occured" (the typo is as-shipped) — it persists 120 seconds or until dismissed.
 3. A genuine failure downloads nothing — never a malformed file.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-N1, S14-N2, S14-E1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-N1, S14-N2, S14-E1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -9288,7 +9452,8 @@
 3. Below the cap, a large Expanded View PDF still generates normally (many reps × many invoices is expected).
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-E2); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8818)
 </t>
         </is>
@@ -9341,7 +9506,8 @@
 4. Both CSVs generate a header-row-only file, still starting with the UTF-8 BOM.
 5. No special "empty" treatment or message appears inside the files.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-E3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -9395,7 +9561,8 @@
 3. The dialog shows the note: "Snapshot of current sales representative assignments. Both active and inactive reps with assignments are listed."
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R1, S15-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S15-R1, S15-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -9450,7 +9617,8 @@
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 5. Note for the tester: this file has only those three columns even if you have several locations in scope. It is a separate customer-to-representative list, not one of the report's four downloads, so it has no Location column - do not fail it for that.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R3, S15-R4, S14-R20); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S15-R3, S15-R4, S14-R20); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -9503,7 +9671,8 @@
 2. Customers with no assigned rep are NOT included.
 3. Rows are sorted by customer name A→Z (primary), then rep name A→Z (secondary).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R5, S15-R7, S15-R10).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S15-R5, S15-R7, S15-R10).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -9554,7 +9723,8 @@
 2. The staff-INACTIVE / toggle-on rep shows "Rep is active?" = "No".
 3. The value is always "Yes" or "No" (never "Deactivated" or another word).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R6, S13-R11).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S15-R6, S13-R11).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -9607,7 +9777,8 @@
 3. When stored names differ across customers for the same rep (name drift), each customer's row uses its OWN stored name — drift never adds extra rows for a customer and never overwrites one customer's stored name with another's.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R8, S15-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S15-R8, S15-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -9659,7 +9830,8 @@
           <t xml:space="preserve">1. With zero assigned customers, the CSV downloads with a header row and no data rows, and the dialog shows its empty-export warning: "There is no data to export for the selected report."
 2. On a generation failure, an error toast reads "An error occurred while exporting the report. Please try again." and auto-fades after 5 seconds.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S15-R11, S15-N2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S15-R11, S15-N2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -9714,7 +9886,8 @@
 4. Whenever at least one rep row (or the Unassigned row) IS in the result set, the rep list renders and no empty/error message shows.
 5. In the empty state the toolbar — filters, column selector, and the ⋯ exports — stays visible and interactive; widening the range re-fetches and renders the matching reps normally.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R1, S16-R2, S16-R3, S16-N1, S2-N1, S21-N2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S16-R1, S16-R2, S16-R3, S16-N1, S2-N1, S21-N2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -9768,7 +9941,8 @@
 3. The toolbar stays interactive so filters can be changed mid-load.
 4. A re-fetch replaces the previous data only when the new data returns — no flash of a blank table beyond the spinner overlay.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S16-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -9821,7 +9995,8 @@
 2. The filters and toolbar remain interactive, and the failure does NOT clear the filter selections.
 3. "Retry" re-runs the CURRENT request — the report loads with the same filters still applied.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S16-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S16-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -9873,7 +10048,8 @@
 2. Below 1024px the toolbar controls stack vertically at full width; the ⋯ exports button — the first control of the action cluster — wraps to a partial row ABOVE the stacked controls.
 3. At 1024px and above the desktop layout applies.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R1, S17-R2, S17-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S17-R1, S17-R2, S17-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -9925,7 +10101,8 @@
 2. The mobile external totals bar ("Totals" left, grand Subtotal right) sits below the table, OUTSIDE the horizontal scroll container — it does not scroll horizontally and is always fully visible.
 3. The chevron expands/collapses the rep on touch.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R4, S17-R5, S10-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S17-R4, S17-R5, S10-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -9976,7 +10153,8 @@
           <t xml:space="preserve">1. Each of these interactive controls presents a touch target of at least 44×44 px.
 2. Hover-only tooltips are not shown on touch; the icons communicate the action and each icon-only control carries an accessible name.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S17-R6, S17-N1, S18-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S17-R6, S17-N1, S18-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -10033,7 +10211,8 @@
 6. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 7. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the alignment look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this — 32px/24px toolbar padding, 2rem edge padding — are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R1, S18-R2, S18-R3, S18-R4, S18-R5, S18-R7, S18-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S18-R1, S18-R2, S18-R3, S18-R4, S18-R5, S18-R7, S18-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -10087,7 +10266,8 @@
 3. Inv. Hrs green/red use the application's positive/negative tokens, mode-appropriate.
 4. PDFs always render in light-mode colors, even when downloaded from dark mode.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S18-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -10141,7 +10321,8 @@
 4. Header chevron = "Expand all reps" / "Collapse all reps".
 5. Dialog X = "Close".
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R9).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S18-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -10194,7 +10375,8 @@
 2. A chevron exposes its expanded/collapsed state to assistive technology.
 3. A sortable header exposes its current sort state (unsorted / ascending / descending) to assistive technology.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R10).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S18-R10).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -10245,7 +10427,8 @@
 2. No information is conveyed by color alone: Inv. Hrs carries its +/- sign, status badges carry their text label, and links carry a hover/focus underline.
 3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can read the grey text easily in both modes, and only report it if you cannot. (The design rule behind this is WCAG AA contrast of at least 4.5:1, which the design and engineering team check with a contrast tool - not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S18-R11, S18-R12).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S18-R11, S18-R12).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -10300,7 +10483,8 @@
 4. The selector is NOT present in History mode.
 5. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R1, S19-N1).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S19-R1, S19-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - waiting on an answer from the product owner
 </t>
         </is>
@@ -10353,7 +10537,8 @@
 3. The selector carries the accessible name "Sales Representative".
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R2, S19-R8).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S19-R2, S19-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - this part of the report is not built yet
 </t>
         </is>
@@ -10405,7 +10590,8 @@
 2. Changing the Sales Representative persists immediately (save-on-change): the selection survives leaving and reopening the WO with no separate Save step.
 3. A new Part Sale WO also opens with the field unassigned.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R3, S19-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S19-R3, S19-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -10457,7 +10643,8 @@
 3. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 4. Note for the tester: this field is only made read-only on the screen. If you find the sales rep can still be changed another way (through the back-end/API), that is expected — mark this test PASSED and do not raise it as a bug.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S19-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -10510,7 +10697,8 @@
 3. Invoice (c) is unassigned — it appears only under the "Unassigned" row.
 4. Changing WO (a)'s Sales Representative afterward does NOT retroactively alter the invoice already created from it — the invoice stays credited to the rep snapshotted at invoice creation.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R6, S19-N2, S22-R3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S19-R6, S19-N2, S22-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -10564,7 +10752,8 @@
 3. On the WO, the selector renders the bound rep's name with an "(Inactive)" indicator so the current assignment stays visible — but that rep is NOT offered as a new selection in the list.
 4. Note for the tester: the product owner has ruled that the full word "Sales Representative" replaces the short "Sales Rep" everywhere. If the screen or file still shows "Sales Rep", mark this test Failed and report it as the pending rename — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S19-R7, S19-E1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S19-R7, S19-E1); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - waiting on an answer from the product owner
 </t>
         </is>
@@ -10618,7 +10807,8 @@
 2. A re-expand within the session does not necessarily re-fetch (the expansion state is session-preserved); no rep's details load before its first expand.
 3. When a rep's matching-invoice count is large, its detail rows are paginated per rep.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S6-R2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S6-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -10670,7 +10860,8 @@
 2. The returned rows arrive already ordered by the requested column and direction — the client does not re-sort locally.
 3. Invoice detail rows continue to load lazily per rep on expand, unaffected by the sort mechanism.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S11-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S11-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -10722,7 +10913,8 @@
 2. The totals cover EVERY matching non-reversed invoice across every rep, independent of which reps are expanded or how many detail rows are loaded.
 3. The on-screen grand Totals match the export's aggregate for the same filter set.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S10-R5).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S10-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -10775,7 +10967,8 @@
 2. A genuine server-side export failure produces NO file and shows the "Ooooops! An error occured" toast — never a malformed/partial file.
 3. An empty-but-loaded result still produces a valid file (header-row-only CSV / no-rows PDF).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-R2a, S14-N2, S14-E3).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-R2a, S14-N2, S14-E3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - this part of the report is not built yet
 </t>
         </is>
@@ -10829,7 +11022,8 @@
 3. A filter set just below the cap still generates a complete (possibly very large) PDF.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S14-E2).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S14-E2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8818)
 </t>
         </is>
@@ -10883,7 +11077,8 @@
 2. The dialog's "{Staff Name} is the sales representative on {N} customer{s}." headline matches the returned count.
 3. No deactivation is committed by the pre-check itself — cancelling leaves the staff member's active status unchanged.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Sales By Representative report specification version 15 (S13-R1, S13-R4).
+This is the expected behaviour as per epic SV-8582 and the Sales By Representative report specification version 16 (S13-R1, S13-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -10936,7 +11131,8 @@
 2. Under Parts there is an entry labeled Parts Velocity; Inventory Value also lives under Parts. The order of the two inside the Parts section is not fixed — do not fail the test on which of them comes first.
 3. Clicking it opens the Parts Velocity report.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-R1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S1-R1); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -10988,7 +11184,8 @@
 2. Report data loads automatically - you do not have to press anything to fetch it.
 3. Rows appear ranked by Demand, highest first (the default order).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-R2, S4-R6).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S1-R2, S4-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -11041,7 +11238,8 @@
 2. During a filter change, the loading indicator shows again.
 3. The rows already on screen are replaced only when the new data comes back - the table does not blank out and rebuild mid-request.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-R3).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S1-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -11095,7 +11293,8 @@
 2. The export downloads successfully — both opening the report and exporting it are allowed by the same ordinary reports access.
 3. Note for the tester: the specification allows ONE ordinary reports access for all six of these new reports and no per-report permission. If the build demands a separate report permission before this works, mark this Failed and report it — do not change the test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S1-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -11145,7 +11344,8 @@
           <t xml:space="preserve">1. The user cannot reach the Reports section.
 2. The Parts Velocity navigation entry is not shown (this is the Reports section's own access control, not a report-specific rule).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-N1).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S1-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -11199,7 +11399,8 @@
 3. The export downloads.
 4. Note for the tester: the specification allows ONE ordinary reports access for all six of these new reports and no per-report permission. If an extra Parts or Inventory reports permission does exist and switching it OFF blocks this report or its export, that is wrong - mark this Failed and report it. If a separate per-report permission is ever added on purpose in a later release, this test will be updated first, so treat that as a planned change and not as a bug.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-N2, S1-R4); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S1-N2, S1-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -11256,7 +11457,8 @@
 4. Both is an explicit selection returning inventory and Special Order rows together - a deliberate filter value, not the absence of a filter.
 5. Each selection immediately reloads the report limited to that type (no separate Apply step) - under Inventory every row's Type column reads Inventory; under Special Order every row's Type column reads Special Order; under Both, rows of both kinds appear.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R1, S3-R5); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R1, S3-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -11308,7 +11510,8 @@
 3. Selecting a non-custom option immediately reloads the report data.
 4. The named ranges use the application's standard shared calendar boundaries (the same boundaries every report's date picker uses).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023). Where the Parts Velocity report specification version 5 (S2-R2) says something different, the behaviour above follows Chris Ward's decision of 8/5/2026 instead, which is the authority - that decision is recorded in his answers, in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. Where the Parts Velocity report specification version 5 (S2-R2) says something different, his decision is the later word and is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -11362,7 +11565,8 @@
 3. With both valid dates selected, the data reloads for that range.
 4. A span wider than 366 days (counting both the start and end dates) is rejected - the selection is not applied.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R3).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -11416,7 +11620,8 @@
 3. With vendors selected, only parts supplied by any of the selected vendors are shown.
 4. Each change reloads the data from the server.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R4, S2-R5, S2-R10).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R4, S2-R5, S2-R10).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -11471,7 +11676,8 @@
 3. The description search returns rows whose description contains the word.
 4. Category and vendor names are NOT searched - use their dedicated filters instead (deliberate, to avoid false matches on common words).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R6).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -11525,7 +11731,8 @@
 2. After step 3 the part disappears - a part must satisfy EVERY active filter to appear (AND logic, not OR).
 3. After step 4 the part is listed again.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R7).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -11577,7 +11784,8 @@
 2. Only inventory parts stocked in ANY of the selected bins are shown.
 3. The filter allows more than one bin (multi-select).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R8).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -11629,7 +11837,8 @@
           <t xml:space="preserve">1. With any Bin filter active, ALL Special Order rows are excluded (they have no bin location).
 2. Special Order combined with any Bin filter yields an empty result showing the empty state - this is by design, not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R8); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -11687,7 +11896,8 @@
 5. The location scope cascades through every metric like the other filters.
 6. With 'All Locations' active you can tell which location each row's data belongs to — a location label or marking is shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R9); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R9); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -11737,7 +11947,8 @@
           <t xml:space="preserve">1. The server returns zero rows and the table shows the empty state.
 2. The empty-state label reads exactly: "Empty bays, endless possibilities. Get Going!" (the application's standard reports no-data label).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R11, S2-N1).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R11, S2-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -11791,7 +12002,8 @@
 2. The part with no vendor does not appear when any Vendor filter is active.
 3. The inventory part with no bin location does not appear when any Bin filter is active.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-E1, S2-E2, S2-E3).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-E1, S2-E2, S2-E3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -11842,7 +12054,8 @@
           <t xml:space="preserve">1. For the single-location user the Location filter is NOT shown at all — the report simply shows that one location's data.
 2. For the user with access to two or more locations the Location filter IS shown.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-E4). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-E4). Chris Ward confirmed this on 8/5/2026 in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -11897,16 +12110,14 @@
           <t xml:space="preserve">1. With more than one location in scope a Location column is shown as the LEFTMOST column, before Type.
 2. Each inventory row shows its own location's name (an inventory row is one part at one location).
 3. The merged Special Order row shows "Multiple", because it is summed across the selected locations.
-4. With a single location in scope the Location column is hidden.
+4. With only one location involved the Location column is not shown.
 5. Both downloads include the Location column in the same position it holds on screen (leftmost, before Type), with the same values — each inventory row's own location, and "Multiple" on the merged Special Order row.
 ---
-Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
-The Location column is not one of the columns in the column-selection control and you cannot switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
-Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
----
----
-This is the expected behaviour as per the Parts Velocity report specification version 5 (S2-R12, S3-R10, S7-R8, S6-R11), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. Parts Velocity is one of the reports where this has not been settled. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+---
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R12, S3-R10, S7-R8, S6-R11). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: version 5 added a summary and a change note saying it can be toggled there, while the requirement that governs the column still says it is not user-toggleable. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
+AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
 </t>
         </is>
       </c>
@@ -11957,7 +12168,8 @@
 2. Each row carries only that one location's On Hand, Min, and Max.
 3. On Hand / Min / Max are NEVER summed across locations.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R1a).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R1a).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -12010,7 +12222,8 @@
 2. Its movement and profitability values are the SUM of the per-location values.
 3. Its inventory-only columns (On Hand, Turns / Yr, Min, Max) show — (em-dash), because special-order parts are not stocked.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R1a).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R1a).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -12065,7 +12278,8 @@
 3. Rows with equal Demand keep inventory-before-special-order order.
 4. The Demand header shows the descending sort indicator - this initial order IS the active sort (it is what the remembered view saves until you click another header).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R2).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -12120,7 +12334,8 @@
 3. Null / — values are placed FIRST on ascending and LAST on descending.
 4. Every column is sortable; each header click re-fetches the data (server-resolved) and shows the first page of the re-sorted result; ties keep a stable order.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R3).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -12172,7 +12387,8 @@
 2. The Type column shows each row's kind as plain text (no badge or chip styling): "Inventory" or "Special Order".
 3. ALL columns - header and cell data, including numbers and money - are left-aligned on screen. (The exports right-align numerics instead: a deliberate export-only difference.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R4, S3-R5, S3-R8); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R4, S3-R5, S3-R8); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -12229,7 +12445,8 @@
 5. The icon is focusable and exposes the same text to assistive technology; activating it does NOT trigger a column sort.
 6. No other column header carries an info icon.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R6).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -12283,7 +12500,8 @@
 2. The full value shows on native hover (browser tooltip).
 3. Part # is NEVER truncated - on screen (and in the exports).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R7).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -12334,7 +12552,8 @@
           <t xml:space="preserve">1. On Hand, Turns / Yr, Min, and Max show — (em-dash) on special-order rows - always.
 2. The count metrics and money totals are NEVER null: Units Sold / Units Returned / Sold (WO) / Sold (Parts Sale) show 0.00, Demand shows 0, Revenue and Margin show $0.00.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R9, S5-R5).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R9, S5-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -12386,7 +12605,8 @@
 2. Part B DOES appear - a part with billed Revenue &gt; 0 is always kept even with no stock movement and no on-hand stock.
 3. (Special Order parts have no such rule: a never-requested special-order part simply produces no row.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-N1).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -12437,7 +12657,8 @@
           <t xml:space="preserve">1. The picker lists all 20 available columns, each with a toggle: Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
 2. No on-hand cost column is offered - the report computes one internally but it is never selectable and never displayed.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-R1, S4-R4, S5-R6).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S4-R1, S4-R4, S5-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -12485,12 +12706,11 @@
         <is>
           <t xml:space="preserve">1. With a single location in scope exactly these 14 columns show, in this left-to-right order: Type, Part #, Description, Category, Vendor, Units Sold, Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand.
 2. The other 6 columns start hidden: Units Returned, Sold (WO), Sold (Parts Sale), Turns / Yr, Min, Max.
-3. When more than one location is in scope the Location column shows as well, leftmost before Type — 15 columns. It is not one of the columns in the column-selection control and you cannot switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope. It is not part of the 14-column default set, so its presence is expected and is not a failure of this test.
-Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
----
----
-This is the expected behaviour as per the Parts Velocity report specification version 5 (S3-R10), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+3. When more than one location is in scope the Location column shows as well, leftmost before Type — 15 columns. Note for the tester: the written description is inconsistent about one point here. One part of it says the Location column is offered in the column-selection control and can be switched on and off; another part says it is never in that list and simply appears by itself whenever more than one location is involved. Parts Velocity is one of the reports where this has not been settled. The product owner has been asked which is right and has not answered yet, so do not raise a bug either way - record what you see and carry on. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx It is not part of the 14-column default set, so its presence is expected and is not a failure of this test.
+---
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R10). That specification is inconsistent about the one point of whether the Location column is offered in the column-selection control: version 5 added a summary and a change note saying it can be toggled there, while the requirement that governs the column still says it is not user-toggleable. Chris Ward has been asked which is right and has not answered, so neither reading is asserted here. The question is in the round-3 question sheet: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Questions-for-Chris-Ward_Report-Suite_Round-3_2026-08-05.xlsx
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
+AUTOMATION: HOLD - the written description says two different things about the Location column and the product owner has been asked
 </t>
         </is>
       </c>
@@ -12541,7 +12761,8 @@
 2. Columns always render in the fixed canonical left-to-right order regardless of the order they were toggled on (with the automatic Location column, when shown, sitting leftmost before Type): Type, Part #, Description, Category, Vendor, Units Sold, Units Returned, Sold (WO), Sold (Parts Sale), Unit Cost, Sell Price, Revenue, Margin, Margin %, Demand, Last Sale, On Hand, Turns/Yr, Min, Max.
 3. So Units Returned slots in right after Units Sold, Turns/Yr after On Hand, and Min before Max - not appended at the end.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-R4, S4-R5, S3-R10).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S4-R4, S4-R5, S3-R10).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -12594,7 +12815,8 @@
 3. The saved values take precedence over the first-visit defaults (This Year / Both / active location / 14 columns / Demand-descending).
 4. The same holds after a full page reload.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-R6, S1-R2).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S4-R6, S1-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -12645,7 +12867,8 @@
 2. That one setting falls back to its default (e.g. the location falls back to the active location); the other saved settings still restore normally.
 3. The report loads without an error.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-R6).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S4-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -12696,7 +12919,8 @@
           <t xml:space="preserve">1. User 2 sees user 1's saved view (Type = Special Order, Last Quarter, the saved columns and sort).
 2. This is by design: storage is per browser, not tied to the account - there is no per-account separation.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-R6).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S4-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -12748,7 +12972,8 @@
 2. The export produces a file containing only the header/metadata rows and no data columns.
 3. On the next visit the all-hidden selection is NOT restored - the report falls back to the default 14-column set (the saved column selection returns to the last NON-EMPTY selection; all-hidden is the exception).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S4-E1, S4-R6).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S4-E1, S4-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -12802,7 +13027,8 @@
 3. After step 3, Units Sold is UNCHANGED - part returns do not affect Units Sold (they feed Units Returned instead).
 4. Units Sold can be 0.00 or negative when reversals exceed sales.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R1, S5-R4).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R1, S5-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -12854,7 +13080,8 @@
 2. The reversed/voided sale is EXCLUDED from the total (net of reversals).
 3. Only requests on work orders at status Invoiced or Paid count; the window is anchored to the work-order date.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R2, S5-R4, S5-R4b).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R2, S5-R4, S5-R4b).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -12909,7 +13136,8 @@
 3. After step 3, it decreases by 2.00 - the column reflects the CURRENT state of return records (cancelled returns are excluded), not a snapshot.
 4. After step 4, Units Returned is UNCHANGED - invoice reversals are not returns (they affect Units Sold instead).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R3, S5-R4).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R3, S5-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -12965,7 +13193,8 @@
 4. Units Returned is independent of the work order's current invoice status.
 5. A part whose ONLY in-window event is a return (no sale, no stock, no revenue) produces no row at all - the rows of this report are built from sales and stock activity, so a return on its own does not create one.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R3).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -13019,7 +13248,8 @@
 3. Both are windowed by the WORK-ORDER date (its end date) - with the range moved off those dates, both drop out.
 4. Both workflows feed the report - a parts sale is a separate workflow from a service work order but counts fully.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -13075,7 +13305,8 @@
 4. Demand is the report's default ranking signal (a whole number, never null - 0 when none).
 5. A part whose single in-window sale is invoiced and then fully reversed shows Demand 1 with Units Sold 0.00 — the Demand count is not decremented, while the movement nets to zero.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4, S3-E1).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4, S3-E1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -13132,7 +13363,8 @@
 4. For a special-order part, the anchor is its most recent vendor-sourced invoiced/paid request.
 5. When the most recent sale is reversed, Last Sale re-anchors to the previous remaining sale (the day count grows accordingly); if no other sale remains it shows —.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4, S5-R5).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4, S5-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -13184,7 +13416,8 @@
 2. Min and Max show the stored minimum / maximum reorder thresholds for that location, as whole numbers (— when not set).
 3. Min and Max are READ-ONLY display columns - no edit control or slide-over opens; editing part attributes from this report is out of scope in this version.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4, S5-R5).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4, S5-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -13240,7 +13473,8 @@
 3. Part C shows a NEGATIVE Turns / Yr with a leading minus (because Units Sold can be negative).
 4. Special Order rows always show — (not applicable).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -13295,7 +13529,8 @@
 5. All five are computed from the RAW (unrounded) Revenue / COGS / billed-units totals and rounded ONCE at the end - not built from already-rounded intermediates.
 6. The same formulas apply to inventory and special-order rows (for special-order, from the vendor part requests).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4a).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4a).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: HOLD - this part of the report is not built yet
 </t>
         </is>
@@ -13348,7 +13583,8 @@
 2. This netting is consistent with inventory Units Sold, which already nets reversals via the stock add-back.
 3. A voided sale therefore inflates NO column.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4b, S5-R4a).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4b, S5-R4a).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -13403,7 +13639,8 @@
 3. Row 3: Unit Cost, Sell Price, and Margin % all show — together - which happens ONLY when both billed units ≤ 0 AND Revenue ≤ 0.
 4. The three triggers are independent: Unit Cost/Sell Price null on billed units ≤ 0; Margin % null on Revenue ≤ 0.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R4a, S3-R9).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R4a, S3-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -13456,7 +13693,8 @@
 4. Demand: whole number. Min, Max: whole numbers (— when null). Last Sale: 'N days' (42 days), — when null.
 5. Rounding is half AWAY from zero: 8.45% displays 8.5% and -8.45% displays -8.5% (a tie rounds up in magnitude); this applies to all money and one-decimal values.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R5, S5-R7).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R5, S5-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -13508,7 +13746,8 @@
 2. The special-order core part does NOT appear either.
 3. Parts flagged as a core are excluded from both result sets by design.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R1, S5-R2).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R1, S5-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -13562,7 +13801,8 @@
 2. Sold (WO) + Sold (Parts Sale) together DO equal the billed-units basis (work orders are only Service- or Parts-type) - but neither equals the movement-based Units Sold.
 3. On the special-order row, everything reconciles: Units Sold = Sold (WO) + Sold (Parts Sale) = billed units (they share the vendor-request quantity as one source).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R7).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -13616,7 +13856,8 @@
 3. The window is the whole-day span inclusive of BOTH the start and end dates, with a floor of 1 day - a single-day range (Today) computes normally (Window = 1 for the Turns / Yr divisor).
 4. Last Sale is not windowed at all (all-time).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R7).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -13673,7 +13914,8 @@
 3. On Hand has gone down by exactly 2.50 from what it was before the sale.
 4. No value anywhere on the row has been quietly rounded to a whole number.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S5-R1, S5-R5).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S5-R1, S5-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -13723,7 +13965,8 @@
           <t xml:space="preserve">1. The ⋯ overflow button sits leftmost in the toolbar's action cluster.
 2. The menu holds exactly two items, in this order: Download (PDF), then Download (CSV).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R1).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -13775,7 +14018,8 @@
 2. The exported rows match what the on-screen grid was showing.
 3. Each file (PDF and CSV) carries a "Locations:" line naming the location(s) the report was scoped to.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R2, S6-R11); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R2, S6-R11); where the wording of that specification differs, the behaviour above follows Chris Ward's later decision, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true, which is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -13827,7 +14071,8 @@
 2. Columns appear in the CANONICAL order (the fixed on-screen order) - the re-enabled Units Returned sits right after Units Sold, NOT appended at the end.
 3. The export mirrors the visible grid.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R3, S4-R4).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R3, S4-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -13880,7 +14125,8 @@
 2. Every column's sort is honored in the export - including Min and Max.
 3. The export renders the EXACT server order, including null placement (nulls first on ascending, last on descending) - the export and the on-screen grid match; there is no on-screen-vs-export null-sorting difference.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R4, S3-R3).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R4, S3-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -13935,7 +14181,8 @@
 5. With a logo uploaded, that logo appears. If a logo is set but fails to load, the built-in ShopView logo is used instead. If no logo is uploaded at all, NO logo is printed and the text fills the space. The CSV never includes a logo.
 Note for the tester: on this build a report with no uploaded logo still prints the built-in ShopView logo. The product owner has decided it should print no logo at all, so record what you see; the change is with the developers.
 ---
-This is the expected behaviour as per Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true. It does NOT match the build tested on 8/4/2026 (build v3.4.1-3d03023) - that change is with the developers - and where the Parts Velocity report specification version 5 (S6-R5, S6-R6) differs, his decision is the authority.
+This is the expected behaviour as per epic SV-8582 and Chris Ward's decision of 8/5/2026, recorded in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true; where the Parts Velocity report specification version 5 (S6-R5, S6-R6) differs, his decision is the authority.
+Last checked against build v3.4.1-3d03023 on 8/4/2026, which does not yet match it - that change is with the developers.
 AUTOMATION: READY
 </t>
         </is>
@@ -13987,7 +14234,8 @@
 2. The CSV carries the FULL, untruncated Description / Category / Vendor values (unlike the PDF's 18-character cut).
 3. Last Sale is a raw integer in the CSV (e.g. 42) - the 'N days' wording is PDF/on-screen only.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R5, S6-R6, S6-R8).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R5, S6-R6, S6-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -14038,7 +14286,8 @@
           <t xml:space="preserve">1. A null value renders as — (em-dash) in BOTH the CSV and the PDF, in every nullable field: Unit Cost, Sell Price, Margin %, On Hand, Turns / Yr, Last Sale, Min, Max.
 2. Revenue, Margin, and the count metrics are never null in the exports either ($0.00 / 0.00 / 0).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R7, S6-R8, S3-R9).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R7, S6-R8, S3-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -14091,7 +14340,8 @@
 4. This is a deliberate export-only treatment - the on-screen table is all-left-aligned; the difference is documented, not a defect.
 5. The CSV is plain data — the alignment assertions apply to the PDF only; how a spreadsheet displays the CSV is not part of this test.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R10, S3-R8).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R10, S3-R8).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -14144,7 +14394,8 @@
 2. An error toast is shown on failure; when the server provides a message, that server message is shown.
 3. Otherwise the failure toast reads exactly: "Failed to export velocity report (csv)" or "Failed to export velocity report (pdf)" — lowercase (csv)/(pdf); the success/failure casing mix is the specified wording (not a bug).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S6-R9, S6-N1).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S6-R9, S6-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -14199,7 +14450,8 @@
 3. After narrowing below the cap, the downloads work again.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (Story 6 exports).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (Story 6 exports).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8818)
 </t>
         </is>
@@ -14255,7 +14507,8 @@
 4. Note for the tester: a very large view is refused politely with "This report is too large to export. Narrow the date range or filters, then try again." — that message is expected and is NOT this failure. This test is about a medium-sized view where the CSV works but the PDF errors.
 Known issue: the product does not currently do this. It has been filed for a fix here: https://shopview.atlassian.net/browse/SV-8818
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (Story 6 exports).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (Story 6 exports).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY - EXPECT FAIL (SV-8818)
 </t>
         </is>
@@ -14306,7 +14559,8 @@
 2. There is NO card border-radius - the table runs edge to edge.
 3. The layout matches the application's other reports.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S7-R1).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S7-R1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -14361,7 +14615,8 @@
 4. It all looks the same as the other reports in the suite: put another report side by side and nothing should look out of place.
 5. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether the spacing and the dividing line look right and consistent with the other reports, and only report it if something looks obviously off. (The exact figures behind this - 32px/24px toolbar padding, a 1px header border, 2rem edge padding - are design-token values the design and engineering team check with their own tooling, not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S7-R2, S7-R3, S7-R4, S7-R5).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S7-R2, S7-R3, S7-R4, S7-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -14413,7 +14668,8 @@
 2. In BOTH light mode and dark mode the grey ⓘ info icon is clearly visible against the cell behind it - you can see it at a glance without leaning in, and it does not disappear into the background.
 3. Note for the tester: you do not need to measure anything and you do not need any tool. Just say whether you can see the icon easily in both modes. Only report it if the icon is hard to see. (The design rule behind this is a minimum 3:1 contrast ratio, which the design and engineering team check with a contrast tool - not by hand.)
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S7-R6).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S7-R6).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -14466,7 +14722,8 @@
 2. Paging is resolved on the server: moving to another page issues a fresh backend request for that page.
 3. This keeps the report responsive at scale (organizations can carry 50-60k parts, multiplied across locations).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R10).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R10).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -14518,7 +14775,8 @@
 2. There is no client-side-only narrowing - every filter or search change re-queries the server.
 3. Each change returns the FIRST page of the new result set.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S2-R10).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S2-R10).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -14571,7 +14829,8 @@
 2. Null values are placed FIRST on ascending and LAST on descending - as a server sort semantic, so the same order appears on screen and in the exports.
 3. Ties keep a stable order (no explicit secondary key).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S3-R3).
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S3-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -14625,7 +14884,8 @@
 3. Both requests succeed with only the ordinary reports access turned on - nothing else had to be enabled.
 4. Note for the tester: if the back end refuses either request for a user who has the ordinary reports access, mark this Failed and report it. If an extra Parts or Inventory reports permission exists in the system it must not change these results - the specification allows no per-report permission at all. A per-report permission added on purpose in a later release is a planned change, not a bug, and this test will be updated first.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Parts Velocity report specification version 5 (S1-R4, S1-N2); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Parts Velocity report specification version 5 (S1-R4, S1-N2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -14683,7 +14943,8 @@
 3. The quantity behind the QuickBooks amount matches the Units Sold value on the report (2.50) — the two systems agree.
 4. No second or correcting journal entry is created to patch up a wrong amount.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and this point is not covered by any of the six report specifications — it comes from the engineering technical plan.
+This is the expected behaviour as per epic SV-8582 and the engineering technical plan; this point is not covered by any of the six report specifications.
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -14736,7 +14997,8 @@
 2. Clicking it opens the report.
 3. The entry sits BELOW the pre-existing report links — Sales, Technician Efficiency, Advisor Analysis, Shop Efficiency — the new reports are added below those items without moving or disturbing them.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R1).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -14787,7 +15049,8 @@
           <t xml:space="preserve">1. Technician A has exactly ONE row.
 2. Technician B has NO row - only technicians with clocked time in the selected range at the selected location(s) appear.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R2).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -14838,7 +15101,8 @@
 2. Because a range never extends past now, the current-month default effectively shows the month to date.
 3. The location filter defaults to the user's currently active location (the one in the application's global location switcher).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R3, S1-R6, S9-R2).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R3, S1-R6, S9-R2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -14890,7 +15154,8 @@
 2. A valid Custom range applies normally.
 3. A Custom span wider than 366 days (matching the largest preset) is rejected - it cannot be applied.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R4, S1-R5).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R4, S1-R5).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -14942,7 +15207,8 @@
 2. The existing rows are replaced only when the new data returns.
 3. The toolbar remains interactive during the load.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R10).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R10).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -14997,7 +15263,8 @@
 3. EVERY record is day-grouped and windowed in a SINGLE report-level time zone - the active workplace's - regardless of the location where it was clocked (a record's day, the current-month boundary, and the midnight split all use that one zone).
 4. This matches the Timesheet Activities report's single-time-zone grouping.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-R7).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -15046,7 +15313,8 @@
         <is>
           <t xml:space="preserve">1. The Technician Utilization report does NOT appear in the navigation.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-N1); where the wording of that specification differs, the behaviour above follows a later product decision, which is the authority.
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-N1).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -15099,7 +15367,8 @@
 2. The Summary row is hidden.
 3. Clearing every technician shows the SAME message and hides the Summary row — this version does not use distinct copy for genuinely-no-data vs a cleared filter.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S1-N2, S3-N1, S5-N1, S9-N2).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S1-N2, S3-N1, S5-N1, S9-N2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -15154,15 +15423,14 @@
 3. WO Hours = time clocked directly to work orders; Internal Hours = time clocked to internal, non-billable activities.
 4. Internal Hours includes ALL internal time - including hours at a location with no configured labor rate.
 5. Hours show two decimal places with NO thousands separator (e.g. "107.70"), rounded from the unrounded hours using round-half-up (a tie rounds away from zero - 0.005 → 0.01).
-6. When more than one location is in scope the Location column also appears, leftmost before Technician.
----
-Note for the tester: on this build the column does not yet behave this way - record what you see and carry on. The change is with the developers.
-The Location column is never listed in the column-selection control and you cannot switch it on or off: it appears by itself whenever more than one location is in scope, and is hidden whenever a single location is in scope.
-Note for the tester: the product owner has been asked to confirm this one point and has not answered yet, so do not raise a bug either way — record what you see. The question is in Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx: https://raw.githubusercontent.com/bilalmuzamil-sketch/Manual-test-Cases/claude/slack-session-0sxnd9/build/report-suite/rulings-2026-08-05/Follow-up-Question-for-Chris-Ward_2026-08-05.xlsx
----
----
-This is the expected behaviour as per the Technician Utilization report specification version 5 (S2-R1, S2-R2, S2-R3, S2-R4, S2-R5, S9-R9), and as per the build tested on 8/4/2026 (build v3.4.1-3d03023). The product owner's answer of 8/5/2026 in this file reads both ways on the one point about the Location column, so it has NOT been treated as overriding the specification and he has been asked again: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
-AUTOMATION: HOLD - waiting on one answer from the product owner about the Location column
+6. If your own account can reach more than one location, a Location column also appears, leftmost before Technician, and it is already switched on when you arrive.
+---
+Note for the tester: if the Location column does not behave this way on the build, mark this test Failed and report it - do not change the test.
+Location is one of the columns you can switch on and off in the column-selection control, but only if your own account can reach more than one location: for you it is already switched on when you arrive, and you can switch it off. Someone whose account can reach only one location never sees the column and it is not offered to them in that list.
+---
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R1, S2-R2, S2-R3, S2-R4, S2-R5, S9-R9). Version 6 of that specification, published on 5 August 2026, is what settles the one point about the Location column: it now states in both of its own requirements that the column belongs to anyone whose account can reach more than one location and can be switched on and off in the column-selection control. Chris Ward asked for that change in his answers in this file: https://docs.google.com/spreadsheets/d/1x8cuYJlFsDHalVZZTh156_ZCq2gcOaGY/edit?usp=sharing&amp;ouid=106388879401921597782&amp;rtpof=true&amp;sd=true
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
+AUTOMATION: READY
 </t>
         </is>
       </c>
@@ -15211,7 +15479,8 @@
           <t xml:space="preserve">1. Utilization % = work-order hours as a percentage of total clocked hours, computed from the unrounded hours (not from the already-rounded displays).
 2. It shows one decimal place followed by a percent sign, rounded round-half-up (66.65% → 66.7%).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R6, S2-R7).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R6, S2-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -15263,7 +15532,8 @@
 2. No row shows more than 100% - work-order hours are always part of total clocked hours.
 3. The "—" (undefined, total = 0) state is unreachable on a rendered technician or day row, because only technicians with clocked time get rows.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E1, S2-R7).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-E1, S2-R7).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -15317,7 +15587,8 @@
 2. In a single-location view it is simply that one location's rate × the technician's internal hours.
 3. The value shows as dollars with two decimals and commas between thousands (e.g. "$1,234.50").
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R8, S2-R9).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R8, S2-R9).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -15372,7 +15643,8 @@
 3. NO column header other than Est. Lost Labor shows the information icon.
 4. Est. Lost Labor can be turned OFF in the Column Selection control; when it is off the column, its bold styling and its information icon are all absent, and the report still works normally.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R10, S2-R11, S8-R4, S8-R6, S8-R7, S8-N1, S10-R3).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R10, S2-R11, S8-R4, S8-R6, S8-R7, S8-N1, S10-R3).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -15424,7 +15696,8 @@
 2. Technician B also shows "$0.00" - a configured rate of exactly $0.00 is a KNOWN rate that values the hours at $0.00, not "—".
 3. "$0.00" means 'the rate is known and there is nothing (or $0) to value' - a different state from "—" ('the rate is unknown').
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E2).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-E2).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -15476,7 +15749,8 @@
 2. The "—" cell carries the assistive-technology label "No default labor rate configured" (distinguishing it from "$0.00", which reads as its dollar value).
 3. The technician's Internal Hours column still shows all the internal hours (they are counted even though they cannot be valued).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E3, S8-R11, S2-R4).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-E3, S8-R11, S2-R4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -15528,7 +15802,8 @@
 2. The amount shows as a normal "$X.XX" with NO partial-value indicator in this version - so the row's Est. Lost Labor values fewer hours than its Internal Hours column shows.
 3. This is a documented known limitation (a partial-value indicator is a possible follow-up) - expected behavior, not a defect.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-E4).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-E4).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -15581,7 +15856,8 @@
 2. The Technician header shows the ascending sort indicator.
 3. The active sort header exposes its state to assistive technology (aria-sort = ascending on the Technician header; none on the others).
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R12, S8-R8, S8-R10).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R12, S8-R8, S8-R10).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -15637,7 +15913,8 @@
 4. Sorting is applied on screen to the loaded rows - NO reload/server request happens.
 5. Technicians tied in the sorted column are ordered by Technician name A to Z; two technicians sharing the same display name keep a stable order between renders.
 ---
-This is the expected behaviour as per the build tested on 8/4/2026 (build v3.4.1-3d03023), and as per the Technician Utilization report specification version 5 (S2-R13, S2-R14).
+This is the expected behaviour as per epic SV-8582 and the Technician Utilization report specification version 6 (S2-R13, S2-R14).
+Last checked against build v3.4.1-3d03023 on 8/4/2026.
 AUTOMATION: READY
 </t>
         </is>
@@ -15688,7 +15965,8 @@
           <t xml:space="preserve">1. After the reload, the rows are back to Technician name A to Z (the sort reset).
 2. On the return visit, the sort is again Technician A to Z - sort is NOT persisted (unlike th